--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -25,7 +25,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-07T04:17:45.096Z</t>
+    <t>2026-07-07T04:26:22.332Z</t>
   </si>
   <si>
     <t>Open Trades</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -25,7 +25,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-07T04:26:22.332Z</t>
+    <t>2026-07-07T04:34:02.981Z</t>
   </si>
   <si>
     <t>Open Trades</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -25,7 +25,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-07T04:34:02.981Z</t>
+    <t>2026-07-07T04:37:00.541Z</t>
   </si>
   <si>
     <t>Open Trades</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -25,7 +25,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-07T04:37:00.541Z</t>
+    <t>2026-07-07T04:39:30.899Z</t>
   </si>
   <si>
     <t>Open Trades</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -25,7 +25,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-07T04:39:30.899Z</t>
+    <t>2026-07-07T04:52:34.716Z</t>
   </si>
   <si>
     <t>Open Trades</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -25,7 +25,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-07T04:52:34.716Z</t>
+    <t>2026-07-07T04:54:55.494Z</t>
   </si>
   <si>
     <t>Open Trades</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="53">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-07T04:54:55.494Z</t>
+    <t>2026-07-07T18:44:43.240Z</t>
   </si>
   <si>
     <t>Open Trades</t>
@@ -79,10 +79,100 @@
     <t>Holding Days</t>
   </si>
   <si>
+    <t>Setup Score</t>
+  </si>
+  <si>
+    <t>Sector Breadth</t>
+  </si>
+  <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>55D Breakout</t>
+  </si>
+  <si>
+    <t>Volume Ratio</t>
+  </si>
+  <si>
+    <t>Risk To ST %</t>
+  </si>
+  <si>
+    <t>Previous Low</t>
+  </si>
+  <si>
+    <t>2 Candle Low</t>
+  </si>
+  <si>
+    <t>4 Candle Low</t>
+  </si>
+  <si>
     <t>Entry Reason</t>
   </si>
   <si>
     <t>Exit Reason</t>
+  </si>
+  <si>
+    <t>Default Nifty 500</t>
+  </si>
+  <si>
+    <t>CUB</t>
+  </si>
+  <si>
+    <t>City Union Bank Ltd.</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>41.58% (42/101)</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Weekly RSI 64.23 is above 50. Daily RSI 73.78 is above 50. Weekly RS 4.9% is above 0. Daily long RS55 10.0% is above 0. Daily short RS21 17.3% is above 0. Daily close 224.69 is above Supertrend(10, 3) 198.54. Price action strength: close crossed 55-day high 220.24. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA.</t>
+  </si>
+  <si>
+    <t>SHREECEM</t>
+  </si>
+  <si>
+    <t>Shree Cement Ltd.</t>
+  </si>
+  <si>
+    <t>18.18% (2/11)</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Weekly RSI 55.89 is above 50. Daily RSI 65.39 is above 50. Weekly RS 1.4% is above 0. Daily long RS55 1.9% is above 0. Daily short RS21 6.0% is above 0. Daily close 26630.00 is above Supertrend(10, 3) 25006.27. RS trend strength: weekly RS and daily RS55 are rising. Risk reference: close is 6.10% above daily Supertrend.</t>
+  </si>
+  <si>
+    <t>CANFINHOME</t>
+  </si>
+  <si>
+    <t>Can Fin Homes Ltd.</t>
+  </si>
+  <si>
+    <t>Weekly RSI 60.24 is above 50. Daily RSI 66.02 is above 50. Weekly RS 3.4% is above 0. Daily long RS55 3.0% is above 0. Daily short RS21 9.0% is above 0. Daily close 918.80 is above Supertrend(10, 3) 836.75. Price action strength: close is within 15% of 52-week high 971.50. RS trend strength: weekly RS and daily RS55 are rising.</t>
+  </si>
+  <si>
+    <t>CONCORDBIO</t>
+  </si>
+  <si>
+    <t>Concord Biotech Ltd.</t>
+  </si>
+  <si>
+    <t>61.22% (30/49)</t>
+  </si>
+  <si>
+    <t>Weekly RSI 52.76 is above 50. Daily RSI 53.60 is above 50. Weekly RS 7.8% is above 0. Daily long RS55 17.4% is above 0. Daily short RS21 1.7% is above 0. Daily close 1283.60 is above Supertrend(10, 3) 1205.14. RS trend strength: weekly RS and daily RS55 are rising. Risk reference: close is 6.11% above daily Supertrend. Sector breadth strong: Healthcare has 30/49 stocks (61.22%) passing daily strength.</t>
   </si>
 </sst>
 </file>
@@ -497,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -532,7 +622,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -544,11 +634,13 @@
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="15" width="54" customWidth="1"/>
+    <col min="13" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="22" width="14" customWidth="1"/>
+    <col min="23" max="24" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -594,9 +686,332 @@
       <c r="O1" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2">
+        <v>224.69</v>
+      </c>
+      <c r="G2">
+        <v>445</v>
+      </c>
+      <c r="H2">
+        <v>99987.05</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2">
+        <v>8</v>
+      </c>
+      <c r="O2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2">
+        <v>0.83</v>
+      </c>
+      <c r="S2">
+        <v>11.64</v>
+      </c>
+      <c r="T2">
+        <v>215.67</v>
+      </c>
+      <c r="U2">
+        <v>214.53</v>
+      </c>
+      <c r="V2">
+        <v>202.5</v>
+      </c>
+      <c r="W2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3">
+        <v>26630</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>79890</v>
+      </c>
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3">
+        <v>6</v>
+      </c>
+      <c r="O3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3">
+        <v>0.27</v>
+      </c>
+      <c r="S3">
+        <v>6.1</v>
+      </c>
+      <c r="T3">
+        <v>26345</v>
+      </c>
+      <c r="U3">
+        <v>25965</v>
+      </c>
+      <c r="V3">
+        <v>25055</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4">
+        <v>918.8</v>
+      </c>
+      <c r="G4">
+        <v>108</v>
+      </c>
+      <c r="H4">
+        <v>99230.4</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4">
+        <v>6</v>
+      </c>
+      <c r="O4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>44</v>
+      </c>
+      <c r="R4">
+        <v>1.23</v>
+      </c>
+      <c r="S4">
+        <v>8.93</v>
+      </c>
+      <c r="T4">
+        <v>879.1</v>
+      </c>
+      <c r="U4">
+        <v>878.3</v>
+      </c>
+      <c r="V4">
+        <v>845.65</v>
+      </c>
+      <c r="W4" t="s">
+        <v>48</v>
+      </c>
+      <c r="X4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5">
+        <v>1283.6</v>
+      </c>
+      <c r="G5">
+        <v>77</v>
+      </c>
+      <c r="H5">
+        <v>98837.2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5">
+        <v>0.24</v>
+      </c>
+      <c r="S5">
+        <v>6.11</v>
+      </c>
+      <c r="T5">
+        <v>1260</v>
+      </c>
+      <c r="U5">
+        <v>1260</v>
+      </c>
+      <c r="V5">
+        <v>1260</v>
+      </c>
+      <c r="W5" t="s">
+        <v>52</v>
+      </c>
+      <c r="X5" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:X1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -604,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -616,11 +1031,13 @@
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="15" width="54" customWidth="1"/>
+    <col min="13" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="22" width="14" customWidth="1"/>
+    <col min="23" max="24" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -666,9 +1083,332 @@
       <c r="O1" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2">
+        <v>224.69</v>
+      </c>
+      <c r="G2">
+        <v>445</v>
+      </c>
+      <c r="H2">
+        <v>99987.05</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2">
+        <v>8</v>
+      </c>
+      <c r="O2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2">
+        <v>0.83</v>
+      </c>
+      <c r="S2">
+        <v>11.64</v>
+      </c>
+      <c r="T2">
+        <v>215.67</v>
+      </c>
+      <c r="U2">
+        <v>214.53</v>
+      </c>
+      <c r="V2">
+        <v>202.5</v>
+      </c>
+      <c r="W2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3">
+        <v>26630</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>79890</v>
+      </c>
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3">
+        <v>6</v>
+      </c>
+      <c r="O3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3">
+        <v>0.27</v>
+      </c>
+      <c r="S3">
+        <v>6.1</v>
+      </c>
+      <c r="T3">
+        <v>26345</v>
+      </c>
+      <c r="U3">
+        <v>25965</v>
+      </c>
+      <c r="V3">
+        <v>25055</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4">
+        <v>918.8</v>
+      </c>
+      <c r="G4">
+        <v>108</v>
+      </c>
+      <c r="H4">
+        <v>99230.4</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4">
+        <v>6</v>
+      </c>
+      <c r="O4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>44</v>
+      </c>
+      <c r="R4">
+        <v>1.23</v>
+      </c>
+      <c r="S4">
+        <v>8.93</v>
+      </c>
+      <c r="T4">
+        <v>879.1</v>
+      </c>
+      <c r="U4">
+        <v>878.3</v>
+      </c>
+      <c r="V4">
+        <v>845.65</v>
+      </c>
+      <c r="W4" t="s">
+        <v>48</v>
+      </c>
+      <c r="X4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5">
+        <v>1283.6</v>
+      </c>
+      <c r="G5">
+        <v>77</v>
+      </c>
+      <c r="H5">
+        <v>98837.2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5">
+        <v>0.24</v>
+      </c>
+      <c r="S5">
+        <v>6.11</v>
+      </c>
+      <c r="T5">
+        <v>1260</v>
+      </c>
+      <c r="U5">
+        <v>1260</v>
+      </c>
+      <c r="V5">
+        <v>1260</v>
+      </c>
+      <c r="W5" t="s">
+        <v>52</v>
+      </c>
+      <c r="X5" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:X1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -676,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -688,11 +1428,13 @@
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="15" width="54" customWidth="1"/>
+    <col min="13" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="22" width="14" customWidth="1"/>
+    <col min="23" max="24" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -738,9 +1480,36 @@
       <c r="O1" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:X1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -25,7 +25,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-07T18:44:43.240Z</t>
+    <t>2026-07-07T18:48:17.090Z</t>
   </si>
   <si>
     <t>Open Trades</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="80">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-07T18:48:17.090Z</t>
+    <t>2026-07-08T05:38:51.946Z</t>
   </si>
   <si>
     <t>Open Trades</t>
@@ -115,27 +115,99 @@
     <t>Default Nifty 500</t>
   </si>
   <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>Bajaj Finance Ltd.</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>44.55% (45/101)</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Weekly RSI 62.81 is above 50. Daily RSI 75.57 is above 50. Weekly RS 1.5% is above 0. Daily long RS55 9.5% is above 0. Daily short RS21 13.6% is above 0. Daily close 1042.50 is above Supertrend(10, 3) 969.01. Price action strength: close crossed 55-day high 1040.20. RS trend strength: weekly RS and daily RS55 are rising.</t>
+  </si>
+  <si>
+    <t>EXIDEIND</t>
+  </si>
+  <si>
+    <t>Exide Industries Ltd.</t>
+  </si>
+  <si>
+    <t>31.58% (12/38)</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Weekly RSI 65.72 is above 50. Daily RSI 65.00 is above 50. Weekly RS 22.8% is above 0. Daily long RS55 22.7% is above 0. Daily short RS21 1.9% is above 0. Daily close 414.50 is above Supertrend(10, 3) 383.35. Price action strength: close is within 15% of 52-week high 431.00. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA.</t>
+  </si>
+  <si>
+    <t>NAUKRI</t>
+  </si>
+  <si>
+    <t>Info Edge (India) Ltd.</t>
+  </si>
+  <si>
+    <t>41.38% (12/29)</t>
+  </si>
+  <si>
+    <t>Weekly RSI 59.34 is above 50. Daily RSI 76.37 is above 50. Weekly RS 1.4% is above 0. Daily long RS55 6.1% is above 0. Daily short RS21 10.1% is above 0. Daily close 1159.45 is above Supertrend(10, 3) 976.52. Price action strength: close crossed 55-day high 1080.90. Volume shocker: latest volume is 7.84x the 50-day average. RS trend strength: weekly RS and daily RS55 are rising.</t>
+  </si>
+  <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
+    <t>Eternal Ltd.</t>
+  </si>
+  <si>
+    <t>Weekly RSI 59.60 is above 50. Daily RSI 75.20 is above 50. Weekly RS 1.2% is above 0. Daily long RS55 10.0% is above 0. Daily short RS21 10.6% is above 0. Daily close 289.40 is above Supertrend(10, 3) 264.96. Price action strength: close crossed 55-day high 287.80. RS trend strength: weekly RS and daily RS55 are rising.</t>
+  </si>
+  <si>
+    <t>RITES</t>
+  </si>
+  <si>
+    <t>RITES Ltd.</t>
+  </si>
+  <si>
+    <t>23.08% (3/13)</t>
+  </si>
+  <si>
+    <t>Weekly RSI 58.43 is above 50. Daily RSI 65.71 is above 50. Weekly RS 7.4% is above 0. Daily long RS55 5.4% is above 0. Daily short RS21 9.7% is above 0. Daily close 235.43 is above Supertrend(10, 3) 205.19. Volume shocker: latest volume is 36.09x the 50-day average. RS trend strength: weekly RS and daily RS55 are rising.</t>
+  </si>
+  <si>
+    <t>LICI</t>
+  </si>
+  <si>
+    <t>Life Insurance Corporation of India</t>
+  </si>
+  <si>
+    <t>Weekly RSI 56.32 is above 50. Daily RSI 60.77 is above 50. Weekly RS 0.7% is above 0. Daily long RS55 4.2% is above 0. Daily short RS21 4.5% is above 0. Daily close 435.40 is above Supertrend(10, 3) 411.00. Price action strength: close is within 15% of 52-week high 485.48. RS trend strength: daily RS55 is rising. Risk reference: close is 5.60% above daily Supertrend.</t>
+  </si>
+  <si>
     <t>CUB</t>
   </si>
   <si>
     <t>City Union Bank Ltd.</t>
   </si>
   <si>
-    <t>OPEN</t>
-  </si>
-  <si>
     <t>2026-07-06</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>41.58% (42/101)</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>Weekly RSI 64.23 is above 50. Daily RSI 73.78 is above 50. Weekly RS 4.9% is above 0. Daily long RS55 10.0% is above 0. Daily short RS21 17.3% is above 0. Daily close 224.69 is above Supertrend(10, 3) 198.54. Price action strength: close crossed 55-day high 220.24. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA.</t>
   </si>
   <si>
@@ -148,9 +220,6 @@
     <t>18.18% (2/11)</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Weekly RSI 55.89 is above 50. Daily RSI 65.39 is above 50. Weekly RS 1.4% is above 0. Daily long RS55 1.9% is above 0. Daily short RS21 6.0% is above 0. Daily close 26630.00 is above Supertrend(10, 3) 25006.27. RS trend strength: weekly RS and daily RS55 are rising. Risk reference: close is 6.10% above daily Supertrend.</t>
   </si>
   <si>
@@ -173,6 +242,18 @@
   </si>
   <si>
     <t>Weekly RSI 52.76 is above 50. Daily RSI 53.60 is above 50. Weekly RS 7.8% is above 0. Daily long RS55 17.4% is above 0. Daily short RS21 1.7% is above 0. Daily close 1283.60 is above Supertrend(10, 3) 1205.14. RS trend strength: weekly RS and daily RS55 are rising. Risk reference: close is 6.11% above daily Supertrend. Sector breadth strong: Healthcare has 30/49 stocks (61.22%) passing daily strength.</t>
+  </si>
+  <si>
+    <t>3MINDIA</t>
+  </si>
+  <si>
+    <t>3M India Ltd.</t>
+  </si>
+  <si>
+    <t>66.67% (2/3)</t>
+  </si>
+  <si>
+    <t>Weekly RSI 58.25 is above 50. Daily RSI 71.19 is above 50. Weekly RS 0.0% is above 0. Daily long RS55 9.4% is above 0. Daily short RS21 5.5% is above 0. Daily close 35210.00 is above Supertrend(10, 3) 32485.81. Price action strength: close is within 15% of 52-week high 38030.00. RS trend strength: weekly RS and daily RS55 are rising.</t>
   </si>
 </sst>
 </file>
@@ -587,7 +668,7 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -622,7 +703,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -731,13 +812,13 @@
         <v>36</v>
       </c>
       <c r="F2">
-        <v>224.69</v>
+        <v>1042.5</v>
       </c>
       <c r="G2">
-        <v>445</v>
+        <v>95</v>
       </c>
       <c r="H2">
-        <v>99987.05</v>
+        <v>99037.5</v>
       </c>
       <c r="I2" t="s">
         <v>37</v>
@@ -755,7 +836,7 @@
         <v>37</v>
       </c>
       <c r="N2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O2" t="s">
         <v>38</v>
@@ -767,19 +848,19 @@
         <v>39</v>
       </c>
       <c r="R2">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>11.64</v>
+        <v>7.05</v>
       </c>
       <c r="T2">
-        <v>215.67</v>
+        <v>1024.8</v>
       </c>
       <c r="U2">
-        <v>214.53</v>
+        <v>1017.6</v>
       </c>
       <c r="V2">
-        <v>202.5</v>
+        <v>993.4</v>
       </c>
       <c r="W2" t="s">
         <v>40</v>
@@ -805,13 +886,13 @@
         <v>36</v>
       </c>
       <c r="F3">
-        <v>26630</v>
+        <v>414.5</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>241</v>
       </c>
       <c r="H3">
-        <v>79890</v>
+        <v>99894.5</v>
       </c>
       <c r="I3" t="s">
         <v>37</v>
@@ -829,31 +910,31 @@
         <v>37</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O3" t="s">
         <v>43</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="Q3" t="s">
         <v>44</v>
       </c>
       <c r="R3">
-        <v>0.27</v>
+        <v>0.76</v>
       </c>
       <c r="S3">
-        <v>6.1</v>
+        <v>7.52</v>
       </c>
       <c r="T3">
-        <v>26345</v>
+        <v>413.5</v>
       </c>
       <c r="U3">
-        <v>25965</v>
+        <v>413.5</v>
       </c>
       <c r="V3">
-        <v>25055</v>
+        <v>385.8</v>
       </c>
       <c r="W3" t="s">
         <v>45</v>
@@ -879,13 +960,13 @@
         <v>36</v>
       </c>
       <c r="F4">
-        <v>918.8</v>
+        <v>1159.45</v>
       </c>
       <c r="G4">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="H4">
-        <v>99230.4</v>
+        <v>99712.7</v>
       </c>
       <c r="I4" t="s">
         <v>37</v>
@@ -906,31 +987,31 @@
         <v>6</v>
       </c>
       <c r="O4" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="P4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" t="s">
         <v>39</v>
       </c>
-      <c r="Q4" t="s">
-        <v>44</v>
-      </c>
       <c r="R4">
-        <v>1.23</v>
+        <v>7.84</v>
       </c>
       <c r="S4">
-        <v>8.93</v>
+        <v>15.78</v>
       </c>
       <c r="T4">
-        <v>879.1</v>
+        <v>1012.8</v>
       </c>
       <c r="U4">
-        <v>878.3</v>
+        <v>1012.8</v>
       </c>
       <c r="V4">
-        <v>845.65</v>
+        <v>974.6</v>
       </c>
       <c r="W4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X4" t="s">
         <v>37</v>
@@ -941,10 +1022,10 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
         <v>35</v>
@@ -953,13 +1034,13 @@
         <v>36</v>
       </c>
       <c r="F5">
-        <v>1283.6</v>
+        <v>289.4</v>
       </c>
       <c r="G5">
-        <v>77</v>
+        <v>345</v>
       </c>
       <c r="H5">
-        <v>98837.2</v>
+        <v>99843</v>
       </c>
       <c r="I5" t="s">
         <v>37</v>
@@ -977,36 +1058,554 @@
         <v>37</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P5" t="s">
         <v>44</v>
       </c>
       <c r="Q5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="R5">
-        <v>0.24</v>
+        <v>1.4</v>
       </c>
       <c r="S5">
-        <v>6.11</v>
+        <v>8.44</v>
       </c>
       <c r="T5">
-        <v>1260</v>
+        <v>279.85</v>
       </c>
       <c r="U5">
-        <v>1260</v>
+        <v>279.65</v>
       </c>
       <c r="V5">
-        <v>1260</v>
+        <v>265.3</v>
       </c>
       <c r="W5" t="s">
         <v>52</v>
       </c>
       <c r="X5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6">
+        <v>235.43</v>
+      </c>
+      <c r="G6">
+        <v>424</v>
+      </c>
+      <c r="H6">
+        <v>99822.32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6">
+        <v>6</v>
+      </c>
+      <c r="O6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>44</v>
+      </c>
+      <c r="R6">
+        <v>36.09</v>
+      </c>
+      <c r="S6">
+        <v>12.85</v>
+      </c>
+      <c r="T6">
+        <v>215.37</v>
+      </c>
+      <c r="U6">
+        <v>215.37</v>
+      </c>
+      <c r="V6">
+        <v>206</v>
+      </c>
+      <c r="W6" t="s">
+        <v>56</v>
+      </c>
+      <c r="X6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7">
+        <v>435.4</v>
+      </c>
+      <c r="G7">
+        <v>229</v>
+      </c>
+      <c r="H7">
+        <v>99706.6</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7">
+        <v>6</v>
+      </c>
+      <c r="O7" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>44</v>
+      </c>
+      <c r="R7">
+        <v>0.79</v>
+      </c>
+      <c r="S7">
+        <v>5.6</v>
+      </c>
+      <c r="T7">
+        <v>428.05</v>
+      </c>
+      <c r="U7">
+        <v>428.05</v>
+      </c>
+      <c r="V7">
+        <v>428.05</v>
+      </c>
+      <c r="W7" t="s">
+        <v>59</v>
+      </c>
+      <c r="X7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8">
+        <v>224.69</v>
+      </c>
+      <c r="G8">
+        <v>445</v>
+      </c>
+      <c r="H8">
+        <v>99987.05</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8">
+        <v>8</v>
+      </c>
+      <c r="O8" t="s">
+        <v>63</v>
+      </c>
+      <c r="P8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>39</v>
+      </c>
+      <c r="R8">
+        <v>0.83</v>
+      </c>
+      <c r="S8">
+        <v>11.64</v>
+      </c>
+      <c r="T8">
+        <v>215.67</v>
+      </c>
+      <c r="U8">
+        <v>214.53</v>
+      </c>
+      <c r="V8">
+        <v>202.5</v>
+      </c>
+      <c r="W8" t="s">
+        <v>64</v>
+      </c>
+      <c r="X8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9">
+        <v>26630</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>79890</v>
+      </c>
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N9">
+        <v>6</v>
+      </c>
+      <c r="O9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P9" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>44</v>
+      </c>
+      <c r="R9">
+        <v>0.27</v>
+      </c>
+      <c r="S9">
+        <v>6.1</v>
+      </c>
+      <c r="T9">
+        <v>26345</v>
+      </c>
+      <c r="U9">
+        <v>25965</v>
+      </c>
+      <c r="V9">
+        <v>25055</v>
+      </c>
+      <c r="W9" t="s">
+        <v>68</v>
+      </c>
+      <c r="X9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10">
+        <v>918.8</v>
+      </c>
+      <c r="G10">
+        <v>108</v>
+      </c>
+      <c r="H10">
+        <v>99230.4</v>
+      </c>
+      <c r="I10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10">
+        <v>6</v>
+      </c>
+      <c r="O10" t="s">
+        <v>63</v>
+      </c>
+      <c r="P10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>44</v>
+      </c>
+      <c r="R10">
+        <v>1.23</v>
+      </c>
+      <c r="S10">
+        <v>8.93</v>
+      </c>
+      <c r="T10">
+        <v>879.1</v>
+      </c>
+      <c r="U10">
+        <v>878.3</v>
+      </c>
+      <c r="V10">
+        <v>845.65</v>
+      </c>
+      <c r="W10" t="s">
+        <v>71</v>
+      </c>
+      <c r="X10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11">
+        <v>1283.6</v>
+      </c>
+      <c r="G11">
+        <v>77</v>
+      </c>
+      <c r="H11">
+        <v>98837.2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" t="s">
+        <v>37</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11" t="s">
+        <v>74</v>
+      </c>
+      <c r="P11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>44</v>
+      </c>
+      <c r="R11">
+        <v>0.24</v>
+      </c>
+      <c r="S11">
+        <v>6.11</v>
+      </c>
+      <c r="T11">
+        <v>1260</v>
+      </c>
+      <c r="U11">
+        <v>1260</v>
+      </c>
+      <c r="V11">
+        <v>1260</v>
+      </c>
+      <c r="W11" t="s">
+        <v>75</v>
+      </c>
+      <c r="X11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12">
+        <v>35210</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>70420</v>
+      </c>
+      <c r="I12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12">
+        <v>6</v>
+      </c>
+      <c r="O12" t="s">
+        <v>78</v>
+      </c>
+      <c r="P12" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>44</v>
+      </c>
+      <c r="R12">
+        <v>0.67</v>
+      </c>
+      <c r="S12">
+        <v>7.74</v>
+      </c>
+      <c r="T12">
+        <v>33800</v>
+      </c>
+      <c r="U12">
+        <v>33320</v>
+      </c>
+      <c r="V12">
+        <v>32605</v>
+      </c>
+      <c r="W12" t="s">
+        <v>79</v>
+      </c>
+      <c r="X12" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1019,7 +1618,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1128,13 +1727,13 @@
         <v>36</v>
       </c>
       <c r="F2">
-        <v>224.69</v>
+        <v>1042.5</v>
       </c>
       <c r="G2">
-        <v>445</v>
+        <v>95</v>
       </c>
       <c r="H2">
-        <v>99987.05</v>
+        <v>99037.5</v>
       </c>
       <c r="I2" t="s">
         <v>37</v>
@@ -1152,7 +1751,7 @@
         <v>37</v>
       </c>
       <c r="N2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O2" t="s">
         <v>38</v>
@@ -1164,19 +1763,19 @@
         <v>39</v>
       </c>
       <c r="R2">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>11.64</v>
+        <v>7.05</v>
       </c>
       <c r="T2">
-        <v>215.67</v>
+        <v>1024.8</v>
       </c>
       <c r="U2">
-        <v>214.53</v>
+        <v>1017.6</v>
       </c>
       <c r="V2">
-        <v>202.5</v>
+        <v>993.4</v>
       </c>
       <c r="W2" t="s">
         <v>40</v>
@@ -1202,13 +1801,13 @@
         <v>36</v>
       </c>
       <c r="F3">
-        <v>26630</v>
+        <v>414.5</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>241</v>
       </c>
       <c r="H3">
-        <v>79890</v>
+        <v>99894.5</v>
       </c>
       <c r="I3" t="s">
         <v>37</v>
@@ -1226,31 +1825,31 @@
         <v>37</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O3" t="s">
         <v>43</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="Q3" t="s">
         <v>44</v>
       </c>
       <c r="R3">
-        <v>0.27</v>
+        <v>0.76</v>
       </c>
       <c r="S3">
-        <v>6.1</v>
+        <v>7.52</v>
       </c>
       <c r="T3">
-        <v>26345</v>
+        <v>413.5</v>
       </c>
       <c r="U3">
-        <v>25965</v>
+        <v>413.5</v>
       </c>
       <c r="V3">
-        <v>25055</v>
+        <v>385.8</v>
       </c>
       <c r="W3" t="s">
         <v>45</v>
@@ -1276,13 +1875,13 @@
         <v>36</v>
       </c>
       <c r="F4">
-        <v>918.8</v>
+        <v>1159.45</v>
       </c>
       <c r="G4">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="H4">
-        <v>99230.4</v>
+        <v>99712.7</v>
       </c>
       <c r="I4" t="s">
         <v>37</v>
@@ -1303,31 +1902,31 @@
         <v>6</v>
       </c>
       <c r="O4" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="P4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" t="s">
         <v>39</v>
       </c>
-      <c r="Q4" t="s">
-        <v>44</v>
-      </c>
       <c r="R4">
-        <v>1.23</v>
+        <v>7.84</v>
       </c>
       <c r="S4">
-        <v>8.93</v>
+        <v>15.78</v>
       </c>
       <c r="T4">
-        <v>879.1</v>
+        <v>1012.8</v>
       </c>
       <c r="U4">
-        <v>878.3</v>
+        <v>1012.8</v>
       </c>
       <c r="V4">
-        <v>845.65</v>
+        <v>974.6</v>
       </c>
       <c r="W4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X4" t="s">
         <v>37</v>
@@ -1338,10 +1937,10 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
         <v>35</v>
@@ -1350,13 +1949,13 @@
         <v>36</v>
       </c>
       <c r="F5">
-        <v>1283.6</v>
+        <v>289.4</v>
       </c>
       <c r="G5">
-        <v>77</v>
+        <v>345</v>
       </c>
       <c r="H5">
-        <v>98837.2</v>
+        <v>99843</v>
       </c>
       <c r="I5" t="s">
         <v>37</v>
@@ -1374,36 +1973,554 @@
         <v>37</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P5" t="s">
         <v>44</v>
       </c>
       <c r="Q5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="R5">
-        <v>0.24</v>
+        <v>1.4</v>
       </c>
       <c r="S5">
-        <v>6.11</v>
+        <v>8.44</v>
       </c>
       <c r="T5">
-        <v>1260</v>
+        <v>279.85</v>
       </c>
       <c r="U5">
-        <v>1260</v>
+        <v>279.65</v>
       </c>
       <c r="V5">
-        <v>1260</v>
+        <v>265.3</v>
       </c>
       <c r="W5" t="s">
         <v>52</v>
       </c>
       <c r="X5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6">
+        <v>235.43</v>
+      </c>
+      <c r="G6">
+        <v>424</v>
+      </c>
+      <c r="H6">
+        <v>99822.32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6">
+        <v>6</v>
+      </c>
+      <c r="O6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>44</v>
+      </c>
+      <c r="R6">
+        <v>36.09</v>
+      </c>
+      <c r="S6">
+        <v>12.85</v>
+      </c>
+      <c r="T6">
+        <v>215.37</v>
+      </c>
+      <c r="U6">
+        <v>215.37</v>
+      </c>
+      <c r="V6">
+        <v>206</v>
+      </c>
+      <c r="W6" t="s">
+        <v>56</v>
+      </c>
+      <c r="X6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7">
+        <v>435.4</v>
+      </c>
+      <c r="G7">
+        <v>229</v>
+      </c>
+      <c r="H7">
+        <v>99706.6</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7">
+        <v>6</v>
+      </c>
+      <c r="O7" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>44</v>
+      </c>
+      <c r="R7">
+        <v>0.79</v>
+      </c>
+      <c r="S7">
+        <v>5.6</v>
+      </c>
+      <c r="T7">
+        <v>428.05</v>
+      </c>
+      <c r="U7">
+        <v>428.05</v>
+      </c>
+      <c r="V7">
+        <v>428.05</v>
+      </c>
+      <c r="W7" t="s">
+        <v>59</v>
+      </c>
+      <c r="X7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8">
+        <v>224.69</v>
+      </c>
+      <c r="G8">
+        <v>445</v>
+      </c>
+      <c r="H8">
+        <v>99987.05</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8">
+        <v>8</v>
+      </c>
+      <c r="O8" t="s">
+        <v>63</v>
+      </c>
+      <c r="P8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>39</v>
+      </c>
+      <c r="R8">
+        <v>0.83</v>
+      </c>
+      <c r="S8">
+        <v>11.64</v>
+      </c>
+      <c r="T8">
+        <v>215.67</v>
+      </c>
+      <c r="U8">
+        <v>214.53</v>
+      </c>
+      <c r="V8">
+        <v>202.5</v>
+      </c>
+      <c r="W8" t="s">
+        <v>64</v>
+      </c>
+      <c r="X8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9">
+        <v>26630</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>79890</v>
+      </c>
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N9">
+        <v>6</v>
+      </c>
+      <c r="O9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P9" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>44</v>
+      </c>
+      <c r="R9">
+        <v>0.27</v>
+      </c>
+      <c r="S9">
+        <v>6.1</v>
+      </c>
+      <c r="T9">
+        <v>26345</v>
+      </c>
+      <c r="U9">
+        <v>25965</v>
+      </c>
+      <c r="V9">
+        <v>25055</v>
+      </c>
+      <c r="W9" t="s">
+        <v>68</v>
+      </c>
+      <c r="X9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10">
+        <v>918.8</v>
+      </c>
+      <c r="G10">
+        <v>108</v>
+      </c>
+      <c r="H10">
+        <v>99230.4</v>
+      </c>
+      <c r="I10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10">
+        <v>6</v>
+      </c>
+      <c r="O10" t="s">
+        <v>63</v>
+      </c>
+      <c r="P10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>44</v>
+      </c>
+      <c r="R10">
+        <v>1.23</v>
+      </c>
+      <c r="S10">
+        <v>8.93</v>
+      </c>
+      <c r="T10">
+        <v>879.1</v>
+      </c>
+      <c r="U10">
+        <v>878.3</v>
+      </c>
+      <c r="V10">
+        <v>845.65</v>
+      </c>
+      <c r="W10" t="s">
+        <v>71</v>
+      </c>
+      <c r="X10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11">
+        <v>1283.6</v>
+      </c>
+      <c r="G11">
+        <v>77</v>
+      </c>
+      <c r="H11">
+        <v>98837.2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" t="s">
+        <v>37</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11" t="s">
+        <v>74</v>
+      </c>
+      <c r="P11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>44</v>
+      </c>
+      <c r="R11">
+        <v>0.24</v>
+      </c>
+      <c r="S11">
+        <v>6.11</v>
+      </c>
+      <c r="T11">
+        <v>1260</v>
+      </c>
+      <c r="U11">
+        <v>1260</v>
+      </c>
+      <c r="V11">
+        <v>1260</v>
+      </c>
+      <c r="W11" t="s">
+        <v>75</v>
+      </c>
+      <c r="X11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12">
+        <v>35210</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>70420</v>
+      </c>
+      <c r="I12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12">
+        <v>6</v>
+      </c>
+      <c r="O12" t="s">
+        <v>78</v>
+      </c>
+      <c r="P12" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>44</v>
+      </c>
+      <c r="R12">
+        <v>0.67</v>
+      </c>
+      <c r="S12">
+        <v>7.74</v>
+      </c>
+      <c r="T12">
+        <v>33800</v>
+      </c>
+      <c r="U12">
+        <v>33320</v>
+      </c>
+      <c r="V12">
+        <v>32605</v>
+      </c>
+      <c r="W12" t="s">
+        <v>79</v>
+      </c>
+      <c r="X12" t="s">
         <v>37</v>
       </c>
     </row>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -26,7 +26,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-09T05:04:51.257Z</t>
+    <t>2026-07-09T05:08:36.386Z</t>
   </si>
   <si>
     <t>Pending Orders</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="117">
   <si>
     <t>Metric</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-10T06:08:24.356Z</t>
+    <t>2026-07-10T08:25:48.823Z</t>
   </si>
   <si>
     <t>Pending Orders</t>
@@ -140,6 +140,36 @@
     <t>Fundamental Score</t>
   </si>
   <si>
+    <t>Institutional Score</t>
+  </si>
+  <si>
+    <t>Index Context</t>
+  </si>
+  <si>
+    <t>Derivatives Context</t>
+  </si>
+  <si>
+    <t>Options Context</t>
+  </si>
+  <si>
+    <t>Commodity Context</t>
+  </si>
+  <si>
+    <t>Concept Score</t>
+  </si>
+  <si>
+    <t>Strong Concepts</t>
+  </si>
+  <si>
+    <t>Weak Concepts</t>
+  </si>
+  <si>
+    <t>Data Gaps</t>
+  </si>
+  <si>
+    <t>Excluded Playbooks</t>
+  </si>
+  <si>
     <t>Sector Breadth</t>
   </si>
   <si>
@@ -174,13 +204,175 @@
   </si>
   <si>
     <t>Exit Reason</t>
+  </si>
+  <si>
+    <t>All NSE Market, My Custom List</t>
+  </si>
+  <si>
+    <t>PGHL</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>09:15 IST</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>2/4</t>
+  </si>
+  <si>
+    <t>NIFTY 500 proxy is BULLISH; broad index support is positive.</t>
+  </si>
+  <si>
+    <t>Not present in NSE F&amp;O lot-size master; treat as cash-equity only.</t>
+  </si>
+  <si>
+    <t>NSE option-chain snapshot unavailable; mark this as data gap, not as bearish.</t>
+  </si>
+  <si>
+    <t>1/5 commodity/currency proxies are bullish; 3 bearish.</t>
+  </si>
+  <si>
+    <t>17/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+  </si>
+  <si>
+    <t>Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Index option-chain positioning</t>
+  </si>
+  <si>
+    <t>Intraday tick scalping; Broker-only live Greeks/order-book depth</t>
+  </si>
+  <si>
+    <t>64.29% (90/140)</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>previous-high confirmation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 73.92 is above 50. Daily RSI 70.18 is above 50. Weekly RS 23.0% is above 0. Daily long RS55 28.3% is above 0. Daily short RS21 2.2% is above 0. Daily close 6612.00 is above Supertrend(10, 3) 6036.47. Price action strength: close is within 15% of 52-week high 6739.00. Volume shocker: latest volume is 2.02x the 50-day average. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.56% of price. Liquidity strength: 20-day average turnover is Rs 92394456.38. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 17/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session 09:15-09:20 IST window.</t>
+  </si>
+  <si>
+    <t>All NSE Market, Default Nifty 500, My Custom List</t>
+  </si>
+  <si>
+    <t>KPIL</t>
+  </si>
+  <si>
+    <t>16/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>bullish engulfing</t>
+  </si>
+  <si>
+    <t>Weekly RSI 66.89 is above 50. Daily RSI 50.91 is above 50. Weekly RS 27.5% is above 0. Daily long RS55 5.5% is above 0. Daily short RS21 2.1% is above 0. Daily close 1349.90 is above Supertrend(10, 3) 1313.78. Price action strength: close is within 15% of 52-week high 1479.60. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 2.68% above daily Supertrend. Price confirmation: bullish engulfing is present. Volatility is controlled: ATR(14) is 3.04% of price. Liquidity strength: 20-day average turnover is Rs 511253745.19. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 16/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session 09:15-09:20 IST window.</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+  </si>
+  <si>
+    <t>Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>No bullish confirmation pattern</t>
+  </si>
+  <si>
+    <t>Weekly RSI 62.41 is above 50. Daily RSI 59.04 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 9.6% is above 0. Daily short RS21 0.7% is above 0. Daily close 1993.20 is above Supertrend(10, 3) 1864.19. Price action strength: close is within 15% of 52-week high 2093.30. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.47% above daily Supertrend. Volatility is controlled: ATR(14) is 2.56% of price. Liquidity strength: 20-day average turnover is Rs 580096417.25. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 16/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session 09:15-09:20 IST window.</t>
+  </si>
+  <si>
+    <t>VIJAYA</t>
+  </si>
+  <si>
+    <t>15/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>previous-high confirmation + bullish engulfing</t>
+  </si>
+  <si>
+    <t>Weekly RSI 66.67 is above 50. Daily RSI 57.60 is above 50. Weekly RS 42.2% is above 0. Daily long RS55 32.3% is above 0. Daily short RS21 4.5% is above 0. Daily close 1377.80 is above Supertrend(10, 3) 1215.62. Price action strength: close is within 15% of 52-week high 1427.80. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.06% of price. Liquidity strength: 20-day average turnover is Rs 464701789.72. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session 09:15-09:20 IST window.</t>
+  </si>
+  <si>
+    <t>PRECOT</t>
+  </si>
+  <si>
+    <t>14/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Volatility and liquidity control; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 64.67 is above 50. Daily RSI 61.84 is above 50. Weekly RS 54.7% is above 0. Daily long RS55 46.8% is above 0. Daily short RS21 15.0% is above 0. Daily close 800.45 is above Supertrend(10, 3) 673.89. Price action strength: close is within 15% of 52-week high 861.25. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.91% of price. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 14/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session 09:15-09:20 IST window.</t>
+  </si>
+  <si>
+    <t>SIS</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 72.14 is above 50. Daily RSI 61.56 is above 50. Weekly RS 25.5% is above 0. Daily long RS55 29.2% is above 0. Daily short RS21 1.5% is above 0. Daily close 437.80 is above Supertrend(10, 3) 397.84. Price action strength: close is within 15% of 52-week high 480.95. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Volatility is controlled: ATR(14) is 3.42% of price. Liquidity strength: 20-day average turnover is Rs 261311772.23. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 14/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session 09:15-09:20 IST window.</t>
+  </si>
+  <si>
+    <t>PRUDENT</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 63.57 is above 50. Daily RSI 53.42 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 4.7% is above 0. Daily close 2960.00 is above Supertrend(10, 3) 2759.71. Price action strength: close is within 15% of 52-week high 3160.10. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.77% above daily Supertrend. Volatility is controlled: ATR(14) is 3.14% of price. Liquidity strength: 20-day average turnover is Rs 67973469.69. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session 09:15-09:20 IST window.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -191,6 +383,9 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <color rgb="FFB4232A"/>
     </font>
   </fonts>
   <fills count="3">
@@ -218,9 +413,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -596,7 +792,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -620,7 +816,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>-7396.55</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -679,7 +875,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AV8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -707,15 +903,21 @@
     <col min="24" max="24" width="13" customWidth="1"/>
     <col min="25" max="25" width="14" customWidth="1"/>
     <col min="26" max="27" width="18" customWidth="1"/>
-    <col min="28" max="30" width="14" customWidth="1"/>
-    <col min="31" max="31" width="12" customWidth="1"/>
-    <col min="32" max="32" width="14" customWidth="1"/>
-    <col min="33" max="33" width="24" customWidth="1"/>
-    <col min="34" max="36" width="14" customWidth="1"/>
-    <col min="37" max="38" width="60" customWidth="1"/>
+    <col min="28" max="31" width="34" customWidth="1"/>
+    <col min="32" max="32" width="16" customWidth="1"/>
+    <col min="33" max="34" width="42" customWidth="1"/>
+    <col min="35" max="35" width="30" customWidth="1"/>
+    <col min="36" max="36" width="36" customWidth="1"/>
+    <col min="37" max="37" width="18" customWidth="1"/>
+    <col min="38" max="40" width="14" customWidth="1"/>
+    <col min="41" max="41" width="12" customWidth="1"/>
+    <col min="42" max="42" width="14" customWidth="1"/>
+    <col min="43" max="43" width="24" customWidth="1"/>
+    <col min="44" max="46" width="14" customWidth="1"/>
+    <col min="47" max="48" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -830,9 +1032,1061 @@
       <c r="AL1" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AM1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2">
+        <v>6612.5</v>
+      </c>
+      <c r="K2">
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>99187.5</v>
+      </c>
+      <c r="M2">
+        <v>6612</v>
+      </c>
+      <c r="N2" s="2">
+        <v>-7.5</v>
+      </c>
+      <c r="O2">
+        <v>-0.01</v>
+      </c>
+      <c r="P2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>69</v>
+      </c>
+      <c r="R2" t="s">
+        <v>69</v>
+      </c>
+      <c r="S2" t="s">
+        <v>69</v>
+      </c>
+      <c r="T2" t="s">
+        <v>69</v>
+      </c>
+      <c r="U2" t="s">
+        <v>69</v>
+      </c>
+      <c r="V2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y2">
+        <v>15</v>
+      </c>
+      <c r="Z2">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN2">
+        <v>2.02</v>
+      </c>
+      <c r="AO2">
+        <v>2.56</v>
+      </c>
+      <c r="AP2">
+        <v>8.7</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR2">
+        <v>6202.5</v>
+      </c>
+      <c r="AS2">
+        <v>6202.5</v>
+      </c>
+      <c r="AT2">
+        <v>6202.5</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3">
+        <v>1360</v>
+      </c>
+      <c r="K3">
+        <v>73</v>
+      </c>
+      <c r="L3">
+        <v>99280</v>
+      </c>
+      <c r="M3">
+        <v>1349.9</v>
+      </c>
+      <c r="N3" s="2">
+        <v>-737.3</v>
+      </c>
+      <c r="O3">
+        <v>-0.74</v>
+      </c>
+      <c r="P3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>69</v>
+      </c>
+      <c r="R3" t="s">
+        <v>69</v>
+      </c>
+      <c r="S3" t="s">
+        <v>69</v>
+      </c>
+      <c r="T3" t="s">
+        <v>69</v>
+      </c>
+      <c r="U3" t="s">
+        <v>69</v>
+      </c>
+      <c r="V3" t="s">
+        <v>69</v>
+      </c>
+      <c r="W3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y3">
+        <v>13</v>
+      </c>
+      <c r="Z3">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN3">
+        <v>0.32</v>
+      </c>
+      <c r="AO3">
+        <v>3.04</v>
+      </c>
+      <c r="AP3">
+        <v>2.68</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR3">
+        <v>1321</v>
+      </c>
+      <c r="AS3">
+        <v>1321</v>
+      </c>
+      <c r="AT3">
+        <v>1321</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J4">
+        <v>2003.1</v>
+      </c>
+      <c r="K4">
+        <v>49</v>
+      </c>
+      <c r="L4">
+        <v>98151.9</v>
+      </c>
+      <c r="M4">
+        <v>1993.2</v>
+      </c>
+      <c r="N4" s="2">
+        <v>-485.1</v>
+      </c>
+      <c r="O4">
+        <v>-0.49</v>
+      </c>
+      <c r="P4" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>69</v>
+      </c>
+      <c r="R4" t="s">
+        <v>69</v>
+      </c>
+      <c r="S4" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" t="s">
+        <v>69</v>
+      </c>
+      <c r="U4" t="s">
+        <v>69</v>
+      </c>
+      <c r="V4" t="s">
+        <v>69</v>
+      </c>
+      <c r="W4" t="s">
+        <v>17</v>
+      </c>
+      <c r="X4" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y4">
+        <v>14</v>
+      </c>
+      <c r="Z4">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN4">
+        <v>0.55</v>
+      </c>
+      <c r="AO4">
+        <v>2.56</v>
+      </c>
+      <c r="AP4">
+        <v>6.47</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR4">
+        <v>1957</v>
+      </c>
+      <c r="AS4">
+        <v>1957</v>
+      </c>
+      <c r="AT4">
+        <v>1957</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5">
+        <v>1397.7</v>
+      </c>
+      <c r="K5">
+        <v>71</v>
+      </c>
+      <c r="L5">
+        <v>99236.7</v>
+      </c>
+      <c r="M5">
+        <v>1377.8</v>
+      </c>
+      <c r="N5" s="2">
+        <v>-1412.9</v>
+      </c>
+      <c r="O5">
+        <v>-1.42</v>
+      </c>
+      <c r="P5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T5" t="s">
+        <v>69</v>
+      </c>
+      <c r="U5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V5" t="s">
+        <v>69</v>
+      </c>
+      <c r="W5" t="s">
+        <v>17</v>
+      </c>
+      <c r="X5" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y5">
+        <v>13</v>
+      </c>
+      <c r="Z5">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN5">
+        <v>0.72</v>
+      </c>
+      <c r="AO5">
+        <v>4.06</v>
+      </c>
+      <c r="AP5">
+        <v>11.77</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR5">
+        <v>1303.2</v>
+      </c>
+      <c r="AS5">
+        <v>1303.2</v>
+      </c>
+      <c r="AT5">
+        <v>1303.2</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6">
+        <v>838.9</v>
+      </c>
+      <c r="K6">
+        <v>119</v>
+      </c>
+      <c r="L6">
+        <v>99829.1</v>
+      </c>
+      <c r="M6">
+        <v>800.45</v>
+      </c>
+      <c r="N6" s="2">
+        <v>-4575.55</v>
+      </c>
+      <c r="O6">
+        <v>-4.58</v>
+      </c>
+      <c r="P6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R6" t="s">
+        <v>69</v>
+      </c>
+      <c r="S6" t="s">
+        <v>69</v>
+      </c>
+      <c r="T6" t="s">
+        <v>69</v>
+      </c>
+      <c r="U6" t="s">
+        <v>69</v>
+      </c>
+      <c r="V6" t="s">
+        <v>69</v>
+      </c>
+      <c r="W6" t="s">
+        <v>17</v>
+      </c>
+      <c r="X6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y6">
+        <v>13</v>
+      </c>
+      <c r="Z6">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN6">
+        <v>1.22</v>
+      </c>
+      <c r="AO6">
+        <v>4.91</v>
+      </c>
+      <c r="AP6">
+        <v>15.81</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR6">
+        <v>770</v>
+      </c>
+      <c r="AS6">
+        <v>770</v>
+      </c>
+      <c r="AT6">
+        <v>721.4</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7">
+        <v>437.8</v>
+      </c>
+      <c r="K7">
+        <v>228</v>
+      </c>
+      <c r="L7">
+        <v>99818.4</v>
+      </c>
+      <c r="M7">
+        <v>437.8</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>69</v>
+      </c>
+      <c r="R7" t="s">
+        <v>69</v>
+      </c>
+      <c r="S7" t="s">
+        <v>69</v>
+      </c>
+      <c r="T7" t="s">
+        <v>69</v>
+      </c>
+      <c r="U7" t="s">
+        <v>69</v>
+      </c>
+      <c r="V7" t="s">
+        <v>69</v>
+      </c>
+      <c r="W7" t="s">
+        <v>17</v>
+      </c>
+      <c r="X7" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y7">
+        <v>11</v>
+      </c>
+      <c r="Z7">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>105</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN7">
+        <v>0.22</v>
+      </c>
+      <c r="AO7">
+        <v>3.42</v>
+      </c>
+      <c r="AP7">
+        <v>9.13</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR7">
+        <v>425.45</v>
+      </c>
+      <c r="AS7">
+        <v>423.3</v>
+      </c>
+      <c r="AT7">
+        <v>422.15</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8">
+        <v>2965.4</v>
+      </c>
+      <c r="K8">
+        <v>33</v>
+      </c>
+      <c r="L8">
+        <v>97858.2</v>
+      </c>
+      <c r="M8">
+        <v>2960</v>
+      </c>
+      <c r="N8" s="2">
+        <v>-178.2</v>
+      </c>
+      <c r="O8">
+        <v>-0.18</v>
+      </c>
+      <c r="P8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>69</v>
+      </c>
+      <c r="R8" t="s">
+        <v>69</v>
+      </c>
+      <c r="S8" t="s">
+        <v>69</v>
+      </c>
+      <c r="T8" t="s">
+        <v>69</v>
+      </c>
+      <c r="U8" t="s">
+        <v>69</v>
+      </c>
+      <c r="V8" t="s">
+        <v>69</v>
+      </c>
+      <c r="W8" t="s">
+        <v>17</v>
+      </c>
+      <c r="X8" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y8">
+        <v>12</v>
+      </c>
+      <c r="Z8">
+        <v>3</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN8">
+        <v>1.21</v>
+      </c>
+      <c r="AO8">
+        <v>3.14</v>
+      </c>
+      <c r="AP8">
+        <v>6.77</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR8">
+        <v>2903.2</v>
+      </c>
+      <c r="AS8">
+        <v>2903.2</v>
+      </c>
+      <c r="AT8">
+        <v>2903.2</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>116</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL1"/>
+  <autoFilter ref="A1:AV1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -840,7 +2094,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -868,15 +2122,21 @@
     <col min="24" max="24" width="13" customWidth="1"/>
     <col min="25" max="25" width="14" customWidth="1"/>
     <col min="26" max="27" width="18" customWidth="1"/>
-    <col min="28" max="30" width="14" customWidth="1"/>
-    <col min="31" max="31" width="12" customWidth="1"/>
-    <col min="32" max="32" width="14" customWidth="1"/>
-    <col min="33" max="33" width="24" customWidth="1"/>
-    <col min="34" max="36" width="14" customWidth="1"/>
-    <col min="37" max="38" width="60" customWidth="1"/>
+    <col min="28" max="31" width="34" customWidth="1"/>
+    <col min="32" max="32" width="16" customWidth="1"/>
+    <col min="33" max="34" width="42" customWidth="1"/>
+    <col min="35" max="35" width="30" customWidth="1"/>
+    <col min="36" max="36" width="36" customWidth="1"/>
+    <col min="37" max="37" width="18" customWidth="1"/>
+    <col min="38" max="40" width="14" customWidth="1"/>
+    <col min="41" max="41" width="12" customWidth="1"/>
+    <col min="42" max="42" width="14" customWidth="1"/>
+    <col min="43" max="43" width="24" customWidth="1"/>
+    <col min="44" max="46" width="14" customWidth="1"/>
+    <col min="47" max="48" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -991,9 +2251,39 @@
       <c r="AL1" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AM1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL1"/>
+  <autoFilter ref="A1:AV1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1001,7 +2291,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1029,15 +2319,21 @@
     <col min="24" max="24" width="13" customWidth="1"/>
     <col min="25" max="25" width="14" customWidth="1"/>
     <col min="26" max="27" width="18" customWidth="1"/>
-    <col min="28" max="30" width="14" customWidth="1"/>
-    <col min="31" max="31" width="12" customWidth="1"/>
-    <col min="32" max="32" width="14" customWidth="1"/>
-    <col min="33" max="33" width="24" customWidth="1"/>
-    <col min="34" max="36" width="14" customWidth="1"/>
-    <col min="37" max="38" width="60" customWidth="1"/>
+    <col min="28" max="31" width="34" customWidth="1"/>
+    <col min="32" max="32" width="16" customWidth="1"/>
+    <col min="33" max="34" width="42" customWidth="1"/>
+    <col min="35" max="35" width="30" customWidth="1"/>
+    <col min="36" max="36" width="36" customWidth="1"/>
+    <col min="37" max="37" width="18" customWidth="1"/>
+    <col min="38" max="40" width="14" customWidth="1"/>
+    <col min="41" max="41" width="12" customWidth="1"/>
+    <col min="42" max="42" width="14" customWidth="1"/>
+    <col min="43" max="43" width="24" customWidth="1"/>
+    <col min="44" max="46" width="14" customWidth="1"/>
+    <col min="47" max="48" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1152,9 +2448,39 @@
       <c r="AL1" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AM1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL1"/>
+  <autoFilter ref="A1:AV1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1162,7 +2488,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AV8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1190,15 +2516,21 @@
     <col min="24" max="24" width="13" customWidth="1"/>
     <col min="25" max="25" width="14" customWidth="1"/>
     <col min="26" max="27" width="18" customWidth="1"/>
-    <col min="28" max="30" width="14" customWidth="1"/>
-    <col min="31" max="31" width="12" customWidth="1"/>
-    <col min="32" max="32" width="14" customWidth="1"/>
-    <col min="33" max="33" width="24" customWidth="1"/>
-    <col min="34" max="36" width="14" customWidth="1"/>
-    <col min="37" max="38" width="60" customWidth="1"/>
+    <col min="28" max="31" width="34" customWidth="1"/>
+    <col min="32" max="32" width="16" customWidth="1"/>
+    <col min="33" max="34" width="42" customWidth="1"/>
+    <col min="35" max="35" width="30" customWidth="1"/>
+    <col min="36" max="36" width="36" customWidth="1"/>
+    <col min="37" max="37" width="18" customWidth="1"/>
+    <col min="38" max="40" width="14" customWidth="1"/>
+    <col min="41" max="41" width="12" customWidth="1"/>
+    <col min="42" max="42" width="14" customWidth="1"/>
+    <col min="43" max="43" width="24" customWidth="1"/>
+    <col min="44" max="46" width="14" customWidth="1"/>
+    <col min="47" max="48" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1313,9 +2645,1061 @@
       <c r="AL1" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AM1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2">
+        <v>6612.5</v>
+      </c>
+      <c r="K2">
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>99187.5</v>
+      </c>
+      <c r="M2">
+        <v>6612</v>
+      </c>
+      <c r="N2" s="2">
+        <v>-7.5</v>
+      </c>
+      <c r="O2">
+        <v>-0.01</v>
+      </c>
+      <c r="P2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>69</v>
+      </c>
+      <c r="R2" t="s">
+        <v>69</v>
+      </c>
+      <c r="S2" t="s">
+        <v>69</v>
+      </c>
+      <c r="T2" t="s">
+        <v>69</v>
+      </c>
+      <c r="U2" t="s">
+        <v>69</v>
+      </c>
+      <c r="V2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y2">
+        <v>15</v>
+      </c>
+      <c r="Z2">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN2">
+        <v>2.02</v>
+      </c>
+      <c r="AO2">
+        <v>2.56</v>
+      </c>
+      <c r="AP2">
+        <v>8.7</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR2">
+        <v>6202.5</v>
+      </c>
+      <c r="AS2">
+        <v>6202.5</v>
+      </c>
+      <c r="AT2">
+        <v>6202.5</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3">
+        <v>1360</v>
+      </c>
+      <c r="K3">
+        <v>73</v>
+      </c>
+      <c r="L3">
+        <v>99280</v>
+      </c>
+      <c r="M3">
+        <v>1349.9</v>
+      </c>
+      <c r="N3" s="2">
+        <v>-737.3</v>
+      </c>
+      <c r="O3">
+        <v>-0.74</v>
+      </c>
+      <c r="P3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>69</v>
+      </c>
+      <c r="R3" t="s">
+        <v>69</v>
+      </c>
+      <c r="S3" t="s">
+        <v>69</v>
+      </c>
+      <c r="T3" t="s">
+        <v>69</v>
+      </c>
+      <c r="U3" t="s">
+        <v>69</v>
+      </c>
+      <c r="V3" t="s">
+        <v>69</v>
+      </c>
+      <c r="W3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y3">
+        <v>13</v>
+      </c>
+      <c r="Z3">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN3">
+        <v>0.32</v>
+      </c>
+      <c r="AO3">
+        <v>3.04</v>
+      </c>
+      <c r="AP3">
+        <v>2.68</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR3">
+        <v>1321</v>
+      </c>
+      <c r="AS3">
+        <v>1321</v>
+      </c>
+      <c r="AT3">
+        <v>1321</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J4">
+        <v>2003.1</v>
+      </c>
+      <c r="K4">
+        <v>49</v>
+      </c>
+      <c r="L4">
+        <v>98151.9</v>
+      </c>
+      <c r="M4">
+        <v>1993.2</v>
+      </c>
+      <c r="N4" s="2">
+        <v>-485.1</v>
+      </c>
+      <c r="O4">
+        <v>-0.49</v>
+      </c>
+      <c r="P4" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>69</v>
+      </c>
+      <c r="R4" t="s">
+        <v>69</v>
+      </c>
+      <c r="S4" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" t="s">
+        <v>69</v>
+      </c>
+      <c r="U4" t="s">
+        <v>69</v>
+      </c>
+      <c r="V4" t="s">
+        <v>69</v>
+      </c>
+      <c r="W4" t="s">
+        <v>17</v>
+      </c>
+      <c r="X4" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y4">
+        <v>14</v>
+      </c>
+      <c r="Z4">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN4">
+        <v>0.55</v>
+      </c>
+      <c r="AO4">
+        <v>2.56</v>
+      </c>
+      <c r="AP4">
+        <v>6.47</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR4">
+        <v>1957</v>
+      </c>
+      <c r="AS4">
+        <v>1957</v>
+      </c>
+      <c r="AT4">
+        <v>1957</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5">
+        <v>1397.7</v>
+      </c>
+      <c r="K5">
+        <v>71</v>
+      </c>
+      <c r="L5">
+        <v>99236.7</v>
+      </c>
+      <c r="M5">
+        <v>1377.8</v>
+      </c>
+      <c r="N5" s="2">
+        <v>-1412.9</v>
+      </c>
+      <c r="O5">
+        <v>-1.42</v>
+      </c>
+      <c r="P5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T5" t="s">
+        <v>69</v>
+      </c>
+      <c r="U5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V5" t="s">
+        <v>69</v>
+      </c>
+      <c r="W5" t="s">
+        <v>17</v>
+      </c>
+      <c r="X5" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y5">
+        <v>13</v>
+      </c>
+      <c r="Z5">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN5">
+        <v>0.72</v>
+      </c>
+      <c r="AO5">
+        <v>4.06</v>
+      </c>
+      <c r="AP5">
+        <v>11.77</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR5">
+        <v>1303.2</v>
+      </c>
+      <c r="AS5">
+        <v>1303.2</v>
+      </c>
+      <c r="AT5">
+        <v>1303.2</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6">
+        <v>838.9</v>
+      </c>
+      <c r="K6">
+        <v>119</v>
+      </c>
+      <c r="L6">
+        <v>99829.1</v>
+      </c>
+      <c r="M6">
+        <v>800.45</v>
+      </c>
+      <c r="N6" s="2">
+        <v>-4575.55</v>
+      </c>
+      <c r="O6">
+        <v>-4.58</v>
+      </c>
+      <c r="P6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R6" t="s">
+        <v>69</v>
+      </c>
+      <c r="S6" t="s">
+        <v>69</v>
+      </c>
+      <c r="T6" t="s">
+        <v>69</v>
+      </c>
+      <c r="U6" t="s">
+        <v>69</v>
+      </c>
+      <c r="V6" t="s">
+        <v>69</v>
+      </c>
+      <c r="W6" t="s">
+        <v>17</v>
+      </c>
+      <c r="X6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y6">
+        <v>13</v>
+      </c>
+      <c r="Z6">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN6">
+        <v>1.22</v>
+      </c>
+      <c r="AO6">
+        <v>4.91</v>
+      </c>
+      <c r="AP6">
+        <v>15.81</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR6">
+        <v>770</v>
+      </c>
+      <c r="AS6">
+        <v>770</v>
+      </c>
+      <c r="AT6">
+        <v>721.4</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7">
+        <v>437.8</v>
+      </c>
+      <c r="K7">
+        <v>228</v>
+      </c>
+      <c r="L7">
+        <v>99818.4</v>
+      </c>
+      <c r="M7">
+        <v>437.8</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>69</v>
+      </c>
+      <c r="R7" t="s">
+        <v>69</v>
+      </c>
+      <c r="S7" t="s">
+        <v>69</v>
+      </c>
+      <c r="T7" t="s">
+        <v>69</v>
+      </c>
+      <c r="U7" t="s">
+        <v>69</v>
+      </c>
+      <c r="V7" t="s">
+        <v>69</v>
+      </c>
+      <c r="W7" t="s">
+        <v>17</v>
+      </c>
+      <c r="X7" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y7">
+        <v>11</v>
+      </c>
+      <c r="Z7">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>105</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN7">
+        <v>0.22</v>
+      </c>
+      <c r="AO7">
+        <v>3.42</v>
+      </c>
+      <c r="AP7">
+        <v>9.13</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR7">
+        <v>425.45</v>
+      </c>
+      <c r="AS7">
+        <v>423.3</v>
+      </c>
+      <c r="AT7">
+        <v>422.15</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8">
+        <v>2965.4</v>
+      </c>
+      <c r="K8">
+        <v>33</v>
+      </c>
+      <c r="L8">
+        <v>97858.2</v>
+      </c>
+      <c r="M8">
+        <v>2960</v>
+      </c>
+      <c r="N8" s="2">
+        <v>-178.2</v>
+      </c>
+      <c r="O8">
+        <v>-0.18</v>
+      </c>
+      <c r="P8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>69</v>
+      </c>
+      <c r="R8" t="s">
+        <v>69</v>
+      </c>
+      <c r="S8" t="s">
+        <v>69</v>
+      </c>
+      <c r="T8" t="s">
+        <v>69</v>
+      </c>
+      <c r="U8" t="s">
+        <v>69</v>
+      </c>
+      <c r="V8" t="s">
+        <v>69</v>
+      </c>
+      <c r="W8" t="s">
+        <v>17</v>
+      </c>
+      <c r="X8" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y8">
+        <v>12</v>
+      </c>
+      <c r="Z8">
+        <v>3</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN8">
+        <v>1.21</v>
+      </c>
+      <c r="AO8">
+        <v>3.14</v>
+      </c>
+      <c r="AP8">
+        <v>6.77</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR8">
+        <v>2903.2</v>
+      </c>
+      <c r="AS8">
+        <v>2903.2</v>
+      </c>
+      <c r="AT8">
+        <v>2903.2</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>116</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL1"/>
+  <autoFilter ref="A1:AV1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="152">
   <si>
     <t>Metric</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-10T08:25:48.823Z</t>
+    <t>2026-07-11T03:46:11.412Z</t>
   </si>
   <si>
     <t>Pending Orders</t>
@@ -56,156 +56,180 @@
     <t>Trade Quality</t>
   </si>
   <si>
+    <t>Strong and best (A+/A/B)</t>
+  </si>
+  <si>
+    <t>Signal Basis</t>
+  </si>
+  <si>
+    <t>completed daily/weekly closing candle</t>
+  </si>
+  <si>
+    <t>Execution Window</t>
+  </si>
+  <si>
+    <t>09:15-09:20 IST</t>
+  </si>
+  <si>
+    <t>Execution Price</t>
+  </si>
+  <si>
+    <t>First 5-minute candle open (09:15)</t>
+  </si>
+  <si>
+    <t>Source Lists</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Entry Signal Date</t>
+  </si>
+  <si>
+    <t>Entry Date</t>
+  </si>
+  <si>
+    <t>Entry Time</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Invested Value</t>
+  </si>
+  <si>
+    <t>Last Close</t>
+  </si>
+  <si>
+    <t>Unrealized P&amp;L %</t>
+  </si>
+  <si>
+    <t>Exit Signal Date</t>
+  </si>
+  <si>
+    <t>Exit Date</t>
+  </si>
+  <si>
+    <t>Exit Time</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Realized P&amp;L %</t>
+  </si>
+  <si>
+    <t>Holding Days</t>
+  </si>
+  <si>
+    <t>Entry Style</t>
+  </si>
+  <si>
+    <t>Setup Grade</t>
+  </si>
+  <si>
+    <t>Setup Score</t>
+  </si>
+  <si>
+    <t>Fundamental Score</t>
+  </si>
+  <si>
+    <t>Institutional Score</t>
+  </si>
+  <si>
+    <t>Index Context</t>
+  </si>
+  <si>
+    <t>Derivatives Context</t>
+  </si>
+  <si>
+    <t>Options Context</t>
+  </si>
+  <si>
+    <t>Commodity Context</t>
+  </si>
+  <si>
+    <t>Concept Score</t>
+  </si>
+  <si>
+    <t>Strong Concepts</t>
+  </si>
+  <si>
+    <t>Weak Concepts</t>
+  </si>
+  <si>
+    <t>Data Gaps</t>
+  </si>
+  <si>
+    <t>Excluded Playbooks</t>
+  </si>
+  <si>
+    <t>Sector Breadth</t>
+  </si>
+  <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>55D Breakout</t>
+  </si>
+  <si>
+    <t>Volume Ratio</t>
+  </si>
+  <si>
+    <t>ATR %</t>
+  </si>
+  <si>
+    <t>Risk To ST %</t>
+  </si>
+  <si>
+    <t>Retracement Buy</t>
+  </si>
+  <si>
+    <t>Pullback Depth %</t>
+  </si>
+  <si>
+    <t>Pullback Support</t>
+  </si>
+  <si>
+    <t>Pullback Risk %</t>
+  </si>
+  <si>
+    <t>Pullback Volume Ratio</t>
+  </si>
+  <si>
+    <t>Reclaim Volume Ratio</t>
+  </si>
+  <si>
+    <t>Candle Pattern</t>
+  </si>
+  <si>
+    <t>Previous Low</t>
+  </si>
+  <si>
+    <t>2 Candle Low</t>
+  </si>
+  <si>
+    <t>4 Candle Low</t>
+  </si>
+  <si>
+    <t>Entry Reason</t>
+  </si>
+  <si>
+    <t>Exit Reason</t>
+  </si>
+  <si>
     <t>Best only (A+/A)</t>
   </si>
   <si>
-    <t>Signal Basis</t>
-  </si>
-  <si>
-    <t>completed daily/weekly closing candle</t>
-  </si>
-  <si>
-    <t>Execution Window</t>
-  </si>
-  <si>
-    <t>09:15-09:20 IST</t>
-  </si>
-  <si>
-    <t>Execution Price</t>
-  </si>
-  <si>
-    <t>First 5-minute candle open (09:15)</t>
-  </si>
-  <si>
-    <t>Source Lists</t>
-  </si>
-  <si>
-    <t>Symbol</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Entry Signal Date</t>
-  </si>
-  <si>
-    <t>Entry Date</t>
-  </si>
-  <si>
-    <t>Entry Time</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Invested Value</t>
-  </si>
-  <si>
-    <t>Last Close</t>
-  </si>
-  <si>
-    <t>Unrealized P&amp;L %</t>
-  </si>
-  <si>
-    <t>Exit Signal Date</t>
-  </si>
-  <si>
-    <t>Exit Date</t>
-  </si>
-  <si>
-    <t>Exit Time</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Realized P&amp;L %</t>
-  </si>
-  <si>
-    <t>Holding Days</t>
-  </si>
-  <si>
-    <t>Setup Grade</t>
-  </si>
-  <si>
-    <t>Setup Score</t>
-  </si>
-  <si>
-    <t>Fundamental Score</t>
-  </si>
-  <si>
-    <t>Institutional Score</t>
-  </si>
-  <si>
-    <t>Index Context</t>
-  </si>
-  <si>
-    <t>Derivatives Context</t>
-  </si>
-  <si>
-    <t>Options Context</t>
-  </si>
-  <si>
-    <t>Commodity Context</t>
-  </si>
-  <si>
-    <t>Concept Score</t>
-  </si>
-  <si>
-    <t>Strong Concepts</t>
-  </si>
-  <si>
-    <t>Weak Concepts</t>
-  </si>
-  <si>
-    <t>Data Gaps</t>
-  </si>
-  <si>
-    <t>Excluded Playbooks</t>
-  </si>
-  <si>
-    <t>Sector Breadth</t>
-  </si>
-  <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>55D Breakout</t>
-  </si>
-  <si>
-    <t>Volume Ratio</t>
-  </si>
-  <si>
-    <t>ATR %</t>
-  </si>
-  <si>
-    <t>Risk To ST %</t>
-  </si>
-  <si>
-    <t>Candle Pattern</t>
-  </si>
-  <si>
-    <t>Previous Low</t>
-  </si>
-  <si>
-    <t>2 Candle Low</t>
-  </si>
-  <si>
-    <t>4 Candle Low</t>
-  </si>
-  <si>
-    <t>Entry Reason</t>
-  </si>
-  <si>
-    <t>Exit Reason</t>
-  </si>
-  <si>
     <t>All NSE Market, My Custom List</t>
   </si>
   <si>
@@ -366,13 +390,94 @@
   </si>
   <si>
     <t>Weekly RSI 63.57 is above 50. Daily RSI 53.42 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 4.7% is above 0. Daily close 2960.00 is above Supertrend(10, 3) 2759.71. Price action strength: close is within 15% of 52-week high 3160.10. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.77% above daily Supertrend. Volatility is controlled: ATR(14) is 3.14% of price. Liquidity strength: 20-day average turnover is Rs 67973469.69. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session 09:15-09:20 IST window.</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>PENDING_ENTRY</t>
+  </si>
+  <si>
+    <t>Retracement buy near 50-DMA</t>
+  </si>
+  <si>
+    <t>3/4</t>
+  </si>
+  <si>
+    <t>F&amp;O listed with lot size 150; OI participation 2.01%, volume 72606.00.</t>
+  </si>
+  <si>
+    <t>2/5 commodity/currency proxies are bullish; 3 bearish.</t>
+  </si>
+  <si>
+    <t>20/22</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+  </si>
+  <si>
+    <t>Volume participation</t>
+  </si>
+  <si>
+    <t>66.43% (93/140)</t>
+  </si>
+  <si>
+    <t>50-DMA</t>
+  </si>
+  <si>
+    <t>Weekly RSI 55.15 is above 50. Daily RSI 60.53 is above 50. Weekly RS 6.8% is above 0. Daily long RS55 2.1% is above 0. Daily short RS21 2.3% is above 0. Daily close 4506.80 is above Supertrend(10, 3) 4193.48. Entry style: Retracement buy near 50-DMA. Price action strength: close is within 15% of 52-week high 5065.00. Retracement buy: price pulled back 6.81% from the 55-day high and reclaimed near 50-DMA 4407.24; support distance is 2.21%. Retracement confirmation: pullback volume ratio 0.58 and reclaim volume ratio 0.99 with candle close location 85.96%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.95% above daily Supertrend. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.15% of price. Liquidity strength: 20-day average turnover is Rs 3498340071.08. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 150; OI participation 2.01%, volume 72606.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 20/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session 09:15-09:20 IST window.</t>
+  </si>
+  <si>
+    <t>PREMIERENE</t>
+  </si>
+  <si>
+    <t>Breakout buy</t>
+  </si>
+  <si>
+    <t>F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00.</t>
+  </si>
+  <si>
+    <t>18/22</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Retracement/pullback buy setup; Risk reference discipline</t>
+  </si>
+  <si>
+    <t>55D high retest</t>
+  </si>
+  <si>
+    <t>Weekly RSI 64.52 is above 50. Daily RSI 67.28 is above 50. Weekly RS 46.9% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 0.0% is above 0. Daily close 1117.20 is above Supertrend(10, 3) 1007.42. Entry style: Breakout buy. Price action strength: close crossed 55-day high 1103.90. Volume shocker: latest volume is 1.56x the 50-day average. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.97% of price. Liquidity strength: 20-day average turnover is Rs 1219054718.79. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 18/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session 09:15-09:20 IST window.</t>
+  </si>
+  <si>
+    <t>SBCL</t>
+  </si>
+  <si>
+    <t>Trend continuation buy</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>14/22</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:15 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Retracement/pullback buy setup; Volume participation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
+  </si>
+  <si>
+    <t>Weekly RSI 66.35 is above 50. Daily RSI 53.52 is above 50. Weekly RS 45.4% is above 0. Daily long RS55 21.9% is above 0. Daily short RS21 5.9% is above 0. Daily close 747.05 is above Supertrend(10, 3) 679.08. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 814.00. Retracement watch: pullback depth 8.22% is valid, but support/reclaim/volume/risk confirmation is incomplete. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 4.83% of price. Liquidity strength: 20-day average turnover is Rs 407588740.32. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 14/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session 09:15-09:20 IST window.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -386,6 +491,9 @@
     </font>
     <font>
       <color rgb="FFB4232A"/>
+    </font>
+    <font>
+      <color rgb="FF147A52"/>
     </font>
   </fonts>
   <fills count="3">
@@ -413,10 +521,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,7 +893,7 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -816,7 +925,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>-7396.55</v>
+        <v>-5725.65</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -875,7 +984,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AV8"/>
+  <dimension ref="A1:BC8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -900,24 +1009,29 @@
     <col min="21" max="21" width="18" customWidth="1"/>
     <col min="22" max="22" width="14" customWidth="1"/>
     <col min="23" max="23" width="20" customWidth="1"/>
-    <col min="24" max="24" width="13" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
-    <col min="26" max="27" width="18" customWidth="1"/>
-    <col min="28" max="31" width="34" customWidth="1"/>
-    <col min="32" max="32" width="16" customWidth="1"/>
-    <col min="33" max="34" width="42" customWidth="1"/>
-    <col min="35" max="35" width="30" customWidth="1"/>
-    <col min="36" max="36" width="36" customWidth="1"/>
-    <col min="37" max="37" width="18" customWidth="1"/>
-    <col min="38" max="40" width="14" customWidth="1"/>
-    <col min="41" max="41" width="12" customWidth="1"/>
-    <col min="42" max="42" width="14" customWidth="1"/>
-    <col min="43" max="43" width="24" customWidth="1"/>
-    <col min="44" max="46" width="14" customWidth="1"/>
-    <col min="47" max="48" width="60" customWidth="1"/>
+    <col min="24" max="24" width="26" customWidth="1"/>
+    <col min="25" max="25" width="13" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
+    <col min="27" max="28" width="18" customWidth="1"/>
+    <col min="29" max="32" width="34" customWidth="1"/>
+    <col min="33" max="33" width="16" customWidth="1"/>
+    <col min="34" max="35" width="42" customWidth="1"/>
+    <col min="36" max="36" width="30" customWidth="1"/>
+    <col min="37" max="37" width="36" customWidth="1"/>
+    <col min="38" max="38" width="18" customWidth="1"/>
+    <col min="39" max="41" width="14" customWidth="1"/>
+    <col min="42" max="42" width="12" customWidth="1"/>
+    <col min="43" max="43" width="14" customWidth="1"/>
+    <col min="44" max="45" width="18" customWidth="1"/>
+    <col min="46" max="46" width="20" customWidth="1"/>
+    <col min="47" max="47" width="18" customWidth="1"/>
+    <col min="48" max="49" width="22" customWidth="1"/>
+    <col min="50" max="50" width="24" customWidth="1"/>
+    <col min="51" max="53" width="14" customWidth="1"/>
+    <col min="54" max="55" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1062,34 +1176,55 @@
       <c r="AV1" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="AW1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J2">
         <v>6612.5</v>
@@ -1110,132 +1245,153 @@
         <v>-0.01</v>
       </c>
       <c r="P2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W2" t="s">
         <v>17</v>
       </c>
       <c r="X2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y2">
+        <v>77</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z2">
         <v>15</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>4</v>
       </c>
-      <c r="AA2" t="s">
-        <v>71</v>
-      </c>
       <c r="AB2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AC2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AE2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AG2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AH2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AK2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AL2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AM2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN2">
+        <v>90</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO2">
         <v>2.02</v>
       </c>
-      <c r="AO2">
+      <c r="AP2">
         <v>2.56</v>
       </c>
-      <c r="AP2">
+      <c r="AQ2">
         <v>8.7</v>
       </c>
-      <c r="AQ2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR2">
+      <c r="AR2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY2">
         <v>6202.5</v>
       </c>
-      <c r="AS2">
+      <c r="AZ2">
         <v>6202.5</v>
       </c>
-      <c r="AT2">
+      <c r="BA2">
         <v>6202.5</v>
       </c>
-      <c r="AU2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>69</v>
+      <c r="BB2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J3">
         <v>1360</v>
@@ -1256,132 +1412,153 @@
         <v>-0.74</v>
       </c>
       <c r="P3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W3" t="s">
         <v>17</v>
       </c>
       <c r="X3" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y3">
+        <v>77</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z3">
         <v>13</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>4</v>
       </c>
-      <c r="AA3" t="s">
-        <v>71</v>
-      </c>
       <c r="AB3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AC3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AE3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK3" t="s">
         <v>88</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AL3" t="s">
         <v>89</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AM3" t="s">
         <v>90</v>
       </c>
-      <c r="AI3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN3">
+      <c r="AN3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO3">
         <v>0.32</v>
       </c>
-      <c r="AO3">
+      <c r="AP3">
         <v>3.04</v>
       </c>
-      <c r="AP3">
+      <c r="AQ3">
         <v>2.68</v>
       </c>
-      <c r="AQ3" t="s">
+      <c r="AR3" t="s">
         <v>91</v>
       </c>
-      <c r="AR3">
+      <c r="AS3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY3">
         <v>1321</v>
       </c>
-      <c r="AS3">
+      <c r="AZ3">
         <v>1321</v>
       </c>
-      <c r="AT3">
+      <c r="BA3">
         <v>1321</v>
       </c>
-      <c r="AU3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>69</v>
+      <c r="BB3" t="s">
+        <v>100</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J4">
         <v>2003.1</v>
@@ -1393,141 +1570,162 @@
         <v>98151.9</v>
       </c>
       <c r="M4">
-        <v>1993.2</v>
-      </c>
-      <c r="N4" s="2">
-        <v>-485.1</v>
+        <v>2027.3</v>
+      </c>
+      <c r="N4" s="3">
+        <v>1185.8</v>
       </c>
       <c r="O4">
-        <v>-0.49</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W4" t="s">
         <v>17</v>
       </c>
       <c r="X4" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y4">
+        <v>77</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z4">
         <v>14</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>3</v>
       </c>
-      <c r="AA4" t="s">
-        <v>71</v>
-      </c>
       <c r="AB4" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AC4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD4" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AE4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK4" t="s">
         <v>88</v>
       </c>
-      <c r="AG4" t="s">
-        <v>94</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>81</v>
-      </c>
       <c r="AL4" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AM4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN4">
+        <v>90</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO4">
         <v>0.55</v>
       </c>
-      <c r="AO4">
+      <c r="AP4">
         <v>2.56</v>
       </c>
-      <c r="AP4">
+      <c r="AQ4">
         <v>6.47</v>
       </c>
-      <c r="AQ4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AR4">
+      <c r="AR4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AY4">
         <v>1957</v>
       </c>
-      <c r="AS4">
+      <c r="AZ4">
         <v>1957</v>
       </c>
-      <c r="AT4">
+      <c r="BA4">
         <v>1957</v>
       </c>
-      <c r="AU4" t="s">
-        <v>97</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>69</v>
+      <c r="BB4" t="s">
+        <v>105</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J5">
         <v>1397.7</v>
@@ -1548,132 +1746,153 @@
         <v>-1.42</v>
       </c>
       <c r="P5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W5" t="s">
         <v>17</v>
       </c>
       <c r="X5" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y5">
+        <v>77</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z5">
         <v>13</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>4</v>
       </c>
-      <c r="AA5" t="s">
-        <v>71</v>
-      </c>
       <c r="AB5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AC5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AE5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF5" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="AH5" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="AI5" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AJ5" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AK5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AL5" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AM5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN5">
+        <v>90</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO5">
         <v>0.72</v>
       </c>
-      <c r="AO5">
+      <c r="AP5">
         <v>4.06</v>
       </c>
-      <c r="AP5">
+      <c r="AQ5">
         <v>11.77</v>
       </c>
-      <c r="AQ5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AR5">
+      <c r="AR5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AY5">
         <v>1303.2</v>
       </c>
-      <c r="AS5">
+      <c r="AZ5">
         <v>1303.2</v>
       </c>
-      <c r="AT5">
+      <c r="BA5">
         <v>1303.2</v>
       </c>
-      <c r="AU5" t="s">
-        <v>103</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>69</v>
+      <c r="BB5" t="s">
+        <v>111</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J6">
         <v>838.9</v>
@@ -1694,132 +1913,153 @@
         <v>-4.58</v>
       </c>
       <c r="P6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W6" t="s">
         <v>17</v>
       </c>
       <c r="X6" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y6">
+        <v>77</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z6">
         <v>13</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>3</v>
       </c>
-      <c r="AA6" t="s">
-        <v>71</v>
-      </c>
       <c r="AB6" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AC6" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD6" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AE6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF6" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="AG6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="AH6" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AI6" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="AJ6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AK6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AL6" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AM6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN6">
+        <v>90</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO6">
         <v>1.22</v>
       </c>
-      <c r="AO6">
+      <c r="AP6">
         <v>4.91</v>
       </c>
-      <c r="AP6">
+      <c r="AQ6">
         <v>15.81</v>
       </c>
-      <c r="AQ6" t="s">
-        <v>102</v>
-      </c>
-      <c r="AR6">
+      <c r="AR6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AY6">
         <v>770</v>
       </c>
-      <c r="AS6">
+      <c r="AZ6">
         <v>770</v>
       </c>
-      <c r="AT6">
+      <c r="BA6">
         <v>721.4</v>
       </c>
-      <c r="AU6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>69</v>
+      <c r="BB6" t="s">
+        <v>116</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J7">
         <v>437.8</v>
@@ -1840,132 +2080,153 @@
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W7" t="s">
         <v>17</v>
       </c>
       <c r="X7" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y7">
+        <v>77</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z7">
         <v>11</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>5</v>
       </c>
-      <c r="AA7" t="s">
-        <v>71</v>
-      </c>
       <c r="AB7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AC7" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD7" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AE7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF7" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="AG7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="AH7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="AI7" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="AJ7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AK7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AL7" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AM7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN7">
+        <v>90</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO7">
         <v>0.22</v>
       </c>
-      <c r="AO7">
+      <c r="AP7">
         <v>3.42</v>
       </c>
-      <c r="AP7">
+      <c r="AQ7">
         <v>9.13</v>
       </c>
-      <c r="AQ7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AR7">
+      <c r="AR7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AY7">
         <v>425.45</v>
       </c>
-      <c r="AS7">
+      <c r="AZ7">
         <v>423.3</v>
       </c>
-      <c r="AT7">
+      <c r="BA7">
         <v>422.15</v>
       </c>
-      <c r="AU7" t="s">
-        <v>112</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>69</v>
+      <c r="BB7" t="s">
+        <v>120</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J8">
         <v>2965.4</v>
@@ -1986,107 +2247,128 @@
         <v>-0.18</v>
       </c>
       <c r="P8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W8" t="s">
         <v>17</v>
       </c>
       <c r="X8" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y8">
+        <v>77</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z8">
         <v>12</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>3</v>
       </c>
-      <c r="AA8" t="s">
-        <v>71</v>
-      </c>
       <c r="AB8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AC8" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AE8" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF8" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="AG8" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="AH8" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="AI8" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="AJ8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AK8" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AL8" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AM8" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN8">
+        <v>90</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO8">
         <v>1.21</v>
       </c>
-      <c r="AO8">
+      <c r="AP8">
         <v>3.14</v>
       </c>
-      <c r="AP8">
+      <c r="AQ8">
         <v>6.77</v>
       </c>
-      <c r="AQ8" t="s">
-        <v>96</v>
-      </c>
-      <c r="AR8">
+      <c r="AR8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>104</v>
+      </c>
+      <c r="AY8">
         <v>2903.2</v>
       </c>
-      <c r="AS8">
+      <c r="AZ8">
         <v>2903.2</v>
       </c>
-      <c r="AT8">
+      <c r="BA8">
         <v>2903.2</v>
       </c>
-      <c r="AU8" t="s">
-        <v>116</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>69</v>
+      <c r="BB8" t="s">
+        <v>124</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV1"/>
+  <autoFilter ref="A1:BC1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2094,7 +2376,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AV1"/>
+  <dimension ref="A1:BC4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2119,24 +2401,29 @@
     <col min="21" max="21" width="18" customWidth="1"/>
     <col min="22" max="22" width="14" customWidth="1"/>
     <col min="23" max="23" width="20" customWidth="1"/>
-    <col min="24" max="24" width="13" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
-    <col min="26" max="27" width="18" customWidth="1"/>
-    <col min="28" max="31" width="34" customWidth="1"/>
-    <col min="32" max="32" width="16" customWidth="1"/>
-    <col min="33" max="34" width="42" customWidth="1"/>
-    <col min="35" max="35" width="30" customWidth="1"/>
-    <col min="36" max="36" width="36" customWidth="1"/>
-    <col min="37" max="37" width="18" customWidth="1"/>
-    <col min="38" max="40" width="14" customWidth="1"/>
-    <col min="41" max="41" width="12" customWidth="1"/>
-    <col min="42" max="42" width="14" customWidth="1"/>
-    <col min="43" max="43" width="24" customWidth="1"/>
-    <col min="44" max="46" width="14" customWidth="1"/>
-    <col min="47" max="48" width="60" customWidth="1"/>
+    <col min="24" max="24" width="26" customWidth="1"/>
+    <col min="25" max="25" width="13" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
+    <col min="27" max="28" width="18" customWidth="1"/>
+    <col min="29" max="32" width="34" customWidth="1"/>
+    <col min="33" max="33" width="16" customWidth="1"/>
+    <col min="34" max="35" width="42" customWidth="1"/>
+    <col min="36" max="36" width="30" customWidth="1"/>
+    <col min="37" max="37" width="36" customWidth="1"/>
+    <col min="38" max="38" width="18" customWidth="1"/>
+    <col min="39" max="41" width="14" customWidth="1"/>
+    <col min="42" max="42" width="12" customWidth="1"/>
+    <col min="43" max="43" width="14" customWidth="1"/>
+    <col min="44" max="45" width="18" customWidth="1"/>
+    <col min="46" max="46" width="20" customWidth="1"/>
+    <col min="47" max="47" width="18" customWidth="1"/>
+    <col min="48" max="49" width="22" customWidth="1"/>
+    <col min="50" max="50" width="24" customWidth="1"/>
+    <col min="51" max="53" width="14" customWidth="1"/>
+    <col min="54" max="55" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2281,9 +2568,531 @@
       <c r="AV1" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="AW1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2">
+        <v>4506.7998046875</v>
+      </c>
+      <c r="N2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P2" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>77</v>
+      </c>
+      <c r="R2" t="s">
+        <v>77</v>
+      </c>
+      <c r="S2" t="s">
+        <v>77</v>
+      </c>
+      <c r="T2" t="s">
+        <v>77</v>
+      </c>
+      <c r="U2" t="s">
+        <v>77</v>
+      </c>
+      <c r="V2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z2">
+        <v>17</v>
+      </c>
+      <c r="AA2">
+        <v>4</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO2">
+        <v>0.99</v>
+      </c>
+      <c r="AP2">
+        <v>2.15</v>
+      </c>
+      <c r="AQ2">
+        <v>6.95</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS2">
+        <v>6.81</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AU2">
+        <v>2.21</v>
+      </c>
+      <c r="AV2">
+        <v>0.58</v>
+      </c>
+      <c r="AW2">
+        <v>0.99</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY2">
+        <v>4331</v>
+      </c>
+      <c r="AZ2">
+        <v>4305.8</v>
+      </c>
+      <c r="BA2">
+        <v>4305.8</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L3" t="s">
+        <v>77</v>
+      </c>
+      <c r="M3">
+        <v>1117.199951171875</v>
+      </c>
+      <c r="N3" t="s">
+        <v>77</v>
+      </c>
+      <c r="O3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>77</v>
+      </c>
+      <c r="R3" t="s">
+        <v>77</v>
+      </c>
+      <c r="S3" t="s">
+        <v>77</v>
+      </c>
+      <c r="T3" t="s">
+        <v>77</v>
+      </c>
+      <c r="U3" t="s">
+        <v>77</v>
+      </c>
+      <c r="V3" t="s">
+        <v>77</v>
+      </c>
+      <c r="W3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z3">
+        <v>16</v>
+      </c>
+      <c r="AA3">
+        <v>4</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>139</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO3">
+        <v>1.56</v>
+      </c>
+      <c r="AP3">
+        <v>2.97</v>
+      </c>
+      <c r="AQ3">
+        <v>9.83</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>143</v>
+      </c>
+      <c r="AU3">
+        <v>1.19</v>
+      </c>
+      <c r="AV3">
+        <v>0.98</v>
+      </c>
+      <c r="AW3">
+        <v>1.56</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY3">
+        <v>1048</v>
+      </c>
+      <c r="AZ3">
+        <v>1021.6</v>
+      </c>
+      <c r="BA3">
+        <v>1012.9</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>144</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" t="s">
+        <v>77</v>
+      </c>
+      <c r="M4">
+        <v>747.0499877929688</v>
+      </c>
+      <c r="N4" t="s">
+        <v>77</v>
+      </c>
+      <c r="O4" t="s">
+        <v>77</v>
+      </c>
+      <c r="P4" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R4" t="s">
+        <v>77</v>
+      </c>
+      <c r="S4" t="s">
+        <v>77</v>
+      </c>
+      <c r="T4" t="s">
+        <v>77</v>
+      </c>
+      <c r="U4" t="s">
+        <v>77</v>
+      </c>
+      <c r="V4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W4" t="s">
+        <v>17</v>
+      </c>
+      <c r="X4" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z4">
+        <v>12</v>
+      </c>
+      <c r="AA4">
+        <v>2</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO4">
+        <v>0.42</v>
+      </c>
+      <c r="AP4">
+        <v>4.83</v>
+      </c>
+      <c r="AQ4">
+        <v>9.1</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS4">
+        <v>8.22</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AU4">
+        <v>6</v>
+      </c>
+      <c r="AV4">
+        <v>1.81</v>
+      </c>
+      <c r="AW4">
+        <v>0.42</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY4">
+        <v>701.8</v>
+      </c>
+      <c r="AZ4">
+        <v>688.05</v>
+      </c>
+      <c r="BA4">
+        <v>688.05</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>151</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>77</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV1"/>
+  <autoFilter ref="A1:BC1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2291,7 +3100,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AV1"/>
+  <dimension ref="A1:BC1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2316,24 +3125,29 @@
     <col min="21" max="21" width="18" customWidth="1"/>
     <col min="22" max="22" width="14" customWidth="1"/>
     <col min="23" max="23" width="20" customWidth="1"/>
-    <col min="24" max="24" width="13" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
-    <col min="26" max="27" width="18" customWidth="1"/>
-    <col min="28" max="31" width="34" customWidth="1"/>
-    <col min="32" max="32" width="16" customWidth="1"/>
-    <col min="33" max="34" width="42" customWidth="1"/>
-    <col min="35" max="35" width="30" customWidth="1"/>
-    <col min="36" max="36" width="36" customWidth="1"/>
-    <col min="37" max="37" width="18" customWidth="1"/>
-    <col min="38" max="40" width="14" customWidth="1"/>
-    <col min="41" max="41" width="12" customWidth="1"/>
-    <col min="42" max="42" width="14" customWidth="1"/>
-    <col min="43" max="43" width="24" customWidth="1"/>
-    <col min="44" max="46" width="14" customWidth="1"/>
-    <col min="47" max="48" width="60" customWidth="1"/>
+    <col min="24" max="24" width="26" customWidth="1"/>
+    <col min="25" max="25" width="13" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
+    <col min="27" max="28" width="18" customWidth="1"/>
+    <col min="29" max="32" width="34" customWidth="1"/>
+    <col min="33" max="33" width="16" customWidth="1"/>
+    <col min="34" max="35" width="42" customWidth="1"/>
+    <col min="36" max="36" width="30" customWidth="1"/>
+    <col min="37" max="37" width="36" customWidth="1"/>
+    <col min="38" max="38" width="18" customWidth="1"/>
+    <col min="39" max="41" width="14" customWidth="1"/>
+    <col min="42" max="42" width="12" customWidth="1"/>
+    <col min="43" max="43" width="14" customWidth="1"/>
+    <col min="44" max="45" width="18" customWidth="1"/>
+    <col min="46" max="46" width="20" customWidth="1"/>
+    <col min="47" max="47" width="18" customWidth="1"/>
+    <col min="48" max="49" width="22" customWidth="1"/>
+    <col min="50" max="50" width="24" customWidth="1"/>
+    <col min="51" max="53" width="14" customWidth="1"/>
+    <col min="54" max="55" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2478,9 +3292,30 @@
       <c r="AV1" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="AW1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV1"/>
+  <autoFilter ref="A1:BC1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2488,7 +3323,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AV8"/>
+  <dimension ref="A1:BC11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2513,24 +3348,29 @@
     <col min="21" max="21" width="18" customWidth="1"/>
     <col min="22" max="22" width="14" customWidth="1"/>
     <col min="23" max="23" width="20" customWidth="1"/>
-    <col min="24" max="24" width="13" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
-    <col min="26" max="27" width="18" customWidth="1"/>
-    <col min="28" max="31" width="34" customWidth="1"/>
-    <col min="32" max="32" width="16" customWidth="1"/>
-    <col min="33" max="34" width="42" customWidth="1"/>
-    <col min="35" max="35" width="30" customWidth="1"/>
-    <col min="36" max="36" width="36" customWidth="1"/>
-    <col min="37" max="37" width="18" customWidth="1"/>
-    <col min="38" max="40" width="14" customWidth="1"/>
-    <col min="41" max="41" width="12" customWidth="1"/>
-    <col min="42" max="42" width="14" customWidth="1"/>
-    <col min="43" max="43" width="24" customWidth="1"/>
-    <col min="44" max="46" width="14" customWidth="1"/>
-    <col min="47" max="48" width="60" customWidth="1"/>
+    <col min="24" max="24" width="26" customWidth="1"/>
+    <col min="25" max="25" width="13" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
+    <col min="27" max="28" width="18" customWidth="1"/>
+    <col min="29" max="32" width="34" customWidth="1"/>
+    <col min="33" max="33" width="16" customWidth="1"/>
+    <col min="34" max="35" width="42" customWidth="1"/>
+    <col min="36" max="36" width="30" customWidth="1"/>
+    <col min="37" max="37" width="36" customWidth="1"/>
+    <col min="38" max="38" width="18" customWidth="1"/>
+    <col min="39" max="41" width="14" customWidth="1"/>
+    <col min="42" max="42" width="12" customWidth="1"/>
+    <col min="43" max="43" width="14" customWidth="1"/>
+    <col min="44" max="45" width="18" customWidth="1"/>
+    <col min="46" max="46" width="20" customWidth="1"/>
+    <col min="47" max="47" width="18" customWidth="1"/>
+    <col min="48" max="49" width="22" customWidth="1"/>
+    <col min="50" max="50" width="24" customWidth="1"/>
+    <col min="51" max="53" width="14" customWidth="1"/>
+    <col min="54" max="55" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2675,8 +3515,29 @@
       <c r="AV1" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="AW1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2684,145 +3545,166 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2">
-        <v>6612.5</v>
-      </c>
-      <c r="K2">
-        <v>15</v>
-      </c>
-      <c r="L2">
-        <v>99187.5</v>
+        <v>77</v>
+      </c>
+      <c r="J2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" t="s">
+        <v>77</v>
       </c>
       <c r="M2">
-        <v>6612</v>
-      </c>
-      <c r="N2" s="2">
-        <v>-7.5</v>
-      </c>
-      <c r="O2">
-        <v>-0.01</v>
+        <v>4506.7998046875</v>
+      </c>
+      <c r="N2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" t="s">
+        <v>77</v>
       </c>
       <c r="P2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W2" t="s">
         <v>17</v>
       </c>
       <c r="X2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y2">
-        <v>15</v>
+        <v>127</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>78</v>
       </c>
       <c r="Z2">
+        <v>17</v>
+      </c>
+      <c r="AA2">
         <v>4</v>
       </c>
-      <c r="AA2" t="s">
-        <v>71</v>
-      </c>
       <c r="AB2" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="AC2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD2" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="AE2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF2" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="AG2" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AH2" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AI2" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AJ2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AK2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AL2" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AM2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN2">
-        <v>2.02</v>
+        <v>90</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>91</v>
       </c>
       <c r="AO2">
-        <v>2.56</v>
+        <v>0.99</v>
       </c>
       <c r="AP2">
-        <v>8.7</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR2">
-        <v>6202.5</v>
+        <v>2.15</v>
+      </c>
+      <c r="AQ2">
+        <v>6.95</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>90</v>
       </c>
       <c r="AS2">
-        <v>6202.5</v>
-      </c>
-      <c r="AT2">
-        <v>6202.5</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>69</v>
+        <v>6.81</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AU2">
+        <v>2.21</v>
+      </c>
+      <c r="AV2">
+        <v>0.58</v>
+      </c>
+      <c r="AW2">
+        <v>0.99</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY2">
+        <v>4331</v>
+      </c>
+      <c r="AZ2">
+        <v>4305.8</v>
+      </c>
+      <c r="BA2">
+        <v>4305.8</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2830,145 +3712,166 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
-      </c>
-      <c r="J3">
-        <v>1360</v>
-      </c>
-      <c r="K3">
-        <v>73</v>
-      </c>
-      <c r="L3">
-        <v>99280</v>
+        <v>77</v>
+      </c>
+      <c r="J3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L3" t="s">
+        <v>77</v>
       </c>
       <c r="M3">
-        <v>1349.9</v>
-      </c>
-      <c r="N3" s="2">
-        <v>-737.3</v>
-      </c>
-      <c r="O3">
-        <v>-0.74</v>
+        <v>1117.199951171875</v>
+      </c>
+      <c r="N3" t="s">
+        <v>77</v>
+      </c>
+      <c r="O3" t="s">
+        <v>77</v>
       </c>
       <c r="P3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W3" t="s">
         <v>17</v>
       </c>
       <c r="X3" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y3">
-        <v>13</v>
+        <v>138</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>78</v>
       </c>
       <c r="Z3">
+        <v>16</v>
+      </c>
+      <c r="AA3">
         <v>4</v>
       </c>
-      <c r="AA3" t="s">
-        <v>71</v>
-      </c>
       <c r="AB3" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="AC3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD3" t="s">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="AE3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK3" t="s">
         <v>88</v>
       </c>
-      <c r="AG3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH3" t="s">
+      <c r="AL3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM3" t="s">
         <v>90</v>
       </c>
-      <c r="AI3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN3">
-        <v>0.32</v>
+      <c r="AN3" t="s">
+        <v>90</v>
       </c>
       <c r="AO3">
-        <v>3.04</v>
+        <v>1.56</v>
       </c>
       <c r="AP3">
-        <v>2.68</v>
-      </c>
-      <c r="AQ3" t="s">
+        <v>2.97</v>
+      </c>
+      <c r="AQ3">
+        <v>9.83</v>
+      </c>
+      <c r="AR3" t="s">
         <v>91</v>
       </c>
-      <c r="AR3">
-        <v>1321</v>
-      </c>
       <c r="AS3">
-        <v>1321</v>
-      </c>
-      <c r="AT3">
-        <v>1321</v>
-      </c>
-      <c r="AU3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>143</v>
+      </c>
+      <c r="AU3">
+        <v>1.19</v>
+      </c>
+      <c r="AV3">
+        <v>0.98</v>
+      </c>
+      <c r="AW3">
+        <v>1.56</v>
+      </c>
+      <c r="AX3" t="s">
         <v>92</v>
       </c>
-      <c r="AV3" t="s">
-        <v>69</v>
+      <c r="AY3">
+        <v>1048</v>
+      </c>
+      <c r="AZ3">
+        <v>1021.6</v>
+      </c>
+      <c r="BA3">
+        <v>1012.9</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>144</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2976,730 +3879,1336 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
-      </c>
-      <c r="J4">
-        <v>2003.1</v>
-      </c>
-      <c r="K4">
-        <v>49</v>
-      </c>
-      <c r="L4">
-        <v>98151.9</v>
+        <v>77</v>
+      </c>
+      <c r="J4" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" t="s">
+        <v>77</v>
       </c>
       <c r="M4">
-        <v>1993.2</v>
-      </c>
-      <c r="N4" s="2">
-        <v>-485.1</v>
-      </c>
-      <c r="O4">
-        <v>-0.49</v>
+        <v>747.0499877929688</v>
+      </c>
+      <c r="N4" t="s">
+        <v>77</v>
+      </c>
+      <c r="O4" t="s">
+        <v>77</v>
       </c>
       <c r="P4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W4" t="s">
         <v>17</v>
       </c>
       <c r="X4" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y4">
-        <v>14</v>
+        <v>146</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>147</v>
       </c>
       <c r="Z4">
-        <v>3</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>71</v>
+        <v>12</v>
+      </c>
+      <c r="AA4">
+        <v>2</v>
       </c>
       <c r="AB4" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AC4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD4" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AE4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF4" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK4" t="s">
         <v>88</v>
       </c>
-      <c r="AG4" t="s">
-        <v>94</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>81</v>
-      </c>
       <c r="AL4" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AM4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN4">
-        <v>0.55</v>
+        <v>90</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>91</v>
       </c>
       <c r="AO4">
-        <v>2.56</v>
+        <v>0.42</v>
       </c>
       <c r="AP4">
-        <v>6.47</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AR4">
-        <v>1957</v>
+        <v>4.83</v>
+      </c>
+      <c r="AQ4">
+        <v>9.1</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>91</v>
       </c>
       <c r="AS4">
-        <v>1957</v>
-      </c>
-      <c r="AT4">
-        <v>1957</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>97</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>69</v>
+        <v>8.22</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AU4">
+        <v>6</v>
+      </c>
+      <c r="AV4">
+        <v>1.81</v>
+      </c>
+      <c r="AW4">
+        <v>0.42</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY4">
+        <v>701.8</v>
+      </c>
+      <c r="AZ4">
+        <v>688.05</v>
+      </c>
+      <c r="BA4">
+        <v>688.05</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>151</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J5">
-        <v>1397.7</v>
+        <v>6612.5</v>
       </c>
       <c r="K5">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="L5">
-        <v>99236.7</v>
+        <v>99187.5</v>
       </c>
       <c r="M5">
-        <v>1377.8</v>
+        <v>6612</v>
       </c>
       <c r="N5" s="2">
-        <v>-1412.9</v>
+        <v>-7.5</v>
       </c>
       <c r="O5">
-        <v>-1.42</v>
+        <v>-0.01</v>
       </c>
       <c r="P5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W5" t="s">
         <v>17</v>
       </c>
       <c r="X5" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y5">
-        <v>13</v>
+        <v>77</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>78</v>
       </c>
       <c r="Z5">
+        <v>15</v>
+      </c>
+      <c r="AA5">
         <v>4</v>
       </c>
-      <c r="AA5" t="s">
-        <v>71</v>
-      </c>
       <c r="AB5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AC5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AE5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF5" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ5" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AK5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AL5" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AM5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN5">
-        <v>0.72</v>
+        <v>90</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>91</v>
       </c>
       <c r="AO5">
-        <v>4.06</v>
+        <v>2.02</v>
       </c>
       <c r="AP5">
-        <v>11.77</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AR5">
-        <v>1303.2</v>
-      </c>
-      <c r="AS5">
-        <v>1303.2</v>
-      </c>
-      <c r="AT5">
-        <v>1303.2</v>
+        <v>2.56</v>
+      </c>
+      <c r="AQ5">
+        <v>8.7</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>77</v>
       </c>
       <c r="AU5" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="AV5" t="s">
-        <v>69</v>
+        <v>77</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY5">
+        <v>6202.5</v>
+      </c>
+      <c r="AZ5">
+        <v>6202.5</v>
+      </c>
+      <c r="BA5">
+        <v>6202.5</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>93</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J6">
-        <v>838.9</v>
+        <v>1360</v>
       </c>
       <c r="K6">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L6">
-        <v>99829.1</v>
+        <v>99280</v>
       </c>
       <c r="M6">
-        <v>800.45</v>
+        <v>1349.9</v>
       </c>
       <c r="N6" s="2">
-        <v>-4575.55</v>
+        <v>-737.3</v>
       </c>
       <c r="O6">
-        <v>-4.58</v>
+        <v>-0.74</v>
       </c>
       <c r="P6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W6" t="s">
         <v>17</v>
       </c>
       <c r="X6" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y6">
+        <v>77</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z6">
         <v>13</v>
       </c>
-      <c r="Z6">
-        <v>3</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>71</v>
+      <c r="AA6">
+        <v>4</v>
       </c>
       <c r="AB6" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AC6" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD6" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AE6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF6" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="AG6" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="AH6" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="AI6" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="AJ6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AK6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AL6" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AM6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN6">
-        <v>1.22</v>
+        <v>90</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>91</v>
       </c>
       <c r="AO6">
-        <v>4.91</v>
+        <v>0.32</v>
       </c>
       <c r="AP6">
-        <v>15.81</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>102</v>
-      </c>
-      <c r="AR6">
-        <v>770</v>
-      </c>
-      <c r="AS6">
-        <v>770</v>
-      </c>
-      <c r="AT6">
-        <v>721.4</v>
+        <v>3.04</v>
+      </c>
+      <c r="AQ6">
+        <v>2.68</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>77</v>
       </c>
       <c r="AU6" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AV6" t="s">
-        <v>69</v>
+        <v>77</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY6">
+        <v>1321</v>
+      </c>
+      <c r="AZ6">
+        <v>1321</v>
+      </c>
+      <c r="BA6">
+        <v>1321</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>100</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J7">
-        <v>437.8</v>
+        <v>2003.1</v>
       </c>
       <c r="K7">
-        <v>228</v>
+        <v>49</v>
       </c>
       <c r="L7">
-        <v>99818.4</v>
+        <v>98151.9</v>
       </c>
       <c r="M7">
-        <v>437.8</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
+        <v>2027.3</v>
+      </c>
+      <c r="N7" s="3">
+        <v>1185.8</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W7" t="s">
         <v>17</v>
       </c>
       <c r="X7" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y7">
-        <v>11</v>
+        <v>77</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>78</v>
       </c>
       <c r="Z7">
-        <v>5</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>71</v>
+        <v>14</v>
+      </c>
+      <c r="AA7">
+        <v>3</v>
       </c>
       <c r="AB7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AC7" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AD7" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AE7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO7">
+        <v>0.55</v>
+      </c>
+      <c r="AP7">
+        <v>2.56</v>
+      </c>
+      <c r="AQ7">
+        <v>6.47</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AY7">
+        <v>1957</v>
+      </c>
+      <c r="AZ7">
+        <v>1957</v>
+      </c>
+      <c r="BA7">
+        <v>1957</v>
+      </c>
+      <c r="BB7" t="s">
         <v>105</v>
       </c>
-      <c r="AG7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>111</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN7">
-        <v>0.22</v>
-      </c>
-      <c r="AO7">
-        <v>3.42</v>
-      </c>
-      <c r="AP7">
-        <v>9.13</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AR7">
-        <v>425.45</v>
-      </c>
-      <c r="AS7">
-        <v>423.3</v>
-      </c>
-      <c r="AT7">
-        <v>422.15</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>112</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>69</v>
+      <c r="BC7" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J8">
-        <v>2965.4</v>
+        <v>1397.7</v>
       </c>
       <c r="K8">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="L8">
-        <v>97858.2</v>
+        <v>99236.7</v>
       </c>
       <c r="M8">
-        <v>2960</v>
+        <v>1377.8</v>
       </c>
       <c r="N8" s="2">
-        <v>-178.2</v>
+        <v>-1412.9</v>
       </c>
       <c r="O8">
-        <v>-0.18</v>
+        <v>-1.42</v>
       </c>
       <c r="P8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="S8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="W8" t="s">
         <v>17</v>
       </c>
       <c r="X8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z8">
+        <v>13</v>
+      </c>
+      <c r="AA8">
+        <v>4</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO8">
+        <v>0.72</v>
+      </c>
+      <c r="AP8">
+        <v>4.06</v>
+      </c>
+      <c r="AQ8">
+        <v>11.77</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AY8">
+        <v>1303.2</v>
+      </c>
+      <c r="AZ8">
+        <v>1303.2</v>
+      </c>
+      <c r="BA8">
+        <v>1303.2</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>111</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
         <v>70</v>
       </c>
-      <c r="Y8">
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J9">
+        <v>838.9</v>
+      </c>
+      <c r="K9">
+        <v>119</v>
+      </c>
+      <c r="L9">
+        <v>99829.1</v>
+      </c>
+      <c r="M9">
+        <v>800.45</v>
+      </c>
+      <c r="N9" s="2">
+        <v>-4575.55</v>
+      </c>
+      <c r="O9">
+        <v>-4.58</v>
+      </c>
+      <c r="P9" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>77</v>
+      </c>
+      <c r="R9" t="s">
+        <v>77</v>
+      </c>
+      <c r="S9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T9" t="s">
+        <v>77</v>
+      </c>
+      <c r="U9" t="s">
+        <v>77</v>
+      </c>
+      <c r="V9" t="s">
+        <v>77</v>
+      </c>
+      <c r="W9" t="s">
+        <v>17</v>
+      </c>
+      <c r="X9" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z9">
+        <v>13</v>
+      </c>
+      <c r="AA9">
+        <v>3</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO9">
+        <v>1.22</v>
+      </c>
+      <c r="AP9">
+        <v>4.91</v>
+      </c>
+      <c r="AQ9">
+        <v>15.81</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AY9">
+        <v>770</v>
+      </c>
+      <c r="AZ9">
+        <v>770</v>
+      </c>
+      <c r="BA9">
+        <v>721.4</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>116</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10">
+        <v>437.8</v>
+      </c>
+      <c r="K10">
+        <v>228</v>
+      </c>
+      <c r="L10">
+        <v>99818.4</v>
+      </c>
+      <c r="M10">
+        <v>437.8</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>77</v>
+      </c>
+      <c r="R10" t="s">
+        <v>77</v>
+      </c>
+      <c r="S10" t="s">
+        <v>77</v>
+      </c>
+      <c r="T10" t="s">
+        <v>77</v>
+      </c>
+      <c r="U10" t="s">
+        <v>77</v>
+      </c>
+      <c r="V10" t="s">
+        <v>77</v>
+      </c>
+      <c r="W10" t="s">
+        <v>17</v>
+      </c>
+      <c r="X10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z10">
+        <v>11</v>
+      </c>
+      <c r="AA10">
+        <v>5</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO10">
+        <v>0.22</v>
+      </c>
+      <c r="AP10">
+        <v>3.42</v>
+      </c>
+      <c r="AQ10">
+        <v>9.13</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>104</v>
+      </c>
+      <c r="AY10">
+        <v>425.45</v>
+      </c>
+      <c r="AZ10">
+        <v>423.3</v>
+      </c>
+      <c r="BA10">
+        <v>422.15</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>120</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11">
+        <v>2965.4</v>
+      </c>
+      <c r="K11">
+        <v>33</v>
+      </c>
+      <c r="L11">
+        <v>97858.2</v>
+      </c>
+      <c r="M11">
+        <v>2960</v>
+      </c>
+      <c r="N11" s="2">
+        <v>-178.2</v>
+      </c>
+      <c r="O11">
+        <v>-0.18</v>
+      </c>
+      <c r="P11" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>77</v>
+      </c>
+      <c r="R11" t="s">
+        <v>77</v>
+      </c>
+      <c r="S11" t="s">
+        <v>77</v>
+      </c>
+      <c r="T11" t="s">
+        <v>77</v>
+      </c>
+      <c r="U11" t="s">
+        <v>77</v>
+      </c>
+      <c r="V11" t="s">
+        <v>77</v>
+      </c>
+      <c r="W11" t="s">
+        <v>17</v>
+      </c>
+      <c r="X11" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z11">
         <v>12</v>
       </c>
-      <c r="Z8">
+      <c r="AA11">
         <v>3</v>
       </c>
-      <c r="AA8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI8" t="s">
+      <c r="AB11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ8" t="s">
+      <c r="AC11" t="s">
         <v>80</v>
       </c>
-      <c r="AK8" t="s">
+      <c r="AD11" t="s">
         <v>81</v>
       </c>
-      <c r="AL8" t="s">
+      <c r="AE11" t="s">
         <v>82</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="AF11" t="s">
         <v>83</v>
       </c>
-      <c r="AN8">
+      <c r="AG11" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO11">
         <v>1.21</v>
       </c>
-      <c r="AO8">
+      <c r="AP11">
         <v>3.14</v>
       </c>
-      <c r="AP8">
+      <c r="AQ11">
         <v>6.77</v>
       </c>
-      <c r="AQ8" t="s">
-        <v>96</v>
-      </c>
-      <c r="AR8">
+      <c r="AR11" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>104</v>
+      </c>
+      <c r="AY11">
         <v>2903.2</v>
       </c>
-      <c r="AS8">
+      <c r="AZ11">
         <v>2903.2</v>
       </c>
-      <c r="AT8">
+      <c r="BA11">
         <v>2903.2</v>
       </c>
-      <c r="AU8" t="s">
-        <v>116</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>69</v>
+      <c r="BB11" t="s">
+        <v>124</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV1"/>
+  <autoFilter ref="A1:BC1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="154">
   <si>
     <t>Metric</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-11T03:46:11.412Z</t>
+    <t>2026-07-11T04:37:29.742Z</t>
   </si>
   <si>
     <t>Pending Orders</t>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>completed daily/weekly closing candle</t>
+  </si>
+  <si>
+    <t>Session Rule</t>
+  </si>
+  <si>
+    <t>first actual exchange session after the signal date; weekends and market holidays are skipped</t>
   </si>
   <si>
     <t>Execution Window</t>
@@ -865,7 +871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -974,6 +980,14 @@
       </c>
       <c r="B13" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1039,163 +1053,163 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.25">
@@ -1203,28 +1217,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J2">
         <v>6612.5</v>
@@ -1245,34 +1259,34 @@
         <v>-0.01</v>
       </c>
       <c r="P2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z2">
         <v>15</v>
@@ -1281,43 +1295,43 @@
         <v>4</v>
       </c>
       <c r="AB2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AH2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AJ2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO2">
         <v>2.02</v>
@@ -1329,25 +1343,25 @@
         <v>8.7</v>
       </c>
       <c r="AR2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AY2">
         <v>6202.5</v>
@@ -1359,10 +1373,10 @@
         <v>6202.5</v>
       </c>
       <c r="BB2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="BC2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.25">
@@ -1370,28 +1384,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J3">
         <v>1360</v>
@@ -1412,34 +1426,34 @@
         <v>-0.74</v>
       </c>
       <c r="P3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z3">
         <v>13</v>
@@ -1448,43 +1462,43 @@
         <v>4</v>
       </c>
       <c r="AB3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AI3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AJ3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO3">
         <v>0.32</v>
@@ -1496,25 +1510,25 @@
         <v>2.68</v>
       </c>
       <c r="AR3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AY3">
         <v>1321</v>
@@ -1526,10 +1540,10 @@
         <v>1321</v>
       </c>
       <c r="BB3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BC3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.25">
@@ -1537,28 +1551,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J4">
         <v>2003.1</v>
@@ -1579,34 +1593,34 @@
         <v>1.21</v>
       </c>
       <c r="P4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z4">
         <v>14</v>
@@ -1615,43 +1629,43 @@
         <v>3</v>
       </c>
       <c r="AB4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AI4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AJ4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO4">
         <v>0.55</v>
@@ -1663,25 +1677,25 @@
         <v>6.47</v>
       </c>
       <c r="AR4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AY4">
         <v>1957</v>
@@ -1693,10 +1707,10 @@
         <v>1957</v>
       </c>
       <c r="BB4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BC4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.25">
@@ -1704,28 +1718,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J5">
         <v>1397.7</v>
@@ -1746,34 +1760,34 @@
         <v>-1.42</v>
       </c>
       <c r="P5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z5">
         <v>13</v>
@@ -1782,43 +1796,43 @@
         <v>4</v>
       </c>
       <c r="AB5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AH5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AI5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AJ5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO5">
         <v>0.72</v>
@@ -1830,25 +1844,25 @@
         <v>11.77</v>
       </c>
       <c r="AR5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AY5">
         <v>1303.2</v>
@@ -1860,10 +1874,10 @@
         <v>1303.2</v>
       </c>
       <c r="BB5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BC5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.25">
@@ -1871,28 +1885,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J6">
         <v>838.9</v>
@@ -1913,34 +1927,34 @@
         <v>-4.58</v>
       </c>
       <c r="P6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z6">
         <v>13</v>
@@ -1949,43 +1963,43 @@
         <v>3</v>
       </c>
       <c r="AB6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AH6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AI6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AJ6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO6">
         <v>1.22</v>
@@ -1997,25 +2011,25 @@
         <v>15.81</v>
       </c>
       <c r="AR6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AY6">
         <v>770</v>
@@ -2027,10 +2041,10 @@
         <v>721.4</v>
       </c>
       <c r="BB6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BC6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:55" x14ac:dyDescent="0.25">
@@ -2038,28 +2052,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J7">
         <v>437.8</v>
@@ -2080,34 +2094,34 @@
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z7">
         <v>11</v>
@@ -2116,43 +2130,43 @@
         <v>5</v>
       </c>
       <c r="AB7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AH7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AI7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AJ7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO7">
         <v>0.22</v>
@@ -2164,25 +2178,25 @@
         <v>9.13</v>
       </c>
       <c r="AR7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AY7">
         <v>425.45</v>
@@ -2194,10 +2208,10 @@
         <v>422.15</v>
       </c>
       <c r="BB7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BC7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.25">
@@ -2205,28 +2219,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J8">
         <v>2965.4</v>
@@ -2247,34 +2261,34 @@
         <v>-0.18</v>
       </c>
       <c r="P8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z8">
         <v>12</v>
@@ -2283,43 +2297,43 @@
         <v>3</v>
       </c>
       <c r="AB8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AH8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AI8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AJ8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO8">
         <v>1.21</v>
@@ -2331,25 +2345,25 @@
         <v>6.77</v>
       </c>
       <c r="AR8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AY8">
         <v>2903.2</v>
@@ -2361,10 +2375,10 @@
         <v>2903.2</v>
       </c>
       <c r="BB8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BC8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2431,163 +2445,163 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.25">
@@ -2598,73 +2612,73 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M2">
         <v>4506.7998046875</v>
       </c>
       <c r="N2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Y2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z2">
         <v>17</v>
@@ -2673,43 +2687,43 @@
         <v>4</v>
       </c>
       <c r="AB2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AC2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AE2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AG2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AH2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AI2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AJ2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AM2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO2">
         <v>0.99</v>
@@ -2721,13 +2735,13 @@
         <v>6.95</v>
       </c>
       <c r="AR2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AS2">
         <v>6.81</v>
       </c>
       <c r="AT2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AU2">
         <v>2.21</v>
@@ -2739,7 +2753,7 @@
         <v>0.99</v>
       </c>
       <c r="AX2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AY2">
         <v>4331</v>
@@ -2751,10 +2765,10 @@
         <v>4305.8</v>
       </c>
       <c r="BB2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BC2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.25">
@@ -2765,73 +2779,73 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M3">
         <v>1117.199951171875</v>
       </c>
       <c r="N3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Y3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z3">
         <v>16</v>
@@ -2840,43 +2854,43 @@
         <v>4</v>
       </c>
       <c r="AB3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AC3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AE3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AG3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AH3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AI3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AJ3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AM3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AO3">
         <v>1.56</v>
@@ -2888,13 +2902,13 @@
         <v>9.83</v>
       </c>
       <c r="AR3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS3">
         <v>0</v>
       </c>
       <c r="AT3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AU3">
         <v>1.19</v>
@@ -2906,7 +2920,7 @@
         <v>1.56</v>
       </c>
       <c r="AX3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AY3">
         <v>1048</v>
@@ -2918,10 +2932,10 @@
         <v>1012.9</v>
       </c>
       <c r="BB3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BC3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.25">
@@ -2932,73 +2946,73 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M4">
         <v>747.0499877929688</v>
       </c>
       <c r="N4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Y4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Z4">
         <v>12</v>
@@ -3007,43 +3021,43 @@
         <v>2</v>
       </c>
       <c r="AB4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AG4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AH4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AI4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AJ4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AM4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO4">
         <v>0.42</v>
@@ -3055,13 +3069,13 @@
         <v>9.1</v>
       </c>
       <c r="AR4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS4">
         <v>8.22</v>
       </c>
       <c r="AT4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AU4">
         <v>6</v>
@@ -3073,7 +3087,7 @@
         <v>0.42</v>
       </c>
       <c r="AX4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AY4">
         <v>701.8</v>
@@ -3085,10 +3099,10 @@
         <v>688.05</v>
       </c>
       <c r="BB4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BC4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3155,163 +3169,163 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3378,163 +3392,163 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.25">
@@ -3545,73 +3559,73 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M2">
         <v>4506.7998046875</v>
       </c>
       <c r="N2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Y2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z2">
         <v>17</v>
@@ -3620,43 +3634,43 @@
         <v>4</v>
       </c>
       <c r="AB2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AC2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AE2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AG2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AH2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AI2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AJ2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AM2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO2">
         <v>0.99</v>
@@ -3668,13 +3682,13 @@
         <v>6.95</v>
       </c>
       <c r="AR2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AS2">
         <v>6.81</v>
       </c>
       <c r="AT2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AU2">
         <v>2.21</v>
@@ -3686,7 +3700,7 @@
         <v>0.99</v>
       </c>
       <c r="AX2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AY2">
         <v>4331</v>
@@ -3698,10 +3712,10 @@
         <v>4305.8</v>
       </c>
       <c r="BB2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BC2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.25">
@@ -3712,73 +3726,73 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M3">
         <v>1117.199951171875</v>
       </c>
       <c r="N3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Y3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z3">
         <v>16</v>
@@ -3787,43 +3801,43 @@
         <v>4</v>
       </c>
       <c r="AB3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AC3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AE3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AG3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AH3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AI3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AJ3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AM3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AO3">
         <v>1.56</v>
@@ -3835,13 +3849,13 @@
         <v>9.83</v>
       </c>
       <c r="AR3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS3">
         <v>0</v>
       </c>
       <c r="AT3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AU3">
         <v>1.19</v>
@@ -3853,7 +3867,7 @@
         <v>1.56</v>
       </c>
       <c r="AX3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AY3">
         <v>1048</v>
@@ -3865,10 +3879,10 @@
         <v>1012.9</v>
       </c>
       <c r="BB3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BC3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.25">
@@ -3879,73 +3893,73 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M4">
         <v>747.0499877929688</v>
       </c>
       <c r="N4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Y4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Z4">
         <v>12</v>
@@ -3954,43 +3968,43 @@
         <v>2</v>
       </c>
       <c r="AB4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AG4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AH4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AI4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AJ4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AM4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO4">
         <v>0.42</v>
@@ -4002,13 +4016,13 @@
         <v>9.1</v>
       </c>
       <c r="AR4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS4">
         <v>8.22</v>
       </c>
       <c r="AT4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AU4">
         <v>6</v>
@@ -4020,7 +4034,7 @@
         <v>0.42</v>
       </c>
       <c r="AX4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AY4">
         <v>701.8</v>
@@ -4032,10 +4046,10 @@
         <v>688.05</v>
       </c>
       <c r="BB4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BC4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.25">
@@ -4043,28 +4057,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J5">
         <v>6612.5</v>
@@ -4085,34 +4099,34 @@
         <v>-0.01</v>
       </c>
       <c r="P5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z5">
         <v>15</v>
@@ -4121,43 +4135,43 @@
         <v>4</v>
       </c>
       <c r="AB5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AH5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AJ5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO5">
         <v>2.02</v>
@@ -4169,25 +4183,25 @@
         <v>8.7</v>
       </c>
       <c r="AR5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AY5">
         <v>6202.5</v>
@@ -4199,10 +4213,10 @@
         <v>6202.5</v>
       </c>
       <c r="BB5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="BC5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.25">
@@ -4210,28 +4224,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J6">
         <v>1360</v>
@@ -4252,34 +4266,34 @@
         <v>-0.74</v>
       </c>
       <c r="P6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z6">
         <v>13</v>
@@ -4288,43 +4302,43 @@
         <v>4</v>
       </c>
       <c r="AB6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AI6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO6">
         <v>0.32</v>
@@ -4336,25 +4350,25 @@
         <v>2.68</v>
       </c>
       <c r="AR6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AY6">
         <v>1321</v>
@@ -4366,10 +4380,10 @@
         <v>1321</v>
       </c>
       <c r="BB6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BC6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:55" x14ac:dyDescent="0.25">
@@ -4377,28 +4391,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J7">
         <v>2003.1</v>
@@ -4419,34 +4433,34 @@
         <v>1.21</v>
       </c>
       <c r="P7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z7">
         <v>14</v>
@@ -4455,43 +4469,43 @@
         <v>3</v>
       </c>
       <c r="AB7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AI7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AJ7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO7">
         <v>0.55</v>
@@ -4503,25 +4517,25 @@
         <v>6.47</v>
       </c>
       <c r="AR7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AY7">
         <v>1957</v>
@@ -4533,10 +4547,10 @@
         <v>1957</v>
       </c>
       <c r="BB7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BC7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.25">
@@ -4544,28 +4558,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J8">
         <v>1397.7</v>
@@ -4586,34 +4600,34 @@
         <v>-1.42</v>
       </c>
       <c r="P8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z8">
         <v>13</v>
@@ -4622,43 +4636,43 @@
         <v>4</v>
       </c>
       <c r="AB8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AH8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AI8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AJ8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO8">
         <v>0.72</v>
@@ -4670,25 +4684,25 @@
         <v>11.77</v>
       </c>
       <c r="AR8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AY8">
         <v>1303.2</v>
@@ -4700,10 +4714,10 @@
         <v>1303.2</v>
       </c>
       <c r="BB8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BC8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.25">
@@ -4711,28 +4725,28 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J9">
         <v>838.9</v>
@@ -4753,34 +4767,34 @@
         <v>-4.58</v>
       </c>
       <c r="P9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z9">
         <v>13</v>
@@ -4789,43 +4803,43 @@
         <v>3</v>
       </c>
       <c r="AB9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AH9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AI9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AJ9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO9">
         <v>1.22</v>
@@ -4837,25 +4851,25 @@
         <v>15.81</v>
       </c>
       <c r="AR9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AY9">
         <v>770</v>
@@ -4867,10 +4881,10 @@
         <v>721.4</v>
       </c>
       <c r="BB9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BC9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.25">
@@ -4878,28 +4892,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J10">
         <v>437.8</v>
@@ -4920,34 +4934,34 @@
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z10">
         <v>11</v>
@@ -4956,43 +4970,43 @@
         <v>5</v>
       </c>
       <c r="AB10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AH10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AI10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AJ10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO10">
         <v>0.22</v>
@@ -5004,25 +5018,25 @@
         <v>9.13</v>
       </c>
       <c r="AR10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AY10">
         <v>425.45</v>
@@ -5034,10 +5048,10 @@
         <v>422.15</v>
       </c>
       <c r="BB10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BC10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:55" x14ac:dyDescent="0.25">
@@ -5045,28 +5059,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J11">
         <v>2965.4</v>
@@ -5087,34 +5101,34 @@
         <v>-0.18</v>
       </c>
       <c r="P11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z11">
         <v>12</v>
@@ -5123,43 +5137,43 @@
         <v>3</v>
       </c>
       <c r="AB11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AH11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AI11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AJ11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AK11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO11">
         <v>1.21</v>
@@ -5171,25 +5185,25 @@
         <v>6.77</v>
       </c>
       <c r="AR11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AT11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AU11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AV11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AW11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AY11">
         <v>2903.2</v>
@@ -5201,10 +5215,10 @@
         <v>2903.2</v>
       </c>
       <c r="BB11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BC11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -28,7 +28,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-11T05:24:17.915Z</t>
+    <t>2026-07-11T05:29:16.885Z</t>
   </si>
   <si>
     <t>Total Capital</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="230">
   <si>
     <t>Metric</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-13T03:47:35.775Z</t>
+    <t>2026-07-13T04:19:25.451Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1137,7 +1137,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>1011905.67</v>
+        <v>1010607.27</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1145,7 +1145,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>898772.15</v>
+        <v>850664.15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1161,7 +1161,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>109117.27</v>
+        <v>157225.27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1169,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>89.88</v>
+        <v>85.07</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1177,7 +1177,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>34294.15</v>
+        <v>32820.72</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1185,7 +1185,7 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>3.43</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1241,7 +1241,7 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>4016.25</v>
+        <v>2717.85</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1668,8 +1668,8 @@
       <c r="AC2">
         <v>2648.1</v>
       </c>
-      <c r="AD2" t="s">
-        <v>105</v>
+      <c r="AD2">
+        <v>0.16</v>
       </c>
       <c r="AE2">
         <v>0</v>
@@ -1827,19 +1827,19 @@
         <v>2004.5</v>
       </c>
       <c r="K3">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="L3">
         <v>49</v>
       </c>
       <c r="M3">
-        <v>98220.5</v>
+        <v>50112.5</v>
       </c>
       <c r="N3">
         <v>2058.6</v>
       </c>
       <c r="O3" s="2">
-        <v>2650.9</v>
+        <v>1352.5</v>
       </c>
       <c r="P3">
         <v>2.7</v>
@@ -1878,16 +1878,16 @@
         <v>1974.43</v>
       </c>
       <c r="AB3">
-        <v>1974.43</v>
+        <v>2015.38</v>
       </c>
       <c r="AC3">
         <v>1473.43</v>
       </c>
-      <c r="AD3" t="s">
-        <v>105</v>
+      <c r="AD3">
+        <v>1.8</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -2098,8 +2098,8 @@
       <c r="AC4">
         <v>2255</v>
       </c>
-      <c r="AD4" t="s">
-        <v>105</v>
+      <c r="AD4">
+        <v>0.29</v>
       </c>
       <c r="AE4">
         <v>0</v>
@@ -4661,8 +4661,8 @@
       <c r="AC2">
         <v>2648.1</v>
       </c>
-      <c r="AD2" t="s">
-        <v>105</v>
+      <c r="AD2">
+        <v>0.16</v>
       </c>
       <c r="AE2">
         <v>0</v>
@@ -4820,19 +4820,19 @@
         <v>2004.5</v>
       </c>
       <c r="K3">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="L3">
         <v>49</v>
       </c>
       <c r="M3">
-        <v>98220.5</v>
+        <v>50112.5</v>
       </c>
       <c r="N3">
         <v>2058.6</v>
       </c>
       <c r="O3" s="2">
-        <v>2650.9</v>
+        <v>1352.5</v>
       </c>
       <c r="P3">
         <v>2.7</v>
@@ -4871,16 +4871,16 @@
         <v>1974.43</v>
       </c>
       <c r="AB3">
-        <v>1974.43</v>
+        <v>2015.38</v>
       </c>
       <c r="AC3">
         <v>1473.43</v>
       </c>
-      <c r="AD3" t="s">
-        <v>105</v>
+      <c r="AD3">
+        <v>1.8</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -5091,8 +5091,8 @@
       <c r="AC4">
         <v>2255</v>
       </c>
-      <c r="AD4" t="s">
-        <v>105</v>
+      <c r="AD4">
+        <v>0.29</v>
       </c>
       <c r="AE4">
         <v>0</v>
@@ -7449,10 +7449,10 @@
         <v>106</v>
       </c>
       <c r="H2">
-        <v>65107</v>
+        <v>93010</v>
       </c>
       <c r="I2">
-        <v>2418.5</v>
+        <v>3455</v>
       </c>
       <c r="J2">
         <v>8955.5</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="230">
   <si>
     <t>Metric</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-13T04:19:25.451Z</t>
+    <t>2026-07-13T04:41:16.905Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1883,8 +1883,8 @@
       <c r="AC3">
         <v>1473.43</v>
       </c>
-      <c r="AD3">
-        <v>1.8</v>
+      <c r="AD3" t="s">
+        <v>105</v>
       </c>
       <c r="AE3">
         <v>1</v>
@@ -4876,8 +4876,8 @@
       <c r="AC3">
         <v>1473.43</v>
       </c>
-      <c r="AD3">
-        <v>1.8</v>
+      <c r="AD3" t="s">
+        <v>105</v>
       </c>
       <c r="AE3">
         <v>1</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -28,7 +28,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-13T04:41:16.905Z</t>
+    <t>2026-07-13T04:52:25.582Z</t>
   </si>
   <si>
     <t>Total Capital</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -28,7 +28,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-13T04:52:25.582Z</t>
+    <t>2026-07-13T05:14:57.794Z</t>
   </si>
   <si>
     <t>Total Capital</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -28,7 +28,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-13T05:37:42.524Z</t>
+    <t>2026-07-13T05:41:37.101Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -376,7 +376,7 @@
     <t>14/26</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Bollinger trend/range context; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Bollinger trend/range context; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>RS trend follow-through; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Volume participation; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
@@ -427,7 +427,7 @@
     <t>15/26</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>RS trend follow-through; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
@@ -451,7 +451,7 @@
     <t>Retracement buy near 50-DMA</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>RS trend follow-through; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
@@ -478,7 +478,7 @@
     <t>17/21</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
@@ -505,7 +505,7 @@
     <t>16/21</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
@@ -520,7 +520,7 @@
     <t>15/21</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>RS trend follow-through; Volume participation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
@@ -535,7 +535,7 @@
     <t>14/21</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>RS trend follow-through; Volume participation; Volatility and liquidity control; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
@@ -547,7 +547,7 @@
     <t>KPIL</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>RS trend follow-through; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
@@ -562,7 +562,7 @@
     <t>SIS</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
@@ -574,7 +574,7 @@
     <t>PRUDENT</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
@@ -607,7 +607,7 @@
     <t>20/22</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>Volume participation</t>
@@ -616,7 +616,7 @@
     <t>66.43% (93/140)</t>
   </si>
   <si>
-    <t>Weekly RSI 55.15 is above 50. Daily RSI 60.53 is above 50. Weekly RS 6.8% is above 0. Daily long RS55 2.1% is above 0. Daily short RS21 2.3% is above 0. Daily close 4506.80 is above Supertrend(10, 3) 4193.48. Entry style: Retracement buy near 50-DMA. Price action strength: close is within 15% of 52-week high 5065.00. Retracement buy: price pulled back 6.81% from the 55-day high and reclaimed near 50-DMA 4407.24; support distance is 2.21%. Retracement confirmation: pullback volume ratio 0.58 and reclaim volume ratio 0.99 with candle close location 85.96%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.95% above daily Supertrend. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.15% of price. Liquidity strength: 20-day average turnover is Rs 3498340071.08. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 150; OI participation 2.01%, volume 72606.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 20/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session 09:15-09:20 IST window.</t>
+    <t>Weekly RSI 55.15 is above 50. Daily RSI 60.53 is above 50. Weekly RS 6.8% is above 0. Daily long RS55 2.1% is above 0. Daily short RS21 2.3% is above 0. Daily close 4506.80 is above Supertrend(10, 3) 4193.48. Entry style: Retracement buy near 50-DMA. Price action strength: close is within 15% of 52-week high 5065.00. Retracement buy: price pulled back 6.81% from the 55-day high and reclaimed near 50-DMA 4407.24; support distance is 2.21%. Retracement confirmation: pullback volume ratio 0.58 and reclaim volume ratio 0.99 with candle close location 85.96%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.95% above daily Supertrend. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.15% of price. Liquidity strength: 20-day average turnover is Rs 3498340071.08. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 150; OI participation 2.01%, volume 72606.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 20/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
   </si>
   <si>
     <t>PREMIERENE</t>
@@ -631,7 +631,7 @@
     <t>18/22</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>RS trend follow-through; Retracement/pullback buy setup; Risk reference discipline</t>
@@ -640,7 +640,7 @@
     <t>55D high retest</t>
   </si>
   <si>
-    <t>Weekly RSI 64.52 is above 50. Daily RSI 67.28 is above 50. Weekly RS 46.9% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 0.0% is above 0. Daily close 1117.20 is above Supertrend(10, 3) 1007.42. Entry style: Breakout buy. Price action strength: close crossed 55-day high 1103.90. Volume shocker: latest volume is 1.56x the 50-day average. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.97% of price. Liquidity strength: 20-day average turnover is Rs 1219054718.79. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 18/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session 09:15-09:20 IST window.</t>
+    <t>Weekly RSI 64.52 is above 50. Daily RSI 67.28 is above 50. Weekly RS 46.9% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 0.0% is above 0. Daily close 1117.20 is above Supertrend(10, 3) 1007.42. Entry style: Breakout buy. Price action strength: close crossed 55-day high 1103.90. Volume shocker: latest volume is 1.56x the 50-day average. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.97% of price. Liquidity strength: 20-day average turnover is Rs 1219054718.79. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 18/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
   </si>
   <si>
     <t>SBCL</t>
@@ -652,13 +652,13 @@
     <t>14/22</t>
   </si>
   <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:15 execution discipline</t>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
     <t>RS trend follow-through; Retracement/pullback buy setup; Volume participation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
   </si>
   <si>
-    <t>Weekly RSI 66.35 is above 50. Daily RSI 53.52 is above 50. Weekly RS 45.4% is above 0. Daily long RS55 21.9% is above 0. Daily short RS21 5.9% is above 0. Daily close 747.05 is above Supertrend(10, 3) 679.08. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 814.00. Retracement watch: pullback depth 8.22% is valid, but support/reclaim/volume/risk confirmation is incomplete. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 4.83% of price. Liquidity strength: 20-day average turnover is Rs 407588740.32. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:15 five-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 14/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session 09:15-09:20 IST window.</t>
+    <t>Weekly RSI 66.35 is above 50. Daily RSI 53.52 is above 50. Weekly RS 45.4% is above 0. Daily long RS55 21.9% is above 0. Daily short RS21 5.9% is above 0. Daily close 747.05 is above Supertrend(10, 3) 679.08. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 814.00. Retracement watch: pullback depth 8.22% is valid, but support/reclaim/volume/risk confirmation is incomplete. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 4.83% of price. Liquidity strength: 20-day average turnover is Rs 407588740.32. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 14/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
   </si>
   <si>
     <t>Industry</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -28,7 +28,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-13T05:41:37.101Z</t>
+    <t>2026-07-13T05:54:12.540Z</t>
   </si>
   <si>
     <t>Total Capital</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="245">
   <si>
     <t>Metric</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-13T05:54:12.540Z</t>
+    <t>2026-07-13T06:00:40.506Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -139,6 +139,9 @@
     <t>Entry Price</t>
   </si>
   <si>
+    <t>Initial Entry Price</t>
+  </si>
+  <si>
     <t>Entry Execution Method</t>
   </si>
   <si>
@@ -148,6 +151,9 @@
     <t>Original Quantity</t>
   </si>
   <si>
+    <t>Initial Quantity</t>
+  </si>
+  <si>
     <t>Invested Value</t>
   </si>
   <si>
@@ -199,6 +205,30 @@
     <t>Current R</t>
   </si>
   <si>
+    <t>Add-On Count</t>
+  </si>
+  <si>
+    <t>Pending Add</t>
+  </si>
+  <si>
+    <t>Last Add Date</t>
+  </si>
+  <si>
+    <t>Last Add Time</t>
+  </si>
+  <si>
+    <t>Last Add Price</t>
+  </si>
+  <si>
+    <t>Last Add Quantity</t>
+  </si>
+  <si>
+    <t>Add-On History</t>
+  </si>
+  <si>
+    <t>Add-On Decision</t>
+  </si>
+  <si>
     <t>Partial Exit Count</t>
   </si>
   <si>
@@ -346,6 +376,9 @@
     <t/>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Trend continuation buy</t>
   </si>
   <si>
@@ -392,9 +425,6 @@
   </si>
   <si>
     <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>50-DMA</t>
@@ -1323,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BU11"/>
+  <dimension ref="A1:CE11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1336,53 +1366,59 @@
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="19" max="20" width="18" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="30" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="18" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
-    <col min="26" max="26" width="20" customWidth="1"/>
-    <col min="27" max="31" width="14" customWidth="1"/>
-    <col min="32" max="32" width="12" customWidth="1"/>
-    <col min="33" max="33" width="18" customWidth="1"/>
-    <col min="34" max="34" width="20" customWidth="1"/>
-    <col min="35" max="35" width="22" customWidth="1"/>
-    <col min="36" max="36" width="24" customWidth="1"/>
-    <col min="37" max="37" width="26" customWidth="1"/>
-    <col min="38" max="38" width="13" customWidth="1"/>
-    <col min="39" max="39" width="14" customWidth="1"/>
-    <col min="40" max="41" width="18" customWidth="1"/>
-    <col min="42" max="42" width="14" customWidth="1"/>
-    <col min="43" max="44" width="28" customWidth="1"/>
-    <col min="45" max="45" width="30" customWidth="1"/>
-    <col min="46" max="46" width="14" customWidth="1"/>
-    <col min="47" max="50" width="34" customWidth="1"/>
-    <col min="51" max="51" width="16" customWidth="1"/>
-    <col min="52" max="53" width="42" customWidth="1"/>
-    <col min="54" max="54" width="30" customWidth="1"/>
-    <col min="55" max="55" width="36" customWidth="1"/>
-    <col min="56" max="56" width="18" customWidth="1"/>
-    <col min="57" max="59" width="14" customWidth="1"/>
-    <col min="60" max="60" width="12" customWidth="1"/>
-    <col min="61" max="61" width="14" customWidth="1"/>
-    <col min="62" max="63" width="18" customWidth="1"/>
-    <col min="64" max="64" width="20" customWidth="1"/>
-    <col min="65" max="65" width="18" customWidth="1"/>
-    <col min="66" max="67" width="22" customWidth="1"/>
-    <col min="68" max="68" width="24" customWidth="1"/>
-    <col min="69" max="71" width="14" customWidth="1"/>
-    <col min="72" max="73" width="60" customWidth="1"/>
+    <col min="22" max="22" width="13" customWidth="1"/>
+    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="24" max="24" width="30" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="14" customWidth="1"/>
+    <col min="28" max="28" width="20" customWidth="1"/>
+    <col min="29" max="33" width="14" customWidth="1"/>
+    <col min="34" max="34" width="12" customWidth="1"/>
+    <col min="35" max="39" width="14" customWidth="1"/>
+    <col min="40" max="40" width="18" customWidth="1"/>
+    <col min="41" max="42" width="60" customWidth="1"/>
+    <col min="43" max="43" width="18" customWidth="1"/>
+    <col min="44" max="44" width="20" customWidth="1"/>
+    <col min="45" max="45" width="22" customWidth="1"/>
+    <col min="46" max="46" width="24" customWidth="1"/>
+    <col min="47" max="47" width="26" customWidth="1"/>
+    <col min="48" max="48" width="13" customWidth="1"/>
+    <col min="49" max="49" width="14" customWidth="1"/>
+    <col min="50" max="51" width="18" customWidth="1"/>
+    <col min="52" max="52" width="14" customWidth="1"/>
+    <col min="53" max="54" width="28" customWidth="1"/>
+    <col min="55" max="55" width="30" customWidth="1"/>
+    <col min="56" max="56" width="14" customWidth="1"/>
+    <col min="57" max="60" width="34" customWidth="1"/>
+    <col min="61" max="61" width="16" customWidth="1"/>
+    <col min="62" max="63" width="42" customWidth="1"/>
+    <col min="64" max="64" width="30" customWidth="1"/>
+    <col min="65" max="65" width="36" customWidth="1"/>
+    <col min="66" max="66" width="18" customWidth="1"/>
+    <col min="67" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="12" customWidth="1"/>
+    <col min="71" max="71" width="14" customWidth="1"/>
+    <col min="72" max="73" width="18" customWidth="1"/>
+    <col min="74" max="74" width="20" customWidth="1"/>
+    <col min="75" max="75" width="18" customWidth="1"/>
+    <col min="76" max="77" width="22" customWidth="1"/>
+    <col min="78" max="78" width="24" customWidth="1"/>
+    <col min="79" max="81" width="14" customWidth="1"/>
+    <col min="82" max="83" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:83" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -1429,13 +1465,13 @@
         <v>44</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>47</v>
@@ -1450,13 +1486,13 @@
         <v>50</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>53</v>
@@ -1602,8 +1638,38 @@
       <c r="BU1" s="1" t="s">
         <v>100</v>
       </c>
+      <c r="BV1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1611,22 +1677,22 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I2" t="s">
         <v>29</v>
@@ -1634,197 +1700,227 @@
       <c r="J2">
         <v>214.01</v>
       </c>
-      <c r="K2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L2">
-        <v>291</v>
+      <c r="K2">
+        <v>214.01</v>
+      </c>
+      <c r="L2" t="s">
+        <v>117</v>
       </c>
       <c r="M2">
         <v>291</v>
       </c>
       <c r="N2">
+        <v>291</v>
+      </c>
+      <c r="O2">
+        <v>291</v>
+      </c>
+      <c r="P2">
         <v>62276.91</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>207.05</v>
       </c>
-      <c r="P2" s="2">
+      <c r="R2" s="2">
         <v>-2025.36</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>-3.25</v>
       </c>
-      <c r="R2" t="s">
-        <v>108</v>
-      </c>
-      <c r="S2" t="s">
-        <v>108</v>
-      </c>
       <c r="T2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB2" t="s">
         <v>29</v>
       </c>
-      <c r="AA2">
+      <c r="AC2">
         <v>179.24</v>
       </c>
-      <c r="AB2">
+      <c r="AD2">
         <v>179.24</v>
       </c>
-      <c r="AC2">
+      <c r="AE2">
         <v>196.45</v>
       </c>
-      <c r="AD2">
+      <c r="AF2">
         <v>196.45</v>
       </c>
-      <c r="AE2">
+      <c r="AG2">
         <v>5109.96</v>
       </c>
-      <c r="AF2">
+      <c r="AH2">
         <v>-0.4</v>
       </c>
-      <c r="AG2">
+      <c r="AI2">
         <v>0</v>
       </c>
-      <c r="AH2">
+      <c r="AJ2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ2">
         <v>0</v>
       </c>
-      <c r="AI2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM2">
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW2">
         <v>12</v>
       </c>
-      <c r="AN2">
+      <c r="AX2">
         <v>4</v>
       </c>
-      <c r="AO2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>117</v>
-      </c>
       <c r="AY2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="AZ2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP2" t="s">
         <v>119</v>
       </c>
-      <c r="BA2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>121</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG2">
+      <c r="BQ2">
         <v>0.55</v>
       </c>
-      <c r="BH2">
+      <c r="BR2">
         <v>4.35</v>
       </c>
-      <c r="BI2">
+      <c r="BS2">
         <v>13.66</v>
       </c>
-      <c r="BJ2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK2">
+      <c r="BT2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU2">
         <v>3.32</v>
       </c>
-      <c r="BL2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BM2">
+      <c r="BV2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BW2">
         <v>13.61</v>
       </c>
-      <c r="BN2">
+      <c r="BX2">
         <v>0.89</v>
       </c>
-      <c r="BO2">
+      <c r="BY2">
         <v>0.55</v>
       </c>
-      <c r="BP2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ2">
+      <c r="BZ2" t="s">
+        <v>137</v>
+      </c>
+      <c r="CA2">
         <v>199.5</v>
       </c>
-      <c r="BR2">
+      <c r="CB2">
         <v>196.45</v>
       </c>
-      <c r="BS2">
+      <c r="CC2">
         <v>186.53</v>
       </c>
-      <c r="BT2" t="s">
-        <v>128</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>108</v>
+      <c r="CD2" t="s">
+        <v>138</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1832,22 +1928,22 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I3" t="s">
         <v>29</v>
@@ -1855,197 +1951,227 @@
       <c r="J3">
         <v>2048.2</v>
       </c>
-      <c r="K3" t="s">
-        <v>107</v>
-      </c>
-      <c r="L3">
+      <c r="K3">
+        <v>2048.2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M3">
         <v>25</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>49</v>
       </c>
-      <c r="N3">
+      <c r="O3">
+        <v>49</v>
+      </c>
+      <c r="P3">
         <v>51205</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>2058.6</v>
       </c>
-      <c r="P3" s="3">
+      <c r="R3" s="3">
         <v>260</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>0.51</v>
       </c>
-      <c r="R3" t="s">
-        <v>108</v>
-      </c>
-      <c r="S3" t="s">
-        <v>108</v>
-      </c>
       <c r="T3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB3" t="s">
         <v>29</v>
       </c>
-      <c r="AA3">
+      <c r="AC3">
         <v>170.76</v>
       </c>
-      <c r="AB3">
+      <c r="AD3">
         <v>170.76</v>
       </c>
-      <c r="AC3">
+      <c r="AE3">
         <v>1974.43</v>
       </c>
-      <c r="AD3">
+      <c r="AF3">
         <v>2015.38</v>
       </c>
-      <c r="AE3">
+      <c r="AG3">
         <v>3614.73</v>
       </c>
-      <c r="AF3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG3">
+      <c r="AH3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ3">
         <v>1</v>
       </c>
-      <c r="AH3">
+      <c r="AR3">
         <v>-1048.8</v>
       </c>
-      <c r="AI3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM3">
+      <c r="AS3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW3">
         <v>11</v>
       </c>
-      <c r="AN3">
+      <c r="AX3">
         <v>4</v>
       </c>
-      <c r="AO3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ3" t="s">
+      <c r="AY3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>141</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>142</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>143</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>144</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>145</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>146</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>147</v>
+      </c>
+      <c r="BL3" t="s">
         <v>132</v>
       </c>
-      <c r="AR3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS3" t="s">
+      <c r="BM3" t="s">
         <v>133</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="BN3" t="s">
         <v>134</v>
       </c>
-      <c r="AU3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY3" t="s">
+      <c r="BO3" t="s">
         <v>135</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>136</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>137</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG3">
+      <c r="BP3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ3">
         <v>0.3</v>
       </c>
-      <c r="BH3">
+      <c r="BR3">
         <v>3.57</v>
       </c>
-      <c r="BI3">
+      <c r="BS3">
         <v>2.1</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK3">
+      <c r="BT3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU3">
         <v>10.28</v>
       </c>
-      <c r="BL3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BM3">
+      <c r="BV3" t="s">
+        <v>148</v>
+      </c>
+      <c r="BW3">
         <v>2.1</v>
       </c>
-      <c r="BN3">
+      <c r="BX3">
         <v>1.68</v>
       </c>
-      <c r="BO3">
+      <c r="BY3">
         <v>0.3</v>
       </c>
-      <c r="BP3" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ3">
+      <c r="BZ3" t="s">
+        <v>149</v>
+      </c>
+      <c r="CA3">
         <v>2002.3</v>
       </c>
-      <c r="BR3">
+      <c r="CB3">
         <v>1981</v>
       </c>
-      <c r="BS3">
+      <c r="CC3">
         <v>1981</v>
       </c>
-      <c r="BT3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>108</v>
+      <c r="CD3" t="s">
+        <v>150</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -2053,22 +2179,22 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G4" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H4" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I4" t="s">
         <v>29</v>
@@ -2076,220 +2202,250 @@
       <c r="J4">
         <v>4421.9</v>
       </c>
-      <c r="K4" t="s">
-        <v>107</v>
-      </c>
-      <c r="L4">
-        <v>22</v>
+      <c r="K4">
+        <v>4421.9</v>
+      </c>
+      <c r="L4" t="s">
+        <v>117</v>
       </c>
       <c r="M4">
         <v>22</v>
       </c>
       <c r="N4">
+        <v>22</v>
+      </c>
+      <c r="O4">
+        <v>22</v>
+      </c>
+      <c r="P4">
         <v>97281.8</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>4452</v>
       </c>
-      <c r="P4" s="3">
+      <c r="R4" s="3">
         <v>662.2</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>0.68</v>
       </c>
-      <c r="R4" t="s">
-        <v>108</v>
-      </c>
-      <c r="S4" t="s">
-        <v>108</v>
-      </c>
       <c r="T4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB4" t="s">
         <v>29</v>
       </c>
-      <c r="AA4">
+      <c r="AC4">
         <v>167.02</v>
       </c>
-      <c r="AB4">
+      <c r="AD4">
         <v>167.02</v>
       </c>
-      <c r="AC4">
+      <c r="AE4">
         <v>4319.5</v>
       </c>
-      <c r="AD4">
+      <c r="AF4">
         <v>4319.5</v>
       </c>
-      <c r="AE4">
+      <c r="AG4">
         <v>2252.8</v>
       </c>
-      <c r="AF4">
+      <c r="AH4">
         <v>0.29</v>
       </c>
-      <c r="AG4">
+      <c r="AI4">
         <v>0</v>
       </c>
-      <c r="AH4">
+      <c r="AJ4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ4">
         <v>0</v>
       </c>
-      <c r="AI4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM4">
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW4">
         <v>14</v>
       </c>
-      <c r="AN4">
+      <c r="AX4">
         <v>1</v>
       </c>
-      <c r="AO4" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>112</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>113</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>117</v>
-      </c>
       <c r="AY4" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>145</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>154</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>155</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>132</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>133</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>134</v>
+      </c>
+      <c r="BO4" t="s">
         <v>135</v>
       </c>
-      <c r="AZ4" t="s">
-        <v>144</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>145</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>121</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG4">
+      <c r="BP4" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ4">
         <v>0.65</v>
       </c>
-      <c r="BH4">
+      <c r="BR4">
         <v>2.9</v>
       </c>
-      <c r="BI4">
+      <c r="BS4">
         <v>5.2</v>
       </c>
-      <c r="BJ4" t="s">
-        <v>124</v>
-      </c>
-      <c r="BK4">
+      <c r="BT4" t="s">
+        <v>135</v>
+      </c>
+      <c r="BU4">
         <v>6.4</v>
       </c>
-      <c r="BL4" t="s">
-        <v>126</v>
-      </c>
-      <c r="BM4">
+      <c r="BV4" t="s">
+        <v>136</v>
+      </c>
+      <c r="BW4">
         <v>2.63</v>
       </c>
-      <c r="BN4">
+      <c r="BX4">
         <v>0.47</v>
       </c>
-      <c r="BO4">
+      <c r="BY4">
         <v>0.65</v>
       </c>
-      <c r="BP4" t="s">
-        <v>146</v>
-      </c>
-      <c r="BQ4">
+      <c r="BZ4" t="s">
+        <v>156</v>
+      </c>
+      <c r="CA4">
         <v>4335</v>
       </c>
-      <c r="BR4">
+      <c r="CB4">
         <v>4319.5</v>
       </c>
-      <c r="BS4">
+      <c r="CC4">
         <v>4319.5</v>
       </c>
-      <c r="BT4" t="s">
-        <v>147</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>108</v>
+      <c r="CD4" t="s">
+        <v>157</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G5" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H5" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -2297,220 +2453,250 @@
       <c r="J5">
         <v>6621.5</v>
       </c>
-      <c r="K5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L5">
-        <v>15</v>
+      <c r="K5">
+        <v>6621.5</v>
+      </c>
+      <c r="L5" t="s">
+        <v>117</v>
       </c>
       <c r="M5">
         <v>15</v>
       </c>
       <c r="N5">
+        <v>15</v>
+      </c>
+      <c r="O5">
+        <v>15</v>
+      </c>
+      <c r="P5">
         <v>99322.5</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>6839</v>
       </c>
-      <c r="P5" s="3">
+      <c r="R5" s="3">
         <v>3262.5</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>3.28</v>
       </c>
-      <c r="R5" t="s">
-        <v>108</v>
-      </c>
-      <c r="S5" t="s">
-        <v>108</v>
-      </c>
       <c r="T5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB5" t="s">
         <v>29</v>
       </c>
-      <c r="AA5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB5">
+      <c r="AC5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD5">
         <v>200.86</v>
       </c>
-      <c r="AC5">
+      <c r="AE5">
         <v>6083.5</v>
       </c>
-      <c r="AD5">
+      <c r="AF5">
         <v>6202.5</v>
       </c>
-      <c r="AE5">
+      <c r="AG5">
         <v>8070</v>
       </c>
-      <c r="AF5">
+      <c r="AH5">
         <v>0.4</v>
       </c>
-      <c r="AG5">
+      <c r="AI5">
         <v>0</v>
       </c>
-      <c r="AH5">
+      <c r="AJ5" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ5">
         <v>0</v>
       </c>
-      <c r="AI5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM5">
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW5">
         <v>15</v>
       </c>
-      <c r="AN5">
+      <c r="AX5">
         <v>4</v>
       </c>
-      <c r="AO5" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>117</v>
-      </c>
       <c r="AY5" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="AZ5" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="BA5" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="BB5" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="BC5" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="BD5" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="BE5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BF5" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG5">
+        <v>126</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>162</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>163</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>164</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>167</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ5">
         <v>2.02</v>
       </c>
-      <c r="BH5">
+      <c r="BR5">
         <v>2.56</v>
       </c>
-      <c r="BI5">
+      <c r="BS5">
         <v>8.7</v>
       </c>
-      <c r="BJ5" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ5">
+      <c r="BT5" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>149</v>
+      </c>
+      <c r="CA5">
         <v>6202.5</v>
       </c>
-      <c r="BR5">
+      <c r="CB5">
         <v>6202.5</v>
       </c>
-      <c r="BS5">
+      <c r="CC5">
         <v>6202.5</v>
       </c>
-      <c r="BT5" t="s">
-        <v>158</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>108</v>
+      <c r="CD5" t="s">
+        <v>168</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C6" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G6" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H6" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I6" t="s">
         <v>29</v>
@@ -2518,220 +2704,250 @@
       <c r="J6">
         <v>1995.8</v>
       </c>
-      <c r="K6" t="s">
-        <v>107</v>
-      </c>
-      <c r="L6">
-        <v>49</v>
+      <c r="K6">
+        <v>1995.8</v>
+      </c>
+      <c r="L6" t="s">
+        <v>117</v>
       </c>
       <c r="M6">
         <v>49</v>
       </c>
       <c r="N6">
+        <v>49</v>
+      </c>
+      <c r="O6">
+        <v>49</v>
+      </c>
+      <c r="P6">
         <v>97794.2</v>
       </c>
-      <c r="O6">
+      <c r="Q6">
         <v>2027.3</v>
       </c>
-      <c r="P6" s="3">
+      <c r="R6" s="3">
         <v>1543.5</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>1.58</v>
       </c>
-      <c r="R6" t="s">
-        <v>108</v>
-      </c>
-      <c r="S6" t="s">
-        <v>108</v>
-      </c>
       <c r="T6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB6" t="s">
         <v>29</v>
       </c>
-      <c r="AA6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB6">
+      <c r="AC6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD6">
         <v>166.92</v>
       </c>
-      <c r="AC6">
+      <c r="AE6">
         <v>1842.85</v>
       </c>
-      <c r="AD6">
+      <c r="AF6">
         <v>1957</v>
       </c>
-      <c r="AE6">
+      <c r="AG6">
         <v>7494.55</v>
       </c>
-      <c r="AF6">
+      <c r="AH6">
         <v>0.21</v>
       </c>
-      <c r="AG6">
+      <c r="AI6">
         <v>0</v>
       </c>
-      <c r="AH6">
+      <c r="AJ6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ6">
         <v>0</v>
       </c>
-      <c r="AI6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM6">
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW6">
         <v>14</v>
       </c>
-      <c r="AN6">
+      <c r="AX6">
         <v>3</v>
       </c>
-      <c r="AO6" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>117</v>
-      </c>
       <c r="AY6" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="AZ6" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="BA6" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="BB6" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="BC6" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="BD6" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="BE6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BF6" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG6">
+        <v>126</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>171</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>172</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>173</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>167</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ6">
         <v>0.55</v>
       </c>
-      <c r="BH6">
+      <c r="BR6">
         <v>2.56</v>
       </c>
-      <c r="BI6">
+      <c r="BS6">
         <v>6.47</v>
       </c>
-      <c r="BJ6" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP6" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ6">
+      <c r="BT6" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>137</v>
+      </c>
+      <c r="CA6">
         <v>1957</v>
       </c>
-      <c r="BR6">
+      <c r="CB6">
         <v>1957</v>
       </c>
-      <c r="BS6">
+      <c r="CC6">
         <v>1957</v>
       </c>
-      <c r="BT6" t="s">
-        <v>164</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>108</v>
+      <c r="CD6" t="s">
+        <v>174</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C7" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="F7" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H7" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I7" t="s">
         <v>29</v>
@@ -2739,220 +2955,250 @@
       <c r="J7">
         <v>1373.5</v>
       </c>
-      <c r="K7" t="s">
-        <v>107</v>
-      </c>
-      <c r="L7">
-        <v>71</v>
+      <c r="K7">
+        <v>1373.5</v>
+      </c>
+      <c r="L7" t="s">
+        <v>117</v>
       </c>
       <c r="M7">
         <v>71</v>
       </c>
       <c r="N7">
+        <v>71</v>
+      </c>
+      <c r="O7">
+        <v>71</v>
+      </c>
+      <c r="P7">
         <v>97518.5</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <v>1389.1</v>
       </c>
-      <c r="P7" s="3">
+      <c r="R7" s="3">
         <v>1107.6</v>
       </c>
-      <c r="Q7">
+      <c r="S7">
         <v>1.14</v>
       </c>
-      <c r="R7" t="s">
-        <v>108</v>
-      </c>
-      <c r="S7" t="s">
-        <v>108</v>
-      </c>
       <c r="T7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB7" t="s">
         <v>29</v>
       </c>
-      <c r="AA7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB7">
+      <c r="AC7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD7">
         <v>184.09</v>
       </c>
-      <c r="AC7">
+      <c r="AE7">
         <v>1285.88</v>
       </c>
-      <c r="AD7">
+      <c r="AF7">
         <v>1303.2</v>
       </c>
-      <c r="AE7">
+      <c r="AG7">
         <v>6221.02</v>
       </c>
-      <c r="AF7">
+      <c r="AH7">
         <v>0.18</v>
       </c>
-      <c r="AG7">
+      <c r="AI7">
         <v>0</v>
       </c>
-      <c r="AH7">
+      <c r="AJ7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ7">
         <v>0</v>
       </c>
-      <c r="AI7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM7">
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW7">
         <v>13</v>
       </c>
-      <c r="AN7">
+      <c r="AX7">
         <v>4</v>
       </c>
-      <c r="AO7" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>117</v>
-      </c>
       <c r="AY7" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>176</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>177</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>178</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM7" t="s">
         <v>166</v>
       </c>
-      <c r="AZ7" t="s">
+      <c r="BN7" t="s">
         <v>167</v>
       </c>
-      <c r="BA7" t="s">
-        <v>168</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>155</v>
-      </c>
-      <c r="BC7" t="s">
+      <c r="BO7" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ7">
+        <v>0.72</v>
+      </c>
+      <c r="BR7">
+        <v>4.06</v>
+      </c>
+      <c r="BS7">
+        <v>11.77</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ7" t="s">
         <v>156</v>
       </c>
-      <c r="BD7" t="s">
-        <v>157</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG7">
-        <v>0.72</v>
-      </c>
-      <c r="BH7">
-        <v>4.06</v>
-      </c>
-      <c r="BI7">
-        <v>11.77</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>146</v>
-      </c>
-      <c r="BQ7">
+      <c r="CA7">
         <v>1303.2</v>
       </c>
-      <c r="BR7">
+      <c r="CB7">
         <v>1303.2</v>
       </c>
-      <c r="BS7">
+      <c r="CC7">
         <v>1303.2</v>
       </c>
-      <c r="BT7" t="s">
-        <v>169</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>108</v>
+      <c r="CD7" t="s">
+        <v>179</v>
+      </c>
+      <c r="CE7" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G8" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H8" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I8" t="s">
         <v>29</v>
@@ -2960,220 +3206,250 @@
       <c r="J8">
         <v>811</v>
       </c>
-      <c r="K8" t="s">
-        <v>107</v>
-      </c>
-      <c r="L8">
-        <v>119</v>
+      <c r="K8">
+        <v>811</v>
+      </c>
+      <c r="L8" t="s">
+        <v>117</v>
       </c>
       <c r="M8">
         <v>119</v>
       </c>
       <c r="N8">
+        <v>119</v>
+      </c>
+      <c r="O8">
+        <v>119</v>
+      </c>
+      <c r="P8">
         <v>96509</v>
       </c>
-      <c r="O8">
+      <c r="Q8">
         <v>809.95</v>
       </c>
-      <c r="P8" s="2">
+      <c r="R8" s="2">
         <v>-124.95</v>
       </c>
-      <c r="Q8">
+      <c r="S8">
         <v>-0.13</v>
       </c>
-      <c r="R8" t="s">
-        <v>108</v>
-      </c>
-      <c r="S8" t="s">
-        <v>108</v>
-      </c>
       <c r="T8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB8" t="s">
         <v>29</v>
       </c>
-      <c r="AA8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB8">
+      <c r="AC8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD8">
         <v>170.78</v>
       </c>
-      <c r="AC8">
+      <c r="AE8">
         <v>771.79</v>
       </c>
-      <c r="AD8">
+      <c r="AF8">
         <v>771.79</v>
       </c>
-      <c r="AE8">
+      <c r="AG8">
         <v>4665.99</v>
       </c>
-      <c r="AF8">
+      <c r="AH8">
         <v>-0.03</v>
       </c>
-      <c r="AG8">
+      <c r="AI8">
         <v>0</v>
       </c>
-      <c r="AH8">
+      <c r="AJ8" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ8">
         <v>0</v>
       </c>
-      <c r="AI8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM8">
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW8">
         <v>13</v>
       </c>
-      <c r="AN8">
+      <c r="AX8">
         <v>3</v>
       </c>
-      <c r="AO8" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>117</v>
-      </c>
       <c r="AY8" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="AZ8" t="s">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="BA8" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="BB8" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="BC8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>181</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>182</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>167</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ8">
+        <v>1.22</v>
+      </c>
+      <c r="BR8">
+        <v>4.91</v>
+      </c>
+      <c r="BS8">
+        <v>15.81</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ8" t="s">
         <v>156</v>
       </c>
-      <c r="BD8" t="s">
-        <v>157</v>
-      </c>
-      <c r="BE8" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF8" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG8">
-        <v>1.22</v>
-      </c>
-      <c r="BH8">
-        <v>4.91</v>
-      </c>
-      <c r="BI8">
-        <v>15.81</v>
-      </c>
-      <c r="BJ8" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK8" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL8" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM8" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN8" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO8" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP8" t="s">
-        <v>146</v>
-      </c>
-      <c r="BQ8">
+      <c r="CA8">
         <v>770</v>
       </c>
-      <c r="BR8">
+      <c r="CB8">
         <v>770</v>
       </c>
-      <c r="BS8">
+      <c r="CC8">
         <v>721.4</v>
       </c>
-      <c r="BT8" t="s">
-        <v>174</v>
-      </c>
-      <c r="BU8" t="s">
-        <v>108</v>
+      <c r="CD8" t="s">
+        <v>184</v>
+      </c>
+      <c r="CE8" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="E9" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="F9" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G9" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H9" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I9" t="s">
         <v>29</v>
@@ -3181,220 +3457,250 @@
       <c r="J9">
         <v>1351.4</v>
       </c>
-      <c r="K9" t="s">
-        <v>107</v>
-      </c>
-      <c r="L9">
-        <v>73</v>
+      <c r="K9">
+        <v>1351.4</v>
+      </c>
+      <c r="L9" t="s">
+        <v>117</v>
       </c>
       <c r="M9">
         <v>73</v>
       </c>
       <c r="N9">
+        <v>73</v>
+      </c>
+      <c r="O9">
+        <v>73</v>
+      </c>
+      <c r="P9">
         <v>98652.2</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>1352</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>43.8</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>0.04</v>
       </c>
-      <c r="R9" t="s">
-        <v>108</v>
-      </c>
-      <c r="S9" t="s">
-        <v>108</v>
-      </c>
       <c r="T9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB9" t="s">
         <v>29</v>
       </c>
-      <c r="AA9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB9">
+      <c r="AC9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD9">
         <v>181.93</v>
       </c>
-      <c r="AC9">
+      <c r="AE9">
         <v>1251.2</v>
       </c>
-      <c r="AD9">
+      <c r="AF9">
         <v>1331.72</v>
       </c>
-      <c r="AE9">
+      <c r="AG9">
         <v>7314.6</v>
       </c>
-      <c r="AF9">
+      <c r="AH9">
         <v>0.01</v>
       </c>
-      <c r="AG9">
+      <c r="AI9">
         <v>0</v>
       </c>
-      <c r="AH9">
+      <c r="AJ9" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ9">
         <v>0</v>
       </c>
-      <c r="AI9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM9">
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW9">
         <v>13</v>
       </c>
-      <c r="AN9">
+      <c r="AX9">
         <v>4</v>
       </c>
-      <c r="AO9" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU9" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>117</v>
-      </c>
       <c r="AY9" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="AZ9" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="BA9" t="s">
-        <v>177</v>
+        <v>118</v>
       </c>
       <c r="BB9" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="BC9" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="BD9" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="BE9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BF9" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG9">
+        <v>126</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>171</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>187</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>167</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ9">
         <v>0.32</v>
       </c>
-      <c r="BH9">
+      <c r="BR9">
         <v>3.04</v>
       </c>
-      <c r="BI9">
+      <c r="BS9">
         <v>2.68</v>
       </c>
-      <c r="BJ9" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK9" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL9" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM9" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN9" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO9" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP9" t="s">
-        <v>178</v>
-      </c>
-      <c r="BQ9">
+      <c r="BT9" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>188</v>
+      </c>
+      <c r="CA9">
         <v>1321</v>
       </c>
-      <c r="BR9">
+      <c r="CB9">
         <v>1321</v>
       </c>
-      <c r="BS9">
+      <c r="CC9">
         <v>1321</v>
       </c>
-      <c r="BT9" t="s">
-        <v>179</v>
-      </c>
-      <c r="BU9" t="s">
-        <v>108</v>
+      <c r="CD9" t="s">
+        <v>189</v>
+      </c>
+      <c r="CE9" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D10" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="F10" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G10" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H10" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I10" t="s">
         <v>29</v>
@@ -3402,220 +3708,250 @@
       <c r="J10">
         <v>437.05</v>
       </c>
-      <c r="K10" t="s">
-        <v>107</v>
-      </c>
-      <c r="L10">
+      <c r="K10">
+        <v>437.05</v>
+      </c>
+      <c r="L10" t="s">
+        <v>117</v>
+      </c>
+      <c r="M10">
         <v>114</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>228</v>
       </c>
-      <c r="N10">
+      <c r="O10">
+        <v>228</v>
+      </c>
+      <c r="P10">
         <v>49823.7</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>435.5</v>
       </c>
-      <c r="P10" s="2">
+      <c r="R10" s="2">
         <v>-176.7</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>-0.35</v>
       </c>
-      <c r="R10" t="s">
-        <v>108</v>
-      </c>
-      <c r="S10" t="s">
-        <v>108</v>
-      </c>
       <c r="T10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB10" t="s">
         <v>29</v>
       </c>
-      <c r="AA10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB10">
+      <c r="AC10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD10">
         <v>92.43</v>
       </c>
-      <c r="AC10">
+      <c r="AE10">
         <v>402.78</v>
       </c>
-      <c r="AD10">
+      <c r="AF10">
         <v>422.15</v>
       </c>
-      <c r="AE10">
+      <c r="AG10">
         <v>7813.56</v>
       </c>
-      <c r="AF10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG10">
+      <c r="AH10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ10">
         <v>1</v>
       </c>
-      <c r="AH10">
+      <c r="AR10">
         <v>-501.6</v>
       </c>
-      <c r="AI10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM10">
+      <c r="AS10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW10">
         <v>11</v>
       </c>
-      <c r="AN10">
+      <c r="AX10">
         <v>5</v>
       </c>
-      <c r="AO10" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>117</v>
-      </c>
       <c r="AY10" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="AZ10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI10" t="s">
         <v>181</v>
       </c>
-      <c r="BA10" t="s">
-        <v>182</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>155</v>
-      </c>
-      <c r="BC10" t="s">
-        <v>156</v>
-      </c>
-      <c r="BD10" t="s">
-        <v>157</v>
-      </c>
-      <c r="BE10" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF10" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG10">
+      <c r="BJ10" t="s">
+        <v>191</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>192</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN10" t="s">
+        <v>167</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP10" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ10">
         <v>0.22</v>
       </c>
-      <c r="BH10">
+      <c r="BR10">
         <v>3.42</v>
       </c>
-      <c r="BI10">
+      <c r="BS10">
         <v>9.13</v>
       </c>
-      <c r="BJ10" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK10" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL10" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM10" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN10" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO10" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP10" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ10">
+      <c r="BT10" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ10" t="s">
+        <v>137</v>
+      </c>
+      <c r="CA10">
         <v>425.45</v>
       </c>
-      <c r="BR10">
+      <c r="CB10">
         <v>423.3</v>
       </c>
-      <c r="BS10">
+      <c r="CC10">
         <v>422.15</v>
       </c>
-      <c r="BT10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU10" t="s">
-        <v>108</v>
+      <c r="CD10" t="s">
+        <v>193</v>
+      </c>
+      <c r="CE10" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="F11" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G11" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I11" t="s">
         <v>29</v>
@@ -3623,198 +3959,228 @@
       <c r="J11">
         <v>2986</v>
       </c>
-      <c r="K11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L11">
-        <v>33</v>
+      <c r="K11">
+        <v>2986</v>
+      </c>
+      <c r="L11" t="s">
+        <v>117</v>
       </c>
       <c r="M11">
         <v>33</v>
       </c>
       <c r="N11">
+        <v>33</v>
+      </c>
+      <c r="O11">
+        <v>33</v>
+      </c>
+      <c r="P11">
         <v>98538</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>2983.2</v>
       </c>
-      <c r="P11" s="2">
+      <c r="R11" s="2">
         <v>-92.4</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>-0.09</v>
       </c>
-      <c r="R11" t="s">
-        <v>108</v>
-      </c>
-      <c r="S11" t="s">
-        <v>108</v>
-      </c>
       <c r="T11" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U11" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V11" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W11" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X11" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y11" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB11" t="s">
         <v>29</v>
       </c>
-      <c r="AA11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB11">
+      <c r="AC11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD11">
         <v>165.43</v>
       </c>
-      <c r="AC11">
+      <c r="AE11">
         <v>2728.17</v>
       </c>
-      <c r="AD11">
+      <c r="AF11">
         <v>2936.17</v>
       </c>
-      <c r="AE11">
+      <c r="AG11">
         <v>8508.39</v>
       </c>
-      <c r="AF11">
+      <c r="AH11">
         <v>-0.01</v>
       </c>
-      <c r="AG11">
+      <c r="AI11">
         <v>0</v>
       </c>
-      <c r="AH11">
+      <c r="AJ11" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ11">
         <v>0</v>
       </c>
-      <c r="AI11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM11">
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW11">
         <v>12</v>
       </c>
-      <c r="AN11">
+      <c r="AX11">
         <v>3</v>
       </c>
-      <c r="AO11" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU11" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>117</v>
-      </c>
       <c r="AY11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>176</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>195</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>196</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM11" t="s">
         <v>166</v>
       </c>
-      <c r="AZ11" t="s">
-        <v>185</v>
-      </c>
-      <c r="BA11" t="s">
-        <v>186</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>155</v>
-      </c>
-      <c r="BC11" t="s">
-        <v>156</v>
-      </c>
-      <c r="BD11" t="s">
-        <v>157</v>
-      </c>
-      <c r="BE11" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF11" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG11">
+      <c r="BN11" t="s">
+        <v>167</v>
+      </c>
+      <c r="BO11" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ11">
         <v>1.21</v>
       </c>
-      <c r="BH11">
+      <c r="BR11">
         <v>3.14</v>
       </c>
-      <c r="BI11">
+      <c r="BS11">
         <v>6.77</v>
       </c>
-      <c r="BJ11" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK11" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL11" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM11" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN11" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO11" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP11" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ11">
+      <c r="BT11" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ11" t="s">
+        <v>137</v>
+      </c>
+      <c r="CA11">
         <v>2903.2</v>
       </c>
-      <c r="BR11">
+      <c r="CB11">
         <v>2903.2</v>
       </c>
-      <c r="BS11">
+      <c r="CC11">
         <v>2903.2</v>
       </c>
-      <c r="BT11" t="s">
-        <v>187</v>
-      </c>
-      <c r="BU11" t="s">
-        <v>108</v>
+      <c r="CD11" t="s">
+        <v>197</v>
+      </c>
+      <c r="CE11" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BU1"/>
+  <autoFilter ref="A1:CE1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3822,7 +4188,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BU1"/>
+  <dimension ref="A1:CE1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3835,53 +4201,59 @@
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="19" max="20" width="18" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="30" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="18" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
-    <col min="26" max="26" width="20" customWidth="1"/>
-    <col min="27" max="31" width="14" customWidth="1"/>
-    <col min="32" max="32" width="12" customWidth="1"/>
-    <col min="33" max="33" width="18" customWidth="1"/>
-    <col min="34" max="34" width="20" customWidth="1"/>
-    <col min="35" max="35" width="22" customWidth="1"/>
-    <col min="36" max="36" width="24" customWidth="1"/>
-    <col min="37" max="37" width="26" customWidth="1"/>
-    <col min="38" max="38" width="13" customWidth="1"/>
-    <col min="39" max="39" width="14" customWidth="1"/>
-    <col min="40" max="41" width="18" customWidth="1"/>
-    <col min="42" max="42" width="14" customWidth="1"/>
-    <col min="43" max="44" width="28" customWidth="1"/>
-    <col min="45" max="45" width="30" customWidth="1"/>
-    <col min="46" max="46" width="14" customWidth="1"/>
-    <col min="47" max="50" width="34" customWidth="1"/>
-    <col min="51" max="51" width="16" customWidth="1"/>
-    <col min="52" max="53" width="42" customWidth="1"/>
-    <col min="54" max="54" width="30" customWidth="1"/>
-    <col min="55" max="55" width="36" customWidth="1"/>
-    <col min="56" max="56" width="18" customWidth="1"/>
-    <col min="57" max="59" width="14" customWidth="1"/>
-    <col min="60" max="60" width="12" customWidth="1"/>
-    <col min="61" max="61" width="14" customWidth="1"/>
-    <col min="62" max="63" width="18" customWidth="1"/>
-    <col min="64" max="64" width="20" customWidth="1"/>
-    <col min="65" max="65" width="18" customWidth="1"/>
-    <col min="66" max="67" width="22" customWidth="1"/>
-    <col min="68" max="68" width="24" customWidth="1"/>
-    <col min="69" max="71" width="14" customWidth="1"/>
-    <col min="72" max="73" width="60" customWidth="1"/>
+    <col min="22" max="22" width="13" customWidth="1"/>
+    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="24" max="24" width="30" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="14" customWidth="1"/>
+    <col min="28" max="28" width="20" customWidth="1"/>
+    <col min="29" max="33" width="14" customWidth="1"/>
+    <col min="34" max="34" width="12" customWidth="1"/>
+    <col min="35" max="39" width="14" customWidth="1"/>
+    <col min="40" max="40" width="18" customWidth="1"/>
+    <col min="41" max="42" width="60" customWidth="1"/>
+    <col min="43" max="43" width="18" customWidth="1"/>
+    <col min="44" max="44" width="20" customWidth="1"/>
+    <col min="45" max="45" width="22" customWidth="1"/>
+    <col min="46" max="46" width="24" customWidth="1"/>
+    <col min="47" max="47" width="26" customWidth="1"/>
+    <col min="48" max="48" width="13" customWidth="1"/>
+    <col min="49" max="49" width="14" customWidth="1"/>
+    <col min="50" max="51" width="18" customWidth="1"/>
+    <col min="52" max="52" width="14" customWidth="1"/>
+    <col min="53" max="54" width="28" customWidth="1"/>
+    <col min="55" max="55" width="30" customWidth="1"/>
+    <col min="56" max="56" width="14" customWidth="1"/>
+    <col min="57" max="60" width="34" customWidth="1"/>
+    <col min="61" max="61" width="16" customWidth="1"/>
+    <col min="62" max="63" width="42" customWidth="1"/>
+    <col min="64" max="64" width="30" customWidth="1"/>
+    <col min="65" max="65" width="36" customWidth="1"/>
+    <col min="66" max="66" width="18" customWidth="1"/>
+    <col min="67" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="12" customWidth="1"/>
+    <col min="71" max="71" width="14" customWidth="1"/>
+    <col min="72" max="73" width="18" customWidth="1"/>
+    <col min="74" max="74" width="20" customWidth="1"/>
+    <col min="75" max="75" width="18" customWidth="1"/>
+    <col min="76" max="77" width="22" customWidth="1"/>
+    <col min="78" max="78" width="24" customWidth="1"/>
+    <col min="79" max="81" width="14" customWidth="1"/>
+    <col min="82" max="83" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:83" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -3928,13 +4300,13 @@
         <v>44</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>47</v>
@@ -3949,13 +4321,13 @@
         <v>50</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>53</v>
@@ -4101,9 +4473,39 @@
       <c r="BU1" s="1" t="s">
         <v>100</v>
       </c>
+      <c r="BV1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BU1"/>
+  <autoFilter ref="A1:CE1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4111,7 +4513,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BU1"/>
+  <dimension ref="A1:CE1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -4124,53 +4526,59 @@
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="19" max="20" width="18" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="30" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="18" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
-    <col min="26" max="26" width="20" customWidth="1"/>
-    <col min="27" max="31" width="14" customWidth="1"/>
-    <col min="32" max="32" width="12" customWidth="1"/>
-    <col min="33" max="33" width="18" customWidth="1"/>
-    <col min="34" max="34" width="20" customWidth="1"/>
-    <col min="35" max="35" width="22" customWidth="1"/>
-    <col min="36" max="36" width="24" customWidth="1"/>
-    <col min="37" max="37" width="26" customWidth="1"/>
-    <col min="38" max="38" width="13" customWidth="1"/>
-    <col min="39" max="39" width="14" customWidth="1"/>
-    <col min="40" max="41" width="18" customWidth="1"/>
-    <col min="42" max="42" width="14" customWidth="1"/>
-    <col min="43" max="44" width="28" customWidth="1"/>
-    <col min="45" max="45" width="30" customWidth="1"/>
-    <col min="46" max="46" width="14" customWidth="1"/>
-    <col min="47" max="50" width="34" customWidth="1"/>
-    <col min="51" max="51" width="16" customWidth="1"/>
-    <col min="52" max="53" width="42" customWidth="1"/>
-    <col min="54" max="54" width="30" customWidth="1"/>
-    <col min="55" max="55" width="36" customWidth="1"/>
-    <col min="56" max="56" width="18" customWidth="1"/>
-    <col min="57" max="59" width="14" customWidth="1"/>
-    <col min="60" max="60" width="12" customWidth="1"/>
-    <col min="61" max="61" width="14" customWidth="1"/>
-    <col min="62" max="63" width="18" customWidth="1"/>
-    <col min="64" max="64" width="20" customWidth="1"/>
-    <col min="65" max="65" width="18" customWidth="1"/>
-    <col min="66" max="67" width="22" customWidth="1"/>
-    <col min="68" max="68" width="24" customWidth="1"/>
-    <col min="69" max="71" width="14" customWidth="1"/>
-    <col min="72" max="73" width="60" customWidth="1"/>
+    <col min="22" max="22" width="13" customWidth="1"/>
+    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="24" max="24" width="30" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="14" customWidth="1"/>
+    <col min="28" max="28" width="20" customWidth="1"/>
+    <col min="29" max="33" width="14" customWidth="1"/>
+    <col min="34" max="34" width="12" customWidth="1"/>
+    <col min="35" max="39" width="14" customWidth="1"/>
+    <col min="40" max="40" width="18" customWidth="1"/>
+    <col min="41" max="42" width="60" customWidth="1"/>
+    <col min="43" max="43" width="18" customWidth="1"/>
+    <col min="44" max="44" width="20" customWidth="1"/>
+    <col min="45" max="45" width="22" customWidth="1"/>
+    <col min="46" max="46" width="24" customWidth="1"/>
+    <col min="47" max="47" width="26" customWidth="1"/>
+    <col min="48" max="48" width="13" customWidth="1"/>
+    <col min="49" max="49" width="14" customWidth="1"/>
+    <col min="50" max="51" width="18" customWidth="1"/>
+    <col min="52" max="52" width="14" customWidth="1"/>
+    <col min="53" max="54" width="28" customWidth="1"/>
+    <col min="55" max="55" width="30" customWidth="1"/>
+    <col min="56" max="56" width="14" customWidth="1"/>
+    <col min="57" max="60" width="34" customWidth="1"/>
+    <col min="61" max="61" width="16" customWidth="1"/>
+    <col min="62" max="63" width="42" customWidth="1"/>
+    <col min="64" max="64" width="30" customWidth="1"/>
+    <col min="65" max="65" width="36" customWidth="1"/>
+    <col min="66" max="66" width="18" customWidth="1"/>
+    <col min="67" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="12" customWidth="1"/>
+    <col min="71" max="71" width="14" customWidth="1"/>
+    <col min="72" max="73" width="18" customWidth="1"/>
+    <col min="74" max="74" width="20" customWidth="1"/>
+    <col min="75" max="75" width="18" customWidth="1"/>
+    <col min="76" max="77" width="22" customWidth="1"/>
+    <col min="78" max="78" width="24" customWidth="1"/>
+    <col min="79" max="81" width="14" customWidth="1"/>
+    <col min="82" max="83" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:83" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -4217,13 +4625,13 @@
         <v>44</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>47</v>
@@ -4238,13 +4646,13 @@
         <v>50</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>53</v>
@@ -4390,9 +4798,39 @@
       <c r="BU1" s="1" t="s">
         <v>100</v>
       </c>
+      <c r="BV1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BU1"/>
+  <autoFilter ref="A1:CE1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4400,7 +4838,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BU14"/>
+  <dimension ref="A1:CE14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -4413,53 +4851,59 @@
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="19" max="20" width="18" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="30" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="18" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
-    <col min="26" max="26" width="20" customWidth="1"/>
-    <col min="27" max="31" width="14" customWidth="1"/>
-    <col min="32" max="32" width="12" customWidth="1"/>
-    <col min="33" max="33" width="18" customWidth="1"/>
-    <col min="34" max="34" width="20" customWidth="1"/>
-    <col min="35" max="35" width="22" customWidth="1"/>
-    <col min="36" max="36" width="24" customWidth="1"/>
-    <col min="37" max="37" width="26" customWidth="1"/>
-    <col min="38" max="38" width="13" customWidth="1"/>
-    <col min="39" max="39" width="14" customWidth="1"/>
-    <col min="40" max="41" width="18" customWidth="1"/>
-    <col min="42" max="42" width="14" customWidth="1"/>
-    <col min="43" max="44" width="28" customWidth="1"/>
-    <col min="45" max="45" width="30" customWidth="1"/>
-    <col min="46" max="46" width="14" customWidth="1"/>
-    <col min="47" max="50" width="34" customWidth="1"/>
-    <col min="51" max="51" width="16" customWidth="1"/>
-    <col min="52" max="53" width="42" customWidth="1"/>
-    <col min="54" max="54" width="30" customWidth="1"/>
-    <col min="55" max="55" width="36" customWidth="1"/>
-    <col min="56" max="56" width="18" customWidth="1"/>
-    <col min="57" max="59" width="14" customWidth="1"/>
-    <col min="60" max="60" width="12" customWidth="1"/>
-    <col min="61" max="61" width="14" customWidth="1"/>
-    <col min="62" max="63" width="18" customWidth="1"/>
-    <col min="64" max="64" width="20" customWidth="1"/>
-    <col min="65" max="65" width="18" customWidth="1"/>
-    <col min="66" max="67" width="22" customWidth="1"/>
-    <col min="68" max="68" width="24" customWidth="1"/>
-    <col min="69" max="71" width="14" customWidth="1"/>
-    <col min="72" max="73" width="60" customWidth="1"/>
+    <col min="22" max="22" width="13" customWidth="1"/>
+    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="24" max="24" width="30" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="14" customWidth="1"/>
+    <col min="28" max="28" width="20" customWidth="1"/>
+    <col min="29" max="33" width="14" customWidth="1"/>
+    <col min="34" max="34" width="12" customWidth="1"/>
+    <col min="35" max="39" width="14" customWidth="1"/>
+    <col min="40" max="40" width="18" customWidth="1"/>
+    <col min="41" max="42" width="60" customWidth="1"/>
+    <col min="43" max="43" width="18" customWidth="1"/>
+    <col min="44" max="44" width="20" customWidth="1"/>
+    <col min="45" max="45" width="22" customWidth="1"/>
+    <col min="46" max="46" width="24" customWidth="1"/>
+    <col min="47" max="47" width="26" customWidth="1"/>
+    <col min="48" max="48" width="13" customWidth="1"/>
+    <col min="49" max="49" width="14" customWidth="1"/>
+    <col min="50" max="51" width="18" customWidth="1"/>
+    <col min="52" max="52" width="14" customWidth="1"/>
+    <col min="53" max="54" width="28" customWidth="1"/>
+    <col min="55" max="55" width="30" customWidth="1"/>
+    <col min="56" max="56" width="14" customWidth="1"/>
+    <col min="57" max="60" width="34" customWidth="1"/>
+    <col min="61" max="61" width="16" customWidth="1"/>
+    <col min="62" max="63" width="42" customWidth="1"/>
+    <col min="64" max="64" width="30" customWidth="1"/>
+    <col min="65" max="65" width="36" customWidth="1"/>
+    <col min="66" max="66" width="18" customWidth="1"/>
+    <col min="67" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="12" customWidth="1"/>
+    <col min="71" max="71" width="14" customWidth="1"/>
+    <col min="72" max="73" width="18" customWidth="1"/>
+    <col min="74" max="74" width="20" customWidth="1"/>
+    <col min="75" max="75" width="18" customWidth="1"/>
+    <col min="76" max="77" width="22" customWidth="1"/>
+    <col min="78" max="78" width="24" customWidth="1"/>
+    <col min="79" max="81" width="14" customWidth="1"/>
+    <col min="82" max="83" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:83" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -4506,13 +4950,13 @@
         <v>44</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>47</v>
@@ -4527,13 +4971,13 @@
         <v>50</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>53</v>
@@ -4679,8 +5123,38 @@
       <c r="BU1" s="1" t="s">
         <v>100</v>
       </c>
+      <c r="BV1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -4688,22 +5162,22 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I2" t="s">
         <v>29</v>
@@ -4711,197 +5185,227 @@
       <c r="J2">
         <v>214.01</v>
       </c>
-      <c r="K2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L2">
-        <v>291</v>
+      <c r="K2">
+        <v>214.01</v>
+      </c>
+      <c r="L2" t="s">
+        <v>117</v>
       </c>
       <c r="M2">
         <v>291</v>
       </c>
       <c r="N2">
+        <v>291</v>
+      </c>
+      <c r="O2">
+        <v>291</v>
+      </c>
+      <c r="P2">
         <v>62276.91</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>207.05</v>
       </c>
-      <c r="P2" s="2">
+      <c r="R2" s="2">
         <v>-2025.36</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>-3.25</v>
       </c>
-      <c r="R2" t="s">
-        <v>108</v>
-      </c>
-      <c r="S2" t="s">
-        <v>108</v>
-      </c>
       <c r="T2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB2" t="s">
         <v>29</v>
       </c>
-      <c r="AA2">
+      <c r="AC2">
         <v>179.24</v>
       </c>
-      <c r="AB2">
+      <c r="AD2">
         <v>179.24</v>
       </c>
-      <c r="AC2">
+      <c r="AE2">
         <v>196.45</v>
       </c>
-      <c r="AD2">
+      <c r="AF2">
         <v>196.45</v>
       </c>
-      <c r="AE2">
+      <c r="AG2">
         <v>5109.96</v>
       </c>
-      <c r="AF2">
+      <c r="AH2">
         <v>-0.4</v>
       </c>
-      <c r="AG2">
+      <c r="AI2">
         <v>0</v>
       </c>
-      <c r="AH2">
+      <c r="AJ2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ2">
         <v>0</v>
       </c>
-      <c r="AI2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM2">
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW2">
         <v>12</v>
       </c>
-      <c r="AN2">
+      <c r="AX2">
         <v>4</v>
       </c>
-      <c r="AO2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>117</v>
-      </c>
       <c r="AY2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="AZ2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP2" t="s">
         <v>119</v>
       </c>
-      <c r="BA2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>121</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG2">
+      <c r="BQ2">
         <v>0.55</v>
       </c>
-      <c r="BH2">
+      <c r="BR2">
         <v>4.35</v>
       </c>
-      <c r="BI2">
+      <c r="BS2">
         <v>13.66</v>
       </c>
-      <c r="BJ2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK2">
+      <c r="BT2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU2">
         <v>3.32</v>
       </c>
-      <c r="BL2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BM2">
+      <c r="BV2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BW2">
         <v>13.61</v>
       </c>
-      <c r="BN2">
+      <c r="BX2">
         <v>0.89</v>
       </c>
-      <c r="BO2">
+      <c r="BY2">
         <v>0.55</v>
       </c>
-      <c r="BP2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ2">
+      <c r="BZ2" t="s">
+        <v>137</v>
+      </c>
+      <c r="CA2">
         <v>199.5</v>
       </c>
-      <c r="BR2">
+      <c r="CB2">
         <v>196.45</v>
       </c>
-      <c r="BS2">
+      <c r="CC2">
         <v>186.53</v>
       </c>
-      <c r="BT2" t="s">
-        <v>128</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>108</v>
+      <c r="CD2" t="s">
+        <v>138</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -4909,22 +5413,22 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I3" t="s">
         <v>29</v>
@@ -4932,197 +5436,227 @@
       <c r="J3">
         <v>2048.2</v>
       </c>
-      <c r="K3" t="s">
-        <v>107</v>
-      </c>
-      <c r="L3">
+      <c r="K3">
+        <v>2048.2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M3">
         <v>25</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>49</v>
       </c>
-      <c r="N3">
+      <c r="O3">
+        <v>49</v>
+      </c>
+      <c r="P3">
         <v>51205</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>2058.6</v>
       </c>
-      <c r="P3" s="3">
+      <c r="R3" s="3">
         <v>260</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>0.51</v>
       </c>
-      <c r="R3" t="s">
-        <v>108</v>
-      </c>
-      <c r="S3" t="s">
-        <v>108</v>
-      </c>
       <c r="T3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB3" t="s">
         <v>29</v>
       </c>
-      <c r="AA3">
+      <c r="AC3">
         <v>170.76</v>
       </c>
-      <c r="AB3">
+      <c r="AD3">
         <v>170.76</v>
       </c>
-      <c r="AC3">
+      <c r="AE3">
         <v>1974.43</v>
       </c>
-      <c r="AD3">
+      <c r="AF3">
         <v>2015.38</v>
       </c>
-      <c r="AE3">
+      <c r="AG3">
         <v>3614.73</v>
       </c>
-      <c r="AF3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG3">
+      <c r="AH3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ3">
         <v>1</v>
       </c>
-      <c r="AH3">
+      <c r="AR3">
         <v>-1048.8</v>
       </c>
-      <c r="AI3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM3">
+      <c r="AS3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW3">
         <v>11</v>
       </c>
-      <c r="AN3">
+      <c r="AX3">
         <v>4</v>
       </c>
-      <c r="AO3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ3" t="s">
+      <c r="AY3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>141</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>142</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>143</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>144</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>145</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>146</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>147</v>
+      </c>
+      <c r="BL3" t="s">
         <v>132</v>
       </c>
-      <c r="AR3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS3" t="s">
+      <c r="BM3" t="s">
         <v>133</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="BN3" t="s">
         <v>134</v>
       </c>
-      <c r="AU3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY3" t="s">
+      <c r="BO3" t="s">
         <v>135</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>136</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>137</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG3">
+      <c r="BP3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ3">
         <v>0.3</v>
       </c>
-      <c r="BH3">
+      <c r="BR3">
         <v>3.57</v>
       </c>
-      <c r="BI3">
+      <c r="BS3">
         <v>2.1</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK3">
+      <c r="BT3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU3">
         <v>10.28</v>
       </c>
-      <c r="BL3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BM3">
+      <c r="BV3" t="s">
+        <v>148</v>
+      </c>
+      <c r="BW3">
         <v>2.1</v>
       </c>
-      <c r="BN3">
+      <c r="BX3">
         <v>1.68</v>
       </c>
-      <c r="BO3">
+      <c r="BY3">
         <v>0.3</v>
       </c>
-      <c r="BP3" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ3">
+      <c r="BZ3" t="s">
+        <v>149</v>
+      </c>
+      <c r="CA3">
         <v>2002.3</v>
       </c>
-      <c r="BR3">
+      <c r="CB3">
         <v>1981</v>
       </c>
-      <c r="BS3">
+      <c r="CC3">
         <v>1981</v>
       </c>
-      <c r="BT3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>108</v>
+      <c r="CD3" t="s">
+        <v>150</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -5130,22 +5664,22 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G4" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H4" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I4" t="s">
         <v>29</v>
@@ -5153,220 +5687,250 @@
       <c r="J4">
         <v>4421.9</v>
       </c>
-      <c r="K4" t="s">
-        <v>107</v>
-      </c>
-      <c r="L4">
-        <v>22</v>
+      <c r="K4">
+        <v>4421.9</v>
+      </c>
+      <c r="L4" t="s">
+        <v>117</v>
       </c>
       <c r="M4">
         <v>22</v>
       </c>
       <c r="N4">
+        <v>22</v>
+      </c>
+      <c r="O4">
+        <v>22</v>
+      </c>
+      <c r="P4">
         <v>97281.8</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>4452</v>
       </c>
-      <c r="P4" s="3">
+      <c r="R4" s="3">
         <v>662.2</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>0.68</v>
       </c>
-      <c r="R4" t="s">
-        <v>108</v>
-      </c>
-      <c r="S4" t="s">
-        <v>108</v>
-      </c>
       <c r="T4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB4" t="s">
         <v>29</v>
       </c>
-      <c r="AA4">
+      <c r="AC4">
         <v>167.02</v>
       </c>
-      <c r="AB4">
+      <c r="AD4">
         <v>167.02</v>
       </c>
-      <c r="AC4">
+      <c r="AE4">
         <v>4319.5</v>
       </c>
-      <c r="AD4">
+      <c r="AF4">
         <v>4319.5</v>
       </c>
-      <c r="AE4">
+      <c r="AG4">
         <v>2252.8</v>
       </c>
-      <c r="AF4">
+      <c r="AH4">
         <v>0.29</v>
       </c>
-      <c r="AG4">
+      <c r="AI4">
         <v>0</v>
       </c>
-      <c r="AH4">
+      <c r="AJ4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ4">
         <v>0</v>
       </c>
-      <c r="AI4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM4">
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW4">
         <v>14</v>
       </c>
-      <c r="AN4">
+      <c r="AX4">
         <v>1</v>
       </c>
-      <c r="AO4" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>112</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>113</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>117</v>
-      </c>
       <c r="AY4" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>145</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>154</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>155</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>132</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>133</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>134</v>
+      </c>
+      <c r="BO4" t="s">
         <v>135</v>
       </c>
-      <c r="AZ4" t="s">
-        <v>144</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>145</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>121</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG4">
+      <c r="BP4" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ4">
         <v>0.65</v>
       </c>
-      <c r="BH4">
+      <c r="BR4">
         <v>2.9</v>
       </c>
-      <c r="BI4">
+      <c r="BS4">
         <v>5.2</v>
       </c>
-      <c r="BJ4" t="s">
-        <v>124</v>
-      </c>
-      <c r="BK4">
+      <c r="BT4" t="s">
+        <v>135</v>
+      </c>
+      <c r="BU4">
         <v>6.4</v>
       </c>
-      <c r="BL4" t="s">
-        <v>126</v>
-      </c>
-      <c r="BM4">
+      <c r="BV4" t="s">
+        <v>136</v>
+      </c>
+      <c r="BW4">
         <v>2.63</v>
       </c>
-      <c r="BN4">
+      <c r="BX4">
         <v>0.47</v>
       </c>
-      <c r="BO4">
+      <c r="BY4">
         <v>0.65</v>
       </c>
-      <c r="BP4" t="s">
-        <v>146</v>
-      </c>
-      <c r="BQ4">
+      <c r="BZ4" t="s">
+        <v>156</v>
+      </c>
+      <c r="CA4">
         <v>4335</v>
       </c>
-      <c r="BR4">
+      <c r="CB4">
         <v>4319.5</v>
       </c>
-      <c r="BS4">
+      <c r="CC4">
         <v>4319.5</v>
       </c>
-      <c r="BT4" t="s">
-        <v>147</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>108</v>
+      <c r="CD4" t="s">
+        <v>157</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G5" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H5" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -5374,220 +5938,250 @@
       <c r="J5">
         <v>6621.5</v>
       </c>
-      <c r="K5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L5">
-        <v>15</v>
+      <c r="K5">
+        <v>6621.5</v>
+      </c>
+      <c r="L5" t="s">
+        <v>117</v>
       </c>
       <c r="M5">
         <v>15</v>
       </c>
       <c r="N5">
+        <v>15</v>
+      </c>
+      <c r="O5">
+        <v>15</v>
+      </c>
+      <c r="P5">
         <v>99322.5</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>6839</v>
       </c>
-      <c r="P5" s="3">
+      <c r="R5" s="3">
         <v>3262.5</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>3.28</v>
       </c>
-      <c r="R5" t="s">
-        <v>108</v>
-      </c>
-      <c r="S5" t="s">
-        <v>108</v>
-      </c>
       <c r="T5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB5" t="s">
         <v>29</v>
       </c>
-      <c r="AA5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB5">
+      <c r="AC5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD5">
         <v>200.86</v>
       </c>
-      <c r="AC5">
+      <c r="AE5">
         <v>6083.5</v>
       </c>
-      <c r="AD5">
+      <c r="AF5">
         <v>6202.5</v>
       </c>
-      <c r="AE5">
+      <c r="AG5">
         <v>8070</v>
       </c>
-      <c r="AF5">
+      <c r="AH5">
         <v>0.4</v>
       </c>
-      <c r="AG5">
+      <c r="AI5">
         <v>0</v>
       </c>
-      <c r="AH5">
+      <c r="AJ5" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ5">
         <v>0</v>
       </c>
-      <c r="AI5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM5">
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW5">
         <v>15</v>
       </c>
-      <c r="AN5">
+      <c r="AX5">
         <v>4</v>
       </c>
-      <c r="AO5" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>117</v>
-      </c>
       <c r="AY5" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="AZ5" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="BA5" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="BB5" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="BC5" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="BD5" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="BE5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BF5" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG5">
+        <v>126</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>162</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>163</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>164</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>167</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ5">
         <v>2.02</v>
       </c>
-      <c r="BH5">
+      <c r="BR5">
         <v>2.56</v>
       </c>
-      <c r="BI5">
+      <c r="BS5">
         <v>8.7</v>
       </c>
-      <c r="BJ5" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ5">
+      <c r="BT5" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>149</v>
+      </c>
+      <c r="CA5">
         <v>6202.5</v>
       </c>
-      <c r="BR5">
+      <c r="CB5">
         <v>6202.5</v>
       </c>
-      <c r="BS5">
+      <c r="CC5">
         <v>6202.5</v>
       </c>
-      <c r="BT5" t="s">
-        <v>158</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>108</v>
+      <c r="CD5" t="s">
+        <v>168</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C6" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G6" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H6" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I6" t="s">
         <v>29</v>
@@ -5595,220 +6189,250 @@
       <c r="J6">
         <v>1995.8</v>
       </c>
-      <c r="K6" t="s">
-        <v>107</v>
-      </c>
-      <c r="L6">
-        <v>49</v>
+      <c r="K6">
+        <v>1995.8</v>
+      </c>
+      <c r="L6" t="s">
+        <v>117</v>
       </c>
       <c r="M6">
         <v>49</v>
       </c>
       <c r="N6">
+        <v>49</v>
+      </c>
+      <c r="O6">
+        <v>49</v>
+      </c>
+      <c r="P6">
         <v>97794.2</v>
       </c>
-      <c r="O6">
+      <c r="Q6">
         <v>2027.3</v>
       </c>
-      <c r="P6" s="3">
+      <c r="R6" s="3">
         <v>1543.5</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>1.58</v>
       </c>
-      <c r="R6" t="s">
-        <v>108</v>
-      </c>
-      <c r="S6" t="s">
-        <v>108</v>
-      </c>
       <c r="T6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB6" t="s">
         <v>29</v>
       </c>
-      <c r="AA6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB6">
+      <c r="AC6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD6">
         <v>166.92</v>
       </c>
-      <c r="AC6">
+      <c r="AE6">
         <v>1842.85</v>
       </c>
-      <c r="AD6">
+      <c r="AF6">
         <v>1957</v>
       </c>
-      <c r="AE6">
+      <c r="AG6">
         <v>7494.55</v>
       </c>
-      <c r="AF6">
+      <c r="AH6">
         <v>0.21</v>
       </c>
-      <c r="AG6">
+      <c r="AI6">
         <v>0</v>
       </c>
-      <c r="AH6">
+      <c r="AJ6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ6">
         <v>0</v>
       </c>
-      <c r="AI6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM6">
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW6">
         <v>14</v>
       </c>
-      <c r="AN6">
+      <c r="AX6">
         <v>3</v>
       </c>
-      <c r="AO6" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>117</v>
-      </c>
       <c r="AY6" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="AZ6" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="BA6" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="BB6" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="BC6" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="BD6" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="BE6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BF6" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG6">
+        <v>126</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>171</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>172</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>173</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>167</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ6">
         <v>0.55</v>
       </c>
-      <c r="BH6">
+      <c r="BR6">
         <v>2.56</v>
       </c>
-      <c r="BI6">
+      <c r="BS6">
         <v>6.47</v>
       </c>
-      <c r="BJ6" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP6" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ6">
+      <c r="BT6" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>137</v>
+      </c>
+      <c r="CA6">
         <v>1957</v>
       </c>
-      <c r="BR6">
+      <c r="CB6">
         <v>1957</v>
       </c>
-      <c r="BS6">
+      <c r="CC6">
         <v>1957</v>
       </c>
-      <c r="BT6" t="s">
-        <v>164</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>108</v>
+      <c r="CD6" t="s">
+        <v>174</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C7" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="F7" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H7" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I7" t="s">
         <v>29</v>
@@ -5816,220 +6440,250 @@
       <c r="J7">
         <v>1373.5</v>
       </c>
-      <c r="K7" t="s">
-        <v>107</v>
-      </c>
-      <c r="L7">
-        <v>71</v>
+      <c r="K7">
+        <v>1373.5</v>
+      </c>
+      <c r="L7" t="s">
+        <v>117</v>
       </c>
       <c r="M7">
         <v>71</v>
       </c>
       <c r="N7">
+        <v>71</v>
+      </c>
+      <c r="O7">
+        <v>71</v>
+      </c>
+      <c r="P7">
         <v>97518.5</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <v>1389.1</v>
       </c>
-      <c r="P7" s="3">
+      <c r="R7" s="3">
         <v>1107.6</v>
       </c>
-      <c r="Q7">
+      <c r="S7">
         <v>1.14</v>
       </c>
-      <c r="R7" t="s">
-        <v>108</v>
-      </c>
-      <c r="S7" t="s">
-        <v>108</v>
-      </c>
       <c r="T7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB7" t="s">
         <v>29</v>
       </c>
-      <c r="AA7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB7">
+      <c r="AC7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD7">
         <v>184.09</v>
       </c>
-      <c r="AC7">
+      <c r="AE7">
         <v>1285.88</v>
       </c>
-      <c r="AD7">
+      <c r="AF7">
         <v>1303.2</v>
       </c>
-      <c r="AE7">
+      <c r="AG7">
         <v>6221.02</v>
       </c>
-      <c r="AF7">
+      <c r="AH7">
         <v>0.18</v>
       </c>
-      <c r="AG7">
+      <c r="AI7">
         <v>0</v>
       </c>
-      <c r="AH7">
+      <c r="AJ7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ7">
         <v>0</v>
       </c>
-      <c r="AI7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM7">
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW7">
         <v>13</v>
       </c>
-      <c r="AN7">
+      <c r="AX7">
         <v>4</v>
       </c>
-      <c r="AO7" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>117</v>
-      </c>
       <c r="AY7" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>176</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>177</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>178</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM7" t="s">
         <v>166</v>
       </c>
-      <c r="AZ7" t="s">
+      <c r="BN7" t="s">
         <v>167</v>
       </c>
-      <c r="BA7" t="s">
-        <v>168</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>155</v>
-      </c>
-      <c r="BC7" t="s">
+      <c r="BO7" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ7">
+        <v>0.72</v>
+      </c>
+      <c r="BR7">
+        <v>4.06</v>
+      </c>
+      <c r="BS7">
+        <v>11.77</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ7" t="s">
         <v>156</v>
       </c>
-      <c r="BD7" t="s">
-        <v>157</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG7">
-        <v>0.72</v>
-      </c>
-      <c r="BH7">
-        <v>4.06</v>
-      </c>
-      <c r="BI7">
-        <v>11.77</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>146</v>
-      </c>
-      <c r="BQ7">
+      <c r="CA7">
         <v>1303.2</v>
       </c>
-      <c r="BR7">
+      <c r="CB7">
         <v>1303.2</v>
       </c>
-      <c r="BS7">
+      <c r="CC7">
         <v>1303.2</v>
       </c>
-      <c r="BT7" t="s">
-        <v>169</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>108</v>
+      <c r="CD7" t="s">
+        <v>179</v>
+      </c>
+      <c r="CE7" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G8" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H8" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I8" t="s">
         <v>29</v>
@@ -6037,220 +6691,250 @@
       <c r="J8">
         <v>811</v>
       </c>
-      <c r="K8" t="s">
-        <v>107</v>
-      </c>
-      <c r="L8">
-        <v>119</v>
+      <c r="K8">
+        <v>811</v>
+      </c>
+      <c r="L8" t="s">
+        <v>117</v>
       </c>
       <c r="M8">
         <v>119</v>
       </c>
       <c r="N8">
+        <v>119</v>
+      </c>
+      <c r="O8">
+        <v>119</v>
+      </c>
+      <c r="P8">
         <v>96509</v>
       </c>
-      <c r="O8">
+      <c r="Q8">
         <v>809.95</v>
       </c>
-      <c r="P8" s="2">
+      <c r="R8" s="2">
         <v>-124.95</v>
       </c>
-      <c r="Q8">
+      <c r="S8">
         <v>-0.13</v>
       </c>
-      <c r="R8" t="s">
-        <v>108</v>
-      </c>
-      <c r="S8" t="s">
-        <v>108</v>
-      </c>
       <c r="T8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB8" t="s">
         <v>29</v>
       </c>
-      <c r="AA8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB8">
+      <c r="AC8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD8">
         <v>170.78</v>
       </c>
-      <c r="AC8">
+      <c r="AE8">
         <v>771.79</v>
       </c>
-      <c r="AD8">
+      <c r="AF8">
         <v>771.79</v>
       </c>
-      <c r="AE8">
+      <c r="AG8">
         <v>4665.99</v>
       </c>
-      <c r="AF8">
+      <c r="AH8">
         <v>-0.03</v>
       </c>
-      <c r="AG8">
+      <c r="AI8">
         <v>0</v>
       </c>
-      <c r="AH8">
+      <c r="AJ8" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ8">
         <v>0</v>
       </c>
-      <c r="AI8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM8">
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW8">
         <v>13</v>
       </c>
-      <c r="AN8">
+      <c r="AX8">
         <v>3</v>
       </c>
-      <c r="AO8" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>117</v>
-      </c>
       <c r="AY8" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="AZ8" t="s">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="BA8" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="BB8" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="BC8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>181</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>182</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>167</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ8">
+        <v>1.22</v>
+      </c>
+      <c r="BR8">
+        <v>4.91</v>
+      </c>
+      <c r="BS8">
+        <v>15.81</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ8" t="s">
         <v>156</v>
       </c>
-      <c r="BD8" t="s">
-        <v>157</v>
-      </c>
-      <c r="BE8" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF8" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG8">
-        <v>1.22</v>
-      </c>
-      <c r="BH8">
-        <v>4.91</v>
-      </c>
-      <c r="BI8">
-        <v>15.81</v>
-      </c>
-      <c r="BJ8" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK8" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL8" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM8" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN8" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO8" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP8" t="s">
-        <v>146</v>
-      </c>
-      <c r="BQ8">
+      <c r="CA8">
         <v>770</v>
       </c>
-      <c r="BR8">
+      <c r="CB8">
         <v>770</v>
       </c>
-      <c r="BS8">
+      <c r="CC8">
         <v>721.4</v>
       </c>
-      <c r="BT8" t="s">
-        <v>174</v>
-      </c>
-      <c r="BU8" t="s">
-        <v>108</v>
+      <c r="CD8" t="s">
+        <v>184</v>
+      </c>
+      <c r="CE8" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="E9" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="F9" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G9" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H9" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I9" t="s">
         <v>29</v>
@@ -6258,220 +6942,250 @@
       <c r="J9">
         <v>1351.4</v>
       </c>
-      <c r="K9" t="s">
-        <v>107</v>
-      </c>
-      <c r="L9">
-        <v>73</v>
+      <c r="K9">
+        <v>1351.4</v>
+      </c>
+      <c r="L9" t="s">
+        <v>117</v>
       </c>
       <c r="M9">
         <v>73</v>
       </c>
       <c r="N9">
+        <v>73</v>
+      </c>
+      <c r="O9">
+        <v>73</v>
+      </c>
+      <c r="P9">
         <v>98652.2</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>1352</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>43.8</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>0.04</v>
       </c>
-      <c r="R9" t="s">
-        <v>108</v>
-      </c>
-      <c r="S9" t="s">
-        <v>108</v>
-      </c>
       <c r="T9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB9" t="s">
         <v>29</v>
       </c>
-      <c r="AA9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB9">
+      <c r="AC9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD9">
         <v>181.93</v>
       </c>
-      <c r="AC9">
+      <c r="AE9">
         <v>1251.2</v>
       </c>
-      <c r="AD9">
+      <c r="AF9">
         <v>1331.72</v>
       </c>
-      <c r="AE9">
+      <c r="AG9">
         <v>7314.6</v>
       </c>
-      <c r="AF9">
+      <c r="AH9">
         <v>0.01</v>
       </c>
-      <c r="AG9">
+      <c r="AI9">
         <v>0</v>
       </c>
-      <c r="AH9">
+      <c r="AJ9" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ9">
         <v>0</v>
       </c>
-      <c r="AI9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM9">
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW9">
         <v>13</v>
       </c>
-      <c r="AN9">
+      <c r="AX9">
         <v>4</v>
       </c>
-      <c r="AO9" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU9" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>117</v>
-      </c>
       <c r="AY9" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="AZ9" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="BA9" t="s">
-        <v>177</v>
+        <v>118</v>
       </c>
       <c r="BB9" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="BC9" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="BD9" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="BE9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BF9" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG9">
+        <v>126</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>171</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>187</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>167</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ9">
         <v>0.32</v>
       </c>
-      <c r="BH9">
+      <c r="BR9">
         <v>3.04</v>
       </c>
-      <c r="BI9">
+      <c r="BS9">
         <v>2.68</v>
       </c>
-      <c r="BJ9" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK9" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL9" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM9" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN9" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO9" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP9" t="s">
-        <v>178</v>
-      </c>
-      <c r="BQ9">
+      <c r="BT9" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>188</v>
+      </c>
+      <c r="CA9">
         <v>1321</v>
       </c>
-      <c r="BR9">
+      <c r="CB9">
         <v>1321</v>
       </c>
-      <c r="BS9">
+      <c r="CC9">
         <v>1321</v>
       </c>
-      <c r="BT9" t="s">
-        <v>179</v>
-      </c>
-      <c r="BU9" t="s">
-        <v>108</v>
+      <c r="CD9" t="s">
+        <v>189</v>
+      </c>
+      <c r="CE9" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D10" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="F10" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G10" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H10" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I10" t="s">
         <v>29</v>
@@ -6479,220 +7193,250 @@
       <c r="J10">
         <v>437.05</v>
       </c>
-      <c r="K10" t="s">
-        <v>107</v>
-      </c>
-      <c r="L10">
+      <c r="K10">
+        <v>437.05</v>
+      </c>
+      <c r="L10" t="s">
+        <v>117</v>
+      </c>
+      <c r="M10">
         <v>114</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>228</v>
       </c>
-      <c r="N10">
+      <c r="O10">
+        <v>228</v>
+      </c>
+      <c r="P10">
         <v>49823.7</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>435.5</v>
       </c>
-      <c r="P10" s="2">
+      <c r="R10" s="2">
         <v>-176.7</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>-0.35</v>
       </c>
-      <c r="R10" t="s">
-        <v>108</v>
-      </c>
-      <c r="S10" t="s">
-        <v>108</v>
-      </c>
       <c r="T10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB10" t="s">
         <v>29</v>
       </c>
-      <c r="AA10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB10">
+      <c r="AC10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD10">
         <v>92.43</v>
       </c>
-      <c r="AC10">
+      <c r="AE10">
         <v>402.78</v>
       </c>
-      <c r="AD10">
+      <c r="AF10">
         <v>422.15</v>
       </c>
-      <c r="AE10">
+      <c r="AG10">
         <v>7813.56</v>
       </c>
-      <c r="AF10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG10">
+      <c r="AH10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ10">
         <v>1</v>
       </c>
-      <c r="AH10">
+      <c r="AR10">
         <v>-501.6</v>
       </c>
-      <c r="AI10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM10">
+      <c r="AS10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW10">
         <v>11</v>
       </c>
-      <c r="AN10">
+      <c r="AX10">
         <v>5</v>
       </c>
-      <c r="AO10" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>117</v>
-      </c>
       <c r="AY10" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="AZ10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI10" t="s">
         <v>181</v>
       </c>
-      <c r="BA10" t="s">
-        <v>182</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>155</v>
-      </c>
-      <c r="BC10" t="s">
-        <v>156</v>
-      </c>
-      <c r="BD10" t="s">
-        <v>157</v>
-      </c>
-      <c r="BE10" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF10" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG10">
+      <c r="BJ10" t="s">
+        <v>191</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>192</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN10" t="s">
+        <v>167</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP10" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ10">
         <v>0.22</v>
       </c>
-      <c r="BH10">
+      <c r="BR10">
         <v>3.42</v>
       </c>
-      <c r="BI10">
+      <c r="BS10">
         <v>9.13</v>
       </c>
-      <c r="BJ10" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK10" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL10" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM10" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN10" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO10" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP10" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ10">
+      <c r="BT10" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY10" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ10" t="s">
+        <v>137</v>
+      </c>
+      <c r="CA10">
         <v>425.45</v>
       </c>
-      <c r="BR10">
+      <c r="CB10">
         <v>423.3</v>
       </c>
-      <c r="BS10">
+      <c r="CC10">
         <v>422.15</v>
       </c>
-      <c r="BT10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU10" t="s">
-        <v>108</v>
+      <c r="CD10" t="s">
+        <v>193</v>
+      </c>
+      <c r="CE10" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="F11" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G11" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I11" t="s">
         <v>29</v>
@@ -6700,197 +7444,227 @@
       <c r="J11">
         <v>2986</v>
       </c>
-      <c r="K11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L11">
-        <v>33</v>
+      <c r="K11">
+        <v>2986</v>
+      </c>
+      <c r="L11" t="s">
+        <v>117</v>
       </c>
       <c r="M11">
         <v>33</v>
       </c>
       <c r="N11">
+        <v>33</v>
+      </c>
+      <c r="O11">
+        <v>33</v>
+      </c>
+      <c r="P11">
         <v>98538</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>2983.2</v>
       </c>
-      <c r="P11" s="2">
+      <c r="R11" s="2">
         <v>-92.4</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>-0.09</v>
       </c>
-      <c r="R11" t="s">
-        <v>108</v>
-      </c>
-      <c r="S11" t="s">
-        <v>108</v>
-      </c>
       <c r="T11" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U11" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V11" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W11" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X11" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y11" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB11" t="s">
         <v>29</v>
       </c>
-      <c r="AA11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB11">
+      <c r="AC11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD11">
         <v>165.43</v>
       </c>
-      <c r="AC11">
+      <c r="AE11">
         <v>2728.17</v>
       </c>
-      <c r="AD11">
+      <c r="AF11">
         <v>2936.17</v>
       </c>
-      <c r="AE11">
+      <c r="AG11">
         <v>8508.39</v>
       </c>
-      <c r="AF11">
+      <c r="AH11">
         <v>-0.01</v>
       </c>
-      <c r="AG11">
+      <c r="AI11">
         <v>0</v>
       </c>
-      <c r="AH11">
+      <c r="AJ11" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ11">
         <v>0</v>
       </c>
-      <c r="AI11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM11">
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW11">
         <v>12</v>
       </c>
-      <c r="AN11">
+      <c r="AX11">
         <v>3</v>
       </c>
-      <c r="AO11" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU11" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>117</v>
-      </c>
       <c r="AY11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>176</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>195</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>196</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM11" t="s">
         <v>166</v>
       </c>
-      <c r="AZ11" t="s">
-        <v>185</v>
-      </c>
-      <c r="BA11" t="s">
-        <v>186</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>155</v>
-      </c>
-      <c r="BC11" t="s">
-        <v>156</v>
-      </c>
-      <c r="BD11" t="s">
-        <v>157</v>
-      </c>
-      <c r="BE11" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF11" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG11">
+      <c r="BN11" t="s">
+        <v>167</v>
+      </c>
+      <c r="BO11" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ11">
         <v>1.21</v>
       </c>
-      <c r="BH11">
+      <c r="BR11">
         <v>3.14</v>
       </c>
-      <c r="BI11">
+      <c r="BS11">
         <v>6.77</v>
       </c>
-      <c r="BJ11" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK11" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL11" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM11" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN11" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO11" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP11" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ11">
+      <c r="BT11" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY11" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ11" t="s">
+        <v>137</v>
+      </c>
+      <c r="CA11">
         <v>2903.2</v>
       </c>
-      <c r="BR11">
+      <c r="CB11">
         <v>2903.2</v>
       </c>
-      <c r="BS11">
+      <c r="CC11">
         <v>2903.2</v>
       </c>
-      <c r="BT11" t="s">
-        <v>187</v>
-      </c>
-      <c r="BU11" t="s">
-        <v>108</v>
+      <c r="CD11" t="s">
+        <v>197</v>
+      </c>
+      <c r="CE11" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -6898,220 +7672,250 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D12" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="E12" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F12" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="G12" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="I12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="K12" t="s">
-        <v>190</v>
+        <v>118</v>
       </c>
       <c r="L12" t="s">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="M12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="N12" t="s">
-        <v>108</v>
-      </c>
-      <c r="O12">
+        <v>118</v>
+      </c>
+      <c r="O12" t="s">
+        <v>118</v>
+      </c>
+      <c r="P12" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q12">
         <v>4506.7998046875</v>
       </c>
-      <c r="P12" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>108</v>
-      </c>
       <c r="R12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="S12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="T12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z12" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
       <c r="AA12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AB12" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="AC12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AD12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AE12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AF12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG12">
+        <v>118</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI12">
         <v>0</v>
       </c>
-      <c r="AH12">
+      <c r="AJ12" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ12">
         <v>0</v>
       </c>
-      <c r="AI12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>143</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM12">
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW12">
         <v>17</v>
       </c>
-      <c r="AN12">
+      <c r="AX12">
         <v>4</v>
       </c>
-      <c r="AO12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>193</v>
-      </c>
-      <c r="AW12" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>194</v>
-      </c>
       <c r="AY12" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AZ12" t="s">
-        <v>196</v>
+        <v>118</v>
       </c>
       <c r="BA12" t="s">
-        <v>197</v>
+        <v>118</v>
       </c>
       <c r="BB12" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="BC12" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="BD12" t="s">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="BE12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BF12" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG12">
+        <v>203</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>204</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>205</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>206</v>
+      </c>
+      <c r="BK12" t="s">
+        <v>207</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM12" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN12" t="s">
+        <v>208</v>
+      </c>
+      <c r="BO12" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP12" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ12">
         <v>0.99</v>
       </c>
-      <c r="BH12">
+      <c r="BR12">
         <v>2.15</v>
       </c>
-      <c r="BI12">
+      <c r="BS12">
         <v>6.95</v>
       </c>
-      <c r="BJ12" t="s">
-        <v>124</v>
-      </c>
-      <c r="BK12">
+      <c r="BT12" t="s">
+        <v>135</v>
+      </c>
+      <c r="BU12">
         <v>6.81</v>
       </c>
-      <c r="BL12" t="s">
-        <v>126</v>
-      </c>
-      <c r="BM12">
+      <c r="BV12" t="s">
+        <v>136</v>
+      </c>
+      <c r="BW12">
         <v>2.21</v>
       </c>
-      <c r="BN12">
+      <c r="BX12">
         <v>0.58</v>
       </c>
-      <c r="BO12">
+      <c r="BY12">
         <v>0.99</v>
       </c>
-      <c r="BP12" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ12">
+      <c r="BZ12" t="s">
+        <v>149</v>
+      </c>
+      <c r="CA12">
         <v>4331</v>
       </c>
-      <c r="BR12">
+      <c r="CB12">
         <v>4305.8</v>
       </c>
-      <c r="BS12">
+      <c r="CC12">
         <v>4305.8</v>
       </c>
-      <c r="BT12" t="s">
-        <v>199</v>
-      </c>
-      <c r="BU12" t="s">
-        <v>108</v>
+      <c r="CD12" t="s">
+        <v>209</v>
+      </c>
+      <c r="CE12" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -7119,220 +7923,250 @@
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D13" t="s">
+        <v>210</v>
+      </c>
+      <c r="E13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F13" t="s">
+        <v>199</v>
+      </c>
+      <c r="G13" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" t="s">
+        <v>118</v>
+      </c>
+      <c r="I13" t="s">
+        <v>118</v>
+      </c>
+      <c r="J13" t="s">
+        <v>118</v>
+      </c>
+      <c r="K13" t="s">
+        <v>118</v>
+      </c>
+      <c r="L13" t="s">
         <v>200</v>
       </c>
-      <c r="E13" t="s">
-        <v>200</v>
-      </c>
-      <c r="F13" t="s">
-        <v>189</v>
-      </c>
-      <c r="G13" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" t="s">
-        <v>108</v>
-      </c>
-      <c r="I13" t="s">
-        <v>108</v>
-      </c>
-      <c r="J13" t="s">
-        <v>108</v>
-      </c>
-      <c r="K13" t="s">
-        <v>190</v>
-      </c>
-      <c r="L13" t="s">
-        <v>108</v>
-      </c>
       <c r="M13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="N13" t="s">
-        <v>108</v>
-      </c>
-      <c r="O13">
+        <v>118</v>
+      </c>
+      <c r="O13" t="s">
+        <v>118</v>
+      </c>
+      <c r="P13" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q13">
         <v>1117.199951171875</v>
       </c>
-      <c r="P13" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>108</v>
-      </c>
       <c r="R13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="S13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="T13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="U13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="V13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="W13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Z13" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
       <c r="AA13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AB13" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="AC13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AD13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AE13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AF13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG13">
+        <v>118</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI13">
         <v>0</v>
       </c>
-      <c r="AH13">
+      <c r="AJ13" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ13">
         <v>0</v>
       </c>
-      <c r="AI13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>201</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM13">
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>211</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW13">
         <v>16</v>
       </c>
-      <c r="AN13">
+      <c r="AX13">
         <v>4</v>
       </c>
-      <c r="AO13" t="s">
-        <v>192</v>
-      </c>
-      <c r="AP13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV13" t="s">
+      <c r="AY13" t="s">
         <v>202</v>
       </c>
-      <c r="AW13" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>194</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>203</v>
-      </c>
       <c r="AZ13" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>118</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>212</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH13" t="s">
         <v>204</v>
       </c>
-      <c r="BA13" t="s">
-        <v>205</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>155</v>
-      </c>
-      <c r="BC13" t="s">
-        <v>156</v>
-      </c>
-      <c r="BD13" t="s">
-        <v>198</v>
-      </c>
-      <c r="BE13" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF13" t="s">
-        <v>124</v>
-      </c>
-      <c r="BG13">
+      <c r="BI13" t="s">
+        <v>213</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>214</v>
+      </c>
+      <c r="BK13" t="s">
+        <v>215</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM13" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>208</v>
+      </c>
+      <c r="BO13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ13">
         <v>1.56</v>
       </c>
-      <c r="BH13">
+      <c r="BR13">
         <v>2.97</v>
       </c>
-      <c r="BI13">
+      <c r="BS13">
         <v>9.83</v>
       </c>
-      <c r="BJ13" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK13">
+      <c r="BT13" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU13">
         <v>0</v>
       </c>
-      <c r="BL13" t="s">
-        <v>206</v>
-      </c>
-      <c r="BM13">
+      <c r="BV13" t="s">
+        <v>216</v>
+      </c>
+      <c r="BW13">
         <v>1.19</v>
       </c>
-      <c r="BN13">
+      <c r="BX13">
         <v>0.98</v>
       </c>
-      <c r="BO13">
+      <c r="BY13">
         <v>1.56</v>
       </c>
-      <c r="BP13" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ13">
+      <c r="BZ13" t="s">
+        <v>149</v>
+      </c>
+      <c r="CA13">
         <v>1048</v>
       </c>
-      <c r="BR13">
+      <c r="CB13">
         <v>1021.6</v>
       </c>
-      <c r="BS13">
+      <c r="CC13">
         <v>1012.9</v>
       </c>
-      <c r="BT13" t="s">
-        <v>207</v>
-      </c>
-      <c r="BU13" t="s">
-        <v>108</v>
+      <c r="CD13" t="s">
+        <v>217</v>
+      </c>
+      <c r="CE13" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -7340,221 +8174,251 @@
         <v>23</v>
       </c>
       <c r="C14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" t="s">
+        <v>218</v>
+      </c>
+      <c r="E14" t="s">
+        <v>218</v>
+      </c>
+      <c r="F14" t="s">
+        <v>199</v>
+      </c>
+      <c r="G14" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I14" t="s">
+        <v>118</v>
+      </c>
+      <c r="J14" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" t="s">
+        <v>118</v>
+      </c>
+      <c r="L14" t="s">
+        <v>200</v>
+      </c>
+      <c r="M14" t="s">
+        <v>118</v>
+      </c>
+      <c r="N14" t="s">
+        <v>118</v>
+      </c>
+      <c r="O14" t="s">
+        <v>118</v>
+      </c>
+      <c r="P14" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q14">
+        <v>747.0499877929688</v>
+      </c>
+      <c r="R14" t="s">
+        <v>118</v>
+      </c>
+      <c r="S14" t="s">
+        <v>118</v>
+      </c>
+      <c r="T14" t="s">
+        <v>118</v>
+      </c>
+      <c r="U14" t="s">
+        <v>118</v>
+      </c>
+      <c r="V14" t="s">
+        <v>118</v>
+      </c>
+      <c r="W14" t="s">
+        <v>118</v>
+      </c>
+      <c r="X14" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>201</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>120</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>219</v>
+      </c>
+      <c r="AW14">
+        <v>12</v>
+      </c>
+      <c r="AX14">
+        <v>2</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>118</v>
+      </c>
+      <c r="BE14" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH14" t="s">
+        <v>204</v>
+      </c>
+      <c r="BI14" t="s">
+        <v>220</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>221</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>222</v>
+      </c>
+      <c r="BL14" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM14" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>208</v>
+      </c>
+      <c r="BO14" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP14" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ14">
+        <v>0.42</v>
+      </c>
+      <c r="BR14">
+        <v>4.83</v>
+      </c>
+      <c r="BS14">
+        <v>9.1</v>
+      </c>
+      <c r="BT14" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU14">
+        <v>8.22</v>
+      </c>
+      <c r="BV14" t="s">
+        <v>136</v>
+      </c>
+      <c r="BW14">
+        <v>6</v>
+      </c>
+      <c r="BX14">
+        <v>1.81</v>
+      </c>
+      <c r="BY14">
+        <v>0.42</v>
+      </c>
+      <c r="BZ14" t="s">
         <v>149</v>
       </c>
-      <c r="D14" t="s">
-        <v>208</v>
-      </c>
-      <c r="E14" t="s">
-        <v>208</v>
-      </c>
-      <c r="F14" t="s">
-        <v>189</v>
-      </c>
-      <c r="G14" t="s">
-        <v>105</v>
-      </c>
-      <c r="H14" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" t="s">
-        <v>108</v>
-      </c>
-      <c r="J14" t="s">
-        <v>108</v>
-      </c>
-      <c r="K14" t="s">
-        <v>190</v>
-      </c>
-      <c r="L14" t="s">
-        <v>108</v>
-      </c>
-      <c r="M14" t="s">
-        <v>108</v>
-      </c>
-      <c r="N14" t="s">
-        <v>108</v>
-      </c>
-      <c r="O14">
-        <v>747.0499877929688</v>
-      </c>
-      <c r="P14" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>108</v>
-      </c>
-      <c r="R14" t="s">
-        <v>108</v>
-      </c>
-      <c r="S14" t="s">
-        <v>108</v>
-      </c>
-      <c r="T14" t="s">
-        <v>108</v>
-      </c>
-      <c r="U14" t="s">
-        <v>108</v>
-      </c>
-      <c r="V14" t="s">
-        <v>108</v>
-      </c>
-      <c r="W14" t="s">
-        <v>108</v>
-      </c>
-      <c r="X14" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>109</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>209</v>
-      </c>
-      <c r="AM14">
-        <v>12</v>
-      </c>
-      <c r="AN14">
-        <v>2</v>
-      </c>
-      <c r="AO14" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU14" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV14" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW14" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX14" t="s">
-        <v>194</v>
-      </c>
-      <c r="AY14" t="s">
-        <v>210</v>
-      </c>
-      <c r="AZ14" t="s">
-        <v>211</v>
-      </c>
-      <c r="BA14" t="s">
-        <v>212</v>
-      </c>
-      <c r="BB14" t="s">
-        <v>155</v>
-      </c>
-      <c r="BC14" t="s">
-        <v>156</v>
-      </c>
-      <c r="BD14" t="s">
-        <v>198</v>
-      </c>
-      <c r="BE14" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF14" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG14">
-        <v>0.42</v>
-      </c>
-      <c r="BH14">
-        <v>4.83</v>
-      </c>
-      <c r="BI14">
-        <v>9.1</v>
-      </c>
-      <c r="BJ14" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK14">
-        <v>8.22</v>
-      </c>
-      <c r="BL14" t="s">
-        <v>126</v>
-      </c>
-      <c r="BM14">
-        <v>6</v>
-      </c>
-      <c r="BN14">
-        <v>1.81</v>
-      </c>
-      <c r="BO14">
-        <v>0.42</v>
-      </c>
-      <c r="BP14" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ14">
+      <c r="CA14">
         <v>701.8</v>
       </c>
-      <c r="BR14">
+      <c r="CB14">
         <v>688.05</v>
       </c>
-      <c r="BS14">
+      <c r="CC14">
         <v>688.05</v>
       </c>
-      <c r="BT14" t="s">
-        <v>213</v>
-      </c>
-      <c r="BU14" t="s">
-        <v>108</v>
+      <c r="CD14" t="s">
+        <v>223</v>
+      </c>
+      <c r="CE14" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BU1"/>
+  <autoFilter ref="A1:CE1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -7584,54 +8448,54 @@
         <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F2">
         <v>130.04</v>
       </c>
       <c r="G2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="H2">
         <v>93010</v>
@@ -7643,7 +8507,7 @@
         <v>8955.5</v>
       </c>
       <c r="K2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -7667,30 +8531,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -7702,7 +8566,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -28,7 +28,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-13T06:00:40.506Z</t>
+    <t>2026-07-13T06:42:17.564Z</t>
   </si>
   <si>
     <t>Total Capital</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="260">
   <si>
     <t>Metric</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-13T08:44:51.558Z</t>
+    <t>2026-07-13T08:47:03.655Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -2615,8 +2615,8 @@
       <c r="AG5">
         <v>3285</v>
       </c>
-      <c r="AH5" t="s">
-        <v>124</v>
+      <c r="AH5">
+        <v>0.05</v>
       </c>
       <c r="AI5">
         <v>0</v>
@@ -6351,8 +6351,8 @@
       <c r="AG5">
         <v>3285</v>
       </c>
-      <c r="AH5" t="s">
-        <v>124</v>
+      <c r="AH5">
+        <v>0.05</v>
       </c>
       <c r="AI5">
         <v>0</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -28,7 +28,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-13T08:47:03.655Z</t>
+    <t>2026-07-13T09:10:46.295Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -2604,7 +2604,7 @@
         <v>131.92</v>
       </c>
       <c r="AD5">
-        <v>131.92</v>
+        <v>150.92</v>
       </c>
       <c r="AE5">
         <v>8955.5</v>
@@ -3106,7 +3106,7 @@
         <v>124</v>
       </c>
       <c r="AD7">
-        <v>170.76</v>
+        <v>174.76</v>
       </c>
       <c r="AE7">
         <v>1842.85</v>
@@ -3357,7 +3357,7 @@
         <v>124</v>
       </c>
       <c r="AD8">
-        <v>185.73</v>
+        <v>189.73</v>
       </c>
       <c r="AE8">
         <v>1285.88</v>
@@ -3859,7 +3859,7 @@
         <v>124</v>
       </c>
       <c r="AD10">
-        <v>183.65</v>
+        <v>187.65</v>
       </c>
       <c r="AE10">
         <v>1251.2</v>
@@ -6340,7 +6340,7 @@
         <v>131.92</v>
       </c>
       <c r="AD5">
-        <v>131.92</v>
+        <v>150.92</v>
       </c>
       <c r="AE5">
         <v>8955.5</v>
@@ -6842,7 +6842,7 @@
         <v>124</v>
       </c>
       <c r="AD7">
-        <v>170.76</v>
+        <v>174.76</v>
       </c>
       <c r="AE7">
         <v>1842.85</v>
@@ -7093,7 +7093,7 @@
         <v>124</v>
       </c>
       <c r="AD8">
-        <v>185.73</v>
+        <v>189.73</v>
       </c>
       <c r="AE8">
         <v>1285.88</v>
@@ -7595,7 +7595,7 @@
         <v>124</v>
       </c>
       <c r="AD10">
-        <v>183.65</v>
+        <v>187.65</v>
       </c>
       <c r="AE10">
         <v>1251.2</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -28,7 +28,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-13T10:52:01.902Z</t>
+    <t>2026-07-13T11:24:55.386Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -841,7 +841,7 @@
     <t>WAITING_ROTATION</t>
   </si>
   <si>
-    <t>Waiting for SIS rotation exit. SANGAMIND rank 190.61 is 106.77 points above weak position SIS rank 83.84.</t>
+    <t>Waiting for SIS exact 09:17 rotation sell to release cash.</t>
   </si>
   <si>
     <t>WAITING_CAPITAL</t>
@@ -10176,7 +10176,7 @@
         <v>132</v>
       </c>
       <c r="F2">
-        <v>190.61</v>
+        <v>196.28</v>
       </c>
       <c r="G2" t="s">
         <v>253</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="343">
   <si>
     <t>Metric</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T04:55:09.134Z</t>
+    <t>2026-07-14T05:01:25.925Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -437,6 +437,9 @@
     <t>No</t>
   </si>
   <si>
+    <t>HOLD</t>
+  </si>
+  <si>
     <t xml:space="preserve">PASS; </t>
   </si>
   <si>
@@ -560,6 +563,12 @@
     <t>09:17 order / 09:21 actual fill</t>
   </si>
   <si>
+    <t>PARTIAL_EXIT</t>
+  </si>
+  <si>
+    <t>Profit reached 2.21R; lock 50% and trail the balance.</t>
+  </si>
+  <si>
     <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Bollinger trend/range context; MACD and OBV confirmation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
@@ -584,9 +593,6 @@
     <t>Rain Industries Limited</t>
   </si>
   <si>
-    <t>HOLD</t>
-  </si>
-  <si>
     <t>GTF confirms less than 2R room</t>
   </si>
   <si>
@@ -1013,7 +1019,7 @@
     <t>ROTATION_DEFERRED</t>
   </si>
   <si>
-    <t>2026-07-14T04:55:08.377Z</t>
+    <t>2026-07-14T05:01:25.100Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -1471,7 +1477,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>1009259.85</v>
+        <v>1009240.65</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1479,7 +1485,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>999849.1</v>
+        <v>999555.25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1495,7 +1501,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>150.9</v>
+        <v>444.75</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1503,7 +1509,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>5977.82</v>
+        <v>6271.67</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1543,7 +1549,7 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>99.98</v>
+        <v>99.96</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1551,7 +1557,7 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>40729.1</v>
+        <v>40720.4</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1615,7 +1621,7 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>3432.93</v>
+        <v>3413.73</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2165,8 +2171,8 @@
       <c r="AJ2">
         <v>3223.2</v>
       </c>
-      <c r="AK2" t="s">
-        <v>137</v>
+      <c r="AK2">
+        <v>0.05</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -2214,7 +2220,7 @@
         <v>137</v>
       </c>
       <c r="BA2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BB2" t="s">
         <v>137</v>
@@ -2226,13 +2232,13 @@
         <v>137</v>
       </c>
       <c r="BE2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BF2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BG2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH2">
         <v>15</v>
@@ -2241,61 +2247,61 @@
         <v>4</v>
       </c>
       <c r="BJ2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BK2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BL2" t="s">
         <v>137</v>
       </c>
       <c r="BM2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BN2" t="s">
         <v>138</v>
       </c>
       <c r="BO2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BP2" t="s">
         <v>137</v>
       </c>
       <c r="BQ2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BR2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BW2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BX2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BY2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BZ2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="CB2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC2" t="s">
         <v>138</v>
@@ -2316,7 +2322,7 @@
         <v>5.72</v>
       </c>
       <c r="CI2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="CJ2">
         <v>8.7</v>
@@ -2328,7 +2334,7 @@
         <v>0.21</v>
       </c>
       <c r="CM2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CN2">
         <v>805.6</v>
@@ -2340,7 +2346,7 @@
         <v>805.6</v>
       </c>
       <c r="CQ2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="CR2" t="s">
         <v>137</v>
@@ -2357,10 +2363,10 @@
         <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
         <v>133</v>
@@ -2455,8 +2461,8 @@
       <c r="AJ3">
         <v>5816.16</v>
       </c>
-      <c r="AK3" t="s">
-        <v>137</v>
+      <c r="AK3">
+        <v>-0.51</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2504,7 +2510,7 @@
         <v>137</v>
       </c>
       <c r="BA3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BB3" t="s">
         <v>137</v>
@@ -2516,13 +2522,13 @@
         <v>137</v>
       </c>
       <c r="BE3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BF3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BG3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH3">
         <v>22</v>
@@ -2531,10 +2537,10 @@
         <v>4</v>
       </c>
       <c r="BJ3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BK3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BL3" t="s">
         <v>137</v>
@@ -2546,49 +2552,49 @@
         <v>138</v>
       </c>
       <c r="BO3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BP3" t="s">
         <v>137</v>
       </c>
       <c r="BQ3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BR3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BV3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BW3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BX3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BY3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BZ3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="CB3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CD3">
         <v>90.28</v>
@@ -2606,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="CI3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CJ3">
         <v>15.12</v>
@@ -2618,7 +2624,7 @@
         <v>90.28</v>
       </c>
       <c r="CM3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CN3">
         <v>556.8</v>
@@ -2630,7 +2636,7 @@
         <v>536</v>
       </c>
       <c r="CQ3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="CR3" t="s">
         <v>137</v>
@@ -2644,19 +2650,19 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F4" t="s">
         <v>133</v>
       </c>
       <c r="G4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H4" t="s">
         <v>134</v>
@@ -2665,7 +2671,7 @@
         <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K4">
         <v>19.59</v>
@@ -2674,10 +2680,10 @@
         <v>19.59</v>
       </c>
       <c r="M4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N4">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="O4">
         <v>31</v>
@@ -2686,16 +2692,16 @@
         <v>31</v>
       </c>
       <c r="Q4">
-        <v>607.29</v>
+        <v>313.44</v>
       </c>
       <c r="R4">
-        <v>646.97</v>
+        <v>333.92</v>
       </c>
       <c r="S4">
         <v>20.87</v>
       </c>
       <c r="T4" s="2">
-        <v>39.68</v>
+        <v>20.48</v>
       </c>
       <c r="U4">
         <v>6.53</v>
@@ -2728,7 +2734,7 @@
         <v>137</v>
       </c>
       <c r="AE4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AF4">
         <v>168.93</v>
@@ -2745,8 +2751,8 @@
       <c r="AJ4">
         <v>17.98</v>
       </c>
-      <c r="AK4" t="s">
-        <v>137</v>
+      <c r="AK4">
+        <v>2.21</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2773,7 +2779,7 @@
         <v>137</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4">
         <v>0</v>
@@ -2794,10 +2800,10 @@
         <v>137</v>
       </c>
       <c r="BA4" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="BB4" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="BC4">
         <v>0</v>
@@ -2806,13 +2812,13 @@
         <v>137</v>
       </c>
       <c r="BE4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BF4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BG4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH4">
         <v>16</v>
@@ -2821,10 +2827,10 @@
         <v>4</v>
       </c>
       <c r="BJ4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BK4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BL4" t="s">
         <v>137</v>
@@ -2836,43 +2842,43 @@
         <v>138</v>
       </c>
       <c r="BO4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BP4" t="s">
         <v>137</v>
       </c>
       <c r="BQ4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BR4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BV4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BW4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="BX4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="BY4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="BZ4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CB4" t="s">
         <v>138</v>
@@ -2896,7 +2902,7 @@
         <v>18.16</v>
       </c>
       <c r="CI4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CJ4">
         <v>1.54</v>
@@ -2908,7 +2914,7 @@
         <v>0.76</v>
       </c>
       <c r="CM4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="CN4">
         <v>20</v>
@@ -2920,7 +2926,7 @@
         <v>19.01</v>
       </c>
       <c r="CQ4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="CR4" t="s">
         <v>137</v>
@@ -2937,16 +2943,16 @@
         <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F5" t="s">
         <v>133</v>
       </c>
       <c r="G5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H5" t="s">
         <v>134</v>
@@ -3084,10 +3090,10 @@
         <v>137</v>
       </c>
       <c r="BA5" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="BC5">
         <v>0</v>
@@ -3099,10 +3105,10 @@
         <v>137</v>
       </c>
       <c r="BF5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BG5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH5">
         <v>12</v>
@@ -3111,10 +3117,10 @@
         <v>4</v>
       </c>
       <c r="BJ5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="BL5" t="s">
         <v>137</v>
@@ -3132,40 +3138,40 @@
         <v>137</v>
       </c>
       <c r="BQ5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BR5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="BW5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="BX5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="BY5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BZ5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="CB5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC5" t="s">
         <v>138</v>
@@ -3186,7 +3192,7 @@
         <v>3.32</v>
       </c>
       <c r="CI5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CJ5">
         <v>13.61</v>
@@ -3198,7 +3204,7 @@
         <v>0.55</v>
       </c>
       <c r="CM5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="CN5">
         <v>199.5</v>
@@ -3210,7 +3216,7 @@
         <v>186.53</v>
       </c>
       <c r="CQ5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="CR5" t="s">
         <v>137</v>
@@ -3227,16 +3233,16 @@
         <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F6" t="s">
         <v>133</v>
       </c>
       <c r="G6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H6" t="s">
         <v>134</v>
@@ -3374,7 +3380,7 @@
         <v>137</v>
       </c>
       <c r="BA6" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB6" t="s">
         <v>137</v>
@@ -3389,10 +3395,10 @@
         <v>137</v>
       </c>
       <c r="BF6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="BG6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH6">
         <v>14</v>
@@ -3401,10 +3407,10 @@
         <v>1</v>
       </c>
       <c r="BJ6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="BL6" t="s">
         <v>137</v>
@@ -3422,40 +3428,40 @@
         <v>137</v>
       </c>
       <c r="BQ6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BR6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="BW6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="BX6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="BY6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BZ6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="CB6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC6" t="s">
         <v>138</v>
@@ -3470,13 +3476,13 @@
         <v>5.2</v>
       </c>
       <c r="CG6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CH6">
         <v>6.4</v>
       </c>
       <c r="CI6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CJ6">
         <v>2.63</v>
@@ -3488,7 +3494,7 @@
         <v>0.65</v>
       </c>
       <c r="CM6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CN6">
         <v>4335</v>
@@ -3500,7 +3506,7 @@
         <v>4319.5</v>
       </c>
       <c r="CQ6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="CR6" t="s">
         <v>137</v>
@@ -3517,16 +3523,16 @@
         <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F7" t="s">
         <v>133</v>
       </c>
       <c r="G7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H7" t="s">
         <v>134</v>
@@ -3664,10 +3670,10 @@
         <v>137</v>
       </c>
       <c r="BA7" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="BC7">
         <v>0</v>
@@ -3679,10 +3685,10 @@
         <v>137</v>
       </c>
       <c r="BF7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BG7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="BH7">
         <v>10</v>
@@ -3691,16 +3697,16 @@
         <v>4</v>
       </c>
       <c r="BJ7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BK7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="BL7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="BM7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="BN7" t="s">
         <v>138</v>
@@ -3709,43 +3715,43 @@
         <v>137</v>
       </c>
       <c r="BP7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="BQ7" t="s">
         <v>137</v>
       </c>
       <c r="BR7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="BW7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="BX7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="BY7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="BZ7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="CB7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC7" t="s">
         <v>138</v>
@@ -3766,7 +3772,7 @@
         <v>6.41</v>
       </c>
       <c r="CI7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CJ7">
         <v>3.87</v>
@@ -3778,7 +3784,7 @@
         <v>0.1</v>
       </c>
       <c r="CM7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="CN7">
         <v>9100</v>
@@ -3790,7 +3796,7 @@
         <v>8955.5</v>
       </c>
       <c r="CQ7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="CR7" t="s">
         <v>137</v>
@@ -3807,16 +3813,16 @@
         <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F8" t="s">
         <v>133</v>
       </c>
       <c r="G8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H8" t="s">
         <v>134</v>
@@ -3954,7 +3960,7 @@
         <v>137</v>
       </c>
       <c r="BA8" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB8" t="s">
         <v>137</v>
@@ -3969,10 +3975,10 @@
         <v>137</v>
       </c>
       <c r="BF8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BG8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH8">
         <v>11</v>
@@ -3981,13 +3987,13 @@
         <v>4</v>
       </c>
       <c r="BJ8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="BL8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="BM8" t="s">
         <v>137</v>
@@ -3999,43 +4005,43 @@
         <v>137</v>
       </c>
       <c r="BP8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="BQ8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="BR8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="BW8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="BX8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="BY8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BZ8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="CB8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC8" t="s">
         <v>138</v>
@@ -4056,7 +4062,7 @@
         <v>10.28</v>
       </c>
       <c r="CI8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="CJ8">
         <v>2.1</v>
@@ -4068,7 +4074,7 @@
         <v>0.3</v>
       </c>
       <c r="CM8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CN8">
         <v>2002.3</v>
@@ -4080,7 +4086,7 @@
         <v>1981</v>
       </c>
       <c r="CQ8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="CR8" t="s">
         <v>137</v>
@@ -4091,25 +4097,25 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F9" t="s">
         <v>133</v>
       </c>
       <c r="G9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -4244,16 +4250,16 @@
         <v>137</v>
       </c>
       <c r="BA9" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB9" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="BC9">
         <v>1</v>
       </c>
       <c r="BD9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="BE9" t="s">
         <v>137</v>
@@ -4262,7 +4268,7 @@
         <v>137</v>
       </c>
       <c r="BG9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH9">
         <v>11</v>
@@ -4271,7 +4277,7 @@
         <v>5</v>
       </c>
       <c r="BJ9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK9" t="s">
         <v>137</v>
@@ -4295,37 +4301,37 @@
         <v>137</v>
       </c>
       <c r="BR9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="BW9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="BX9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="BY9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC9" t="s">
         <v>138</v>
@@ -4358,7 +4364,7 @@
         <v>137</v>
       </c>
       <c r="CM9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="CN9">
         <v>425.45</v>
@@ -4370,7 +4376,7 @@
         <v>422.15</v>
       </c>
       <c r="CQ9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="CR9" t="s">
         <v>137</v>
@@ -4381,25 +4387,25 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F10" t="s">
         <v>133</v>
       </c>
       <c r="G10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -4534,7 +4540,7 @@
         <v>137</v>
       </c>
       <c r="BA10" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB10" t="s">
         <v>137</v>
@@ -4552,7 +4558,7 @@
         <v>137</v>
       </c>
       <c r="BG10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH10">
         <v>15</v>
@@ -4561,7 +4567,7 @@
         <v>4</v>
       </c>
       <c r="BJ10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK10" t="s">
         <v>137</v>
@@ -4585,37 +4591,37 @@
         <v>137</v>
       </c>
       <c r="BR10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="BW10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="BX10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="BY10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC10" t="s">
         <v>138</v>
@@ -4648,7 +4654,7 @@
         <v>137</v>
       </c>
       <c r="CM10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CN10">
         <v>6202.5</v>
@@ -4660,7 +4666,7 @@
         <v>6202.5</v>
       </c>
       <c r="CQ10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="CR10" t="s">
         <v>137</v>
@@ -4671,25 +4677,25 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F11" t="s">
         <v>133</v>
       </c>
       <c r="G11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I11" t="s">
         <v>36</v>
@@ -4824,7 +4830,7 @@
         <v>137</v>
       </c>
       <c r="BA11" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB11" t="s">
         <v>137</v>
@@ -4842,7 +4848,7 @@
         <v>137</v>
       </c>
       <c r="BG11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH11">
         <v>14</v>
@@ -4851,7 +4857,7 @@
         <v>3</v>
       </c>
       <c r="BJ11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK11" t="s">
         <v>137</v>
@@ -4875,37 +4881,37 @@
         <v>137</v>
       </c>
       <c r="BR11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="BW11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BX11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BY11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC11" t="s">
         <v>138</v>
@@ -4938,7 +4944,7 @@
         <v>137</v>
       </c>
       <c r="CM11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="CN11">
         <v>1957</v>
@@ -4950,7 +4956,7 @@
         <v>1957</v>
       </c>
       <c r="CQ11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CR11" t="s">
         <v>137</v>
@@ -4961,25 +4967,25 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F12" t="s">
         <v>133</v>
       </c>
       <c r="G12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I12" t="s">
         <v>36</v>
@@ -5114,7 +5120,7 @@
         <v>137</v>
       </c>
       <c r="BA12" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB12" t="s">
         <v>137</v>
@@ -5132,7 +5138,7 @@
         <v>137</v>
       </c>
       <c r="BG12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH12">
         <v>13</v>
@@ -5141,7 +5147,7 @@
         <v>4</v>
       </c>
       <c r="BJ12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK12" t="s">
         <v>137</v>
@@ -5165,37 +5171,37 @@
         <v>137</v>
       </c>
       <c r="BR12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="BW12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="BX12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="BY12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC12" t="s">
         <v>138</v>
@@ -5228,7 +5234,7 @@
         <v>137</v>
       </c>
       <c r="CM12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CN12">
         <v>1303.2</v>
@@ -5240,7 +5246,7 @@
         <v>1303.2</v>
       </c>
       <c r="CQ12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="CR12" t="s">
         <v>137</v>
@@ -5251,25 +5257,25 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F13" t="s">
         <v>133</v>
       </c>
       <c r="G13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I13" t="s">
         <v>36</v>
@@ -5404,7 +5410,7 @@
         <v>137</v>
       </c>
       <c r="BA13" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB13" t="s">
         <v>137</v>
@@ -5422,7 +5428,7 @@
         <v>137</v>
       </c>
       <c r="BG13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH13">
         <v>13</v>
@@ -5431,7 +5437,7 @@
         <v>3</v>
       </c>
       <c r="BJ13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK13" t="s">
         <v>137</v>
@@ -5455,37 +5461,37 @@
         <v>137</v>
       </c>
       <c r="BR13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="BW13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BX13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="BY13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ13" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA13" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC13" t="s">
         <v>138</v>
@@ -5518,7 +5524,7 @@
         <v>137</v>
       </c>
       <c r="CM13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CN13">
         <v>770</v>
@@ -5530,7 +5536,7 @@
         <v>721.4</v>
       </c>
       <c r="CQ13" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="CR13" t="s">
         <v>137</v>
@@ -5541,25 +5547,25 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F14" t="s">
         <v>133</v>
       </c>
       <c r="G14" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I14" t="s">
         <v>36</v>
@@ -5694,7 +5700,7 @@
         <v>137</v>
       </c>
       <c r="BA14" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB14" t="s">
         <v>137</v>
@@ -5712,7 +5718,7 @@
         <v>137</v>
       </c>
       <c r="BG14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH14">
         <v>12</v>
@@ -5721,7 +5727,7 @@
         <v>3</v>
       </c>
       <c r="BJ14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK14" t="s">
         <v>137</v>
@@ -5745,37 +5751,37 @@
         <v>137</v>
       </c>
       <c r="BR14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="BW14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="BX14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BY14" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA14" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC14" t="s">
         <v>138</v>
@@ -5808,7 +5814,7 @@
         <v>137</v>
       </c>
       <c r="CM14" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="CN14">
         <v>2903.2</v>
@@ -5820,7 +5826,7 @@
         <v>2903.2</v>
       </c>
       <c r="CQ14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="CR14" t="s">
         <v>137</v>
@@ -5831,25 +5837,25 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F15" t="s">
         <v>133</v>
       </c>
       <c r="G15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I15" t="s">
         <v>36</v>
@@ -5984,7 +5990,7 @@
         <v>137</v>
       </c>
       <c r="BA15" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB15" t="s">
         <v>137</v>
@@ -6002,7 +6008,7 @@
         <v>137</v>
       </c>
       <c r="BG15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH15">
         <v>13</v>
@@ -6011,7 +6017,7 @@
         <v>4</v>
       </c>
       <c r="BJ15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK15" t="s">
         <v>137</v>
@@ -6035,37 +6041,37 @@
         <v>137</v>
       </c>
       <c r="BR15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="BW15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="BX15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="BY15" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ15" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC15" t="s">
         <v>138</v>
@@ -6098,7 +6104,7 @@
         <v>137</v>
       </c>
       <c r="CM15" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="CN15">
         <v>1321</v>
@@ -6110,7 +6116,7 @@
         <v>1321</v>
       </c>
       <c r="CQ15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CR15" t="s">
         <v>137</v>
@@ -7350,8 +7356,8 @@
       <c r="AJ2">
         <v>3223.2</v>
       </c>
-      <c r="AK2" t="s">
-        <v>137</v>
+      <c r="AK2">
+        <v>0.05</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -7399,7 +7405,7 @@
         <v>137</v>
       </c>
       <c r="BA2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BB2" t="s">
         <v>137</v>
@@ -7411,13 +7417,13 @@
         <v>137</v>
       </c>
       <c r="BE2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BF2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BG2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH2">
         <v>15</v>
@@ -7426,61 +7432,61 @@
         <v>4</v>
       </c>
       <c r="BJ2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BK2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BL2" t="s">
         <v>137</v>
       </c>
       <c r="BM2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BN2" t="s">
         <v>138</v>
       </c>
       <c r="BO2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BP2" t="s">
         <v>137</v>
       </c>
       <c r="BQ2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BR2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BW2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BX2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BY2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BZ2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="CB2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC2" t="s">
         <v>138</v>
@@ -7501,7 +7507,7 @@
         <v>5.72</v>
       </c>
       <c r="CI2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="CJ2">
         <v>8.7</v>
@@ -7513,7 +7519,7 @@
         <v>0.21</v>
       </c>
       <c r="CM2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CN2">
         <v>805.6</v>
@@ -7525,7 +7531,7 @@
         <v>805.6</v>
       </c>
       <c r="CQ2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="CR2" t="s">
         <v>137</v>
@@ -7542,10 +7548,10 @@
         <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
         <v>133</v>
@@ -7640,8 +7646,8 @@
       <c r="AJ3">
         <v>5816.16</v>
       </c>
-      <c r="AK3" t="s">
-        <v>137</v>
+      <c r="AK3">
+        <v>-0.51</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -7689,7 +7695,7 @@
         <v>137</v>
       </c>
       <c r="BA3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BB3" t="s">
         <v>137</v>
@@ -7701,13 +7707,13 @@
         <v>137</v>
       </c>
       <c r="BE3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BF3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BG3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH3">
         <v>22</v>
@@ -7716,10 +7722,10 @@
         <v>4</v>
       </c>
       <c r="BJ3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BK3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BL3" t="s">
         <v>137</v>
@@ -7731,49 +7737,49 @@
         <v>138</v>
       </c>
       <c r="BO3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BP3" t="s">
         <v>137</v>
       </c>
       <c r="BQ3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BR3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BV3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BW3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BX3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BY3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BZ3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="CB3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CD3">
         <v>90.28</v>
@@ -7791,7 +7797,7 @@
         <v>0</v>
       </c>
       <c r="CI3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CJ3">
         <v>15.12</v>
@@ -7803,7 +7809,7 @@
         <v>90.28</v>
       </c>
       <c r="CM3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CN3">
         <v>556.8</v>
@@ -7815,7 +7821,7 @@
         <v>536</v>
       </c>
       <c r="CQ3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="CR3" t="s">
         <v>137</v>
@@ -7829,19 +7835,19 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F4" t="s">
         <v>133</v>
       </c>
       <c r="G4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H4" t="s">
         <v>134</v>
@@ -7850,7 +7856,7 @@
         <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K4">
         <v>19.59</v>
@@ -7859,10 +7865,10 @@
         <v>19.59</v>
       </c>
       <c r="M4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N4">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="O4">
         <v>31</v>
@@ -7871,16 +7877,16 @@
         <v>31</v>
       </c>
       <c r="Q4">
-        <v>607.29</v>
+        <v>313.44</v>
       </c>
       <c r="R4">
-        <v>646.97</v>
+        <v>333.92</v>
       </c>
       <c r="S4">
         <v>20.87</v>
       </c>
       <c r="T4" s="2">
-        <v>39.68</v>
+        <v>20.48</v>
       </c>
       <c r="U4">
         <v>6.53</v>
@@ -7913,7 +7919,7 @@
         <v>137</v>
       </c>
       <c r="AE4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AF4">
         <v>168.93</v>
@@ -7930,8 +7936,8 @@
       <c r="AJ4">
         <v>17.98</v>
       </c>
-      <c r="AK4" t="s">
-        <v>137</v>
+      <c r="AK4">
+        <v>2.21</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -7958,7 +7964,7 @@
         <v>137</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4">
         <v>0</v>
@@ -7979,10 +7985,10 @@
         <v>137</v>
       </c>
       <c r="BA4" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="BB4" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="BC4">
         <v>0</v>
@@ -7991,13 +7997,13 @@
         <v>137</v>
       </c>
       <c r="BE4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BF4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BG4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH4">
         <v>16</v>
@@ -8006,10 +8012,10 @@
         <v>4</v>
       </c>
       <c r="BJ4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BK4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BL4" t="s">
         <v>137</v>
@@ -8021,43 +8027,43 @@
         <v>138</v>
       </c>
       <c r="BO4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BP4" t="s">
         <v>137</v>
       </c>
       <c r="BQ4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BR4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BV4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BW4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="BX4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="BY4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="BZ4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CB4" t="s">
         <v>138</v>
@@ -8081,7 +8087,7 @@
         <v>18.16</v>
       </c>
       <c r="CI4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CJ4">
         <v>1.54</v>
@@ -8093,7 +8099,7 @@
         <v>0.76</v>
       </c>
       <c r="CM4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="CN4">
         <v>20</v>
@@ -8105,7 +8111,7 @@
         <v>19.01</v>
       </c>
       <c r="CQ4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="CR4" t="s">
         <v>137</v>
@@ -8122,16 +8128,16 @@
         <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F5" t="s">
         <v>133</v>
       </c>
       <c r="G5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H5" t="s">
         <v>134</v>
@@ -8269,10 +8275,10 @@
         <v>137</v>
       </c>
       <c r="BA5" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="BC5">
         <v>0</v>
@@ -8284,10 +8290,10 @@
         <v>137</v>
       </c>
       <c r="BF5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BG5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH5">
         <v>12</v>
@@ -8296,10 +8302,10 @@
         <v>4</v>
       </c>
       <c r="BJ5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="BL5" t="s">
         <v>137</v>
@@ -8317,40 +8323,40 @@
         <v>137</v>
       </c>
       <c r="BQ5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BR5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="BW5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="BX5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="BY5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BZ5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="CB5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC5" t="s">
         <v>138</v>
@@ -8371,7 +8377,7 @@
         <v>3.32</v>
       </c>
       <c r="CI5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CJ5">
         <v>13.61</v>
@@ -8383,7 +8389,7 @@
         <v>0.55</v>
       </c>
       <c r="CM5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="CN5">
         <v>199.5</v>
@@ -8395,7 +8401,7 @@
         <v>186.53</v>
       </c>
       <c r="CQ5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="CR5" t="s">
         <v>137</v>
@@ -8412,16 +8418,16 @@
         <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F6" t="s">
         <v>133</v>
       </c>
       <c r="G6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H6" t="s">
         <v>134</v>
@@ -8559,7 +8565,7 @@
         <v>137</v>
       </c>
       <c r="BA6" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB6" t="s">
         <v>137</v>
@@ -8574,10 +8580,10 @@
         <v>137</v>
       </c>
       <c r="BF6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="BG6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH6">
         <v>14</v>
@@ -8586,10 +8592,10 @@
         <v>1</v>
       </c>
       <c r="BJ6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="BL6" t="s">
         <v>137</v>
@@ -8607,40 +8613,40 @@
         <v>137</v>
       </c>
       <c r="BQ6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BR6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="BW6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="BX6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="BY6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BZ6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="CB6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC6" t="s">
         <v>138</v>
@@ -8655,13 +8661,13 @@
         <v>5.2</v>
       </c>
       <c r="CG6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CH6">
         <v>6.4</v>
       </c>
       <c r="CI6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CJ6">
         <v>2.63</v>
@@ -8673,7 +8679,7 @@
         <v>0.65</v>
       </c>
       <c r="CM6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CN6">
         <v>4335</v>
@@ -8685,7 +8691,7 @@
         <v>4319.5</v>
       </c>
       <c r="CQ6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="CR6" t="s">
         <v>137</v>
@@ -8702,16 +8708,16 @@
         <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F7" t="s">
         <v>133</v>
       </c>
       <c r="G7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H7" t="s">
         <v>134</v>
@@ -8849,10 +8855,10 @@
         <v>137</v>
       </c>
       <c r="BA7" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="BC7">
         <v>0</v>
@@ -8864,10 +8870,10 @@
         <v>137</v>
       </c>
       <c r="BF7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BG7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="BH7">
         <v>10</v>
@@ -8876,16 +8882,16 @@
         <v>4</v>
       </c>
       <c r="BJ7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BK7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="BL7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="BM7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="BN7" t="s">
         <v>138</v>
@@ -8894,43 +8900,43 @@
         <v>137</v>
       </c>
       <c r="BP7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="BQ7" t="s">
         <v>137</v>
       </c>
       <c r="BR7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="BW7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="BX7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="BY7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="BZ7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="CB7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC7" t="s">
         <v>138</v>
@@ -8951,7 +8957,7 @@
         <v>6.41</v>
       </c>
       <c r="CI7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CJ7">
         <v>3.87</v>
@@ -8963,7 +8969,7 @@
         <v>0.1</v>
       </c>
       <c r="CM7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="CN7">
         <v>9100</v>
@@ -8975,7 +8981,7 @@
         <v>8955.5</v>
       </c>
       <c r="CQ7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="CR7" t="s">
         <v>137</v>
@@ -8992,16 +8998,16 @@
         <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F8" t="s">
         <v>133</v>
       </c>
       <c r="G8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H8" t="s">
         <v>134</v>
@@ -9139,7 +9145,7 @@
         <v>137</v>
       </c>
       <c r="BA8" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB8" t="s">
         <v>137</v>
@@ -9154,10 +9160,10 @@
         <v>137</v>
       </c>
       <c r="BF8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BG8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH8">
         <v>11</v>
@@ -9166,13 +9172,13 @@
         <v>4</v>
       </c>
       <c r="BJ8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="BL8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="BM8" t="s">
         <v>137</v>
@@ -9184,43 +9190,43 @@
         <v>137</v>
       </c>
       <c r="BP8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="BQ8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="BR8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="BW8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="BX8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="BY8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BZ8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="CA8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="CB8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC8" t="s">
         <v>138</v>
@@ -9241,7 +9247,7 @@
         <v>10.28</v>
       </c>
       <c r="CI8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="CJ8">
         <v>2.1</v>
@@ -9253,7 +9259,7 @@
         <v>0.3</v>
       </c>
       <c r="CM8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CN8">
         <v>2002.3</v>
@@ -9265,7 +9271,7 @@
         <v>1981</v>
       </c>
       <c r="CQ8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="CR8" t="s">
         <v>137</v>
@@ -9276,25 +9282,25 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F9" t="s">
         <v>133</v>
       </c>
       <c r="G9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -9429,16 +9435,16 @@
         <v>137</v>
       </c>
       <c r="BA9" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB9" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="BC9">
         <v>1</v>
       </c>
       <c r="BD9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="BE9" t="s">
         <v>137</v>
@@ -9447,7 +9453,7 @@
         <v>137</v>
       </c>
       <c r="BG9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH9">
         <v>11</v>
@@ -9456,7 +9462,7 @@
         <v>5</v>
       </c>
       <c r="BJ9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK9" t="s">
         <v>137</v>
@@ -9480,37 +9486,37 @@
         <v>137</v>
       </c>
       <c r="BR9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="BW9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="BX9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="BY9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC9" t="s">
         <v>138</v>
@@ -9543,7 +9549,7 @@
         <v>137</v>
       </c>
       <c r="CM9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="CN9">
         <v>425.45</v>
@@ -9555,7 +9561,7 @@
         <v>422.15</v>
       </c>
       <c r="CQ9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="CR9" t="s">
         <v>137</v>
@@ -9566,25 +9572,25 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F10" t="s">
         <v>133</v>
       </c>
       <c r="G10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -9719,7 +9725,7 @@
         <v>137</v>
       </c>
       <c r="BA10" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB10" t="s">
         <v>137</v>
@@ -9737,7 +9743,7 @@
         <v>137</v>
       </c>
       <c r="BG10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH10">
         <v>15</v>
@@ -9746,7 +9752,7 @@
         <v>4</v>
       </c>
       <c r="BJ10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK10" t="s">
         <v>137</v>
@@ -9770,37 +9776,37 @@
         <v>137</v>
       </c>
       <c r="BR10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="BW10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="BX10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="BY10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC10" t="s">
         <v>138</v>
@@ -9833,7 +9839,7 @@
         <v>137</v>
       </c>
       <c r="CM10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CN10">
         <v>6202.5</v>
@@ -9845,7 +9851,7 @@
         <v>6202.5</v>
       </c>
       <c r="CQ10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="CR10" t="s">
         <v>137</v>
@@ -9856,25 +9862,25 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F11" t="s">
         <v>133</v>
       </c>
       <c r="G11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I11" t="s">
         <v>36</v>
@@ -10009,7 +10015,7 @@
         <v>137</v>
       </c>
       <c r="BA11" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB11" t="s">
         <v>137</v>
@@ -10027,7 +10033,7 @@
         <v>137</v>
       </c>
       <c r="BG11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH11">
         <v>14</v>
@@ -10036,7 +10042,7 @@
         <v>3</v>
       </c>
       <c r="BJ11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK11" t="s">
         <v>137</v>
@@ -10060,37 +10066,37 @@
         <v>137</v>
       </c>
       <c r="BR11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="BW11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BX11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BY11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC11" t="s">
         <v>138</v>
@@ -10123,7 +10129,7 @@
         <v>137</v>
       </c>
       <c r="CM11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="CN11">
         <v>1957</v>
@@ -10135,7 +10141,7 @@
         <v>1957</v>
       </c>
       <c r="CQ11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CR11" t="s">
         <v>137</v>
@@ -10146,25 +10152,25 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F12" t="s">
         <v>133</v>
       </c>
       <c r="G12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I12" t="s">
         <v>36</v>
@@ -10299,7 +10305,7 @@
         <v>137</v>
       </c>
       <c r="BA12" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB12" t="s">
         <v>137</v>
@@ -10317,7 +10323,7 @@
         <v>137</v>
       </c>
       <c r="BG12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH12">
         <v>13</v>
@@ -10326,7 +10332,7 @@
         <v>4</v>
       </c>
       <c r="BJ12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK12" t="s">
         <v>137</v>
@@ -10350,37 +10356,37 @@
         <v>137</v>
       </c>
       <c r="BR12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="BW12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="BX12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="BY12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC12" t="s">
         <v>138</v>
@@ -10413,7 +10419,7 @@
         <v>137</v>
       </c>
       <c r="CM12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CN12">
         <v>1303.2</v>
@@ -10425,7 +10431,7 @@
         <v>1303.2</v>
       </c>
       <c r="CQ12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="CR12" t="s">
         <v>137</v>
@@ -10436,25 +10442,25 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F13" t="s">
         <v>133</v>
       </c>
       <c r="G13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I13" t="s">
         <v>36</v>
@@ -10589,7 +10595,7 @@
         <v>137</v>
       </c>
       <c r="BA13" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB13" t="s">
         <v>137</v>
@@ -10607,7 +10613,7 @@
         <v>137</v>
       </c>
       <c r="BG13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH13">
         <v>13</v>
@@ -10616,7 +10622,7 @@
         <v>3</v>
       </c>
       <c r="BJ13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK13" t="s">
         <v>137</v>
@@ -10640,37 +10646,37 @@
         <v>137</v>
       </c>
       <c r="BR13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="BW13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BX13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="BY13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ13" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA13" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC13" t="s">
         <v>138</v>
@@ -10703,7 +10709,7 @@
         <v>137</v>
       </c>
       <c r="CM13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CN13">
         <v>770</v>
@@ -10715,7 +10721,7 @@
         <v>721.4</v>
       </c>
       <c r="CQ13" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="CR13" t="s">
         <v>137</v>
@@ -10726,25 +10732,25 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F14" t="s">
         <v>133</v>
       </c>
       <c r="G14" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I14" t="s">
         <v>36</v>
@@ -10879,7 +10885,7 @@
         <v>137</v>
       </c>
       <c r="BA14" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB14" t="s">
         <v>137</v>
@@ -10897,7 +10903,7 @@
         <v>137</v>
       </c>
       <c r="BG14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH14">
         <v>12</v>
@@ -10906,7 +10912,7 @@
         <v>3</v>
       </c>
       <c r="BJ14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK14" t="s">
         <v>137</v>
@@ -10930,37 +10936,37 @@
         <v>137</v>
       </c>
       <c r="BR14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="BW14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="BX14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BY14" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA14" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC14" t="s">
         <v>138</v>
@@ -10993,7 +10999,7 @@
         <v>137</v>
       </c>
       <c r="CM14" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="CN14">
         <v>2903.2</v>
@@ -11005,7 +11011,7 @@
         <v>2903.2</v>
       </c>
       <c r="CQ14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="CR14" t="s">
         <v>137</v>
@@ -11016,25 +11022,25 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F15" t="s">
         <v>133</v>
       </c>
       <c r="G15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I15" t="s">
         <v>36</v>
@@ -11169,7 +11175,7 @@
         <v>137</v>
       </c>
       <c r="BA15" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="BB15" t="s">
         <v>137</v>
@@ -11187,7 +11193,7 @@
         <v>137</v>
       </c>
       <c r="BG15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH15">
         <v>13</v>
@@ -11196,7 +11202,7 @@
         <v>4</v>
       </c>
       <c r="BJ15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK15" t="s">
         <v>137</v>
@@ -11220,37 +11226,37 @@
         <v>137</v>
       </c>
       <c r="BR15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BV15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="BW15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="BX15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="BY15" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ15" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="CB15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC15" t="s">
         <v>138</v>
@@ -11283,7 +11289,7 @@
         <v>137</v>
       </c>
       <c r="CM15" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="CN15">
         <v>1321</v>
@@ -11295,7 +11301,7 @@
         <v>1321</v>
       </c>
       <c r="CQ15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CR15" t="s">
         <v>137</v>
@@ -11309,19 +11315,19 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D16" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E16" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F16" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H16" t="s">
         <v>137</v>
@@ -11339,7 +11345,7 @@
         <v>137</v>
       </c>
       <c r="M16" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N16" t="s">
         <v>137</v>
@@ -11393,7 +11399,7 @@
         <v>137</v>
       </c>
       <c r="AE16" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AF16" t="s">
         <v>137</v>
@@ -11474,10 +11480,10 @@
         <v>137</v>
       </c>
       <c r="BF16" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="BG16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH16">
         <v>17</v>
@@ -11486,7 +11492,7 @@
         <v>4</v>
       </c>
       <c r="BJ16" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="BK16" t="s">
         <v>137</v>
@@ -11510,37 +11516,37 @@
         <v>137</v>
       </c>
       <c r="BR16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS16" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="BT16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BV16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BW16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BX16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="BY16" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ16" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="CB16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC16" t="s">
         <v>138</v>
@@ -11555,13 +11561,13 @@
         <v>6.95</v>
       </c>
       <c r="CG16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CH16">
         <v>6.81</v>
       </c>
       <c r="CI16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CJ16">
         <v>2.21</v>
@@ -11573,7 +11579,7 @@
         <v>0.99</v>
       </c>
       <c r="CM16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CN16">
         <v>4331</v>
@@ -11585,7 +11591,7 @@
         <v>4305.8</v>
       </c>
       <c r="CQ16" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="CR16" t="s">
         <v>137</v>
@@ -11599,19 +11605,19 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H17" t="s">
         <v>137</v>
@@ -11629,7 +11635,7 @@
         <v>137</v>
       </c>
       <c r="M17" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N17" t="s">
         <v>137</v>
@@ -11683,7 +11689,7 @@
         <v>137</v>
       </c>
       <c r="AE17" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AF17" t="s">
         <v>137</v>
@@ -11764,10 +11770,10 @@
         <v>137</v>
       </c>
       <c r="BF17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BG17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BH17">
         <v>16</v>
@@ -11776,7 +11782,7 @@
         <v>4</v>
       </c>
       <c r="BJ17" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="BK17" t="s">
         <v>137</v>
@@ -11800,40 +11806,40 @@
         <v>137</v>
       </c>
       <c r="BR17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS17" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="BT17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU17" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BV17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="BW17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="BX17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="BY17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ17" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="CB17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CD17">
         <v>1.56</v>
@@ -11851,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="CI17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="CJ17">
         <v>1.19</v>
@@ -11863,7 +11869,7 @@
         <v>1.56</v>
       </c>
       <c r="CM17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CN17">
         <v>1048</v>
@@ -11875,7 +11881,7 @@
         <v>1012.9</v>
       </c>
       <c r="CQ17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="CR17" t="s">
         <v>137</v>
@@ -11889,19 +11895,19 @@
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D18" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E18" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F18" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H18" t="s">
         <v>137</v>
@@ -11919,7 +11925,7 @@
         <v>137</v>
       </c>
       <c r="M18" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N18" t="s">
         <v>137</v>
@@ -11973,7 +11979,7 @@
         <v>137</v>
       </c>
       <c r="AE18" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AF18" t="s">
         <v>137</v>
@@ -12054,10 +12060,10 @@
         <v>137</v>
       </c>
       <c r="BF18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BG18" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="BH18">
         <v>12</v>
@@ -12066,7 +12072,7 @@
         <v>2</v>
       </c>
       <c r="BJ18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK18" t="s">
         <v>137</v>
@@ -12090,37 +12096,37 @@
         <v>137</v>
       </c>
       <c r="BR18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BS18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BU18" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BV18" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="BW18" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="BX18" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="BY18" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BZ18" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="CA18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="CB18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CC18" t="s">
         <v>138</v>
@@ -12141,7 +12147,7 @@
         <v>8.22</v>
       </c>
       <c r="CI18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CJ18">
         <v>6</v>
@@ -12153,7 +12159,7 @@
         <v>0.42</v>
       </c>
       <c r="CM18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CN18">
         <v>701.8</v>
@@ -12165,7 +12171,7 @@
         <v>688.05</v>
       </c>
       <c r="CQ18" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="CR18" t="s">
         <v>137</v>
@@ -12206,57 +12212,57 @@
         <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>91</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
@@ -12265,10 +12271,10 @@
         <v>134</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F2">
-        <v>194.22</v>
+        <v>199.89</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -12286,10 +12292,10 @@
         <v>2.1</v>
       </c>
       <c r="L2">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -12301,27 +12307,27 @@
         <v>794.42</v>
       </c>
       <c r="Q2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F3">
-        <v>190.17</v>
+        <v>195.83</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -12339,10 +12345,10 @@
         <v>1.44</v>
       </c>
       <c r="L3">
-        <v>5.66</v>
+        <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -12354,24 +12360,24 @@
         <v>628.33</v>
       </c>
       <c r="Q3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F4">
         <v>170.4</v>
@@ -12395,7 +12401,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -12407,7 +12413,7 @@
         <v>790</v>
       </c>
       <c r="Q4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -12439,81 +12445,81 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="Q1" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B2" t="s">
         <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E2" t="s">
         <v>134</v>
       </c>
       <c r="G2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J2">
         <v>186.88</v>
@@ -12537,18 +12543,18 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B3" t="s">
         <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -12557,13 +12563,13 @@
         <v>134</v>
       </c>
       <c r="G3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J3">
         <v>170.68</v>
@@ -12587,33 +12593,33 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B4" t="s">
         <v>134</v>
       </c>
       <c r="C4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E4" t="s">
         <v>134</v>
       </c>
       <c r="G4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J4">
         <v>170.12</v>
@@ -12637,18 +12643,18 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
         <v>134</v>
       </c>
       <c r="C5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -12657,13 +12663,13 @@
         <v>134</v>
       </c>
       <c r="G5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J5">
         <v>160.76</v>
@@ -12687,18 +12693,18 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B6" t="s">
         <v>134</v>
       </c>
       <c r="C6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -12710,13 +12716,13 @@
         <v>622.5499877929688</v>
       </c>
       <c r="G6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J6">
         <v>195.78</v>
@@ -12740,18 +12746,18 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B7" t="s">
         <v>134</v>
       </c>
       <c r="C7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -12763,16 +12769,16 @@
         <v>863.5</v>
       </c>
       <c r="G7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H7" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J7">
-        <v>194.22</v>
+        <v>199.89</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -12787,45 +12793,45 @@
         <v>2.1</v>
       </c>
       <c r="O7">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F8">
         <v>637.9000244140625</v>
       </c>
       <c r="G8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H8" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J8">
-        <v>190.17</v>
+        <v>195.83</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -12840,42 +12846,42 @@
         <v>1.44</v>
       </c>
       <c r="O8">
-        <v>5.66</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F9">
         <v>814.9000244140625</v>
       </c>
       <c r="G9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J9">
         <v>170.4</v>
@@ -12899,7 +12905,7 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -12923,30 +12929,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -12958,7 +12964,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2679" uniqueCount="341">
   <si>
     <t>Metric</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T05:01:25.925Z</t>
+    <t>2026-07-14T05:14:01.566Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -563,12 +563,6 @@
     <t>09:17 order / 09:21 actual fill</t>
   </si>
   <si>
-    <t>PARTIAL_EXIT</t>
-  </si>
-  <si>
-    <t>Profit reached 2.21R; lock 50% and trail the balance.</t>
-  </si>
-  <si>
     <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Bollinger trend/range context; MACD and OBV confirmation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
@@ -1019,7 +1013,7 @@
     <t>ROTATION_DEFERRED</t>
   </si>
   <si>
-    <t>2026-07-14T05:01:25.100Z</t>
+    <t>2026-07-14T05:14:01.226Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -2751,8 +2745,8 @@
       <c r="AJ4">
         <v>17.98</v>
       </c>
-      <c r="AK4">
-        <v>2.21</v>
+      <c r="AK4" t="s">
+        <v>137</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2800,10 +2794,10 @@
         <v>137</v>
       </c>
       <c r="BA4" t="s">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="BB4" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="BC4">
         <v>0</v>
@@ -2866,19 +2860,19 @@
         <v>152</v>
       </c>
       <c r="BW4" t="s">
+        <v>181</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>182</v>
+      </c>
+      <c r="BY4" t="s">
         <v>183</v>
-      </c>
-      <c r="BX4" t="s">
-        <v>184</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>185</v>
       </c>
       <c r="BZ4" t="s">
         <v>156</v>
       </c>
       <c r="CA4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CB4" t="s">
         <v>138</v>
@@ -2914,7 +2908,7 @@
         <v>0.76</v>
       </c>
       <c r="CM4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="CN4">
         <v>20</v>
@@ -2926,7 +2920,7 @@
         <v>19.01</v>
       </c>
       <c r="CQ4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="CR4" t="s">
         <v>137</v>
@@ -2943,10 +2937,10 @@
         <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F5" t="s">
         <v>133</v>
@@ -3093,7 +3087,7 @@
         <v>139</v>
       </c>
       <c r="BB5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="BC5">
         <v>0</v>
@@ -3117,10 +3111,10 @@
         <v>4</v>
       </c>
       <c r="BJ5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BL5" t="s">
         <v>137</v>
@@ -3153,13 +3147,13 @@
         <v>151</v>
       </c>
       <c r="BV5" t="s">
+        <v>192</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>193</v>
+      </c>
+      <c r="BX5" t="s">
         <v>194</v>
-      </c>
-      <c r="BW5" t="s">
-        <v>195</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>196</v>
       </c>
       <c r="BY5" t="s">
         <v>155</v>
@@ -3168,7 +3162,7 @@
         <v>156</v>
       </c>
       <c r="CA5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="CB5" t="s">
         <v>158</v>
@@ -3204,7 +3198,7 @@
         <v>0.55</v>
       </c>
       <c r="CM5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CN5">
         <v>199.5</v>
@@ -3216,7 +3210,7 @@
         <v>186.53</v>
       </c>
       <c r="CQ5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="CR5" t="s">
         <v>137</v>
@@ -3233,10 +3227,10 @@
         <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F6" t="s">
         <v>133</v>
@@ -3395,7 +3389,7 @@
         <v>137</v>
       </c>
       <c r="BF6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="BG6" t="s">
         <v>142</v>
@@ -3407,10 +3401,10 @@
         <v>1</v>
       </c>
       <c r="BJ6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BL6" t="s">
         <v>137</v>
@@ -3443,13 +3437,13 @@
         <v>151</v>
       </c>
       <c r="BV6" t="s">
+        <v>201</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>202</v>
+      </c>
+      <c r="BX6" t="s">
         <v>203</v>
-      </c>
-      <c r="BW6" t="s">
-        <v>204</v>
-      </c>
-      <c r="BX6" t="s">
-        <v>205</v>
       </c>
       <c r="BY6" t="s">
         <v>155</v>
@@ -3458,7 +3452,7 @@
         <v>156</v>
       </c>
       <c r="CA6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="CB6" t="s">
         <v>158</v>
@@ -3506,7 +3500,7 @@
         <v>4319.5</v>
       </c>
       <c r="CQ6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="CR6" t="s">
         <v>137</v>
@@ -3523,10 +3517,10 @@
         <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F7" t="s">
         <v>133</v>
@@ -3673,7 +3667,7 @@
         <v>139</v>
       </c>
       <c r="BB7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="BC7">
         <v>0</v>
@@ -3688,7 +3682,7 @@
         <v>141</v>
       </c>
       <c r="BG7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="BH7">
         <v>10</v>
@@ -3700,13 +3694,13 @@
         <v>143</v>
       </c>
       <c r="BK7" t="s">
+        <v>209</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>210</v>
+      </c>
+      <c r="BM7" t="s">
         <v>211</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>212</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>213</v>
       </c>
       <c r="BN7" t="s">
         <v>138</v>
@@ -3715,7 +3709,7 @@
         <v>137</v>
       </c>
       <c r="BP7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="BQ7" t="s">
         <v>137</v>
@@ -3733,22 +3727,22 @@
         <v>151</v>
       </c>
       <c r="BV7" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX7" t="s">
         <v>215</v>
       </c>
-      <c r="BW7" t="s">
+      <c r="BY7" t="s">
         <v>216</v>
-      </c>
-      <c r="BX7" t="s">
-        <v>217</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>218</v>
       </c>
       <c r="BZ7" t="s">
         <v>156</v>
       </c>
       <c r="CA7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="CB7" t="s">
         <v>158</v>
@@ -3784,7 +3778,7 @@
         <v>0.1</v>
       </c>
       <c r="CM7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CN7">
         <v>9100</v>
@@ -3796,7 +3790,7 @@
         <v>8955.5</v>
       </c>
       <c r="CQ7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="CR7" t="s">
         <v>137</v>
@@ -3813,10 +3807,10 @@
         <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F8" t="s">
         <v>133</v>
@@ -3987,13 +3981,13 @@
         <v>4</v>
       </c>
       <c r="BJ8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="BL8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="BM8" t="s">
         <v>137</v>
@@ -4005,10 +3999,10 @@
         <v>137</v>
       </c>
       <c r="BP8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="BQ8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="BR8" t="s">
         <v>148</v>
@@ -4023,13 +4017,13 @@
         <v>151</v>
       </c>
       <c r="BV8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="BW8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="BX8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="BY8" t="s">
         <v>155</v>
@@ -4038,7 +4032,7 @@
         <v>156</v>
       </c>
       <c r="CA8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="CB8" t="s">
         <v>158</v>
@@ -4086,7 +4080,7 @@
         <v>1981</v>
       </c>
       <c r="CQ8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="CR8" t="s">
         <v>137</v>
@@ -4097,22 +4091,22 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" t="s">
         <v>230</v>
       </c>
-      <c r="C9" t="s">
-        <v>231</v>
-      </c>
-      <c r="D9" t="s">
-        <v>232</v>
-      </c>
       <c r="E9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F9" t="s">
         <v>133</v>
       </c>
       <c r="G9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H9" t="s">
         <v>177</v>
@@ -4253,13 +4247,13 @@
         <v>139</v>
       </c>
       <c r="BB9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="BC9">
         <v>1</v>
       </c>
       <c r="BD9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="BE9" t="s">
         <v>137</v>
@@ -4277,7 +4271,7 @@
         <v>5</v>
       </c>
       <c r="BJ9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK9" t="s">
         <v>137</v>
@@ -4313,22 +4307,22 @@
         <v>151</v>
       </c>
       <c r="BV9" t="s">
+        <v>234</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>235</v>
+      </c>
+      <c r="BX9" t="s">
         <v>236</v>
       </c>
-      <c r="BW9" t="s">
+      <c r="BY9" t="s">
         <v>237</v>
       </c>
-      <c r="BX9" t="s">
+      <c r="BZ9" t="s">
         <v>238</v>
       </c>
-      <c r="BY9" t="s">
+      <c r="CA9" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA9" t="s">
-        <v>241</v>
       </c>
       <c r="CB9" t="s">
         <v>158</v>
@@ -4364,7 +4358,7 @@
         <v>137</v>
       </c>
       <c r="CM9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CN9">
         <v>425.45</v>
@@ -4376,7 +4370,7 @@
         <v>422.15</v>
       </c>
       <c r="CQ9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="CR9" t="s">
         <v>137</v>
@@ -4387,22 +4381,22 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F10" t="s">
         <v>133</v>
       </c>
       <c r="G10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H10" t="s">
         <v>177</v>
@@ -4567,7 +4561,7 @@
         <v>4</v>
       </c>
       <c r="BJ10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK10" t="s">
         <v>137</v>
@@ -4603,22 +4597,22 @@
         <v>151</v>
       </c>
       <c r="BV10" t="s">
+        <v>242</v>
+      </c>
+      <c r="BW10" t="s">
+        <v>243</v>
+      </c>
+      <c r="BX10" t="s">
         <v>244</v>
       </c>
-      <c r="BW10" t="s">
-        <v>245</v>
-      </c>
-      <c r="BX10" t="s">
-        <v>246</v>
-      </c>
       <c r="BY10" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ10" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA10" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ10" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA10" t="s">
-        <v>241</v>
       </c>
       <c r="CB10" t="s">
         <v>158</v>
@@ -4666,7 +4660,7 @@
         <v>6202.5</v>
       </c>
       <c r="CQ10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="CR10" t="s">
         <v>137</v>
@@ -4677,22 +4671,22 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F11" t="s">
         <v>133</v>
       </c>
       <c r="G11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H11" t="s">
         <v>177</v>
@@ -4857,7 +4851,7 @@
         <v>3</v>
       </c>
       <c r="BJ11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK11" t="s">
         <v>137</v>
@@ -4893,22 +4887,22 @@
         <v>151</v>
       </c>
       <c r="BV11" t="s">
+        <v>248</v>
+      </c>
+      <c r="BW11" t="s">
+        <v>249</v>
+      </c>
+      <c r="BX11" t="s">
         <v>250</v>
       </c>
-      <c r="BW11" t="s">
-        <v>251</v>
-      </c>
-      <c r="BX11" t="s">
-        <v>252</v>
-      </c>
       <c r="BY11" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ11" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA11" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ11" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA11" t="s">
-        <v>241</v>
       </c>
       <c r="CB11" t="s">
         <v>158</v>
@@ -4944,7 +4938,7 @@
         <v>137</v>
       </c>
       <c r="CM11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CN11">
         <v>1957</v>
@@ -4956,7 +4950,7 @@
         <v>1957</v>
       </c>
       <c r="CQ11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="CR11" t="s">
         <v>137</v>
@@ -4967,22 +4961,22 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F12" t="s">
         <v>133</v>
       </c>
       <c r="G12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H12" t="s">
         <v>177</v>
@@ -5147,7 +5141,7 @@
         <v>4</v>
       </c>
       <c r="BJ12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK12" t="s">
         <v>137</v>
@@ -5183,22 +5177,22 @@
         <v>151</v>
       </c>
       <c r="BV12" t="s">
+        <v>253</v>
+      </c>
+      <c r="BW12" t="s">
+        <v>254</v>
+      </c>
+      <c r="BX12" t="s">
         <v>255</v>
       </c>
-      <c r="BW12" t="s">
-        <v>256</v>
-      </c>
-      <c r="BX12" t="s">
-        <v>257</v>
-      </c>
       <c r="BY12" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ12" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA12" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ12" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA12" t="s">
-        <v>241</v>
       </c>
       <c r="CB12" t="s">
         <v>158</v>
@@ -5246,7 +5240,7 @@
         <v>1303.2</v>
       </c>
       <c r="CQ12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="CR12" t="s">
         <v>137</v>
@@ -5257,22 +5251,22 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F13" t="s">
         <v>133</v>
       </c>
       <c r="G13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H13" t="s">
         <v>177</v>
@@ -5437,7 +5431,7 @@
         <v>3</v>
       </c>
       <c r="BJ13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK13" t="s">
         <v>137</v>
@@ -5473,22 +5467,22 @@
         <v>151</v>
       </c>
       <c r="BV13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="BW13" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="BX13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="BY13" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ13" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA13" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ13" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA13" t="s">
-        <v>241</v>
       </c>
       <c r="CB13" t="s">
         <v>158</v>
@@ -5536,7 +5530,7 @@
         <v>721.4</v>
       </c>
       <c r="CQ13" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="CR13" t="s">
         <v>137</v>
@@ -5547,22 +5541,22 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F14" t="s">
         <v>133</v>
       </c>
       <c r="G14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H14" t="s">
         <v>177</v>
@@ -5727,7 +5721,7 @@
         <v>3</v>
       </c>
       <c r="BJ14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK14" t="s">
         <v>137</v>
@@ -5763,22 +5757,22 @@
         <v>151</v>
       </c>
       <c r="BV14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="BW14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="BX14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="BY14" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ14" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA14" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ14" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA14" t="s">
-        <v>241</v>
       </c>
       <c r="CB14" t="s">
         <v>158</v>
@@ -5814,7 +5808,7 @@
         <v>137</v>
       </c>
       <c r="CM14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CN14">
         <v>2903.2</v>
@@ -5826,7 +5820,7 @@
         <v>2903.2</v>
       </c>
       <c r="CQ14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="CR14" t="s">
         <v>137</v>
@@ -5837,22 +5831,22 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F15" t="s">
         <v>133</v>
       </c>
       <c r="G15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H15" t="s">
         <v>177</v>
@@ -6017,7 +6011,7 @@
         <v>4</v>
       </c>
       <c r="BJ15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK15" t="s">
         <v>137</v>
@@ -6053,22 +6047,22 @@
         <v>151</v>
       </c>
       <c r="BV15" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="BW15" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="BX15" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="BY15" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ15" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA15" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ15" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA15" t="s">
-        <v>241</v>
       </c>
       <c r="CB15" t="s">
         <v>158</v>
@@ -6104,7 +6098,7 @@
         <v>137</v>
       </c>
       <c r="CM15" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="CN15">
         <v>1321</v>
@@ -6116,7 +6110,7 @@
         <v>1321</v>
       </c>
       <c r="CQ15" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="CR15" t="s">
         <v>137</v>
@@ -7936,8 +7930,8 @@
       <c r="AJ4">
         <v>17.98</v>
       </c>
-      <c r="AK4">
-        <v>2.21</v>
+      <c r="AK4" t="s">
+        <v>137</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -7985,10 +7979,10 @@
         <v>137</v>
       </c>
       <c r="BA4" t="s">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="BB4" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="BC4">
         <v>0</v>
@@ -8051,19 +8045,19 @@
         <v>152</v>
       </c>
       <c r="BW4" t="s">
+        <v>181</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>182</v>
+      </c>
+      <c r="BY4" t="s">
         <v>183</v>
-      </c>
-      <c r="BX4" t="s">
-        <v>184</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>185</v>
       </c>
       <c r="BZ4" t="s">
         <v>156</v>
       </c>
       <c r="CA4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CB4" t="s">
         <v>138</v>
@@ -8099,7 +8093,7 @@
         <v>0.76</v>
       </c>
       <c r="CM4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="CN4">
         <v>20</v>
@@ -8111,7 +8105,7 @@
         <v>19.01</v>
       </c>
       <c r="CQ4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="CR4" t="s">
         <v>137</v>
@@ -8128,10 +8122,10 @@
         <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F5" t="s">
         <v>133</v>
@@ -8278,7 +8272,7 @@
         <v>139</v>
       </c>
       <c r="BB5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="BC5">
         <v>0</v>
@@ -8302,10 +8296,10 @@
         <v>4</v>
       </c>
       <c r="BJ5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BL5" t="s">
         <v>137</v>
@@ -8338,13 +8332,13 @@
         <v>151</v>
       </c>
       <c r="BV5" t="s">
+        <v>192</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>193</v>
+      </c>
+      <c r="BX5" t="s">
         <v>194</v>
-      </c>
-      <c r="BW5" t="s">
-        <v>195</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>196</v>
       </c>
       <c r="BY5" t="s">
         <v>155</v>
@@ -8353,7 +8347,7 @@
         <v>156</v>
       </c>
       <c r="CA5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="CB5" t="s">
         <v>158</v>
@@ -8389,7 +8383,7 @@
         <v>0.55</v>
       </c>
       <c r="CM5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CN5">
         <v>199.5</v>
@@ -8401,7 +8395,7 @@
         <v>186.53</v>
       </c>
       <c r="CQ5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="CR5" t="s">
         <v>137</v>
@@ -8418,10 +8412,10 @@
         <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F6" t="s">
         <v>133</v>
@@ -8580,7 +8574,7 @@
         <v>137</v>
       </c>
       <c r="BF6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="BG6" t="s">
         <v>142</v>
@@ -8592,10 +8586,10 @@
         <v>1</v>
       </c>
       <c r="BJ6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BL6" t="s">
         <v>137</v>
@@ -8628,13 +8622,13 @@
         <v>151</v>
       </c>
       <c r="BV6" t="s">
+        <v>201</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>202</v>
+      </c>
+      <c r="BX6" t="s">
         <v>203</v>
-      </c>
-      <c r="BW6" t="s">
-        <v>204</v>
-      </c>
-      <c r="BX6" t="s">
-        <v>205</v>
       </c>
       <c r="BY6" t="s">
         <v>155</v>
@@ -8643,7 +8637,7 @@
         <v>156</v>
       </c>
       <c r="CA6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="CB6" t="s">
         <v>158</v>
@@ -8691,7 +8685,7 @@
         <v>4319.5</v>
       </c>
       <c r="CQ6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="CR6" t="s">
         <v>137</v>
@@ -8708,10 +8702,10 @@
         <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F7" t="s">
         <v>133</v>
@@ -8858,7 +8852,7 @@
         <v>139</v>
       </c>
       <c r="BB7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="BC7">
         <v>0</v>
@@ -8873,7 +8867,7 @@
         <v>141</v>
       </c>
       <c r="BG7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="BH7">
         <v>10</v>
@@ -8885,13 +8879,13 @@
         <v>143</v>
       </c>
       <c r="BK7" t="s">
+        <v>209</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>210</v>
+      </c>
+      <c r="BM7" t="s">
         <v>211</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>212</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>213</v>
       </c>
       <c r="BN7" t="s">
         <v>138</v>
@@ -8900,7 +8894,7 @@
         <v>137</v>
       </c>
       <c r="BP7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="BQ7" t="s">
         <v>137</v>
@@ -8918,22 +8912,22 @@
         <v>151</v>
       </c>
       <c r="BV7" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX7" t="s">
         <v>215</v>
       </c>
-      <c r="BW7" t="s">
+      <c r="BY7" t="s">
         <v>216</v>
-      </c>
-      <c r="BX7" t="s">
-        <v>217</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>218</v>
       </c>
       <c r="BZ7" t="s">
         <v>156</v>
       </c>
       <c r="CA7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="CB7" t="s">
         <v>158</v>
@@ -8969,7 +8963,7 @@
         <v>0.1</v>
       </c>
       <c r="CM7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CN7">
         <v>9100</v>
@@ -8981,7 +8975,7 @@
         <v>8955.5</v>
       </c>
       <c r="CQ7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="CR7" t="s">
         <v>137</v>
@@ -8998,10 +8992,10 @@
         <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F8" t="s">
         <v>133</v>
@@ -9172,13 +9166,13 @@
         <v>4</v>
       </c>
       <c r="BJ8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="BL8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="BM8" t="s">
         <v>137</v>
@@ -9190,10 +9184,10 @@
         <v>137</v>
       </c>
       <c r="BP8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="BQ8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="BR8" t="s">
         <v>148</v>
@@ -9208,13 +9202,13 @@
         <v>151</v>
       </c>
       <c r="BV8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="BW8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="BX8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="BY8" t="s">
         <v>155</v>
@@ -9223,7 +9217,7 @@
         <v>156</v>
       </c>
       <c r="CA8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="CB8" t="s">
         <v>158</v>
@@ -9271,7 +9265,7 @@
         <v>1981</v>
       </c>
       <c r="CQ8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="CR8" t="s">
         <v>137</v>
@@ -9282,22 +9276,22 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" t="s">
         <v>230</v>
       </c>
-      <c r="C9" t="s">
-        <v>231</v>
-      </c>
-      <c r="D9" t="s">
-        <v>232</v>
-      </c>
       <c r="E9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F9" t="s">
         <v>133</v>
       </c>
       <c r="G9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H9" t="s">
         <v>177</v>
@@ -9438,13 +9432,13 @@
         <v>139</v>
       </c>
       <c r="BB9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="BC9">
         <v>1</v>
       </c>
       <c r="BD9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="BE9" t="s">
         <v>137</v>
@@ -9462,7 +9456,7 @@
         <v>5</v>
       </c>
       <c r="BJ9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK9" t="s">
         <v>137</v>
@@ -9498,22 +9492,22 @@
         <v>151</v>
       </c>
       <c r="BV9" t="s">
+        <v>234</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>235</v>
+      </c>
+      <c r="BX9" t="s">
         <v>236</v>
       </c>
-      <c r="BW9" t="s">
+      <c r="BY9" t="s">
         <v>237</v>
       </c>
-      <c r="BX9" t="s">
+      <c r="BZ9" t="s">
         <v>238</v>
       </c>
-      <c r="BY9" t="s">
+      <c r="CA9" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA9" t="s">
-        <v>241</v>
       </c>
       <c r="CB9" t="s">
         <v>158</v>
@@ -9549,7 +9543,7 @@
         <v>137</v>
       </c>
       <c r="CM9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CN9">
         <v>425.45</v>
@@ -9561,7 +9555,7 @@
         <v>422.15</v>
       </c>
       <c r="CQ9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="CR9" t="s">
         <v>137</v>
@@ -9572,22 +9566,22 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F10" t="s">
         <v>133</v>
       </c>
       <c r="G10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H10" t="s">
         <v>177</v>
@@ -9752,7 +9746,7 @@
         <v>4</v>
       </c>
       <c r="BJ10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK10" t="s">
         <v>137</v>
@@ -9788,22 +9782,22 @@
         <v>151</v>
       </c>
       <c r="BV10" t="s">
+        <v>242</v>
+      </c>
+      <c r="BW10" t="s">
+        <v>243</v>
+      </c>
+      <c r="BX10" t="s">
         <v>244</v>
       </c>
-      <c r="BW10" t="s">
-        <v>245</v>
-      </c>
-      <c r="BX10" t="s">
-        <v>246</v>
-      </c>
       <c r="BY10" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ10" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA10" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ10" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA10" t="s">
-        <v>241</v>
       </c>
       <c r="CB10" t="s">
         <v>158</v>
@@ -9851,7 +9845,7 @@
         <v>6202.5</v>
       </c>
       <c r="CQ10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="CR10" t="s">
         <v>137</v>
@@ -9862,22 +9856,22 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F11" t="s">
         <v>133</v>
       </c>
       <c r="G11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H11" t="s">
         <v>177</v>
@@ -10042,7 +10036,7 @@
         <v>3</v>
       </c>
       <c r="BJ11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK11" t="s">
         <v>137</v>
@@ -10078,22 +10072,22 @@
         <v>151</v>
       </c>
       <c r="BV11" t="s">
+        <v>248</v>
+      </c>
+      <c r="BW11" t="s">
+        <v>249</v>
+      </c>
+      <c r="BX11" t="s">
         <v>250</v>
       </c>
-      <c r="BW11" t="s">
-        <v>251</v>
-      </c>
-      <c r="BX11" t="s">
-        <v>252</v>
-      </c>
       <c r="BY11" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ11" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA11" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ11" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA11" t="s">
-        <v>241</v>
       </c>
       <c r="CB11" t="s">
         <v>158</v>
@@ -10129,7 +10123,7 @@
         <v>137</v>
       </c>
       <c r="CM11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CN11">
         <v>1957</v>
@@ -10141,7 +10135,7 @@
         <v>1957</v>
       </c>
       <c r="CQ11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="CR11" t="s">
         <v>137</v>
@@ -10152,22 +10146,22 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F12" t="s">
         <v>133</v>
       </c>
       <c r="G12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H12" t="s">
         <v>177</v>
@@ -10332,7 +10326,7 @@
         <v>4</v>
       </c>
       <c r="BJ12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK12" t="s">
         <v>137</v>
@@ -10368,22 +10362,22 @@
         <v>151</v>
       </c>
       <c r="BV12" t="s">
+        <v>253</v>
+      </c>
+      <c r="BW12" t="s">
+        <v>254</v>
+      </c>
+      <c r="BX12" t="s">
         <v>255</v>
       </c>
-      <c r="BW12" t="s">
-        <v>256</v>
-      </c>
-      <c r="BX12" t="s">
-        <v>257</v>
-      </c>
       <c r="BY12" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ12" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA12" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ12" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA12" t="s">
-        <v>241</v>
       </c>
       <c r="CB12" t="s">
         <v>158</v>
@@ -10431,7 +10425,7 @@
         <v>1303.2</v>
       </c>
       <c r="CQ12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="CR12" t="s">
         <v>137</v>
@@ -10442,22 +10436,22 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F13" t="s">
         <v>133</v>
       </c>
       <c r="G13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H13" t="s">
         <v>177</v>
@@ -10622,7 +10616,7 @@
         <v>3</v>
       </c>
       <c r="BJ13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK13" t="s">
         <v>137</v>
@@ -10658,22 +10652,22 @@
         <v>151</v>
       </c>
       <c r="BV13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="BW13" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="BX13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="BY13" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ13" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA13" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ13" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA13" t="s">
-        <v>241</v>
       </c>
       <c r="CB13" t="s">
         <v>158</v>
@@ -10721,7 +10715,7 @@
         <v>721.4</v>
       </c>
       <c r="CQ13" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="CR13" t="s">
         <v>137</v>
@@ -10732,22 +10726,22 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F14" t="s">
         <v>133</v>
       </c>
       <c r="G14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H14" t="s">
         <v>177</v>
@@ -10912,7 +10906,7 @@
         <v>3</v>
       </c>
       <c r="BJ14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK14" t="s">
         <v>137</v>
@@ -10948,22 +10942,22 @@
         <v>151</v>
       </c>
       <c r="BV14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="BW14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="BX14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="BY14" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ14" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA14" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ14" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA14" t="s">
-        <v>241</v>
       </c>
       <c r="CB14" t="s">
         <v>158</v>
@@ -10999,7 +10993,7 @@
         <v>137</v>
       </c>
       <c r="CM14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CN14">
         <v>2903.2</v>
@@ -11011,7 +11005,7 @@
         <v>2903.2</v>
       </c>
       <c r="CQ14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="CR14" t="s">
         <v>137</v>
@@ -11022,22 +11016,22 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F15" t="s">
         <v>133</v>
       </c>
       <c r="G15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H15" t="s">
         <v>177</v>
@@ -11202,7 +11196,7 @@
         <v>4</v>
       </c>
       <c r="BJ15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK15" t="s">
         <v>137</v>
@@ -11238,22 +11232,22 @@
         <v>151</v>
       </c>
       <c r="BV15" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="BW15" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="BX15" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="BY15" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ15" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA15" t="s">
         <v>239</v>
-      </c>
-      <c r="BZ15" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA15" t="s">
-        <v>241</v>
       </c>
       <c r="CB15" t="s">
         <v>158</v>
@@ -11289,7 +11283,7 @@
         <v>137</v>
       </c>
       <c r="CM15" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="CN15">
         <v>1321</v>
@@ -11301,7 +11295,7 @@
         <v>1321</v>
       </c>
       <c r="CQ15" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="CR15" t="s">
         <v>137</v>
@@ -11315,16 +11309,16 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F16" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G16" t="s">
         <v>177</v>
@@ -11345,7 +11339,7 @@
         <v>137</v>
       </c>
       <c r="M16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N16" t="s">
         <v>137</v>
@@ -11399,7 +11393,7 @@
         <v>137</v>
       </c>
       <c r="AE16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AF16" t="s">
         <v>137</v>
@@ -11480,7 +11474,7 @@
         <v>137</v>
       </c>
       <c r="BF16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="BG16" t="s">
         <v>142</v>
@@ -11492,7 +11486,7 @@
         <v>4</v>
       </c>
       <c r="BJ16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="BK16" t="s">
         <v>137</v>
@@ -11519,31 +11513,31 @@
         <v>148</v>
       </c>
       <c r="BS16" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="BT16" t="s">
         <v>150</v>
       </c>
       <c r="BU16" t="s">
+        <v>276</v>
+      </c>
+      <c r="BV16" t="s">
+        <v>277</v>
+      </c>
+      <c r="BW16" t="s">
         <v>278</v>
       </c>
-      <c r="BV16" t="s">
+      <c r="BX16" t="s">
         <v>279</v>
       </c>
-      <c r="BW16" t="s">
+      <c r="BY16" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ16" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA16" t="s">
         <v>280</v>
-      </c>
-      <c r="BX16" t="s">
-        <v>281</v>
-      </c>
-      <c r="BY16" t="s">
-        <v>239</v>
-      </c>
-      <c r="BZ16" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA16" t="s">
-        <v>282</v>
       </c>
       <c r="CB16" t="s">
         <v>158</v>
@@ -11591,7 +11585,7 @@
         <v>4305.8</v>
       </c>
       <c r="CQ16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="CR16" t="s">
         <v>137</v>
@@ -11605,16 +11599,16 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E17" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G17" t="s">
         <v>177</v>
@@ -11635,7 +11629,7 @@
         <v>137</v>
       </c>
       <c r="M17" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N17" t="s">
         <v>137</v>
@@ -11689,7 +11683,7 @@
         <v>137</v>
       </c>
       <c r="AE17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AF17" t="s">
         <v>137</v>
@@ -11782,7 +11776,7 @@
         <v>4</v>
       </c>
       <c r="BJ17" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="BK17" t="s">
         <v>137</v>
@@ -11809,31 +11803,31 @@
         <v>148</v>
       </c>
       <c r="BS17" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="BT17" t="s">
         <v>150</v>
       </c>
       <c r="BU17" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="BV17" t="s">
+        <v>284</v>
+      </c>
+      <c r="BW17" t="s">
+        <v>285</v>
+      </c>
+      <c r="BX17" t="s">
         <v>286</v>
       </c>
-      <c r="BW17" t="s">
-        <v>287</v>
-      </c>
-      <c r="BX17" t="s">
-        <v>288</v>
-      </c>
       <c r="BY17" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="BZ17" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="CA17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="CB17" t="s">
         <v>158</v>
@@ -11857,7 +11851,7 @@
         <v>0</v>
       </c>
       <c r="CI17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="CJ17">
         <v>1.19</v>
@@ -11881,7 +11875,7 @@
         <v>1012.9</v>
       </c>
       <c r="CQ17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="CR17" t="s">
         <v>137</v>
@@ -11895,16 +11889,16 @@
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F18" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G18" t="s">
         <v>177</v>
@@ -11925,7 +11919,7 @@
         <v>137</v>
       </c>
       <c r="M18" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N18" t="s">
         <v>137</v>
@@ -11979,7 +11973,7 @@
         <v>137</v>
       </c>
       <c r="AE18" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AF18" t="s">
         <v>137</v>
@@ -12063,7 +12057,7 @@
         <v>141</v>
       </c>
       <c r="BG18" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="BH18">
         <v>12</v>
@@ -12072,7 +12066,7 @@
         <v>2</v>
       </c>
       <c r="BJ18" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BK18" t="s">
         <v>137</v>
@@ -12105,25 +12099,25 @@
         <v>150</v>
       </c>
       <c r="BU18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="BV18" t="s">
+        <v>290</v>
+      </c>
+      <c r="BW18" t="s">
+        <v>291</v>
+      </c>
+      <c r="BX18" t="s">
         <v>292</v>
       </c>
-      <c r="BW18" t="s">
-        <v>293</v>
-      </c>
-      <c r="BX18" t="s">
-        <v>294</v>
-      </c>
       <c r="BY18" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="BZ18" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="CA18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="CB18" t="s">
         <v>158</v>
@@ -12171,7 +12165,7 @@
         <v>688.05</v>
       </c>
       <c r="CQ18" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="CR18" t="s">
         <v>137</v>
@@ -12212,57 +12206,57 @@
         <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>91</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
@@ -12307,15 +12301,15 @@
         <v>794.42</v>
       </c>
       <c r="Q2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
@@ -12360,18 +12354,18 @@
         <v>628.33</v>
       </c>
       <c r="Q3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D4" t="s">
         <v>177</v>
@@ -12413,7 +12407,7 @@
         <v>790</v>
       </c>
       <c r="Q4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -12445,78 +12439,78 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B2" t="s">
         <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E2" t="s">
         <v>134</v>
       </c>
       <c r="G2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I2" t="s">
         <v>142</v>
@@ -12543,18 +12537,18 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B3" t="s">
         <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -12563,10 +12557,10 @@
         <v>134</v>
       </c>
       <c r="G3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I3" t="s">
         <v>142</v>
@@ -12593,30 +12587,30 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B4" t="s">
         <v>134</v>
       </c>
       <c r="C4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E4" t="s">
         <v>134</v>
       </c>
       <c r="G4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I4" t="s">
         <v>142</v>
@@ -12643,18 +12637,18 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B5" t="s">
         <v>134</v>
       </c>
       <c r="C5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -12663,10 +12657,10 @@
         <v>134</v>
       </c>
       <c r="G5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I5" t="s">
         <v>142</v>
@@ -12693,12 +12687,12 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B6" t="s">
         <v>134</v>
@@ -12716,10 +12710,10 @@
         <v>622.5499877929688</v>
       </c>
       <c r="G6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I6" t="s">
         <v>142</v>
@@ -12746,18 +12740,18 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B7" t="s">
         <v>134</v>
       </c>
       <c r="C7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -12769,10 +12763,10 @@
         <v>863.5</v>
       </c>
       <c r="G7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I7" t="s">
         <v>142</v>
@@ -12799,18 +12793,18 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B8" t="s">
         <v>177</v>
       </c>
       <c r="C8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -12822,10 +12816,10 @@
         <v>637.9000244140625</v>
       </c>
       <c r="G8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I8" t="s">
         <v>142</v>
@@ -12852,21 +12846,21 @@
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B9" t="s">
         <v>177</v>
       </c>
       <c r="C9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D9" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E9" t="s">
         <v>177</v>
@@ -12875,10 +12869,10 @@
         <v>814.9000244140625</v>
       </c>
       <c r="G9" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I9" t="s">
         <v>142</v>
@@ -12905,7 +12899,7 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -12929,30 +12923,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -12964,7 +12958,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T05:14:01.566Z</t>
+    <t>2026-07-14T05:16:16.764Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1013,7 +1013,7 @@
     <t>ROTATION_DEFERRED</t>
   </si>
   <si>
-    <t>2026-07-14T05:14:01.226Z</t>
+    <t>2026-07-14T05:16:16.143Z</t>
   </si>
   <si>
     <t>Date</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T05:16:16.764Z</t>
+    <t>2026-07-14T06:12:57.802Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1013,7 +1013,7 @@
     <t>ROTATION_DEFERRED</t>
   </si>
   <si>
-    <t>2026-07-14T05:16:16.143Z</t>
+    <t>2026-07-14T06:12:57.508Z</t>
   </si>
   <si>
     <t>Date</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T06:12:57.802Z</t>
+    <t>2026-07-14T06:23:45.198Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1013,7 +1013,7 @@
     <t>ROTATION_DEFERRED</t>
   </si>
   <si>
-    <t>2026-07-14T06:12:57.508Z</t>
+    <t>2026-07-14T06:23:44.900Z</t>
   </si>
   <si>
     <t>Date</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T06:23:45.198Z</t>
+    <t>2026-07-14T06:50:12.738Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1013,7 +1013,7 @@
     <t>ROTATION_DEFERRED</t>
   </si>
   <si>
-    <t>2026-07-14T06:23:44.900Z</t>
+    <t>2026-07-14T06:50:12.433Z</t>
   </si>
   <si>
     <t>Date</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T06:50:12.738Z</t>
+    <t>2026-07-14T08:05:40.115Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1013,7 +1013,7 @@
     <t>ROTATION_DEFERRED</t>
   </si>
   <si>
-    <t>2026-07-14T06:50:12.433Z</t>
+    <t>2026-07-14T08:05:39.733Z</t>
   </si>
   <si>
     <t>Date</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2679" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="354">
   <si>
     <t>Metric</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T08:05:40.115Z</t>
+    <t>2026-07-14T09:43:28.746Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -545,13 +545,298 @@
     <t>Weekly RSI 69.24 is above 50. Daily RSI 78.99 is above 50. Weekly RS 20.1% is above 0. Daily long RS55 17.3% is above 0. Daily short RS21 11.1% is above 0. Daily close 622.55 is above Supertrend(10, 3) 521.71. Entry style: Breakout buy. Price action strength: close crossed 55-day high 574.90. 52-week breakout: close crossed prior 52-week high 576.95. 20-day base breakout above 574.90 with a higher-low structure. Volume shocker: latest volume is 90.28x the 50-day average. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: close is above the middle band 547.68 with bandwidth 14.29%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 3.77% of price. Liquidity strength: 20-day average turnover is Rs 132125809.42. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 0/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Operator accumulation confirmed: price 11.42%, traded quantity 69.12x, delivery 12.84x, close above average price 620.33. Institutional confluence score 3/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 20/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 195.78; planned allocation Rs 72838.35, quantity 117, initial stop 572.75, planned risk Rs 5826.6. Closing signal dated 2026-07-13; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
   </si>
   <si>
+    <t>All NSE Market, Default Nifty 500, My Custom List</t>
+  </si>
+  <si>
+    <t>NIVABUPA</t>
+  </si>
+  <si>
+    <t>Momentum continuation buy</t>
+  </si>
+  <si>
+    <t>daily DBR 84.13-85.12; tests 2; 4/7</t>
+  </si>
+  <si>
+    <t>weekly DBR 76.36-84.4; tests 2; 3/7</t>
+  </si>
+  <si>
+    <t>17/30</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; MACD and OBV confirmation; Operator delivery confirmation; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>Price-action base and higher-low structure; Retracement/pullback buy setup; GTF demand/supply confluence; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Bollinger trend/range context; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
+  </si>
+  <si>
+    <t>Index option-chain positioning; News/event context</t>
+  </si>
+  <si>
+    <t>70.29% (123/175)</t>
+  </si>
+  <si>
+    <t>55D high retest</t>
+  </si>
+  <si>
+    <t>No bullish confirmation pattern</t>
+  </si>
+  <si>
+    <t>Weekly RSI 61.25 is above 50. Daily RSI 63.34 is above 50. Weekly RS 13.3% is above 0. Daily long RS55 10.5% is above 0. Daily short RS21 1.6% is above 0. Daily close 88.09 is above Supertrend(10, 3) 81.07. Entry style: Momentum continuation buy. Price action strength: close is within 15% of 52-week high 92.90. Volume shocker: latest volume is 2.77x the 50-day average. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: bandwidth 4.85% indicates a range-bound/compressed phase. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Volatility is controlled: ATR(14) is 2.54% of price. Liquidity strength: 20-day average turnover is Rs 190458904.28. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly sideways. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 0/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Operator accumulation confirmed: price 1.83%, traded quantity 6.96x, delivery 8.40x, close above average price 87.40. Institutional confluence score 3/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Sector breadth strong: My List has 123/175 stocks (70.29%) passing daily strength. Institutional concept coverage: 17/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 180.45; planned allocation Rs 440.45, quantity 5, initial stop 84.5, planned risk Rs 17.95. Closing signal dated 2026-07-13; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>RAIN</t>
+  </si>
+  <si>
+    <t>Rain Industries Limited</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>GTF confirms less than 2R room</t>
+  </si>
+  <si>
+    <t>2/4</t>
+  </si>
+  <si>
+    <t>3/9 (GTF C)</t>
+  </si>
+  <si>
+    <t>14/26</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Bollinger trend/range context; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Volume participation; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>28.25% (495/1752)</t>
+  </si>
+  <si>
+    <t>Weekly RSI 71.58 is above 50. Daily RSI 64.68 is above 50. Weekly RS 35.7% is above 0. Daily long RS55 56.1% is above 0. Daily short RS21 0.7% is above 0. Daily close 207.05 is above Supertrend(10, 3) 178.77. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 214.17. Retracement watch: pullback depth 3.32% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: close is above the middle band 192.70 with bandwidth 16.23%. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Volatility is controlled: ATR(14) is 4.35% of price. Liquidity strength: 20-day average turnover is Rs 991729867.12. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next actual market session using the 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 14/26 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 179.24; planned allocation Rs 99798.1, quantity 482, initial stop 196.45, planned risk Rs 5109.2. Closing signal dated 2026-07-10; buy fill must come from the next actual market session exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>INGERRAND</t>
+  </si>
+  <si>
+    <t>Ingersoll Rand (India) Limited</t>
+  </si>
+  <si>
+    <t>Retracement buy near 50-DMA</t>
+  </si>
+  <si>
+    <t>15/26</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
+  </si>
+  <si>
+    <t>Weekly RSI 57.94 is above 50. Daily RSI 53.75 is above 50. Weekly RS 19.4% is above 0. Daily long RS55 2.1% is above 0. Daily short RS21 5.4% is above 0. Daily close 4452.00 is above Supertrend(10, 3) 4220.30. Entry style: Retracement buy near 50-DMA. Price action strength: close is within 15% of 52-week high 4756.20. Retracement buy: price pulled back 6.40% from the 55-day high and reclaimed near 50-DMA 4334.98; support distance is 2.63%. Retracement confirmation: pullback volume ratio 0.47 and reclaim volume ratio 0.65 with candle close location 61.83%. Bollinger context: close is below the middle band 4487.32 with bandwidth 10.02%. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 5.20% above daily Supertrend. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 2.90% of price. Liquidity strength: 20-day average turnover is Rs 79382544.10. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next actual market session using the 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 15/26 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 167.02; planned allocation Rs 97944, quantity 22, initial stop 4319.5, planned risk Rs 2915. Closing signal dated 2026-07-10; buy fill must come from the next actual market session exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>CRAFTSMAN</t>
+  </si>
+  <si>
+    <t>Craftsman Automation Limited</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>0/9 (GTF neutral)</t>
+  </si>
+  <si>
+    <t>daily RBR 8613.5-8978; tests 4; 3/7</t>
+  </si>
+  <si>
+    <t>weekly DBR 8242.5-9074; tests 2; 4/7</t>
+  </si>
+  <si>
+    <t>daily RBD 9528-9402.5; fresh; 7/7</t>
+  </si>
+  <si>
+    <t>14/29</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Price-action base and higher-low structure; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; MACD and OBV confirmation; Operator delivery confirmation; Sector breadth; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>42.11% (16/38)</t>
+  </si>
+  <si>
+    <t>Weekly RSI 62.77 is above 50. Daily RSI 55.38 is above 50. Weekly RS 20.2% is above 0. Daily long RS55 17.2% is above 0. Daily short RS21 0.2% is above 0. Daily close 9301.00 is above Supertrend(10, 3) 8728.10. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 9938.00. Momentum confirmation: MACD is not fully confirmed; OBV is rising. Retracement watch: pullback depth 6.41% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: bandwidth 7.09% indicates a range-bound/compressed phase. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.16% above daily Supertrend. Volatility is controlled: ATR(14) is 2.80% of price. Liquidity strength: 20-day average turnover is Rs 787112608.80. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. Opposing daily supply 9402.5-9528; blocker/early-risk flag. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Operator/delivery context: Delivery neutral: traded quantity 0.33x, delivery 0.27x, delivery percentage 49.09%. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 14/29 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 131.92; planned allocation Rs 93010, quantity 10, initial stop 8955.5, planned risk Rs 3455. Closing signal dated 2026-07-10; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>GRINDWELL</t>
+  </si>
+  <si>
+    <t>Grindwell Norton Limited</t>
+  </si>
+  <si>
+    <t>daily RSI below 50 setup grade WATCH GTF confirms less than 2R room</t>
+  </si>
+  <si>
+    <t>4/9 (GTF C)</t>
+  </si>
+  <si>
+    <t>daily DBR 1886.4-1932.3; fresh; 7/7</t>
+  </si>
+  <si>
+    <t>daily DBD 2244-2146.8; fresh; 7/7</t>
+  </si>
+  <si>
+    <t>0.49R</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 63.02 is above 50. Daily RSI 52.01 is above 50. Weekly RS 25.7% is above 0. Daily long RS55 22.2% is above 0. Daily short RS21 2.9% is above 0. Daily close 2058.60 is above Supertrend(10, 3) 2015.38. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 2294.40. Retracement watch: pullback depth 10.28% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: close is below the middle band 2106.53 with bandwidth 12.00%. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 2.10% above daily Supertrend. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 3.57% of price. Liquidity strength: 20-day average turnover is Rs 210232154.56. Market regime supports longs: NIFTY 500 bullish/healthy. Daily demand DBR 1886.4-1932.3: fresh, score 7/7, achievement 7.89R, significant_gap. GTF 50-SMA slope: daily up, weekly up. Opposing daily supply 2146.8-2244; estimated room 0.49R. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next actual market session using the 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 15/26 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 170.76; planned allocation Rs 98812.8, quantity 48, initial stop 2015.38, planned risk Rs 2074.56. Closing signal dated 2026-07-10; buy fill must come from the next actual market session exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>Best only (A+/A)</t>
+  </si>
+  <si>
+    <t>All NSE Market, My Custom List</t>
+  </si>
+  <si>
+    <t>SIS</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>daily RS21 below zero setup grade WATCH GTF confirms less than 2R room</t>
+  </si>
+  <si>
+    <t>2026-07-14T03:32:23.269Z: SANGAMIND; Optional rotation cancelled before selling SIS: Rotation requires 2 distinct valid ENTRY closes; candidate has 0.</t>
+  </si>
+  <si>
+    <t>14/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Index option-chain positioning</t>
+  </si>
+  <si>
+    <t>Intraday tick scalping; Broker-only live Greeks/order-book depth</t>
+  </si>
+  <si>
+    <t>64.29% (90/140)</t>
+  </si>
+  <si>
+    <t>Weekly RSI 72.14 is above 50. Daily RSI 61.56 is above 50. Weekly RS 25.5% is above 0. Daily long RS55 29.2% is above 0. Daily short RS21 1.5% is above 0. Daily close 437.80 is above Supertrend(10, 3) 397.84. Price action strength: close is within 15% of 52-week high 480.95. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Volatility is controlled: ATR(14) is 3.42% of price. Liquidity strength: 20-day average turnover is Rs 261311772.23. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 14/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>PGHL</t>
+  </si>
+  <si>
+    <t>17/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 73.92 is above 50. Daily RSI 70.18 is above 50. Weekly RS 23.0% is above 0. Daily long RS55 28.3% is above 0. Daily short RS21 2.2% is above 0. Daily close 6612.00 is above Supertrend(10, 3) 6036.47. Price action strength: close is within 15% of 52-week high 6739.00. Volume shocker: latest volume is 2.02x the 50-day average. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.56% of price. Liquidity strength: 20-day average turnover is Rs 92394456.38. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 17/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>16/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 62.41 is above 50. Daily RSI 59.04 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 9.6% is above 0. Daily short RS21 0.7% is above 0. Daily close 1993.20 is above Supertrend(10, 3) 1864.19. Price action strength: close is within 15% of 52-week high 2093.30. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.47% above daily Supertrend. Volatility is controlled: ATR(14) is 2.56% of price. Liquidity strength: 20-day average turnover is Rs 580096417.25. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 16/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>VIJAYA</t>
+  </si>
+  <si>
+    <t>15/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 66.67 is above 50. Daily RSI 57.60 is above 50. Weekly RS 42.2% is above 0. Daily long RS55 32.3% is above 0. Daily short RS21 4.5% is above 0. Daily close 1377.80 is above Supertrend(10, 3) 1215.62. Price action strength: close is within 15% of 52-week high 1427.80. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.06% of price. Liquidity strength: 20-day average turnover is Rs 464701789.72. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>PRECOT</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Volatility and liquidity control; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 64.67 is above 50. Daily RSI 61.84 is above 50. Weekly RS 54.7% is above 0. Daily long RS55 46.8% is above 0. Daily short RS21 15.0% is above 0. Daily close 800.45 is above Supertrend(10, 3) 673.89. Price action strength: close is within 15% of 52-week high 861.25. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.91% of price. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 14/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>PRUDENT</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 63.57 is above 50. Daily RSI 53.42 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 4.7% is above 0. Daily close 2960.00 is above Supertrend(10, 3) 2759.71. Price action strength: close is within 15% of 52-week high 3160.10. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.77% above daily Supertrend. Volatility is controlled: ATR(14) is 3.14% of price. Liquidity strength: 20-day average turnover is Rs 67973469.69. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>KPIL</t>
+  </si>
+  <si>
+    <t>daily RS21 below zero daily RSI below 50 setup grade WATCH</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>bullish engulfing</t>
+  </si>
+  <si>
+    <t>Weekly RSI 66.89 is above 50. Daily RSI 50.91 is above 50. Weekly RS 27.5% is above 0. Daily long RS55 5.5% is above 0. Daily short RS21 2.1% is above 0. Daily close 1349.90 is above Supertrend(10, 3) 1313.78. Price action strength: close is within 15% of 52-week high 1479.60. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 2.68% above daily Supertrend. Price confirmation: bullish engulfing is present. Volatility is controlled: ATR(14) is 3.04% of price. Liquidity strength: 20-day average turnover is Rs 511253745.19. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 16/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
     <t>My Custom List</t>
   </si>
   <si>
     <t>NEXUSSURGL</t>
   </si>
   <si>
-    <t>2026-07-10</t>
+    <t>PENDING_PARTIAL_EXIT</t>
   </si>
   <si>
     <t>09:21 IST</t>
@@ -563,6 +848,12 @@
     <t>09:17 order / 09:21 actual fill</t>
   </si>
   <si>
+    <t>PARTIAL_EXIT</t>
+  </si>
+  <si>
+    <t>Early deterioration: daily RS21 below zero; daily RS55 below zero; daily RSI below 50; close below 50-DMA; setup grade WATCH. Fundamental score materially deteriorated from the entry snapshot.</t>
+  </si>
+  <si>
     <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Bollinger trend/range context; MACD and OBV confirmation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
@@ -572,264 +863,12 @@
     <t>Operator delivery confirmation; Index option-chain positioning; News/event context</t>
   </si>
   <si>
-    <t>70.29% (123/175)</t>
-  </si>
-  <si>
     <t>hammer</t>
   </si>
   <si>
     <t>Weekly RSI 58.57 is above 50. Daily RSI 52.69 is above 50. Weekly RS 21.8% is above 0. Daily long RS55 4.6% is above 0. Daily short RS21 1.3% is above 0. Daily close 20.87 is above Supertrend(10, 3) 18.63. Entry style: Trend continuation buy. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: close is above the middle band 20.41 with bandwidth 14.62%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: hammer is present. Volatility is controlled: ATR(14) is 5.69% of price. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 0/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Official NSE delivery history loaded for 2395 EQ symbols across 6 sessions. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Sector breadth strong: My List has 123/175 stocks (70.29%) passing daily strength. Institutional concept coverage: 16/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 168.93; planned allocation Rs 83.48, quantity 4, initial stop 20, planned risk Rs 3.48. Closing signal dated 2026-07-10; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
   </si>
   <si>
-    <t>RAIN</t>
-  </si>
-  <si>
-    <t>Rain Industries Limited</t>
-  </si>
-  <si>
-    <t>GTF confirms less than 2R room</t>
-  </si>
-  <si>
-    <t>2/4</t>
-  </si>
-  <si>
-    <t>3/9 (GTF C)</t>
-  </si>
-  <si>
-    <t>14/26</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Bollinger trend/range context; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Volume participation; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>28.25% (495/1752)</t>
-  </si>
-  <si>
-    <t>No bullish confirmation pattern</t>
-  </si>
-  <si>
-    <t>Weekly RSI 71.58 is above 50. Daily RSI 64.68 is above 50. Weekly RS 35.7% is above 0. Daily long RS55 56.1% is above 0. Daily short RS21 0.7% is above 0. Daily close 207.05 is above Supertrend(10, 3) 178.77. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 214.17. Retracement watch: pullback depth 3.32% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: close is above the middle band 192.70 with bandwidth 16.23%. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Volatility is controlled: ATR(14) is 4.35% of price. Liquidity strength: 20-day average turnover is Rs 991729867.12. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next actual market session using the 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 14/26 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 179.24; planned allocation Rs 99798.1, quantity 482, initial stop 196.45, planned risk Rs 5109.2. Closing signal dated 2026-07-10; buy fill must come from the next actual market session exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>INGERRAND</t>
-  </si>
-  <si>
-    <t>Ingersoll Rand (India) Limited</t>
-  </si>
-  <si>
-    <t>Retracement buy near 50-DMA</t>
-  </si>
-  <si>
-    <t>15/26</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
-  </si>
-  <si>
-    <t>Weekly RSI 57.94 is above 50. Daily RSI 53.75 is above 50. Weekly RS 19.4% is above 0. Daily long RS55 2.1% is above 0. Daily short RS21 5.4% is above 0. Daily close 4452.00 is above Supertrend(10, 3) 4220.30. Entry style: Retracement buy near 50-DMA. Price action strength: close is within 15% of 52-week high 4756.20. Retracement buy: price pulled back 6.40% from the 55-day high and reclaimed near 50-DMA 4334.98; support distance is 2.63%. Retracement confirmation: pullback volume ratio 0.47 and reclaim volume ratio 0.65 with candle close location 61.83%. Bollinger context: close is below the middle band 4487.32 with bandwidth 10.02%. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 5.20% above daily Supertrend. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 2.90% of price. Liquidity strength: 20-day average turnover is Rs 79382544.10. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next actual market session using the 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 15/26 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 167.02; planned allocation Rs 97944, quantity 22, initial stop 4319.5, planned risk Rs 2915. Closing signal dated 2026-07-10; buy fill must come from the next actual market session exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>CRAFTSMAN</t>
-  </si>
-  <si>
-    <t>Craftsman Automation Limited</t>
-  </si>
-  <si>
-    <t>GTF opposing supply confirmation GTF confirms less than 2R room</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>0/9 (GTF neutral)</t>
-  </si>
-  <si>
-    <t>daily RBR 8613.5-8978; tests 4; 3/7</t>
-  </si>
-  <si>
-    <t>weekly DBR 8242.5-9074; tests 2; 4/7</t>
-  </si>
-  <si>
-    <t>daily RBD 9528-9402.5; fresh; 7/7</t>
-  </si>
-  <si>
-    <t>14/29</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Price-action base and higher-low structure; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; MACD and OBV confirmation; Operator delivery confirmation; Sector breadth; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Index option-chain positioning; News/event context</t>
-  </si>
-  <si>
-    <t>42.11% (16/38)</t>
-  </si>
-  <si>
-    <t>Weekly RSI 62.77 is above 50. Daily RSI 55.38 is above 50. Weekly RS 20.2% is above 0. Daily long RS55 17.2% is above 0. Daily short RS21 0.2% is above 0. Daily close 9301.00 is above Supertrend(10, 3) 8728.10. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 9938.00. Momentum confirmation: MACD is not fully confirmed; OBV is rising. Retracement watch: pullback depth 6.41% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: bandwidth 7.09% indicates a range-bound/compressed phase. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.16% above daily Supertrend. Volatility is controlled: ATR(14) is 2.80% of price. Liquidity strength: 20-day average turnover is Rs 787112608.80. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. Opposing daily supply 9402.5-9528; blocker/early-risk flag. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Operator/delivery context: Delivery neutral: traded quantity 0.33x, delivery 0.27x, delivery percentage 49.09%. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 14/29 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 131.92; planned allocation Rs 93010, quantity 10, initial stop 8955.5, planned risk Rs 3455. Closing signal dated 2026-07-10; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>GRINDWELL</t>
-  </si>
-  <si>
-    <t>Grindwell Norton Limited</t>
-  </si>
-  <si>
-    <t>4/9 (GTF C)</t>
-  </si>
-  <si>
-    <t>daily DBR 1886.4-1932.3; fresh; 7/7</t>
-  </si>
-  <si>
-    <t>daily DBD 2244-2146.8; fresh; 7/7</t>
-  </si>
-  <si>
-    <t>0.49R</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 63.02 is above 50. Daily RSI 52.01 is above 50. Weekly RS 25.7% is above 0. Daily long RS55 22.2% is above 0. Daily short RS21 2.9% is above 0. Daily close 2058.60 is above Supertrend(10, 3) 2015.38. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 2294.40. Retracement watch: pullback depth 10.28% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: close is below the middle band 2106.53 with bandwidth 12.00%. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 2.10% above daily Supertrend. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 3.57% of price. Liquidity strength: 20-day average turnover is Rs 210232154.56. Market regime supports longs: NIFTY 500 bullish/healthy. Daily demand DBR 1886.4-1932.3: fresh, score 7/7, achievement 7.89R, significant_gap. GTF 50-SMA slope: daily up, weekly up. Opposing daily supply 2146.8-2244; estimated room 0.49R. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next actual market session using the 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 15/26 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 170.76; planned allocation Rs 98812.8, quantity 48, initial stop 2015.38, planned risk Rs 2074.56. Closing signal dated 2026-07-10; buy fill must come from the next actual market session exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>Best only (A+/A)</t>
-  </si>
-  <si>
-    <t>All NSE Market, My Custom List</t>
-  </si>
-  <si>
-    <t>SIS</t>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>daily RS21 below zero setup grade WATCH GTF confirms less than 2R room</t>
-  </si>
-  <si>
-    <t>2026-07-14T03:32:23.269Z: SANGAMIND; Optional rotation cancelled before selling SIS: Rotation requires 2 distinct valid ENTRY closes; candidate has 0.</t>
-  </si>
-  <si>
-    <t>14/21</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Index option-chain positioning</t>
-  </si>
-  <si>
-    <t>Intraday tick scalping; Broker-only live Greeks/order-book depth</t>
-  </si>
-  <si>
-    <t>64.29% (90/140)</t>
-  </si>
-  <si>
-    <t>Weekly RSI 72.14 is above 50. Daily RSI 61.56 is above 50. Weekly RS 25.5% is above 0. Daily long RS55 29.2% is above 0. Daily short RS21 1.5% is above 0. Daily close 437.80 is above Supertrend(10, 3) 397.84. Price action strength: close is within 15% of 52-week high 480.95. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Volatility is controlled: ATR(14) is 3.42% of price. Liquidity strength: 20-day average turnover is Rs 261311772.23. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 14/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>PGHL</t>
-  </si>
-  <si>
-    <t>17/21</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 73.92 is above 50. Daily RSI 70.18 is above 50. Weekly RS 23.0% is above 0. Daily long RS55 28.3% is above 0. Daily short RS21 2.2% is above 0. Daily close 6612.00 is above Supertrend(10, 3) 6036.47. Price action strength: close is within 15% of 52-week high 6739.00. Volume shocker: latest volume is 2.02x the 50-day average. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.56% of price. Liquidity strength: 20-day average turnover is Rs 92394456.38. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 17/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>All NSE Market, Default Nifty 500, My Custom List</t>
-  </si>
-  <si>
-    <t>NH</t>
-  </si>
-  <si>
-    <t>16/21</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 62.41 is above 50. Daily RSI 59.04 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 9.6% is above 0. Daily short RS21 0.7% is above 0. Daily close 1993.20 is above Supertrend(10, 3) 1864.19. Price action strength: close is within 15% of 52-week high 2093.30. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.47% above daily Supertrend. Volatility is controlled: ATR(14) is 2.56% of price. Liquidity strength: 20-day average turnover is Rs 580096417.25. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 16/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>VIJAYA</t>
-  </si>
-  <si>
-    <t>15/21</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Volume participation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 66.67 is above 50. Daily RSI 57.60 is above 50. Weekly RS 42.2% is above 0. Daily long RS55 32.3% is above 0. Daily short RS21 4.5% is above 0. Daily close 1377.80 is above Supertrend(10, 3) 1215.62. Price action strength: close is within 15% of 52-week high 1427.80. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.06% of price. Liquidity strength: 20-day average turnover is Rs 464701789.72. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>PRECOT</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Volume participation; Volatility and liquidity control; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 64.67 is above 50. Daily RSI 61.84 is above 50. Weekly RS 54.7% is above 0. Daily long RS55 46.8% is above 0. Daily short RS21 15.0% is above 0. Daily close 800.45 is above Supertrend(10, 3) 673.89. Price action strength: close is within 15% of 52-week high 861.25. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.91% of price. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 14/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>PRUDENT</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 63.57 is above 50. Daily RSI 53.42 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 4.7% is above 0. Daily close 2960.00 is above Supertrend(10, 3) 2759.71. Price action strength: close is within 15% of 52-week high 3160.10. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.77% above daily Supertrend. Volatility is controlled: ATR(14) is 3.14% of price. Liquidity strength: 20-day average turnover is Rs 67973469.69. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>KPIL</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>bullish engulfing</t>
-  </si>
-  <si>
-    <t>Weekly RSI 66.89 is above 50. Daily RSI 50.91 is above 50. Weekly RS 27.5% is above 0. Daily long RS55 5.5% is above 0. Daily short RS21 2.1% is above 0. Daily close 1349.90 is above Supertrend(10, 3) 1313.78. Price action strength: close is within 15% of 52-week high 1479.60. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 2.68% above daily Supertrend. Price confirmation: bullish engulfing is present. Volatility is controlled: ATR(14) is 3.04% of price. Liquidity strength: 20-day average turnover is Rs 511253745.19. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 16/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
     <t>HAL</t>
   </si>
   <si>
@@ -881,9 +920,6 @@
     <t>RS trend follow-through; Retracement/pullback buy setup; Risk reference discipline</t>
   </si>
   <si>
-    <t>55D high retest</t>
-  </si>
-  <si>
     <t>Weekly RSI 64.52 is above 50. Daily RSI 67.28 is above 50. Weekly RS 46.9% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 0.0% is above 0. Daily close 1117.20 is above Supertrend(10, 3) 1007.42. Entry style: Breakout buy. Price action strength: close crossed 55-day high 1103.90. Volume shocker: latest volume is 1.56x the 50-day average. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.97% of price. Liquidity strength: 20-day average turnover is Rs 1219054718.79. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 18/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
   </si>
   <si>
@@ -953,67 +989,70 @@
     <t>Rotation requires 2 distinct valid ENTRY closes; candidate has 1.</t>
   </si>
   <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>INDIGRID</t>
+  </si>
+  <si>
+    <t>LMW</t>
+  </si>
+  <si>
+    <t>FINEORG</t>
+  </si>
+  <si>
+    <t>Evaluated At</t>
+  </si>
+  <si>
+    <t>Closing Date</t>
+  </si>
+  <si>
+    <t>First Signal</t>
+  </si>
+  <si>
+    <t>First Signal Close</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>Disposition</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>2026-07-14T03:32:23.269Z</t>
+  </si>
+  <si>
+    <t>REMOVED</t>
+  </si>
+  <si>
+    <t>EXPIRED</t>
+  </si>
+  <si>
+    <t>Latest completed-candle status is WATCH, not ENTRY. Current setup grade WATCH no longer passes the selected trade-quality filter.</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>ROTATION_DEFERRED</t>
+  </si>
+  <si>
+    <t>2026-07-14T08:05:39.733Z</t>
+  </si>
+  <si>
     <t>SGFIN</t>
   </si>
   <si>
     <t>KIMS</t>
   </si>
   <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Evaluated At</t>
-  </si>
-  <si>
-    <t>Closing Date</t>
-  </si>
-  <si>
-    <t>First Signal</t>
-  </si>
-  <si>
-    <t>First Signal Close</t>
-  </si>
-  <si>
-    <t>Outcome</t>
-  </si>
-  <si>
-    <t>Disposition</t>
-  </si>
-  <si>
-    <t>Reason</t>
-  </si>
-  <si>
-    <t>2026-07-14T03:32:23.269Z</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>REMOVED</t>
-  </si>
-  <si>
-    <t>EXPIRED</t>
-  </si>
-  <si>
-    <t>Latest completed-candle status is WATCH, not ENTRY. Current setup grade WATCH no longer passes the selected trade-quality filter.</t>
-  </si>
-  <si>
-    <t>LMW</t>
-  </si>
-  <si>
-    <t>NIVABUPA</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>FINEORG</t>
-  </si>
-  <si>
-    <t>ROTATION_DEFERRED</t>
-  </si>
-  <si>
-    <t>2026-07-14T08:05:39.733Z</t>
+    <t>2026-07-14T09:43:28.265Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -1471,7 +1510,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>1009240.65</v>
+        <v>1010846.08</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1479,7 +1518,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>999555.25</v>
+        <v>999997.7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1495,7 +1534,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>444.75</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1503,7 +1542,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>6271.67</v>
+        <v>5829.22</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1543,7 +1582,7 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>99.96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1551,7 +1590,7 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>40720.4</v>
+        <v>41266.57</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1559,7 +1598,7 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1575,7 +1614,7 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1583,7 +1622,7 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1615,7 +1654,7 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>3413.73</v>
+        <v>5014.2</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1623,7 +1662,7 @@
         <v>25</v>
       </c>
       <c r="B23">
-        <v>0.34</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2154,7 +2193,7 @@
         <v>191.09</v>
       </c>
       <c r="AG2">
-        <v>191.09</v>
+        <v>193.59</v>
       </c>
       <c r="AH2">
         <v>805.6</v>
@@ -2444,7 +2483,7 @@
         <v>195.78</v>
       </c>
       <c r="AG3">
-        <v>195.78</v>
+        <v>198.28</v>
       </c>
       <c r="AH3">
         <v>597.22</v>
@@ -2656,49 +2695,49 @@
         <v>133</v>
       </c>
       <c r="G4" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="H4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I4" t="s">
         <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="K4">
-        <v>19.59</v>
+        <v>88.49</v>
       </c>
       <c r="L4">
-        <v>19.59</v>
+        <v>88.49</v>
       </c>
       <c r="M4" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="N4">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>313.44</v>
+        <v>442.45</v>
       </c>
       <c r="R4">
-        <v>333.92</v>
+        <v>440.45</v>
       </c>
       <c r="S4">
-        <v>20.87</v>
-      </c>
-      <c r="T4" s="2">
-        <v>20.48</v>
+        <v>88.09</v>
+      </c>
+      <c r="T4" s="3">
+        <v>-2</v>
       </c>
       <c r="U4">
-        <v>6.53</v>
+        <v>-0.45</v>
       </c>
       <c r="V4" t="s">
         <v>137</v>
@@ -2728,22 +2767,22 @@
         <v>137</v>
       </c>
       <c r="AE4" t="s">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="AF4">
-        <v>168.93</v>
+        <v>176.28</v>
       </c>
       <c r="AG4">
-        <v>168.93</v>
+        <v>176.28</v>
       </c>
       <c r="AH4">
-        <v>19.01</v>
+        <v>84.5</v>
       </c>
       <c r="AI4">
-        <v>19.01</v>
+        <v>84.5</v>
       </c>
       <c r="AJ4">
-        <v>17.98</v>
+        <v>19.95</v>
       </c>
       <c r="AK4" t="s">
         <v>137</v>
@@ -2773,7 +2812,7 @@
         <v>137</v>
       </c>
       <c r="AT4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4">
         <v>0</v>
@@ -2794,7 +2833,7 @@
         <v>137</v>
       </c>
       <c r="BA4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="BB4" t="s">
         <v>137</v>
@@ -2809,28 +2848,28 @@
         <v>140</v>
       </c>
       <c r="BF4" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="BG4" t="s">
         <v>142</v>
       </c>
       <c r="BH4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BI4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BJ4" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="BK4" t="s">
         <v>166</v>
       </c>
       <c r="BL4" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="BM4" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="BN4" t="s">
         <v>138</v>
@@ -2857,7 +2896,7 @@
         <v>167</v>
       </c>
       <c r="BV4" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="BW4" t="s">
         <v>181</v>
@@ -2875,52 +2914,52 @@
         <v>184</v>
       </c>
       <c r="CB4" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="CC4" t="s">
         <v>138</v>
       </c>
       <c r="CD4">
-        <v>0.76</v>
+        <v>2.77</v>
       </c>
       <c r="CE4">
-        <v>5.69</v>
+        <v>2.54</v>
       </c>
       <c r="CF4">
-        <v>10.75</v>
+        <v>7.97</v>
       </c>
       <c r="CG4" t="s">
         <v>138</v>
       </c>
       <c r="CH4">
-        <v>18.16</v>
+        <v>1.87</v>
       </c>
       <c r="CI4" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="CJ4">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="CK4">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="CL4">
-        <v>0.76</v>
+        <v>2.77</v>
       </c>
       <c r="CM4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="CN4">
-        <v>20</v>
+        <v>85.99</v>
       </c>
       <c r="CO4">
-        <v>20</v>
+        <v>84.5</v>
       </c>
       <c r="CP4">
-        <v>19.01</v>
+        <v>84.44</v>
       </c>
       <c r="CQ4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CR4" t="s">
         <v>137</v>
@@ -2937,16 +2976,16 @@
         <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F5" t="s">
         <v>133</v>
       </c>
       <c r="G5" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H5" t="s">
         <v>134</v>
@@ -3024,7 +3063,7 @@
         <v>179.24</v>
       </c>
       <c r="AG5">
-        <v>180.4</v>
+        <v>184.4</v>
       </c>
       <c r="AH5">
         <v>196.45</v>
@@ -3087,7 +3126,7 @@
         <v>139</v>
       </c>
       <c r="BB5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="BC5">
         <v>0</v>
@@ -3111,10 +3150,10 @@
         <v>4</v>
       </c>
       <c r="BJ5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="BL5" t="s">
         <v>137</v>
@@ -3147,13 +3186,13 @@
         <v>151</v>
       </c>
       <c r="BV5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="BW5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="BX5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="BY5" t="s">
         <v>155</v>
@@ -3162,7 +3201,7 @@
         <v>156</v>
       </c>
       <c r="CA5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="CB5" t="s">
         <v>158</v>
@@ -3198,7 +3237,7 @@
         <v>0.55</v>
       </c>
       <c r="CM5" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="CN5">
         <v>199.5</v>
@@ -3210,7 +3249,7 @@
         <v>186.53</v>
       </c>
       <c r="CQ5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="CR5" t="s">
         <v>137</v>
@@ -3227,16 +3266,16 @@
         <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F6" t="s">
         <v>133</v>
       </c>
       <c r="G6" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H6" t="s">
         <v>134</v>
@@ -3269,16 +3308,16 @@
         <v>97281.8</v>
       </c>
       <c r="R6">
-        <v>97944</v>
+        <v>97776.8</v>
       </c>
       <c r="S6">
-        <v>4452</v>
+        <v>4444.4</v>
       </c>
       <c r="T6" s="2">
-        <v>662.2</v>
+        <v>495</v>
       </c>
       <c r="U6">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
       <c r="V6" t="s">
         <v>137</v>
@@ -3314,7 +3353,7 @@
         <v>167.02</v>
       </c>
       <c r="AG6">
-        <v>166.98</v>
+        <v>133.99</v>
       </c>
       <c r="AH6">
         <v>4319.5</v>
@@ -3326,7 +3365,7 @@
         <v>2252.8</v>
       </c>
       <c r="AK6">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -3389,7 +3428,7 @@
         <v>137</v>
       </c>
       <c r="BF6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="BG6" t="s">
         <v>142</v>
@@ -3401,10 +3440,10 @@
         <v>1</v>
       </c>
       <c r="BJ6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="BL6" t="s">
         <v>137</v>
@@ -3437,13 +3476,13 @@
         <v>151</v>
       </c>
       <c r="BV6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="BW6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="BX6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BY6" t="s">
         <v>155</v>
@@ -3452,7 +3491,7 @@
         <v>156</v>
       </c>
       <c r="CA6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="CB6" t="s">
         <v>158</v>
@@ -3500,7 +3539,7 @@
         <v>4319.5</v>
       </c>
       <c r="CQ6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="CR6" t="s">
         <v>137</v>
@@ -3517,16 +3556,16 @@
         <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F7" t="s">
         <v>133</v>
       </c>
       <c r="G7" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H7" t="s">
         <v>134</v>
@@ -3559,16 +3598,16 @@
         <v>92840</v>
       </c>
       <c r="R7">
-        <v>93010</v>
+        <v>93330</v>
       </c>
       <c r="S7">
-        <v>9301</v>
+        <v>9333</v>
       </c>
       <c r="T7" s="2">
-        <v>170</v>
+        <v>490</v>
       </c>
       <c r="U7">
-        <v>0.18</v>
+        <v>0.53</v>
       </c>
       <c r="V7" t="s">
         <v>137</v>
@@ -3604,7 +3643,7 @@
         <v>131.92</v>
       </c>
       <c r="AG7">
-        <v>150.6</v>
+        <v>189.74</v>
       </c>
       <c r="AH7">
         <v>8955.5</v>
@@ -3616,7 +3655,7 @@
         <v>3285</v>
       </c>
       <c r="AK7">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3667,7 +3706,7 @@
         <v>139</v>
       </c>
       <c r="BB7" t="s">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="BC7">
         <v>0</v>
@@ -3736,13 +3775,13 @@
         <v>215</v>
       </c>
       <c r="BY7" t="s">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="BZ7" t="s">
         <v>156</v>
       </c>
       <c r="CA7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="CB7" t="s">
         <v>158</v>
@@ -3778,7 +3817,7 @@
         <v>0.1</v>
       </c>
       <c r="CM7" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="CN7">
         <v>9100</v>
@@ -3790,7 +3829,7 @@
         <v>8955.5</v>
       </c>
       <c r="CQ7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="CR7" t="s">
         <v>137</v>
@@ -3807,16 +3846,16 @@
         <v>130</v>
       </c>
       <c r="D8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" t="s">
         <v>219</v>
-      </c>
-      <c r="E8" t="s">
-        <v>220</v>
       </c>
       <c r="F8" t="s">
         <v>133</v>
       </c>
       <c r="G8" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H8" t="s">
         <v>134</v>
@@ -3849,16 +3888,16 @@
         <v>26626.6</v>
       </c>
       <c r="R8">
-        <v>26761.8</v>
+        <v>26445.9</v>
       </c>
       <c r="S8">
-        <v>2058.6</v>
-      </c>
-      <c r="T8" s="2">
-        <v>135.2</v>
+        <v>2034.3</v>
+      </c>
+      <c r="T8" s="3">
+        <v>-180.7</v>
       </c>
       <c r="U8">
-        <v>0.51</v>
+        <v>-0.68</v>
       </c>
       <c r="V8" t="s">
         <v>137</v>
@@ -3894,19 +3933,19 @@
         <v>170.76</v>
       </c>
       <c r="AG8">
-        <v>170.72</v>
+        <v>96.97</v>
       </c>
       <c r="AH8">
         <v>1974.43</v>
       </c>
       <c r="AI8">
-        <v>2015.38</v>
+        <v>2003.79</v>
       </c>
       <c r="AJ8">
         <v>3614.73</v>
       </c>
-      <c r="AK8" t="s">
-        <v>137</v>
+      <c r="AK8">
+        <v>-0.19</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3957,10 +3996,10 @@
         <v>139</v>
       </c>
       <c r="BB8" t="s">
-        <v>137</v>
+        <v>220</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD8" t="s">
         <v>137</v>
@@ -3981,7 +4020,7 @@
         <v>4</v>
       </c>
       <c r="BJ8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK8" t="s">
         <v>221</v>
@@ -4017,7 +4056,7 @@
         <v>151</v>
       </c>
       <c r="BV8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="BW8" t="s">
         <v>225</v>
@@ -4032,7 +4071,7 @@
         <v>156</v>
       </c>
       <c r="CA8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="CB8" t="s">
         <v>158</v>
@@ -4109,7 +4148,7 @@
         <v>231</v>
       </c>
       <c r="H9" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -4184,7 +4223,7 @@
         <v>137</v>
       </c>
       <c r="AG9">
-        <v>83.84</v>
+        <v>88.84</v>
       </c>
       <c r="AH9">
         <v>402.78</v>
@@ -4271,7 +4310,7 @@
         <v>5</v>
       </c>
       <c r="BJ9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK9" t="s">
         <v>137</v>
@@ -4358,7 +4397,7 @@
         <v>137</v>
       </c>
       <c r="CM9" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="CN9">
         <v>425.45</v>
@@ -4399,7 +4438,7 @@
         <v>231</v>
       </c>
       <c r="H10" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -4429,16 +4468,16 @@
         <v>99322.5</v>
       </c>
       <c r="R10">
-        <v>102585</v>
+        <v>103005</v>
       </c>
       <c r="S10">
-        <v>6839</v>
+        <v>6867</v>
       </c>
       <c r="T10" s="2">
-        <v>3262.5</v>
+        <v>3682.5</v>
       </c>
       <c r="U10">
-        <v>3.28</v>
+        <v>3.71</v>
       </c>
       <c r="V10" t="s">
         <v>137</v>
@@ -4474,7 +4513,7 @@
         <v>137</v>
       </c>
       <c r="AG10">
-        <v>206.45</v>
+        <v>193.14</v>
       </c>
       <c r="AH10">
         <v>6083.5</v>
@@ -4486,7 +4525,7 @@
         <v>8070</v>
       </c>
       <c r="AK10">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -4561,7 +4600,7 @@
         <v>4</v>
       </c>
       <c r="BJ10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK10" t="s">
         <v>137</v>
@@ -4674,13 +4713,13 @@
         <v>228</v>
       </c>
       <c r="C11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" t="s">
         <v>246</v>
       </c>
-      <c r="D11" t="s">
-        <v>247</v>
-      </c>
       <c r="E11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F11" t="s">
         <v>133</v>
@@ -4689,7 +4728,7 @@
         <v>231</v>
       </c>
       <c r="H11" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I11" t="s">
         <v>36</v>
@@ -4719,16 +4758,16 @@
         <v>97794.2</v>
       </c>
       <c r="R11">
-        <v>99337.7</v>
+        <v>99852.2</v>
       </c>
       <c r="S11">
-        <v>2027.3</v>
+        <v>2037.8</v>
       </c>
       <c r="T11" s="2">
-        <v>1543.5</v>
+        <v>2058</v>
       </c>
       <c r="U11">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="s">
         <v>137</v>
@@ -4764,7 +4803,7 @@
         <v>137</v>
       </c>
       <c r="AG11">
-        <v>174.34</v>
+        <v>182.64</v>
       </c>
       <c r="AH11">
         <v>1842.85</v>
@@ -4776,7 +4815,7 @@
         <v>7494.55</v>
       </c>
       <c r="AK11">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -4851,7 +4890,7 @@
         <v>3</v>
       </c>
       <c r="BJ11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK11" t="s">
         <v>137</v>
@@ -4887,13 +4926,13 @@
         <v>151</v>
       </c>
       <c r="BV11" t="s">
+        <v>247</v>
+      </c>
+      <c r="BW11" t="s">
         <v>248</v>
       </c>
-      <c r="BW11" t="s">
+      <c r="BX11" t="s">
         <v>249</v>
-      </c>
-      <c r="BX11" t="s">
-        <v>250</v>
       </c>
       <c r="BY11" t="s">
         <v>237</v>
@@ -4938,7 +4977,7 @@
         <v>137</v>
       </c>
       <c r="CM11" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="CN11">
         <v>1957</v>
@@ -4950,7 +4989,7 @@
         <v>1957</v>
       </c>
       <c r="CQ11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CR11" t="s">
         <v>137</v>
@@ -4964,13 +5003,13 @@
         <v>228</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F12" t="s">
         <v>133</v>
@@ -4979,7 +5018,7 @@
         <v>231</v>
       </c>
       <c r="H12" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I12" t="s">
         <v>36</v>
@@ -5009,16 +5048,16 @@
         <v>97518.5</v>
       </c>
       <c r="R12">
-        <v>98626.1</v>
+        <v>98604.8</v>
       </c>
       <c r="S12">
-        <v>1389.1</v>
+        <v>1388.8</v>
       </c>
       <c r="T12" s="2">
-        <v>1107.6</v>
+        <v>1086.3</v>
       </c>
       <c r="U12">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="s">
         <v>137</v>
@@ -5054,7 +5093,7 @@
         <v>137</v>
       </c>
       <c r="AG12">
-        <v>189.34</v>
+        <v>182.98</v>
       </c>
       <c r="AH12">
         <v>1285.88</v>
@@ -5066,7 +5105,7 @@
         <v>6221.02</v>
       </c>
       <c r="AK12">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -5141,7 +5180,7 @@
         <v>4</v>
       </c>
       <c r="BJ12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK12" t="s">
         <v>137</v>
@@ -5177,13 +5216,13 @@
         <v>151</v>
       </c>
       <c r="BV12" t="s">
+        <v>252</v>
+      </c>
+      <c r="BW12" t="s">
         <v>253</v>
       </c>
-      <c r="BW12" t="s">
+      <c r="BX12" t="s">
         <v>254</v>
-      </c>
-      <c r="BX12" t="s">
-        <v>255</v>
       </c>
       <c r="BY12" t="s">
         <v>237</v>
@@ -5240,7 +5279,7 @@
         <v>1303.2</v>
       </c>
       <c r="CQ12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="CR12" t="s">
         <v>137</v>
@@ -5257,10 +5296,10 @@
         <v>229</v>
       </c>
       <c r="D13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F13" t="s">
         <v>133</v>
@@ -5269,7 +5308,7 @@
         <v>231</v>
       </c>
       <c r="H13" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I13" t="s">
         <v>36</v>
@@ -5299,16 +5338,16 @@
         <v>96509</v>
       </c>
       <c r="R13">
-        <v>96384.05</v>
+        <v>94783.5</v>
       </c>
       <c r="S13">
-        <v>809.95</v>
+        <v>796.5</v>
       </c>
       <c r="T13" s="3">
-        <v>-124.95</v>
+        <v>-1725.5</v>
       </c>
       <c r="U13">
-        <v>-0.13</v>
+        <v>-1.79</v>
       </c>
       <c r="V13" t="s">
         <v>137</v>
@@ -5344,7 +5383,7 @@
         <v>137</v>
       </c>
       <c r="AG13">
-        <v>189.61</v>
+        <v>186.42</v>
       </c>
       <c r="AH13">
         <v>771.79</v>
@@ -5356,7 +5395,7 @@
         <v>4665.99</v>
       </c>
       <c r="AK13">
-        <v>-0.03</v>
+        <v>-0.37</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -5431,7 +5470,7 @@
         <v>3</v>
       </c>
       <c r="BJ13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK13" t="s">
         <v>137</v>
@@ -5470,10 +5509,10 @@
         <v>234</v>
       </c>
       <c r="BW13" t="s">
+        <v>257</v>
+      </c>
+      <c r="BX13" t="s">
         <v>258</v>
-      </c>
-      <c r="BX13" t="s">
-        <v>259</v>
       </c>
       <c r="BY13" t="s">
         <v>237</v>
@@ -5530,7 +5569,7 @@
         <v>721.4</v>
       </c>
       <c r="CQ13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="CR13" t="s">
         <v>137</v>
@@ -5547,10 +5586,10 @@
         <v>229</v>
       </c>
       <c r="D14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F14" t="s">
         <v>133</v>
@@ -5559,7 +5598,7 @@
         <v>231</v>
       </c>
       <c r="H14" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I14" t="s">
         <v>36</v>
@@ -5589,16 +5628,16 @@
         <v>98538</v>
       </c>
       <c r="R14">
-        <v>98445.6</v>
+        <v>101300.1</v>
       </c>
       <c r="S14">
-        <v>2983.2</v>
-      </c>
-      <c r="T14" s="3">
-        <v>-92.4</v>
+        <v>3069.7</v>
+      </c>
+      <c r="T14" s="2">
+        <v>2762.1</v>
       </c>
       <c r="U14">
-        <v>-0.09</v>
+        <v>2.8</v>
       </c>
       <c r="V14" t="s">
         <v>137</v>
@@ -5634,7 +5673,7 @@
         <v>137</v>
       </c>
       <c r="AG14">
-        <v>172.05</v>
+        <v>170.48</v>
       </c>
       <c r="AH14">
         <v>2728.17</v>
@@ -5646,7 +5685,7 @@
         <v>8508.39</v>
       </c>
       <c r="AK14">
-        <v>-0.01</v>
+        <v>0.32</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -5721,7 +5760,7 @@
         <v>3</v>
       </c>
       <c r="BJ14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK14" t="s">
         <v>137</v>
@@ -5757,13 +5796,13 @@
         <v>151</v>
       </c>
       <c r="BV14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BW14" t="s">
+        <v>261</v>
+      </c>
+      <c r="BX14" t="s">
         <v>262</v>
-      </c>
-      <c r="BX14" t="s">
-        <v>263</v>
       </c>
       <c r="BY14" t="s">
         <v>237</v>
@@ -5808,7 +5847,7 @@
         <v>137</v>
       </c>
       <c r="CM14" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="CN14">
         <v>2903.2</v>
@@ -5820,7 +5859,7 @@
         <v>2903.2</v>
       </c>
       <c r="CQ14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="CR14" t="s">
         <v>137</v>
@@ -5834,13 +5873,13 @@
         <v>228</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="D15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F15" t="s">
         <v>133</v>
@@ -5849,7 +5888,7 @@
         <v>231</v>
       </c>
       <c r="H15" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I15" t="s">
         <v>36</v>
@@ -5879,16 +5918,16 @@
         <v>50001.8</v>
       </c>
       <c r="R15">
-        <v>50024</v>
+        <v>49642.9</v>
       </c>
       <c r="S15">
-        <v>1352</v>
-      </c>
-      <c r="T15" s="2">
-        <v>22.2</v>
+        <v>1341.7</v>
+      </c>
+      <c r="T15" s="3">
+        <v>-358.9</v>
       </c>
       <c r="U15">
-        <v>0.04</v>
+        <v>-0.72</v>
       </c>
       <c r="V15" t="s">
         <v>137</v>
@@ -5924,19 +5963,19 @@
         <v>137</v>
       </c>
       <c r="AG15">
-        <v>192.45</v>
+        <v>118.38</v>
       </c>
       <c r="AH15">
         <v>1251.2</v>
       </c>
       <c r="AI15">
-        <v>1331.72</v>
+        <v>1321.57</v>
       </c>
       <c r="AJ15">
         <v>7314.6</v>
       </c>
-      <c r="AK15" t="s">
-        <v>137</v>
+      <c r="AK15">
+        <v>-0.1</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -5987,10 +6026,10 @@
         <v>139</v>
       </c>
       <c r="BB15" t="s">
-        <v>137</v>
+        <v>265</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD15" t="s">
         <v>137</v>
@@ -6011,7 +6050,7 @@
         <v>4</v>
       </c>
       <c r="BJ15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK15" t="s">
         <v>137</v>
@@ -6047,7 +6086,7 @@
         <v>151</v>
       </c>
       <c r="BV15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="BW15" t="s">
         <v>266</v>
@@ -6125,7 +6164,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CR1"/>
+  <dimension ref="A1:CR2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6489,6 +6528,296 @@
       </c>
       <c r="CR1" s="1" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:96" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" t="s">
+        <v>273</v>
+      </c>
+      <c r="K2">
+        <v>19.59</v>
+      </c>
+      <c r="L2">
+        <v>19.59</v>
+      </c>
+      <c r="M2" t="s">
+        <v>274</v>
+      </c>
+      <c r="N2">
+        <v>16</v>
+      </c>
+      <c r="O2">
+        <v>31</v>
+      </c>
+      <c r="P2">
+        <v>31</v>
+      </c>
+      <c r="Q2">
+        <v>313.44</v>
+      </c>
+      <c r="R2">
+        <v>318.4</v>
+      </c>
+      <c r="S2">
+        <v>19.9</v>
+      </c>
+      <c r="T2" s="2">
+        <v>4.96</v>
+      </c>
+      <c r="U2">
+        <v>1.58</v>
+      </c>
+      <c r="V2" t="s">
+        <v>137</v>
+      </c>
+      <c r="W2" t="s">
+        <v>137</v>
+      </c>
+      <c r="X2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AF2">
+        <v>168.93</v>
+      </c>
+      <c r="AG2">
+        <v>64.43</v>
+      </c>
+      <c r="AH2">
+        <v>19.01</v>
+      </c>
+      <c r="AI2">
+        <v>19.01</v>
+      </c>
+      <c r="AJ2">
+        <v>17.98</v>
+      </c>
+      <c r="AK2">
+        <v>0.53</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AT2">
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>276</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>277</v>
+      </c>
+      <c r="BC2">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BH2">
+        <v>16</v>
+      </c>
+      <c r="BI2">
+        <v>4</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>143</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>166</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>138</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>146</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>147</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>167</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>278</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>279</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>280</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>156</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>138</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>138</v>
+      </c>
+      <c r="CD2">
+        <v>0.76</v>
+      </c>
+      <c r="CE2">
+        <v>5.69</v>
+      </c>
+      <c r="CF2">
+        <v>10.75</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>138</v>
+      </c>
+      <c r="CH2">
+        <v>18.16</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>172</v>
+      </c>
+      <c r="CJ2">
+        <v>1.54</v>
+      </c>
+      <c r="CK2">
+        <v>0.3</v>
+      </c>
+      <c r="CL2">
+        <v>0.76</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>281</v>
+      </c>
+      <c r="CN2">
+        <v>20</v>
+      </c>
+      <c r="CO2">
+        <v>20</v>
+      </c>
+      <c r="CP2">
+        <v>19.01</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>282</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -6875,7 +7204,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CR18"/>
+  <dimension ref="A1:CR19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -7339,7 +7668,7 @@
         <v>191.09</v>
       </c>
       <c r="AG2">
-        <v>191.09</v>
+        <v>193.59</v>
       </c>
       <c r="AH2">
         <v>805.6</v>
@@ -7629,7 +7958,7 @@
         <v>195.78</v>
       </c>
       <c r="AG3">
-        <v>195.78</v>
+        <v>198.28</v>
       </c>
       <c r="AH3">
         <v>597.22</v>
@@ -7841,49 +8170,49 @@
         <v>133</v>
       </c>
       <c r="G4" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="H4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I4" t="s">
         <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="K4">
-        <v>19.59</v>
+        <v>88.49</v>
       </c>
       <c r="L4">
-        <v>19.59</v>
+        <v>88.49</v>
       </c>
       <c r="M4" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="N4">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>313.44</v>
+        <v>442.45</v>
       </c>
       <c r="R4">
-        <v>333.92</v>
+        <v>440.45</v>
       </c>
       <c r="S4">
-        <v>20.87</v>
-      </c>
-      <c r="T4" s="2">
-        <v>20.48</v>
+        <v>88.09</v>
+      </c>
+      <c r="T4" s="3">
+        <v>-2</v>
       </c>
       <c r="U4">
-        <v>6.53</v>
+        <v>-0.45</v>
       </c>
       <c r="V4" t="s">
         <v>137</v>
@@ -7913,22 +8242,22 @@
         <v>137</v>
       </c>
       <c r="AE4" t="s">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="AF4">
-        <v>168.93</v>
+        <v>176.28</v>
       </c>
       <c r="AG4">
-        <v>168.93</v>
+        <v>176.28</v>
       </c>
       <c r="AH4">
-        <v>19.01</v>
+        <v>84.5</v>
       </c>
       <c r="AI4">
-        <v>19.01</v>
+        <v>84.5</v>
       </c>
       <c r="AJ4">
-        <v>17.98</v>
+        <v>19.95</v>
       </c>
       <c r="AK4" t="s">
         <v>137</v>
@@ -7958,7 +8287,7 @@
         <v>137</v>
       </c>
       <c r="AT4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4">
         <v>0</v>
@@ -7979,7 +8308,7 @@
         <v>137</v>
       </c>
       <c r="BA4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="BB4" t="s">
         <v>137</v>
@@ -7994,28 +8323,28 @@
         <v>140</v>
       </c>
       <c r="BF4" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="BG4" t="s">
         <v>142</v>
       </c>
       <c r="BH4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BI4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BJ4" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="BK4" t="s">
         <v>166</v>
       </c>
       <c r="BL4" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="BM4" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="BN4" t="s">
         <v>138</v>
@@ -8042,7 +8371,7 @@
         <v>167</v>
       </c>
       <c r="BV4" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="BW4" t="s">
         <v>181</v>
@@ -8060,52 +8389,52 @@
         <v>184</v>
       </c>
       <c r="CB4" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="CC4" t="s">
         <v>138</v>
       </c>
       <c r="CD4">
-        <v>0.76</v>
+        <v>2.77</v>
       </c>
       <c r="CE4">
-        <v>5.69</v>
+        <v>2.54</v>
       </c>
       <c r="CF4">
-        <v>10.75</v>
+        <v>7.97</v>
       </c>
       <c r="CG4" t="s">
         <v>138</v>
       </c>
       <c r="CH4">
-        <v>18.16</v>
+        <v>1.87</v>
       </c>
       <c r="CI4" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="CJ4">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="CK4">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="CL4">
-        <v>0.76</v>
+        <v>2.77</v>
       </c>
       <c r="CM4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="CN4">
-        <v>20</v>
+        <v>85.99</v>
       </c>
       <c r="CO4">
-        <v>20</v>
+        <v>84.5</v>
       </c>
       <c r="CP4">
-        <v>19.01</v>
+        <v>84.44</v>
       </c>
       <c r="CQ4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CR4" t="s">
         <v>137</v>
@@ -8122,16 +8451,16 @@
         <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F5" t="s">
         <v>133</v>
       </c>
       <c r="G5" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H5" t="s">
         <v>134</v>
@@ -8209,7 +8538,7 @@
         <v>179.24</v>
       </c>
       <c r="AG5">
-        <v>180.4</v>
+        <v>184.4</v>
       </c>
       <c r="AH5">
         <v>196.45</v>
@@ -8272,7 +8601,7 @@
         <v>139</v>
       </c>
       <c r="BB5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="BC5">
         <v>0</v>
@@ -8296,10 +8625,10 @@
         <v>4</v>
       </c>
       <c r="BJ5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="BL5" t="s">
         <v>137</v>
@@ -8332,13 +8661,13 @@
         <v>151</v>
       </c>
       <c r="BV5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="BW5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="BX5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="BY5" t="s">
         <v>155</v>
@@ -8347,7 +8676,7 @@
         <v>156</v>
       </c>
       <c r="CA5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="CB5" t="s">
         <v>158</v>
@@ -8383,7 +8712,7 @@
         <v>0.55</v>
       </c>
       <c r="CM5" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="CN5">
         <v>199.5</v>
@@ -8395,7 +8724,7 @@
         <v>186.53</v>
       </c>
       <c r="CQ5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="CR5" t="s">
         <v>137</v>
@@ -8412,16 +8741,16 @@
         <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F6" t="s">
         <v>133</v>
       </c>
       <c r="G6" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H6" t="s">
         <v>134</v>
@@ -8454,16 +8783,16 @@
         <v>97281.8</v>
       </c>
       <c r="R6">
-        <v>97944</v>
+        <v>97776.8</v>
       </c>
       <c r="S6">
-        <v>4452</v>
+        <v>4444.4</v>
       </c>
       <c r="T6" s="2">
-        <v>662.2</v>
+        <v>495</v>
       </c>
       <c r="U6">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
       <c r="V6" t="s">
         <v>137</v>
@@ -8499,7 +8828,7 @@
         <v>167.02</v>
       </c>
       <c r="AG6">
-        <v>166.98</v>
+        <v>133.99</v>
       </c>
       <c r="AH6">
         <v>4319.5</v>
@@ -8511,7 +8840,7 @@
         <v>2252.8</v>
       </c>
       <c r="AK6">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -8574,7 +8903,7 @@
         <v>137</v>
       </c>
       <c r="BF6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="BG6" t="s">
         <v>142</v>
@@ -8586,10 +8915,10 @@
         <v>1</v>
       </c>
       <c r="BJ6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="BL6" t="s">
         <v>137</v>
@@ -8622,13 +8951,13 @@
         <v>151</v>
       </c>
       <c r="BV6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="BW6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="BX6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BY6" t="s">
         <v>155</v>
@@ -8637,7 +8966,7 @@
         <v>156</v>
       </c>
       <c r="CA6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="CB6" t="s">
         <v>158</v>
@@ -8685,7 +9014,7 @@
         <v>4319.5</v>
       </c>
       <c r="CQ6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="CR6" t="s">
         <v>137</v>
@@ -8702,16 +9031,16 @@
         <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F7" t="s">
         <v>133</v>
       </c>
       <c r="G7" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H7" t="s">
         <v>134</v>
@@ -8744,16 +9073,16 @@
         <v>92840</v>
       </c>
       <c r="R7">
-        <v>93010</v>
+        <v>93330</v>
       </c>
       <c r="S7">
-        <v>9301</v>
+        <v>9333</v>
       </c>
       <c r="T7" s="2">
-        <v>170</v>
+        <v>490</v>
       </c>
       <c r="U7">
-        <v>0.18</v>
+        <v>0.53</v>
       </c>
       <c r="V7" t="s">
         <v>137</v>
@@ -8789,7 +9118,7 @@
         <v>131.92</v>
       </c>
       <c r="AG7">
-        <v>150.6</v>
+        <v>189.74</v>
       </c>
       <c r="AH7">
         <v>8955.5</v>
@@ -8801,7 +9130,7 @@
         <v>3285</v>
       </c>
       <c r="AK7">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -8852,7 +9181,7 @@
         <v>139</v>
       </c>
       <c r="BB7" t="s">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="BC7">
         <v>0</v>
@@ -8921,13 +9250,13 @@
         <v>215</v>
       </c>
       <c r="BY7" t="s">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="BZ7" t="s">
         <v>156</v>
       </c>
       <c r="CA7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="CB7" t="s">
         <v>158</v>
@@ -8963,7 +9292,7 @@
         <v>0.1</v>
       </c>
       <c r="CM7" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="CN7">
         <v>9100</v>
@@ -8975,7 +9304,7 @@
         <v>8955.5</v>
       </c>
       <c r="CQ7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="CR7" t="s">
         <v>137</v>
@@ -8992,16 +9321,16 @@
         <v>130</v>
       </c>
       <c r="D8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" t="s">
         <v>219</v>
-      </c>
-      <c r="E8" t="s">
-        <v>220</v>
       </c>
       <c r="F8" t="s">
         <v>133</v>
       </c>
       <c r="G8" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H8" t="s">
         <v>134</v>
@@ -9034,16 +9363,16 @@
         <v>26626.6</v>
       </c>
       <c r="R8">
-        <v>26761.8</v>
+        <v>26445.9</v>
       </c>
       <c r="S8">
-        <v>2058.6</v>
-      </c>
-      <c r="T8" s="2">
-        <v>135.2</v>
+        <v>2034.3</v>
+      </c>
+      <c r="T8" s="3">
+        <v>-180.7</v>
       </c>
       <c r="U8">
-        <v>0.51</v>
+        <v>-0.68</v>
       </c>
       <c r="V8" t="s">
         <v>137</v>
@@ -9079,19 +9408,19 @@
         <v>170.76</v>
       </c>
       <c r="AG8">
-        <v>170.72</v>
+        <v>96.97</v>
       </c>
       <c r="AH8">
         <v>1974.43</v>
       </c>
       <c r="AI8">
-        <v>2015.38</v>
+        <v>2003.79</v>
       </c>
       <c r="AJ8">
         <v>3614.73</v>
       </c>
-      <c r="AK8" t="s">
-        <v>137</v>
+      <c r="AK8">
+        <v>-0.19</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -9142,10 +9471,10 @@
         <v>139</v>
       </c>
       <c r="BB8" t="s">
-        <v>137</v>
+        <v>220</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD8" t="s">
         <v>137</v>
@@ -9166,7 +9495,7 @@
         <v>4</v>
       </c>
       <c r="BJ8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK8" t="s">
         <v>221</v>
@@ -9202,7 +9531,7 @@
         <v>151</v>
       </c>
       <c r="BV8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="BW8" t="s">
         <v>225</v>
@@ -9217,7 +9546,7 @@
         <v>156</v>
       </c>
       <c r="CA8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="CB8" t="s">
         <v>158</v>
@@ -9294,7 +9623,7 @@
         <v>231</v>
       </c>
       <c r="H9" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -9369,7 +9698,7 @@
         <v>137</v>
       </c>
       <c r="AG9">
-        <v>83.84</v>
+        <v>88.84</v>
       </c>
       <c r="AH9">
         <v>402.78</v>
@@ -9456,7 +9785,7 @@
         <v>5</v>
       </c>
       <c r="BJ9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK9" t="s">
         <v>137</v>
@@ -9543,7 +9872,7 @@
         <v>137</v>
       </c>
       <c r="CM9" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="CN9">
         <v>425.45</v>
@@ -9584,7 +9913,7 @@
         <v>231</v>
       </c>
       <c r="H10" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -9614,16 +9943,16 @@
         <v>99322.5</v>
       </c>
       <c r="R10">
-        <v>102585</v>
+        <v>103005</v>
       </c>
       <c r="S10">
-        <v>6839</v>
+        <v>6867</v>
       </c>
       <c r="T10" s="2">
-        <v>3262.5</v>
+        <v>3682.5</v>
       </c>
       <c r="U10">
-        <v>3.28</v>
+        <v>3.71</v>
       </c>
       <c r="V10" t="s">
         <v>137</v>
@@ -9659,7 +9988,7 @@
         <v>137</v>
       </c>
       <c r="AG10">
-        <v>206.45</v>
+        <v>193.14</v>
       </c>
       <c r="AH10">
         <v>6083.5</v>
@@ -9671,7 +10000,7 @@
         <v>8070</v>
       </c>
       <c r="AK10">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -9746,7 +10075,7 @@
         <v>4</v>
       </c>
       <c r="BJ10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK10" t="s">
         <v>137</v>
@@ -9859,13 +10188,13 @@
         <v>228</v>
       </c>
       <c r="C11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" t="s">
         <v>246</v>
       </c>
-      <c r="D11" t="s">
-        <v>247</v>
-      </c>
       <c r="E11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F11" t="s">
         <v>133</v>
@@ -9874,7 +10203,7 @@
         <v>231</v>
       </c>
       <c r="H11" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I11" t="s">
         <v>36</v>
@@ -9904,16 +10233,16 @@
         <v>97794.2</v>
       </c>
       <c r="R11">
-        <v>99337.7</v>
+        <v>99852.2</v>
       </c>
       <c r="S11">
-        <v>2027.3</v>
+        <v>2037.8</v>
       </c>
       <c r="T11" s="2">
-        <v>1543.5</v>
+        <v>2058</v>
       </c>
       <c r="U11">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="s">
         <v>137</v>
@@ -9949,7 +10278,7 @@
         <v>137</v>
       </c>
       <c r="AG11">
-        <v>174.34</v>
+        <v>182.64</v>
       </c>
       <c r="AH11">
         <v>1842.85</v>
@@ -9961,7 +10290,7 @@
         <v>7494.55</v>
       </c>
       <c r="AK11">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -10036,7 +10365,7 @@
         <v>3</v>
       </c>
       <c r="BJ11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK11" t="s">
         <v>137</v>
@@ -10072,13 +10401,13 @@
         <v>151</v>
       </c>
       <c r="BV11" t="s">
+        <v>247</v>
+      </c>
+      <c r="BW11" t="s">
         <v>248</v>
       </c>
-      <c r="BW11" t="s">
+      <c r="BX11" t="s">
         <v>249</v>
-      </c>
-      <c r="BX11" t="s">
-        <v>250</v>
       </c>
       <c r="BY11" t="s">
         <v>237</v>
@@ -10123,7 +10452,7 @@
         <v>137</v>
       </c>
       <c r="CM11" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="CN11">
         <v>1957</v>
@@ -10135,7 +10464,7 @@
         <v>1957</v>
       </c>
       <c r="CQ11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CR11" t="s">
         <v>137</v>
@@ -10149,13 +10478,13 @@
         <v>228</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F12" t="s">
         <v>133</v>
@@ -10164,7 +10493,7 @@
         <v>231</v>
       </c>
       <c r="H12" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I12" t="s">
         <v>36</v>
@@ -10194,16 +10523,16 @@
         <v>97518.5</v>
       </c>
       <c r="R12">
-        <v>98626.1</v>
+        <v>98604.8</v>
       </c>
       <c r="S12">
-        <v>1389.1</v>
+        <v>1388.8</v>
       </c>
       <c r="T12" s="2">
-        <v>1107.6</v>
+        <v>1086.3</v>
       </c>
       <c r="U12">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="s">
         <v>137</v>
@@ -10239,7 +10568,7 @@
         <v>137</v>
       </c>
       <c r="AG12">
-        <v>189.34</v>
+        <v>182.98</v>
       </c>
       <c r="AH12">
         <v>1285.88</v>
@@ -10251,7 +10580,7 @@
         <v>6221.02</v>
       </c>
       <c r="AK12">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -10326,7 +10655,7 @@
         <v>4</v>
       </c>
       <c r="BJ12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK12" t="s">
         <v>137</v>
@@ -10362,13 +10691,13 @@
         <v>151</v>
       </c>
       <c r="BV12" t="s">
+        <v>252</v>
+      </c>
+      <c r="BW12" t="s">
         <v>253</v>
       </c>
-      <c r="BW12" t="s">
+      <c r="BX12" t="s">
         <v>254</v>
-      </c>
-      <c r="BX12" t="s">
-        <v>255</v>
       </c>
       <c r="BY12" t="s">
         <v>237</v>
@@ -10425,7 +10754,7 @@
         <v>1303.2</v>
       </c>
       <c r="CQ12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="CR12" t="s">
         <v>137</v>
@@ -10442,10 +10771,10 @@
         <v>229</v>
       </c>
       <c r="D13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F13" t="s">
         <v>133</v>
@@ -10454,7 +10783,7 @@
         <v>231</v>
       </c>
       <c r="H13" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I13" t="s">
         <v>36</v>
@@ -10484,16 +10813,16 @@
         <v>96509</v>
       </c>
       <c r="R13">
-        <v>96384.05</v>
+        <v>94783.5</v>
       </c>
       <c r="S13">
-        <v>809.95</v>
+        <v>796.5</v>
       </c>
       <c r="T13" s="3">
-        <v>-124.95</v>
+        <v>-1725.5</v>
       </c>
       <c r="U13">
-        <v>-0.13</v>
+        <v>-1.79</v>
       </c>
       <c r="V13" t="s">
         <v>137</v>
@@ -10529,7 +10858,7 @@
         <v>137</v>
       </c>
       <c r="AG13">
-        <v>189.61</v>
+        <v>186.42</v>
       </c>
       <c r="AH13">
         <v>771.79</v>
@@ -10541,7 +10870,7 @@
         <v>4665.99</v>
       </c>
       <c r="AK13">
-        <v>-0.03</v>
+        <v>-0.37</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -10616,7 +10945,7 @@
         <v>3</v>
       </c>
       <c r="BJ13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK13" t="s">
         <v>137</v>
@@ -10655,10 +10984,10 @@
         <v>234</v>
       </c>
       <c r="BW13" t="s">
+        <v>257</v>
+      </c>
+      <c r="BX13" t="s">
         <v>258</v>
-      </c>
-      <c r="BX13" t="s">
-        <v>259</v>
       </c>
       <c r="BY13" t="s">
         <v>237</v>
@@ -10715,7 +11044,7 @@
         <v>721.4</v>
       </c>
       <c r="CQ13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="CR13" t="s">
         <v>137</v>
@@ -10732,10 +11061,10 @@
         <v>229</v>
       </c>
       <c r="D14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F14" t="s">
         <v>133</v>
@@ -10744,7 +11073,7 @@
         <v>231</v>
       </c>
       <c r="H14" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I14" t="s">
         <v>36</v>
@@ -10774,16 +11103,16 @@
         <v>98538</v>
       </c>
       <c r="R14">
-        <v>98445.6</v>
+        <v>101300.1</v>
       </c>
       <c r="S14">
-        <v>2983.2</v>
-      </c>
-      <c r="T14" s="3">
-        <v>-92.4</v>
+        <v>3069.7</v>
+      </c>
+      <c r="T14" s="2">
+        <v>2762.1</v>
       </c>
       <c r="U14">
-        <v>-0.09</v>
+        <v>2.8</v>
       </c>
       <c r="V14" t="s">
         <v>137</v>
@@ -10819,7 +11148,7 @@
         <v>137</v>
       </c>
       <c r="AG14">
-        <v>172.05</v>
+        <v>170.48</v>
       </c>
       <c r="AH14">
         <v>2728.17</v>
@@ -10831,7 +11160,7 @@
         <v>8508.39</v>
       </c>
       <c r="AK14">
-        <v>-0.01</v>
+        <v>0.32</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -10906,7 +11235,7 @@
         <v>3</v>
       </c>
       <c r="BJ14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK14" t="s">
         <v>137</v>
@@ -10942,13 +11271,13 @@
         <v>151</v>
       </c>
       <c r="BV14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BW14" t="s">
+        <v>261</v>
+      </c>
+      <c r="BX14" t="s">
         <v>262</v>
-      </c>
-      <c r="BX14" t="s">
-        <v>263</v>
       </c>
       <c r="BY14" t="s">
         <v>237</v>
@@ -10993,7 +11322,7 @@
         <v>137</v>
       </c>
       <c r="CM14" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="CN14">
         <v>2903.2</v>
@@ -11005,7 +11334,7 @@
         <v>2903.2</v>
       </c>
       <c r="CQ14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="CR14" t="s">
         <v>137</v>
@@ -11019,13 +11348,13 @@
         <v>228</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="D15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F15" t="s">
         <v>133</v>
@@ -11034,7 +11363,7 @@
         <v>231</v>
       </c>
       <c r="H15" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I15" t="s">
         <v>36</v>
@@ -11064,16 +11393,16 @@
         <v>50001.8</v>
       </c>
       <c r="R15">
-        <v>50024</v>
+        <v>49642.9</v>
       </c>
       <c r="S15">
-        <v>1352</v>
-      </c>
-      <c r="T15" s="2">
-        <v>22.2</v>
+        <v>1341.7</v>
+      </c>
+      <c r="T15" s="3">
+        <v>-358.9</v>
       </c>
       <c r="U15">
-        <v>0.04</v>
+        <v>-0.72</v>
       </c>
       <c r="V15" t="s">
         <v>137</v>
@@ -11109,19 +11438,19 @@
         <v>137</v>
       </c>
       <c r="AG15">
-        <v>192.45</v>
+        <v>118.38</v>
       </c>
       <c r="AH15">
         <v>1251.2</v>
       </c>
       <c r="AI15">
-        <v>1331.72</v>
+        <v>1321.57</v>
       </c>
       <c r="AJ15">
         <v>7314.6</v>
       </c>
-      <c r="AK15" t="s">
-        <v>137</v>
+      <c r="AK15">
+        <v>-0.1</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -11172,10 +11501,10 @@
         <v>139</v>
       </c>
       <c r="BB15" t="s">
-        <v>137</v>
+        <v>265</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD15" t="s">
         <v>137</v>
@@ -11196,7 +11525,7 @@
         <v>4</v>
       </c>
       <c r="BJ15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BK15" t="s">
         <v>137</v>
@@ -11232,7 +11561,7 @@
         <v>151</v>
       </c>
       <c r="BV15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="BW15" t="s">
         <v>266</v>
@@ -11309,61 +11638,61 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="D16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G16" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I16" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="J16" t="s">
-        <v>137</v>
-      </c>
-      <c r="K16" t="s">
-        <v>137</v>
-      </c>
-      <c r="L16" t="s">
-        <v>137</v>
+        <v>273</v>
+      </c>
+      <c r="K16">
+        <v>19.59</v>
+      </c>
+      <c r="L16">
+        <v>19.59</v>
       </c>
       <c r="M16" t="s">
-        <v>272</v>
-      </c>
-      <c r="N16" t="s">
-        <v>137</v>
-      </c>
-      <c r="O16" t="s">
-        <v>137</v>
-      </c>
-      <c r="P16" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>137</v>
-      </c>
-      <c r="R16" t="s">
-        <v>137</v>
+        <v>274</v>
+      </c>
+      <c r="N16">
+        <v>16</v>
+      </c>
+      <c r="O16">
+        <v>31</v>
+      </c>
+      <c r="P16">
+        <v>31</v>
+      </c>
+      <c r="Q16">
+        <v>313.44</v>
+      </c>
+      <c r="R16">
+        <v>318.4</v>
       </c>
       <c r="S16">
-        <v>4506.7998046875</v>
-      </c>
-      <c r="T16" t="s">
-        <v>137</v>
-      </c>
-      <c r="U16" t="s">
-        <v>137</v>
+        <v>19.9</v>
+      </c>
+      <c r="T16" s="2">
+        <v>4.96</v>
+      </c>
+      <c r="U16">
+        <v>1.58</v>
       </c>
       <c r="V16" t="s">
         <v>137</v>
@@ -11393,25 +11722,25 @@
         <v>137</v>
       </c>
       <c r="AE16" t="s">
-        <v>273</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>137</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>137</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>137</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>137</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>137</v>
+        <v>275</v>
+      </c>
+      <c r="AF16">
+        <v>168.93</v>
+      </c>
+      <c r="AG16">
+        <v>64.43</v>
+      </c>
+      <c r="AH16">
+        <v>19.01</v>
+      </c>
+      <c r="AI16">
+        <v>19.01</v>
+      </c>
+      <c r="AJ16">
+        <v>17.98</v>
+      </c>
+      <c r="AK16">
+        <v>0.53</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -11438,7 +11767,7 @@
         <v>137</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16">
         <v>0</v>
@@ -11459,37 +11788,37 @@
         <v>137</v>
       </c>
       <c r="BA16" t="s">
-        <v>137</v>
+        <v>276</v>
       </c>
       <c r="BB16" t="s">
-        <v>137</v>
+        <v>277</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD16" t="s">
         <v>137</v>
       </c>
       <c r="BE16" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="BF16" t="s">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="BG16" t="s">
         <v>142</v>
       </c>
       <c r="BH16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BI16">
         <v>4</v>
       </c>
       <c r="BJ16" t="s">
-        <v>274</v>
+        <v>143</v>
       </c>
       <c r="BK16" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="BL16" t="s">
         <v>137</v>
@@ -11501,28 +11830,28 @@
         <v>138</v>
       </c>
       <c r="BO16" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="BP16" t="s">
         <v>137</v>
       </c>
       <c r="BQ16" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="BR16" t="s">
         <v>148</v>
       </c>
       <c r="BS16" t="s">
-        <v>275</v>
+        <v>149</v>
       </c>
       <c r="BT16" t="s">
         <v>150</v>
       </c>
       <c r="BU16" t="s">
-        <v>276</v>
+        <v>167</v>
       </c>
       <c r="BV16" t="s">
-        <v>277</v>
+        <v>152</v>
       </c>
       <c r="BW16" t="s">
         <v>278</v>
@@ -11531,61 +11860,61 @@
         <v>279</v>
       </c>
       <c r="BY16" t="s">
-        <v>237</v>
+        <v>280</v>
       </c>
       <c r="BZ16" t="s">
-        <v>238</v>
+        <v>156</v>
       </c>
       <c r="CA16" t="s">
-        <v>280</v>
+        <v>184</v>
       </c>
       <c r="CB16" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="CC16" t="s">
         <v>138</v>
       </c>
       <c r="CD16">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="CE16">
-        <v>2.15</v>
+        <v>5.69</v>
       </c>
       <c r="CF16">
-        <v>6.95</v>
+        <v>10.75</v>
       </c>
       <c r="CG16" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="CH16">
-        <v>6.81</v>
+        <v>18.16</v>
       </c>
       <c r="CI16" t="s">
         <v>172</v>
       </c>
       <c r="CJ16">
-        <v>2.21</v>
+        <v>1.54</v>
       </c>
       <c r="CK16">
-        <v>0.58</v>
+        <v>0.3</v>
       </c>
       <c r="CL16">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="CM16" t="s">
-        <v>173</v>
+        <v>281</v>
       </c>
       <c r="CN16">
-        <v>4331</v>
+        <v>20</v>
       </c>
       <c r="CO16">
-        <v>4305.8</v>
+        <v>20</v>
       </c>
       <c r="CP16">
-        <v>4305.8</v>
+        <v>19.01</v>
       </c>
       <c r="CQ16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="CR16" t="s">
         <v>137</v>
@@ -11599,19 +11928,19 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="D17" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E17" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F17" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="G17" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H17" t="s">
         <v>137</v>
@@ -11629,7 +11958,7 @@
         <v>137</v>
       </c>
       <c r="M17" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="N17" t="s">
         <v>137</v>
@@ -11647,7 +11976,7 @@
         <v>137</v>
       </c>
       <c r="S17">
-        <v>1117.199951171875</v>
+        <v>4506.7998046875</v>
       </c>
       <c r="T17" t="s">
         <v>137</v>
@@ -11683,7 +12012,7 @@
         <v>137</v>
       </c>
       <c r="AE17" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="AF17" t="s">
         <v>137</v>
@@ -11764,19 +12093,19 @@
         <v>137</v>
       </c>
       <c r="BF17" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="BG17" t="s">
         <v>142</v>
       </c>
       <c r="BH17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BI17">
         <v>4</v>
       </c>
       <c r="BJ17" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="BK17" t="s">
         <v>137</v>
@@ -11803,22 +12132,22 @@
         <v>148</v>
       </c>
       <c r="BS17" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="BT17" t="s">
         <v>150</v>
       </c>
       <c r="BU17" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="BV17" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="BW17" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="BX17" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="BY17" t="s">
         <v>237</v>
@@ -11827,55 +12156,55 @@
         <v>238</v>
       </c>
       <c r="CA17" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="CB17" t="s">
         <v>158</v>
       </c>
       <c r="CC17" t="s">
+        <v>138</v>
+      </c>
+      <c r="CD17">
+        <v>0.99</v>
+      </c>
+      <c r="CE17">
+        <v>2.15</v>
+      </c>
+      <c r="CF17">
+        <v>6.95</v>
+      </c>
+      <c r="CG17" t="s">
         <v>158</v>
       </c>
-      <c r="CD17">
-        <v>1.56</v>
-      </c>
-      <c r="CE17">
-        <v>2.97</v>
-      </c>
-      <c r="CF17">
-        <v>9.83</v>
-      </c>
-      <c r="CG17" t="s">
-        <v>138</v>
-      </c>
       <c r="CH17">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="CI17" t="s">
-        <v>287</v>
+        <v>172</v>
       </c>
       <c r="CJ17">
-        <v>1.19</v>
+        <v>2.21</v>
       </c>
       <c r="CK17">
-        <v>0.98</v>
+        <v>0.58</v>
       </c>
       <c r="CL17">
-        <v>1.56</v>
+        <v>0.99</v>
       </c>
       <c r="CM17" t="s">
         <v>173</v>
       </c>
       <c r="CN17">
-        <v>1048</v>
+        <v>4331</v>
       </c>
       <c r="CO17">
-        <v>1021.6</v>
+        <v>4305.8</v>
       </c>
       <c r="CP17">
-        <v>1012.9</v>
+        <v>4305.8</v>
       </c>
       <c r="CQ17" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="CR17" t="s">
         <v>137</v>
@@ -11889,19 +12218,19 @@
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="D18" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E18" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F18" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="G18" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H18" t="s">
         <v>137</v>
@@ -11919,7 +12248,7 @@
         <v>137</v>
       </c>
       <c r="M18" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="N18" t="s">
         <v>137</v>
@@ -11937,7 +12266,7 @@
         <v>137</v>
       </c>
       <c r="S18">
-        <v>747.0499877929688</v>
+        <v>1117.199951171875</v>
       </c>
       <c r="T18" t="s">
         <v>137</v>
@@ -11973,7 +12302,7 @@
         <v>137</v>
       </c>
       <c r="AE18" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="AF18" t="s">
         <v>137</v>
@@ -12054,19 +12383,19 @@
         <v>137</v>
       </c>
       <c r="BF18" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="BG18" t="s">
-        <v>208</v>
+        <v>142</v>
       </c>
       <c r="BH18">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BI18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ18" t="s">
-        <v>190</v>
+        <v>287</v>
       </c>
       <c r="BK18" t="s">
         <v>137</v>
@@ -12093,22 +12422,22 @@
         <v>148</v>
       </c>
       <c r="BS18" t="s">
-        <v>149</v>
+        <v>296</v>
       </c>
       <c r="BT18" t="s">
         <v>150</v>
       </c>
       <c r="BU18" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="BV18" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="BW18" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="BX18" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="BY18" t="s">
         <v>237</v>
@@ -12117,57 +12446,347 @@
         <v>238</v>
       </c>
       <c r="CA18" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="CB18" t="s">
         <v>158</v>
       </c>
       <c r="CC18" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="CD18">
-        <v>0.42</v>
+        <v>1.56</v>
       </c>
       <c r="CE18">
-        <v>4.83</v>
+        <v>2.97</v>
       </c>
       <c r="CF18">
-        <v>9.1</v>
+        <v>9.83</v>
       </c>
       <c r="CG18" t="s">
         <v>138</v>
       </c>
       <c r="CH18">
-        <v>8.22</v>
+        <v>0</v>
       </c>
       <c r="CI18" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="CJ18">
-        <v>6</v>
+        <v>1.19</v>
       </c>
       <c r="CK18">
-        <v>1.81</v>
+        <v>0.98</v>
       </c>
       <c r="CL18">
-        <v>0.42</v>
+        <v>1.56</v>
       </c>
       <c r="CM18" t="s">
         <v>173</v>
       </c>
       <c r="CN18">
+        <v>1048</v>
+      </c>
+      <c r="CO18">
+        <v>1021.6</v>
+      </c>
+      <c r="CP18">
+        <v>1012.9</v>
+      </c>
+      <c r="CQ18" t="s">
+        <v>300</v>
+      </c>
+      <c r="CR18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:96" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
+        <v>229</v>
+      </c>
+      <c r="D19" t="s">
+        <v>301</v>
+      </c>
+      <c r="E19" t="s">
+        <v>301</v>
+      </c>
+      <c r="F19" t="s">
+        <v>284</v>
+      </c>
+      <c r="G19" t="s">
+        <v>190</v>
+      </c>
+      <c r="H19" t="s">
+        <v>137</v>
+      </c>
+      <c r="I19" t="s">
+        <v>137</v>
+      </c>
+      <c r="J19" t="s">
+        <v>137</v>
+      </c>
+      <c r="K19" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" t="s">
+        <v>137</v>
+      </c>
+      <c r="M19" t="s">
+        <v>285</v>
+      </c>
+      <c r="N19" t="s">
+        <v>137</v>
+      </c>
+      <c r="O19" t="s">
+        <v>137</v>
+      </c>
+      <c r="P19" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>137</v>
+      </c>
+      <c r="R19" t="s">
+        <v>137</v>
+      </c>
+      <c r="S19">
+        <v>747.0499877929688</v>
+      </c>
+      <c r="T19" t="s">
+        <v>137</v>
+      </c>
+      <c r="U19" t="s">
+        <v>137</v>
+      </c>
+      <c r="V19" t="s">
+        <v>137</v>
+      </c>
+      <c r="W19" t="s">
+        <v>137</v>
+      </c>
+      <c r="X19" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>286</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AY19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AZ19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BE19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BF19" t="s">
+        <v>141</v>
+      </c>
+      <c r="BG19" t="s">
+        <v>208</v>
+      </c>
+      <c r="BH19">
+        <v>12</v>
+      </c>
+      <c r="BI19">
+        <v>2</v>
+      </c>
+      <c r="BJ19" t="s">
+        <v>192</v>
+      </c>
+      <c r="BK19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BL19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BM19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BN19" t="s">
+        <v>138</v>
+      </c>
+      <c r="BO19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BP19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BQ19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR19" t="s">
+        <v>148</v>
+      </c>
+      <c r="BS19" t="s">
+        <v>149</v>
+      </c>
+      <c r="BT19" t="s">
+        <v>150</v>
+      </c>
+      <c r="BU19" t="s">
+        <v>289</v>
+      </c>
+      <c r="BV19" t="s">
+        <v>302</v>
+      </c>
+      <c r="BW19" t="s">
+        <v>303</v>
+      </c>
+      <c r="BX19" t="s">
+        <v>304</v>
+      </c>
+      <c r="BY19" t="s">
+        <v>237</v>
+      </c>
+      <c r="BZ19" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA19" t="s">
+        <v>293</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>158</v>
+      </c>
+      <c r="CC19" t="s">
+        <v>138</v>
+      </c>
+      <c r="CD19">
+        <v>0.42</v>
+      </c>
+      <c r="CE19">
+        <v>4.83</v>
+      </c>
+      <c r="CF19">
+        <v>9.1</v>
+      </c>
+      <c r="CG19" t="s">
+        <v>138</v>
+      </c>
+      <c r="CH19">
+        <v>8.22</v>
+      </c>
+      <c r="CI19" t="s">
+        <v>172</v>
+      </c>
+      <c r="CJ19">
+        <v>6</v>
+      </c>
+      <c r="CK19">
+        <v>1.81</v>
+      </c>
+      <c r="CL19">
+        <v>0.42</v>
+      </c>
+      <c r="CM19" t="s">
+        <v>173</v>
+      </c>
+      <c r="CN19">
         <v>701.8</v>
       </c>
-      <c r="CO18">
+      <c r="CO19">
         <v>688.05</v>
       </c>
-      <c r="CP18">
+      <c r="CP19">
         <v>688.05</v>
       </c>
-      <c r="CQ18" t="s">
-        <v>293</v>
-      </c>
-      <c r="CR18" t="s">
+      <c r="CQ19" t="s">
+        <v>305</v>
+      </c>
+      <c r="CR19" t="s">
         <v>137</v>
       </c>
     </row>
@@ -12180,7 +12799,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -12206,57 +12825,57 @@
         <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>91</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B2" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
@@ -12268,7 +12887,7 @@
         <v>142</v>
       </c>
       <c r="F2">
-        <v>199.89</v>
+        <v>202.39</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -12301,27 +12920,27 @@
         <v>794.42</v>
       </c>
       <c r="Q2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B3" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>324</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
         <v>142</v>
       </c>
       <c r="F3">
-        <v>195.83</v>
+        <v>191.38</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -12333,10 +12952,10 @@
         <v>137</v>
       </c>
       <c r="J3">
-        <v>5.69</v>
+        <v>3.4</v>
       </c>
       <c r="K3">
-        <v>1.44</v>
+        <v>2.9</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -12351,30 +12970,30 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>628.33</v>
+        <v>8650.76</v>
       </c>
       <c r="Q3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B4" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="C4" t="s">
-        <v>313</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
         <v>142</v>
       </c>
       <c r="F4">
-        <v>170.4</v>
+        <v>177.33</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -12386,10 +13005,10 @@
         <v>137</v>
       </c>
       <c r="J4">
-        <v>4.02</v>
+        <v>2.62</v>
       </c>
       <c r="K4">
-        <v>1.65</v>
+        <v>3.44</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -12404,10 +13023,116 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>790</v>
+        <v>176.13</v>
       </c>
       <c r="Q4" t="s">
-        <v>310</v>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5">
+        <v>173.68</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>137</v>
+      </c>
+      <c r="J5">
+        <v>5.67</v>
+      </c>
+      <c r="K5">
+        <v>2.04</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>201</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>15684</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F6">
+        <v>166.42</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>137</v>
+      </c>
+      <c r="J6">
+        <v>4.16</v>
+      </c>
+      <c r="K6">
+        <v>1.22</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>141</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>4875</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -12419,7 +13144,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -12439,78 +13164,78 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B2" t="s">
         <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D2" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E2" t="s">
         <v>134</v>
       </c>
       <c r="G2" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="H2" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="I2" t="s">
         <v>142</v>
@@ -12537,12 +13262,12 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B3" t="s">
         <v>134</v>
@@ -12557,10 +13282,10 @@
         <v>134</v>
       </c>
       <c r="G3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="H3" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="I3" t="s">
         <v>142</v>
@@ -12587,30 +13312,30 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B4" t="s">
         <v>134</v>
       </c>
       <c r="C4" t="s">
-        <v>327</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="E4" t="s">
         <v>134</v>
       </c>
       <c r="G4" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="H4" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="I4" t="s">
         <v>142</v>
@@ -12637,18 +13362,18 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B5" t="s">
         <v>134</v>
       </c>
       <c r="C5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -12657,10 +13382,10 @@
         <v>134</v>
       </c>
       <c r="G5" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="H5" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="I5" t="s">
         <v>142</v>
@@ -12687,12 +13412,12 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B6" t="s">
         <v>134</v>
@@ -12710,10 +13435,10 @@
         <v>622.5499877929688</v>
       </c>
       <c r="G6" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="H6" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="I6" t="s">
         <v>142</v>
@@ -12740,39 +13465,39 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="C7" t="s">
-        <v>309</v>
+        <v>342</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="F7">
-        <v>863.5</v>
+        <v>637.9000244140625</v>
       </c>
       <c r="G7" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="H7" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="I7" t="s">
         <v>142</v>
       </c>
       <c r="J7">
-        <v>199.89</v>
+        <v>195.83</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -12781,10 +13506,10 @@
         <v>137</v>
       </c>
       <c r="M7">
-        <v>15.28</v>
+        <v>5.69</v>
       </c>
       <c r="N7">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -12793,39 +13518,39 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>324</v>
       </c>
       <c r="E8" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="F8">
-        <v>637.9000244140625</v>
+        <v>814.9000244140625</v>
       </c>
       <c r="G8" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="H8" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="I8" t="s">
         <v>142</v>
       </c>
       <c r="J8">
-        <v>195.83</v>
+        <v>170.4</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -12834,10 +13559,10 @@
         <v>137</v>
       </c>
       <c r="M8">
-        <v>5.69</v>
+        <v>4.02</v>
       </c>
       <c r="N8">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -12846,60 +13571,378 @@
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B9" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C9" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="D9" t="s">
-        <v>313</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="F9">
-        <v>814.9000244140625</v>
+        <v>637.9000244140625</v>
       </c>
       <c r="G9" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="H9" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="I9" t="s">
         <v>142</v>
       </c>
       <c r="J9">
-        <v>170.4</v>
+        <v>195.83</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>-3.27</v>
       </c>
       <c r="L9" t="s">
         <v>137</v>
       </c>
       <c r="M9">
-        <v>4.02</v>
+        <v>2.5</v>
       </c>
       <c r="N9">
-        <v>1.65</v>
+        <v>0.7</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>70.28</v>
       </c>
       <c r="P9">
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>310</v>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>344</v>
+      </c>
+      <c r="B10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" t="s">
+        <v>343</v>
+      </c>
+      <c r="D10" t="s">
+        <v>324</v>
+      </c>
+      <c r="E10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F10">
+        <v>814.9000244140625</v>
+      </c>
+      <c r="G10" t="s">
+        <v>336</v>
+      </c>
+      <c r="H10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I10" t="s">
+        <v>142</v>
+      </c>
+      <c r="J10">
+        <v>170.4</v>
+      </c>
+      <c r="K10">
+        <v>-1.71</v>
+      </c>
+      <c r="L10" t="s">
+        <v>137</v>
+      </c>
+      <c r="M10">
+        <v>2.35</v>
+      </c>
+      <c r="N10">
+        <v>0.99</v>
+      </c>
+      <c r="O10">
+        <v>81.22</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>344</v>
+      </c>
+      <c r="B11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11">
+        <v>863.5</v>
+      </c>
+      <c r="G11" t="s">
+        <v>340</v>
+      </c>
+      <c r="H11" t="s">
+        <v>320</v>
+      </c>
+      <c r="I11" t="s">
+        <v>142</v>
+      </c>
+      <c r="J11">
+        <v>202.39</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>137</v>
+      </c>
+      <c r="M11">
+        <v>15.28</v>
+      </c>
+      <c r="N11">
+        <v>2.1</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>344</v>
+      </c>
+      <c r="B12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D12" t="s">
+        <v>324</v>
+      </c>
+      <c r="E12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12">
+        <v>8782.5</v>
+      </c>
+      <c r="G12" t="s">
+        <v>340</v>
+      </c>
+      <c r="H12" t="s">
+        <v>320</v>
+      </c>
+      <c r="I12" t="s">
+        <v>142</v>
+      </c>
+      <c r="J12">
+        <v>191.38</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
+        <v>137</v>
+      </c>
+      <c r="M12">
+        <v>3.4</v>
+      </c>
+      <c r="N12">
+        <v>2.9</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>344</v>
+      </c>
+      <c r="B13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" t="s">
+        <v>325</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13">
+        <v>179.52000427246094</v>
+      </c>
+      <c r="G13" t="s">
+        <v>340</v>
+      </c>
+      <c r="H13" t="s">
+        <v>320</v>
+      </c>
+      <c r="I13" t="s">
+        <v>142</v>
+      </c>
+      <c r="J13">
+        <v>177.33</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
+        <v>137</v>
+      </c>
+      <c r="M13">
+        <v>2.62</v>
+      </c>
+      <c r="N13">
+        <v>3.44</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>344</v>
+      </c>
+      <c r="B14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" t="s">
+        <v>326</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14">
+        <v>16326</v>
+      </c>
+      <c r="G14" t="s">
+        <v>340</v>
+      </c>
+      <c r="H14" t="s">
+        <v>320</v>
+      </c>
+      <c r="I14" t="s">
+        <v>142</v>
+      </c>
+      <c r="J14">
+        <v>173.68</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14" t="s">
+        <v>137</v>
+      </c>
+      <c r="M14">
+        <v>5.67</v>
+      </c>
+      <c r="N14">
+        <v>2.04</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>344</v>
+      </c>
+      <c r="B15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" t="s">
+        <v>327</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15">
+        <v>5024</v>
+      </c>
+      <c r="G15" t="s">
+        <v>340</v>
+      </c>
+      <c r="H15" t="s">
+        <v>320</v>
+      </c>
+      <c r="I15" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15">
+        <v>166.42</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>137</v>
+      </c>
+      <c r="M15">
+        <v>4.16</v>
+      </c>
+      <c r="N15">
+        <v>1.22</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -12923,30 +13966,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B2" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -12958,7 +14001,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2877" uniqueCount="355">
   <si>
     <t>Metric</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T09:43:28.746Z</t>
+    <t>2026-07-14T09:47:40.780Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1053,6 +1053,9 @@
   </si>
   <si>
     <t>2026-07-14T09:43:28.265Z</t>
+  </si>
+  <si>
+    <t>2026-07-14T09:47:40.366Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -2784,8 +2787,8 @@
       <c r="AJ4">
         <v>19.95</v>
       </c>
-      <c r="AK4" t="s">
-        <v>137</v>
+      <c r="AK4">
+        <v>-0.1</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2833,7 +2836,7 @@
         <v>137</v>
       </c>
       <c r="BA4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BB4" t="s">
         <v>137</v>
@@ -8259,8 +8262,8 @@
       <c r="AJ4">
         <v>19.95</v>
       </c>
-      <c r="AK4" t="s">
-        <v>137</v>
+      <c r="AK4">
+        <v>-0.1</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -8308,7 +8311,7 @@
         <v>137</v>
       </c>
       <c r="BA4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BB4" t="s">
         <v>137</v>
@@ -13682,7 +13685,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B11" t="s">
         <v>134</v>
@@ -13735,7 +13738,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B12" t="s">
         <v>134</v>
@@ -13788,7 +13791,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B13" t="s">
         <v>134</v>
@@ -13841,7 +13844,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B14" t="s">
         <v>134</v>
@@ -13894,7 +13897,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B15" t="s">
         <v>134</v>
@@ -13966,30 +13969,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -14001,7 +14004,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T09:47:40.780Z</t>
+    <t>2026-07-14T09:56:50.329Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1055,7 +1055,7 @@
     <t>2026-07-14T09:43:28.265Z</t>
   </si>
   <si>
-    <t>2026-07-14T09:47:40.366Z</t>
+    <t>2026-07-14T09:56:49.837Z</t>
   </si>
   <si>
     <t>Date</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T09:56:50.329Z</t>
+    <t>2026-07-14T10:19:15.087Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1055,7 +1055,7 @@
     <t>2026-07-14T09:43:28.265Z</t>
   </si>
   <si>
-    <t>2026-07-14T09:56:49.837Z</t>
+    <t>2026-07-14T10:19:14.585Z</t>
   </si>
   <si>
     <t>Date</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="365">
   <si>
     <t>Metric</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T10:56:39.209Z</t>
+    <t>2026-07-14T11:24:44.571Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1083,6 +1083,9 @@
   </si>
   <si>
     <t>2026-07-14T10:56:37.603Z</t>
+  </si>
+  <si>
+    <t>2026-07-14T11:24:43.380Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -14139,7 +14142,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B15" t="s">
         <v>135</v>
@@ -14192,7 +14195,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B16" t="s">
         <v>135</v>
@@ -14245,7 +14248,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B17" t="s">
         <v>135</v>
@@ -14298,7 +14301,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B18" t="s">
         <v>135</v>
@@ -14351,7 +14354,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B19" t="s">
         <v>134</v>
@@ -14404,7 +14407,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B20" t="s">
         <v>135</v>
@@ -14476,30 +14479,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -14511,7 +14514,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="366">
   <si>
     <t>Metric</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T11:24:44.571Z</t>
+    <t>2026-07-14T11:35:10.635Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -551,6 +551,9 @@
     <t>NIVABUPA</t>
   </si>
   <si>
+    <t>official NSE delivery distribution</t>
+  </si>
+  <si>
     <t>Momentum continuation buy</t>
   </si>
   <si>
@@ -1085,7 +1088,7 @@
     <t>2026-07-14T10:56:37.603Z</t>
   </si>
   <si>
-    <t>2026-07-14T11:24:43.380Z</t>
+    <t>2026-07-14T11:35:09.136Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -2516,7 +2519,7 @@
         <v>195.78</v>
       </c>
       <c r="AG3">
-        <v>184.69</v>
+        <v>179.52</v>
       </c>
       <c r="AH3">
         <v>597.22</v>
@@ -2806,7 +2809,7 @@
         <v>176.28</v>
       </c>
       <c r="AG4">
-        <v>176.87</v>
+        <v>171.71</v>
       </c>
       <c r="AH4">
         <v>84.5</v>
@@ -2869,7 +2872,7 @@
         <v>139</v>
       </c>
       <c r="BB4" t="s">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="BC4">
         <v>0</v>
@@ -2881,7 +2884,7 @@
         <v>140</v>
       </c>
       <c r="BF4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="BG4" t="s">
         <v>142</v>
@@ -2899,10 +2902,10 @@
         <v>166</v>
       </c>
       <c r="BL4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="BM4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="BN4" t="s">
         <v>138</v>
@@ -2929,22 +2932,22 @@
         <v>167</v>
       </c>
       <c r="BV4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="BW4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="BX4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BY4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BZ4" t="s">
         <v>156</v>
       </c>
       <c r="CA4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="CB4" t="s">
         <v>158</v>
@@ -2968,7 +2971,7 @@
         <v>1.87</v>
       </c>
       <c r="CI4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="CJ4">
         <v>1.91</v>
@@ -2980,7 +2983,7 @@
         <v>2.77</v>
       </c>
       <c r="CM4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CN4">
         <v>85.99</v>
@@ -2992,7 +2995,7 @@
         <v>84.44</v>
       </c>
       <c r="CQ4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="CR4" t="s">
         <v>137</v>
@@ -3009,16 +3012,16 @@
         <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F5" t="s">
         <v>133</v>
       </c>
       <c r="G5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H5" t="s">
         <v>134</v>
@@ -3171,7 +3174,7 @@
         <v>137</v>
       </c>
       <c r="BF5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="BG5" t="s">
         <v>142</v>
@@ -3183,10 +3186,10 @@
         <v>1</v>
       </c>
       <c r="BJ5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="BL5" t="s">
         <v>137</v>
@@ -3219,13 +3222,13 @@
         <v>151</v>
       </c>
       <c r="BV5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="BW5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BX5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="BY5" t="s">
         <v>155</v>
@@ -3234,7 +3237,7 @@
         <v>156</v>
       </c>
       <c r="CA5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="CB5" t="s">
         <v>158</v>
@@ -3282,7 +3285,7 @@
         <v>4319.5</v>
       </c>
       <c r="CQ5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="CR5" t="s">
         <v>137</v>
@@ -3293,25 +3296,25 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F6" t="s">
         <v>133</v>
       </c>
       <c r="G6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I6" t="s">
         <v>36</v>
@@ -3449,13 +3452,13 @@
         <v>139</v>
       </c>
       <c r="BB6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BC6">
         <v>0</v>
       </c>
       <c r="BD6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="BE6" t="s">
         <v>137</v>
@@ -3473,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="BJ6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK6" t="s">
         <v>137</v>
@@ -3509,22 +3512,22 @@
         <v>151</v>
       </c>
       <c r="BV6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="BW6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="BX6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="BY6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB6" t="s">
         <v>158</v>
@@ -3560,7 +3563,7 @@
         <v>137</v>
       </c>
       <c r="CM6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CN6">
         <v>425.45</v>
@@ -3572,7 +3575,7 @@
         <v>422.15</v>
       </c>
       <c r="CQ6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="CR6" t="s">
         <v>137</v>
@@ -3583,25 +3586,25 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F7" t="s">
         <v>133</v>
       </c>
       <c r="G7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I7" t="s">
         <v>36</v>
@@ -3763,7 +3766,7 @@
         <v>4</v>
       </c>
       <c r="BJ7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK7" t="s">
         <v>137</v>
@@ -3799,22 +3802,22 @@
         <v>151</v>
       </c>
       <c r="BV7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="BW7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="BX7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="BY7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB7" t="s">
         <v>158</v>
@@ -3862,7 +3865,7 @@
         <v>6202.5</v>
       </c>
       <c r="CQ7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="CR7" t="s">
         <v>137</v>
@@ -3873,25 +3876,25 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C8" t="s">
         <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F8" t="s">
         <v>133</v>
       </c>
       <c r="G8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I8" t="s">
         <v>36</v>
@@ -4053,7 +4056,7 @@
         <v>3</v>
       </c>
       <c r="BJ8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK8" t="s">
         <v>137</v>
@@ -4089,22 +4092,22 @@
         <v>151</v>
       </c>
       <c r="BV8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="BW8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="BX8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="BY8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB8" t="s">
         <v>158</v>
@@ -4140,7 +4143,7 @@
         <v>137</v>
       </c>
       <c r="CM8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CN8">
         <v>1957</v>
@@ -4152,7 +4155,7 @@
         <v>1957</v>
       </c>
       <c r="CQ8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="CR8" t="s">
         <v>137</v>
@@ -4163,25 +4166,25 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
         <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F9" t="s">
         <v>133</v>
       </c>
       <c r="G9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -4343,7 +4346,7 @@
         <v>4</v>
       </c>
       <c r="BJ9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK9" t="s">
         <v>137</v>
@@ -4379,22 +4382,22 @@
         <v>151</v>
       </c>
       <c r="BV9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="BW9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="BX9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="BY9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB9" t="s">
         <v>158</v>
@@ -4442,7 +4445,7 @@
         <v>1303.2</v>
       </c>
       <c r="CQ9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="CR9" t="s">
         <v>137</v>
@@ -4453,25 +4456,25 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F10" t="s">
         <v>133</v>
       </c>
       <c r="G10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -4633,7 +4636,7 @@
         <v>3</v>
       </c>
       <c r="BJ10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK10" t="s">
         <v>137</v>
@@ -4669,22 +4672,22 @@
         <v>151</v>
       </c>
       <c r="BV10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="BW10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="BX10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="BY10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB10" t="s">
         <v>158</v>
@@ -4732,7 +4735,7 @@
         <v>721.4</v>
       </c>
       <c r="CQ10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="CR10" t="s">
         <v>137</v>
@@ -5124,16 +5127,16 @@
         <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H2" t="s">
         <v>134</v>
@@ -5271,10 +5274,10 @@
         <v>137</v>
       </c>
       <c r="BA2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BB2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BC2">
         <v>1</v>
@@ -5298,10 +5301,10 @@
         <v>4</v>
       </c>
       <c r="BJ2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="BL2" t="s">
         <v>137</v>
@@ -5334,13 +5337,13 @@
         <v>151</v>
       </c>
       <c r="BV2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="BW2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="BX2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="BY2" t="s">
         <v>155</v>
@@ -5349,7 +5352,7 @@
         <v>156</v>
       </c>
       <c r="CA2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="CB2" t="s">
         <v>158</v>
@@ -5385,7 +5388,7 @@
         <v>0.55</v>
       </c>
       <c r="CM2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CN2">
         <v>199.5</v>
@@ -5397,7 +5400,7 @@
         <v>186.53</v>
       </c>
       <c r="CQ2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="CR2" t="s">
         <v>137</v>
@@ -5414,16 +5417,16 @@
         <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H3" t="s">
         <v>134</v>
@@ -5561,10 +5564,10 @@
         <v>137</v>
       </c>
       <c r="BA3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BB3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="BC3">
         <v>1</v>
@@ -5579,7 +5582,7 @@
         <v>141</v>
       </c>
       <c r="BG3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="BH3">
         <v>10</v>
@@ -5591,13 +5594,13 @@
         <v>143</v>
       </c>
       <c r="BK3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="BL3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="BM3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="BN3" t="s">
         <v>138</v>
@@ -5606,7 +5609,7 @@
         <v>137</v>
       </c>
       <c r="BP3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="BQ3" t="s">
         <v>137</v>
@@ -5624,22 +5627,22 @@
         <v>151</v>
       </c>
       <c r="BV3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="BW3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="BX3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="BY3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BZ3" t="s">
         <v>156</v>
       </c>
       <c r="CA3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="CB3" t="s">
         <v>158</v>
@@ -5675,7 +5678,7 @@
         <v>0.1</v>
       </c>
       <c r="CM3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CN3">
         <v>9100</v>
@@ -5687,7 +5690,7 @@
         <v>8955.5</v>
       </c>
       <c r="CQ3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="CR3" t="s">
         <v>137</v>
@@ -5704,16 +5707,16 @@
         <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H4" t="s">
         <v>134</v>
@@ -5851,10 +5854,10 @@
         <v>137</v>
       </c>
       <c r="BA4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BB4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="BC4">
         <v>2</v>
@@ -5878,13 +5881,13 @@
         <v>4</v>
       </c>
       <c r="BJ4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="BL4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="BM4" t="s">
         <v>137</v>
@@ -5896,10 +5899,10 @@
         <v>137</v>
       </c>
       <c r="BP4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BQ4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BR4" t="s">
         <v>148</v>
@@ -5914,13 +5917,13 @@
         <v>151</v>
       </c>
       <c r="BV4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="BW4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BX4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="BY4" t="s">
         <v>155</v>
@@ -5929,7 +5932,7 @@
         <v>156</v>
       </c>
       <c r="CA4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="CB4" t="s">
         <v>158</v>
@@ -5977,7 +5980,7 @@
         <v>1981</v>
       </c>
       <c r="CQ4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="CR4" t="s">
         <v>137</v>
@@ -5991,19 +5994,19 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H5" t="s">
         <v>134</v>
@@ -6012,7 +6015,7 @@
         <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K5">
         <v>19.59</v>
@@ -6021,7 +6024,7 @@
         <v>19.59</v>
       </c>
       <c r="M5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N5">
         <v>16</v>
@@ -6075,7 +6078,7 @@
         <v>137</v>
       </c>
       <c r="AE5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AF5">
         <v>168.93</v>
@@ -6141,10 +6144,10 @@
         <v>137</v>
       </c>
       <c r="BA5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BB5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="BC5">
         <v>2</v>
@@ -6207,19 +6210,19 @@
         <v>152</v>
       </c>
       <c r="BW5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="BX5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="BY5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="BZ5" t="s">
         <v>156</v>
       </c>
       <c r="CA5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="CB5" t="s">
         <v>138</v>
@@ -6255,7 +6258,7 @@
         <v>0.76</v>
       </c>
       <c r="CM5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="CN5">
         <v>20</v>
@@ -6267,7 +6270,7 @@
         <v>19.01</v>
       </c>
       <c r="CQ5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="CR5" t="s">
         <v>137</v>
@@ -6278,25 +6281,25 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I6" t="s">
         <v>36</v>
@@ -6371,7 +6374,7 @@
         <v>137</v>
       </c>
       <c r="AG6">
-        <v>93.36</v>
+        <v>88.2</v>
       </c>
       <c r="AH6">
         <v>2728.17</v>
@@ -6431,10 +6434,10 @@
         <v>137</v>
       </c>
       <c r="BA6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BB6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="BC6">
         <v>1</v>
@@ -6458,7 +6461,7 @@
         <v>3</v>
       </c>
       <c r="BJ6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK6" t="s">
         <v>137</v>
@@ -6494,22 +6497,22 @@
         <v>151</v>
       </c>
       <c r="BV6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="BW6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="BX6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="BY6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB6" t="s">
         <v>158</v>
@@ -6545,7 +6548,7 @@
         <v>137</v>
       </c>
       <c r="CM6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CN6">
         <v>2903.2</v>
@@ -6557,7 +6560,7 @@
         <v>2903.2</v>
       </c>
       <c r="CQ6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="CR6" t="s">
         <v>137</v>
@@ -6568,25 +6571,25 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
         <v>175</v>
       </c>
       <c r="D7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I7" t="s">
         <v>36</v>
@@ -6721,10 +6724,10 @@
         <v>137</v>
       </c>
       <c r="BA7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BB7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="BC7">
         <v>2</v>
@@ -6748,7 +6751,7 @@
         <v>4</v>
       </c>
       <c r="BJ7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK7" t="s">
         <v>137</v>
@@ -6784,22 +6787,22 @@
         <v>151</v>
       </c>
       <c r="BV7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="BW7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="BX7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="BY7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB7" t="s">
         <v>158</v>
@@ -6835,7 +6838,7 @@
         <v>137</v>
       </c>
       <c r="CM7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="CN7">
         <v>1321</v>
@@ -6847,7 +6850,7 @@
         <v>1321</v>
       </c>
       <c r="CQ7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="CR7" t="s">
         <v>137</v>
@@ -7991,7 +7994,7 @@
         <v>195.78</v>
       </c>
       <c r="AG3">
-        <v>184.69</v>
+        <v>179.52</v>
       </c>
       <c r="AH3">
         <v>597.22</v>
@@ -8281,7 +8284,7 @@
         <v>176.28</v>
       </c>
       <c r="AG4">
-        <v>176.87</v>
+        <v>171.71</v>
       </c>
       <c r="AH4">
         <v>84.5</v>
@@ -8344,7 +8347,7 @@
         <v>139</v>
       </c>
       <c r="BB4" t="s">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="BC4">
         <v>0</v>
@@ -8356,7 +8359,7 @@
         <v>140</v>
       </c>
       <c r="BF4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="BG4" t="s">
         <v>142</v>
@@ -8374,10 +8377,10 @@
         <v>166</v>
       </c>
       <c r="BL4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="BM4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="BN4" t="s">
         <v>138</v>
@@ -8404,22 +8407,22 @@
         <v>167</v>
       </c>
       <c r="BV4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="BW4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="BX4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BY4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BZ4" t="s">
         <v>156</v>
       </c>
       <c r="CA4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="CB4" t="s">
         <v>158</v>
@@ -8443,7 +8446,7 @@
         <v>1.87</v>
       </c>
       <c r="CI4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="CJ4">
         <v>1.91</v>
@@ -8455,7 +8458,7 @@
         <v>2.77</v>
       </c>
       <c r="CM4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CN4">
         <v>85.99</v>
@@ -8467,7 +8470,7 @@
         <v>84.44</v>
       </c>
       <c r="CQ4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="CR4" t="s">
         <v>137</v>
@@ -8484,16 +8487,16 @@
         <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F5" t="s">
         <v>133</v>
       </c>
       <c r="G5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H5" t="s">
         <v>134</v>
@@ -8646,7 +8649,7 @@
         <v>137</v>
       </c>
       <c r="BF5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="BG5" t="s">
         <v>142</v>
@@ -8658,10 +8661,10 @@
         <v>1</v>
       </c>
       <c r="BJ5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="BL5" t="s">
         <v>137</v>
@@ -8694,13 +8697,13 @@
         <v>151</v>
       </c>
       <c r="BV5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="BW5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BX5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="BY5" t="s">
         <v>155</v>
@@ -8709,7 +8712,7 @@
         <v>156</v>
       </c>
       <c r="CA5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="CB5" t="s">
         <v>158</v>
@@ -8757,7 +8760,7 @@
         <v>4319.5</v>
       </c>
       <c r="CQ5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="CR5" t="s">
         <v>137</v>
@@ -8768,25 +8771,25 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F6" t="s">
         <v>133</v>
       </c>
       <c r="G6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I6" t="s">
         <v>36</v>
@@ -8924,13 +8927,13 @@
         <v>139</v>
       </c>
       <c r="BB6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BC6">
         <v>0</v>
       </c>
       <c r="BD6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="BE6" t="s">
         <v>137</v>
@@ -8948,7 +8951,7 @@
         <v>5</v>
       </c>
       <c r="BJ6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK6" t="s">
         <v>137</v>
@@ -8984,22 +8987,22 @@
         <v>151</v>
       </c>
       <c r="BV6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="BW6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="BX6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="BY6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB6" t="s">
         <v>158</v>
@@ -9035,7 +9038,7 @@
         <v>137</v>
       </c>
       <c r="CM6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CN6">
         <v>425.45</v>
@@ -9047,7 +9050,7 @@
         <v>422.15</v>
       </c>
       <c r="CQ6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="CR6" t="s">
         <v>137</v>
@@ -9058,25 +9061,25 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F7" t="s">
         <v>133</v>
       </c>
       <c r="G7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I7" t="s">
         <v>36</v>
@@ -9238,7 +9241,7 @@
         <v>4</v>
       </c>
       <c r="BJ7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK7" t="s">
         <v>137</v>
@@ -9274,22 +9277,22 @@
         <v>151</v>
       </c>
       <c r="BV7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="BW7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="BX7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="BY7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB7" t="s">
         <v>158</v>
@@ -9337,7 +9340,7 @@
         <v>6202.5</v>
       </c>
       <c r="CQ7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="CR7" t="s">
         <v>137</v>
@@ -9348,25 +9351,25 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C8" t="s">
         <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F8" t="s">
         <v>133</v>
       </c>
       <c r="G8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I8" t="s">
         <v>36</v>
@@ -9528,7 +9531,7 @@
         <v>3</v>
       </c>
       <c r="BJ8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK8" t="s">
         <v>137</v>
@@ -9564,22 +9567,22 @@
         <v>151</v>
       </c>
       <c r="BV8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="BW8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="BX8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="BY8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB8" t="s">
         <v>158</v>
@@ -9615,7 +9618,7 @@
         <v>137</v>
       </c>
       <c r="CM8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CN8">
         <v>1957</v>
@@ -9627,7 +9630,7 @@
         <v>1957</v>
       </c>
       <c r="CQ8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="CR8" t="s">
         <v>137</v>
@@ -9638,25 +9641,25 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
         <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F9" t="s">
         <v>133</v>
       </c>
       <c r="G9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -9818,7 +9821,7 @@
         <v>4</v>
       </c>
       <c r="BJ9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK9" t="s">
         <v>137</v>
@@ -9854,22 +9857,22 @@
         <v>151</v>
       </c>
       <c r="BV9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="BW9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="BX9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="BY9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB9" t="s">
         <v>158</v>
@@ -9917,7 +9920,7 @@
         <v>1303.2</v>
       </c>
       <c r="CQ9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="CR9" t="s">
         <v>137</v>
@@ -9928,25 +9931,25 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F10" t="s">
         <v>133</v>
       </c>
       <c r="G10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -10108,7 +10111,7 @@
         <v>3</v>
       </c>
       <c r="BJ10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK10" t="s">
         <v>137</v>
@@ -10144,22 +10147,22 @@
         <v>151</v>
       </c>
       <c r="BV10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="BW10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="BX10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="BY10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB10" t="s">
         <v>158</v>
@@ -10207,7 +10210,7 @@
         <v>721.4</v>
       </c>
       <c r="CQ10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="CR10" t="s">
         <v>137</v>
@@ -10224,16 +10227,16 @@
         <v>130</v>
       </c>
       <c r="D11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H11" t="s">
         <v>134</v>
@@ -10371,10 +10374,10 @@
         <v>137</v>
       </c>
       <c r="BA11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BB11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BC11">
         <v>1</v>
@@ -10398,10 +10401,10 @@
         <v>4</v>
       </c>
       <c r="BJ11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="BL11" t="s">
         <v>137</v>
@@ -10434,13 +10437,13 @@
         <v>151</v>
       </c>
       <c r="BV11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="BW11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="BX11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="BY11" t="s">
         <v>155</v>
@@ -10449,7 +10452,7 @@
         <v>156</v>
       </c>
       <c r="CA11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="CB11" t="s">
         <v>158</v>
@@ -10485,7 +10488,7 @@
         <v>0.55</v>
       </c>
       <c r="CM11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CN11">
         <v>199.5</v>
@@ -10497,7 +10500,7 @@
         <v>186.53</v>
       </c>
       <c r="CQ11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="CR11" t="s">
         <v>137</v>
@@ -10514,16 +10517,16 @@
         <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H12" t="s">
         <v>134</v>
@@ -10661,10 +10664,10 @@
         <v>137</v>
       </c>
       <c r="BA12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BB12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="BC12">
         <v>1</v>
@@ -10679,7 +10682,7 @@
         <v>141</v>
       </c>
       <c r="BG12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="BH12">
         <v>10</v>
@@ -10691,13 +10694,13 @@
         <v>143</v>
       </c>
       <c r="BK12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="BL12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="BM12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="BN12" t="s">
         <v>138</v>
@@ -10706,7 +10709,7 @@
         <v>137</v>
       </c>
       <c r="BP12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="BQ12" t="s">
         <v>137</v>
@@ -10724,22 +10727,22 @@
         <v>151</v>
       </c>
       <c r="BV12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="BW12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="BX12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="BY12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BZ12" t="s">
         <v>156</v>
       </c>
       <c r="CA12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="CB12" t="s">
         <v>158</v>
@@ -10775,7 +10778,7 @@
         <v>0.1</v>
       </c>
       <c r="CM12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CN12">
         <v>9100</v>
@@ -10787,7 +10790,7 @@
         <v>8955.5</v>
       </c>
       <c r="CQ12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="CR12" t="s">
         <v>137</v>
@@ -10804,16 +10807,16 @@
         <v>130</v>
       </c>
       <c r="D13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H13" t="s">
         <v>134</v>
@@ -10951,10 +10954,10 @@
         <v>137</v>
       </c>
       <c r="BA13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BB13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="BC13">
         <v>2</v>
@@ -10978,13 +10981,13 @@
         <v>4</v>
       </c>
       <c r="BJ13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="BL13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="BM13" t="s">
         <v>137</v>
@@ -10996,10 +10999,10 @@
         <v>137</v>
       </c>
       <c r="BP13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BQ13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BR13" t="s">
         <v>148</v>
@@ -11014,13 +11017,13 @@
         <v>151</v>
       </c>
       <c r="BV13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="BW13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BX13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="BY13" t="s">
         <v>155</v>
@@ -11029,7 +11032,7 @@
         <v>156</v>
       </c>
       <c r="CA13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="CB13" t="s">
         <v>158</v>
@@ -11077,7 +11080,7 @@
         <v>1981</v>
       </c>
       <c r="CQ13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="CR13" t="s">
         <v>137</v>
@@ -11091,19 +11094,19 @@
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H14" t="s">
         <v>134</v>
@@ -11112,7 +11115,7 @@
         <v>36</v>
       </c>
       <c r="J14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K14">
         <v>19.59</v>
@@ -11121,7 +11124,7 @@
         <v>19.59</v>
       </c>
       <c r="M14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N14">
         <v>16</v>
@@ -11175,7 +11178,7 @@
         <v>137</v>
       </c>
       <c r="AE14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AF14">
         <v>168.93</v>
@@ -11241,10 +11244,10 @@
         <v>137</v>
       </c>
       <c r="BA14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BB14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="BC14">
         <v>2</v>
@@ -11307,19 +11310,19 @@
         <v>152</v>
       </c>
       <c r="BW14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="BX14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="BY14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="BZ14" t="s">
         <v>156</v>
       </c>
       <c r="CA14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="CB14" t="s">
         <v>138</v>
@@ -11355,7 +11358,7 @@
         <v>0.76</v>
       </c>
       <c r="CM14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="CN14">
         <v>20</v>
@@ -11367,7 +11370,7 @@
         <v>19.01</v>
       </c>
       <c r="CQ14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="CR14" t="s">
         <v>137</v>
@@ -11384,16 +11387,16 @@
         <v>175</v>
       </c>
       <c r="D15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H15" t="s">
         <v>137</v>
@@ -11411,7 +11414,7 @@
         <v>137</v>
       </c>
       <c r="M15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N15" t="s">
         <v>137</v>
@@ -11465,7 +11468,7 @@
         <v>137</v>
       </c>
       <c r="AE15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF15" t="s">
         <v>137</v>
@@ -11546,7 +11549,7 @@
         <v>137</v>
       </c>
       <c r="BF15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="BG15" t="s">
         <v>142</v>
@@ -11558,7 +11561,7 @@
         <v>4</v>
       </c>
       <c r="BJ15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="BK15" t="s">
         <v>137</v>
@@ -11585,31 +11588,31 @@
         <v>148</v>
       </c>
       <c r="BS15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BT15" t="s">
         <v>150</v>
       </c>
       <c r="BU15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BV15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BW15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BX15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BY15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CB15" t="s">
         <v>158</v>
@@ -11657,7 +11660,7 @@
         <v>4305.8</v>
       </c>
       <c r="CQ15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="CR15" t="s">
         <v>137</v>
@@ -11674,16 +11677,16 @@
         <v>175</v>
       </c>
       <c r="D16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F16" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H16" t="s">
         <v>137</v>
@@ -11701,7 +11704,7 @@
         <v>137</v>
       </c>
       <c r="M16" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N16" t="s">
         <v>137</v>
@@ -11755,7 +11758,7 @@
         <v>137</v>
       </c>
       <c r="AE16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF16" t="s">
         <v>137</v>
@@ -11848,7 +11851,7 @@
         <v>4</v>
       </c>
       <c r="BJ16" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="BK16" t="s">
         <v>137</v>
@@ -11875,31 +11878,31 @@
         <v>148</v>
       </c>
       <c r="BS16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="BT16" t="s">
         <v>150</v>
       </c>
       <c r="BU16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BV16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="BW16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="BX16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="BY16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA16" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CB16" t="s">
         <v>158</v>
@@ -11923,7 +11926,7 @@
         <v>0</v>
       </c>
       <c r="CI16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="CJ16">
         <v>1.19</v>
@@ -11947,7 +11950,7 @@
         <v>1012.9</v>
       </c>
       <c r="CQ16" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="CR16" t="s">
         <v>137</v>
@@ -11961,19 +11964,19 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D17" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E17" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H17" t="s">
         <v>137</v>
@@ -11991,7 +11994,7 @@
         <v>137</v>
       </c>
       <c r="M17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N17" t="s">
         <v>137</v>
@@ -12045,7 +12048,7 @@
         <v>137</v>
       </c>
       <c r="AE17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF17" t="s">
         <v>137</v>
@@ -12129,7 +12132,7 @@
         <v>141</v>
       </c>
       <c r="BG17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="BH17">
         <v>12</v>
@@ -12138,7 +12141,7 @@
         <v>2</v>
       </c>
       <c r="BJ17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK17" t="s">
         <v>137</v>
@@ -12171,25 +12174,25 @@
         <v>150</v>
       </c>
       <c r="BU17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BV17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="BW17" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="BX17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="BY17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CB17" t="s">
         <v>158</v>
@@ -12237,7 +12240,7 @@
         <v>688.05</v>
       </c>
       <c r="CQ17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="CR17" t="s">
         <v>137</v>
@@ -12248,25 +12251,25 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I18" t="s">
         <v>36</v>
@@ -12341,7 +12344,7 @@
         <v>137</v>
       </c>
       <c r="AG18">
-        <v>93.36</v>
+        <v>88.2</v>
       </c>
       <c r="AH18">
         <v>2728.17</v>
@@ -12401,10 +12404,10 @@
         <v>137</v>
       </c>
       <c r="BA18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BB18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="BC18">
         <v>1</v>
@@ -12428,7 +12431,7 @@
         <v>3</v>
       </c>
       <c r="BJ18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK18" t="s">
         <v>137</v>
@@ -12464,22 +12467,22 @@
         <v>151</v>
       </c>
       <c r="BV18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="BW18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="BX18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="BY18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB18" t="s">
         <v>158</v>
@@ -12515,7 +12518,7 @@
         <v>137</v>
       </c>
       <c r="CM18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CN18">
         <v>2903.2</v>
@@ -12527,7 +12530,7 @@
         <v>2903.2</v>
       </c>
       <c r="CQ18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="CR18" t="s">
         <v>137</v>
@@ -12538,25 +12541,25 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" t="s">
         <v>175</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I19" t="s">
         <v>36</v>
@@ -12691,10 +12694,10 @@
         <v>137</v>
       </c>
       <c r="BA19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BB19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="BC19">
         <v>2</v>
@@ -12718,7 +12721,7 @@
         <v>4</v>
       </c>
       <c r="BJ19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BK19" t="s">
         <v>137</v>
@@ -12754,22 +12757,22 @@
         <v>151</v>
       </c>
       <c r="BV19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="BW19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="BX19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="BY19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BZ19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CA19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="CB19" t="s">
         <v>158</v>
@@ -12805,7 +12808,7 @@
         <v>137</v>
       </c>
       <c r="CM19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="CN19">
         <v>1321</v>
@@ -12817,7 +12820,7 @@
         <v>1321</v>
       </c>
       <c r="CQ19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="CR19" t="s">
         <v>137</v>
@@ -12858,57 +12861,57 @@
         <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>91</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
@@ -12920,7 +12923,7 @@
         <v>142</v>
       </c>
       <c r="F2">
-        <v>222.31</v>
+        <v>217.14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -12938,7 +12941,7 @@
         <v>2.72</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="M2" t="s">
         <v>164</v>
@@ -12953,18 +12956,18 @@
         <v>832.09</v>
       </c>
       <c r="Q2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D3" t="s">
         <v>134</v>
@@ -12973,7 +12976,7 @@
         <v>142</v>
       </c>
       <c r="F3">
-        <v>198.67</v>
+        <v>203.83</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -13006,18 +13009,18 @@
         <v>8764.5</v>
       </c>
       <c r="Q3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D4" t="s">
         <v>135</v>
@@ -13026,7 +13029,7 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>193.73</v>
+        <v>188.56</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -13044,10 +13047,10 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="M4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -13059,15 +13062,15 @@
         <v>10013.51</v>
       </c>
       <c r="Q4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
@@ -13100,7 +13103,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -13112,15 +13115,15 @@
         <v>501.1</v>
       </c>
       <c r="Q5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C6" t="s">
         <v>28</v>
@@ -13165,18 +13168,18 @@
         <v>22.35</v>
       </c>
       <c r="Q6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B7" t="s">
+        <v>333</v>
+      </c>
+      <c r="C7" t="s">
         <v>326</v>
-      </c>
-      <c r="B7" t="s">
-        <v>332</v>
-      </c>
-      <c r="C7" t="s">
-        <v>325</v>
       </c>
       <c r="D7" t="s">
         <v>135</v>
@@ -13218,15 +13221,15 @@
         <v>801</v>
       </c>
       <c r="Q7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
@@ -13271,18 +13274,18 @@
         <v>176.13</v>
       </c>
       <c r="Q8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C9" t="s">
         <v>326</v>
-      </c>
-      <c r="B9" t="s">
-        <v>334</v>
-      </c>
-      <c r="C9" t="s">
-        <v>325</v>
       </c>
       <c r="D9" t="s">
         <v>135</v>
@@ -13324,15 +13327,15 @@
         <v>794.6</v>
       </c>
       <c r="Q9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
@@ -13377,7 +13380,7 @@
         <v>15848.82</v>
       </c>
       <c r="Q10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -13409,78 +13412,78 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="Q1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B2" t="s">
         <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E2" t="s">
         <v>134</v>
       </c>
       <c r="G2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I2" t="s">
         <v>142</v>
@@ -13507,18 +13510,18 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B3" t="s">
         <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -13527,10 +13530,10 @@
         <v>134</v>
       </c>
       <c r="G3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I3" t="s">
         <v>142</v>
@@ -13557,12 +13560,12 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B4" t="s">
         <v>134</v>
@@ -13571,16 +13574,16 @@
         <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E4" t="s">
         <v>134</v>
       </c>
       <c r="G4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I4" t="s">
         <v>142</v>
@@ -13607,12 +13610,12 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B5" t="s">
         <v>134</v>
@@ -13630,10 +13633,10 @@
         <v>622.5499877929688</v>
       </c>
       <c r="G5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I5" t="s">
         <v>142</v>
@@ -13660,33 +13663,33 @@
         <v>1</v>
       </c>
       <c r="Q5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F6">
         <v>637.9000244140625</v>
       </c>
       <c r="G6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I6" t="s">
         <v>142</v>
@@ -13713,33 +13716,33 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F7">
         <v>814.9000244140625</v>
       </c>
       <c r="G7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I7" t="s">
         <v>142</v>
@@ -13766,33 +13769,33 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>352</v>
+      </c>
+      <c r="B8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" t="s">
         <v>351</v>
-      </c>
-      <c r="B8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" t="s">
-        <v>350</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F8">
         <v>637.9000244140625</v>
       </c>
       <c r="G8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I8" t="s">
         <v>142</v>
@@ -13819,33 +13822,33 @@
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F9">
         <v>814.9000244140625</v>
       </c>
       <c r="G9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I9" t="s">
         <v>142</v>
@@ -13872,18 +13875,18 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B10" t="s">
         <v>134</v>
       </c>
       <c r="C10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
@@ -13895,10 +13898,10 @@
         <v>863.5</v>
       </c>
       <c r="G10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I10" t="s">
         <v>142</v>
@@ -13925,21 +13928,21 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B11" t="s">
         <v>134</v>
       </c>
       <c r="C11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E11" t="s">
         <v>134</v>
@@ -13948,10 +13951,10 @@
         <v>8782.5</v>
       </c>
       <c r="G11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I11" t="s">
         <v>142</v>
@@ -13978,18 +13981,18 @@
         <v>1</v>
       </c>
       <c r="Q11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B12" t="s">
         <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D12" t="s">
         <v>28</v>
@@ -14001,10 +14004,10 @@
         <v>16326</v>
       </c>
       <c r="G12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I12" t="s">
         <v>142</v>
@@ -14031,18 +14034,18 @@
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B13" t="s">
         <v>134</v>
       </c>
       <c r="C13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D13" t="s">
         <v>28</v>
@@ -14054,10 +14057,10 @@
         <v>5024</v>
       </c>
       <c r="G13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I13" t="s">
         <v>142</v>
@@ -14084,18 +14087,18 @@
         <v>1</v>
       </c>
       <c r="Q13" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B14" t="s">
         <v>134</v>
       </c>
       <c r="C14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
@@ -14107,10 +14110,10 @@
         <v>5024</v>
       </c>
       <c r="G14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I14" t="s">
         <v>142</v>
@@ -14137,21 +14140,21 @@
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B15" t="s">
         <v>135</v>
       </c>
       <c r="C15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E15" t="s">
         <v>135</v>
@@ -14160,16 +14163,16 @@
         <v>10166</v>
       </c>
       <c r="G15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I15" t="s">
         <v>142</v>
       </c>
       <c r="J15">
-        <v>193.73</v>
+        <v>188.56</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -14184,24 +14187,24 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="P15">
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B16" t="s">
         <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
@@ -14213,10 +14216,10 @@
         <v>527.9000244140625</v>
       </c>
       <c r="G16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H16" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I16" t="s">
         <v>142</v>
@@ -14243,18 +14246,18 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B17" t="s">
         <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
@@ -14266,10 +14269,10 @@
         <v>23.700000762939453</v>
       </c>
       <c r="G17" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H17" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I17" t="s">
         <v>142</v>
@@ -14296,21 +14299,21 @@
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B18" t="s">
         <v>135</v>
       </c>
       <c r="C18" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D18" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E18" t="s">
         <v>135</v>
@@ -14319,10 +14322,10 @@
         <v>813.2000122070312</v>
       </c>
       <c r="G18" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H18" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I18" t="s">
         <v>142</v>
@@ -14349,18 +14352,18 @@
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B19" t="s">
         <v>134</v>
       </c>
       <c r="C19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D19" t="s">
         <v>28</v>
@@ -14372,10 +14375,10 @@
         <v>179.52000427246094</v>
       </c>
       <c r="G19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I19" t="s">
         <v>142</v>
@@ -14402,21 +14405,21 @@
         <v>1</v>
       </c>
       <c r="Q19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B20" t="s">
         <v>135</v>
       </c>
       <c r="C20" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D20" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E20" t="s">
         <v>135</v>
@@ -14425,10 +14428,10 @@
         <v>806.7000122070312</v>
       </c>
       <c r="G20" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H20" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I20" t="s">
         <v>142</v>
@@ -14455,7 +14458,7 @@
         <v>1</v>
       </c>
       <c r="Q20" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -14479,30 +14482,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -14514,7 +14517,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T11:35:10.635Z</t>
+    <t>2026-07-14T11:40:18.285Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1088,7 +1088,7 @@
     <t>2026-07-14T10:56:37.603Z</t>
   </si>
   <si>
-    <t>2026-07-14T11:35:09.136Z</t>
+    <t>2026-07-14T11:40:17.173Z</t>
   </si>
   <si>
     <t>Date</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="372">
   <si>
     <t>Metric</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-14T11:40:18.285Z</t>
+    <t>2026-07-15T03:17:37.496Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -551,9 +551,6 @@
     <t>NIVABUPA</t>
   </si>
   <si>
-    <t>official NSE delivery distribution</t>
-  </si>
-  <si>
     <t>Momentum continuation buy</t>
   </si>
   <si>
@@ -632,7 +629,7 @@
     <t>2026-07-09</t>
   </si>
   <si>
-    <t>GTF confirms less than 2R room</t>
+    <t>daily RS21 below zero setup grade WATCH GTF confirms less than 2R room</t>
   </si>
   <si>
     <t>2026-07-14T03:32:23.269Z: SANGAMIND; Optional rotation cancelled before selling SIS: Rotation requires 2 distinct valid ENTRY closes; candidate has 0.</t>
@@ -1013,6 +1010,93 @@
     <t>Rotation requires 2 distinct valid ENTRY closes; candidate has 1.</t>
   </si>
   <si>
+    <t>SCHNEIDER</t>
+  </si>
+  <si>
+    <t>Capital Goods</t>
+  </si>
+  <si>
+    <t>RASRESOR</t>
+  </si>
+  <si>
+    <t>UCIL</t>
+  </si>
+  <si>
+    <t>INDIGRID</t>
+  </si>
+  <si>
+    <t>LMW</t>
+  </si>
+  <si>
+    <t>FINEORG</t>
+  </si>
+  <si>
+    <t>KVFORGE</t>
+  </si>
+  <si>
+    <t>HARSHA</t>
+  </si>
+  <si>
+    <t>Evaluated At</t>
+  </si>
+  <si>
+    <t>Closing Date</t>
+  </si>
+  <si>
+    <t>First Signal</t>
+  </si>
+  <si>
+    <t>First Signal Close</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>Disposition</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>2026-07-14T03:32:23.269Z</t>
+  </si>
+  <si>
+    <t>REMOVED</t>
+  </si>
+  <si>
+    <t>EXPIRED</t>
+  </si>
+  <si>
+    <t>Latest completed-candle status is WATCH, not ENTRY. Current setup grade WATCH no longer passes the selected trade-quality filter.</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>ROTATION_DEFERRED</t>
+  </si>
+  <si>
+    <t>2026-07-14T08:05:39.733Z</t>
+  </si>
+  <si>
+    <t>SGFIN</t>
+  </si>
+  <si>
+    <t>KIMS</t>
+  </si>
+  <si>
+    <t>2026-07-14T09:43:28.265Z</t>
+  </si>
+  <si>
+    <t>2026-07-14T10:19:14.585Z</t>
+  </si>
+  <si>
+    <t>2026-07-14T10:56:37.603Z</t>
+  </si>
+  <si>
+    <t>2026-07-14T11:40:17.173Z</t>
+  </si>
+  <si>
     <t>APCOTEXIND</t>
   </si>
   <si>
@@ -1022,73 +1106,7 @@
     <t>ASTERDM</t>
   </si>
   <si>
-    <t>INDIGRID</t>
-  </si>
-  <si>
-    <t>KIMS</t>
-  </si>
-  <si>
-    <t>LMW</t>
-  </si>
-  <si>
-    <t>Evaluated At</t>
-  </si>
-  <si>
-    <t>Closing Date</t>
-  </si>
-  <si>
-    <t>First Signal</t>
-  </si>
-  <si>
-    <t>First Signal Close</t>
-  </si>
-  <si>
-    <t>Outcome</t>
-  </si>
-  <si>
-    <t>Disposition</t>
-  </si>
-  <si>
-    <t>Reason</t>
-  </si>
-  <si>
-    <t>2026-07-14T03:32:23.269Z</t>
-  </si>
-  <si>
-    <t>REMOVED</t>
-  </si>
-  <si>
-    <t>EXPIRED</t>
-  </si>
-  <si>
-    <t>Latest completed-candle status is WATCH, not ENTRY. Current setup grade WATCH no longer passes the selected trade-quality filter.</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>ROTATION_DEFERRED</t>
-  </si>
-  <si>
-    <t>2026-07-14T08:05:39.733Z</t>
-  </si>
-  <si>
-    <t>SGFIN</t>
-  </si>
-  <si>
-    <t>2026-07-14T09:43:28.265Z</t>
-  </si>
-  <si>
-    <t>2026-07-14T10:19:14.585Z</t>
-  </si>
-  <si>
-    <t>FINEORG</t>
-  </si>
-  <si>
-    <t>2026-07-14T10:56:37.603Z</t>
-  </si>
-  <si>
-    <t>2026-07-14T11:40:17.173Z</t>
+    <t>2026-07-15T03:17:36.413Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -1135,10 +1153,10 @@
       <color rgb="FFFFFFFF"/>
     </font>
     <font>
-      <color rgb="FFB4232A"/>
+      <color rgb="FF147A52"/>
     </font>
     <font>
-      <color rgb="FF147A52"/>
+      <color rgb="FFB4232A"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1546,7 +1564,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>997143.87</v>
+        <v>1006788.73</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1610,7 +1628,7 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>0.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1626,7 +1644,7 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>42847.66</v>
+        <v>42391.87</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1634,7 +1652,7 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1650,7 +1668,7 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1690,7 +1708,7 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>-2233.4</v>
+        <v>2304.9</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1698,7 +1716,7 @@
         <v>25</v>
       </c>
       <c r="B23">
-        <v>-0.87</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2184,16 +2202,16 @@
         <v>58004</v>
       </c>
       <c r="R2">
-        <v>55678.4</v>
+        <v>58150.2</v>
       </c>
       <c r="S2">
-        <v>818.8</v>
+        <v>855.15</v>
       </c>
       <c r="T2" s="2">
-        <v>-2325.6</v>
+        <v>146.2</v>
       </c>
       <c r="U2">
-        <v>-4.01</v>
+        <v>0.25</v>
       </c>
       <c r="V2" t="s">
         <v>137</v>
@@ -2229,7 +2247,7 @@
         <v>191.09</v>
       </c>
       <c r="AG2">
-        <v>191.73</v>
+        <v>193.59</v>
       </c>
       <c r="AH2">
         <v>805.6</v>
@@ -2241,7 +2259,7 @@
         <v>3223.2</v>
       </c>
       <c r="AK2">
-        <v>-0.72</v>
+        <v>0.05</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -2479,7 +2497,7 @@
       <c r="S3">
         <v>624.95</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T3" s="3">
         <v>-2710.4</v>
       </c>
       <c r="U3">
@@ -2519,7 +2537,7 @@
         <v>195.78</v>
       </c>
       <c r="AG3">
-        <v>179.52</v>
+        <v>184.32</v>
       </c>
       <c r="AH3">
         <v>597.22</v>
@@ -2764,16 +2782,16 @@
         <v>442.45</v>
       </c>
       <c r="R4">
-        <v>430.85</v>
+        <v>440.45</v>
       </c>
       <c r="S4">
-        <v>86.17</v>
-      </c>
-      <c r="T4" s="2">
-        <v>-11.6</v>
+        <v>88.09</v>
+      </c>
+      <c r="T4" s="3">
+        <v>-2</v>
       </c>
       <c r="U4">
-        <v>-2.62</v>
+        <v>-0.45</v>
       </c>
       <c r="V4" t="s">
         <v>137</v>
@@ -2809,7 +2827,7 @@
         <v>176.28</v>
       </c>
       <c r="AG4">
-        <v>171.71</v>
+        <v>176.28</v>
       </c>
       <c r="AH4">
         <v>84.5</v>
@@ -2821,7 +2839,7 @@
         <v>19.95</v>
       </c>
       <c r="AK4">
-        <v>-0.58</v>
+        <v>-0.1</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2872,7 +2890,7 @@
         <v>139</v>
       </c>
       <c r="BB4" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="BC4">
         <v>0</v>
@@ -2884,7 +2902,7 @@
         <v>140</v>
       </c>
       <c r="BF4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="BG4" t="s">
         <v>142</v>
@@ -2902,10 +2920,10 @@
         <v>166</v>
       </c>
       <c r="BL4" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM4" t="s">
         <v>179</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>180</v>
       </c>
       <c r="BN4" t="s">
         <v>138</v>
@@ -2932,22 +2950,22 @@
         <v>167</v>
       </c>
       <c r="BV4" t="s">
+        <v>180</v>
+      </c>
+      <c r="BW4" t="s">
         <v>181</v>
       </c>
-      <c r="BW4" t="s">
+      <c r="BX4" t="s">
         <v>182</v>
       </c>
-      <c r="BX4" t="s">
+      <c r="BY4" t="s">
         <v>183</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>184</v>
       </c>
       <c r="BZ4" t="s">
         <v>156</v>
       </c>
       <c r="CA4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CB4" t="s">
         <v>158</v>
@@ -2971,7 +2989,7 @@
         <v>1.87</v>
       </c>
       <c r="CI4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="CJ4">
         <v>1.91</v>
@@ -2983,7 +3001,7 @@
         <v>2.77</v>
       </c>
       <c r="CM4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="CN4">
         <v>85.99</v>
@@ -2995,7 +3013,7 @@
         <v>84.44</v>
       </c>
       <c r="CQ4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="CR4" t="s">
         <v>137</v>
@@ -3012,16 +3030,16 @@
         <v>130</v>
       </c>
       <c r="D5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" t="s">
         <v>189</v>
-      </c>
-      <c r="E5" t="s">
-        <v>190</v>
       </c>
       <c r="F5" t="s">
         <v>133</v>
       </c>
       <c r="G5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H5" t="s">
         <v>134</v>
@@ -3054,16 +3072,16 @@
         <v>97281.8</v>
       </c>
       <c r="R5">
-        <v>96619.6</v>
+        <v>97776.8</v>
       </c>
       <c r="S5">
-        <v>4391.8</v>
+        <v>4444.4</v>
       </c>
       <c r="T5" s="2">
-        <v>-662.2</v>
+        <v>495</v>
       </c>
       <c r="U5">
-        <v>-0.68</v>
+        <v>0.51</v>
       </c>
       <c r="V5" t="s">
         <v>137</v>
@@ -3099,7 +3117,7 @@
         <v>167.02</v>
       </c>
       <c r="AG5">
-        <v>133.61</v>
+        <v>133.99</v>
       </c>
       <c r="AH5">
         <v>4319.5</v>
@@ -3111,7 +3129,7 @@
         <v>2252.8</v>
       </c>
       <c r="AK5">
-        <v>-0.29</v>
+        <v>0.22</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -3174,7 +3192,7 @@
         <v>137</v>
       </c>
       <c r="BF5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BG5" t="s">
         <v>142</v>
@@ -3186,10 +3204,10 @@
         <v>1</v>
       </c>
       <c r="BJ5" t="s">
+        <v>192</v>
+      </c>
+      <c r="BK5" t="s">
         <v>193</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>194</v>
       </c>
       <c r="BL5" t="s">
         <v>137</v>
@@ -3222,13 +3240,13 @@
         <v>151</v>
       </c>
       <c r="BV5" t="s">
+        <v>194</v>
+      </c>
+      <c r="BW5" t="s">
         <v>195</v>
       </c>
-      <c r="BW5" t="s">
+      <c r="BX5" t="s">
         <v>196</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>197</v>
       </c>
       <c r="BY5" t="s">
         <v>155</v>
@@ -3237,7 +3255,7 @@
         <v>156</v>
       </c>
       <c r="CA5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="CB5" t="s">
         <v>158</v>
@@ -3285,7 +3303,7 @@
         <v>4319.5</v>
       </c>
       <c r="CQ5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="CR5" t="s">
         <v>137</v>
@@ -3296,25 +3314,25 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" t="s">
         <v>200</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>201</v>
       </c>
-      <c r="D6" t="s">
-        <v>202</v>
-      </c>
       <c r="E6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F6" t="s">
         <v>133</v>
       </c>
       <c r="G6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I6" t="s">
         <v>36</v>
@@ -3344,16 +3362,16 @@
         <v>49823.7</v>
       </c>
       <c r="R6">
-        <v>49544.4</v>
+        <v>49538.7</v>
       </c>
       <c r="S6">
-        <v>434.6</v>
-      </c>
-      <c r="T6" s="2">
-        <v>-279.3</v>
+        <v>434.55</v>
+      </c>
+      <c r="T6" s="3">
+        <v>-285</v>
       </c>
       <c r="U6">
-        <v>-0.56</v>
+        <v>-0.57</v>
       </c>
       <c r="V6" t="s">
         <v>137</v>
@@ -3389,7 +3407,7 @@
         <v>137</v>
       </c>
       <c r="AG6">
-        <v>166.7</v>
+        <v>88.84</v>
       </c>
       <c r="AH6">
         <v>402.78</v>
@@ -3452,13 +3470,13 @@
         <v>139</v>
       </c>
       <c r="BB6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BC6">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="s">
         <v>204</v>
-      </c>
-      <c r="BC6">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>205</v>
       </c>
       <c r="BE6" t="s">
         <v>137</v>
@@ -3476,7 +3494,7 @@
         <v>5</v>
       </c>
       <c r="BJ6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK6" t="s">
         <v>137</v>
@@ -3512,22 +3530,22 @@
         <v>151</v>
       </c>
       <c r="BV6" t="s">
+        <v>205</v>
+      </c>
+      <c r="BW6" t="s">
         <v>206</v>
       </c>
-      <c r="BW6" t="s">
+      <c r="BX6" t="s">
         <v>207</v>
       </c>
-      <c r="BX6" t="s">
+      <c r="BY6" t="s">
         <v>208</v>
       </c>
-      <c r="BY6" t="s">
+      <c r="BZ6" t="s">
         <v>209</v>
       </c>
-      <c r="BZ6" t="s">
+      <c r="CA6" t="s">
         <v>210</v>
-      </c>
-      <c r="CA6" t="s">
-        <v>211</v>
       </c>
       <c r="CB6" t="s">
         <v>158</v>
@@ -3563,7 +3581,7 @@
         <v>137</v>
       </c>
       <c r="CM6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="CN6">
         <v>425.45</v>
@@ -3575,7 +3593,7 @@
         <v>422.15</v>
       </c>
       <c r="CQ6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="CR6" t="s">
         <v>137</v>
@@ -3586,25 +3604,25 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C7" t="s">
         <v>200</v>
       </c>
-      <c r="C7" t="s">
-        <v>201</v>
-      </c>
       <c r="D7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F7" t="s">
         <v>133</v>
       </c>
       <c r="G7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I7" t="s">
         <v>36</v>
@@ -3634,16 +3652,16 @@
         <v>99322.5</v>
       </c>
       <c r="R7">
-        <v>103777.5</v>
+        <v>103005</v>
       </c>
       <c r="S7">
-        <v>6918.5</v>
-      </c>
-      <c r="T7" s="3">
-        <v>4455</v>
+        <v>6867</v>
+      </c>
+      <c r="T7" s="2">
+        <v>3682.5</v>
       </c>
       <c r="U7">
-        <v>4.49</v>
+        <v>3.71</v>
       </c>
       <c r="V7" t="s">
         <v>137</v>
@@ -3679,7 +3697,7 @@
         <v>137</v>
       </c>
       <c r="AG7">
-        <v>198.78</v>
+        <v>193.14</v>
       </c>
       <c r="AH7">
         <v>6083.5</v>
@@ -3691,7 +3709,7 @@
         <v>8070</v>
       </c>
       <c r="AK7">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3766,7 +3784,7 @@
         <v>4</v>
       </c>
       <c r="BJ7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK7" t="s">
         <v>137</v>
@@ -3802,22 +3820,22 @@
         <v>151</v>
       </c>
       <c r="BV7" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW7" t="s">
         <v>214</v>
       </c>
-      <c r="BW7" t="s">
+      <c r="BX7" t="s">
         <v>215</v>
       </c>
-      <c r="BX7" t="s">
-        <v>216</v>
-      </c>
       <c r="BY7" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ7" t="s">
         <v>209</v>
       </c>
-      <c r="BZ7" t="s">
+      <c r="CA7" t="s">
         <v>210</v>
-      </c>
-      <c r="CA7" t="s">
-        <v>211</v>
       </c>
       <c r="CB7" t="s">
         <v>158</v>
@@ -3865,7 +3883,7 @@
         <v>6202.5</v>
       </c>
       <c r="CQ7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="CR7" t="s">
         <v>137</v>
@@ -3876,25 +3894,25 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
         <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F8" t="s">
         <v>133</v>
       </c>
       <c r="G8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I8" t="s">
         <v>36</v>
@@ -3924,16 +3942,16 @@
         <v>97794.2</v>
       </c>
       <c r="R8">
-        <v>98352.8</v>
+        <v>99852.2</v>
       </c>
       <c r="S8">
-        <v>2007.2</v>
-      </c>
-      <c r="T8" s="3">
-        <v>558.6</v>
+        <v>2037.8</v>
+      </c>
+      <c r="T8" s="2">
+        <v>2058</v>
       </c>
       <c r="U8">
-        <v>0.57</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="s">
         <v>137</v>
@@ -3969,7 +3987,7 @@
         <v>137</v>
       </c>
       <c r="AG8">
-        <v>181.22</v>
+        <v>182.64</v>
       </c>
       <c r="AH8">
         <v>1842.85</v>
@@ -3981,7 +3999,7 @@
         <v>7494.55</v>
       </c>
       <c r="AK8">
-        <v>0.07</v>
+        <v>0.27</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4056,7 +4074,7 @@
         <v>3</v>
       </c>
       <c r="BJ8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK8" t="s">
         <v>137</v>
@@ -4092,22 +4110,22 @@
         <v>151</v>
       </c>
       <c r="BV8" t="s">
+        <v>218</v>
+      </c>
+      <c r="BW8" t="s">
         <v>219</v>
       </c>
-      <c r="BW8" t="s">
+      <c r="BX8" t="s">
         <v>220</v>
       </c>
-      <c r="BX8" t="s">
-        <v>221</v>
-      </c>
       <c r="BY8" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ8" t="s">
         <v>209</v>
       </c>
-      <c r="BZ8" t="s">
+      <c r="CA8" t="s">
         <v>210</v>
-      </c>
-      <c r="CA8" t="s">
-        <v>211</v>
       </c>
       <c r="CB8" t="s">
         <v>158</v>
@@ -4143,7 +4161,7 @@
         <v>137</v>
       </c>
       <c r="CM8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="CN8">
         <v>1957</v>
@@ -4155,7 +4173,7 @@
         <v>1957</v>
       </c>
       <c r="CQ8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="CR8" t="s">
         <v>137</v>
@@ -4166,25 +4184,25 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C9" t="s">
         <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F9" t="s">
         <v>133</v>
       </c>
       <c r="G9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -4219,7 +4237,7 @@
       <c r="S9">
         <v>1382.6</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="2">
         <v>646.1</v>
       </c>
       <c r="U9">
@@ -4259,7 +4277,7 @@
         <v>137</v>
       </c>
       <c r="AG9">
-        <v>183.38</v>
+        <v>183.02</v>
       </c>
       <c r="AH9">
         <v>1285.88</v>
@@ -4346,7 +4364,7 @@
         <v>4</v>
       </c>
       <c r="BJ9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK9" t="s">
         <v>137</v>
@@ -4382,22 +4400,22 @@
         <v>151</v>
       </c>
       <c r="BV9" t="s">
+        <v>223</v>
+      </c>
+      <c r="BW9" t="s">
         <v>224</v>
       </c>
-      <c r="BW9" t="s">
+      <c r="BX9" t="s">
         <v>225</v>
       </c>
-      <c r="BX9" t="s">
-        <v>226</v>
-      </c>
       <c r="BY9" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ9" t="s">
         <v>209</v>
       </c>
-      <c r="BZ9" t="s">
+      <c r="CA9" t="s">
         <v>210</v>
-      </c>
-      <c r="CA9" t="s">
-        <v>211</v>
       </c>
       <c r="CB9" t="s">
         <v>158</v>
@@ -4445,7 +4463,7 @@
         <v>1303.2</v>
       </c>
       <c r="CQ9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="CR9" t="s">
         <v>137</v>
@@ -4456,25 +4474,25 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" t="s">
         <v>200</v>
       </c>
-      <c r="C10" t="s">
-        <v>201</v>
-      </c>
       <c r="D10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F10" t="s">
         <v>133</v>
       </c>
       <c r="G10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -4504,16 +4522,16 @@
         <v>96509</v>
       </c>
       <c r="R10">
-        <v>94605</v>
+        <v>94783.5</v>
       </c>
       <c r="S10">
-        <v>795</v>
-      </c>
-      <c r="T10" s="2">
-        <v>-1904</v>
+        <v>796.5</v>
+      </c>
+      <c r="T10" s="3">
+        <v>-1725.5</v>
       </c>
       <c r="U10">
-        <v>-1.97</v>
+        <v>-1.79</v>
       </c>
       <c r="V10" t="s">
         <v>137</v>
@@ -4549,7 +4567,7 @@
         <v>137</v>
       </c>
       <c r="AG10">
-        <v>187.21</v>
+        <v>186.42</v>
       </c>
       <c r="AH10">
         <v>771.79</v>
@@ -4561,7 +4579,7 @@
         <v>4665.99</v>
       </c>
       <c r="AK10">
-        <v>-0.41</v>
+        <v>-0.37</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -4636,7 +4654,7 @@
         <v>3</v>
       </c>
       <c r="BJ10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK10" t="s">
         <v>137</v>
@@ -4672,22 +4690,22 @@
         <v>151</v>
       </c>
       <c r="BV10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BW10" t="s">
+        <v>228</v>
+      </c>
+      <c r="BX10" t="s">
         <v>229</v>
       </c>
-      <c r="BX10" t="s">
-        <v>230</v>
-      </c>
       <c r="BY10" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ10" t="s">
         <v>209</v>
       </c>
-      <c r="BZ10" t="s">
+      <c r="CA10" t="s">
         <v>210</v>
-      </c>
-      <c r="CA10" t="s">
-        <v>211</v>
       </c>
       <c r="CB10" t="s">
         <v>158</v>
@@ -4735,7 +4753,7 @@
         <v>721.4</v>
       </c>
       <c r="CQ10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CR10" t="s">
         <v>137</v>
@@ -5127,16 +5145,16 @@
         <v>130</v>
       </c>
       <c r="D2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E2" t="s">
         <v>232</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>233</v>
       </c>
-      <c r="F2" t="s">
-        <v>234</v>
-      </c>
       <c r="G2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H2" t="s">
         <v>134</v>
@@ -5174,7 +5192,7 @@
       <c r="S2">
         <v>205.46</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="3">
         <v>-2488.05</v>
       </c>
       <c r="U2">
@@ -5214,7 +5232,7 @@
         <v>179.24</v>
       </c>
       <c r="AG2">
-        <v>99.14</v>
+        <v>98.72</v>
       </c>
       <c r="AH2">
         <v>196.45</v>
@@ -5274,10 +5292,10 @@
         <v>137</v>
       </c>
       <c r="BA2" t="s">
+        <v>234</v>
+      </c>
+      <c r="BB2" t="s">
         <v>235</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>236</v>
       </c>
       <c r="BC2">
         <v>1</v>
@@ -5301,10 +5319,10 @@
         <v>4</v>
       </c>
       <c r="BJ2" t="s">
+        <v>192</v>
+      </c>
+      <c r="BK2" t="s">
         <v>193</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>194</v>
       </c>
       <c r="BL2" t="s">
         <v>137</v>
@@ -5337,13 +5355,13 @@
         <v>151</v>
       </c>
       <c r="BV2" t="s">
+        <v>236</v>
+      </c>
+      <c r="BW2" t="s">
         <v>237</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BX2" t="s">
         <v>238</v>
-      </c>
-      <c r="BX2" t="s">
-        <v>239</v>
       </c>
       <c r="BY2" t="s">
         <v>155</v>
@@ -5352,7 +5370,7 @@
         <v>156</v>
       </c>
       <c r="CA2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="CB2" t="s">
         <v>158</v>
@@ -5388,7 +5406,7 @@
         <v>0.55</v>
       </c>
       <c r="CM2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="CN2">
         <v>199.5</v>
@@ -5400,7 +5418,7 @@
         <v>186.53</v>
       </c>
       <c r="CQ2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="CR2" t="s">
         <v>137</v>
@@ -5417,16 +5435,16 @@
         <v>130</v>
       </c>
       <c r="D3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" t="s">
         <v>241</v>
       </c>
-      <c r="E3" t="s">
-        <v>242</v>
-      </c>
       <c r="F3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H3" t="s">
         <v>134</v>
@@ -5459,16 +5477,16 @@
         <v>92840</v>
       </c>
       <c r="R3">
-        <v>91580</v>
+        <v>93330</v>
       </c>
       <c r="S3">
-        <v>9158</v>
+        <v>9333</v>
       </c>
       <c r="T3" s="2">
-        <v>-1260</v>
+        <v>490</v>
       </c>
       <c r="U3">
-        <v>-1.36</v>
+        <v>0.53</v>
       </c>
       <c r="V3" t="s">
         <v>137</v>
@@ -5504,7 +5522,7 @@
         <v>131.92</v>
       </c>
       <c r="AG3">
-        <v>101.32</v>
+        <v>189.74</v>
       </c>
       <c r="AH3">
         <v>8955.5</v>
@@ -5564,13 +5582,13 @@
         <v>137</v>
       </c>
       <c r="BA3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BB3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BC3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="s">
         <v>137</v>
@@ -5582,7 +5600,7 @@
         <v>141</v>
       </c>
       <c r="BG3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="BH3">
         <v>10</v>
@@ -5594,13 +5612,13 @@
         <v>143</v>
       </c>
       <c r="BK3" t="s">
+        <v>244</v>
+      </c>
+      <c r="BL3" t="s">
         <v>245</v>
       </c>
-      <c r="BL3" t="s">
+      <c r="BM3" t="s">
         <v>246</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>247</v>
       </c>
       <c r="BN3" t="s">
         <v>138</v>
@@ -5609,7 +5627,7 @@
         <v>137</v>
       </c>
       <c r="BP3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="BQ3" t="s">
         <v>137</v>
@@ -5627,22 +5645,22 @@
         <v>151</v>
       </c>
       <c r="BV3" t="s">
+        <v>248</v>
+      </c>
+      <c r="BW3" t="s">
         <v>249</v>
       </c>
-      <c r="BW3" t="s">
+      <c r="BX3" t="s">
         <v>250</v>
       </c>
-      <c r="BX3" t="s">
-        <v>251</v>
-      </c>
       <c r="BY3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BZ3" t="s">
         <v>156</v>
       </c>
       <c r="CA3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="CB3" t="s">
         <v>158</v>
@@ -5678,7 +5696,7 @@
         <v>0.1</v>
       </c>
       <c r="CM3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="CN3">
         <v>9100</v>
@@ -5690,7 +5708,7 @@
         <v>8955.5</v>
       </c>
       <c r="CQ3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="CR3" t="s">
         <v>137</v>
@@ -5707,16 +5725,16 @@
         <v>130</v>
       </c>
       <c r="D4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E4" t="s">
         <v>254</v>
       </c>
-      <c r="E4" t="s">
-        <v>255</v>
-      </c>
       <c r="F4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H4" t="s">
         <v>134</v>
@@ -5749,16 +5767,16 @@
         <v>26626.6</v>
       </c>
       <c r="R4">
-        <v>26014.3</v>
+        <v>26445.9</v>
       </c>
       <c r="S4">
-        <v>2001.1</v>
-      </c>
-      <c r="T4" s="2">
-        <v>-612.3</v>
+        <v>2034.3</v>
+      </c>
+      <c r="T4" s="3">
+        <v>-180.7</v>
       </c>
       <c r="U4">
-        <v>-2.3</v>
+        <v>-0.68</v>
       </c>
       <c r="V4" t="s">
         <v>137</v>
@@ -5794,13 +5812,13 @@
         <v>170.76</v>
       </c>
       <c r="AG4">
-        <v>73.69</v>
+        <v>96.97</v>
       </c>
       <c r="AH4">
         <v>1974.43</v>
       </c>
       <c r="AI4">
-        <v>1971.08</v>
+        <v>2003.79</v>
       </c>
       <c r="AJ4">
         <v>3614.73</v>
@@ -5854,10 +5872,10 @@
         <v>137</v>
       </c>
       <c r="BA4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BB4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="BC4">
         <v>2</v>
@@ -5881,13 +5899,13 @@
         <v>4</v>
       </c>
       <c r="BJ4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK4" t="s">
+        <v>256</v>
+      </c>
+      <c r="BL4" t="s">
         <v>257</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>258</v>
       </c>
       <c r="BM4" t="s">
         <v>137</v>
@@ -5899,10 +5917,10 @@
         <v>137</v>
       </c>
       <c r="BP4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BQ4" t="s">
         <v>259</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>260</v>
       </c>
       <c r="BR4" t="s">
         <v>148</v>
@@ -5917,13 +5935,13 @@
         <v>151</v>
       </c>
       <c r="BV4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BW4" t="s">
+        <v>260</v>
+      </c>
+      <c r="BX4" t="s">
         <v>261</v>
-      </c>
-      <c r="BX4" t="s">
-        <v>262</v>
       </c>
       <c r="BY4" t="s">
         <v>155</v>
@@ -5932,7 +5950,7 @@
         <v>156</v>
       </c>
       <c r="CA4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="CB4" t="s">
         <v>158</v>
@@ -5980,7 +5998,7 @@
         <v>1981</v>
       </c>
       <c r="CQ4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="CR4" t="s">
         <v>137</v>
@@ -5994,19 +6012,19 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D5" t="s">
         <v>264</v>
       </c>
-      <c r="D5" t="s">
-        <v>265</v>
-      </c>
       <c r="E5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H5" t="s">
         <v>134</v>
@@ -6015,7 +6033,7 @@
         <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K5">
         <v>19.59</v>
@@ -6024,7 +6042,7 @@
         <v>19.59</v>
       </c>
       <c r="M5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N5">
         <v>16</v>
@@ -6039,16 +6057,16 @@
         <v>313.44</v>
       </c>
       <c r="R5">
-        <v>297.44</v>
+        <v>318.4</v>
       </c>
       <c r="S5">
-        <v>18.59</v>
+        <v>19.9</v>
       </c>
       <c r="T5" s="2">
-        <v>-16</v>
+        <v>4.96</v>
       </c>
       <c r="U5">
-        <v>-5.1</v>
+        <v>1.58</v>
       </c>
       <c r="V5" t="s">
         <v>137</v>
@@ -6078,19 +6096,19 @@
         <v>137</v>
       </c>
       <c r="AE5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AF5">
         <v>168.93</v>
       </c>
       <c r="AG5">
-        <v>56.58</v>
+        <v>64.43</v>
       </c>
       <c r="AH5">
         <v>19.01</v>
       </c>
       <c r="AI5">
-        <v>17.1</v>
+        <v>19.01</v>
       </c>
       <c r="AJ5">
         <v>17.98</v>
@@ -6144,10 +6162,10 @@
         <v>137</v>
       </c>
       <c r="BA5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BB5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="BC5">
         <v>2</v>
@@ -6210,19 +6228,19 @@
         <v>152</v>
       </c>
       <c r="BW5" t="s">
+        <v>269</v>
+      </c>
+      <c r="BX5" t="s">
         <v>270</v>
       </c>
-      <c r="BX5" t="s">
+      <c r="BY5" t="s">
         <v>271</v>
-      </c>
-      <c r="BY5" t="s">
-        <v>272</v>
       </c>
       <c r="BZ5" t="s">
         <v>156</v>
       </c>
       <c r="CA5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CB5" t="s">
         <v>138</v>
@@ -6258,7 +6276,7 @@
         <v>0.76</v>
       </c>
       <c r="CM5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="CN5">
         <v>20</v>
@@ -6270,7 +6288,7 @@
         <v>19.01</v>
       </c>
       <c r="CQ5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="CR5" t="s">
         <v>137</v>
@@ -6281,25 +6299,25 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" t="s">
         <v>200</v>
       </c>
-      <c r="C6" t="s">
-        <v>201</v>
-      </c>
       <c r="D6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I6" t="s">
         <v>36</v>
@@ -6329,16 +6347,16 @@
         <v>98538</v>
       </c>
       <c r="R6">
-        <v>98396.1</v>
+        <v>101300.1</v>
       </c>
       <c r="S6">
-        <v>2981.7</v>
+        <v>3069.7</v>
       </c>
       <c r="T6" s="2">
-        <v>-141.9</v>
+        <v>2762.1</v>
       </c>
       <c r="U6">
-        <v>-0.14</v>
+        <v>2.8</v>
       </c>
       <c r="V6" t="s">
         <v>137</v>
@@ -6374,7 +6392,7 @@
         <v>137</v>
       </c>
       <c r="AG6">
-        <v>88.2</v>
+        <v>170.48</v>
       </c>
       <c r="AH6">
         <v>2728.17</v>
@@ -6434,13 +6452,13 @@
         <v>137</v>
       </c>
       <c r="BA6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BB6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BC6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="s">
         <v>137</v>
@@ -6461,7 +6479,7 @@
         <v>3</v>
       </c>
       <c r="BJ6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK6" t="s">
         <v>137</v>
@@ -6497,22 +6515,22 @@
         <v>151</v>
       </c>
       <c r="BV6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BW6" t="s">
+        <v>276</v>
+      </c>
+      <c r="BX6" t="s">
         <v>277</v>
       </c>
-      <c r="BX6" t="s">
-        <v>278</v>
-      </c>
       <c r="BY6" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ6" t="s">
         <v>209</v>
       </c>
-      <c r="BZ6" t="s">
+      <c r="CA6" t="s">
         <v>210</v>
-      </c>
-      <c r="CA6" t="s">
-        <v>211</v>
       </c>
       <c r="CB6" t="s">
         <v>158</v>
@@ -6548,7 +6566,7 @@
         <v>137</v>
       </c>
       <c r="CM6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="CN6">
         <v>2903.2</v>
@@ -6560,7 +6578,7 @@
         <v>2903.2</v>
       </c>
       <c r="CQ6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="CR6" t="s">
         <v>137</v>
@@ -6571,25 +6589,25 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C7" t="s">
         <v>175</v>
       </c>
       <c r="D7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I7" t="s">
         <v>36</v>
@@ -6624,7 +6642,7 @@
       <c r="S7">
         <v>1299.2</v>
       </c>
-      <c r="T7" s="2">
+      <c r="T7" s="3">
         <v>-1931.4</v>
       </c>
       <c r="U7">
@@ -6664,7 +6682,7 @@
         <v>137</v>
       </c>
       <c r="AG7">
-        <v>90.23</v>
+        <v>89.92</v>
       </c>
       <c r="AH7">
         <v>1251.2</v>
@@ -6724,10 +6742,10 @@
         <v>137</v>
       </c>
       <c r="BA7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BB7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="BC7">
         <v>2</v>
@@ -6751,7 +6769,7 @@
         <v>4</v>
       </c>
       <c r="BJ7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK7" t="s">
         <v>137</v>
@@ -6787,22 +6805,22 @@
         <v>151</v>
       </c>
       <c r="BV7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BW7" t="s">
+        <v>280</v>
+      </c>
+      <c r="BX7" t="s">
         <v>281</v>
       </c>
-      <c r="BX7" t="s">
-        <v>282</v>
-      </c>
       <c r="BY7" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ7" t="s">
         <v>209</v>
       </c>
-      <c r="BZ7" t="s">
+      <c r="CA7" t="s">
         <v>210</v>
-      </c>
-      <c r="CA7" t="s">
-        <v>211</v>
       </c>
       <c r="CB7" t="s">
         <v>158</v>
@@ -6838,7 +6856,7 @@
         <v>137</v>
       </c>
       <c r="CM7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="CN7">
         <v>1321</v>
@@ -6850,7 +6868,7 @@
         <v>1321</v>
       </c>
       <c r="CQ7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="CR7" t="s">
         <v>137</v>
@@ -7659,16 +7677,16 @@
         <v>58004</v>
       </c>
       <c r="R2">
-        <v>55678.4</v>
+        <v>58150.2</v>
       </c>
       <c r="S2">
-        <v>818.8</v>
+        <v>855.15</v>
       </c>
       <c r="T2" s="2">
-        <v>-2325.6</v>
+        <v>146.2</v>
       </c>
       <c r="U2">
-        <v>-4.01</v>
+        <v>0.25</v>
       </c>
       <c r="V2" t="s">
         <v>137</v>
@@ -7704,7 +7722,7 @@
         <v>191.09</v>
       </c>
       <c r="AG2">
-        <v>191.73</v>
+        <v>193.59</v>
       </c>
       <c r="AH2">
         <v>805.6</v>
@@ -7716,7 +7734,7 @@
         <v>3223.2</v>
       </c>
       <c r="AK2">
-        <v>-0.72</v>
+        <v>0.05</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -7954,7 +7972,7 @@
       <c r="S3">
         <v>624.95</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T3" s="3">
         <v>-2710.4</v>
       </c>
       <c r="U3">
@@ -7994,7 +8012,7 @@
         <v>195.78</v>
       </c>
       <c r="AG3">
-        <v>179.52</v>
+        <v>184.32</v>
       </c>
       <c r="AH3">
         <v>597.22</v>
@@ -8239,16 +8257,16 @@
         <v>442.45</v>
       </c>
       <c r="R4">
-        <v>430.85</v>
+        <v>440.45</v>
       </c>
       <c r="S4">
-        <v>86.17</v>
-      </c>
-      <c r="T4" s="2">
-        <v>-11.6</v>
+        <v>88.09</v>
+      </c>
+      <c r="T4" s="3">
+        <v>-2</v>
       </c>
       <c r="U4">
-        <v>-2.62</v>
+        <v>-0.45</v>
       </c>
       <c r="V4" t="s">
         <v>137</v>
@@ -8284,7 +8302,7 @@
         <v>176.28</v>
       </c>
       <c r="AG4">
-        <v>171.71</v>
+        <v>176.28</v>
       </c>
       <c r="AH4">
         <v>84.5</v>
@@ -8296,7 +8314,7 @@
         <v>19.95</v>
       </c>
       <c r="AK4">
-        <v>-0.58</v>
+        <v>-0.1</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -8347,7 +8365,7 @@
         <v>139</v>
       </c>
       <c r="BB4" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="BC4">
         <v>0</v>
@@ -8359,7 +8377,7 @@
         <v>140</v>
       </c>
       <c r="BF4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="BG4" t="s">
         <v>142</v>
@@ -8377,10 +8395,10 @@
         <v>166</v>
       </c>
       <c r="BL4" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM4" t="s">
         <v>179</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>180</v>
       </c>
       <c r="BN4" t="s">
         <v>138</v>
@@ -8407,22 +8425,22 @@
         <v>167</v>
       </c>
       <c r="BV4" t="s">
+        <v>180</v>
+      </c>
+      <c r="BW4" t="s">
         <v>181</v>
       </c>
-      <c r="BW4" t="s">
+      <c r="BX4" t="s">
         <v>182</v>
       </c>
-      <c r="BX4" t="s">
+      <c r="BY4" t="s">
         <v>183</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>184</v>
       </c>
       <c r="BZ4" t="s">
         <v>156</v>
       </c>
       <c r="CA4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CB4" t="s">
         <v>158</v>
@@ -8446,7 +8464,7 @@
         <v>1.87</v>
       </c>
       <c r="CI4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="CJ4">
         <v>1.91</v>
@@ -8458,7 +8476,7 @@
         <v>2.77</v>
       </c>
       <c r="CM4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="CN4">
         <v>85.99</v>
@@ -8470,7 +8488,7 @@
         <v>84.44</v>
       </c>
       <c r="CQ4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="CR4" t="s">
         <v>137</v>
@@ -8487,16 +8505,16 @@
         <v>130</v>
       </c>
       <c r="D5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" t="s">
         <v>189</v>
-      </c>
-      <c r="E5" t="s">
-        <v>190</v>
       </c>
       <c r="F5" t="s">
         <v>133</v>
       </c>
       <c r="G5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H5" t="s">
         <v>134</v>
@@ -8529,16 +8547,16 @@
         <v>97281.8</v>
       </c>
       <c r="R5">
-        <v>96619.6</v>
+        <v>97776.8</v>
       </c>
       <c r="S5">
-        <v>4391.8</v>
+        <v>4444.4</v>
       </c>
       <c r="T5" s="2">
-        <v>-662.2</v>
+        <v>495</v>
       </c>
       <c r="U5">
-        <v>-0.68</v>
+        <v>0.51</v>
       </c>
       <c r="V5" t="s">
         <v>137</v>
@@ -8574,7 +8592,7 @@
         <v>167.02</v>
       </c>
       <c r="AG5">
-        <v>133.61</v>
+        <v>133.99</v>
       </c>
       <c r="AH5">
         <v>4319.5</v>
@@ -8586,7 +8604,7 @@
         <v>2252.8</v>
       </c>
       <c r="AK5">
-        <v>-0.29</v>
+        <v>0.22</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -8649,7 +8667,7 @@
         <v>137</v>
       </c>
       <c r="BF5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BG5" t="s">
         <v>142</v>
@@ -8661,10 +8679,10 @@
         <v>1</v>
       </c>
       <c r="BJ5" t="s">
+        <v>192</v>
+      </c>
+      <c r="BK5" t="s">
         <v>193</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>194</v>
       </c>
       <c r="BL5" t="s">
         <v>137</v>
@@ -8697,13 +8715,13 @@
         <v>151</v>
       </c>
       <c r="BV5" t="s">
+        <v>194</v>
+      </c>
+      <c r="BW5" t="s">
         <v>195</v>
       </c>
-      <c r="BW5" t="s">
+      <c r="BX5" t="s">
         <v>196</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>197</v>
       </c>
       <c r="BY5" t="s">
         <v>155</v>
@@ -8712,7 +8730,7 @@
         <v>156</v>
       </c>
       <c r="CA5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="CB5" t="s">
         <v>158</v>
@@ -8760,7 +8778,7 @@
         <v>4319.5</v>
       </c>
       <c r="CQ5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="CR5" t="s">
         <v>137</v>
@@ -8771,25 +8789,25 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" t="s">
         <v>200</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>201</v>
       </c>
-      <c r="D6" t="s">
-        <v>202</v>
-      </c>
       <c r="E6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F6" t="s">
         <v>133</v>
       </c>
       <c r="G6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I6" t="s">
         <v>36</v>
@@ -8819,16 +8837,16 @@
         <v>49823.7</v>
       </c>
       <c r="R6">
-        <v>49544.4</v>
+        <v>49538.7</v>
       </c>
       <c r="S6">
-        <v>434.6</v>
-      </c>
-      <c r="T6" s="2">
-        <v>-279.3</v>
+        <v>434.55</v>
+      </c>
+      <c r="T6" s="3">
+        <v>-285</v>
       </c>
       <c r="U6">
-        <v>-0.56</v>
+        <v>-0.57</v>
       </c>
       <c r="V6" t="s">
         <v>137</v>
@@ -8864,7 +8882,7 @@
         <v>137</v>
       </c>
       <c r="AG6">
-        <v>166.7</v>
+        <v>88.84</v>
       </c>
       <c r="AH6">
         <v>402.78</v>
@@ -8927,13 +8945,13 @@
         <v>139</v>
       </c>
       <c r="BB6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BC6">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="s">
         <v>204</v>
-      </c>
-      <c r="BC6">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>205</v>
       </c>
       <c r="BE6" t="s">
         <v>137</v>
@@ -8951,7 +8969,7 @@
         <v>5</v>
       </c>
       <c r="BJ6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK6" t="s">
         <v>137</v>
@@ -8987,22 +9005,22 @@
         <v>151</v>
       </c>
       <c r="BV6" t="s">
+        <v>205</v>
+      </c>
+      <c r="BW6" t="s">
         <v>206</v>
       </c>
-      <c r="BW6" t="s">
+      <c r="BX6" t="s">
         <v>207</v>
       </c>
-      <c r="BX6" t="s">
+      <c r="BY6" t="s">
         <v>208</v>
       </c>
-      <c r="BY6" t="s">
+      <c r="BZ6" t="s">
         <v>209</v>
       </c>
-      <c r="BZ6" t="s">
+      <c r="CA6" t="s">
         <v>210</v>
-      </c>
-      <c r="CA6" t="s">
-        <v>211</v>
       </c>
       <c r="CB6" t="s">
         <v>158</v>
@@ -9038,7 +9056,7 @@
         <v>137</v>
       </c>
       <c r="CM6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="CN6">
         <v>425.45</v>
@@ -9050,7 +9068,7 @@
         <v>422.15</v>
       </c>
       <c r="CQ6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="CR6" t="s">
         <v>137</v>
@@ -9061,25 +9079,25 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C7" t="s">
         <v>200</v>
       </c>
-      <c r="C7" t="s">
-        <v>201</v>
-      </c>
       <c r="D7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F7" t="s">
         <v>133</v>
       </c>
       <c r="G7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I7" t="s">
         <v>36</v>
@@ -9109,16 +9127,16 @@
         <v>99322.5</v>
       </c>
       <c r="R7">
-        <v>103777.5</v>
+        <v>103005</v>
       </c>
       <c r="S7">
-        <v>6918.5</v>
-      </c>
-      <c r="T7" s="3">
-        <v>4455</v>
+        <v>6867</v>
+      </c>
+      <c r="T7" s="2">
+        <v>3682.5</v>
       </c>
       <c r="U7">
-        <v>4.49</v>
+        <v>3.71</v>
       </c>
       <c r="V7" t="s">
         <v>137</v>
@@ -9154,7 +9172,7 @@
         <v>137</v>
       </c>
       <c r="AG7">
-        <v>198.78</v>
+        <v>193.14</v>
       </c>
       <c r="AH7">
         <v>6083.5</v>
@@ -9166,7 +9184,7 @@
         <v>8070</v>
       </c>
       <c r="AK7">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -9241,7 +9259,7 @@
         <v>4</v>
       </c>
       <c r="BJ7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK7" t="s">
         <v>137</v>
@@ -9277,22 +9295,22 @@
         <v>151</v>
       </c>
       <c r="BV7" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW7" t="s">
         <v>214</v>
       </c>
-      <c r="BW7" t="s">
+      <c r="BX7" t="s">
         <v>215</v>
       </c>
-      <c r="BX7" t="s">
-        <v>216</v>
-      </c>
       <c r="BY7" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ7" t="s">
         <v>209</v>
       </c>
-      <c r="BZ7" t="s">
+      <c r="CA7" t="s">
         <v>210</v>
-      </c>
-      <c r="CA7" t="s">
-        <v>211</v>
       </c>
       <c r="CB7" t="s">
         <v>158</v>
@@ -9340,7 +9358,7 @@
         <v>6202.5</v>
       </c>
       <c r="CQ7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="CR7" t="s">
         <v>137</v>
@@ -9351,25 +9369,25 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
         <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F8" t="s">
         <v>133</v>
       </c>
       <c r="G8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I8" t="s">
         <v>36</v>
@@ -9399,16 +9417,16 @@
         <v>97794.2</v>
       </c>
       <c r="R8">
-        <v>98352.8</v>
+        <v>99852.2</v>
       </c>
       <c r="S8">
-        <v>2007.2</v>
-      </c>
-      <c r="T8" s="3">
-        <v>558.6</v>
+        <v>2037.8</v>
+      </c>
+      <c r="T8" s="2">
+        <v>2058</v>
       </c>
       <c r="U8">
-        <v>0.57</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="s">
         <v>137</v>
@@ -9444,7 +9462,7 @@
         <v>137</v>
       </c>
       <c r="AG8">
-        <v>181.22</v>
+        <v>182.64</v>
       </c>
       <c r="AH8">
         <v>1842.85</v>
@@ -9456,7 +9474,7 @@
         <v>7494.55</v>
       </c>
       <c r="AK8">
-        <v>0.07</v>
+        <v>0.27</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -9531,7 +9549,7 @@
         <v>3</v>
       </c>
       <c r="BJ8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK8" t="s">
         <v>137</v>
@@ -9567,22 +9585,22 @@
         <v>151</v>
       </c>
       <c r="BV8" t="s">
+        <v>218</v>
+      </c>
+      <c r="BW8" t="s">
         <v>219</v>
       </c>
-      <c r="BW8" t="s">
+      <c r="BX8" t="s">
         <v>220</v>
       </c>
-      <c r="BX8" t="s">
-        <v>221</v>
-      </c>
       <c r="BY8" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ8" t="s">
         <v>209</v>
       </c>
-      <c r="BZ8" t="s">
+      <c r="CA8" t="s">
         <v>210</v>
-      </c>
-      <c r="CA8" t="s">
-        <v>211</v>
       </c>
       <c r="CB8" t="s">
         <v>158</v>
@@ -9618,7 +9636,7 @@
         <v>137</v>
       </c>
       <c r="CM8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="CN8">
         <v>1957</v>
@@ -9630,7 +9648,7 @@
         <v>1957</v>
       </c>
       <c r="CQ8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="CR8" t="s">
         <v>137</v>
@@ -9641,25 +9659,25 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C9" t="s">
         <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F9" t="s">
         <v>133</v>
       </c>
       <c r="G9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -9694,7 +9712,7 @@
       <c r="S9">
         <v>1382.6</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="2">
         <v>646.1</v>
       </c>
       <c r="U9">
@@ -9734,7 +9752,7 @@
         <v>137</v>
       </c>
       <c r="AG9">
-        <v>183.38</v>
+        <v>183.02</v>
       </c>
       <c r="AH9">
         <v>1285.88</v>
@@ -9821,7 +9839,7 @@
         <v>4</v>
       </c>
       <c r="BJ9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK9" t="s">
         <v>137</v>
@@ -9857,22 +9875,22 @@
         <v>151</v>
       </c>
       <c r="BV9" t="s">
+        <v>223</v>
+      </c>
+      <c r="BW9" t="s">
         <v>224</v>
       </c>
-      <c r="BW9" t="s">
+      <c r="BX9" t="s">
         <v>225</v>
       </c>
-      <c r="BX9" t="s">
-        <v>226</v>
-      </c>
       <c r="BY9" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ9" t="s">
         <v>209</v>
       </c>
-      <c r="BZ9" t="s">
+      <c r="CA9" t="s">
         <v>210</v>
-      </c>
-      <c r="CA9" t="s">
-        <v>211</v>
       </c>
       <c r="CB9" t="s">
         <v>158</v>
@@ -9920,7 +9938,7 @@
         <v>1303.2</v>
       </c>
       <c r="CQ9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="CR9" t="s">
         <v>137</v>
@@ -9931,25 +9949,25 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" t="s">
         <v>200</v>
       </c>
-      <c r="C10" t="s">
-        <v>201</v>
-      </c>
       <c r="D10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F10" t="s">
         <v>133</v>
       </c>
       <c r="G10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -9979,16 +9997,16 @@
         <v>96509</v>
       </c>
       <c r="R10">
-        <v>94605</v>
+        <v>94783.5</v>
       </c>
       <c r="S10">
-        <v>795</v>
-      </c>
-      <c r="T10" s="2">
-        <v>-1904</v>
+        <v>796.5</v>
+      </c>
+      <c r="T10" s="3">
+        <v>-1725.5</v>
       </c>
       <c r="U10">
-        <v>-1.97</v>
+        <v>-1.79</v>
       </c>
       <c r="V10" t="s">
         <v>137</v>
@@ -10024,7 +10042,7 @@
         <v>137</v>
       </c>
       <c r="AG10">
-        <v>187.21</v>
+        <v>186.42</v>
       </c>
       <c r="AH10">
         <v>771.79</v>
@@ -10036,7 +10054,7 @@
         <v>4665.99</v>
       </c>
       <c r="AK10">
-        <v>-0.41</v>
+        <v>-0.37</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -10111,7 +10129,7 @@
         <v>3</v>
       </c>
       <c r="BJ10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK10" t="s">
         <v>137</v>
@@ -10147,22 +10165,22 @@
         <v>151</v>
       </c>
       <c r="BV10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BW10" t="s">
+        <v>228</v>
+      </c>
+      <c r="BX10" t="s">
         <v>229</v>
       </c>
-      <c r="BX10" t="s">
-        <v>230</v>
-      </c>
       <c r="BY10" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ10" t="s">
         <v>209</v>
       </c>
-      <c r="BZ10" t="s">
+      <c r="CA10" t="s">
         <v>210</v>
-      </c>
-      <c r="CA10" t="s">
-        <v>211</v>
       </c>
       <c r="CB10" t="s">
         <v>158</v>
@@ -10210,7 +10228,7 @@
         <v>721.4</v>
       </c>
       <c r="CQ10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CR10" t="s">
         <v>137</v>
@@ -10227,16 +10245,16 @@
         <v>130</v>
       </c>
       <c r="D11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" t="s">
         <v>232</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>233</v>
       </c>
-      <c r="F11" t="s">
-        <v>234</v>
-      </c>
       <c r="G11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H11" t="s">
         <v>134</v>
@@ -10274,7 +10292,7 @@
       <c r="S11">
         <v>205.46</v>
       </c>
-      <c r="T11" s="2">
+      <c r="T11" s="3">
         <v>-2488.05</v>
       </c>
       <c r="U11">
@@ -10314,7 +10332,7 @@
         <v>179.24</v>
       </c>
       <c r="AG11">
-        <v>99.14</v>
+        <v>98.72</v>
       </c>
       <c r="AH11">
         <v>196.45</v>
@@ -10374,10 +10392,10 @@
         <v>137</v>
       </c>
       <c r="BA11" t="s">
+        <v>234</v>
+      </c>
+      <c r="BB11" t="s">
         <v>235</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>236</v>
       </c>
       <c r="BC11">
         <v>1</v>
@@ -10401,10 +10419,10 @@
         <v>4</v>
       </c>
       <c r="BJ11" t="s">
+        <v>192</v>
+      </c>
+      <c r="BK11" t="s">
         <v>193</v>
-      </c>
-      <c r="BK11" t="s">
-        <v>194</v>
       </c>
       <c r="BL11" t="s">
         <v>137</v>
@@ -10437,13 +10455,13 @@
         <v>151</v>
       </c>
       <c r="BV11" t="s">
+        <v>236</v>
+      </c>
+      <c r="BW11" t="s">
         <v>237</v>
       </c>
-      <c r="BW11" t="s">
+      <c r="BX11" t="s">
         <v>238</v>
-      </c>
-      <c r="BX11" t="s">
-        <v>239</v>
       </c>
       <c r="BY11" t="s">
         <v>155</v>
@@ -10452,7 +10470,7 @@
         <v>156</v>
       </c>
       <c r="CA11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="CB11" t="s">
         <v>158</v>
@@ -10488,7 +10506,7 @@
         <v>0.55</v>
       </c>
       <c r="CM11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="CN11">
         <v>199.5</v>
@@ -10500,7 +10518,7 @@
         <v>186.53</v>
       </c>
       <c r="CQ11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="CR11" t="s">
         <v>137</v>
@@ -10517,16 +10535,16 @@
         <v>130</v>
       </c>
       <c r="D12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E12" t="s">
         <v>241</v>
       </c>
-      <c r="E12" t="s">
-        <v>242</v>
-      </c>
       <c r="F12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H12" t="s">
         <v>134</v>
@@ -10559,16 +10577,16 @@
         <v>92840</v>
       </c>
       <c r="R12">
-        <v>91580</v>
+        <v>93330</v>
       </c>
       <c r="S12">
-        <v>9158</v>
+        <v>9333</v>
       </c>
       <c r="T12" s="2">
-        <v>-1260</v>
+        <v>490</v>
       </c>
       <c r="U12">
-        <v>-1.36</v>
+        <v>0.53</v>
       </c>
       <c r="V12" t="s">
         <v>137</v>
@@ -10604,7 +10622,7 @@
         <v>131.92</v>
       </c>
       <c r="AG12">
-        <v>101.32</v>
+        <v>189.74</v>
       </c>
       <c r="AH12">
         <v>8955.5</v>
@@ -10664,13 +10682,13 @@
         <v>137</v>
       </c>
       <c r="BA12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BB12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BC12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="s">
         <v>137</v>
@@ -10682,7 +10700,7 @@
         <v>141</v>
       </c>
       <c r="BG12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="BH12">
         <v>10</v>
@@ -10694,13 +10712,13 @@
         <v>143</v>
       </c>
       <c r="BK12" t="s">
+        <v>244</v>
+      </c>
+      <c r="BL12" t="s">
         <v>245</v>
       </c>
-      <c r="BL12" t="s">
+      <c r="BM12" t="s">
         <v>246</v>
-      </c>
-      <c r="BM12" t="s">
-        <v>247</v>
       </c>
       <c r="BN12" t="s">
         <v>138</v>
@@ -10709,7 +10727,7 @@
         <v>137</v>
       </c>
       <c r="BP12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="BQ12" t="s">
         <v>137</v>
@@ -10727,22 +10745,22 @@
         <v>151</v>
       </c>
       <c r="BV12" t="s">
+        <v>248</v>
+      </c>
+      <c r="BW12" t="s">
         <v>249</v>
       </c>
-      <c r="BW12" t="s">
+      <c r="BX12" t="s">
         <v>250</v>
       </c>
-      <c r="BX12" t="s">
-        <v>251</v>
-      </c>
       <c r="BY12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BZ12" t="s">
         <v>156</v>
       </c>
       <c r="CA12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="CB12" t="s">
         <v>158</v>
@@ -10778,7 +10796,7 @@
         <v>0.1</v>
       </c>
       <c r="CM12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="CN12">
         <v>9100</v>
@@ -10790,7 +10808,7 @@
         <v>8955.5</v>
       </c>
       <c r="CQ12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="CR12" t="s">
         <v>137</v>
@@ -10807,16 +10825,16 @@
         <v>130</v>
       </c>
       <c r="D13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E13" t="s">
         <v>254</v>
       </c>
-      <c r="E13" t="s">
-        <v>255</v>
-      </c>
       <c r="F13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H13" t="s">
         <v>134</v>
@@ -10849,16 +10867,16 @@
         <v>26626.6</v>
       </c>
       <c r="R13">
-        <v>26014.3</v>
+        <v>26445.9</v>
       </c>
       <c r="S13">
-        <v>2001.1</v>
-      </c>
-      <c r="T13" s="2">
-        <v>-612.3</v>
+        <v>2034.3</v>
+      </c>
+      <c r="T13" s="3">
+        <v>-180.7</v>
       </c>
       <c r="U13">
-        <v>-2.3</v>
+        <v>-0.68</v>
       </c>
       <c r="V13" t="s">
         <v>137</v>
@@ -10894,13 +10912,13 @@
         <v>170.76</v>
       </c>
       <c r="AG13">
-        <v>73.69</v>
+        <v>96.97</v>
       </c>
       <c r="AH13">
         <v>1974.43</v>
       </c>
       <c r="AI13">
-        <v>1971.08</v>
+        <v>2003.79</v>
       </c>
       <c r="AJ13">
         <v>3614.73</v>
@@ -10954,10 +10972,10 @@
         <v>137</v>
       </c>
       <c r="BA13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BB13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="BC13">
         <v>2</v>
@@ -10981,13 +10999,13 @@
         <v>4</v>
       </c>
       <c r="BJ13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK13" t="s">
+        <v>256</v>
+      </c>
+      <c r="BL13" t="s">
         <v>257</v>
-      </c>
-      <c r="BL13" t="s">
-        <v>258</v>
       </c>
       <c r="BM13" t="s">
         <v>137</v>
@@ -10999,10 +11017,10 @@
         <v>137</v>
       </c>
       <c r="BP13" t="s">
+        <v>258</v>
+      </c>
+      <c r="BQ13" t="s">
         <v>259</v>
-      </c>
-      <c r="BQ13" t="s">
-        <v>260</v>
       </c>
       <c r="BR13" t="s">
         <v>148</v>
@@ -11017,13 +11035,13 @@
         <v>151</v>
       </c>
       <c r="BV13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BW13" t="s">
+        <v>260</v>
+      </c>
+      <c r="BX13" t="s">
         <v>261</v>
-      </c>
-      <c r="BX13" t="s">
-        <v>262</v>
       </c>
       <c r="BY13" t="s">
         <v>155</v>
@@ -11032,7 +11050,7 @@
         <v>156</v>
       </c>
       <c r="CA13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="CB13" t="s">
         <v>158</v>
@@ -11080,7 +11098,7 @@
         <v>1981</v>
       </c>
       <c r="CQ13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="CR13" t="s">
         <v>137</v>
@@ -11094,19 +11112,19 @@
         <v>30</v>
       </c>
       <c r="C14" t="s">
+        <v>263</v>
+      </c>
+      <c r="D14" t="s">
         <v>264</v>
       </c>
-      <c r="D14" t="s">
-        <v>265</v>
-      </c>
       <c r="E14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H14" t="s">
         <v>134</v>
@@ -11115,7 +11133,7 @@
         <v>36</v>
       </c>
       <c r="J14" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K14">
         <v>19.59</v>
@@ -11124,7 +11142,7 @@
         <v>19.59</v>
       </c>
       <c r="M14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N14">
         <v>16</v>
@@ -11139,16 +11157,16 @@
         <v>313.44</v>
       </c>
       <c r="R14">
-        <v>297.44</v>
+        <v>318.4</v>
       </c>
       <c r="S14">
-        <v>18.59</v>
+        <v>19.9</v>
       </c>
       <c r="T14" s="2">
-        <v>-16</v>
+        <v>4.96</v>
       </c>
       <c r="U14">
-        <v>-5.1</v>
+        <v>1.58</v>
       </c>
       <c r="V14" t="s">
         <v>137</v>
@@ -11178,19 +11196,19 @@
         <v>137</v>
       </c>
       <c r="AE14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AF14">
         <v>168.93</v>
       </c>
       <c r="AG14">
-        <v>56.58</v>
+        <v>64.43</v>
       </c>
       <c r="AH14">
         <v>19.01</v>
       </c>
       <c r="AI14">
-        <v>17.1</v>
+        <v>19.01</v>
       </c>
       <c r="AJ14">
         <v>17.98</v>
@@ -11244,10 +11262,10 @@
         <v>137</v>
       </c>
       <c r="BA14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BB14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="BC14">
         <v>2</v>
@@ -11310,19 +11328,19 @@
         <v>152</v>
       </c>
       <c r="BW14" t="s">
+        <v>269</v>
+      </c>
+      <c r="BX14" t="s">
         <v>270</v>
       </c>
-      <c r="BX14" t="s">
+      <c r="BY14" t="s">
         <v>271</v>
-      </c>
-      <c r="BY14" t="s">
-        <v>272</v>
       </c>
       <c r="BZ14" t="s">
         <v>156</v>
       </c>
       <c r="CA14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CB14" t="s">
         <v>138</v>
@@ -11358,7 +11376,7 @@
         <v>0.76</v>
       </c>
       <c r="CM14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="CN14">
         <v>20</v>
@@ -11370,7 +11388,7 @@
         <v>19.01</v>
       </c>
       <c r="CQ14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="CR14" t="s">
         <v>137</v>
@@ -11387,34 +11405,34 @@
         <v>175</v>
       </c>
       <c r="D15" t="s">
+        <v>284</v>
+      </c>
+      <c r="E15" t="s">
+        <v>284</v>
+      </c>
+      <c r="F15" t="s">
         <v>285</v>
       </c>
-      <c r="E15" t="s">
-        <v>285</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>190</v>
+      </c>
+      <c r="H15" t="s">
+        <v>137</v>
+      </c>
+      <c r="I15" t="s">
+        <v>137</v>
+      </c>
+      <c r="J15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K15" t="s">
+        <v>137</v>
+      </c>
+      <c r="L15" t="s">
+        <v>137</v>
+      </c>
+      <c r="M15" t="s">
         <v>286</v>
-      </c>
-      <c r="G15" t="s">
-        <v>191</v>
-      </c>
-      <c r="H15" t="s">
-        <v>137</v>
-      </c>
-      <c r="I15" t="s">
-        <v>137</v>
-      </c>
-      <c r="J15" t="s">
-        <v>137</v>
-      </c>
-      <c r="K15" t="s">
-        <v>137</v>
-      </c>
-      <c r="L15" t="s">
-        <v>137</v>
-      </c>
-      <c r="M15" t="s">
-        <v>287</v>
       </c>
       <c r="N15" t="s">
         <v>137</v>
@@ -11468,7 +11486,7 @@
         <v>137</v>
       </c>
       <c r="AE15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AF15" t="s">
         <v>137</v>
@@ -11549,7 +11567,7 @@
         <v>137</v>
       </c>
       <c r="BF15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BG15" t="s">
         <v>142</v>
@@ -11561,7 +11579,7 @@
         <v>4</v>
       </c>
       <c r="BJ15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BK15" t="s">
         <v>137</v>
@@ -11588,31 +11606,31 @@
         <v>148</v>
       </c>
       <c r="BS15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="BT15" t="s">
         <v>150</v>
       </c>
       <c r="BU15" t="s">
+        <v>290</v>
+      </c>
+      <c r="BV15" t="s">
         <v>291</v>
       </c>
-      <c r="BV15" t="s">
+      <c r="BW15" t="s">
         <v>292</v>
       </c>
-      <c r="BW15" t="s">
+      <c r="BX15" t="s">
         <v>293</v>
       </c>
-      <c r="BX15" t="s">
+      <c r="BY15" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ15" t="s">
+        <v>209</v>
+      </c>
+      <c r="CA15" t="s">
         <v>294</v>
-      </c>
-      <c r="BY15" t="s">
-        <v>209</v>
-      </c>
-      <c r="BZ15" t="s">
-        <v>210</v>
-      </c>
-      <c r="CA15" t="s">
-        <v>295</v>
       </c>
       <c r="CB15" t="s">
         <v>158</v>
@@ -11660,7 +11678,7 @@
         <v>4305.8</v>
       </c>
       <c r="CQ15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="CR15" t="s">
         <v>137</v>
@@ -11677,34 +11695,34 @@
         <v>175</v>
       </c>
       <c r="D16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F16" t="s">
+        <v>285</v>
+      </c>
+      <c r="G16" t="s">
+        <v>190</v>
+      </c>
+      <c r="H16" t="s">
+        <v>137</v>
+      </c>
+      <c r="I16" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" t="s">
+        <v>137</v>
+      </c>
+      <c r="K16" t="s">
+        <v>137</v>
+      </c>
+      <c r="L16" t="s">
+        <v>137</v>
+      </c>
+      <c r="M16" t="s">
         <v>286</v>
-      </c>
-      <c r="G16" t="s">
-        <v>191</v>
-      </c>
-      <c r="H16" t="s">
-        <v>137</v>
-      </c>
-      <c r="I16" t="s">
-        <v>137</v>
-      </c>
-      <c r="J16" t="s">
-        <v>137</v>
-      </c>
-      <c r="K16" t="s">
-        <v>137</v>
-      </c>
-      <c r="L16" t="s">
-        <v>137</v>
-      </c>
-      <c r="M16" t="s">
-        <v>287</v>
       </c>
       <c r="N16" t="s">
         <v>137</v>
@@ -11758,7 +11776,7 @@
         <v>137</v>
       </c>
       <c r="AE16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AF16" t="s">
         <v>137</v>
@@ -11851,7 +11869,7 @@
         <v>4</v>
       </c>
       <c r="BJ16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BK16" t="s">
         <v>137</v>
@@ -11878,31 +11896,31 @@
         <v>148</v>
       </c>
       <c r="BS16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="BT16" t="s">
         <v>150</v>
       </c>
       <c r="BU16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="BV16" t="s">
+        <v>298</v>
+      </c>
+      <c r="BW16" t="s">
         <v>299</v>
       </c>
-      <c r="BW16" t="s">
+      <c r="BX16" t="s">
         <v>300</v>
       </c>
-      <c r="BX16" t="s">
-        <v>301</v>
-      </c>
       <c r="BY16" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ16" t="s">
         <v>209</v>
       </c>
-      <c r="BZ16" t="s">
-        <v>210</v>
-      </c>
       <c r="CA16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="CB16" t="s">
         <v>158</v>
@@ -11926,7 +11944,7 @@
         <v>0</v>
       </c>
       <c r="CI16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="CJ16">
         <v>1.19</v>
@@ -11950,7 +11968,7 @@
         <v>1012.9</v>
       </c>
       <c r="CQ16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="CR16" t="s">
         <v>137</v>
@@ -11964,37 +11982,37 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F17" t="s">
+        <v>285</v>
+      </c>
+      <c r="G17" t="s">
+        <v>190</v>
+      </c>
+      <c r="H17" t="s">
+        <v>137</v>
+      </c>
+      <c r="I17" t="s">
+        <v>137</v>
+      </c>
+      <c r="J17" t="s">
+        <v>137</v>
+      </c>
+      <c r="K17" t="s">
+        <v>137</v>
+      </c>
+      <c r="L17" t="s">
+        <v>137</v>
+      </c>
+      <c r="M17" t="s">
         <v>286</v>
-      </c>
-      <c r="G17" t="s">
-        <v>191</v>
-      </c>
-      <c r="H17" t="s">
-        <v>137</v>
-      </c>
-      <c r="I17" t="s">
-        <v>137</v>
-      </c>
-      <c r="J17" t="s">
-        <v>137</v>
-      </c>
-      <c r="K17" t="s">
-        <v>137</v>
-      </c>
-      <c r="L17" t="s">
-        <v>137</v>
-      </c>
-      <c r="M17" t="s">
-        <v>287</v>
       </c>
       <c r="N17" t="s">
         <v>137</v>
@@ -12048,7 +12066,7 @@
         <v>137</v>
       </c>
       <c r="AE17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AF17" t="s">
         <v>137</v>
@@ -12132,7 +12150,7 @@
         <v>141</v>
       </c>
       <c r="BG17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="BH17">
         <v>12</v>
@@ -12141,7 +12159,7 @@
         <v>2</v>
       </c>
       <c r="BJ17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK17" t="s">
         <v>137</v>
@@ -12174,25 +12192,25 @@
         <v>150</v>
       </c>
       <c r="BU17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="BV17" t="s">
+        <v>303</v>
+      </c>
+      <c r="BW17" t="s">
         <v>304</v>
       </c>
-      <c r="BW17" t="s">
+      <c r="BX17" t="s">
         <v>305</v>
       </c>
-      <c r="BX17" t="s">
-        <v>306</v>
-      </c>
       <c r="BY17" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ17" t="s">
         <v>209</v>
       </c>
-      <c r="BZ17" t="s">
-        <v>210</v>
-      </c>
       <c r="CA17" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="CB17" t="s">
         <v>158</v>
@@ -12240,7 +12258,7 @@
         <v>688.05</v>
       </c>
       <c r="CQ17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="CR17" t="s">
         <v>137</v>
@@ -12251,25 +12269,25 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
+        <v>199</v>
+      </c>
+      <c r="C18" t="s">
         <v>200</v>
       </c>
-      <c r="C18" t="s">
-        <v>201</v>
-      </c>
       <c r="D18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I18" t="s">
         <v>36</v>
@@ -12299,16 +12317,16 @@
         <v>98538</v>
       </c>
       <c r="R18">
-        <v>98396.1</v>
+        <v>101300.1</v>
       </c>
       <c r="S18">
-        <v>2981.7</v>
+        <v>3069.7</v>
       </c>
       <c r="T18" s="2">
-        <v>-141.9</v>
+        <v>2762.1</v>
       </c>
       <c r="U18">
-        <v>-0.14</v>
+        <v>2.8</v>
       </c>
       <c r="V18" t="s">
         <v>137</v>
@@ -12344,7 +12362,7 @@
         <v>137</v>
       </c>
       <c r="AG18">
-        <v>88.2</v>
+        <v>170.48</v>
       </c>
       <c r="AH18">
         <v>2728.17</v>
@@ -12404,13 +12422,13 @@
         <v>137</v>
       </c>
       <c r="BA18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BB18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BC18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="s">
         <v>137</v>
@@ -12431,7 +12449,7 @@
         <v>3</v>
       </c>
       <c r="BJ18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK18" t="s">
         <v>137</v>
@@ -12467,22 +12485,22 @@
         <v>151</v>
       </c>
       <c r="BV18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BW18" t="s">
+        <v>276</v>
+      </c>
+      <c r="BX18" t="s">
         <v>277</v>
       </c>
-      <c r="BX18" t="s">
-        <v>278</v>
-      </c>
       <c r="BY18" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ18" t="s">
         <v>209</v>
       </c>
-      <c r="BZ18" t="s">
+      <c r="CA18" t="s">
         <v>210</v>
-      </c>
-      <c r="CA18" t="s">
-        <v>211</v>
       </c>
       <c r="CB18" t="s">
         <v>158</v>
@@ -12518,7 +12536,7 @@
         <v>137</v>
       </c>
       <c r="CM18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="CN18">
         <v>2903.2</v>
@@ -12530,7 +12548,7 @@
         <v>2903.2</v>
       </c>
       <c r="CQ18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="CR18" t="s">
         <v>137</v>
@@ -12541,25 +12559,25 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C19" t="s">
         <v>175</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I19" t="s">
         <v>36</v>
@@ -12594,7 +12612,7 @@
       <c r="S19">
         <v>1299.2</v>
       </c>
-      <c r="T19" s="2">
+      <c r="T19" s="3">
         <v>-1931.4</v>
       </c>
       <c r="U19">
@@ -12634,7 +12652,7 @@
         <v>137</v>
       </c>
       <c r="AG19">
-        <v>90.23</v>
+        <v>89.92</v>
       </c>
       <c r="AH19">
         <v>1251.2</v>
@@ -12694,10 +12712,10 @@
         <v>137</v>
       </c>
       <c r="BA19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BB19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="BC19">
         <v>2</v>
@@ -12721,7 +12739,7 @@
         <v>4</v>
       </c>
       <c r="BJ19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BK19" t="s">
         <v>137</v>
@@ -12757,22 +12775,22 @@
         <v>151</v>
       </c>
       <c r="BV19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BW19" t="s">
+        <v>280</v>
+      </c>
+      <c r="BX19" t="s">
         <v>281</v>
       </c>
-      <c r="BX19" t="s">
-        <v>282</v>
-      </c>
       <c r="BY19" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ19" t="s">
         <v>209</v>
       </c>
-      <c r="BZ19" t="s">
+      <c r="CA19" t="s">
         <v>210</v>
-      </c>
-      <c r="CA19" t="s">
-        <v>211</v>
       </c>
       <c r="CB19" t="s">
         <v>158</v>
@@ -12808,7 +12826,7 @@
         <v>137</v>
       </c>
       <c r="CM19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="CN19">
         <v>1321</v>
@@ -12820,7 +12838,7 @@
         <v>1321</v>
       </c>
       <c r="CQ19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="CR19" t="s">
         <v>137</v>
@@ -12835,7 +12853,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -12861,57 +12879,57 @@
         <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>91</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B2" t="s">
         <v>322</v>
-      </c>
-      <c r="B2" t="s">
-        <v>323</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
@@ -12923,28 +12941,28 @@
         <v>142</v>
       </c>
       <c r="F2">
-        <v>217.14</v>
+        <v>202.39</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="I2" t="s">
         <v>137</v>
       </c>
       <c r="J2">
-        <v>16.27</v>
+        <v>15.28</v>
       </c>
       <c r="K2">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="L2">
-        <v>5.17</v>
+        <v>19.92</v>
       </c>
       <c r="M2" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -12953,21 +12971,21 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>832.09</v>
+        <v>794.42</v>
       </c>
       <c r="Q2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
         <v>325</v>
-      </c>
-      <c r="C3" t="s">
-        <v>326</v>
       </c>
       <c r="D3" t="s">
         <v>134</v>
@@ -12976,7 +12994,7 @@
         <v>142</v>
       </c>
       <c r="F3">
-        <v>203.83</v>
+        <v>194.82</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -12994,7 +13012,7 @@
         <v>3.5</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>9.01</v>
       </c>
       <c r="M3" t="s">
         <v>141</v>
@@ -13009,18 +13027,18 @@
         <v>8764.5</v>
       </c>
       <c r="Q3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B4" t="s">
         <v>327</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>328</v>
-      </c>
-      <c r="C4" t="s">
-        <v>329</v>
       </c>
       <c r="D4" t="s">
         <v>135</v>
@@ -13029,7 +13047,7 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>188.56</v>
+        <v>193.4</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -13047,10 +13065,10 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>5.17</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -13062,27 +13080,27 @@
         <v>10013.51</v>
       </c>
       <c r="Q4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5" t="s">
         <v>331</v>
       </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
         <v>142</v>
       </c>
       <c r="F5">
-        <v>188.39</v>
+        <v>190.49</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -13094,16 +13112,16 @@
         <v>137</v>
       </c>
       <c r="J5">
-        <v>9.31</v>
+        <v>5.72</v>
       </c>
       <c r="K5">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -13112,15 +13130,15 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>501.1</v>
+        <v>1357.63</v>
       </c>
       <c r="Q5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B6" t="s">
         <v>332</v>
@@ -13129,13 +13147,13 @@
         <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
         <v>142</v>
       </c>
       <c r="F6">
-        <v>183.51</v>
+        <v>181.4</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -13147,10 +13165,10 @@
         <v>137</v>
       </c>
       <c r="J6">
-        <v>10.89</v>
+        <v>13.41</v>
       </c>
       <c r="K6">
-        <v>2.94</v>
+        <v>0.97</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -13165,30 +13183,30 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>22.35</v>
+        <v>56</v>
       </c>
       <c r="Q6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
         <v>333</v>
       </c>
       <c r="C7" t="s">
-        <v>326</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E7" t="s">
         <v>142</v>
       </c>
       <c r="F7">
-        <v>178.96</v>
+        <v>180.09</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -13200,10 +13218,10 @@
         <v>137</v>
       </c>
       <c r="J7">
-        <v>8.01</v>
+        <v>4.76</v>
       </c>
       <c r="K7">
-        <v>1.96</v>
+        <v>5.01</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -13218,15 +13236,15 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>801</v>
+        <v>115.25</v>
       </c>
       <c r="Q7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B8" t="s">
         <v>334</v>
@@ -13274,30 +13292,30 @@
         <v>176.13</v>
       </c>
       <c r="Q8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B9" t="s">
         <v>335</v>
       </c>
       <c r="C9" t="s">
-        <v>326</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E9" t="s">
         <v>142</v>
       </c>
       <c r="F9">
-        <v>172.48</v>
+        <v>173.68</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -13306,16 +13324,16 @@
         <v>137</v>
       </c>
       <c r="J9">
-        <v>3.05</v>
+        <v>5.67</v>
       </c>
       <c r="K9">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -13324,15 +13342,15 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>794.6</v>
+        <v>15684</v>
       </c>
       <c r="Q9" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B10" t="s">
         <v>336</v>
@@ -13347,25 +13365,25 @@
         <v>142</v>
       </c>
       <c r="F10">
-        <v>162.71</v>
+        <v>166.42</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="I10" t="s">
         <v>137</v>
       </c>
       <c r="J10">
-        <v>4.47</v>
+        <v>4.16</v>
       </c>
       <c r="K10">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="L10">
-        <v>10.97</v>
+        <v>0</v>
       </c>
       <c r="M10" t="s">
         <v>141</v>
@@ -13377,10 +13395,116 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>15848.82</v>
+        <v>4875</v>
       </c>
       <c r="Q10" t="s">
-        <v>324</v>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>326</v>
+      </c>
+      <c r="B11" t="s">
+        <v>337</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11">
+        <v>161.75</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>137</v>
+      </c>
+      <c r="J11">
+        <v>10.81</v>
+      </c>
+      <c r="K11">
+        <v>1.27</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>141</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>143.84</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>326</v>
+      </c>
+      <c r="B12" t="s">
+        <v>338</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12">
+        <v>161.4</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>137</v>
+      </c>
+      <c r="J12">
+        <v>7.52</v>
+      </c>
+      <c r="K12">
+        <v>0.74</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>141</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>416.11</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -13392,7 +13516,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -13412,78 +13536,78 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="Q1" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B2" t="s">
         <v>134</v>
       </c>
       <c r="C2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D2" t="s">
         <v>325</v>
-      </c>
-      <c r="D2" t="s">
-        <v>326</v>
       </c>
       <c r="E2" t="s">
         <v>134</v>
       </c>
       <c r="G2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I2" t="s">
         <v>142</v>
@@ -13510,18 +13634,18 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B3" t="s">
         <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -13530,10 +13654,10 @@
         <v>134</v>
       </c>
       <c r="G3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I3" t="s">
         <v>142</v>
@@ -13560,12 +13684,12 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B4" t="s">
         <v>134</v>
@@ -13574,16 +13698,16 @@
         <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E4" t="s">
         <v>134</v>
       </c>
       <c r="G4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I4" t="s">
         <v>142</v>
@@ -13610,12 +13734,12 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B5" t="s">
         <v>134</v>
@@ -13633,10 +13757,10 @@
         <v>622.5499877929688</v>
       </c>
       <c r="G5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I5" t="s">
         <v>142</v>
@@ -13663,33 +13787,33 @@
         <v>1</v>
       </c>
       <c r="Q5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F6">
         <v>637.9000244140625</v>
       </c>
       <c r="G6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I6" t="s">
         <v>142</v>
@@ -13716,33 +13840,33 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C7" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="D7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F7">
         <v>814.9000244140625</v>
       </c>
       <c r="G7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I7" t="s">
         <v>142</v>
@@ -13769,33 +13893,33 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F8">
         <v>637.9000244140625</v>
       </c>
       <c r="G8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H8" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I8" t="s">
         <v>142</v>
@@ -13822,33 +13946,33 @@
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C9" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="D9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F9">
         <v>814.9000244140625</v>
       </c>
       <c r="G9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I9" t="s">
         <v>142</v>
@@ -13875,18 +13999,18 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B10" t="s">
         <v>134</v>
       </c>
       <c r="C10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
@@ -13898,10 +14022,10 @@
         <v>863.5</v>
       </c>
       <c r="G10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I10" t="s">
         <v>142</v>
@@ -13928,21 +14052,21 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B11" t="s">
         <v>134</v>
       </c>
       <c r="C11" t="s">
+        <v>324</v>
+      </c>
+      <c r="D11" t="s">
         <v>325</v>
-      </c>
-      <c r="D11" t="s">
-        <v>326</v>
       </c>
       <c r="E11" t="s">
         <v>134</v>
@@ -13951,10 +14075,10 @@
         <v>8782.5</v>
       </c>
       <c r="G11" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I11" t="s">
         <v>142</v>
@@ -13981,18 +14105,18 @@
         <v>1</v>
       </c>
       <c r="Q11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B12" t="s">
         <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D12" t="s">
         <v>28</v>
@@ -14004,10 +14128,10 @@
         <v>16326</v>
       </c>
       <c r="G12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I12" t="s">
         <v>142</v>
@@ -14034,18 +14158,18 @@
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B13" t="s">
         <v>134</v>
       </c>
       <c r="C13" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="D13" t="s">
         <v>28</v>
@@ -14057,10 +14181,10 @@
         <v>5024</v>
       </c>
       <c r="G13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H13" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="I13" t="s">
         <v>142</v>
@@ -14069,110 +14193,110 @@
         <v>166.42</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="L13" t="s">
         <v>137</v>
       </c>
       <c r="M13">
-        <v>4.16</v>
+        <v>3.39</v>
       </c>
       <c r="N13">
-        <v>1.22</v>
+        <v>0.92</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>78.35</v>
       </c>
       <c r="P13">
         <v>1</v>
       </c>
       <c r="Q13" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C14" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F14">
-        <v>5024</v>
+        <v>527.9000244140625</v>
       </c>
       <c r="G14" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="H14" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="I14" t="s">
         <v>142</v>
       </c>
       <c r="J14">
-        <v>166.42</v>
+        <v>188.39</v>
       </c>
       <c r="K14">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="L14" t="s">
         <v>137</v>
       </c>
       <c r="M14">
-        <v>3.39</v>
+        <v>9.31</v>
       </c>
       <c r="N14">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O14">
-        <v>78.35</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B15" t="s">
         <v>135</v>
       </c>
       <c r="C15" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="D15" t="s">
-        <v>329</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
         <v>135</v>
       </c>
       <c r="F15">
-        <v>10166</v>
+        <v>23.700000762939453</v>
       </c>
       <c r="G15" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I15" t="s">
         <v>142</v>
       </c>
       <c r="J15">
-        <v>188.56</v>
+        <v>183.51</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -14181,51 +14305,51 @@
         <v>137</v>
       </c>
       <c r="M15">
-        <v>5.67</v>
+        <v>10.89</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O15">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B16" t="s">
         <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>325</v>
       </c>
       <c r="E16" t="s">
         <v>135</v>
       </c>
       <c r="F16">
-        <v>527.9000244140625</v>
+        <v>813.2000122070312</v>
       </c>
       <c r="G16" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I16" t="s">
         <v>142</v>
       </c>
       <c r="J16">
-        <v>188.39</v>
+        <v>178.96</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -14234,10 +14358,10 @@
         <v>137</v>
       </c>
       <c r="M16">
-        <v>9.31</v>
+        <v>8.01</v>
       </c>
       <c r="N16">
-        <v>0.95</v>
+        <v>1.96</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -14246,39 +14370,39 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B17" t="s">
         <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>325</v>
       </c>
       <c r="E17" t="s">
         <v>135</v>
       </c>
       <c r="F17">
-        <v>23.700000762939453</v>
+        <v>806.7000122070312</v>
       </c>
       <c r="G17" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I17" t="s">
         <v>142</v>
       </c>
       <c r="J17">
-        <v>183.51</v>
+        <v>172.48</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -14287,10 +14411,10 @@
         <v>137</v>
       </c>
       <c r="M17">
-        <v>10.89</v>
+        <v>3.05</v>
       </c>
       <c r="N17">
-        <v>2.94</v>
+        <v>1.14</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -14299,166 +14423,643 @@
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B18" t="s">
         <v>135</v>
       </c>
       <c r="C18" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="D18" t="s">
-        <v>326</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s">
         <v>135</v>
       </c>
       <c r="F18">
-        <v>813.2000122070312</v>
+        <v>527.9000244140625</v>
       </c>
       <c r="G18" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H18" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="I18" t="s">
         <v>142</v>
       </c>
       <c r="J18">
-        <v>178.96</v>
+        <v>188.39</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>-1.62</v>
       </c>
       <c r="L18" t="s">
         <v>137</v>
       </c>
       <c r="M18">
-        <v>8.01</v>
+        <v>7.81</v>
       </c>
       <c r="N18">
-        <v>1.96</v>
+        <v>0.64</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>72.13</v>
       </c>
       <c r="P18">
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="D19" t="s">
         <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F19">
-        <v>179.52000427246094</v>
+        <v>23.700000762939453</v>
       </c>
       <c r="G19" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H19" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="I19" t="s">
         <v>142</v>
       </c>
       <c r="J19">
-        <v>177.33</v>
+        <v>183.51</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>-4.6</v>
       </c>
       <c r="L19" t="s">
         <v>137</v>
       </c>
       <c r="M19">
-        <v>2.62</v>
+        <v>6.59</v>
       </c>
       <c r="N19">
-        <v>3.44</v>
+        <v>2.07</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>74.87</v>
       </c>
       <c r="P19">
         <v>1</v>
       </c>
       <c r="Q19" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B20" t="s">
         <v>135</v>
       </c>
       <c r="C20" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="D20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E20" t="s">
         <v>135</v>
       </c>
       <c r="F20">
-        <v>806.7000122070312</v>
+        <v>813.2000122070312</v>
       </c>
       <c r="G20" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H20" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="I20" t="s">
         <v>142</v>
       </c>
       <c r="J20">
-        <v>172.48</v>
+        <v>178.96</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="L20" t="s">
         <v>137</v>
       </c>
       <c r="M20">
-        <v>3.05</v>
+        <v>8.63</v>
       </c>
       <c r="N20">
-        <v>1.14</v>
+        <v>2.03</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>68.28</v>
       </c>
       <c r="P20">
         <v>1</v>
       </c>
       <c r="Q20" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>362</v>
+      </c>
+      <c r="B21" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" t="s">
+        <v>354</v>
+      </c>
+      <c r="D21" t="s">
+        <v>325</v>
+      </c>
+      <c r="E21" t="s">
+        <v>135</v>
+      </c>
+      <c r="F21">
+        <v>806.7000122070312</v>
+      </c>
+      <c r="G21" t="s">
+        <v>347</v>
+      </c>
+      <c r="H21" t="s">
+        <v>348</v>
+      </c>
+      <c r="I21" t="s">
+        <v>142</v>
+      </c>
+      <c r="J21">
+        <v>172.48</v>
+      </c>
+      <c r="K21">
+        <v>-0.71</v>
+      </c>
+      <c r="L21" t="s">
+        <v>137</v>
+      </c>
+      <c r="M21">
+        <v>2.35</v>
+      </c>
+      <c r="N21">
+        <v>0.99</v>
+      </c>
+      <c r="O21">
+        <v>83.3</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>362</v>
+      </c>
+      <c r="B22" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" t="s">
+        <v>327</v>
+      </c>
+      <c r="D22" t="s">
+        <v>328</v>
+      </c>
+      <c r="E22" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22">
+        <v>10166</v>
+      </c>
+      <c r="G22" t="s">
+        <v>351</v>
+      </c>
+      <c r="H22" t="s">
+        <v>326</v>
+      </c>
+      <c r="I22" t="s">
+        <v>142</v>
+      </c>
+      <c r="J22">
+        <v>193.4</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22" t="s">
+        <v>137</v>
+      </c>
+      <c r="M22">
+        <v>5.67</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0.33</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>362</v>
+      </c>
+      <c r="B23" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" t="s">
         <v>330</v>
+      </c>
+      <c r="D23" t="s">
+        <v>331</v>
+      </c>
+      <c r="E23" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23">
+        <v>1378.300048828125</v>
+      </c>
+      <c r="G23" t="s">
+        <v>351</v>
+      </c>
+      <c r="H23" t="s">
+        <v>326</v>
+      </c>
+      <c r="I23" t="s">
+        <v>142</v>
+      </c>
+      <c r="J23">
+        <v>190.49</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23" t="s">
+        <v>137</v>
+      </c>
+      <c r="M23">
+        <v>5.72</v>
+      </c>
+      <c r="N23">
+        <v>1.02</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>362</v>
+      </c>
+      <c r="B24" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" t="s">
+        <v>332</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24">
+        <v>56.9900016784668</v>
+      </c>
+      <c r="G24" t="s">
+        <v>351</v>
+      </c>
+      <c r="H24" t="s">
+        <v>326</v>
+      </c>
+      <c r="I24" t="s">
+        <v>142</v>
+      </c>
+      <c r="J24">
+        <v>181.4</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24" t="s">
+        <v>137</v>
+      </c>
+      <c r="M24">
+        <v>13.41</v>
+      </c>
+      <c r="N24">
+        <v>0.97</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>362</v>
+      </c>
+      <c r="B25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" t="s">
+        <v>333</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25">
+        <v>121</v>
+      </c>
+      <c r="G25" t="s">
+        <v>351</v>
+      </c>
+      <c r="H25" t="s">
+        <v>326</v>
+      </c>
+      <c r="I25" t="s">
+        <v>142</v>
+      </c>
+      <c r="J25">
+        <v>180.09</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25" t="s">
+        <v>137</v>
+      </c>
+      <c r="M25">
+        <v>4.76</v>
+      </c>
+      <c r="N25">
+        <v>5.01</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>362</v>
+      </c>
+      <c r="B26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" t="s">
+        <v>334</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26">
+        <v>179.52000427246094</v>
+      </c>
+      <c r="G26" t="s">
+        <v>351</v>
+      </c>
+      <c r="H26" t="s">
+        <v>326</v>
+      </c>
+      <c r="I26" t="s">
+        <v>142</v>
+      </c>
+      <c r="J26">
+        <v>177.33</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26" t="s">
+        <v>137</v>
+      </c>
+      <c r="M26">
+        <v>2.62</v>
+      </c>
+      <c r="N26">
+        <v>3.44</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>362</v>
+      </c>
+      <c r="B27" t="s">
+        <v>134</v>
+      </c>
+      <c r="C27" t="s">
+        <v>336</v>
+      </c>
+      <c r="D27" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27">
+        <v>5024</v>
+      </c>
+      <c r="G27" t="s">
+        <v>351</v>
+      </c>
+      <c r="H27" t="s">
+        <v>326</v>
+      </c>
+      <c r="I27" t="s">
+        <v>142</v>
+      </c>
+      <c r="J27">
+        <v>166.42</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27" t="s">
+        <v>137</v>
+      </c>
+      <c r="M27">
+        <v>4.16</v>
+      </c>
+      <c r="N27">
+        <v>1.22</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>362</v>
+      </c>
+      <c r="B28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" t="s">
+        <v>337</v>
+      </c>
+      <c r="D28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F28">
+        <v>156.35000610351562</v>
+      </c>
+      <c r="G28" t="s">
+        <v>351</v>
+      </c>
+      <c r="H28" t="s">
+        <v>326</v>
+      </c>
+      <c r="I28" t="s">
+        <v>142</v>
+      </c>
+      <c r="J28">
+        <v>161.75</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28" t="s">
+        <v>137</v>
+      </c>
+      <c r="M28">
+        <v>10.81</v>
+      </c>
+      <c r="N28">
+        <v>1.27</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>362</v>
+      </c>
+      <c r="B29" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" t="s">
+        <v>338</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29">
+        <v>422.45001220703125</v>
+      </c>
+      <c r="G29" t="s">
+        <v>351</v>
+      </c>
+      <c r="H29" t="s">
+        <v>326</v>
+      </c>
+      <c r="I29" t="s">
+        <v>142</v>
+      </c>
+      <c r="J29">
+        <v>161.4</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29" t="s">
+        <v>137</v>
+      </c>
+      <c r="M29">
+        <v>7.52</v>
+      </c>
+      <c r="N29">
+        <v>0.74</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -14482,30 +15083,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B2" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -14517,7 +15118,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3108" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3144" uniqueCount="370">
   <si>
     <t>Metric</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-15T03:47:24.633Z</t>
+    <t>2026-07-15T04:00:50.511Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -992,16 +992,19 @@
     <t>WAITING_CONFIRMATION</t>
   </si>
   <si>
+    <t>APCOTEXIND</t>
+  </si>
+  <si>
+    <t>Rotation requires 2 distinct valid ENTRY closes; candidate has 1.</t>
+  </si>
+  <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
     <t>Automobile and Auto Components</t>
   </si>
   <si>
-    <t>Rotation requires 2 distinct valid ENTRY closes; candidate has 1.</t>
-  </si>
-  <si>
-    <t>APCOTEXIND</t>
+    <t>Capital Goods</t>
   </si>
   <si>
     <t>CJGEL</t>
@@ -1076,9 +1079,6 @@
     <t>SCHNEIDER</t>
   </si>
   <si>
-    <t>Capital Goods</t>
-  </si>
-  <si>
     <t>RASRESOR</t>
   </si>
   <si>
@@ -1098,6 +1098,9 @@
   </si>
   <si>
     <t>Latest completed-candle status is WATCH, not ENTRY. Current setup grade WATCH no longer passes the selected trade-quality filter. Current/09:17 price is below daily Supertrend.</t>
+  </si>
+  <si>
+    <t>2026-07-15T04:00:49.945Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -1659,7 +1662,7 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2528,7 +2531,7 @@
         <v>195.78</v>
       </c>
       <c r="AG3">
-        <v>184.32</v>
+        <v>179.52</v>
       </c>
       <c r="AH3">
         <v>597.22</v>
@@ -3398,7 +3401,7 @@
         <v>179.24</v>
       </c>
       <c r="AG6">
-        <v>98.72</v>
+        <v>99.14</v>
       </c>
       <c r="AH6">
         <v>196.45</v>
@@ -4848,7 +4851,7 @@
         <v>137</v>
       </c>
       <c r="AG11">
-        <v>182.72</v>
+        <v>184.22</v>
       </c>
       <c r="AH11">
         <v>1842.85</v>
@@ -5138,7 +5141,7 @@
         <v>137</v>
       </c>
       <c r="AG12">
-        <v>183.02</v>
+        <v>183.38</v>
       </c>
       <c r="AH12">
         <v>1285.88</v>
@@ -6008,7 +6011,7 @@
         <v>137</v>
       </c>
       <c r="AG15">
-        <v>89.92</v>
+        <v>90.23</v>
       </c>
       <c r="AH15">
         <v>1251.2</v>
@@ -6673,7 +6676,7 @@
         <v>168.93</v>
       </c>
       <c r="AG2">
-        <v>58.08</v>
+        <v>59.58</v>
       </c>
       <c r="AH2">
         <v>19.01</v>
@@ -8003,7 +8006,7 @@
         <v>195.78</v>
       </c>
       <c r="AG3">
-        <v>184.32</v>
+        <v>179.52</v>
       </c>
       <c r="AH3">
         <v>597.22</v>
@@ -8873,7 +8876,7 @@
         <v>179.24</v>
       </c>
       <c r="AG6">
-        <v>98.72</v>
+        <v>99.14</v>
       </c>
       <c r="AH6">
         <v>196.45</v>
@@ -10323,7 +10326,7 @@
         <v>137</v>
       </c>
       <c r="AG11">
-        <v>182.72</v>
+        <v>184.22</v>
       </c>
       <c r="AH11">
         <v>1842.85</v>
@@ -10613,7 +10616,7 @@
         <v>137</v>
       </c>
       <c r="AG12">
-        <v>183.02</v>
+        <v>183.38</v>
       </c>
       <c r="AH12">
         <v>1285.88</v>
@@ -11483,7 +11486,7 @@
         <v>137</v>
       </c>
       <c r="AG15">
-        <v>89.92</v>
+        <v>90.23</v>
       </c>
       <c r="AH15">
         <v>1251.2</v>
@@ -11773,7 +11776,7 @@
         <v>168.93</v>
       </c>
       <c r="AG16">
-        <v>58.08</v>
+        <v>59.58</v>
       </c>
       <c r="AH16">
         <v>19.01</v>
@@ -12844,7 +12847,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -12932,7 +12935,7 @@
         <v>142</v>
       </c>
       <c r="F2">
-        <v>218.64</v>
+        <v>220.14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -12950,7 +12953,7 @@
         <v>2.72</v>
       </c>
       <c r="L2">
-        <v>3.67</v>
+        <v>2.17</v>
       </c>
       <c r="M2" t="s">
         <v>164</v>
@@ -12985,7 +12988,7 @@
         <v>142</v>
       </c>
       <c r="F3">
-        <v>194.16</v>
+        <v>203.83</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -13003,7 +13006,7 @@
         <v>3.5</v>
       </c>
       <c r="L3">
-        <v>9.67</v>
+        <v>0</v>
       </c>
       <c r="M3" t="s">
         <v>141</v>
@@ -13029,7 +13032,7 @@
         <v>324</v>
       </c>
       <c r="C4" t="s">
-        <v>325</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
         <v>135</v>
@@ -13038,7 +13041,7 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>192.73</v>
+        <v>191.39</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -13050,28 +13053,28 @@
         <v>137</v>
       </c>
       <c r="J4">
-        <v>5.67</v>
+        <v>9.31</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="N4">
-        <v>91494</v>
+        <v>99773.1</v>
       </c>
       <c r="O4">
-        <v>1372.41</v>
+        <v>5065.2</v>
       </c>
       <c r="P4">
-        <v>10013.51</v>
+        <v>501.1</v>
       </c>
       <c r="Q4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -13079,10 +13082,10 @@
         <v>323</v>
       </c>
       <c r="B5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C5" t="s">
         <v>327</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
       </c>
       <c r="D5" t="s">
         <v>135</v>
@@ -13091,7 +13094,7 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>189.89</v>
+        <v>188.56</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -13103,28 +13106,28 @@
         <v>137</v>
       </c>
       <c r="J5">
-        <v>9.31</v>
+        <v>5.67</v>
       </c>
       <c r="K5">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="M5" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="N5">
-        <v>99773.1</v>
+        <v>91494</v>
       </c>
       <c r="O5">
-        <v>5065.2</v>
+        <v>1372.41</v>
       </c>
       <c r="P5">
-        <v>501.1</v>
+        <v>10013.51</v>
       </c>
       <c r="Q5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -13132,10 +13135,10 @@
         <v>323</v>
       </c>
       <c r="B6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" t="s">
         <v>328</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>135</v>
@@ -13144,7 +13147,7 @@
         <v>142</v>
       </c>
       <c r="F6">
-        <v>185.01</v>
+        <v>186.81</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -13156,10 +13159,10 @@
         <v>137</v>
       </c>
       <c r="J6">
-        <v>10.89</v>
+        <v>5.48</v>
       </c>
       <c r="K6">
-        <v>2.94</v>
+        <v>0.41</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -13168,16 +13171,16 @@
         <v>141</v>
       </c>
       <c r="N6">
-        <v>99990.3</v>
+        <v>97732.8</v>
       </c>
       <c r="O6">
-        <v>5695.65</v>
+        <v>1466.08</v>
       </c>
       <c r="P6">
-        <v>22.35</v>
+        <v>4375.76</v>
       </c>
       <c r="Q6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -13188,7 +13191,7 @@
         <v>329</v>
       </c>
       <c r="C7" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
         <v>135</v>
@@ -13197,7 +13200,7 @@
         <v>142</v>
       </c>
       <c r="F7">
-        <v>180.46</v>
+        <v>186.51</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -13209,10 +13212,10 @@
         <v>137</v>
       </c>
       <c r="J7">
-        <v>8.01</v>
+        <v>10.89</v>
       </c>
       <c r="K7">
-        <v>1.96</v>
+        <v>2.94</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -13221,16 +13224,16 @@
         <v>141</v>
       </c>
       <c r="N7">
-        <v>99210.4</v>
+        <v>99990.3</v>
       </c>
       <c r="O7">
-        <v>1488.4</v>
+        <v>5695.65</v>
       </c>
       <c r="P7">
-        <v>801</v>
+        <v>22.35</v>
       </c>
       <c r="Q7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -13241,16 +13244,16 @@
         <v>330</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>322</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E8" t="s">
         <v>142</v>
       </c>
       <c r="F8">
-        <v>177.33</v>
+        <v>181.96</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -13262,10 +13265,10 @@
         <v>137</v>
       </c>
       <c r="J8">
-        <v>2.62</v>
+        <v>8.01</v>
       </c>
       <c r="K8">
-        <v>3.44</v>
+        <v>1.96</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -13274,16 +13277,16 @@
         <v>141</v>
       </c>
       <c r="N8">
-        <v>99992.64</v>
+        <v>99210.4</v>
       </c>
       <c r="O8">
-        <v>1888.23</v>
+        <v>1488.4</v>
       </c>
       <c r="P8">
-        <v>176.13</v>
+        <v>801</v>
       </c>
       <c r="Q8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -13294,16 +13297,16 @@
         <v>331</v>
       </c>
       <c r="C9" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E9" t="s">
         <v>142</v>
       </c>
       <c r="F9">
-        <v>173.98</v>
+        <v>177.33</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -13315,10 +13318,10 @@
         <v>137</v>
       </c>
       <c r="J9">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="K9">
-        <v>1.14</v>
+        <v>3.44</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -13327,68 +13330,174 @@
         <v>141</v>
       </c>
       <c r="N9">
-        <v>99224.1</v>
+        <v>99992.64</v>
       </c>
       <c r="O9">
-        <v>1488.3</v>
+        <v>1888.23</v>
       </c>
       <c r="P9">
-        <v>794.6</v>
+        <v>176.13</v>
       </c>
       <c r="Q9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B10" t="s">
         <v>332</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>322</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
         <v>142</v>
       </c>
       <c r="F10">
-        <v>164.21</v>
+        <v>175.48</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="I10" t="s">
         <v>137</v>
       </c>
       <c r="J10">
-        <v>4.47</v>
+        <v>3.05</v>
       </c>
       <c r="K10">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="L10">
-        <v>9.47</v>
+        <v>0</v>
       </c>
       <c r="M10" t="s">
         <v>141</v>
       </c>
       <c r="N10">
+        <v>99224.1</v>
+      </c>
+      <c r="O10">
+        <v>1488.3</v>
+      </c>
+      <c r="P10">
+        <v>794.6</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>323</v>
+      </c>
+      <c r="B11" t="s">
+        <v>299</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E11" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11">
+        <v>175.03</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>137</v>
+      </c>
+      <c r="J11">
+        <v>8.15</v>
+      </c>
+      <c r="K11">
+        <v>0.93</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>192</v>
+      </c>
+      <c r="N11">
+        <v>99812.25</v>
+      </c>
+      <c r="O11">
+        <v>2038.5</v>
+      </c>
+      <c r="P11">
+        <v>724.25</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B12" t="s">
+        <v>333</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12">
+        <v>165.71</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>-1.25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>137</v>
+      </c>
+      <c r="J12">
+        <v>4.47</v>
+      </c>
+      <c r="K12">
+        <v>1.46</v>
+      </c>
+      <c r="L12">
+        <v>7.97</v>
+      </c>
+      <c r="M12" t="s">
+        <v>141</v>
+      </c>
+      <c r="N12">
         <v>96732</v>
       </c>
-      <c r="O10">
+      <c r="O12">
         <v>1639.08</v>
       </c>
-      <c r="P10">
+      <c r="P12">
         <v>15848.82</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="Q12" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13401,7 +13510,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -13421,10 +13530,10 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>40</v>
@@ -13433,16 +13542,16 @@
         <v>304</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>306</v>
@@ -13469,12 +13578,12 @@
         <v>308</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B2" t="s">
         <v>134</v>
@@ -13489,10 +13598,10 @@
         <v>134</v>
       </c>
       <c r="G2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I2" t="s">
         <v>142</v>
@@ -13519,18 +13628,18 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B3" t="s">
         <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -13539,10 +13648,10 @@
         <v>134</v>
       </c>
       <c r="G3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I3" t="s">
         <v>142</v>
@@ -13569,12 +13678,12 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B4" t="s">
         <v>134</v>
@@ -13583,16 +13692,16 @@
         <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E4" t="s">
         <v>134</v>
       </c>
       <c r="G4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I4" t="s">
         <v>142</v>
@@ -13619,12 +13728,12 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B5" t="s">
         <v>134</v>
@@ -13642,7 +13751,7 @@
         <v>622.5499877929688</v>
       </c>
       <c r="G5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H5" t="s">
         <v>323</v>
@@ -13672,18 +13781,18 @@
         <v>1</v>
       </c>
       <c r="Q5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B6" t="s">
         <v>191</v>
       </c>
       <c r="C6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -13695,7 +13804,7 @@
         <v>637.9000244140625</v>
       </c>
       <c r="G6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H6" t="s">
         <v>323</v>
@@ -13725,18 +13834,18 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B7" t="s">
         <v>191</v>
       </c>
       <c r="C7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D7" t="s">
         <v>322</v>
@@ -13748,7 +13857,7 @@
         <v>814.9000244140625</v>
       </c>
       <c r="G7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H7" t="s">
         <v>323</v>
@@ -13778,18 +13887,18 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B8" t="s">
         <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -13801,10 +13910,10 @@
         <v>637.9000244140625</v>
       </c>
       <c r="G8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I8" t="s">
         <v>142</v>
@@ -13831,18 +13940,18 @@
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B9" t="s">
         <v>191</v>
       </c>
       <c r="C9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D9" t="s">
         <v>322</v>
@@ -13854,10 +13963,10 @@
         <v>814.9000244140625</v>
       </c>
       <c r="G9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I9" t="s">
         <v>142</v>
@@ -13884,12 +13993,12 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B10" t="s">
         <v>134</v>
@@ -13907,7 +14016,7 @@
         <v>863.5</v>
       </c>
       <c r="G10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H10" t="s">
         <v>323</v>
@@ -13937,12 +14046,12 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B11" t="s">
         <v>134</v>
@@ -13960,7 +14069,7 @@
         <v>8782.5</v>
       </c>
       <c r="G11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H11" t="s">
         <v>323</v>
@@ -13990,18 +14099,18 @@
         <v>1</v>
       </c>
       <c r="Q11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B12" t="s">
         <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D12" t="s">
         <v>28</v>
@@ -14013,7 +14122,7 @@
         <v>16326</v>
       </c>
       <c r="G12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H12" t="s">
         <v>323</v>
@@ -14043,18 +14152,18 @@
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B13" t="s">
         <v>135</v>
       </c>
       <c r="C13" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D13" t="s">
         <v>28</v>
@@ -14066,10 +14175,10 @@
         <v>527.9000244140625</v>
       </c>
       <c r="G13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I13" t="s">
         <v>142</v>
@@ -14096,18 +14205,18 @@
         <v>1</v>
       </c>
       <c r="Q13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B14" t="s">
         <v>135</v>
       </c>
       <c r="C14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
@@ -14119,10 +14228,10 @@
         <v>23.700000762939453</v>
       </c>
       <c r="G14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I14" t="s">
         <v>142</v>
@@ -14149,18 +14258,18 @@
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B15" t="s">
         <v>135</v>
       </c>
       <c r="C15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D15" t="s">
         <v>322</v>
@@ -14172,10 +14281,10 @@
         <v>813.2000122070312</v>
       </c>
       <c r="G15" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I15" t="s">
         <v>142</v>
@@ -14202,18 +14311,18 @@
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B16" t="s">
         <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D16" t="s">
         <v>322</v>
@@ -14225,10 +14334,10 @@
         <v>806.7000122070312</v>
       </c>
       <c r="G16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I16" t="s">
         <v>142</v>
@@ -14255,21 +14364,21 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B17" t="s">
         <v>134</v>
       </c>
       <c r="C17" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D17" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="E17" t="s">
         <v>134</v>
@@ -14278,7 +14387,7 @@
         <v>1378.300048828125</v>
       </c>
       <c r="G17" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H17" t="s">
         <v>323</v>
@@ -14308,12 +14417,12 @@
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B18" t="s">
         <v>134</v>
@@ -14331,7 +14440,7 @@
         <v>56.9900016784668</v>
       </c>
       <c r="G18" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H18" t="s">
         <v>323</v>
@@ -14361,12 +14470,12 @@
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B19" t="s">
         <v>134</v>
@@ -14384,7 +14493,7 @@
         <v>121</v>
       </c>
       <c r="G19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H19" t="s">
         <v>323</v>
@@ -14414,12 +14523,12 @@
         <v>1</v>
       </c>
       <c r="Q19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B20" t="s">
         <v>134</v>
@@ -14437,7 +14546,7 @@
         <v>5024</v>
       </c>
       <c r="G20" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H20" t="s">
         <v>323</v>
@@ -14467,12 +14576,12 @@
         <v>1</v>
       </c>
       <c r="Q20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B21" t="s">
         <v>134</v>
@@ -14490,7 +14599,7 @@
         <v>156.35000610351562</v>
       </c>
       <c r="G21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H21" t="s">
         <v>323</v>
@@ -14520,12 +14629,12 @@
         <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B22" t="s">
         <v>134</v>
@@ -14543,7 +14652,7 @@
         <v>422.45001220703125</v>
       </c>
       <c r="G22" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H22" t="s">
         <v>323</v>
@@ -14573,7 +14682,7 @@
         <v>1</v>
       </c>
       <c r="Q22" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -14584,10 +14693,10 @@
         <v>134</v>
       </c>
       <c r="C23" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D23" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="E23" t="s">
         <v>134</v>
@@ -14596,10 +14705,10 @@
         <v>1378.300048828125</v>
       </c>
       <c r="G23" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H23" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I23" t="s">
         <v>142</v>
@@ -14626,7 +14735,7 @@
         <v>1</v>
       </c>
       <c r="Q23" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -14649,10 +14758,10 @@
         <v>56.9900016784668</v>
       </c>
       <c r="G24" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H24" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I24" t="s">
         <v>142</v>
@@ -14679,7 +14788,7 @@
         <v>1</v>
       </c>
       <c r="Q24" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -14702,10 +14811,10 @@
         <v>121</v>
       </c>
       <c r="G25" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H25" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I25" t="s">
         <v>142</v>
@@ -14755,10 +14864,10 @@
         <v>5024</v>
       </c>
       <c r="G26" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H26" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I26" t="s">
         <v>142</v>
@@ -14785,7 +14894,7 @@
         <v>1</v>
       </c>
       <c r="Q26" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -14808,10 +14917,10 @@
         <v>156.35000610351562</v>
       </c>
       <c r="G27" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H27" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I27" t="s">
         <v>142</v>
@@ -14838,7 +14947,7 @@
         <v>1</v>
       </c>
       <c r="Q27" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -14861,10 +14970,10 @@
         <v>422.45001220703125</v>
       </c>
       <c r="G28" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H28" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I28" t="s">
         <v>142</v>
@@ -14891,12 +15000,12 @@
         <v>1</v>
       </c>
       <c r="Q28" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B29" t="s">
         <v>135</v>
@@ -14905,16 +15014,16 @@
         <v>324</v>
       </c>
       <c r="D29" t="s">
-        <v>325</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s">
         <v>135</v>
       </c>
       <c r="F29">
-        <v>10166</v>
+        <v>527.9000244140625</v>
       </c>
       <c r="G29" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H29" t="s">
         <v>323</v>
@@ -14923,7 +15032,7 @@
         <v>142</v>
       </c>
       <c r="J29">
-        <v>192.73</v>
+        <v>191.39</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -14932,42 +15041,42 @@
         <v>137</v>
       </c>
       <c r="M29">
-        <v>5.67</v>
+        <v>9.31</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="O29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29">
         <v>1</v>
       </c>
       <c r="Q29" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B30" t="s">
         <v>135</v>
       </c>
       <c r="C30" t="s">
+        <v>326</v>
+      </c>
+      <c r="D30" t="s">
         <v>327</v>
-      </c>
-      <c r="D30" t="s">
-        <v>28</v>
       </c>
       <c r="E30" t="s">
         <v>135</v>
       </c>
       <c r="F30">
-        <v>527.9000244140625</v>
+        <v>10166</v>
       </c>
       <c r="G30" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H30" t="s">
         <v>323</v>
@@ -14976,7 +15085,7 @@
         <v>142</v>
       </c>
       <c r="J30">
-        <v>189.89</v>
+        <v>188.56</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -14985,42 +15094,42 @@
         <v>137</v>
       </c>
       <c r="M30">
-        <v>9.31</v>
+        <v>5.67</v>
       </c>
       <c r="N30">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="P30">
         <v>1</v>
       </c>
       <c r="Q30" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B31" t="s">
         <v>135</v>
       </c>
       <c r="C31" t="s">
+        <v>281</v>
+      </c>
+      <c r="D31" t="s">
         <v>328</v>
-      </c>
-      <c r="D31" t="s">
-        <v>28</v>
       </c>
       <c r="E31" t="s">
         <v>135</v>
       </c>
       <c r="F31">
-        <v>23.700000762939453</v>
+        <v>4442.39990234375</v>
       </c>
       <c r="G31" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H31" t="s">
         <v>323</v>
@@ -15029,7 +15138,7 @@
         <v>142</v>
       </c>
       <c r="J31">
-        <v>185.01</v>
+        <v>186.81</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -15038,10 +15147,10 @@
         <v>137</v>
       </c>
       <c r="M31">
-        <v>10.89</v>
+        <v>5.48</v>
       </c>
       <c r="N31">
-        <v>2.94</v>
+        <v>0.41</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -15050,12 +15159,12 @@
         <v>1</v>
       </c>
       <c r="Q31" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B32" t="s">
         <v>135</v>
@@ -15064,16 +15173,16 @@
         <v>329</v>
       </c>
       <c r="D32" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s">
         <v>135</v>
       </c>
       <c r="F32">
-        <v>813.2000122070312</v>
+        <v>23.700000762939453</v>
       </c>
       <c r="G32" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H32" t="s">
         <v>323</v>
@@ -15082,7 +15191,7 @@
         <v>142</v>
       </c>
       <c r="J32">
-        <v>180.46</v>
+        <v>186.51</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -15091,10 +15200,10 @@
         <v>137</v>
       </c>
       <c r="M32">
-        <v>8.01</v>
+        <v>10.89</v>
       </c>
       <c r="N32">
-        <v>1.96</v>
+        <v>2.94</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -15103,30 +15212,30 @@
         <v>1</v>
       </c>
       <c r="Q32" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C33" t="s">
         <v>330</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>322</v>
       </c>
       <c r="E33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F33">
-        <v>179.52000427246094</v>
+        <v>813.2000122070312</v>
       </c>
       <c r="G33" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H33" t="s">
         <v>323</v>
@@ -15135,7 +15244,7 @@
         <v>142</v>
       </c>
       <c r="J33">
-        <v>177.33</v>
+        <v>181.96</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -15144,10 +15253,10 @@
         <v>137</v>
       </c>
       <c r="M33">
-        <v>2.62</v>
+        <v>8.01</v>
       </c>
       <c r="N33">
-        <v>3.44</v>
+        <v>1.96</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -15156,30 +15265,30 @@
         <v>1</v>
       </c>
       <c r="Q33" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C34" t="s">
         <v>331</v>
       </c>
       <c r="D34" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F34">
-        <v>806.7000122070312</v>
+        <v>179.52000427246094</v>
       </c>
       <c r="G34" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H34" t="s">
         <v>323</v>
@@ -15188,7 +15297,7 @@
         <v>142</v>
       </c>
       <c r="J34">
-        <v>173.98</v>
+        <v>177.33</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -15197,10 +15306,10 @@
         <v>137</v>
       </c>
       <c r="M34">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="N34">
-        <v>1.14</v>
+        <v>3.44</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -15209,7 +15318,113 @@
         <v>1</v>
       </c>
       <c r="Q34" t="s">
-        <v>326</v>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>360</v>
+      </c>
+      <c r="B35" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35" t="s">
+        <v>332</v>
+      </c>
+      <c r="D35" t="s">
+        <v>322</v>
+      </c>
+      <c r="E35" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35">
+        <v>806.7000122070312</v>
+      </c>
+      <c r="G35" t="s">
+        <v>346</v>
+      </c>
+      <c r="H35" t="s">
+        <v>323</v>
+      </c>
+      <c r="I35" t="s">
+        <v>142</v>
+      </c>
+      <c r="J35">
+        <v>175.48</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35" t="s">
+        <v>137</v>
+      </c>
+      <c r="M35">
+        <v>3.05</v>
+      </c>
+      <c r="N35">
+        <v>1.14</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>360</v>
+      </c>
+      <c r="B36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" t="s">
+        <v>299</v>
+      </c>
+      <c r="D36" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" t="s">
+        <v>135</v>
+      </c>
+      <c r="F36">
+        <v>739.3499755859375</v>
+      </c>
+      <c r="G36" t="s">
+        <v>346</v>
+      </c>
+      <c r="H36" t="s">
+        <v>323</v>
+      </c>
+      <c r="I36" t="s">
+        <v>142</v>
+      </c>
+      <c r="J36">
+        <v>175.03</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36" t="s">
+        <v>137</v>
+      </c>
+      <c r="M36">
+        <v>8.15</v>
+      </c>
+      <c r="N36">
+        <v>0.93</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -15233,30 +15448,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -15268,7 +15483,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-15T04:00:50.511Z</t>
+    <t>2026-07-15T05:17:28.521Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1004,12 +1004,12 @@
     <t>Automobile and Auto Components</t>
   </si>
   <si>
+    <t>CJGEL</t>
+  </si>
+  <si>
     <t>Capital Goods</t>
   </si>
   <si>
-    <t>CJGEL</t>
-  </si>
-  <si>
     <t>ASTERDM</t>
   </si>
   <si>
@@ -1100,7 +1100,7 @@
     <t>Latest completed-candle status is WATCH, not ENTRY. Current setup grade WATCH no longer passes the selected trade-quality filter. Current/09:17 price is below daily Supertrend.</t>
   </si>
   <si>
-    <t>2026-07-15T04:00:49.945Z</t>
+    <t>2026-07-15T05:17:28.079Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -4851,7 +4851,7 @@
         <v>137</v>
       </c>
       <c r="AG11">
-        <v>184.22</v>
+        <v>185.72</v>
       </c>
       <c r="AH11">
         <v>1842.85</v>
@@ -6676,7 +6676,7 @@
         <v>168.93</v>
       </c>
       <c r="AG2">
-        <v>59.58</v>
+        <v>61.08</v>
       </c>
       <c r="AH2">
         <v>19.01</v>
@@ -10326,7 +10326,7 @@
         <v>137</v>
       </c>
       <c r="AG11">
-        <v>184.22</v>
+        <v>185.72</v>
       </c>
       <c r="AH11">
         <v>1842.85</v>
@@ -11776,7 +11776,7 @@
         <v>168.93</v>
       </c>
       <c r="AG16">
-        <v>59.58</v>
+        <v>61.08</v>
       </c>
       <c r="AH16">
         <v>19.01</v>
@@ -12935,7 +12935,7 @@
         <v>142</v>
       </c>
       <c r="F2">
-        <v>220.14</v>
+        <v>221.64</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -12953,7 +12953,7 @@
         <v>2.72</v>
       </c>
       <c r="L2">
-        <v>2.17</v>
+        <v>0.67</v>
       </c>
       <c r="M2" t="s">
         <v>164</v>
@@ -13041,7 +13041,7 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>191.39</v>
+        <v>192.89</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -13135,10 +13135,10 @@
         <v>323</v>
       </c>
       <c r="B6" t="s">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="C6" t="s">
-        <v>328</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>135</v>
@@ -13147,7 +13147,7 @@
         <v>142</v>
       </c>
       <c r="F6">
-        <v>186.81</v>
+        <v>188.01</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -13159,10 +13159,10 @@
         <v>137</v>
       </c>
       <c r="J6">
-        <v>5.48</v>
+        <v>10.89</v>
       </c>
       <c r="K6">
-        <v>0.41</v>
+        <v>2.94</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -13171,13 +13171,13 @@
         <v>141</v>
       </c>
       <c r="N6">
-        <v>97732.8</v>
+        <v>99990.3</v>
       </c>
       <c r="O6">
-        <v>1466.08</v>
+        <v>5695.65</v>
       </c>
       <c r="P6">
-        <v>4375.76</v>
+        <v>22.35</v>
       </c>
       <c r="Q6" t="s">
         <v>325</v>
@@ -13188,10 +13188,10 @@
         <v>323</v>
       </c>
       <c r="B7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C7" t="s">
         <v>329</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
       </c>
       <c r="D7" t="s">
         <v>135</v>
@@ -13200,7 +13200,7 @@
         <v>142</v>
       </c>
       <c r="F7">
-        <v>186.51</v>
+        <v>186.14</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -13212,25 +13212,25 @@
         <v>137</v>
       </c>
       <c r="J7">
-        <v>10.89</v>
+        <v>5.48</v>
       </c>
       <c r="K7">
-        <v>2.94</v>
+        <v>0.41</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="M7" t="s">
         <v>141</v>
       </c>
       <c r="N7">
-        <v>99990.3</v>
+        <v>97732.8</v>
       </c>
       <c r="O7">
-        <v>5695.65</v>
+        <v>1466.08</v>
       </c>
       <c r="P7">
-        <v>22.35</v>
+        <v>4375.76</v>
       </c>
       <c r="Q7" t="s">
         <v>325</v>
@@ -13253,7 +13253,7 @@
         <v>142</v>
       </c>
       <c r="F8">
-        <v>181.96</v>
+        <v>183.46</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -13359,7 +13359,7 @@
         <v>142</v>
       </c>
       <c r="F10">
-        <v>175.48</v>
+        <v>176.98</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -13465,7 +13465,7 @@
         <v>142</v>
       </c>
       <c r="F12">
-        <v>165.71</v>
+        <v>167.21</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -13483,7 +13483,7 @@
         <v>1.46</v>
       </c>
       <c r="L12">
-        <v>7.97</v>
+        <v>6.47</v>
       </c>
       <c r="M12" t="s">
         <v>141</v>
@@ -14216,7 +14216,7 @@
         <v>135</v>
       </c>
       <c r="C14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
@@ -14378,7 +14378,7 @@
         <v>352</v>
       </c>
       <c r="D17" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E17" t="s">
         <v>134</v>
@@ -14696,7 +14696,7 @@
         <v>352</v>
       </c>
       <c r="D23" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E23" t="s">
         <v>134</v>
@@ -15032,7 +15032,7 @@
         <v>142</v>
       </c>
       <c r="J29">
-        <v>191.39</v>
+        <v>192.89</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -15117,16 +15117,16 @@
         <v>135</v>
       </c>
       <c r="C31" t="s">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="D31" t="s">
-        <v>328</v>
+        <v>28</v>
       </c>
       <c r="E31" t="s">
         <v>135</v>
       </c>
       <c r="F31">
-        <v>4442.39990234375</v>
+        <v>23.700000762939453</v>
       </c>
       <c r="G31" t="s">
         <v>346</v>
@@ -15138,7 +15138,7 @@
         <v>142</v>
       </c>
       <c r="J31">
-        <v>186.81</v>
+        <v>188.01</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -15147,10 +15147,10 @@
         <v>137</v>
       </c>
       <c r="M31">
-        <v>5.48</v>
+        <v>10.89</v>
       </c>
       <c r="N31">
-        <v>0.41</v>
+        <v>2.94</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -15170,16 +15170,16 @@
         <v>135</v>
       </c>
       <c r="C32" t="s">
+        <v>281</v>
+      </c>
+      <c r="D32" t="s">
         <v>329</v>
-      </c>
-      <c r="D32" t="s">
-        <v>28</v>
       </c>
       <c r="E32" t="s">
         <v>135</v>
       </c>
       <c r="F32">
-        <v>23.700000762939453</v>
+        <v>4442.39990234375</v>
       </c>
       <c r="G32" t="s">
         <v>346</v>
@@ -15191,7 +15191,7 @@
         <v>142</v>
       </c>
       <c r="J32">
-        <v>186.51</v>
+        <v>186.14</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -15200,13 +15200,13 @@
         <v>137</v>
       </c>
       <c r="M32">
-        <v>10.89</v>
+        <v>5.48</v>
       </c>
       <c r="N32">
-        <v>2.94</v>
+        <v>0.41</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="P32">
         <v>1</v>
@@ -15244,7 +15244,7 @@
         <v>142</v>
       </c>
       <c r="J33">
-        <v>181.96</v>
+        <v>183.46</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -15350,7 +15350,7 @@
         <v>142</v>
       </c>
       <c r="J35">
-        <v>175.48</v>
+        <v>176.98</v>
       </c>
       <c r="K35">
         <v>0</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3264" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3262" uniqueCount="380">
   <si>
     <t>Metric</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-15T05:51:18.530Z</t>
+    <t>2026-07-15T05:58:04.586Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -434,6 +434,12 @@
     <t>No</t>
   </si>
   <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>TREND RIDE: weekly/daily leadership and price structure remain healthy; trail the stop instead of cutting the winner.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PASS; </t>
   </si>
   <si>
@@ -509,12 +515,6 @@
     <t>2026-07-13</t>
   </si>
   <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>TREND RIDE: weekly/daily leadership and price structure remain healthy; trail the stop instead of cutting the winner.</t>
-  </si>
-  <si>
     <t>Trend continuation buy</t>
   </si>
   <si>
@@ -1037,12 +1037,12 @@
     <t>Automobile and Auto Components</t>
   </si>
   <si>
+    <t>ASTERDM</t>
+  </si>
+  <si>
     <t>Capital Goods</t>
   </si>
   <si>
-    <t>ASTERDM</t>
-  </si>
-  <si>
     <t>KIMS</t>
   </si>
   <si>
@@ -1130,7 +1130,7 @@
     <t>Latest completed-candle status is WATCH, not ENTRY. Current setup grade WATCH no longer passes the selected trade-quality filter. Current/09:17 price is below daily Supertrend.</t>
   </si>
   <si>
-    <t>2026-07-15T05:51:17.690Z</t>
+    <t>2026-07-15T05:58:03.939Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -1588,7 +1588,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>996624.38</v>
+        <v>988147.86</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1612,7 +1612,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>62662.59</v>
+        <v>58131.15</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1620,7 +1620,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>66607.67</v>
+        <v>58131.15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1652,7 +1652,7 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>0.34</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2282,8 +2282,8 @@
       <c r="AJ2">
         <v>7959.6</v>
       </c>
-      <c r="AK2" t="s">
-        <v>136</v>
+      <c r="AK2">
+        <v>-0.23</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -2331,10 +2331,10 @@
         <v>136</v>
       </c>
       <c r="BA2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BB2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="BC2">
         <v>0</v>
@@ -2343,13 +2343,13 @@
         <v>136</v>
       </c>
       <c r="BE2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BF2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="BG2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH2">
         <v>25</v>
@@ -2358,10 +2358,10 @@
         <v>4</v>
       </c>
       <c r="BJ2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BK2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BL2" t="s">
         <v>136</v>
@@ -2373,49 +2373,49 @@
         <v>137</v>
       </c>
       <c r="BO2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BP2" t="s">
         <v>136</v>
       </c>
       <c r="BQ2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BV2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BW2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BX2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BY2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BZ2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="CB2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CD2">
         <v>3.69</v>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="CI2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="CJ2">
         <v>1.6</v>
@@ -2445,7 +2445,7 @@
         <v>3.69</v>
       </c>
       <c r="CM2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CN2">
         <v>822.4</v>
@@ -2457,7 +2457,7 @@
         <v>794</v>
       </c>
       <c r="CQ2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="CR2" t="s">
         <v>136</v>
@@ -2471,19 +2471,19 @@
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
         <v>132</v>
       </c>
       <c r="G3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H3" t="s">
         <v>133</v>
@@ -2621,10 +2621,10 @@
         <v>136</v>
       </c>
       <c r="BA3" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB3" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="BC3">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         <v>136</v>
       </c>
       <c r="BE3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BF3" t="s">
         <v>165</v>
       </c>
       <c r="BG3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH3">
         <v>15</v>
@@ -2648,7 +2648,7 @@
         <v>4</v>
       </c>
       <c r="BJ3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BK3" t="s">
         <v>166</v>
@@ -2663,22 +2663,22 @@
         <v>137</v>
       </c>
       <c r="BO3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BP3" t="s">
         <v>136</v>
       </c>
       <c r="BQ3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU3" t="s">
         <v>168</v>
@@ -2696,13 +2696,13 @@
         <v>172</v>
       </c>
       <c r="BZ3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA3" t="s">
         <v>173</v>
       </c>
       <c r="CB3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC3" t="s">
         <v>137</v>
@@ -2761,7 +2761,7 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
         <v>177</v>
@@ -2773,7 +2773,7 @@
         <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H4" t="s">
         <v>133</v>
@@ -2911,7 +2911,7 @@
         <v>136</v>
       </c>
       <c r="BA4" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB4" t="s">
         <v>136</v>
@@ -2923,13 +2923,13 @@
         <v>136</v>
       </c>
       <c r="BE4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BF4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="BG4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH4">
         <v>22</v>
@@ -2941,7 +2941,7 @@
         <v>179</v>
       </c>
       <c r="BK4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BL4" t="s">
         <v>136</v>
@@ -2953,22 +2953,22 @@
         <v>137</v>
       </c>
       <c r="BO4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BP4" t="s">
         <v>136</v>
       </c>
       <c r="BQ4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU4" t="s">
         <v>180</v>
@@ -2986,16 +2986,16 @@
         <v>172</v>
       </c>
       <c r="BZ4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA4" t="s">
         <v>184</v>
       </c>
       <c r="CB4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CD4">
         <v>90.28</v>
@@ -3025,7 +3025,7 @@
         <v>90.28</v>
       </c>
       <c r="CM4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CN4">
         <v>556.8</v>
@@ -3063,7 +3063,7 @@
         <v>132</v>
       </c>
       <c r="G5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H5" t="s">
         <v>133</v>
@@ -3201,7 +3201,7 @@
         <v>136</v>
       </c>
       <c r="BA5" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB5" t="s">
         <v>189</v>
@@ -3213,13 +3213,13 @@
         <v>136</v>
       </c>
       <c r="BE5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BF5" t="s">
         <v>190</v>
       </c>
       <c r="BG5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH5">
         <v>19</v>
@@ -3231,7 +3231,7 @@
         <v>179</v>
       </c>
       <c r="BK5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BL5" t="s">
         <v>191</v>
@@ -3243,22 +3243,22 @@
         <v>137</v>
       </c>
       <c r="BO5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BP5" t="s">
         <v>136</v>
       </c>
       <c r="BQ5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU5" t="s">
         <v>180</v>
@@ -3273,16 +3273,16 @@
         <v>195</v>
       </c>
       <c r="BY5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BZ5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA5" t="s">
         <v>196</v>
       </c>
       <c r="CB5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC5" t="s">
         <v>137</v>
@@ -3303,7 +3303,7 @@
         <v>1.87</v>
       </c>
       <c r="CI5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="CJ5">
         <v>1.91</v>
@@ -3341,7 +3341,7 @@
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D6" t="s">
         <v>199</v>
@@ -3356,7 +3356,7 @@
         <v>201</v>
       </c>
       <c r="H6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I6" t="s">
         <v>36</v>
@@ -3491,10 +3491,10 @@
         <v>136</v>
       </c>
       <c r="BA6" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB6" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="BC6">
         <v>0</v>
@@ -3509,7 +3509,7 @@
         <v>202</v>
       </c>
       <c r="BG6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH6">
         <v>14</v>
@@ -3539,16 +3539,16 @@
         <v>136</v>
       </c>
       <c r="BQ6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU6" t="s">
         <v>168</v>
@@ -3566,13 +3566,13 @@
         <v>172</v>
       </c>
       <c r="BZ6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA6" t="s">
         <v>208</v>
       </c>
       <c r="CB6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC6" t="s">
         <v>137</v>
@@ -3587,7 +3587,7 @@
         <v>5.2</v>
       </c>
       <c r="CG6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CH6">
         <v>6.4</v>
@@ -3631,7 +3631,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D7" t="s">
         <v>210</v>
@@ -3646,7 +3646,7 @@
         <v>201</v>
       </c>
       <c r="H7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I7" t="s">
         <v>36</v>
@@ -3781,7 +3781,7 @@
         <v>136</v>
       </c>
       <c r="BA7" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB7" t="s">
         <v>136</v>
@@ -3799,7 +3799,7 @@
         <v>165</v>
       </c>
       <c r="BG7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH7">
         <v>12</v>
@@ -3829,16 +3829,16 @@
         <v>136</v>
       </c>
       <c r="BQ7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU7" t="s">
         <v>168</v>
@@ -3856,13 +3856,13 @@
         <v>172</v>
       </c>
       <c r="BZ7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA7" t="s">
         <v>208</v>
       </c>
       <c r="CB7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC7" t="s">
         <v>137</v>
@@ -3921,7 +3921,7 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D8" t="s">
         <v>216</v>
@@ -3936,7 +3936,7 @@
         <v>201</v>
       </c>
       <c r="H8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I8" t="s">
         <v>36</v>
@@ -4071,7 +4071,7 @@
         <v>136</v>
       </c>
       <c r="BA8" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB8" t="s">
         <v>136</v>
@@ -4098,7 +4098,7 @@
         <v>4</v>
       </c>
       <c r="BJ8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BK8" t="s">
         <v>219</v>
@@ -4122,13 +4122,13 @@
         <v>136</v>
       </c>
       <c r="BR8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU8" t="s">
         <v>168</v>
@@ -4143,16 +4143,16 @@
         <v>225</v>
       </c>
       <c r="BY8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BZ8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA8" t="s">
         <v>226</v>
       </c>
       <c r="CB8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC8" t="s">
         <v>137</v>
@@ -4211,7 +4211,7 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D9" t="s">
         <v>228</v>
@@ -4226,7 +4226,7 @@
         <v>201</v>
       </c>
       <c r="H9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -4361,7 +4361,7 @@
         <v>136</v>
       </c>
       <c r="BA9" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB9" t="s">
         <v>136</v>
@@ -4379,7 +4379,7 @@
         <v>165</v>
       </c>
       <c r="BG9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH9">
         <v>11</v>
@@ -4412,13 +4412,13 @@
         <v>233</v>
       </c>
       <c r="BR9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU9" t="s">
         <v>168</v>
@@ -4436,13 +4436,13 @@
         <v>172</v>
       </c>
       <c r="BZ9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA9" t="s">
         <v>208</v>
       </c>
       <c r="CB9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC9" t="s">
         <v>137</v>
@@ -4475,7 +4475,7 @@
         <v>0.3</v>
       </c>
       <c r="CM9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CN9">
         <v>2002.3</v>
@@ -4651,7 +4651,7 @@
         <v>136</v>
       </c>
       <c r="BA10" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB10" t="s">
         <v>240</v>
@@ -4669,7 +4669,7 @@
         <v>136</v>
       </c>
       <c r="BG10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH10">
         <v>11</v>
@@ -4702,13 +4702,13 @@
         <v>136</v>
       </c>
       <c r="BR10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU10" t="s">
         <v>168</v>
@@ -4732,7 +4732,7 @@
         <v>247</v>
       </c>
       <c r="CB10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC10" t="s">
         <v>137</v>
@@ -4941,7 +4941,7 @@
         <v>136</v>
       </c>
       <c r="BA11" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB11" t="s">
         <v>136</v>
@@ -4959,7 +4959,7 @@
         <v>136</v>
       </c>
       <c r="BG11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH11">
         <v>15</v>
@@ -4992,13 +4992,13 @@
         <v>136</v>
       </c>
       <c r="BR11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU11" t="s">
         <v>168</v>
@@ -5022,7 +5022,7 @@
         <v>247</v>
       </c>
       <c r="CB11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC11" t="s">
         <v>137</v>
@@ -5055,7 +5055,7 @@
         <v>136</v>
       </c>
       <c r="CM11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CN11">
         <v>6202.5</v>
@@ -5171,7 +5171,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>187.22</v>
+        <v>188.72</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -5231,10 +5231,10 @@
         <v>136</v>
       </c>
       <c r="BA12" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB12" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="BC12">
         <v>0</v>
@@ -5249,7 +5249,7 @@
         <v>136</v>
       </c>
       <c r="BG12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH12">
         <v>14</v>
@@ -5282,13 +5282,13 @@
         <v>136</v>
       </c>
       <c r="BR12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU12" t="s">
         <v>168</v>
@@ -5312,7 +5312,7 @@
         <v>247</v>
       </c>
       <c r="CB12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC12" t="s">
         <v>137</v>
@@ -5521,10 +5521,10 @@
         <v>136</v>
       </c>
       <c r="BA13" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB13" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="BC13">
         <v>0</v>
@@ -5539,7 +5539,7 @@
         <v>136</v>
       </c>
       <c r="BG13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH13">
         <v>13</v>
@@ -5572,13 +5572,13 @@
         <v>136</v>
       </c>
       <c r="BR13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU13" t="s">
         <v>168</v>
@@ -5602,7 +5602,7 @@
         <v>247</v>
       </c>
       <c r="CB13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC13" t="s">
         <v>137</v>
@@ -5811,10 +5811,10 @@
         <v>136</v>
       </c>
       <c r="BA14" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB14" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="BC14">
         <v>0</v>
@@ -5829,7 +5829,7 @@
         <v>136</v>
       </c>
       <c r="BG14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH14">
         <v>13</v>
@@ -5862,13 +5862,13 @@
         <v>136</v>
       </c>
       <c r="BR14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU14" t="s">
         <v>168</v>
@@ -5892,7 +5892,7 @@
         <v>247</v>
       </c>
       <c r="CB14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC14" t="s">
         <v>137</v>
@@ -6101,7 +6101,7 @@
         <v>136</v>
       </c>
       <c r="BA15" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB15" t="s">
         <v>136</v>
@@ -6119,7 +6119,7 @@
         <v>136</v>
       </c>
       <c r="BG15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH15">
         <v>12</v>
@@ -6152,13 +6152,13 @@
         <v>136</v>
       </c>
       <c r="BR15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU15" t="s">
         <v>168</v>
@@ -6182,7 +6182,7 @@
         <v>247</v>
       </c>
       <c r="CB15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC15" t="s">
         <v>137</v>
@@ -6391,7 +6391,7 @@
         <v>136</v>
       </c>
       <c r="BA16" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB16" t="s">
         <v>136</v>
@@ -6409,7 +6409,7 @@
         <v>136</v>
       </c>
       <c r="BG16" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH16">
         <v>13</v>
@@ -6442,13 +6442,13 @@
         <v>136</v>
       </c>
       <c r="BR16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS16" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU16" t="s">
         <v>168</v>
@@ -6472,7 +6472,7 @@
         <v>247</v>
       </c>
       <c r="CB16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC16" t="s">
         <v>137</v>
@@ -7296,7 +7296,7 @@
         <v>201</v>
       </c>
       <c r="H2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I2" t="s">
         <v>36</v>
@@ -7443,13 +7443,13 @@
         <v>136</v>
       </c>
       <c r="BE2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BF2" t="s">
         <v>165</v>
       </c>
       <c r="BG2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH2">
         <v>16</v>
@@ -7458,10 +7458,10 @@
         <v>4</v>
       </c>
       <c r="BJ2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BK2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BL2" t="s">
         <v>136</v>
@@ -7473,22 +7473,22 @@
         <v>137</v>
       </c>
       <c r="BO2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BP2" t="s">
         <v>136</v>
       </c>
       <c r="BQ2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU2" t="s">
         <v>180</v>
@@ -7506,7 +7506,7 @@
         <v>288</v>
       </c>
       <c r="BZ2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA2" t="s">
         <v>196</v>
@@ -8047,8 +8047,8 @@
       <c r="AJ2">
         <v>7959.6</v>
       </c>
-      <c r="AK2" t="s">
-        <v>136</v>
+      <c r="AK2">
+        <v>-0.23</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         <v>136</v>
       </c>
       <c r="BA2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BB2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="BC2">
         <v>0</v>
@@ -8108,13 +8108,13 @@
         <v>136</v>
       </c>
       <c r="BE2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BF2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="BG2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH2">
         <v>25</v>
@@ -8123,10 +8123,10 @@
         <v>4</v>
       </c>
       <c r="BJ2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BK2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BL2" t="s">
         <v>136</v>
@@ -8138,49 +8138,49 @@
         <v>137</v>
       </c>
       <c r="BO2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BP2" t="s">
         <v>136</v>
       </c>
       <c r="BQ2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BV2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BW2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BX2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BY2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BZ2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="CB2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CD2">
         <v>3.69</v>
@@ -8198,7 +8198,7 @@
         <v>0</v>
       </c>
       <c r="CI2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="CJ2">
         <v>1.6</v>
@@ -8210,7 +8210,7 @@
         <v>3.69</v>
       </c>
       <c r="CM2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CN2">
         <v>822.4</v>
@@ -8222,7 +8222,7 @@
         <v>794</v>
       </c>
       <c r="CQ2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="CR2" t="s">
         <v>136</v>
@@ -8236,19 +8236,19 @@
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
         <v>132</v>
       </c>
       <c r="G3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H3" t="s">
         <v>133</v>
@@ -8386,10 +8386,10 @@
         <v>136</v>
       </c>
       <c r="BA3" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB3" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="BC3">
         <v>0</v>
@@ -8398,13 +8398,13 @@
         <v>136</v>
       </c>
       <c r="BE3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BF3" t="s">
         <v>165</v>
       </c>
       <c r="BG3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH3">
         <v>15</v>
@@ -8413,7 +8413,7 @@
         <v>4</v>
       </c>
       <c r="BJ3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BK3" t="s">
         <v>166</v>
@@ -8428,22 +8428,22 @@
         <v>137</v>
       </c>
       <c r="BO3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BP3" t="s">
         <v>136</v>
       </c>
       <c r="BQ3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU3" t="s">
         <v>168</v>
@@ -8461,13 +8461,13 @@
         <v>172</v>
       </c>
       <c r="BZ3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA3" t="s">
         <v>173</v>
       </c>
       <c r="CB3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC3" t="s">
         <v>137</v>
@@ -8526,7 +8526,7 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
         <v>177</v>
@@ -8538,7 +8538,7 @@
         <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H4" t="s">
         <v>133</v>
@@ -8676,7 +8676,7 @@
         <v>136</v>
       </c>
       <c r="BA4" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB4" t="s">
         <v>136</v>
@@ -8688,13 +8688,13 @@
         <v>136</v>
       </c>
       <c r="BE4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BF4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="BG4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH4">
         <v>22</v>
@@ -8706,7 +8706,7 @@
         <v>179</v>
       </c>
       <c r="BK4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BL4" t="s">
         <v>136</v>
@@ -8718,22 +8718,22 @@
         <v>137</v>
       </c>
       <c r="BO4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BP4" t="s">
         <v>136</v>
       </c>
       <c r="BQ4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU4" t="s">
         <v>180</v>
@@ -8751,16 +8751,16 @@
         <v>172</v>
       </c>
       <c r="BZ4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA4" t="s">
         <v>184</v>
       </c>
       <c r="CB4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CD4">
         <v>90.28</v>
@@ -8790,7 +8790,7 @@
         <v>90.28</v>
       </c>
       <c r="CM4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CN4">
         <v>556.8</v>
@@ -8828,7 +8828,7 @@
         <v>132</v>
       </c>
       <c r="G5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H5" t="s">
         <v>133</v>
@@ -8966,7 +8966,7 @@
         <v>136</v>
       </c>
       <c r="BA5" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB5" t="s">
         <v>189</v>
@@ -8978,13 +8978,13 @@
         <v>136</v>
       </c>
       <c r="BE5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BF5" t="s">
         <v>190</v>
       </c>
       <c r="BG5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH5">
         <v>19</v>
@@ -8996,7 +8996,7 @@
         <v>179</v>
       </c>
       <c r="BK5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BL5" t="s">
         <v>191</v>
@@ -9008,22 +9008,22 @@
         <v>137</v>
       </c>
       <c r="BO5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BP5" t="s">
         <v>136</v>
       </c>
       <c r="BQ5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU5" t="s">
         <v>180</v>
@@ -9038,16 +9038,16 @@
         <v>195</v>
       </c>
       <c r="BY5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BZ5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA5" t="s">
         <v>196</v>
       </c>
       <c r="CB5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC5" t="s">
         <v>137</v>
@@ -9068,7 +9068,7 @@
         <v>1.87</v>
       </c>
       <c r="CI5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="CJ5">
         <v>1.91</v>
@@ -9106,7 +9106,7 @@
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D6" t="s">
         <v>199</v>
@@ -9121,7 +9121,7 @@
         <v>201</v>
       </c>
       <c r="H6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I6" t="s">
         <v>36</v>
@@ -9256,10 +9256,10 @@
         <v>136</v>
       </c>
       <c r="BA6" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB6" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="BC6">
         <v>0</v>
@@ -9274,7 +9274,7 @@
         <v>202</v>
       </c>
       <c r="BG6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH6">
         <v>14</v>
@@ -9304,16 +9304,16 @@
         <v>136</v>
       </c>
       <c r="BQ6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU6" t="s">
         <v>168</v>
@@ -9331,13 +9331,13 @@
         <v>172</v>
       </c>
       <c r="BZ6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA6" t="s">
         <v>208</v>
       </c>
       <c r="CB6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC6" t="s">
         <v>137</v>
@@ -9352,7 +9352,7 @@
         <v>5.2</v>
       </c>
       <c r="CG6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CH6">
         <v>6.4</v>
@@ -9396,7 +9396,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D7" t="s">
         <v>210</v>
@@ -9411,7 +9411,7 @@
         <v>201</v>
       </c>
       <c r="H7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I7" t="s">
         <v>36</v>
@@ -9546,7 +9546,7 @@
         <v>136</v>
       </c>
       <c r="BA7" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB7" t="s">
         <v>136</v>
@@ -9564,7 +9564,7 @@
         <v>165</v>
       </c>
       <c r="BG7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH7">
         <v>12</v>
@@ -9594,16 +9594,16 @@
         <v>136</v>
       </c>
       <c r="BQ7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU7" t="s">
         <v>168</v>
@@ -9621,13 +9621,13 @@
         <v>172</v>
       </c>
       <c r="BZ7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA7" t="s">
         <v>208</v>
       </c>
       <c r="CB7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC7" t="s">
         <v>137</v>
@@ -9686,7 +9686,7 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D8" t="s">
         <v>216</v>
@@ -9701,7 +9701,7 @@
         <v>201</v>
       </c>
       <c r="H8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I8" t="s">
         <v>36</v>
@@ -9836,7 +9836,7 @@
         <v>136</v>
       </c>
       <c r="BA8" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB8" t="s">
         <v>136</v>
@@ -9863,7 +9863,7 @@
         <v>4</v>
       </c>
       <c r="BJ8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BK8" t="s">
         <v>219</v>
@@ -9887,13 +9887,13 @@
         <v>136</v>
       </c>
       <c r="BR8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU8" t="s">
         <v>168</v>
@@ -9908,16 +9908,16 @@
         <v>225</v>
       </c>
       <c r="BY8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BZ8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA8" t="s">
         <v>226</v>
       </c>
       <c r="CB8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC8" t="s">
         <v>137</v>
@@ -9976,7 +9976,7 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D9" t="s">
         <v>228</v>
@@ -9991,7 +9991,7 @@
         <v>201</v>
       </c>
       <c r="H9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -10126,7 +10126,7 @@
         <v>136</v>
       </c>
       <c r="BA9" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB9" t="s">
         <v>136</v>
@@ -10144,7 +10144,7 @@
         <v>165</v>
       </c>
       <c r="BG9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH9">
         <v>11</v>
@@ -10177,13 +10177,13 @@
         <v>233</v>
       </c>
       <c r="BR9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU9" t="s">
         <v>168</v>
@@ -10201,13 +10201,13 @@
         <v>172</v>
       </c>
       <c r="BZ9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA9" t="s">
         <v>208</v>
       </c>
       <c r="CB9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC9" t="s">
         <v>137</v>
@@ -10240,7 +10240,7 @@
         <v>0.3</v>
       </c>
       <c r="CM9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CN9">
         <v>2002.3</v>
@@ -10416,7 +10416,7 @@
         <v>136</v>
       </c>
       <c r="BA10" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB10" t="s">
         <v>240</v>
@@ -10434,7 +10434,7 @@
         <v>136</v>
       </c>
       <c r="BG10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH10">
         <v>11</v>
@@ -10467,13 +10467,13 @@
         <v>136</v>
       </c>
       <c r="BR10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU10" t="s">
         <v>168</v>
@@ -10497,7 +10497,7 @@
         <v>247</v>
       </c>
       <c r="CB10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC10" t="s">
         <v>137</v>
@@ -10706,7 +10706,7 @@
         <v>136</v>
       </c>
       <c r="BA11" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB11" t="s">
         <v>136</v>
@@ -10724,7 +10724,7 @@
         <v>136</v>
       </c>
       <c r="BG11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH11">
         <v>15</v>
@@ -10757,13 +10757,13 @@
         <v>136</v>
       </c>
       <c r="BR11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU11" t="s">
         <v>168</v>
@@ -10787,7 +10787,7 @@
         <v>247</v>
       </c>
       <c r="CB11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC11" t="s">
         <v>137</v>
@@ -10820,7 +10820,7 @@
         <v>136</v>
       </c>
       <c r="CM11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CN11">
         <v>6202.5</v>
@@ -10936,7 +10936,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>187.22</v>
+        <v>188.72</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -10996,10 +10996,10 @@
         <v>136</v>
       </c>
       <c r="BA12" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB12" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="BC12">
         <v>0</v>
@@ -11014,7 +11014,7 @@
         <v>136</v>
       </c>
       <c r="BG12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH12">
         <v>14</v>
@@ -11047,13 +11047,13 @@
         <v>136</v>
       </c>
       <c r="BR12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU12" t="s">
         <v>168</v>
@@ -11077,7 +11077,7 @@
         <v>247</v>
       </c>
       <c r="CB12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC12" t="s">
         <v>137</v>
@@ -11286,10 +11286,10 @@
         <v>136</v>
       </c>
       <c r="BA13" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB13" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="BC13">
         <v>0</v>
@@ -11304,7 +11304,7 @@
         <v>136</v>
       </c>
       <c r="BG13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH13">
         <v>13</v>
@@ -11337,13 +11337,13 @@
         <v>136</v>
       </c>
       <c r="BR13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU13" t="s">
         <v>168</v>
@@ -11367,7 +11367,7 @@
         <v>247</v>
       </c>
       <c r="CB13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC13" t="s">
         <v>137</v>
@@ -11576,10 +11576,10 @@
         <v>136</v>
       </c>
       <c r="BA14" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB14" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="BC14">
         <v>0</v>
@@ -11594,7 +11594,7 @@
         <v>136</v>
       </c>
       <c r="BG14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH14">
         <v>13</v>
@@ -11627,13 +11627,13 @@
         <v>136</v>
       </c>
       <c r="BR14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU14" t="s">
         <v>168</v>
@@ -11657,7 +11657,7 @@
         <v>247</v>
       </c>
       <c r="CB14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC14" t="s">
         <v>137</v>
@@ -11866,7 +11866,7 @@
         <v>136</v>
       </c>
       <c r="BA15" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB15" t="s">
         <v>136</v>
@@ -11884,7 +11884,7 @@
         <v>136</v>
       </c>
       <c r="BG15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH15">
         <v>12</v>
@@ -11917,13 +11917,13 @@
         <v>136</v>
       </c>
       <c r="BR15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU15" t="s">
         <v>168</v>
@@ -11947,7 +11947,7 @@
         <v>247</v>
       </c>
       <c r="CB15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC15" t="s">
         <v>137</v>
@@ -12156,7 +12156,7 @@
         <v>136</v>
       </c>
       <c r="BA16" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="BB16" t="s">
         <v>136</v>
@@ -12174,7 +12174,7 @@
         <v>136</v>
       </c>
       <c r="BG16" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH16">
         <v>13</v>
@@ -12207,13 +12207,13 @@
         <v>136</v>
       </c>
       <c r="BR16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS16" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU16" t="s">
         <v>168</v>
@@ -12237,7 +12237,7 @@
         <v>247</v>
       </c>
       <c r="CB16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC16" t="s">
         <v>137</v>
@@ -12311,7 +12311,7 @@
         <v>201</v>
       </c>
       <c r="H17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I17" t="s">
         <v>36</v>
@@ -12458,13 +12458,13 @@
         <v>136</v>
       </c>
       <c r="BE17" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BF17" t="s">
         <v>165</v>
       </c>
       <c r="BG17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH17">
         <v>16</v>
@@ -12473,10 +12473,10 @@
         <v>4</v>
       </c>
       <c r="BJ17" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BK17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BL17" t="s">
         <v>136</v>
@@ -12488,22 +12488,22 @@
         <v>137</v>
       </c>
       <c r="BO17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BP17" t="s">
         <v>136</v>
       </c>
       <c r="BQ17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU17" t="s">
         <v>180</v>
@@ -12521,7 +12521,7 @@
         <v>288</v>
       </c>
       <c r="BZ17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CA17" t="s">
         <v>196</v>
@@ -12754,7 +12754,7 @@
         <v>202</v>
       </c>
       <c r="BG18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH18">
         <v>17</v>
@@ -12787,13 +12787,13 @@
         <v>136</v>
       </c>
       <c r="BR18" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS18" t="s">
         <v>297</v>
       </c>
       <c r="BT18" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU18" t="s">
         <v>298</v>
@@ -12817,7 +12817,7 @@
         <v>302</v>
       </c>
       <c r="CB18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC18" t="s">
         <v>137</v>
@@ -12832,7 +12832,7 @@
         <v>6.95</v>
       </c>
       <c r="CG18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CH18">
         <v>6.81</v>
@@ -12850,7 +12850,7 @@
         <v>0.99</v>
       </c>
       <c r="CM18" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CN18">
         <v>4331</v>
@@ -13041,10 +13041,10 @@
         <v>136</v>
       </c>
       <c r="BF19" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="BG19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BH19">
         <v>16</v>
@@ -13077,13 +13077,13 @@
         <v>136</v>
       </c>
       <c r="BR19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS19" t="s">
         <v>305</v>
       </c>
       <c r="BT19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU19" t="s">
         <v>298</v>
@@ -13107,10 +13107,10 @@
         <v>302</v>
       </c>
       <c r="CB19" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC19" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CD19">
         <v>1.56</v>
@@ -13128,7 +13128,7 @@
         <v>0</v>
       </c>
       <c r="CI19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="CJ19">
         <v>1.19</v>
@@ -13140,7 +13140,7 @@
         <v>1.56</v>
       </c>
       <c r="CM19" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CN19">
         <v>1048</v>
@@ -13367,13 +13367,13 @@
         <v>136</v>
       </c>
       <c r="BR20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BS20" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BT20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU20" t="s">
         <v>298</v>
@@ -13397,7 +13397,7 @@
         <v>302</v>
       </c>
       <c r="CB20" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CC20" t="s">
         <v>137</v>
@@ -13430,7 +13430,7 @@
         <v>0.42</v>
       </c>
       <c r="CM20" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CN20">
         <v>701.8</v>
@@ -13539,10 +13539,10 @@
         <v>331</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F2">
         <v>203.83</v>
@@ -13595,10 +13595,10 @@
         <v>133</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F3">
-        <v>194.39</v>
+        <v>195.89</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -13648,10 +13648,10 @@
         <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F4">
-        <v>189.51</v>
+        <v>191.01</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -13675,10 +13675,10 @@
         <v>165</v>
       </c>
       <c r="N4">
-        <v>62662.8</v>
+        <v>62639.1</v>
       </c>
       <c r="O4">
-        <v>3569.4</v>
+        <v>3568.05</v>
       </c>
       <c r="P4">
         <v>22.35</v>
@@ -13701,7 +13701,7 @@
         <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F5">
         <v>188.56</v>
@@ -13745,19 +13745,19 @@
         <v>333</v>
       </c>
       <c r="B6" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="C6" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D6" t="s">
         <v>133</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F6">
-        <v>186.14</v>
+        <v>186.46</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -13769,25 +13769,25 @@
         <v>136</v>
       </c>
       <c r="J6">
-        <v>5.48</v>
+        <v>8.01</v>
       </c>
       <c r="K6">
-        <v>0.41</v>
+        <v>1.96</v>
       </c>
       <c r="L6">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="M6" t="s">
         <v>165</v>
       </c>
       <c r="N6">
-        <v>62193.6</v>
+        <v>62616.4</v>
       </c>
       <c r="O6">
-        <v>932.96</v>
+        <v>939.4</v>
       </c>
       <c r="P6">
-        <v>4375.76</v>
+        <v>801</v>
       </c>
       <c r="Q6" t="s">
         <v>335</v>
@@ -13798,19 +13798,19 @@
         <v>333</v>
       </c>
       <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
         <v>340</v>
-      </c>
-      <c r="C7" t="s">
-        <v>331</v>
       </c>
       <c r="D7" t="s">
         <v>133</v>
       </c>
       <c r="E7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F7">
-        <v>184.96</v>
+        <v>186.14</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -13822,25 +13822,25 @@
         <v>136</v>
       </c>
       <c r="J7">
-        <v>8.01</v>
+        <v>5.48</v>
       </c>
       <c r="K7">
-        <v>1.96</v>
+        <v>0.41</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="M7" t="s">
         <v>165</v>
       </c>
       <c r="N7">
-        <v>62616.4</v>
+        <v>62193.6</v>
       </c>
       <c r="O7">
-        <v>939.4</v>
+        <v>932.96</v>
       </c>
       <c r="P7">
-        <v>801</v>
+        <v>4375.76</v>
       </c>
       <c r="Q7" t="s">
         <v>335</v>
@@ -13860,10 +13860,10 @@
         <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F8">
-        <v>178.48</v>
+        <v>179.98</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -13910,10 +13910,10 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F9">
         <v>177.33</v>
@@ -13966,7 +13966,7 @@
         <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F10">
         <v>175.03</v>
@@ -14016,13 +14016,13 @@
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F11">
-        <v>168.71</v>
+        <v>170.21</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -14040,7 +14040,7 @@
         <v>1.46</v>
       </c>
       <c r="L11">
-        <v>4.97</v>
+        <v>3.47</v>
       </c>
       <c r="M11" t="s">
         <v>165</v>
@@ -14143,7 +14143,7 @@
         <v>351</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C2" t="s">
         <v>330</v>
@@ -14152,7 +14152,7 @@
         <v>331</v>
       </c>
       <c r="E2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G2" t="s">
         <v>352</v>
@@ -14161,7 +14161,7 @@
         <v>353</v>
       </c>
       <c r="I2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J2">
         <v>186.88</v>
@@ -14193,7 +14193,7 @@
         <v>351</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C3" t="s">
         <v>343</v>
@@ -14202,7 +14202,7 @@
         <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G3" t="s">
         <v>352</v>
@@ -14211,7 +14211,7 @@
         <v>353</v>
       </c>
       <c r="I3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J3">
         <v>170.68</v>
@@ -14243,7 +14243,7 @@
         <v>351</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
         <v>188</v>
@@ -14252,7 +14252,7 @@
         <v>355</v>
       </c>
       <c r="E4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G4" t="s">
         <v>352</v>
@@ -14261,7 +14261,7 @@
         <v>353</v>
       </c>
       <c r="I4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J4">
         <v>170.12</v>
@@ -14293,7 +14293,7 @@
         <v>351</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
         <v>177</v>
@@ -14302,7 +14302,7 @@
         <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F5">
         <v>622.5499877929688</v>
@@ -14314,7 +14314,7 @@
         <v>333</v>
       </c>
       <c r="I5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J5">
         <v>195.78</v>
@@ -14367,7 +14367,7 @@
         <v>333</v>
       </c>
       <c r="I6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J6">
         <v>195.83</v>
@@ -14420,7 +14420,7 @@
         <v>333</v>
       </c>
       <c r="I7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J7">
         <v>170.4</v>
@@ -14473,7 +14473,7 @@
         <v>353</v>
       </c>
       <c r="I8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J8">
         <v>195.83</v>
@@ -14526,7 +14526,7 @@
         <v>353</v>
       </c>
       <c r="I9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J9">
         <v>170.4</v>
@@ -14558,7 +14558,7 @@
         <v>360</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C10" t="s">
         <v>131</v>
@@ -14567,7 +14567,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F10">
         <v>863.5</v>
@@ -14579,7 +14579,7 @@
         <v>333</v>
       </c>
       <c r="I10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J10">
         <v>202.39</v>
@@ -14611,7 +14611,7 @@
         <v>360</v>
       </c>
       <c r="B11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C11" t="s">
         <v>330</v>
@@ -14620,7 +14620,7 @@
         <v>331</v>
       </c>
       <c r="E11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F11">
         <v>8782.5</v>
@@ -14632,7 +14632,7 @@
         <v>333</v>
       </c>
       <c r="I11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J11">
         <v>191.38</v>
@@ -14664,7 +14664,7 @@
         <v>360</v>
       </c>
       <c r="B12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C12" t="s">
         <v>343</v>
@@ -14673,7 +14673,7 @@
         <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F12">
         <v>16326</v>
@@ -14685,7 +14685,7 @@
         <v>333</v>
       </c>
       <c r="I12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J12">
         <v>173.68</v>
@@ -14738,7 +14738,7 @@
         <v>353</v>
       </c>
       <c r="I13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J13">
         <v>188.39</v>
@@ -14791,7 +14791,7 @@
         <v>353</v>
       </c>
       <c r="I14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J14">
         <v>183.51</v>
@@ -14826,7 +14826,7 @@
         <v>133</v>
       </c>
       <c r="C15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D15" t="s">
         <v>331</v>
@@ -14844,7 +14844,7 @@
         <v>353</v>
       </c>
       <c r="I15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J15">
         <v>178.96</v>
@@ -14897,7 +14897,7 @@
         <v>353</v>
       </c>
       <c r="I16" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J16">
         <v>172.48</v>
@@ -14929,16 +14929,16 @@
         <v>361</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C17" t="s">
         <v>362</v>
       </c>
       <c r="D17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F17">
         <v>1378.300048828125</v>
@@ -14950,7 +14950,7 @@
         <v>333</v>
       </c>
       <c r="I17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J17">
         <v>190.49</v>
@@ -14982,7 +14982,7 @@
         <v>361</v>
       </c>
       <c r="B18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C18" t="s">
         <v>363</v>
@@ -14991,7 +14991,7 @@
         <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F18">
         <v>56.9900016784668</v>
@@ -15003,7 +15003,7 @@
         <v>333</v>
       </c>
       <c r="I18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J18">
         <v>181.4</v>
@@ -15035,7 +15035,7 @@
         <v>361</v>
       </c>
       <c r="B19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s">
         <v>364</v>
@@ -15044,7 +15044,7 @@
         <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F19">
         <v>121</v>
@@ -15056,7 +15056,7 @@
         <v>333</v>
       </c>
       <c r="I19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J19">
         <v>180.09</v>
@@ -15088,7 +15088,7 @@
         <v>361</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C20" t="s">
         <v>365</v>
@@ -15097,7 +15097,7 @@
         <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F20">
         <v>5024</v>
@@ -15109,7 +15109,7 @@
         <v>333</v>
       </c>
       <c r="I20" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J20">
         <v>166.42</v>
@@ -15141,7 +15141,7 @@
         <v>361</v>
       </c>
       <c r="B21" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C21" t="s">
         <v>366</v>
@@ -15150,7 +15150,7 @@
         <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F21">
         <v>156.35000610351562</v>
@@ -15162,7 +15162,7 @@
         <v>333</v>
       </c>
       <c r="I21" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J21">
         <v>161.75</v>
@@ -15194,7 +15194,7 @@
         <v>361</v>
       </c>
       <c r="B22" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s">
         <v>367</v>
@@ -15203,7 +15203,7 @@
         <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F22">
         <v>422.45001220703125</v>
@@ -15215,7 +15215,7 @@
         <v>333</v>
       </c>
       <c r="I22" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J22">
         <v>161.4</v>
@@ -15247,16 +15247,16 @@
         <v>368</v>
       </c>
       <c r="B23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C23" t="s">
         <v>362</v>
       </c>
       <c r="D23" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F23">
         <v>1378.300048828125</v>
@@ -15268,7 +15268,7 @@
         <v>353</v>
       </c>
       <c r="I23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J23">
         <v>190.49</v>
@@ -15300,7 +15300,7 @@
         <v>368</v>
       </c>
       <c r="B24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C24" t="s">
         <v>363</v>
@@ -15309,7 +15309,7 @@
         <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F24">
         <v>56.9900016784668</v>
@@ -15321,7 +15321,7 @@
         <v>353</v>
       </c>
       <c r="I24" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J24">
         <v>181.4</v>
@@ -15353,7 +15353,7 @@
         <v>368</v>
       </c>
       <c r="B25" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C25" t="s">
         <v>364</v>
@@ -15362,7 +15362,7 @@
         <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F25">
         <v>121</v>
@@ -15374,7 +15374,7 @@
         <v>353</v>
       </c>
       <c r="I25" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J25">
         <v>180.09</v>
@@ -15406,7 +15406,7 @@
         <v>368</v>
       </c>
       <c r="B26" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C26" t="s">
         <v>365</v>
@@ -15415,7 +15415,7 @@
         <v>28</v>
       </c>
       <c r="E26" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F26">
         <v>5024</v>
@@ -15427,7 +15427,7 @@
         <v>353</v>
       </c>
       <c r="I26" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J26">
         <v>166.42</v>
@@ -15459,7 +15459,7 @@
         <v>368</v>
       </c>
       <c r="B27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C27" t="s">
         <v>366</v>
@@ -15468,7 +15468,7 @@
         <v>28</v>
       </c>
       <c r="E27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F27">
         <v>156.35000610351562</v>
@@ -15480,7 +15480,7 @@
         <v>353</v>
       </c>
       <c r="I27" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J27">
         <v>161.75</v>
@@ -15512,7 +15512,7 @@
         <v>368</v>
       </c>
       <c r="B28" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C28" t="s">
         <v>367</v>
@@ -15521,7 +15521,7 @@
         <v>28</v>
       </c>
       <c r="E28" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F28">
         <v>422.45001220703125</v>
@@ -15533,7 +15533,7 @@
         <v>353</v>
       </c>
       <c r="I28" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J28">
         <v>161.4</v>
@@ -15586,10 +15586,10 @@
         <v>333</v>
       </c>
       <c r="I29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J29">
-        <v>194.39</v>
+        <v>195.89</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -15639,10 +15639,10 @@
         <v>333</v>
       </c>
       <c r="I30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J30">
-        <v>189.51</v>
+        <v>191.01</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -15692,7 +15692,7 @@
         <v>333</v>
       </c>
       <c r="I31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J31">
         <v>188.56</v>
@@ -15727,16 +15727,16 @@
         <v>133</v>
       </c>
       <c r="C32" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="D32" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="E32" t="s">
         <v>133</v>
       </c>
       <c r="F32">
-        <v>4442.39990234375</v>
+        <v>813.2000122070312</v>
       </c>
       <c r="G32" t="s">
         <v>356</v>
@@ -15745,10 +15745,10 @@
         <v>333</v>
       </c>
       <c r="I32" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J32">
-        <v>186.14</v>
+        <v>186.46</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -15757,13 +15757,13 @@
         <v>136</v>
       </c>
       <c r="M32">
-        <v>5.48</v>
+        <v>8.01</v>
       </c>
       <c r="N32">
-        <v>0.41</v>
+        <v>1.96</v>
       </c>
       <c r="O32">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="P32">
         <v>1</v>
@@ -15780,16 +15780,16 @@
         <v>133</v>
       </c>
       <c r="C33" t="s">
+        <v>292</v>
+      </c>
+      <c r="D33" t="s">
         <v>340</v>
-      </c>
-      <c r="D33" t="s">
-        <v>331</v>
       </c>
       <c r="E33" t="s">
         <v>133</v>
       </c>
       <c r="F33">
-        <v>813.2000122070312</v>
+        <v>4442.39990234375</v>
       </c>
       <c r="G33" t="s">
         <v>356</v>
@@ -15798,10 +15798,10 @@
         <v>333</v>
       </c>
       <c r="I33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J33">
-        <v>184.96</v>
+        <v>186.14</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -15810,13 +15810,13 @@
         <v>136</v>
       </c>
       <c r="M33">
-        <v>8.01</v>
+        <v>5.48</v>
       </c>
       <c r="N33">
-        <v>1.96</v>
+        <v>0.41</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="P33">
         <v>1</v>
@@ -15851,10 +15851,10 @@
         <v>333</v>
       </c>
       <c r="I34" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J34">
-        <v>178.48</v>
+        <v>179.98</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -15883,7 +15883,7 @@
         <v>370</v>
       </c>
       <c r="B35" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C35" t="s">
         <v>342</v>
@@ -15892,7 +15892,7 @@
         <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F35">
         <v>179.52000427246094</v>
@@ -15904,7 +15904,7 @@
         <v>333</v>
       </c>
       <c r="I35" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J35">
         <v>177.33</v>
@@ -15957,7 +15957,7 @@
         <v>333</v>
       </c>
       <c r="I36" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J36">
         <v>175.03</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-15T05:58:04.586Z</t>
+    <t>2026-07-15T06:05:34.873Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1130,7 +1130,7 @@
     <t>Latest completed-candle status is WATCH, not ENTRY. Current setup grade WATCH no longer passes the selected trade-quality filter. Current/09:17 price is below daily Supertrend.</t>
   </si>
   <si>
-    <t>2026-07-15T05:58:03.939Z</t>
+    <t>2026-07-15T06:05:34.516Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -5171,7 +5171,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>188.72</v>
+        <v>190.22</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -10936,7 +10936,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>188.72</v>
+        <v>190.22</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -13598,7 +13598,7 @@
         <v>142</v>
       </c>
       <c r="F3">
-        <v>195.89</v>
+        <v>197.39</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -13651,7 +13651,7 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>191.01</v>
+        <v>192.51</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -13757,7 +13757,7 @@
         <v>142</v>
       </c>
       <c r="F6">
-        <v>186.46</v>
+        <v>187.96</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -13863,7 +13863,7 @@
         <v>142</v>
       </c>
       <c r="F8">
-        <v>179.98</v>
+        <v>181.48</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -14022,7 +14022,7 @@
         <v>142</v>
       </c>
       <c r="F11">
-        <v>170.21</v>
+        <v>171.71</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -14040,7 +14040,7 @@
         <v>1.46</v>
       </c>
       <c r="L11">
-        <v>3.47</v>
+        <v>1.97</v>
       </c>
       <c r="M11" t="s">
         <v>165</v>
@@ -15589,7 +15589,7 @@
         <v>142</v>
       </c>
       <c r="J29">
-        <v>195.89</v>
+        <v>197.39</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -15642,7 +15642,7 @@
         <v>142</v>
       </c>
       <c r="J30">
-        <v>191.01</v>
+        <v>192.51</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -15748,7 +15748,7 @@
         <v>142</v>
       </c>
       <c r="J32">
-        <v>186.46</v>
+        <v>187.96</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -15854,7 +15854,7 @@
         <v>142</v>
       </c>
       <c r="J34">
-        <v>179.98</v>
+        <v>181.48</v>
       </c>
       <c r="K34">
         <v>0</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-15T06:05:34.873Z</t>
+    <t>2026-07-15T06:44:44.927Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1031,15 +1031,15 @@
     <t>CJGEL</t>
   </si>
   <si>
+    <t>ASTERDM</t>
+  </si>
+  <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
     <t>Automobile and Auto Components</t>
   </si>
   <si>
-    <t>ASTERDM</t>
-  </si>
-  <si>
     <t>Capital Goods</t>
   </si>
   <si>
@@ -1130,7 +1130,7 @@
     <t>Latest completed-candle status is WATCH, not ENTRY. Current setup grade WATCH no longer passes the selected trade-quality filter. Current/09:17 price is below daily Supertrend.</t>
   </si>
   <si>
-    <t>2026-07-15T06:05:34.516Z</t>
+    <t>2026-07-15T06:44:44.567Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -5171,7 +5171,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>190.22</v>
+        <v>191.72</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -10936,7 +10936,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>190.22</v>
+        <v>191.72</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -13598,7 +13598,7 @@
         <v>142</v>
       </c>
       <c r="F3">
-        <v>197.39</v>
+        <v>198.89</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -13651,7 +13651,7 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>192.51</v>
+        <v>194.01</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -13695,7 +13695,7 @@
         <v>337</v>
       </c>
       <c r="C5" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D5" t="s">
         <v>133</v>
@@ -13704,7 +13704,7 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>188.56</v>
+        <v>189.46</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -13716,25 +13716,25 @@
         <v>136</v>
       </c>
       <c r="J5">
-        <v>5.67</v>
+        <v>8.01</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="L5">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="N5">
-        <v>60996</v>
+        <v>62616.4</v>
       </c>
       <c r="O5">
-        <v>914.94</v>
+        <v>939.4</v>
       </c>
       <c r="P5">
-        <v>10013.51</v>
+        <v>801</v>
       </c>
       <c r="Q5" t="s">
         <v>335</v>
@@ -13745,10 +13745,10 @@
         <v>333</v>
       </c>
       <c r="B6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C6" t="s">
         <v>339</v>
-      </c>
-      <c r="C6" t="s">
-        <v>331</v>
       </c>
       <c r="D6" t="s">
         <v>133</v>
@@ -13757,7 +13757,7 @@
         <v>142</v>
       </c>
       <c r="F6">
-        <v>187.96</v>
+        <v>188.56</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -13769,25 +13769,25 @@
         <v>136</v>
       </c>
       <c r="J6">
-        <v>8.01</v>
+        <v>5.67</v>
       </c>
       <c r="K6">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="M6" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="N6">
-        <v>62616.4</v>
+        <v>60996</v>
       </c>
       <c r="O6">
-        <v>939.4</v>
+        <v>914.94</v>
       </c>
       <c r="P6">
-        <v>801</v>
+        <v>10013.51</v>
       </c>
       <c r="Q6" t="s">
         <v>335</v>
@@ -13863,7 +13863,7 @@
         <v>142</v>
       </c>
       <c r="F8">
-        <v>181.48</v>
+        <v>182.98</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -14022,7 +14022,7 @@
         <v>142</v>
       </c>
       <c r="F11">
-        <v>171.71</v>
+        <v>173.21</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -14040,7 +14040,7 @@
         <v>1.46</v>
       </c>
       <c r="L11">
-        <v>1.97</v>
+        <v>0.47</v>
       </c>
       <c r="M11" t="s">
         <v>165</v>
@@ -14826,7 +14826,7 @@
         <v>133</v>
       </c>
       <c r="C15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D15" t="s">
         <v>331</v>
@@ -15589,7 +15589,7 @@
         <v>142</v>
       </c>
       <c r="J29">
-        <v>197.39</v>
+        <v>198.89</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -15642,7 +15642,7 @@
         <v>142</v>
       </c>
       <c r="J30">
-        <v>192.51</v>
+        <v>194.01</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -15677,13 +15677,13 @@
         <v>337</v>
       </c>
       <c r="D31" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="E31" t="s">
         <v>133</v>
       </c>
       <c r="F31">
-        <v>10166</v>
+        <v>813.2000122070312</v>
       </c>
       <c r="G31" t="s">
         <v>356</v>
@@ -15695,7 +15695,7 @@
         <v>142</v>
       </c>
       <c r="J31">
-        <v>188.56</v>
+        <v>189.46</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -15704,13 +15704,13 @@
         <v>136</v>
       </c>
       <c r="M31">
-        <v>5.67</v>
+        <v>8.01</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O31">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="P31">
         <v>1</v>
@@ -15727,16 +15727,16 @@
         <v>133</v>
       </c>
       <c r="C32" t="s">
+        <v>338</v>
+      </c>
+      <c r="D32" t="s">
         <v>339</v>
-      </c>
-      <c r="D32" t="s">
-        <v>331</v>
       </c>
       <c r="E32" t="s">
         <v>133</v>
       </c>
       <c r="F32">
-        <v>813.2000122070312</v>
+        <v>10166</v>
       </c>
       <c r="G32" t="s">
         <v>356</v>
@@ -15748,7 +15748,7 @@
         <v>142</v>
       </c>
       <c r="J32">
-        <v>187.96</v>
+        <v>188.56</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -15757,13 +15757,13 @@
         <v>136</v>
       </c>
       <c r="M32">
-        <v>8.01</v>
+        <v>5.67</v>
       </c>
       <c r="N32">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="P32">
         <v>1</v>
@@ -15854,7 +15854,7 @@
         <v>142</v>
       </c>
       <c r="J34">
-        <v>181.48</v>
+        <v>182.98</v>
       </c>
       <c r="K34">
         <v>0</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-15T06:44:44.927Z</t>
+    <t>2026-07-15T06:57:07.177Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1130,7 +1130,7 @@
     <t>Latest completed-candle status is WATCH, not ENTRY. Current setup grade WATCH no longer passes the selected trade-quality filter. Current/09:17 price is below daily Supertrend.</t>
   </si>
   <si>
-    <t>2026-07-15T06:44:44.567Z</t>
+    <t>2026-07-15T06:57:06.854Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -5171,7 +5171,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>191.72</v>
+        <v>193.22</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -10936,7 +10936,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>191.72</v>
+        <v>193.22</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -13598,7 +13598,7 @@
         <v>142</v>
       </c>
       <c r="F3">
-        <v>198.89</v>
+        <v>200.39</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -13651,7 +13651,7 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>194.01</v>
+        <v>195.51</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -13704,7 +13704,7 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>189.46</v>
+        <v>190.96</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -13810,7 +13810,7 @@
         <v>142</v>
       </c>
       <c r="F7">
-        <v>186.14</v>
+        <v>186.81</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -13828,7 +13828,7 @@
         <v>0.41</v>
       </c>
       <c r="L7">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="M7" t="s">
         <v>165</v>
@@ -13863,7 +13863,7 @@
         <v>142</v>
       </c>
       <c r="F8">
-        <v>182.98</v>
+        <v>184.48</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -14022,7 +14022,7 @@
         <v>142</v>
       </c>
       <c r="F11">
-        <v>173.21</v>
+        <v>174.71</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -14040,7 +14040,7 @@
         <v>1.46</v>
       </c>
       <c r="L11">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="M11" t="s">
         <v>165</v>
@@ -15589,7 +15589,7 @@
         <v>142</v>
       </c>
       <c r="J29">
-        <v>198.89</v>
+        <v>200.39</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -15642,7 +15642,7 @@
         <v>142</v>
       </c>
       <c r="J30">
-        <v>194.01</v>
+        <v>195.51</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -15695,7 +15695,7 @@
         <v>142</v>
       </c>
       <c r="J31">
-        <v>189.46</v>
+        <v>190.96</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -15801,7 +15801,7 @@
         <v>142</v>
       </c>
       <c r="J33">
-        <v>186.14</v>
+        <v>186.81</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -15816,7 +15816,7 @@
         <v>0.41</v>
       </c>
       <c r="O33">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="P33">
         <v>1</v>
@@ -15854,7 +15854,7 @@
         <v>142</v>
       </c>
       <c r="J34">
-        <v>182.98</v>
+        <v>184.48</v>
       </c>
       <c r="K34">
         <v>0</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-15T06:57:07.177Z</t>
+    <t>2026-07-15T08:02:54.704Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1130,7 +1130,7 @@
     <t>Latest completed-candle status is WATCH, not ENTRY. Current setup grade WATCH no longer passes the selected trade-quality filter. Current/09:17 price is below daily Supertrend.</t>
   </si>
   <si>
-    <t>2026-07-15T06:57:06.854Z</t>
+    <t>2026-07-15T08:02:54.364Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -5171,7 +5171,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>193.22</v>
+        <v>194.72</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -10936,7 +10936,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>193.22</v>
+        <v>194.72</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -13598,7 +13598,7 @@
         <v>142</v>
       </c>
       <c r="F3">
-        <v>200.39</v>
+        <v>201.89</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -13651,7 +13651,7 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>195.51</v>
+        <v>197.01</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -13704,7 +13704,7 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>190.96</v>
+        <v>192.46</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -13863,7 +13863,7 @@
         <v>142</v>
       </c>
       <c r="F8">
-        <v>184.48</v>
+        <v>185.98</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -13954,108 +13954,108 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>310</v>
+        <v>343</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="E10" t="s">
         <v>142</v>
       </c>
       <c r="F10">
-        <v>175.03</v>
+        <v>176.21</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="I10" t="s">
         <v>136</v>
       </c>
       <c r="J10">
-        <v>8.15</v>
+        <v>4.47</v>
       </c>
       <c r="K10">
-        <v>0.93</v>
+        <v>1.46</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="N10">
-        <v>62105.4</v>
+        <v>48366</v>
       </c>
       <c r="O10">
-        <v>1268.4</v>
+        <v>819.54</v>
       </c>
       <c r="P10">
-        <v>724.25</v>
+        <v>15848.82</v>
       </c>
       <c r="Q10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B11" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
         <v>142</v>
       </c>
       <c r="F11">
-        <v>174.71</v>
+        <v>175.03</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="I11" t="s">
         <v>136</v>
       </c>
       <c r="J11">
-        <v>4.47</v>
+        <v>8.15</v>
       </c>
       <c r="K11">
-        <v>1.46</v>
+        <v>0.93</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="N11">
-        <v>48366</v>
+        <v>62105.4</v>
       </c>
       <c r="O11">
-        <v>819.54</v>
+        <v>1268.4</v>
       </c>
       <c r="P11">
-        <v>15848.82</v>
+        <v>724.25</v>
       </c>
       <c r="Q11" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -15589,7 +15589,7 @@
         <v>142</v>
       </c>
       <c r="J29">
-        <v>200.39</v>
+        <v>201.89</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -15642,7 +15642,7 @@
         <v>142</v>
       </c>
       <c r="J30">
-        <v>195.51</v>
+        <v>197.01</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -15695,7 +15695,7 @@
         <v>142</v>
       </c>
       <c r="J31">
-        <v>190.96</v>
+        <v>192.46</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -15854,7 +15854,7 @@
         <v>142</v>
       </c>
       <c r="J34">
-        <v>184.48</v>
+        <v>185.98</v>
       </c>
       <c r="K34">
         <v>0</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-15T08:02:54.704Z</t>
+    <t>2026-07-15T08:22:05.661Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1040,18 +1040,18 @@
     <t>Automobile and Auto Components</t>
   </si>
   <si>
+    <t>KIMS</t>
+  </si>
+  <si>
     <t>Capital Goods</t>
   </si>
   <si>
-    <t>KIMS</t>
+    <t>LMW</t>
   </si>
   <si>
     <t>INDIGRID</t>
   </si>
   <si>
-    <t>LMW</t>
-  </si>
-  <si>
     <t>Evaluated At</t>
   </si>
   <si>
@@ -1130,7 +1130,7 @@
     <t>Latest completed-candle status is WATCH, not ENTRY. Current setup grade WATCH no longer passes the selected trade-quality filter. Current/09:17 price is below daily Supertrend.</t>
   </si>
   <si>
-    <t>2026-07-15T08:02:54.364Z</t>
+    <t>2026-07-15T08:22:05.305Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -5171,7 +5171,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>194.72</v>
+        <v>196.22</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -10936,7 +10936,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>194.72</v>
+        <v>196.22</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -13598,7 +13598,7 @@
         <v>142</v>
       </c>
       <c r="F3">
-        <v>201.89</v>
+        <v>203.39</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -13651,7 +13651,7 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>197.01</v>
+        <v>198.51</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -13704,7 +13704,7 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>192.46</v>
+        <v>193.96</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -13798,10 +13798,10 @@
         <v>333</v>
       </c>
       <c r="B7" t="s">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="C7" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="D7" t="s">
         <v>133</v>
@@ -13810,7 +13810,7 @@
         <v>142</v>
       </c>
       <c r="F7">
-        <v>186.81</v>
+        <v>187.48</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -13822,10 +13822,10 @@
         <v>136</v>
       </c>
       <c r="J7">
-        <v>5.48</v>
+        <v>3.05</v>
       </c>
       <c r="K7">
-        <v>0.41</v>
+        <v>1.14</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -13834,13 +13834,13 @@
         <v>165</v>
       </c>
       <c r="N7">
-        <v>62193.6</v>
+        <v>62115.9</v>
       </c>
       <c r="O7">
-        <v>932.96</v>
+        <v>931.7</v>
       </c>
       <c r="P7">
-        <v>4375.76</v>
+        <v>794.6</v>
       </c>
       <c r="Q7" t="s">
         <v>335</v>
@@ -13851,10 +13851,10 @@
         <v>333</v>
       </c>
       <c r="B8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C8" t="s">
         <v>341</v>
-      </c>
-      <c r="C8" t="s">
-        <v>331</v>
       </c>
       <c r="D8" t="s">
         <v>133</v>
@@ -13863,7 +13863,7 @@
         <v>142</v>
       </c>
       <c r="F8">
-        <v>185.98</v>
+        <v>186.81</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -13875,10 +13875,10 @@
         <v>136</v>
       </c>
       <c r="J8">
-        <v>3.05</v>
+        <v>5.48</v>
       </c>
       <c r="K8">
-        <v>1.14</v>
+        <v>0.41</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -13887,13 +13887,13 @@
         <v>165</v>
       </c>
       <c r="N8">
-        <v>62115.9</v>
+        <v>62193.6</v>
       </c>
       <c r="O8">
-        <v>931.7</v>
+        <v>932.96</v>
       </c>
       <c r="P8">
-        <v>794.6</v>
+        <v>4375.76</v>
       </c>
       <c r="Q8" t="s">
         <v>335</v>
@@ -13901,7 +13901,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B9" t="s">
         <v>342</v>
@@ -13916,22 +13916,22 @@
         <v>142</v>
       </c>
       <c r="F9">
-        <v>177.33</v>
+        <v>177.71</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="I9" t="s">
         <v>136</v>
       </c>
       <c r="J9">
-        <v>2.62</v>
+        <v>4.47</v>
       </c>
       <c r="K9">
-        <v>3.44</v>
+        <v>1.46</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -13940,21 +13940,21 @@
         <v>165</v>
       </c>
       <c r="N9">
-        <v>62652.48</v>
+        <v>48366</v>
       </c>
       <c r="O9">
-        <v>1183.11</v>
+        <v>819.54</v>
       </c>
       <c r="P9">
-        <v>176.13</v>
+        <v>15848.82</v>
       </c>
       <c r="Q9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B10" t="s">
         <v>343</v>
@@ -13969,22 +13969,22 @@
         <v>142</v>
       </c>
       <c r="F10">
-        <v>176.21</v>
+        <v>177.33</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="I10" t="s">
         <v>136</v>
       </c>
       <c r="J10">
-        <v>4.47</v>
+        <v>2.62</v>
       </c>
       <c r="K10">
-        <v>1.46</v>
+        <v>3.44</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -13993,16 +13993,16 @@
         <v>165</v>
       </c>
       <c r="N10">
-        <v>48366</v>
+        <v>62652.48</v>
       </c>
       <c r="O10">
-        <v>819.54</v>
+        <v>1183.11</v>
       </c>
       <c r="P10">
-        <v>15848.82</v>
+        <v>176.13</v>
       </c>
       <c r="Q10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -14196,7 +14196,7 @@
         <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>201</v>
       </c>
       <c r="C7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D7" t="s">
         <v>331</v>
@@ -14508,7 +14508,7 @@
         <v>201</v>
       </c>
       <c r="C9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D9" t="s">
         <v>331</v>
@@ -14667,7 +14667,7 @@
         <v>164</v>
       </c>
       <c r="C12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D12" t="s">
         <v>28</v>
@@ -14879,7 +14879,7 @@
         <v>133</v>
       </c>
       <c r="C16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D16" t="s">
         <v>331</v>
@@ -14935,7 +14935,7 @@
         <v>362</v>
       </c>
       <c r="D17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E17" t="s">
         <v>164</v>
@@ -15253,7 +15253,7 @@
         <v>362</v>
       </c>
       <c r="D23" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E23" t="s">
         <v>164</v>
@@ -15589,7 +15589,7 @@
         <v>142</v>
       </c>
       <c r="J29">
-        <v>201.89</v>
+        <v>203.39</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -15642,7 +15642,7 @@
         <v>142</v>
       </c>
       <c r="J30">
-        <v>197.01</v>
+        <v>198.51</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -15695,7 +15695,7 @@
         <v>142</v>
       </c>
       <c r="J31">
-        <v>192.46</v>
+        <v>193.96</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -15780,16 +15780,16 @@
         <v>133</v>
       </c>
       <c r="C33" t="s">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="D33" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="E33" t="s">
         <v>133</v>
       </c>
       <c r="F33">
-        <v>4442.39990234375</v>
+        <v>806.7000122070312</v>
       </c>
       <c r="G33" t="s">
         <v>356</v>
@@ -15801,7 +15801,7 @@
         <v>142</v>
       </c>
       <c r="J33">
-        <v>186.81</v>
+        <v>187.48</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -15810,10 +15810,10 @@
         <v>136</v>
       </c>
       <c r="M33">
-        <v>5.48</v>
+        <v>3.05</v>
       </c>
       <c r="N33">
-        <v>0.41</v>
+        <v>1.14</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -15833,16 +15833,16 @@
         <v>133</v>
       </c>
       <c r="C34" t="s">
+        <v>292</v>
+      </c>
+      <c r="D34" t="s">
         <v>341</v>
-      </c>
-      <c r="D34" t="s">
-        <v>331</v>
       </c>
       <c r="E34" t="s">
         <v>133</v>
       </c>
       <c r="F34">
-        <v>806.7000122070312</v>
+        <v>4442.39990234375</v>
       </c>
       <c r="G34" t="s">
         <v>356</v>
@@ -15854,7 +15854,7 @@
         <v>142</v>
       </c>
       <c r="J34">
-        <v>185.98</v>
+        <v>186.81</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -15863,10 +15863,10 @@
         <v>136</v>
       </c>
       <c r="M34">
-        <v>3.05</v>
+        <v>5.48</v>
       </c>
       <c r="N34">
-        <v>1.14</v>
+        <v>0.41</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -15886,7 +15886,7 @@
         <v>164</v>
       </c>
       <c r="C35" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D35" t="s">
         <v>28</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3262" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3262" uniqueCount="381">
   <si>
     <t>Metric</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-15T08:22:05.661Z</t>
+    <t>2026-07-15T09:07:03.410Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1022,36 +1022,36 @@
     <t>WAITING_CONFIRMATION</t>
   </si>
   <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>Automobile and Auto Components</t>
+  </si>
+  <si>
+    <t>Rotation requires 2 distinct valid ENTRY closes; candidate has 1.</t>
+  </si>
+  <si>
     <t>APCOTEXIND</t>
   </si>
   <si>
-    <t>Rotation requires 2 distinct valid ENTRY closes; candidate has 1.</t>
+    <t>Capital Goods</t>
   </si>
   <si>
     <t>CJGEL</t>
   </si>
   <si>
+    <t>INDIGRID</t>
+  </si>
+  <si>
     <t>ASTERDM</t>
   </si>
   <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>Automobile and Auto Components</t>
-  </si>
-  <si>
     <t>KIMS</t>
   </si>
   <si>
-    <t>Capital Goods</t>
-  </si>
-  <si>
     <t>LMW</t>
   </si>
   <si>
-    <t>INDIGRID</t>
-  </si>
-  <si>
     <t>Evaluated At</t>
   </si>
   <si>
@@ -1131,6 +1131,9 @@
   </si>
   <si>
     <t>2026-07-15T08:22:05.305Z</t>
+  </si>
+  <si>
+    <t>2026-07-15T09:07:03.050Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -2271,7 +2274,7 @@
         <v>213.48</v>
       </c>
       <c r="AG2">
-        <v>213.48</v>
+        <v>211.48</v>
       </c>
       <c r="AH2">
         <v>847.55</v>
@@ -5171,7 +5174,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>196.22</v>
+        <v>181.22</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -8036,7 +8039,7 @@
         <v>213.48</v>
       </c>
       <c r="AG2">
-        <v>213.48</v>
+        <v>211.48</v>
       </c>
       <c r="AH2">
         <v>847.55</v>
@@ -10936,7 +10939,7 @@
         <v>136</v>
       </c>
       <c r="AG12">
-        <v>196.22</v>
+        <v>181.22</v>
       </c>
       <c r="AH12">
         <v>1842.85</v>
@@ -13589,7 +13592,7 @@
         <v>334</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>335</v>
       </c>
       <c r="D3" t="s">
         <v>133</v>
@@ -13598,7 +13601,7 @@
         <v>142</v>
       </c>
       <c r="F3">
-        <v>203.39</v>
+        <v>188.56</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -13610,28 +13613,28 @@
         <v>136</v>
       </c>
       <c r="J3">
-        <v>9.31</v>
+        <v>5.67</v>
       </c>
       <c r="K3">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="M3" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="N3">
-        <v>62292.2</v>
+        <v>60996</v>
       </c>
       <c r="O3">
-        <v>3162.4</v>
+        <v>914.94</v>
       </c>
       <c r="P3">
-        <v>501.1</v>
+        <v>10013.51</v>
       </c>
       <c r="Q3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -13639,7 +13642,7 @@
         <v>333</v>
       </c>
       <c r="B4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
@@ -13651,7 +13654,7 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>198.51</v>
+        <v>188.39</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -13663,28 +13666,28 @@
         <v>136</v>
       </c>
       <c r="J4">
-        <v>10.89</v>
+        <v>9.31</v>
       </c>
       <c r="K4">
-        <v>2.94</v>
+        <v>0.95</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M4" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="N4">
-        <v>62639.1</v>
+        <v>62292.2</v>
       </c>
       <c r="O4">
-        <v>3568.05</v>
+        <v>3162.4</v>
       </c>
       <c r="P4">
-        <v>22.35</v>
+        <v>501.1</v>
       </c>
       <c r="Q4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -13692,10 +13695,10 @@
         <v>333</v>
       </c>
       <c r="B5" t="s">
-        <v>337</v>
+        <v>292</v>
       </c>
       <c r="C5" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="D5" t="s">
         <v>133</v>
@@ -13704,7 +13707,7 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>193.96</v>
+        <v>186.81</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -13716,10 +13719,10 @@
         <v>136</v>
       </c>
       <c r="J5">
-        <v>8.01</v>
+        <v>5.48</v>
       </c>
       <c r="K5">
-        <v>1.96</v>
+        <v>0.41</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -13728,16 +13731,16 @@
         <v>165</v>
       </c>
       <c r="N5">
-        <v>62616.4</v>
+        <v>62193.6</v>
       </c>
       <c r="O5">
-        <v>939.4</v>
+        <v>932.96</v>
       </c>
       <c r="P5">
-        <v>801</v>
+        <v>4375.76</v>
       </c>
       <c r="Q5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -13745,10 +13748,10 @@
         <v>333</v>
       </c>
       <c r="B6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C6" t="s">
-        <v>339</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>133</v>
@@ -13757,7 +13760,7 @@
         <v>142</v>
       </c>
       <c r="F6">
-        <v>188.56</v>
+        <v>183.51</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -13769,63 +13772,63 @@
         <v>136</v>
       </c>
       <c r="J6">
-        <v>5.67</v>
+        <v>10.89</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="L6">
-        <v>5.17</v>
+        <v>15</v>
       </c>
       <c r="M6" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="N6">
-        <v>60996</v>
+        <v>62639.1</v>
       </c>
       <c r="O6">
-        <v>914.94</v>
+        <v>3568.05</v>
       </c>
       <c r="P6">
-        <v>10013.51</v>
+        <v>22.35</v>
       </c>
       <c r="Q6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B7" t="s">
         <v>340</v>
       </c>
       <c r="C7" t="s">
-        <v>331</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="E7" t="s">
         <v>142</v>
       </c>
       <c r="F7">
-        <v>187.48</v>
+        <v>180.91</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>-0.94</v>
       </c>
       <c r="I7" t="s">
         <v>136</v>
       </c>
       <c r="J7">
-        <v>3.05</v>
+        <v>1.7</v>
       </c>
       <c r="K7">
-        <v>1.14</v>
+        <v>2.36</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -13834,16 +13837,16 @@
         <v>165</v>
       </c>
       <c r="N7">
-        <v>62115.9</v>
+        <v>62596.16</v>
       </c>
       <c r="O7">
-        <v>931.7</v>
+        <v>939.84</v>
       </c>
       <c r="P7">
-        <v>794.6</v>
+        <v>175.16</v>
       </c>
       <c r="Q7" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -13851,10 +13854,10 @@
         <v>333</v>
       </c>
       <c r="B8" t="s">
-        <v>292</v>
+        <v>341</v>
       </c>
       <c r="C8" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D8" t="s">
         <v>133</v>
@@ -13863,7 +13866,7 @@
         <v>142</v>
       </c>
       <c r="F8">
-        <v>186.81</v>
+        <v>178.96</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -13875,81 +13878,81 @@
         <v>136</v>
       </c>
       <c r="J8">
-        <v>5.48</v>
+        <v>8.01</v>
       </c>
       <c r="K8">
-        <v>0.41</v>
+        <v>1.96</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M8" t="s">
         <v>165</v>
       </c>
       <c r="N8">
-        <v>62193.6</v>
+        <v>62616.4</v>
       </c>
       <c r="O8">
-        <v>932.96</v>
+        <v>939.4</v>
       </c>
       <c r="P8">
-        <v>4375.76</v>
+        <v>801</v>
       </c>
       <c r="Q8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B9" t="s">
-        <v>342</v>
+        <v>310</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
         <v>142</v>
       </c>
       <c r="F9">
-        <v>177.71</v>
+        <v>175.03</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="I9" t="s">
         <v>136</v>
       </c>
       <c r="J9">
-        <v>4.47</v>
+        <v>8.15</v>
       </c>
       <c r="K9">
-        <v>1.46</v>
+        <v>0.93</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="N9">
-        <v>48366</v>
+        <v>62105.4</v>
       </c>
       <c r="O9">
-        <v>819.54</v>
+        <v>1268.4</v>
       </c>
       <c r="P9">
-        <v>15848.82</v>
+        <v>724.25</v>
       </c>
       <c r="Q9" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -13957,19 +13960,19 @@
         <v>333</v>
       </c>
       <c r="B10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>331</v>
       </c>
       <c r="D10" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
         <v>142</v>
       </c>
       <c r="F10">
-        <v>177.33</v>
+        <v>172.48</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -13981,81 +13984,81 @@
         <v>136</v>
       </c>
       <c r="J10">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="K10">
-        <v>3.44</v>
+        <v>1.14</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M10" t="s">
         <v>165</v>
       </c>
       <c r="N10">
-        <v>62652.48</v>
+        <v>62115.9</v>
       </c>
       <c r="O10">
-        <v>1183.11</v>
+        <v>931.7</v>
       </c>
       <c r="P10">
-        <v>176.13</v>
+        <v>794.6</v>
       </c>
       <c r="Q10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B11" t="s">
-        <v>310</v>
+        <v>343</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="E11" t="s">
         <v>142</v>
       </c>
       <c r="F11">
-        <v>175.03</v>
+        <v>162.71</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="I11" t="s">
         <v>136</v>
       </c>
       <c r="J11">
-        <v>8.15</v>
+        <v>4.47</v>
       </c>
       <c r="K11">
-        <v>0.93</v>
+        <v>1.46</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M11" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="N11">
-        <v>62105.4</v>
+        <v>48366</v>
       </c>
       <c r="O11">
-        <v>1268.4</v>
+        <v>819.54</v>
       </c>
       <c r="P11">
-        <v>724.25</v>
+        <v>15848.82</v>
       </c>
       <c r="Q11" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -14196,7 +14199,7 @@
         <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -14338,7 +14341,7 @@
         <v>1</v>
       </c>
       <c r="Q5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -14391,7 +14394,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -14402,7 +14405,7 @@
         <v>201</v>
       </c>
       <c r="C7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D7" t="s">
         <v>331</v>
@@ -14444,7 +14447,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -14508,7 +14511,7 @@
         <v>201</v>
       </c>
       <c r="C9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D9" t="s">
         <v>331</v>
@@ -14603,7 +14606,7 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -14656,7 +14659,7 @@
         <v>1</v>
       </c>
       <c r="Q11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -14667,7 +14670,7 @@
         <v>164</v>
       </c>
       <c r="C12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D12" t="s">
         <v>28</v>
@@ -14709,7 +14712,7 @@
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -14720,7 +14723,7 @@
         <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D13" t="s">
         <v>28</v>
@@ -14773,7 +14776,7 @@
         <v>133</v>
       </c>
       <c r="C14" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
@@ -14826,7 +14829,7 @@
         <v>133</v>
       </c>
       <c r="C15" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D15" t="s">
         <v>331</v>
@@ -14879,7 +14882,7 @@
         <v>133</v>
       </c>
       <c r="C16" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D16" t="s">
         <v>331</v>
@@ -14935,7 +14938,7 @@
         <v>362</v>
       </c>
       <c r="D17" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E17" t="s">
         <v>164</v>
@@ -14974,7 +14977,7 @@
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -15027,7 +15030,7 @@
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -15080,7 +15083,7 @@
         <v>1</v>
       </c>
       <c r="Q19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -15133,7 +15136,7 @@
         <v>1</v>
       </c>
       <c r="Q20" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -15186,7 +15189,7 @@
         <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -15239,7 +15242,7 @@
         <v>1</v>
       </c>
       <c r="Q22" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -15253,7 +15256,7 @@
         <v>362</v>
       </c>
       <c r="D23" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E23" t="s">
         <v>164</v>
@@ -15565,19 +15568,19 @@
         <v>370</v>
       </c>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="C29" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D29" t="s">
         <v>28</v>
       </c>
       <c r="E29" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="F29">
-        <v>527.9000244140625</v>
+        <v>179.52000427246094</v>
       </c>
       <c r="G29" t="s">
         <v>356</v>
@@ -15589,7 +15592,7 @@
         <v>142</v>
       </c>
       <c r="J29">
-        <v>203.39</v>
+        <v>177.33</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -15598,10 +15601,10 @@
         <v>136</v>
       </c>
       <c r="M29">
-        <v>9.31</v>
+        <v>2.62</v>
       </c>
       <c r="N29">
-        <v>0.95</v>
+        <v>3.44</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -15610,27 +15613,27 @@
         <v>1</v>
       </c>
       <c r="Q29" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B30" t="s">
         <v>133</v>
       </c>
       <c r="C30" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>335</v>
       </c>
       <c r="E30" t="s">
         <v>133</v>
       </c>
       <c r="F30">
-        <v>23.700000762939453</v>
+        <v>10166</v>
       </c>
       <c r="G30" t="s">
         <v>356</v>
@@ -15642,7 +15645,7 @@
         <v>142</v>
       </c>
       <c r="J30">
-        <v>198.51</v>
+        <v>188.56</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -15651,24 +15654,24 @@
         <v>136</v>
       </c>
       <c r="M30">
-        <v>10.89</v>
+        <v>5.67</v>
       </c>
       <c r="N30">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="P30">
         <v>1</v>
       </c>
       <c r="Q30" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B31" t="s">
         <v>133</v>
@@ -15677,13 +15680,13 @@
         <v>337</v>
       </c>
       <c r="D31" t="s">
-        <v>331</v>
+        <v>28</v>
       </c>
       <c r="E31" t="s">
         <v>133</v>
       </c>
       <c r="F31">
-        <v>813.2000122070312</v>
+        <v>527.9000244140625</v>
       </c>
       <c r="G31" t="s">
         <v>356</v>
@@ -15695,7 +15698,7 @@
         <v>142</v>
       </c>
       <c r="J31">
-        <v>193.96</v>
+        <v>188.39</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -15704,39 +15707,39 @@
         <v>136</v>
       </c>
       <c r="M31">
-        <v>8.01</v>
+        <v>9.31</v>
       </c>
       <c r="N31">
-        <v>1.96</v>
+        <v>0.95</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P31">
         <v>1</v>
       </c>
       <c r="Q31" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B32" t="s">
         <v>133</v>
       </c>
       <c r="C32" t="s">
+        <v>292</v>
+      </c>
+      <c r="D32" t="s">
         <v>338</v>
-      </c>
-      <c r="D32" t="s">
-        <v>339</v>
       </c>
       <c r="E32" t="s">
         <v>133</v>
       </c>
       <c r="F32">
-        <v>10166</v>
+        <v>4442.39990234375</v>
       </c>
       <c r="G32" t="s">
         <v>356</v>
@@ -15748,7 +15751,7 @@
         <v>142</v>
       </c>
       <c r="J32">
-        <v>188.56</v>
+        <v>186.81</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -15757,39 +15760,39 @@
         <v>136</v>
       </c>
       <c r="M32">
-        <v>5.67</v>
+        <v>5.48</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="O32">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="P32">
         <v>1</v>
       </c>
       <c r="Q32" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B33" t="s">
         <v>133</v>
       </c>
       <c r="C33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D33" t="s">
-        <v>331</v>
+        <v>28</v>
       </c>
       <c r="E33" t="s">
         <v>133</v>
       </c>
       <c r="F33">
-        <v>806.7000122070312</v>
+        <v>23.700000762939453</v>
       </c>
       <c r="G33" t="s">
         <v>356</v>
@@ -15801,7 +15804,7 @@
         <v>142</v>
       </c>
       <c r="J33">
-        <v>187.48</v>
+        <v>183.51</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -15810,39 +15813,39 @@
         <v>136</v>
       </c>
       <c r="M33">
-        <v>3.05</v>
+        <v>10.89</v>
       </c>
       <c r="N33">
-        <v>1.14</v>
+        <v>2.94</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P33">
         <v>1</v>
       </c>
       <c r="Q33" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B34" t="s">
         <v>133</v>
       </c>
       <c r="C34" t="s">
-        <v>292</v>
+        <v>341</v>
       </c>
       <c r="D34" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="E34" t="s">
         <v>133</v>
       </c>
       <c r="F34">
-        <v>4442.39990234375</v>
+        <v>813.2000122070312</v>
       </c>
       <c r="G34" t="s">
         <v>356</v>
@@ -15854,7 +15857,7 @@
         <v>142</v>
       </c>
       <c r="J34">
-        <v>186.81</v>
+        <v>178.96</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -15863,39 +15866,39 @@
         <v>136</v>
       </c>
       <c r="M34">
-        <v>5.48</v>
+        <v>8.01</v>
       </c>
       <c r="N34">
-        <v>0.41</v>
+        <v>1.96</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P34">
         <v>1</v>
       </c>
       <c r="Q34" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B35" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="C35" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="D35" t="s">
         <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="F35">
-        <v>179.52000427246094</v>
+        <v>739.3499755859375</v>
       </c>
       <c r="G35" t="s">
         <v>356</v>
@@ -15907,7 +15910,7 @@
         <v>142</v>
       </c>
       <c r="J35">
-        <v>177.33</v>
+        <v>175.03</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -15916,10 +15919,10 @@
         <v>136</v>
       </c>
       <c r="M35">
-        <v>2.62</v>
+        <v>8.15</v>
       </c>
       <c r="N35">
-        <v>3.44</v>
+        <v>0.93</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -15928,27 +15931,27 @@
         <v>1</v>
       </c>
       <c r="Q35" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B36" t="s">
         <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>331</v>
       </c>
       <c r="E36" t="s">
         <v>133</v>
       </c>
       <c r="F36">
-        <v>739.3499755859375</v>
+        <v>806.7000122070312</v>
       </c>
       <c r="G36" t="s">
         <v>356</v>
@@ -15960,7 +15963,7 @@
         <v>142</v>
       </c>
       <c r="J36">
-        <v>175.03</v>
+        <v>172.48</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -15969,19 +15972,19 @@
         <v>136</v>
       </c>
       <c r="M36">
-        <v>8.15</v>
+        <v>3.05</v>
       </c>
       <c r="N36">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P36">
         <v>1</v>
       </c>
       <c r="Q36" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -16005,30 +16008,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -16040,7 +16043,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -29,7 +29,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-15T09:07:03.410Z</t>
+    <t>2026-07-15T09:18:49.234Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1133,7 +1133,7 @@
     <t>2026-07-15T08:22:05.305Z</t>
   </si>
   <si>
-    <t>2026-07-15T09:07:03.050Z</t>
+    <t>2026-07-15T09:18:48.877Z</t>
   </si>
   <si>
     <t>Date</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3616" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3626" uniqueCount="455">
   <si>
     <t>Metric</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-15T10:40:24.640Z</t>
+    <t>2026-07-15T11:09:23.555Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -945,207 +945,210 @@
     <t>KPIL</t>
   </si>
   <si>
-    <t>PENDING_PARTIAL_EXIT</t>
-  </si>
-  <si>
     <t>2026-07-10 09:17 IST ENTRY_BUY BUY 73 @ 1351.4; turnover 98652.2; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-14 09:17 IST PARTIAL_EXIT SELL 36 @ 1333.5; turnover 48006; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -644.4 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 18 @ 1305.2; turnover 23493.6; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -831.6</t>
   </si>
   <si>
+    <t>CJGEL</t>
+  </si>
+  <si>
+    <t>daily RS21 below zero daily RSI below 50 close below Supertrend close below 50-DMA official NSE delivery distribution setup grade WATCH</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>bullish engulfing</t>
+  </si>
+  <si>
+    <t>Weekly RSI 66.89 is above 50. Daily RSI 50.91 is above 50. Weekly RS 27.5% is above 0. Daily long RS55 5.5% is above 0. Daily short RS21 2.1% is above 0. Daily close 1349.90 is above Supertrend(10, 3) 1313.78. Price action strength: close is within 15% of 52-week high 1479.60. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 2.68% above daily Supertrend. Price confirmation: bullish engulfing is present. Volatility is controlled: ATR(14) is 3.04% of price. Liquidity strength: 20-day average turnover is Rs 511253745.19. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 16/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>CJGEL rank 195.82 is 108.18 points above weak position KPIL rank 87.64; replacement and weakness are confirmed across distinct closes. Weakness: daily RS21 below zero; daily RSI below 50; close below Supertrend; close below 50-DMA; official NSE delivery distribution; setup grade WATCH. Closing exit signal dated 2026-07-15; sell fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>My Custom List</t>
+  </si>
+  <si>
+    <t>NEXUSSURGL</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>09:21 IST</t>
+  </si>
+  <si>
+    <t>09:17 market order; first actual traded candle at 09:21 IST</t>
+  </si>
+  <si>
+    <t>09:17 order / 09:21 actual fill</t>
+  </si>
+  <si>
+    <t>2026-07-13 09:17 IST ENTRY_BUY BUY 31 @ 19.59; turnover 607.29; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-13 09:17 IST PARTIAL_EXIT SELL 15 @ 19.59; turnover 293.85; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST FULL_EXIT SELL 16 @ 18.5; turnover 296; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -17.44</t>
+  </si>
+  <si>
+    <t>MODEL_EXIT</t>
+  </si>
+  <si>
+    <t>FULL_EXIT</t>
+  </si>
+  <si>
+    <t>Daily RS55 is below zero and daily close is below Supertrend.</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Bollinger trend/range context; MACD and OBV confirmation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>Breakout or 52-week high zone; Price-action base and higher-low structure; Retracement/pullback buy setup; GTF demand/supply confluence; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Volume participation; Volatility and liquidity control; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Operator delivery confirmation; Index option-chain positioning; News/event context</t>
+  </si>
+  <si>
+    <t>hammer</t>
+  </si>
+  <si>
+    <t>Weekly RSI 58.57 is above 50. Daily RSI 52.69 is above 50. Weekly RS 21.8% is above 0. Daily long RS55 4.6% is above 0. Daily short RS21 1.3% is above 0. Daily close 20.87 is above Supertrend(10, 3) 18.63. Entry style: Trend continuation buy. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: close is above the middle band 20.41 with bandwidth 14.62%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: hammer is present. Volatility is controlled: ATR(14) is 5.69% of price. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 0/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Official NSE delivery history loaded for 2395 EQ symbols across 6 sessions. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Sector breadth strong: My List has 123/175 stocks (70.29%) passing daily strength. Institutional concept coverage: 16/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 168.93; planned allocation Rs 83.48, quantity 4, initial stop 20, planned risk Rs 3.48. Closing signal dated 2026-07-10; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>Daily RS55 is below zero and daily close is below Supertrend. Closing exit signal dated 2026-07-14; sell fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>SKIPPED_ENTRY</t>
+  </si>
+  <si>
+    <t>first_5m_candle_open</t>
+  </si>
+  <si>
+    <t>09:15-09:20 IST</t>
+  </si>
+  <si>
+    <t>3/4</t>
+  </si>
+  <si>
+    <t>F&amp;O listed with lot size 150; OI participation 2.01%, volume 72606.00.</t>
+  </si>
+  <si>
+    <t>2/5 commodity/currency proxies are bullish; 3 bearish.</t>
+  </si>
+  <si>
+    <t>20/22</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>Volume participation</t>
+  </si>
+  <si>
+    <t>66.43% (93/140)</t>
+  </si>
+  <si>
+    <t>Weekly RSI 55.15 is above 50. Daily RSI 60.53 is above 50. Weekly RS 6.8% is above 0. Daily long RS55 2.1% is above 0. Daily short RS21 2.3% is above 0. Daily close 4506.80 is above Supertrend(10, 3) 4193.48. Entry style: Retracement buy near 50-DMA. Price action strength: close is within 15% of 52-week high 5065.00. Retracement buy: price pulled back 6.81% from the 55-day high and reclaimed near 50-DMA 4407.24; support distance is 2.21%. Retracement confirmation: pullback volume ratio 0.58 and reclaim volume ratio 0.99 with candle close location 85.96%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.95% above daily Supertrend. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.15% of price. Liquidity strength: 20-day average turnover is Rs 3498340071.08. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 150; OI participation 2.01%, volume 72606.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 20/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>PREMIERENE</t>
+  </si>
+  <si>
+    <t>F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00.</t>
+  </si>
+  <si>
+    <t>18/22</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Retracement/pullback buy setup; Risk reference discipline</t>
+  </si>
+  <si>
+    <t>Weekly RSI 64.52 is above 50. Daily RSI 67.28 is above 50. Weekly RS 46.9% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 0.0% is above 0. Daily close 1117.20 is above Supertrend(10, 3) 1007.42. Entry style: Breakout buy. Price action strength: close crossed 55-day high 1103.90. Volume shocker: latest volume is 1.56x the 50-day average. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.97% of price. Liquidity strength: 20-day average turnover is Rs 1219054718.79. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 18/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>SBCL</t>
+  </si>
+  <si>
+    <t>14/22</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Retracement/pullback buy setup; Volume participation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
+  </si>
+  <si>
+    <t>Weekly RSI 66.35 is above 50. Daily RSI 53.52 is above 50. Weekly RS 45.4% is above 0. Daily long RS55 21.9% is above 0. Daily short RS21 5.9% is above 0. Daily close 747.05 is above Supertrend(10, 3) 679.08. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 814.00. Retracement watch: pullback depth 8.22% is valid, but support/reclaim/volume/risk confirmation is incomplete. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 4.83% of price. Liquidity strength: 20-day average turnover is Rs 407588740.32. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 14/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>Transaction</t>
+  </si>
+  <si>
+    <t>Side</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Turnover</t>
+  </si>
+  <si>
+    <t>Brokerage</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Exchange Charges</t>
+  </si>
+  <si>
+    <t>SEBI Charges</t>
+  </si>
+  <si>
+    <t>Stamp Duty</t>
+  </si>
+  <si>
+    <t>IPFT</t>
+  </si>
+  <si>
+    <t>GST</t>
+  </si>
+  <si>
+    <t>DP Charge</t>
+  </si>
+  <si>
+    <t>Total Charges</t>
+  </si>
+  <si>
+    <t>Gross P&amp;L</t>
+  </si>
+  <si>
+    <t>Allocated Buy Charges</t>
+  </si>
+  <si>
+    <t>Net P&amp;L</t>
+  </si>
+  <si>
+    <t>ENTRY_BUY</t>
+  </si>
+  <si>
+    <t>BUY</t>
+  </si>
+  <si>
     <t>PARTIAL_EXIT</t>
   </si>
   <si>
-    <t>Fundamental deterioration confirms the already-established technical weakness.</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>bullish engulfing</t>
-  </si>
-  <si>
-    <t>Weekly RSI 66.89 is above 50. Daily RSI 50.91 is above 50. Weekly RS 27.5% is above 0. Daily long RS55 5.5% is above 0. Daily short RS21 2.1% is above 0. Daily close 1349.90 is above Supertrend(10, 3) 1313.78. Price action strength: close is within 15% of 52-week high 1479.60. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 2.68% above daily Supertrend. Price confirmation: bullish engulfing is present. Volatility is controlled: ATR(14) is 3.04% of price. Liquidity strength: 20-day average turnover is Rs 511253745.19. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 16/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>My Custom List</t>
-  </si>
-  <si>
-    <t>NEXUSSURGL</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>09:21 IST</t>
-  </si>
-  <si>
-    <t>09:17 market order; first actual traded candle at 09:21 IST</t>
-  </si>
-  <si>
-    <t>09:17 order / 09:21 actual fill</t>
-  </si>
-  <si>
-    <t>2026-07-13 09:17 IST ENTRY_BUY BUY 31 @ 19.59; turnover 607.29; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-13 09:17 IST PARTIAL_EXIT SELL 15 @ 19.59; turnover 293.85; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST FULL_EXIT SELL 16 @ 18.5; turnover 296; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -17.44</t>
-  </si>
-  <si>
-    <t>MODEL_EXIT</t>
-  </si>
-  <si>
-    <t>FULL_EXIT</t>
-  </si>
-  <si>
-    <t>Daily RS55 is below zero and daily close is below Supertrend.</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Bollinger trend/range context; MACD and OBV confirmation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>Breakout or 52-week high zone; Price-action base and higher-low structure; Retracement/pullback buy setup; GTF demand/supply confluence; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Volume participation; Volatility and liquidity control; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Operator delivery confirmation; Index option-chain positioning; News/event context</t>
-  </si>
-  <si>
-    <t>hammer</t>
-  </si>
-  <si>
-    <t>Weekly RSI 58.57 is above 50. Daily RSI 52.69 is above 50. Weekly RS 21.8% is above 0. Daily long RS55 4.6% is above 0. Daily short RS21 1.3% is above 0. Daily close 20.87 is above Supertrend(10, 3) 18.63. Entry style: Trend continuation buy. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: close is above the middle band 20.41 with bandwidth 14.62%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: hammer is present. Volatility is controlled: ATR(14) is 5.69% of price. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 0/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Official NSE delivery history loaded for 2395 EQ symbols across 6 sessions. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Sector breadth strong: My List has 123/175 stocks (70.29%) passing daily strength. Institutional concept coverage: 16/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 168.93; planned allocation Rs 83.48, quantity 4, initial stop 20, planned risk Rs 3.48. Closing signal dated 2026-07-10; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>Daily RS55 is below zero and daily close is below Supertrend. Closing exit signal dated 2026-07-14; sell fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>HAL</t>
-  </si>
-  <si>
-    <t>SKIPPED_ENTRY</t>
-  </si>
-  <si>
-    <t>first_5m_candle_open</t>
-  </si>
-  <si>
-    <t>09:15-09:20 IST</t>
-  </si>
-  <si>
-    <t>3/4</t>
-  </si>
-  <si>
-    <t>F&amp;O listed with lot size 150; OI participation 2.01%, volume 72606.00.</t>
-  </si>
-  <si>
-    <t>2/5 commodity/currency proxies are bullish; 3 bearish.</t>
-  </si>
-  <si>
-    <t>20/22</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>Volume participation</t>
-  </si>
-  <si>
-    <t>66.43% (93/140)</t>
-  </si>
-  <si>
-    <t>Weekly RSI 55.15 is above 50. Daily RSI 60.53 is above 50. Weekly RS 6.8% is above 0. Daily long RS55 2.1% is above 0. Daily short RS21 2.3% is above 0. Daily close 4506.80 is above Supertrend(10, 3) 4193.48. Entry style: Retracement buy near 50-DMA. Price action strength: close is within 15% of 52-week high 5065.00. Retracement buy: price pulled back 6.81% from the 55-day high and reclaimed near 50-DMA 4407.24; support distance is 2.21%. Retracement confirmation: pullback volume ratio 0.58 and reclaim volume ratio 0.99 with candle close location 85.96%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.95% above daily Supertrend. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.15% of price. Liquidity strength: 20-day average turnover is Rs 3498340071.08. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 150; OI participation 2.01%, volume 72606.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 20/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>PREMIERENE</t>
-  </si>
-  <si>
-    <t>F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00.</t>
-  </si>
-  <si>
-    <t>18/22</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Retracement/pullback buy setup; Risk reference discipline</t>
-  </si>
-  <si>
-    <t>Weekly RSI 64.52 is above 50. Daily RSI 67.28 is above 50. Weekly RS 46.9% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 0.0% is above 0. Daily close 1117.20 is above Supertrend(10, 3) 1007.42. Entry style: Breakout buy. Price action strength: close crossed 55-day high 1103.90. Volume shocker: latest volume is 1.56x the 50-day average. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.97% of price. Liquidity strength: 20-day average turnover is Rs 1219054718.79. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 18/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>SBCL</t>
-  </si>
-  <si>
-    <t>14/22</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Retracement/pullback buy setup; Volume participation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
-  </si>
-  <si>
-    <t>Weekly RSI 66.35 is above 50. Daily RSI 53.52 is above 50. Weekly RS 45.4% is above 0. Daily long RS55 21.9% is above 0. Daily short RS21 5.9% is above 0. Daily close 747.05 is above Supertrend(10, 3) 679.08. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 814.00. Retracement watch: pullback depth 8.22% is valid, but support/reclaim/volume/risk confirmation is incomplete. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 4.83% of price. Liquidity strength: 20-day average turnover is Rs 407588740.32. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 14/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>Transaction</t>
-  </si>
-  <si>
-    <t>Side</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Turnover</t>
-  </si>
-  <si>
-    <t>Brokerage</t>
-  </si>
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Exchange Charges</t>
-  </si>
-  <si>
-    <t>SEBI Charges</t>
-  </si>
-  <si>
-    <t>Stamp Duty</t>
-  </si>
-  <si>
-    <t>IPFT</t>
-  </si>
-  <si>
-    <t>GST</t>
-  </si>
-  <si>
-    <t>DP Charge</t>
-  </si>
-  <si>
-    <t>Total Charges</t>
-  </si>
-  <si>
-    <t>Gross P&amp;L</t>
-  </si>
-  <si>
-    <t>Allocated Buy Charges</t>
-  </si>
-  <si>
-    <t>Net P&amp;L</t>
-  </si>
-  <si>
-    <t>ENTRY_BUY</t>
-  </si>
-  <si>
-    <t>BUY</t>
-  </si>
-  <si>
     <t>SELL</t>
   </si>
   <si>
@@ -1212,10 +1215,22 @@
     <t>Capital Goods</t>
   </si>
   <si>
+    <t>WAITING_ROTATION</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Waiting for GRINDWELL exact 09:17 rotation sell to release cash.</t>
+  </si>
+  <si>
+    <t>SGFIN</t>
+  </si>
+  <si>
     <t>WAITING_EXECUTION_PREFLIGHT</t>
   </si>
   <si>
-    <t>Healthcare</t>
+    <t>Retracement buy near 55D high retest</t>
   </si>
   <si>
     <t>Rotation sell is waiting because the replacement's exact next-session 09:17 price is not available for preflight.</t>
@@ -1224,21 +1239,12 @@
     <t>WAITING_CAPITAL</t>
   </si>
   <si>
-    <t>SGFIN</t>
+    <t>ASTERDM</t>
   </si>
   <si>
     <t>Maximum open-position limit reached.</t>
   </si>
   <si>
-    <t>CJGEL</t>
-  </si>
-  <si>
-    <t>Retracement buy near 55D high retest</t>
-  </si>
-  <si>
-    <t>ASTERDM</t>
-  </si>
-  <si>
     <t>ENDURANCE</t>
   </si>
   <si>
@@ -1351,6 +1357,9 @@
   </si>
   <si>
     <t>2026-07-15T10:40:23.503Z</t>
+  </si>
+  <si>
+    <t>2026-07-15T11:09:22.908Z</t>
   </si>
   <si>
     <t>Type</t>
@@ -7316,7 +7325,7 @@
         <v>307</v>
       </c>
       <c r="F3" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="G3" t="s">
         <v>254</v>
@@ -7373,7 +7382,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z3" t="s">
         <v>150</v>
@@ -7463,14 +7472,14 @@
         <v>-1476</v>
       </c>
       <c r="BC3" t="s">
+        <v>308</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>296</v>
+      </c>
+      <c r="BE3" t="s">
         <v>309</v>
       </c>
-      <c r="BD3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>150</v>
-      </c>
       <c r="BF3" t="s">
         <v>150</v>
       </c>
@@ -7481,10 +7490,10 @@
         <v>150</v>
       </c>
       <c r="BI3" t="s">
+        <v>152</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>310</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>311</v>
       </c>
       <c r="BK3">
         <v>2</v>
@@ -7547,10 +7556,10 @@
         <v>272</v>
       </c>
       <c r="CE3" t="s">
+        <v>311</v>
+      </c>
+      <c r="CF3" t="s">
         <v>312</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>313</v>
       </c>
       <c r="CG3" t="s">
         <v>260</v>
@@ -7595,7 +7604,7 @@
         <v>150</v>
       </c>
       <c r="CU3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="CV3">
         <v>1321</v>
@@ -7607,10 +7616,10 @@
         <v>1321</v>
       </c>
       <c r="CY3" t="s">
+        <v>314</v>
+      </c>
+      <c r="CZ3" t="s">
         <v>315</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -9062,25 +9071,25 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>252</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>307</v>
       </c>
       <c r="E3" t="s">
-        <v>145</v>
+        <v>307</v>
       </c>
       <c r="F3" t="s">
-        <v>146</v>
+        <v>294</v>
       </c>
       <c r="G3" t="s">
-        <v>147</v>
+        <v>254</v>
       </c>
       <c r="H3" t="s">
-        <v>148</v>
+        <v>219</v>
       </c>
       <c r="I3" t="s">
         <v>47</v>
@@ -9089,40 +9098,40 @@
         <v>47</v>
       </c>
       <c r="K3">
-        <v>921.25</v>
+        <v>1351.4</v>
       </c>
       <c r="L3">
-        <v>921.25</v>
+        <v>1351.4</v>
       </c>
       <c r="M3" t="s">
         <v>149</v>
       </c>
       <c r="N3">
-        <v>108</v>
+        <v>19</v>
       </c>
       <c r="O3">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="P3">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="Q3">
-        <v>99495</v>
+        <v>25676.6</v>
       </c>
       <c r="R3">
-        <v>99030.6</v>
+        <v>24660.1</v>
       </c>
       <c r="S3">
-        <v>916.95</v>
+        <v>1297.9</v>
       </c>
       <c r="T3" s="2">
-        <v>-464.4</v>
+        <v>-1016.5</v>
       </c>
       <c r="U3">
-        <v>-0.47</v>
+        <v>-3.96</v>
       </c>
       <c r="V3">
-        <v>-464.4</v>
+        <v>-1016.5</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -9131,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z3" t="s">
         <v>150</v>
@@ -9155,7 +9164,7 @@
         <v>150</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-1476</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -9172,23 +9181,23 @@
       <c r="AL3" t="s">
         <v>47</v>
       </c>
-      <c r="AM3">
-        <v>213.48</v>
+      <c r="AM3" t="s">
+        <v>150</v>
       </c>
       <c r="AN3">
-        <v>196.25</v>
+        <v>87.64</v>
       </c>
       <c r="AO3">
-        <v>847.55</v>
+        <v>1251.2</v>
       </c>
       <c r="AP3">
-        <v>847.55</v>
+        <v>1278.43</v>
       </c>
       <c r="AQ3">
-        <v>7959.6</v>
+        <v>7314.6</v>
       </c>
       <c r="AR3">
-        <v>-0.06</v>
+        <v>-0.53</v>
       </c>
       <c r="AS3">
         <v>0</v>
@@ -9215,19 +9224,19 @@
         <v>150</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>-1476</v>
       </c>
       <c r="BC3" t="s">
-        <v>151</v>
+        <v>308</v>
       </c>
       <c r="BD3" t="s">
-        <v>150</v>
+        <v>296</v>
       </c>
       <c r="BE3" t="s">
-        <v>150</v>
+        <v>309</v>
       </c>
       <c r="BF3" t="s">
         <v>150</v>
@@ -9242,34 +9251,34 @@
         <v>152</v>
       </c>
       <c r="BJ3" t="s">
-        <v>153</v>
+        <v>310</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL3" t="s">
         <v>150</v>
       </c>
       <c r="BM3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="BN3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="BO3" t="s">
         <v>156</v>
       </c>
       <c r="BP3">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="BQ3">
         <v>4</v>
       </c>
       <c r="BR3" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="BS3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="BT3" t="s">
         <v>150</v>
@@ -9281,13 +9290,13 @@
         <v>27</v>
       </c>
       <c r="BW3" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="BX3" t="s">
         <v>150</v>
       </c>
       <c r="BY3" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BZ3" t="s">
         <v>161</v>
@@ -9299,76 +9308,76 @@
         <v>163</v>
       </c>
       <c r="CC3" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="CD3" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
       <c r="CE3" t="s">
-        <v>166</v>
+        <v>311</v>
       </c>
       <c r="CF3" t="s">
-        <v>167</v>
+        <v>312</v>
       </c>
       <c r="CG3" t="s">
-        <v>168</v>
+        <v>260</v>
       </c>
       <c r="CH3" t="s">
-        <v>169</v>
+        <v>261</v>
       </c>
       <c r="CI3" t="s">
-        <v>170</v>
+        <v>262</v>
       </c>
       <c r="CJ3" t="s">
         <v>171</v>
       </c>
       <c r="CK3" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="CL3">
-        <v>3.69</v>
+        <v>0.32</v>
       </c>
       <c r="CM3">
-        <v>5.2</v>
+        <v>3.04</v>
       </c>
       <c r="CN3">
-        <v>16.27</v>
+        <v>2.68</v>
       </c>
       <c r="CO3" t="s">
         <v>27</v>
       </c>
-      <c r="CP3">
-        <v>0</v>
+      <c r="CP3" t="s">
+        <v>150</v>
       </c>
       <c r="CQ3" t="s">
-        <v>172</v>
-      </c>
-      <c r="CR3">
-        <v>1.6</v>
-      </c>
-      <c r="CS3">
-        <v>0.6</v>
-      </c>
-      <c r="CT3">
-        <v>3.69</v>
+        <v>150</v>
+      </c>
+      <c r="CR3" t="s">
+        <v>150</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>150</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>150</v>
       </c>
       <c r="CU3" t="s">
-        <v>173</v>
+        <v>313</v>
       </c>
       <c r="CV3">
-        <v>822.4</v>
+        <v>1321</v>
       </c>
       <c r="CW3">
-        <v>800.6</v>
+        <v>1321</v>
       </c>
       <c r="CX3">
-        <v>794</v>
+        <v>1321</v>
       </c>
       <c r="CY3" t="s">
-        <v>174</v>
+        <v>314</v>
       </c>
       <c r="CZ3" t="s">
-        <v>150</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:104" x14ac:dyDescent="0.25">
@@ -9379,22 +9388,22 @@
         <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="F4" t="s">
         <v>146</v>
       </c>
       <c r="G4" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I4" t="s">
         <v>47</v>
@@ -9403,40 +9412,40 @@
         <v>47</v>
       </c>
       <c r="K4">
-        <v>853</v>
+        <v>921.25</v>
       </c>
       <c r="L4">
-        <v>853</v>
+        <v>921.25</v>
       </c>
       <c r="M4" t="s">
         <v>149</v>
       </c>
       <c r="N4">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="P4">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="Q4">
-        <v>58004</v>
+        <v>99495</v>
       </c>
       <c r="R4">
-        <v>55239.8</v>
+        <v>99030.6</v>
       </c>
       <c r="S4">
-        <v>812.35</v>
+        <v>916.95</v>
       </c>
       <c r="T4" s="2">
-        <v>-2764.2</v>
+        <v>-464.4</v>
       </c>
       <c r="U4">
-        <v>-4.77</v>
+        <v>-0.47</v>
       </c>
       <c r="V4">
-        <v>-2764.2</v>
+        <v>-464.4</v>
       </c>
       <c r="W4">
         <v>0</v>
@@ -9487,22 +9496,22 @@
         <v>47</v>
       </c>
       <c r="AM4">
-        <v>191.09</v>
+        <v>213.48</v>
       </c>
       <c r="AN4">
-        <v>113.61</v>
+        <v>196.25</v>
       </c>
       <c r="AO4">
-        <v>805.6</v>
+        <v>847.55</v>
       </c>
       <c r="AP4">
-        <v>800.16</v>
+        <v>847.55</v>
       </c>
       <c r="AQ4">
-        <v>3223.2</v>
+        <v>7959.6</v>
       </c>
       <c r="AR4">
-        <v>-0.86</v>
+        <v>-0.06</v>
       </c>
       <c r="AS4">
         <v>0</v>
@@ -9535,7 +9544,7 @@
         <v>0</v>
       </c>
       <c r="BC4" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="BD4" t="s">
         <v>150</v>
@@ -9556,10 +9565,10 @@
         <v>152</v>
       </c>
       <c r="BJ4" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="BK4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="s">
         <v>150</v>
@@ -9568,13 +9577,13 @@
         <v>154</v>
       </c>
       <c r="BN4" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="BO4" t="s">
         <v>156</v>
       </c>
       <c r="BP4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="BQ4">
         <v>4</v>
@@ -9583,13 +9592,13 @@
         <v>157</v>
       </c>
       <c r="BS4" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="BT4" t="s">
         <v>150</v>
       </c>
       <c r="BU4" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="BV4" t="s">
         <v>27</v>
@@ -9613,73 +9622,73 @@
         <v>163</v>
       </c>
       <c r="CC4" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="CD4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="CE4" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="CF4" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="CG4" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="CH4" t="s">
         <v>169</v>
       </c>
       <c r="CI4" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="CJ4" t="s">
         <v>171</v>
       </c>
       <c r="CK4" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="CL4">
-        <v>0.21</v>
+        <v>3.69</v>
       </c>
       <c r="CM4">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
       <c r="CN4">
-        <v>8.7</v>
+        <v>16.27</v>
       </c>
       <c r="CO4" t="s">
         <v>27</v>
       </c>
       <c r="CP4">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="CQ4" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="CR4">
-        <v>8.7</v>
+        <v>1.6</v>
       </c>
       <c r="CS4">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="CT4">
-        <v>0.21</v>
+        <v>3.69</v>
       </c>
       <c r="CU4" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="CV4">
-        <v>805.6</v>
+        <v>822.4</v>
       </c>
       <c r="CW4">
-        <v>805.6</v>
+        <v>800.6</v>
       </c>
       <c r="CX4">
-        <v>805.6</v>
+        <v>794</v>
       </c>
       <c r="CY4" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="CZ4" t="s">
         <v>150</v>
@@ -9696,10 +9705,10 @@
         <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="E5" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="F5" t="s">
         <v>146</v>
@@ -9717,40 +9726,40 @@
         <v>47</v>
       </c>
       <c r="K5">
-        <v>649.15</v>
+        <v>853</v>
       </c>
       <c r="L5">
-        <v>649.15</v>
+        <v>853</v>
       </c>
       <c r="M5" t="s">
         <v>149</v>
       </c>
       <c r="N5">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="O5">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="P5">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="Q5">
-        <v>72704.8</v>
+        <v>58004</v>
       </c>
       <c r="R5">
-        <v>70492.8</v>
+        <v>55239.8</v>
       </c>
       <c r="S5">
-        <v>629.4</v>
+        <v>812.35</v>
       </c>
       <c r="T5" s="2">
-        <v>-2212</v>
+        <v>-2764.2</v>
       </c>
       <c r="U5">
-        <v>-3.04</v>
+        <v>-4.77</v>
       </c>
       <c r="V5">
-        <v>-2212</v>
+        <v>-2764.2</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -9801,22 +9810,22 @@
         <v>47</v>
       </c>
       <c r="AM5">
-        <v>195.78</v>
+        <v>191.09</v>
       </c>
       <c r="AN5">
-        <v>176.71</v>
+        <v>113.61</v>
       </c>
       <c r="AO5">
-        <v>597.22</v>
+        <v>805.6</v>
       </c>
       <c r="AP5">
-        <v>597.22</v>
+        <v>800.16</v>
       </c>
       <c r="AQ5">
-        <v>5816.16</v>
+        <v>3223.2</v>
       </c>
       <c r="AR5">
-        <v>-0.38</v>
+        <v>-0.86</v>
       </c>
       <c r="AS5">
         <v>0</v>
@@ -9849,7 +9858,7 @@
         <v>0</v>
       </c>
       <c r="BC5" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="BD5" t="s">
         <v>150</v>
@@ -9870,10 +9879,10 @@
         <v>152</v>
       </c>
       <c r="BJ5" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL5" t="s">
         <v>150</v>
@@ -9882,28 +9891,28 @@
         <v>154</v>
       </c>
       <c r="BN5" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="BO5" t="s">
         <v>156</v>
       </c>
       <c r="BP5">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BQ5">
         <v>4</v>
       </c>
       <c r="BR5" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="BS5" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="BT5" t="s">
         <v>150</v>
       </c>
       <c r="BU5" t="s">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="BV5" t="s">
         <v>27</v>
@@ -9927,16 +9936,16 @@
         <v>163</v>
       </c>
       <c r="CC5" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="CD5" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="CE5" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="CF5" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="CG5" t="s">
         <v>188</v>
@@ -9945,55 +9954,55 @@
         <v>169</v>
       </c>
       <c r="CI5" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="CJ5" t="s">
         <v>171</v>
       </c>
       <c r="CK5" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="CL5">
-        <v>90.28</v>
+        <v>0.21</v>
       </c>
       <c r="CM5">
-        <v>3.77</v>
+        <v>4.11</v>
       </c>
       <c r="CN5">
-        <v>16.2</v>
+        <v>8.7</v>
       </c>
       <c r="CO5" t="s">
         <v>27</v>
       </c>
       <c r="CP5">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="CQ5" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="CR5">
-        <v>15.12</v>
+        <v>8.7</v>
       </c>
       <c r="CS5">
-        <v>1.31</v>
+        <v>0.33</v>
       </c>
       <c r="CT5">
-        <v>90.28</v>
+        <v>0.21</v>
       </c>
       <c r="CU5" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="CV5">
-        <v>556.8</v>
+        <v>805.6</v>
       </c>
       <c r="CW5">
-        <v>549</v>
+        <v>805.6</v>
       </c>
       <c r="CX5">
-        <v>536</v>
+        <v>805.6</v>
       </c>
       <c r="CY5" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="CZ5" t="s">
         <v>150</v>
@@ -10007,13 +10016,13 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="D6" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="E6" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F6" t="s">
         <v>146</v>
@@ -10031,40 +10040,40 @@
         <v>47</v>
       </c>
       <c r="K6">
-        <v>88.49</v>
+        <v>649.15</v>
       </c>
       <c r="L6">
-        <v>88.49</v>
+        <v>649.15</v>
       </c>
       <c r="M6" t="s">
         <v>149</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="P6">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="Q6">
-        <v>442.45</v>
+        <v>72704.8</v>
       </c>
       <c r="R6">
-        <v>441.8</v>
+        <v>70492.8</v>
       </c>
       <c r="S6">
-        <v>88.36</v>
+        <v>629.4</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.65</v>
+        <v>-2212</v>
       </c>
       <c r="U6">
-        <v>-0.15</v>
+        <v>-3.04</v>
       </c>
       <c r="V6">
-        <v>-0.65</v>
+        <v>-2212</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -10115,22 +10124,22 @@
         <v>47</v>
       </c>
       <c r="AM6">
-        <v>176.28</v>
+        <v>195.78</v>
       </c>
       <c r="AN6">
-        <v>161.9</v>
+        <v>176.71</v>
       </c>
       <c r="AO6">
-        <v>84.5</v>
+        <v>597.22</v>
       </c>
       <c r="AP6">
-        <v>84.65</v>
+        <v>597.22</v>
       </c>
       <c r="AQ6">
-        <v>19.95</v>
+        <v>5816.16</v>
       </c>
       <c r="AR6">
-        <v>-0.03</v>
+        <v>-0.38</v>
       </c>
       <c r="AS6">
         <v>0</v>
@@ -10163,7 +10172,7 @@
         <v>0</v>
       </c>
       <c r="BC6" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="BD6" t="s">
         <v>150</v>
@@ -10184,7 +10193,7 @@
         <v>152</v>
       </c>
       <c r="BJ6" t="s">
-        <v>207</v>
+        <v>150</v>
       </c>
       <c r="BK6">
         <v>0</v>
@@ -10196,16 +10205,16 @@
         <v>154</v>
       </c>
       <c r="BN6" t="s">
-        <v>208</v>
+        <v>155</v>
       </c>
       <c r="BO6" t="s">
         <v>156</v>
       </c>
       <c r="BP6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BQ6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BR6" t="s">
         <v>196</v>
@@ -10214,10 +10223,10 @@
         <v>158</v>
       </c>
       <c r="BT6" t="s">
-        <v>209</v>
+        <v>150</v>
       </c>
       <c r="BU6" t="s">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="BV6" t="s">
         <v>27</v>
@@ -10244,70 +10253,70 @@
         <v>197</v>
       </c>
       <c r="CD6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="CE6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="CF6" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="CG6" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="CH6" t="s">
         <v>169</v>
       </c>
       <c r="CI6" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="CJ6" t="s">
         <v>171</v>
       </c>
       <c r="CK6" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="CL6">
-        <v>2.77</v>
+        <v>90.28</v>
       </c>
       <c r="CM6">
-        <v>2.54</v>
+        <v>3.77</v>
       </c>
       <c r="CN6">
-        <v>7.97</v>
+        <v>16.2</v>
       </c>
       <c r="CO6" t="s">
         <v>27</v>
       </c>
       <c r="CP6">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="CR6">
-        <v>1.91</v>
+        <v>15.12</v>
       </c>
       <c r="CS6">
-        <v>0.4</v>
+        <v>1.31</v>
       </c>
       <c r="CT6">
-        <v>2.77</v>
+        <v>90.28</v>
       </c>
       <c r="CU6" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="CV6">
-        <v>85.99</v>
+        <v>556.8</v>
       </c>
       <c r="CW6">
-        <v>84.5</v>
+        <v>549</v>
       </c>
       <c r="CX6">
-        <v>84.44</v>
+        <v>536</v>
       </c>
       <c r="CY6" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="CZ6" t="s">
         <v>150</v>
@@ -10321,22 +10330,22 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D7" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="E7" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="F7" t="s">
         <v>146</v>
       </c>
       <c r="G7" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="H7" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="I7" t="s">
         <v>47</v>
@@ -10345,40 +10354,40 @@
         <v>47</v>
       </c>
       <c r="K7">
-        <v>4421.9</v>
+        <v>88.49</v>
       </c>
       <c r="L7">
-        <v>4421.9</v>
+        <v>88.49</v>
       </c>
       <c r="M7" t="s">
         <v>149</v>
       </c>
       <c r="N7">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>97281.8</v>
+        <v>442.45</v>
       </c>
       <c r="R7">
-        <v>97455.6</v>
+        <v>441.8</v>
       </c>
       <c r="S7">
-        <v>4429.8</v>
-      </c>
-      <c r="T7" s="3">
-        <v>173.8</v>
+        <v>88.36</v>
+      </c>
+      <c r="T7" s="2">
+        <v>-0.65</v>
       </c>
       <c r="U7">
-        <v>0.18</v>
+        <v>-0.15</v>
       </c>
       <c r="V7">
-        <v>173.8</v>
+        <v>-0.65</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -10429,22 +10438,22 @@
         <v>47</v>
       </c>
       <c r="AM7">
-        <v>167.02</v>
+        <v>176.28</v>
       </c>
       <c r="AN7">
-        <v>77.5</v>
+        <v>161.9</v>
       </c>
       <c r="AO7">
-        <v>4319.5</v>
+        <v>84.5</v>
       </c>
       <c r="AP7">
-        <v>4352.73</v>
+        <v>84.65</v>
       </c>
       <c r="AQ7">
-        <v>2252.8</v>
+        <v>19.95</v>
       </c>
       <c r="AR7">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="AS7">
         <v>0</v>
@@ -10477,7 +10486,7 @@
         <v>0</v>
       </c>
       <c r="BC7" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="BD7" t="s">
         <v>150</v>
@@ -10498,7 +10507,7 @@
         <v>152</v>
       </c>
       <c r="BJ7" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="BK7">
         <v>0</v>
@@ -10507,37 +10516,37 @@
         <v>150</v>
       </c>
       <c r="BM7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="BN7" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="BO7" t="s">
         <v>156</v>
       </c>
       <c r="BP7">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BQ7">
         <v>1</v>
       </c>
       <c r="BR7" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="BS7" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="BT7" t="s">
-        <v>150</v>
+        <v>209</v>
       </c>
       <c r="BU7" t="s">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="BV7" t="s">
         <v>27</v>
       </c>
       <c r="BW7" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="BX7" t="s">
         <v>150</v>
@@ -10555,25 +10564,25 @@
         <v>163</v>
       </c>
       <c r="CC7" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="CD7" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="CE7" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="CF7" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="CG7" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="CH7" t="s">
         <v>169</v>
       </c>
       <c r="CI7" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="CJ7" t="s">
         <v>171</v>
@@ -10582,46 +10591,46 @@
         <v>27</v>
       </c>
       <c r="CL7">
-        <v>0.65</v>
+        <v>2.77</v>
       </c>
       <c r="CM7">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="CN7">
-        <v>5.2</v>
+        <v>7.97</v>
       </c>
       <c r="CO7" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="CP7">
-        <v>6.4</v>
+        <v>1.87</v>
       </c>
       <c r="CQ7" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="CR7">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="CS7">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="CT7">
-        <v>0.65</v>
+        <v>2.77</v>
       </c>
       <c r="CU7" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="CV7">
-        <v>4335</v>
+        <v>85.99</v>
       </c>
       <c r="CW7">
-        <v>4319.5</v>
+        <v>84.5</v>
       </c>
       <c r="CX7">
-        <v>4319.5</v>
+        <v>84.44</v>
       </c>
       <c r="CY7" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="CZ7" t="s">
         <v>150</v>
@@ -10638,10 +10647,10 @@
         <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="F8" t="s">
         <v>146</v>
@@ -10659,40 +10668,40 @@
         <v>47</v>
       </c>
       <c r="K8">
-        <v>214.01</v>
+        <v>4421.9</v>
       </c>
       <c r="L8">
-        <v>214.01</v>
+        <v>4421.9</v>
       </c>
       <c r="M8" t="s">
         <v>149</v>
       </c>
       <c r="N8">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="O8">
-        <v>291</v>
+        <v>22</v>
       </c>
       <c r="P8">
-        <v>291</v>
+        <v>22</v>
       </c>
       <c r="Q8">
-        <v>31245.46</v>
+        <v>97281.8</v>
       </c>
       <c r="R8">
-        <v>30471.66</v>
+        <v>97455.6</v>
       </c>
       <c r="S8">
-        <v>208.71</v>
-      </c>
-      <c r="T8" s="2">
-        <v>-773.8</v>
+        <v>4429.8</v>
+      </c>
+      <c r="T8" s="3">
+        <v>173.8</v>
       </c>
       <c r="U8">
-        <v>-2.48</v>
+        <v>0.18</v>
       </c>
       <c r="V8">
-        <v>-773.8</v>
+        <v>173.8</v>
       </c>
       <c r="W8">
         <v>0</v>
@@ -10725,7 +10734,7 @@
         <v>150</v>
       </c>
       <c r="AG8">
-        <v>-867.1</v>
+        <v>0</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -10743,22 +10752,22 @@
         <v>47</v>
       </c>
       <c r="AM8">
-        <v>179.24</v>
+        <v>167.02</v>
       </c>
       <c r="AN8">
-        <v>179.47</v>
+        <v>77.5</v>
       </c>
       <c r="AO8">
-        <v>196.45</v>
+        <v>4319.5</v>
       </c>
       <c r="AP8">
-        <v>199.5</v>
+        <v>4352.73</v>
       </c>
       <c r="AQ8">
-        <v>5109.96</v>
+        <v>2252.8</v>
       </c>
       <c r="AR8">
-        <v>-0.3</v>
+        <v>0.08</v>
       </c>
       <c r="AS8">
         <v>0</v>
@@ -10785,13 +10794,13 @@
         <v>150</v>
       </c>
       <c r="BA8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>-867.1</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="BD8" t="s">
         <v>150</v>
@@ -10812,7 +10821,7 @@
         <v>152</v>
       </c>
       <c r="BJ8" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="BK8">
         <v>0</v>
@@ -10824,16 +10833,16 @@
         <v>150</v>
       </c>
       <c r="BN8" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="BO8" t="s">
         <v>156</v>
       </c>
       <c r="BP8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BQ8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BR8" t="s">
         <v>223</v>
@@ -10872,13 +10881,13 @@
         <v>184</v>
       </c>
       <c r="CD8" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="CE8" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="CF8" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="CG8" t="s">
         <v>188</v>
@@ -10896,46 +10905,46 @@
         <v>27</v>
       </c>
       <c r="CL8">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="CM8">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="CN8">
-        <v>13.66</v>
+        <v>5.2</v>
       </c>
       <c r="CO8" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="CP8">
-        <v>3.32</v>
+        <v>6.4</v>
       </c>
       <c r="CQ8" t="s">
         <v>202</v>
       </c>
       <c r="CR8">
-        <v>13.61</v>
+        <v>2.63</v>
       </c>
       <c r="CS8">
-        <v>0.89</v>
+        <v>0.47</v>
       </c>
       <c r="CT8">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="CU8" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="CV8">
-        <v>199.5</v>
+        <v>4335</v>
       </c>
       <c r="CW8">
-        <v>196.45</v>
+        <v>4319.5</v>
       </c>
       <c r="CX8">
-        <v>186.53</v>
+        <v>4319.5</v>
       </c>
       <c r="CY8" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="CZ8" t="s">
         <v>150</v>
@@ -10952,10 +10961,10 @@
         <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="E9" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="F9" t="s">
         <v>146</v>
@@ -10973,40 +10982,40 @@
         <v>47</v>
       </c>
       <c r="K9">
-        <v>9284</v>
+        <v>214.01</v>
       </c>
       <c r="L9">
-        <v>9284</v>
+        <v>214.01</v>
       </c>
       <c r="M9" t="s">
         <v>149</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>146</v>
       </c>
       <c r="O9">
-        <v>10</v>
+        <v>291</v>
       </c>
       <c r="P9">
-        <v>10</v>
+        <v>291</v>
       </c>
       <c r="Q9">
-        <v>46420</v>
+        <v>31245.46</v>
       </c>
       <c r="R9">
-        <v>46152.5</v>
+        <v>30471.66</v>
       </c>
       <c r="S9">
-        <v>9230.5</v>
+        <v>208.71</v>
       </c>
       <c r="T9" s="2">
-        <v>-267.5</v>
+        <v>-773.8</v>
       </c>
       <c r="U9">
-        <v>-0.58</v>
+        <v>-2.48</v>
       </c>
       <c r="V9">
-        <v>-267.5</v>
+        <v>-773.8</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -11039,7 +11048,7 @@
         <v>150</v>
       </c>
       <c r="AG9">
-        <v>-162.5</v>
+        <v>-867.1</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -11057,22 +11066,22 @@
         <v>47</v>
       </c>
       <c r="AM9">
-        <v>131.92</v>
+        <v>179.24</v>
       </c>
       <c r="AN9">
-        <v>105.58</v>
+        <v>179.47</v>
       </c>
       <c r="AO9">
-        <v>8955.5</v>
+        <v>196.45</v>
       </c>
       <c r="AP9">
-        <v>9071</v>
+        <v>199.5</v>
       </c>
       <c r="AQ9">
-        <v>3285</v>
+        <v>5109.96</v>
       </c>
       <c r="AR9">
-        <v>-0.16</v>
+        <v>-0.3</v>
       </c>
       <c r="AS9">
         <v>0</v>
@@ -11102,10 +11111,10 @@
         <v>1</v>
       </c>
       <c r="BB9">
-        <v>-162.5</v>
+        <v>-867.1</v>
       </c>
       <c r="BC9" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="BD9" t="s">
         <v>150</v>
@@ -11126,10 +11135,10 @@
         <v>152</v>
       </c>
       <c r="BJ9" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="BK9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="s">
         <v>150</v>
@@ -11141,25 +11150,25 @@
         <v>181</v>
       </c>
       <c r="BO9" t="s">
-        <v>242</v>
+        <v>156</v>
       </c>
       <c r="BP9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BQ9">
         <v>4</v>
       </c>
       <c r="BR9" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="BS9" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="BT9" t="s">
-        <v>244</v>
+        <v>150</v>
       </c>
       <c r="BU9" t="s">
-        <v>245</v>
+        <v>150</v>
       </c>
       <c r="BV9" t="s">
         <v>27</v>
@@ -11168,10 +11177,10 @@
         <v>150</v>
       </c>
       <c r="BX9" t="s">
-        <v>246</v>
+        <v>150</v>
       </c>
       <c r="BY9" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BZ9" t="s">
         <v>161</v>
@@ -11186,22 +11195,22 @@
         <v>184</v>
       </c>
       <c r="CD9" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="CE9" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="CF9" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="CG9" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="CH9" t="s">
         <v>169</v>
       </c>
       <c r="CI9" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="CJ9" t="s">
         <v>171</v>
@@ -11210,46 +11219,46 @@
         <v>27</v>
       </c>
       <c r="CL9">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="CM9">
-        <v>2.8</v>
+        <v>4.35</v>
       </c>
       <c r="CN9">
-        <v>6.16</v>
+        <v>13.66</v>
       </c>
       <c r="CO9" t="s">
         <v>27</v>
       </c>
       <c r="CP9">
-        <v>6.41</v>
+        <v>3.32</v>
       </c>
       <c r="CQ9" t="s">
         <v>202</v>
       </c>
       <c r="CR9">
-        <v>3.87</v>
+        <v>13.61</v>
       </c>
       <c r="CS9">
-        <v>0.32</v>
+        <v>0.89</v>
       </c>
       <c r="CT9">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="CU9" t="s">
         <v>215</v>
       </c>
       <c r="CV9">
-        <v>9100</v>
+        <v>199.5</v>
       </c>
       <c r="CW9">
-        <v>8955.5</v>
+        <v>196.45</v>
       </c>
       <c r="CX9">
-        <v>8955.5</v>
+        <v>186.53</v>
       </c>
       <c r="CY9" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="CZ9" t="s">
         <v>150</v>
@@ -11260,25 +11269,25 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>252</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="D10" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="E10" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="F10" t="s">
         <v>146</v>
       </c>
       <c r="G10" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="H10" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="I10" t="s">
         <v>47</v>
@@ -11287,40 +11296,40 @@
         <v>47</v>
       </c>
       <c r="K10">
-        <v>437.05</v>
+        <v>9284</v>
       </c>
       <c r="L10">
-        <v>437.05</v>
+        <v>9284</v>
       </c>
       <c r="M10" t="s">
         <v>149</v>
       </c>
       <c r="N10">
-        <v>114</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>228</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>228</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>49823.7</v>
+        <v>46420</v>
       </c>
       <c r="R10">
-        <v>50023.2</v>
+        <v>46152.5</v>
       </c>
       <c r="S10">
-        <v>438.8</v>
-      </c>
-      <c r="T10" s="3">
-        <v>199.5</v>
+        <v>9230.5</v>
+      </c>
+      <c r="T10" s="2">
+        <v>-267.5</v>
       </c>
       <c r="U10">
-        <v>0.4</v>
+        <v>-0.58</v>
       </c>
       <c r="V10">
-        <v>199.5</v>
+        <v>-267.5</v>
       </c>
       <c r="W10">
         <v>0</v>
@@ -11353,7 +11362,7 @@
         <v>150</v>
       </c>
       <c r="AG10">
-        <v>-501.6</v>
+        <v>-162.5</v>
       </c>
       <c r="AH10">
         <v>0</v>
@@ -11370,23 +11379,23 @@
       <c r="AL10" t="s">
         <v>47</v>
       </c>
-      <c r="AM10" t="s">
-        <v>150</v>
+      <c r="AM10">
+        <v>131.92</v>
       </c>
       <c r="AN10">
-        <v>167.34</v>
+        <v>105.58</v>
       </c>
       <c r="AO10">
-        <v>402.78</v>
+        <v>8955.5</v>
       </c>
       <c r="AP10">
-        <v>429.85</v>
+        <v>9071</v>
       </c>
       <c r="AQ10">
-        <v>7813.56</v>
+        <v>3285</v>
       </c>
       <c r="AR10">
-        <v>0.05</v>
+        <v>-0.16</v>
       </c>
       <c r="AS10">
         <v>0</v>
@@ -11416,10 +11425,10 @@
         <v>1</v>
       </c>
       <c r="BB10">
-        <v>-501.6</v>
+        <v>-162.5</v>
       </c>
       <c r="BC10" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="BD10" t="s">
         <v>150</v>
@@ -11440,40 +11449,40 @@
         <v>152</v>
       </c>
       <c r="BJ10" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL10" t="s">
-        <v>256</v>
+        <v>150</v>
       </c>
       <c r="BM10" t="s">
         <v>150</v>
       </c>
       <c r="BN10" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="BO10" t="s">
-        <v>156</v>
+        <v>242</v>
       </c>
       <c r="BP10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BQ10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BR10" t="s">
-        <v>223</v>
+        <v>157</v>
       </c>
       <c r="BS10" t="s">
-        <v>150</v>
+        <v>243</v>
       </c>
       <c r="BT10" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="BU10" t="s">
-        <v>150</v>
+        <v>245</v>
       </c>
       <c r="BV10" t="s">
         <v>27</v>
@@ -11482,7 +11491,7 @@
         <v>150</v>
       </c>
       <c r="BX10" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="BY10" t="s">
         <v>150</v>
@@ -11500,22 +11509,22 @@
         <v>184</v>
       </c>
       <c r="CD10" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="CE10" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="CF10" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="CG10" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="CH10" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="CI10" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="CJ10" t="s">
         <v>171</v>
@@ -11524,46 +11533,46 @@
         <v>27</v>
       </c>
       <c r="CL10">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="CM10">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="CN10">
-        <v>9.13</v>
+        <v>6.16</v>
       </c>
       <c r="CO10" t="s">
         <v>27</v>
       </c>
-      <c r="CP10" t="s">
-        <v>150</v>
+      <c r="CP10">
+        <v>6.41</v>
       </c>
       <c r="CQ10" t="s">
-        <v>150</v>
-      </c>
-      <c r="CR10" t="s">
-        <v>150</v>
-      </c>
-      <c r="CS10" t="s">
-        <v>150</v>
-      </c>
-      <c r="CT10" t="s">
-        <v>150</v>
+        <v>202</v>
+      </c>
+      <c r="CR10">
+        <v>3.87</v>
+      </c>
+      <c r="CS10">
+        <v>0.32</v>
+      </c>
+      <c r="CT10">
+        <v>0.1</v>
       </c>
       <c r="CU10" t="s">
         <v>215</v>
       </c>
       <c r="CV10">
-        <v>425.45</v>
+        <v>9100</v>
       </c>
       <c r="CW10">
-        <v>423.3</v>
+        <v>8955.5</v>
       </c>
       <c r="CX10">
-        <v>422.15</v>
+        <v>8955.5</v>
       </c>
       <c r="CY10" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="CZ10" t="s">
         <v>150</v>
@@ -11580,10 +11589,10 @@
         <v>144</v>
       </c>
       <c r="D11" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="E11" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="F11" t="s">
         <v>146</v>
@@ -11601,40 +11610,40 @@
         <v>47</v>
       </c>
       <c r="K11">
-        <v>6621.5</v>
+        <v>437.05</v>
       </c>
       <c r="L11">
-        <v>6621.5</v>
+        <v>437.05</v>
       </c>
       <c r="M11" t="s">
         <v>149</v>
       </c>
       <c r="N11">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="O11">
-        <v>15</v>
+        <v>228</v>
       </c>
       <c r="P11">
-        <v>15</v>
+        <v>228</v>
       </c>
       <c r="Q11">
-        <v>99322.5</v>
+        <v>49823.7</v>
       </c>
       <c r="R11">
-        <v>103005</v>
+        <v>50023.2</v>
       </c>
       <c r="S11">
-        <v>6867</v>
+        <v>438.8</v>
       </c>
       <c r="T11" s="3">
-        <v>3682.5</v>
+        <v>199.5</v>
       </c>
       <c r="U11">
-        <v>3.71</v>
+        <v>0.4</v>
       </c>
       <c r="V11">
-        <v>3682.5</v>
+        <v>199.5</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -11667,7 +11676,7 @@
         <v>150</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>-501.6</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -11688,19 +11697,19 @@
         <v>150</v>
       </c>
       <c r="AN11">
-        <v>200.47</v>
+        <v>167.34</v>
       </c>
       <c r="AO11">
-        <v>6083.5</v>
+        <v>402.78</v>
       </c>
       <c r="AP11">
-        <v>6359.98</v>
+        <v>429.85</v>
       </c>
       <c r="AQ11">
-        <v>8070</v>
+        <v>7813.56</v>
       </c>
       <c r="AR11">
-        <v>0.46</v>
+        <v>0.05</v>
       </c>
       <c r="AS11">
         <v>0</v>
@@ -11727,13 +11736,13 @@
         <v>150</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>-501.6</v>
       </c>
       <c r="BC11" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="BD11" t="s">
         <v>150</v>
@@ -11754,13 +11763,13 @@
         <v>152</v>
       </c>
       <c r="BJ11" t="s">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="BK11">
         <v>0</v>
       </c>
       <c r="BL11" t="s">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="BM11" t="s">
         <v>150</v>
@@ -11772,10 +11781,10 @@
         <v>156</v>
       </c>
       <c r="BP11">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BQ11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="s">
         <v>223</v>
@@ -11814,13 +11823,13 @@
         <v>184</v>
       </c>
       <c r="CD11" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="CE11" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="CF11" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="CG11" t="s">
         <v>260</v>
@@ -11838,13 +11847,13 @@
         <v>27</v>
       </c>
       <c r="CL11">
-        <v>2.02</v>
+        <v>0.22</v>
       </c>
       <c r="CM11">
-        <v>2.56</v>
+        <v>3.42</v>
       </c>
       <c r="CN11">
-        <v>8.7</v>
+        <v>9.13</v>
       </c>
       <c r="CO11" t="s">
         <v>27</v>
@@ -11865,19 +11874,19 @@
         <v>150</v>
       </c>
       <c r="CU11" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="CV11">
-        <v>6202.5</v>
+        <v>425.45</v>
       </c>
       <c r="CW11">
-        <v>6202.5</v>
+        <v>423.3</v>
       </c>
       <c r="CX11">
-        <v>6202.5</v>
+        <v>422.15</v>
       </c>
       <c r="CY11" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="CZ11" t="s">
         <v>150</v>
@@ -11891,13 +11900,13 @@
         <v>252</v>
       </c>
       <c r="C12" t="s">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="D12" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="E12" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="F12" t="s">
         <v>146</v>
@@ -11915,40 +11924,40 @@
         <v>47</v>
       </c>
       <c r="K12">
-        <v>1995.8</v>
+        <v>6621.5</v>
       </c>
       <c r="L12">
-        <v>1995.8</v>
+        <v>6621.5</v>
       </c>
       <c r="M12" t="s">
         <v>149</v>
       </c>
       <c r="N12">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="O12">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="P12">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="Q12">
-        <v>97794.2</v>
+        <v>99322.5</v>
       </c>
       <c r="R12">
-        <v>99832.6</v>
+        <v>103005</v>
       </c>
       <c r="S12">
-        <v>2037.4</v>
+        <v>6867</v>
       </c>
       <c r="T12" s="3">
-        <v>2038.4</v>
+        <v>3682.5</v>
       </c>
       <c r="U12">
-        <v>2.08</v>
+        <v>3.71</v>
       </c>
       <c r="V12">
-        <v>2038.4</v>
+        <v>3682.5</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -12002,19 +12011,19 @@
         <v>150</v>
       </c>
       <c r="AN12">
-        <v>179.17</v>
+        <v>200.47</v>
       </c>
       <c r="AO12">
-        <v>1842.85</v>
+        <v>6083.5</v>
       </c>
       <c r="AP12">
-        <v>1968</v>
+        <v>6359.98</v>
       </c>
       <c r="AQ12">
-        <v>7494.55</v>
+        <v>8070</v>
       </c>
       <c r="AR12">
-        <v>0.27</v>
+        <v>0.46</v>
       </c>
       <c r="AS12">
         <v>0</v>
@@ -12047,7 +12056,7 @@
         <v>0</v>
       </c>
       <c r="BC12" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="BD12" t="s">
         <v>150</v>
@@ -12086,10 +12095,10 @@
         <v>156</v>
       </c>
       <c r="BP12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BQ12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR12" t="s">
         <v>223</v>
@@ -12128,13 +12137,13 @@
         <v>184</v>
       </c>
       <c r="CD12" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="CE12" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="CF12" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="CG12" t="s">
         <v>260</v>
@@ -12152,13 +12161,13 @@
         <v>27</v>
       </c>
       <c r="CL12">
-        <v>0.55</v>
+        <v>2.02</v>
       </c>
       <c r="CM12">
         <v>2.56</v>
       </c>
       <c r="CN12">
-        <v>6.47</v>
+        <v>8.7</v>
       </c>
       <c r="CO12" t="s">
         <v>27</v>
@@ -12179,19 +12188,19 @@
         <v>150</v>
       </c>
       <c r="CU12" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="CV12">
-        <v>1957</v>
+        <v>6202.5</v>
       </c>
       <c r="CW12">
-        <v>1957</v>
+        <v>6202.5</v>
       </c>
       <c r="CX12">
-        <v>1957</v>
+        <v>6202.5</v>
       </c>
       <c r="CY12" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="CZ12" t="s">
         <v>150</v>
@@ -12208,10 +12217,10 @@
         <v>204</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E13" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F13" t="s">
         <v>146</v>
@@ -12229,40 +12238,40 @@
         <v>47</v>
       </c>
       <c r="K13">
-        <v>1373.5</v>
+        <v>1995.8</v>
       </c>
       <c r="L13">
-        <v>1373.5</v>
+        <v>1995.8</v>
       </c>
       <c r="M13" t="s">
         <v>149</v>
       </c>
       <c r="N13">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="O13">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="P13">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="Q13">
-        <v>97518.5</v>
+        <v>97794.2</v>
       </c>
       <c r="R13">
-        <v>98647.4</v>
+        <v>99832.6</v>
       </c>
       <c r="S13">
-        <v>1389.4</v>
+        <v>2037.4</v>
       </c>
       <c r="T13" s="3">
-        <v>1128.9</v>
+        <v>2038.4</v>
       </c>
       <c r="U13">
-        <v>1.16</v>
+        <v>2.08</v>
       </c>
       <c r="V13">
-        <v>1128.9</v>
+        <v>2038.4</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -12316,19 +12325,19 @@
         <v>150</v>
       </c>
       <c r="AN13">
-        <v>192.74</v>
+        <v>179.17</v>
       </c>
       <c r="AO13">
-        <v>1285.88</v>
+        <v>1842.85</v>
       </c>
       <c r="AP13">
-        <v>1324.8</v>
+        <v>1968</v>
       </c>
       <c r="AQ13">
-        <v>6221.02</v>
+        <v>7494.55</v>
       </c>
       <c r="AR13">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="AS13">
         <v>0</v>
@@ -12361,7 +12370,7 @@
         <v>0</v>
       </c>
       <c r="BC13" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="BD13" t="s">
         <v>150</v>
@@ -12400,10 +12409,10 @@
         <v>156</v>
       </c>
       <c r="BP13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BQ13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR13" t="s">
         <v>223</v>
@@ -12442,13 +12451,13 @@
         <v>184</v>
       </c>
       <c r="CD13" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="CE13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="CF13" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="CG13" t="s">
         <v>260</v>
@@ -12466,13 +12475,13 @@
         <v>27</v>
       </c>
       <c r="CL13">
-        <v>0.72</v>
+        <v>0.55</v>
       </c>
       <c r="CM13">
-        <v>4.06</v>
+        <v>2.56</v>
       </c>
       <c r="CN13">
-        <v>11.77</v>
+        <v>6.47</v>
       </c>
       <c r="CO13" t="s">
         <v>27</v>
@@ -12493,19 +12502,19 @@
         <v>150</v>
       </c>
       <c r="CU13" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="CV13">
-        <v>1303.2</v>
+        <v>1957</v>
       </c>
       <c r="CW13">
-        <v>1303.2</v>
+        <v>1957</v>
       </c>
       <c r="CX13">
-        <v>1303.2</v>
+        <v>1957</v>
       </c>
       <c r="CY13" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="CZ13" t="s">
         <v>150</v>
@@ -12519,13 +12528,13 @@
         <v>252</v>
       </c>
       <c r="C14" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="E14" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="F14" t="s">
         <v>146</v>
@@ -12543,40 +12552,40 @@
         <v>47</v>
       </c>
       <c r="K14">
-        <v>811</v>
+        <v>1373.5</v>
       </c>
       <c r="L14">
-        <v>811</v>
+        <v>1373.5</v>
       </c>
       <c r="M14" t="s">
         <v>149</v>
       </c>
       <c r="N14">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="O14">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="P14">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="Q14">
-        <v>96509</v>
+        <v>97518.5</v>
       </c>
       <c r="R14">
-        <v>97395.55</v>
+        <v>98647.4</v>
       </c>
       <c r="S14">
-        <v>818.45</v>
+        <v>1389.4</v>
       </c>
       <c r="T14" s="3">
-        <v>886.55</v>
+        <v>1128.9</v>
       </c>
       <c r="U14">
-        <v>0.92</v>
+        <v>1.16</v>
       </c>
       <c r="V14">
-        <v>886.55</v>
+        <v>1128.9</v>
       </c>
       <c r="W14">
         <v>0</v>
@@ -12630,19 +12639,19 @@
         <v>150</v>
       </c>
       <c r="AN14">
-        <v>189.66</v>
+        <v>192.74</v>
       </c>
       <c r="AO14">
-        <v>771.79</v>
+        <v>1285.88</v>
       </c>
       <c r="AP14">
-        <v>771.79</v>
+        <v>1324.8</v>
       </c>
       <c r="AQ14">
-        <v>4665.99</v>
+        <v>6221.02</v>
       </c>
       <c r="AR14">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AS14">
         <v>0</v>
@@ -12675,7 +12684,7 @@
         <v>0</v>
       </c>
       <c r="BC14" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="BD14" t="s">
         <v>150</v>
@@ -12717,7 +12726,7 @@
         <v>13</v>
       </c>
       <c r="BQ14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR14" t="s">
         <v>223</v>
@@ -12756,13 +12765,13 @@
         <v>184</v>
       </c>
       <c r="CD14" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="CE14" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="CF14" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="CG14" t="s">
         <v>260</v>
@@ -12780,13 +12789,13 @@
         <v>27</v>
       </c>
       <c r="CL14">
-        <v>1.22</v>
+        <v>0.72</v>
       </c>
       <c r="CM14">
-        <v>4.91</v>
+        <v>4.06</v>
       </c>
       <c r="CN14">
-        <v>15.81</v>
+        <v>11.77</v>
       </c>
       <c r="CO14" t="s">
         <v>27</v>
@@ -12810,16 +12819,16 @@
         <v>191</v>
       </c>
       <c r="CV14">
-        <v>770</v>
+        <v>1303.2</v>
       </c>
       <c r="CW14">
-        <v>770</v>
+        <v>1303.2</v>
       </c>
       <c r="CX14">
-        <v>721.4</v>
+        <v>1303.2</v>
       </c>
       <c r="CY14" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="CZ14" t="s">
         <v>150</v>
@@ -12836,10 +12845,10 @@
         <v>144</v>
       </c>
       <c r="D15" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E15" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F15" t="s">
         <v>146</v>
@@ -12857,40 +12866,40 @@
         <v>47</v>
       </c>
       <c r="K15">
-        <v>2986</v>
+        <v>811</v>
       </c>
       <c r="L15">
-        <v>2986</v>
+        <v>811</v>
       </c>
       <c r="M15" t="s">
         <v>149</v>
       </c>
       <c r="N15">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="O15">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="P15">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="Q15">
-        <v>50762</v>
+        <v>96509</v>
       </c>
       <c r="R15">
-        <v>49752.2</v>
+        <v>97395.55</v>
       </c>
       <c r="S15">
-        <v>2926.6</v>
-      </c>
-      <c r="T15" s="2">
-        <v>-1009.8</v>
+        <v>818.45</v>
+      </c>
+      <c r="T15" s="3">
+        <v>886.55</v>
       </c>
       <c r="U15">
-        <v>-1.99</v>
+        <v>0.92</v>
       </c>
       <c r="V15">
-        <v>-1009.8</v>
+        <v>886.55</v>
       </c>
       <c r="W15">
         <v>0</v>
@@ -12923,7 +12932,7 @@
         <v>150</v>
       </c>
       <c r="AG15">
-        <v>54.4</v>
+        <v>0</v>
       </c>
       <c r="AH15">
         <v>0</v>
@@ -12944,19 +12953,19 @@
         <v>150</v>
       </c>
       <c r="AN15">
-        <v>88.31</v>
+        <v>189.66</v>
       </c>
       <c r="AO15">
-        <v>2728.17</v>
+        <v>771.79</v>
       </c>
       <c r="AP15">
-        <v>2882.7</v>
+        <v>771.79</v>
       </c>
       <c r="AQ15">
-        <v>8508.39</v>
+        <v>4665.99</v>
       </c>
       <c r="AR15">
-        <v>-0.23</v>
+        <v>0.19</v>
       </c>
       <c r="AS15">
         <v>0</v>
@@ -12983,13 +12992,13 @@
         <v>150</v>
       </c>
       <c r="BA15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>54.4</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="BD15" t="s">
         <v>150</v>
@@ -13010,10 +13019,10 @@
         <v>152</v>
       </c>
       <c r="BJ15" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="BK15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL15" t="s">
         <v>150</v>
@@ -13028,7 +13037,7 @@
         <v>156</v>
       </c>
       <c r="BP15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BQ15">
         <v>3</v>
@@ -13070,13 +13079,13 @@
         <v>184</v>
       </c>
       <c r="CD15" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="CE15" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="CF15" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="CG15" t="s">
         <v>260</v>
@@ -13094,13 +13103,13 @@
         <v>27</v>
       </c>
       <c r="CL15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CM15">
-        <v>3.14</v>
+        <v>4.91</v>
       </c>
       <c r="CN15">
-        <v>6.77</v>
+        <v>15.81</v>
       </c>
       <c r="CO15" t="s">
         <v>27</v>
@@ -13121,19 +13130,19 @@
         <v>150</v>
       </c>
       <c r="CU15" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="CV15">
-        <v>2903.2</v>
+        <v>770</v>
       </c>
       <c r="CW15">
-        <v>2903.2</v>
+        <v>770</v>
       </c>
       <c r="CX15">
-        <v>2903.2</v>
+        <v>721.4</v>
       </c>
       <c r="CY15" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="CZ15" t="s">
         <v>150</v>
@@ -13144,67 +13153,67 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>252</v>
       </c>
       <c r="C16" t="s">
-        <v>316</v>
+        <v>144</v>
       </c>
       <c r="D16" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="E16" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="F16" t="s">
-        <v>318</v>
+        <v>146</v>
       </c>
       <c r="G16" t="s">
+        <v>254</v>
+      </c>
+      <c r="H16" t="s">
         <v>219</v>
-      </c>
-      <c r="H16" t="s">
-        <v>178</v>
       </c>
       <c r="I16" t="s">
         <v>47</v>
       </c>
       <c r="J16" t="s">
-        <v>319</v>
+        <v>47</v>
       </c>
       <c r="K16">
-        <v>19.59</v>
+        <v>2986</v>
       </c>
       <c r="L16">
-        <v>19.59</v>
+        <v>2986</v>
       </c>
       <c r="M16" t="s">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="N16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O16">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P16">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q16">
-        <v>313.44</v>
+        <v>50762</v>
       </c>
       <c r="R16">
-        <v>297.44</v>
+        <v>49752.2</v>
       </c>
       <c r="S16">
-        <v>18.5</v>
-      </c>
-      <c r="T16" t="s">
-        <v>150</v>
-      </c>
-      <c r="U16" t="s">
-        <v>150</v>
+        <v>2926.6</v>
+      </c>
+      <c r="T16" s="2">
+        <v>-1009.8</v>
+      </c>
+      <c r="U16">
+        <v>-1.99</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>-1009.8</v>
       </c>
       <c r="W16">
         <v>0</v>
@@ -13213,31 +13222,31 @@
         <v>0</v>
       </c>
       <c r="Y16" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Z16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AA16" t="s">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="AB16" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC16">
-        <v>18.5</v>
+        <v>150</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>150</v>
       </c>
       <c r="AD16" t="s">
-        <v>149</v>
-      </c>
-      <c r="AE16" s="2">
-        <v>-17.44</v>
-      </c>
-      <c r="AF16">
-        <v>-2.87</v>
+        <v>150</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>150</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>150</v>
       </c>
       <c r="AG16">
-        <v>-17.44</v>
+        <v>54.4</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -13248,29 +13257,29 @@
       <c r="AJ16" t="s">
         <v>27</v>
       </c>
-      <c r="AK16">
-        <v>2</v>
+      <c r="AK16" t="s">
+        <v>150</v>
       </c>
       <c r="AL16" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM16">
-        <v>168.93</v>
+        <v>47</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>150</v>
       </c>
       <c r="AN16">
-        <v>62.58</v>
+        <v>88.31</v>
       </c>
       <c r="AO16">
-        <v>19.01</v>
+        <v>2728.17</v>
       </c>
       <c r="AP16">
-        <v>17.1</v>
+        <v>2882.7</v>
       </c>
       <c r="AQ16">
-        <v>17.98</v>
-      </c>
-      <c r="AR16" t="s">
-        <v>150</v>
+        <v>8508.39</v>
+      </c>
+      <c r="AR16">
+        <v>-0.23</v>
       </c>
       <c r="AS16">
         <v>0</v>
@@ -13300,13 +13309,13 @@
         <v>1</v>
       </c>
       <c r="BB16">
-        <v>-17.44</v>
+        <v>54.4</v>
       </c>
       <c r="BC16" t="s">
-        <v>322</v>
+        <v>288</v>
       </c>
       <c r="BD16" t="s">
-        <v>323</v>
+        <v>150</v>
       </c>
       <c r="BE16" t="s">
         <v>150</v>
@@ -13321,10 +13330,10 @@
         <v>150</v>
       </c>
       <c r="BI16" t="s">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="BJ16" t="s">
-        <v>325</v>
+        <v>180</v>
       </c>
       <c r="BK16">
         <v>1</v>
@@ -13333,25 +13342,25 @@
         <v>150</v>
       </c>
       <c r="BM16" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="BN16" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="BO16" t="s">
         <v>156</v>
       </c>
       <c r="BP16">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BQ16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR16" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="BS16" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="BT16" t="s">
         <v>150</v>
@@ -13363,13 +13372,13 @@
         <v>27</v>
       </c>
       <c r="BW16" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="BX16" t="s">
         <v>150</v>
       </c>
       <c r="BY16" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BZ16" t="s">
         <v>161</v>
@@ -13381,76 +13390,76 @@
         <v>163</v>
       </c>
       <c r="CC16" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="CD16" t="s">
-        <v>185</v>
+        <v>278</v>
       </c>
       <c r="CE16" t="s">
-        <v>326</v>
+        <v>289</v>
       </c>
       <c r="CF16" t="s">
-        <v>327</v>
+        <v>290</v>
       </c>
       <c r="CG16" t="s">
-        <v>328</v>
+        <v>260</v>
       </c>
       <c r="CH16" t="s">
-        <v>169</v>
+        <v>261</v>
       </c>
       <c r="CI16" t="s">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="CJ16" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="CK16" t="s">
         <v>27</v>
       </c>
       <c r="CL16">
-        <v>0.76</v>
+        <v>1.21</v>
       </c>
       <c r="CM16">
-        <v>5.69</v>
+        <v>3.14</v>
       </c>
       <c r="CN16">
-        <v>10.75</v>
+        <v>6.77</v>
       </c>
       <c r="CO16" t="s">
         <v>27</v>
       </c>
-      <c r="CP16">
-        <v>18.16</v>
+      <c r="CP16" t="s">
+        <v>150</v>
       </c>
       <c r="CQ16" t="s">
-        <v>202</v>
-      </c>
-      <c r="CR16">
-        <v>1.54</v>
-      </c>
-      <c r="CS16">
-        <v>0.3</v>
-      </c>
-      <c r="CT16">
-        <v>0.76</v>
+        <v>150</v>
+      </c>
+      <c r="CR16" t="s">
+        <v>150</v>
+      </c>
+      <c r="CS16" t="s">
+        <v>150</v>
+      </c>
+      <c r="CT16" t="s">
+        <v>150</v>
       </c>
       <c r="CU16" t="s">
-        <v>329</v>
+        <v>215</v>
       </c>
       <c r="CV16">
-        <v>20</v>
+        <v>2903.2</v>
       </c>
       <c r="CW16">
-        <v>20</v>
+        <v>2903.2</v>
       </c>
       <c r="CX16">
-        <v>19.01</v>
+        <v>2903.2</v>
       </c>
       <c r="CY16" t="s">
-        <v>330</v>
+        <v>291</v>
       </c>
       <c r="CZ16" t="s">
-        <v>331</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:104" x14ac:dyDescent="0.25">
@@ -13461,55 +13470,55 @@
         <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>204</v>
+        <v>316</v>
       </c>
       <c r="D17" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="E17" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="F17" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="G17" t="s">
         <v>219</v>
       </c>
       <c r="H17" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="I17" t="s">
-        <v>150</v>
+        <v>47</v>
       </c>
       <c r="J17" t="s">
-        <v>150</v>
-      </c>
-      <c r="K17" t="s">
-        <v>150</v>
-      </c>
-      <c r="L17" t="s">
-        <v>150</v>
+        <v>319</v>
+      </c>
+      <c r="K17">
+        <v>19.59</v>
+      </c>
+      <c r="L17">
+        <v>19.59</v>
       </c>
       <c r="M17" t="s">
-        <v>334</v>
-      </c>
-      <c r="N17" t="s">
-        <v>150</v>
-      </c>
-      <c r="O17" t="s">
-        <v>150</v>
-      </c>
-      <c r="P17" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>150</v>
-      </c>
-      <c r="R17" t="s">
-        <v>150</v>
+        <v>320</v>
+      </c>
+      <c r="N17">
+        <v>16</v>
+      </c>
+      <c r="O17">
+        <v>31</v>
+      </c>
+      <c r="P17">
+        <v>31</v>
+      </c>
+      <c r="Q17">
+        <v>313.44</v>
+      </c>
+      <c r="R17">
+        <v>297.44</v>
       </c>
       <c r="S17">
-        <v>4506.7998046875</v>
+        <v>18.5</v>
       </c>
       <c r="T17" t="s">
         <v>150</v>
@@ -13527,31 +13536,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Z17" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AA17" t="s">
-        <v>150</v>
+        <v>47</v>
       </c>
       <c r="AB17" t="s">
-        <v>150</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>150</v>
+        <v>47</v>
+      </c>
+      <c r="AC17">
+        <v>18.5</v>
       </c>
       <c r="AD17" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>150</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>150</v>
+        <v>149</v>
+      </c>
+      <c r="AE17" s="2">
+        <v>-17.44</v>
+      </c>
+      <c r="AF17">
+        <v>-2.87</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>-17.44</v>
       </c>
       <c r="AH17">
         <v>0</v>
@@ -13562,26 +13571,26 @@
       <c r="AJ17" t="s">
         <v>27</v>
       </c>
-      <c r="AK17" t="s">
-        <v>150</v>
+      <c r="AK17">
+        <v>2</v>
       </c>
       <c r="AL17" t="s">
-        <v>335</v>
-      </c>
-      <c r="AM17" t="s">
-        <v>150</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>150</v>
-      </c>
-      <c r="AO17" t="s">
-        <v>150</v>
-      </c>
-      <c r="AP17" t="s">
-        <v>150</v>
-      </c>
-      <c r="AQ17" t="s">
-        <v>150</v>
+        <v>321</v>
+      </c>
+      <c r="AM17">
+        <v>168.93</v>
+      </c>
+      <c r="AN17">
+        <v>62.58</v>
+      </c>
+      <c r="AO17">
+        <v>19.01</v>
+      </c>
+      <c r="AP17">
+        <v>17.1</v>
+      </c>
+      <c r="AQ17">
+        <v>17.98</v>
       </c>
       <c r="AR17" t="s">
         <v>150</v>
@@ -13611,16 +13620,16 @@
         <v>150</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>-17.44</v>
       </c>
       <c r="BC17" t="s">
-        <v>150</v>
+        <v>322</v>
       </c>
       <c r="BD17" t="s">
-        <v>150</v>
+        <v>323</v>
       </c>
       <c r="BE17" t="s">
         <v>150</v>
@@ -13635,37 +13644,37 @@
         <v>150</v>
       </c>
       <c r="BI17" t="s">
-        <v>150</v>
+        <v>324</v>
       </c>
       <c r="BJ17" t="s">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL17" t="s">
         <v>150</v>
       </c>
       <c r="BM17" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="BN17" t="s">
-        <v>222</v>
+        <v>181</v>
       </c>
       <c r="BO17" t="s">
         <v>156</v>
       </c>
       <c r="BP17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BQ17">
         <v>4</v>
       </c>
       <c r="BR17" t="s">
-        <v>336</v>
+        <v>157</v>
       </c>
       <c r="BS17" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="BT17" t="s">
         <v>150</v>
@@ -13677,94 +13686,94 @@
         <v>27</v>
       </c>
       <c r="BW17" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="BX17" t="s">
         <v>150</v>
       </c>
       <c r="BY17" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BZ17" t="s">
         <v>161</v>
       </c>
       <c r="CA17" t="s">
-        <v>337</v>
+        <v>162</v>
       </c>
       <c r="CB17" t="s">
         <v>163</v>
       </c>
       <c r="CC17" t="s">
-        <v>338</v>
+        <v>197</v>
       </c>
       <c r="CD17" t="s">
-        <v>339</v>
+        <v>185</v>
       </c>
       <c r="CE17" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="CF17" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="CG17" t="s">
-        <v>260</v>
+        <v>328</v>
       </c>
       <c r="CH17" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="CI17" t="s">
-        <v>342</v>
+        <v>214</v>
       </c>
       <c r="CJ17" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="CK17" t="s">
         <v>27</v>
       </c>
       <c r="CL17">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="CM17">
-        <v>2.15</v>
+        <v>5.69</v>
       </c>
       <c r="CN17">
-        <v>6.95</v>
+        <v>10.75</v>
       </c>
       <c r="CO17" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="CP17">
-        <v>6.81</v>
+        <v>18.16</v>
       </c>
       <c r="CQ17" t="s">
         <v>202</v>
       </c>
       <c r="CR17">
-        <v>2.21</v>
+        <v>1.54</v>
       </c>
       <c r="CS17">
-        <v>0.58</v>
+        <v>0.3</v>
       </c>
       <c r="CT17">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="CU17" t="s">
-        <v>173</v>
+        <v>329</v>
       </c>
       <c r="CV17">
-        <v>4331</v>
+        <v>20</v>
       </c>
       <c r="CW17">
-        <v>4305.8</v>
+        <v>20</v>
       </c>
       <c r="CX17">
-        <v>4305.8</v>
+        <v>19.01</v>
       </c>
       <c r="CY17" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="CZ17" t="s">
-        <v>150</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" spans="1:104" x14ac:dyDescent="0.25">
@@ -13778,10 +13787,10 @@
         <v>204</v>
       </c>
       <c r="D18" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="E18" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="F18" t="s">
         <v>333</v>
@@ -13823,7 +13832,7 @@
         <v>150</v>
       </c>
       <c r="S18">
-        <v>1117.199951171875</v>
+        <v>4506.7998046875</v>
       </c>
       <c r="T18" t="s">
         <v>150</v>
@@ -13964,13 +13973,13 @@
         <v>150</v>
       </c>
       <c r="BN18" t="s">
-        <v>155</v>
+        <v>222</v>
       </c>
       <c r="BO18" t="s">
         <v>156</v>
       </c>
       <c r="BP18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BQ18">
         <v>4</v>
@@ -14003,7 +14012,7 @@
         <v>161</v>
       </c>
       <c r="CA18" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="CB18" t="s">
         <v>163</v>
@@ -14012,13 +14021,13 @@
         <v>338</v>
       </c>
       <c r="CD18" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="CE18" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="CF18" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="CG18" t="s">
         <v>260</v>
@@ -14033,49 +14042,49 @@
         <v>171</v>
       </c>
       <c r="CK18" t="s">
+        <v>27</v>
+      </c>
+      <c r="CL18">
+        <v>0.99</v>
+      </c>
+      <c r="CM18">
+        <v>2.15</v>
+      </c>
+      <c r="CN18">
+        <v>6.95</v>
+      </c>
+      <c r="CO18" t="s">
         <v>171</v>
       </c>
-      <c r="CL18">
-        <v>1.56</v>
-      </c>
-      <c r="CM18">
-        <v>2.97</v>
-      </c>
-      <c r="CN18">
-        <v>9.83</v>
-      </c>
-      <c r="CO18" t="s">
-        <v>27</v>
-      </c>
       <c r="CP18">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="CQ18" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="CR18">
-        <v>1.19</v>
+        <v>2.21</v>
       </c>
       <c r="CS18">
-        <v>0.98</v>
+        <v>0.58</v>
       </c>
       <c r="CT18">
-        <v>1.56</v>
+        <v>0.99</v>
       </c>
       <c r="CU18" t="s">
         <v>173</v>
       </c>
       <c r="CV18">
-        <v>1048</v>
+        <v>4331</v>
       </c>
       <c r="CW18">
-        <v>1021.6</v>
+        <v>4305.8</v>
       </c>
       <c r="CX18">
-        <v>1012.9</v>
+        <v>4305.8</v>
       </c>
       <c r="CY18" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="CZ18" t="s">
         <v>150</v>
@@ -14089,13 +14098,13 @@
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E19" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F19" t="s">
         <v>333</v>
@@ -14137,7 +14146,7 @@
         <v>150</v>
       </c>
       <c r="S19">
-        <v>747.0499877929688</v>
+        <v>1117.199951171875</v>
       </c>
       <c r="T19" t="s">
         <v>150</v>
@@ -14278,19 +14287,19 @@
         <v>150</v>
       </c>
       <c r="BN19" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="BO19" t="s">
-        <v>242</v>
+        <v>156</v>
       </c>
       <c r="BP19">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BQ19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR19" t="s">
-        <v>223</v>
+        <v>336</v>
       </c>
       <c r="BS19" t="s">
         <v>150</v>
@@ -14317,7 +14326,7 @@
         <v>161</v>
       </c>
       <c r="CA19" t="s">
-        <v>162</v>
+        <v>345</v>
       </c>
       <c r="CB19" t="s">
         <v>163</v>
@@ -14326,13 +14335,13 @@
         <v>338</v>
       </c>
       <c r="CD19" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="CE19" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="CF19" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="CG19" t="s">
         <v>260</v>
@@ -14347,49 +14356,49 @@
         <v>171</v>
       </c>
       <c r="CK19" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="CL19">
-        <v>0.42</v>
+        <v>1.56</v>
       </c>
       <c r="CM19">
-        <v>4.83</v>
+        <v>2.97</v>
       </c>
       <c r="CN19">
-        <v>9.1</v>
+        <v>9.83</v>
       </c>
       <c r="CO19" t="s">
         <v>27</v>
       </c>
       <c r="CP19">
-        <v>8.22</v>
+        <v>0</v>
       </c>
       <c r="CQ19" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="CR19">
-        <v>6</v>
+        <v>1.19</v>
       </c>
       <c r="CS19">
-        <v>1.81</v>
+        <v>0.98</v>
       </c>
       <c r="CT19">
-        <v>0.42</v>
+        <v>1.56</v>
       </c>
       <c r="CU19" t="s">
         <v>173</v>
       </c>
       <c r="CV19">
-        <v>701.8</v>
+        <v>1048</v>
       </c>
       <c r="CW19">
-        <v>688.05</v>
+        <v>1021.6</v>
       </c>
       <c r="CX19">
-        <v>688.05</v>
+        <v>1012.9</v>
       </c>
       <c r="CY19" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="CZ19" t="s">
         <v>150</v>
@@ -14400,67 +14409,67 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>252</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="D20" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="E20" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="F20" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="G20" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="H20" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="I20" t="s">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="J20" t="s">
-        <v>47</v>
-      </c>
-      <c r="K20">
-        <v>1351.4</v>
-      </c>
-      <c r="L20">
-        <v>1351.4</v>
+        <v>150</v>
+      </c>
+      <c r="K20" t="s">
+        <v>150</v>
+      </c>
+      <c r="L20" t="s">
+        <v>150</v>
       </c>
       <c r="M20" t="s">
-        <v>149</v>
-      </c>
-      <c r="N20">
-        <v>19</v>
-      </c>
-      <c r="O20">
-        <v>73</v>
-      </c>
-      <c r="P20">
-        <v>73</v>
-      </c>
-      <c r="Q20">
-        <v>25676.6</v>
-      </c>
-      <c r="R20">
-        <v>24660.1</v>
+        <v>334</v>
+      </c>
+      <c r="N20" t="s">
+        <v>150</v>
+      </c>
+      <c r="O20" t="s">
+        <v>150</v>
+      </c>
+      <c r="P20" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>150</v>
+      </c>
+      <c r="R20" t="s">
+        <v>150</v>
       </c>
       <c r="S20">
-        <v>1297.9</v>
-      </c>
-      <c r="T20" s="2">
-        <v>-1016.5</v>
-      </c>
-      <c r="U20">
-        <v>-3.96</v>
+        <v>747.0499877929688</v>
+      </c>
+      <c r="T20" t="s">
+        <v>150</v>
+      </c>
+      <c r="U20" t="s">
+        <v>150</v>
       </c>
       <c r="V20">
-        <v>-1016.5</v>
+        <v>0</v>
       </c>
       <c r="W20">
         <v>0</v>
@@ -14493,7 +14502,7 @@
         <v>150</v>
       </c>
       <c r="AG20">
-        <v>-1476</v>
+        <v>0</v>
       </c>
       <c r="AH20">
         <v>0</v>
@@ -14508,25 +14517,25 @@
         <v>150</v>
       </c>
       <c r="AL20" t="s">
-        <v>47</v>
+        <v>335</v>
       </c>
       <c r="AM20" t="s">
         <v>150</v>
       </c>
-      <c r="AN20">
-        <v>87.64</v>
-      </c>
-      <c r="AO20">
-        <v>1251.2</v>
-      </c>
-      <c r="AP20">
-        <v>1278.43</v>
-      </c>
-      <c r="AQ20">
-        <v>7314.6</v>
-      </c>
-      <c r="AR20">
-        <v>-0.53</v>
+      <c r="AN20" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>150</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>150</v>
+      </c>
+      <c r="AQ20" t="s">
+        <v>150</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>150</v>
       </c>
       <c r="AS20">
         <v>0</v>
@@ -14553,55 +14562,55 @@
         <v>150</v>
       </c>
       <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="s">
+        <v>150</v>
+      </c>
+      <c r="BD20" t="s">
+        <v>150</v>
+      </c>
+      <c r="BE20" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF20" t="s">
+        <v>150</v>
+      </c>
+      <c r="BG20" t="s">
+        <v>150</v>
+      </c>
+      <c r="BH20" t="s">
+        <v>150</v>
+      </c>
+      <c r="BI20" t="s">
+        <v>150</v>
+      </c>
+      <c r="BJ20" t="s">
+        <v>150</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="s">
+        <v>150</v>
+      </c>
+      <c r="BM20" t="s">
+        <v>150</v>
+      </c>
+      <c r="BN20" t="s">
+        <v>181</v>
+      </c>
+      <c r="BO20" t="s">
+        <v>242</v>
+      </c>
+      <c r="BP20">
+        <v>12</v>
+      </c>
+      <c r="BQ20">
         <v>2</v>
-      </c>
-      <c r="BB20">
-        <v>-1476</v>
-      </c>
-      <c r="BC20" t="s">
-        <v>309</v>
-      </c>
-      <c r="BD20" t="s">
-        <v>150</v>
-      </c>
-      <c r="BE20" t="s">
-        <v>150</v>
-      </c>
-      <c r="BF20" t="s">
-        <v>150</v>
-      </c>
-      <c r="BG20" t="s">
-        <v>150</v>
-      </c>
-      <c r="BH20" t="s">
-        <v>150</v>
-      </c>
-      <c r="BI20" t="s">
-        <v>310</v>
-      </c>
-      <c r="BJ20" t="s">
-        <v>311</v>
-      </c>
-      <c r="BK20">
-        <v>2</v>
-      </c>
-      <c r="BL20" t="s">
-        <v>150</v>
-      </c>
-      <c r="BM20" t="s">
-        <v>150</v>
-      </c>
-      <c r="BN20" t="s">
-        <v>150</v>
-      </c>
-      <c r="BO20" t="s">
-        <v>156</v>
-      </c>
-      <c r="BP20">
-        <v>13</v>
-      </c>
-      <c r="BQ20">
-        <v>4</v>
       </c>
       <c r="BR20" t="s">
         <v>223</v>
@@ -14637,16 +14646,16 @@
         <v>163</v>
       </c>
       <c r="CC20" t="s">
-        <v>184</v>
+        <v>338</v>
       </c>
       <c r="CD20" t="s">
-        <v>272</v>
+        <v>351</v>
       </c>
       <c r="CE20" t="s">
-        <v>312</v>
+        <v>352</v>
       </c>
       <c r="CF20" t="s">
-        <v>313</v>
+        <v>353</v>
       </c>
       <c r="CG20" t="s">
         <v>260</v>
@@ -14655,7 +14664,7 @@
         <v>261</v>
       </c>
       <c r="CI20" t="s">
-        <v>262</v>
+        <v>342</v>
       </c>
       <c r="CJ20" t="s">
         <v>171</v>
@@ -14664,46 +14673,46 @@
         <v>27</v>
       </c>
       <c r="CL20">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="CM20">
-        <v>3.04</v>
+        <v>4.83</v>
       </c>
       <c r="CN20">
-        <v>2.68</v>
+        <v>9.1</v>
       </c>
       <c r="CO20" t="s">
         <v>27</v>
       </c>
-      <c r="CP20" t="s">
-        <v>150</v>
+      <c r="CP20">
+        <v>8.22</v>
       </c>
       <c r="CQ20" t="s">
-        <v>150</v>
-      </c>
-      <c r="CR20" t="s">
-        <v>150</v>
-      </c>
-      <c r="CS20" t="s">
-        <v>150</v>
-      </c>
-      <c r="CT20" t="s">
-        <v>150</v>
+        <v>202</v>
+      </c>
+      <c r="CR20">
+        <v>6</v>
+      </c>
+      <c r="CS20">
+        <v>1.81</v>
+      </c>
+      <c r="CT20">
+        <v>0.42</v>
       </c>
       <c r="CU20" t="s">
-        <v>314</v>
+        <v>173</v>
       </c>
       <c r="CV20">
-        <v>1321</v>
+        <v>701.8</v>
       </c>
       <c r="CW20">
-        <v>1321</v>
+        <v>688.05</v>
       </c>
       <c r="CX20">
-        <v>1321</v>
+        <v>688.05</v>
       </c>
       <c r="CY20" t="s">
-        <v>315</v>
+        <v>354</v>
       </c>
       <c r="CZ20" t="s">
         <v>150</v>
@@ -14866,16 +14875,16 @@
         <v>292</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>375</v>
       </c>
       <c r="C3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D3" t="s">
         <v>178</v>
       </c>
       <c r="E3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F3">
         <v>2004.5</v>
@@ -14928,10 +14937,10 @@
         <v>292</v>
       </c>
       <c r="B4" t="s">
-        <v>310</v>
+        <v>375</v>
       </c>
       <c r="C4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D4" t="s">
         <v>147</v>
@@ -14990,10 +14999,10 @@
         <v>292</v>
       </c>
       <c r="B5" t="s">
-        <v>310</v>
+        <v>375</v>
       </c>
       <c r="C5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D5" t="s">
         <v>148</v>
@@ -15049,7 +15058,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>307</v>
       </c>
       <c r="B6" t="s">
         <v>373</v>
@@ -15058,19 +15067,19 @@
         <v>374</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>219</v>
       </c>
       <c r="E6" t="s">
         <v>47</v>
       </c>
       <c r="F6">
-        <v>921.25</v>
+        <v>1351.4</v>
       </c>
       <c r="G6">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="H6">
-        <v>99495</v>
+        <v>98652.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -15111,13 +15120,13 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>176</v>
+        <v>307</v>
       </c>
       <c r="B7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D7" t="s">
         <v>147</v>
@@ -15126,13 +15135,13 @@
         <v>47</v>
       </c>
       <c r="F7">
-        <v>853</v>
+        <v>1333.5</v>
       </c>
       <c r="G7">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="H7">
-        <v>58004</v>
+        <v>48006</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -15162,39 +15171,39 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7" t="s">
-        <v>150</v>
+        <v>-644.4</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>-644.4</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>193</v>
+        <v>307</v>
       </c>
       <c r="B8" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E8" t="s">
         <v>47</v>
       </c>
       <c r="F8">
-        <v>649.15</v>
+        <v>1305.2</v>
       </c>
       <c r="G8">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="H8">
-        <v>72704.8</v>
+        <v>23493.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -15224,18 +15233,18 @@
         <v>0</v>
       </c>
       <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8" t="s">
-        <v>150</v>
+        <v>-831.6</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>-831.6</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="B9" t="s">
         <v>373</v>
@@ -15244,19 +15253,19 @@
         <v>374</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
         <v>47</v>
       </c>
       <c r="F9">
-        <v>88.49</v>
+        <v>921.25</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="H9">
-        <v>442.45</v>
+        <v>99495</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -15297,7 +15306,7 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
         <v>373</v>
@@ -15306,19 +15315,19 @@
         <v>374</v>
       </c>
       <c r="D10" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
         <v>47</v>
       </c>
       <c r="F10">
-        <v>4421.9</v>
+        <v>853</v>
       </c>
       <c r="G10">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="H10">
-        <v>97281.8</v>
+        <v>58004</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -15359,7 +15368,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="B11" t="s">
         <v>373</v>
@@ -15368,19 +15377,19 @@
         <v>374</v>
       </c>
       <c r="D11" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="E11" t="s">
         <v>47</v>
       </c>
       <c r="F11">
-        <v>214.01</v>
+        <v>649.15</v>
       </c>
       <c r="G11">
-        <v>291</v>
+        <v>112</v>
       </c>
       <c r="H11">
-        <v>62276.91</v>
+        <v>72704.8</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -15421,28 +15430,28 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="B12" t="s">
-        <v>310</v>
+        <v>373</v>
       </c>
       <c r="C12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E12" t="s">
         <v>47</v>
       </c>
       <c r="F12">
-        <v>208.03</v>
+        <v>88.49</v>
       </c>
       <c r="G12">
-        <v>145</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>30164.35</v>
+        <v>442.45</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -15472,18 +15481,18 @@
         <v>0</v>
       </c>
       <c r="R12">
-        <v>-867.1</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="S12" t="s">
+        <v>150</v>
       </c>
       <c r="T12">
-        <v>-867.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="B13" t="s">
         <v>373</v>
@@ -15498,13 +15507,13 @@
         <v>47</v>
       </c>
       <c r="F13">
-        <v>9284</v>
+        <v>4421.9</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H13">
-        <v>92840</v>
+        <v>97281.8</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -15545,28 +15554,28 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B14" t="s">
-        <v>310</v>
+        <v>373</v>
       </c>
       <c r="C14" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="E14" t="s">
         <v>47</v>
       </c>
       <c r="F14">
-        <v>9251.5</v>
+        <v>214.01</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>291</v>
       </c>
       <c r="H14">
-        <v>46257.5</v>
+        <v>62276.91</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -15596,39 +15605,39 @@
         <v>0</v>
       </c>
       <c r="R14">
-        <v>-162.5</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="S14" t="s">
+        <v>150</v>
       </c>
       <c r="T14">
-        <v>-162.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="B15" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D15" t="s">
-        <v>219</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
         <v>47</v>
       </c>
       <c r="F15">
-        <v>437.05</v>
+        <v>208.03</v>
       </c>
       <c r="G15">
-        <v>228</v>
+        <v>145</v>
       </c>
       <c r="H15">
-        <v>99647.4</v>
+        <v>30164.35</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -15658,39 +15667,39 @@
         <v>0</v>
       </c>
       <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15" t="s">
-        <v>150</v>
+        <v>-867.1</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>-867.1</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="B16" t="s">
-        <v>310</v>
+        <v>373</v>
       </c>
       <c r="C16" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D16" t="s">
         <v>178</v>
       </c>
       <c r="E16" t="s">
-        <v>376</v>
+        <v>47</v>
       </c>
       <c r="F16">
-        <v>432.65</v>
+        <v>9284</v>
       </c>
       <c r="G16">
-        <v>114</v>
+        <v>10</v>
       </c>
       <c r="H16">
-        <v>49322.1</v>
+        <v>92840</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -15720,39 +15729,39 @@
         <v>0</v>
       </c>
       <c r="R16">
-        <v>-501.6</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="S16" t="s">
+        <v>150</v>
       </c>
       <c r="T16">
-        <v>-501.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="B17" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C17" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D17" t="s">
-        <v>219</v>
+        <v>148</v>
       </c>
       <c r="E17" t="s">
         <v>47</v>
       </c>
       <c r="F17">
-        <v>6621.5</v>
+        <v>9251.5</v>
       </c>
       <c r="G17">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>99322.5</v>
+        <v>46257.5</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -15782,18 +15791,18 @@
         <v>0</v>
       </c>
       <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17" t="s">
-        <v>150</v>
+        <v>-162.5</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>-162.5</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="B18" t="s">
         <v>373</v>
@@ -15808,13 +15817,13 @@
         <v>47</v>
       </c>
       <c r="F18">
-        <v>1995.8</v>
+        <v>437.05</v>
       </c>
       <c r="G18">
-        <v>49</v>
+        <v>228</v>
       </c>
       <c r="H18">
-        <v>97794.2</v>
+        <v>99647.4</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -15855,28 +15864,28 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="B19" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C19" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D19" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>377</v>
       </c>
       <c r="F19">
-        <v>1373.5</v>
+        <v>432.65</v>
       </c>
       <c r="G19">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="H19">
-        <v>97518.5</v>
+        <v>49322.1</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -15906,18 +15915,18 @@
         <v>0</v>
       </c>
       <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19" t="s">
-        <v>150</v>
+        <v>-501.6</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>-501.6</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="B20" t="s">
         <v>373</v>
@@ -15932,13 +15941,13 @@
         <v>47</v>
       </c>
       <c r="F20">
-        <v>811</v>
+        <v>6621.5</v>
       </c>
       <c r="G20">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="H20">
-        <v>96509</v>
+        <v>99322.5</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -15979,7 +15988,7 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="B21" t="s">
         <v>373</v>
@@ -15994,13 +16003,13 @@
         <v>47</v>
       </c>
       <c r="F21">
-        <v>2986</v>
+        <v>1995.8</v>
       </c>
       <c r="G21">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H21">
-        <v>98538</v>
+        <v>97794.2</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -16041,28 +16050,28 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B22" t="s">
-        <v>310</v>
+        <v>373</v>
       </c>
       <c r="C22" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>219</v>
       </c>
       <c r="E22" t="s">
         <v>47</v>
       </c>
       <c r="F22">
-        <v>2989.4</v>
+        <v>1373.5</v>
       </c>
       <c r="G22">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="H22">
-        <v>47830.4</v>
+        <v>97518.5</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -16092,18 +16101,18 @@
         <v>0</v>
       </c>
       <c r="R22">
-        <v>54.4</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="S22" t="s">
+        <v>150</v>
       </c>
       <c r="T22">
-        <v>54.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>317</v>
+        <v>282</v>
       </c>
       <c r="B23" t="s">
         <v>373</v>
@@ -16112,19 +16121,19 @@
         <v>374</v>
       </c>
       <c r="D23" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E23" t="s">
         <v>47</v>
       </c>
       <c r="F23">
-        <v>19.59</v>
+        <v>811</v>
       </c>
       <c r="G23">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="H23">
-        <v>607.29</v>
+        <v>96509</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -16165,28 +16174,28 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="B24" t="s">
-        <v>310</v>
+        <v>373</v>
       </c>
       <c r="C24" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D24" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E24" t="s">
         <v>47</v>
       </c>
       <c r="F24">
-        <v>19.59</v>
+        <v>2986</v>
       </c>
       <c r="G24">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H24">
-        <v>293.85</v>
+        <v>98538</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -16218,8 +16227,8 @@
       <c r="R24">
         <v>0</v>
       </c>
-      <c r="S24">
-        <v>0</v>
+      <c r="S24" t="s">
+        <v>150</v>
       </c>
       <c r="T24">
         <v>0</v>
@@ -16227,13 +16236,13 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="B25" t="s">
-        <v>324</v>
+        <v>375</v>
       </c>
       <c r="C25" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D25" t="s">
         <v>148</v>
@@ -16242,13 +16251,13 @@
         <v>47</v>
       </c>
       <c r="F25">
-        <v>18.5</v>
+        <v>2989.4</v>
       </c>
       <c r="G25">
         <v>16</v>
       </c>
       <c r="H25">
-        <v>296</v>
+        <v>47830.4</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -16278,18 +16287,18 @@
         <v>0</v>
       </c>
       <c r="R25">
-        <v>-17.44</v>
+        <v>54.4</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
       <c r="T25">
-        <v>-17.44</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B26" t="s">
         <v>373</v>
@@ -16298,19 +16307,19 @@
         <v>374</v>
       </c>
       <c r="D26" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="E26" t="s">
         <v>47</v>
       </c>
       <c r="F26">
-        <v>1351.4</v>
+        <v>19.59</v>
       </c>
       <c r="G26">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="H26">
-        <v>98652.2</v>
+        <v>607.29</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -16351,28 +16360,28 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B27" t="s">
-        <v>310</v>
+        <v>375</v>
       </c>
       <c r="C27" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="E27" t="s">
         <v>47</v>
       </c>
       <c r="F27">
-        <v>1333.5</v>
+        <v>19.59</v>
       </c>
       <c r="G27">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="H27">
-        <v>48006</v>
+        <v>293.85</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -16402,24 +16411,24 @@
         <v>0</v>
       </c>
       <c r="R27">
-        <v>-644.4</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="T27">
-        <v>-644.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B28" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="C28" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D28" t="s">
         <v>148</v>
@@ -16428,13 +16437,13 @@
         <v>47</v>
       </c>
       <c r="F28">
-        <v>1305.2</v>
+        <v>18.5</v>
       </c>
       <c r="G28">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H28">
-        <v>23493.6</v>
+        <v>296</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -16464,13 +16473,13 @@
         <v>0</v>
       </c>
       <c r="R28">
-        <v>-831.6</v>
+        <v>-17.44</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
       <c r="T28">
-        <v>-831.6</v>
+        <v>-17.44</v>
       </c>
     </row>
   </sheetData>
@@ -16508,60 +16517,60 @@
         <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>105</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D2" t="s">
         <v>148</v>
@@ -16603,18 +16612,18 @@
         <v>1776.1</v>
       </c>
       <c r="Q2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D3" t="s">
         <v>148</v>
@@ -16656,18 +16665,18 @@
         <v>389.6</v>
       </c>
       <c r="Q3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B4" t="s">
         <v>297</v>
       </c>
       <c r="C4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D4" t="s">
         <v>178</v>
@@ -16709,12 +16718,12 @@
         <v>8739</v>
       </c>
       <c r="Q4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B5" t="s">
         <v>401</v>
@@ -16762,15 +16771,15 @@
         <v>616.27</v>
       </c>
       <c r="Q5" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B6" t="s">
-        <v>403</v>
+        <v>309</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
@@ -16803,7 +16812,7 @@
         <v>2.69</v>
       </c>
       <c r="M6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N6">
         <v>62659.2</v>
@@ -16815,18 +16824,18 @@
         <v>22.45</v>
       </c>
       <c r="Q6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D7" t="s">
         <v>147</v>
@@ -16868,18 +16877,18 @@
         <v>805.05</v>
       </c>
       <c r="Q7" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
@@ -16909,7 +16918,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N8">
         <v>60416.4</v>
@@ -16921,15 +16930,15 @@
         <v>2621</v>
       </c>
       <c r="Q8" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B9" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C9" t="s">
         <v>39</v>
@@ -16962,7 +16971,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N9">
         <v>59860</v>
@@ -16974,18 +16983,18 @@
         <v>5896.21</v>
       </c>
       <c r="Q9" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B10" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D10" t="s">
         <v>147</v>
@@ -17015,7 +17024,7 @@
         <v>9.59</v>
       </c>
       <c r="M10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N10">
         <v>61938</v>
@@ -17027,15 +17036,15 @@
         <v>10168.16</v>
       </c>
       <c r="Q10" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B11" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C11" t="s">
         <v>39</v>
@@ -17080,15 +17089,15 @@
         <v>175.16</v>
       </c>
       <c r="Q11" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B12" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C12" t="s">
         <v>39</v>
@@ -17121,7 +17130,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N12">
         <v>61422</v>
@@ -17133,18 +17142,18 @@
         <v>5031.53</v>
       </c>
       <c r="Q12" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B13" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D13" t="s">
         <v>147</v>
@@ -17186,15 +17195,15 @@
         <v>795.05</v>
       </c>
       <c r="Q13" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B14" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C14" t="s">
         <v>39</v>
@@ -17239,15 +17248,15 @@
         <v>16002</v>
       </c>
       <c r="Q14" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B15" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C15" t="s">
         <v>39</v>
@@ -17292,15 +17301,15 @@
         <v>150.3</v>
       </c>
       <c r="Q15" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B16" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -17345,7 +17354,7 @@
         <v>806.35</v>
       </c>
       <c r="Q16" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -17357,7 +17366,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -17377,60 +17386,60 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="Q1" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B2" t="s">
         <v>178</v>
@@ -17439,16 +17448,16 @@
         <v>297</v>
       </c>
       <c r="D2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E2" t="s">
         <v>178</v>
       </c>
       <c r="G2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I2" t="s">
         <v>156</v>
@@ -17475,18 +17484,18 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B3" t="s">
         <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D3" t="s">
         <v>39</v>
@@ -17495,10 +17504,10 @@
         <v>178</v>
       </c>
       <c r="G3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I3" t="s">
         <v>156</v>
@@ -17525,12 +17534,12 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B4" t="s">
         <v>178</v>
@@ -17539,16 +17548,16 @@
         <v>205</v>
       </c>
       <c r="D4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E4" t="s">
         <v>178</v>
       </c>
       <c r="G4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I4" t="s">
         <v>156</v>
@@ -17575,12 +17584,12 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B5" t="s">
         <v>178</v>
@@ -17598,10 +17607,10 @@
         <v>622.5499877929688</v>
       </c>
       <c r="G5" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I5" t="s">
         <v>156</v>
@@ -17628,12 +17637,12 @@
         <v>1</v>
       </c>
       <c r="Q5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B6" t="s">
         <v>219</v>
@@ -17651,10 +17660,10 @@
         <v>637.9000244140625</v>
       </c>
       <c r="G6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I6" t="s">
         <v>156</v>
@@ -17681,21 +17690,21 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B7" t="s">
         <v>219</v>
       </c>
       <c r="C7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E7" t="s">
         <v>219</v>
@@ -17704,10 +17713,10 @@
         <v>814.9000244140625</v>
       </c>
       <c r="G7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I7" t="s">
         <v>156</v>
@@ -17734,12 +17743,12 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B8" t="s">
         <v>219</v>
@@ -17757,10 +17766,10 @@
         <v>637.9000244140625</v>
       </c>
       <c r="G8" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H8" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I8" t="s">
         <v>156</v>
@@ -17787,21 +17796,21 @@
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B9" t="s">
         <v>219</v>
       </c>
       <c r="C9" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E9" t="s">
         <v>219</v>
@@ -17810,10 +17819,10 @@
         <v>814.9000244140625</v>
       </c>
       <c r="G9" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H9" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I9" t="s">
         <v>156</v>
@@ -17840,12 +17849,12 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B10" t="s">
         <v>178</v>
@@ -17863,10 +17872,10 @@
         <v>863.5</v>
       </c>
       <c r="G10" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I10" t="s">
         <v>156</v>
@@ -17893,12 +17902,12 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B11" t="s">
         <v>178</v>
@@ -17907,7 +17916,7 @@
         <v>297</v>
       </c>
       <c r="D11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E11" t="s">
         <v>178</v>
@@ -17916,10 +17925,10 @@
         <v>8782.5</v>
       </c>
       <c r="G11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I11" t="s">
         <v>156</v>
@@ -17946,18 +17955,18 @@
         <v>1</v>
       </c>
       <c r="Q11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B12" t="s">
         <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D12" t="s">
         <v>39</v>
@@ -17969,10 +17978,10 @@
         <v>16326</v>
       </c>
       <c r="G12" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H12" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I12" t="s">
         <v>156</v>
@@ -17999,18 +18008,18 @@
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B13" t="s">
         <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>403</v>
+        <v>309</v>
       </c>
       <c r="D13" t="s">
         <v>39</v>
@@ -18022,10 +18031,10 @@
         <v>23.700000762939453</v>
       </c>
       <c r="G13" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H13" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I13" t="s">
         <v>156</v>
@@ -18052,21 +18061,21 @@
         <v>1</v>
       </c>
       <c r="Q13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B14" t="s">
         <v>147</v>
       </c>
       <c r="C14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E14" t="s">
         <v>147</v>
@@ -18075,10 +18084,10 @@
         <v>813.2000122070312</v>
       </c>
       <c r="G14" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H14" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I14" t="s">
         <v>156</v>
@@ -18105,21 +18114,21 @@
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B15" t="s">
         <v>147</v>
       </c>
       <c r="C15" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E15" t="s">
         <v>147</v>
@@ -18128,10 +18137,10 @@
         <v>806.7000122070312</v>
       </c>
       <c r="G15" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H15" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I15" t="s">
         <v>156</v>
@@ -18158,21 +18167,21 @@
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B16" t="s">
         <v>178</v>
       </c>
       <c r="C16" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D16" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E16" t="s">
         <v>178</v>
@@ -18181,10 +18190,10 @@
         <v>1378.300048828125</v>
       </c>
       <c r="G16" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I16" t="s">
         <v>156</v>
@@ -18211,18 +18220,18 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B17" t="s">
         <v>178</v>
       </c>
       <c r="C17" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D17" t="s">
         <v>39</v>
@@ -18234,10 +18243,10 @@
         <v>56.9900016784668</v>
       </c>
       <c r="G17" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H17" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I17" t="s">
         <v>156</v>
@@ -18264,18 +18273,18 @@
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B18" t="s">
         <v>178</v>
       </c>
       <c r="C18" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D18" t="s">
         <v>39</v>
@@ -18287,10 +18296,10 @@
         <v>121</v>
       </c>
       <c r="G18" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H18" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I18" t="s">
         <v>156</v>
@@ -18317,18 +18326,18 @@
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B19" t="s">
         <v>178</v>
       </c>
       <c r="C19" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D19" t="s">
         <v>39</v>
@@ -18340,10 +18349,10 @@
         <v>5024</v>
       </c>
       <c r="G19" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I19" t="s">
         <v>156</v>
@@ -18370,18 +18379,18 @@
         <v>1</v>
       </c>
       <c r="Q19" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B20" t="s">
         <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D20" t="s">
         <v>39</v>
@@ -18393,10 +18402,10 @@
         <v>156.35000610351562</v>
       </c>
       <c r="G20" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H20" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I20" t="s">
         <v>156</v>
@@ -18423,18 +18432,18 @@
         <v>1</v>
       </c>
       <c r="Q20" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B21" t="s">
         <v>178</v>
       </c>
       <c r="C21" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D21" t="s">
         <v>39</v>
@@ -18446,10 +18455,10 @@
         <v>422.45001220703125</v>
       </c>
       <c r="G21" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H21" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I21" t="s">
         <v>156</v>
@@ -18476,21 +18485,21 @@
         <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B22" t="s">
         <v>178</v>
       </c>
       <c r="C22" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D22" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E22" t="s">
         <v>178</v>
@@ -18499,10 +18508,10 @@
         <v>1378.300048828125</v>
       </c>
       <c r="G22" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H22" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I22" t="s">
         <v>156</v>
@@ -18529,18 +18538,18 @@
         <v>1</v>
       </c>
       <c r="Q22" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B23" t="s">
         <v>178</v>
       </c>
       <c r="C23" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D23" t="s">
         <v>39</v>
@@ -18552,10 +18561,10 @@
         <v>56.9900016784668</v>
       </c>
       <c r="G23" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H23" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I23" t="s">
         <v>156</v>
@@ -18582,18 +18591,18 @@
         <v>1</v>
       </c>
       <c r="Q23" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B24" t="s">
         <v>178</v>
       </c>
       <c r="C24" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D24" t="s">
         <v>39</v>
@@ -18605,10 +18614,10 @@
         <v>121</v>
       </c>
       <c r="G24" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H24" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I24" t="s">
         <v>156</v>
@@ -18635,18 +18644,18 @@
         <v>1</v>
       </c>
       <c r="Q24" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B25" t="s">
         <v>178</v>
       </c>
       <c r="C25" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D25" t="s">
         <v>39</v>
@@ -18658,10 +18667,10 @@
         <v>5024</v>
       </c>
       <c r="G25" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H25" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I25" t="s">
         <v>156</v>
@@ -18688,18 +18697,18 @@
         <v>1</v>
       </c>
       <c r="Q25" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B26" t="s">
         <v>178</v>
       </c>
       <c r="C26" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D26" t="s">
         <v>39</v>
@@ -18711,10 +18720,10 @@
         <v>156.35000610351562</v>
       </c>
       <c r="G26" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H26" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I26" t="s">
         <v>156</v>
@@ -18741,18 +18750,18 @@
         <v>1</v>
       </c>
       <c r="Q26" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B27" t="s">
         <v>178</v>
       </c>
       <c r="C27" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D27" t="s">
         <v>39</v>
@@ -18764,10 +18773,10 @@
         <v>422.45001220703125</v>
       </c>
       <c r="G27" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H27" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I27" t="s">
         <v>156</v>
@@ -18794,18 +18803,18 @@
         <v>1</v>
       </c>
       <c r="Q27" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B28" t="s">
         <v>178</v>
       </c>
       <c r="C28" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D28" t="s">
         <v>39</v>
@@ -18817,10 +18826,10 @@
         <v>179.52000427246094</v>
       </c>
       <c r="G28" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H28" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I28" t="s">
         <v>156</v>
@@ -18847,21 +18856,21 @@
         <v>1</v>
       </c>
       <c r="Q28" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B29" t="s">
         <v>147</v>
       </c>
       <c r="C29" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D29" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E29" t="s">
         <v>147</v>
@@ -18870,10 +18879,10 @@
         <v>10166</v>
       </c>
       <c r="G29" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H29" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I29" t="s">
         <v>156</v>
@@ -18900,18 +18909,18 @@
         <v>1</v>
       </c>
       <c r="Q29" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B30" t="s">
         <v>147</v>
       </c>
       <c r="C30" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D30" t="s">
         <v>39</v>
@@ -18923,10 +18932,10 @@
         <v>527.9000244140625</v>
       </c>
       <c r="G30" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H30" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I30" t="s">
         <v>156</v>
@@ -18953,12 +18962,12 @@
         <v>1</v>
       </c>
       <c r="Q30" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B31" t="s">
         <v>147</v>
@@ -18967,7 +18976,7 @@
         <v>332</v>
       </c>
       <c r="D31" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E31" t="s">
         <v>147</v>
@@ -18976,10 +18985,10 @@
         <v>4442.39990234375</v>
       </c>
       <c r="G31" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H31" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I31" t="s">
         <v>156</v>
@@ -19006,18 +19015,18 @@
         <v>1</v>
       </c>
       <c r="Q31" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B32" t="s">
         <v>147</v>
       </c>
       <c r="C32" t="s">
-        <v>403</v>
+        <v>309</v>
       </c>
       <c r="D32" t="s">
         <v>39</v>
@@ -19029,10 +19038,10 @@
         <v>23.700000762939453</v>
       </c>
       <c r="G32" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H32" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I32" t="s">
         <v>156</v>
@@ -19059,21 +19068,21 @@
         <v>1</v>
       </c>
       <c r="Q32" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B33" t="s">
         <v>147</v>
       </c>
       <c r="C33" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D33" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E33" t="s">
         <v>147</v>
@@ -19082,10 +19091,10 @@
         <v>813.2000122070312</v>
       </c>
       <c r="G33" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H33" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I33" t="s">
         <v>156</v>
@@ -19112,12 +19121,12 @@
         <v>1</v>
       </c>
       <c r="Q33" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B34" t="s">
         <v>147</v>
@@ -19135,10 +19144,10 @@
         <v>739.3499755859375</v>
       </c>
       <c r="G34" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H34" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I34" t="s">
         <v>156</v>
@@ -19165,21 +19174,21 @@
         <v>1</v>
       </c>
       <c r="Q34" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B35" t="s">
         <v>147</v>
       </c>
       <c r="C35" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D35" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E35" t="s">
         <v>147</v>
@@ -19188,10 +19197,10 @@
         <v>806.7000122070312</v>
       </c>
       <c r="G35" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H35" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I35" t="s">
         <v>156</v>
@@ -19218,18 +19227,18 @@
         <v>1</v>
       </c>
       <c r="Q35" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B36" t="s">
         <v>147</v>
       </c>
       <c r="C36" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D36" t="s">
         <v>39</v>
@@ -19241,10 +19250,10 @@
         <v>527.9000244140625</v>
       </c>
       <c r="G36" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H36" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I36" t="s">
         <v>156</v>
@@ -19271,12 +19280,12 @@
         <v>1</v>
       </c>
       <c r="Q36" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B37" t="s">
         <v>147</v>
@@ -19285,7 +19294,7 @@
         <v>332</v>
       </c>
       <c r="D37" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E37" t="s">
         <v>147</v>
@@ -19294,10 +19303,10 @@
         <v>4442.39990234375</v>
       </c>
       <c r="G37" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H37" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I37" t="s">
         <v>156</v>
@@ -19324,12 +19333,12 @@
         <v>1</v>
       </c>
       <c r="Q37" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B38" t="s">
         <v>147</v>
@@ -19347,10 +19356,10 @@
         <v>739.3499755859375</v>
       </c>
       <c r="G38" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H38" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I38" t="s">
         <v>156</v>
@@ -19377,21 +19386,21 @@
         <v>1</v>
       </c>
       <c r="Q38" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B39" t="s">
         <v>148</v>
       </c>
       <c r="C39" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D39" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E39" t="s">
         <v>148</v>
@@ -19400,10 +19409,10 @@
         <v>1866.0999755859375</v>
       </c>
       <c r="G39" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H39" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I39" t="s">
         <v>156</v>
@@ -19430,21 +19439,21 @@
         <v>1</v>
       </c>
       <c r="Q39" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B40" t="s">
         <v>148</v>
       </c>
       <c r="C40" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D40" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
@@ -19453,10 +19462,10 @@
         <v>417.95001220703125</v>
       </c>
       <c r="G40" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H40" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I40" t="s">
         <v>156</v>
@@ -19483,7 +19492,60 @@
         <v>1</v>
       </c>
       <c r="Q40" t="s">
-        <v>394</v>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>446</v>
+      </c>
+      <c r="B41" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" t="s">
+        <v>401</v>
+      </c>
+      <c r="D41" t="s">
+        <v>39</v>
+      </c>
+      <c r="E41" t="s">
+        <v>148</v>
+      </c>
+      <c r="F41">
+        <v>625.6500244140625</v>
+      </c>
+      <c r="G41" t="s">
+        <v>431</v>
+      </c>
+      <c r="H41" t="s">
+        <v>392</v>
+      </c>
+      <c r="I41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J41">
+        <v>201.82</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41" t="s">
+        <v>150</v>
+      </c>
+      <c r="M41">
+        <v>3.84</v>
+      </c>
+      <c r="N41">
+        <v>0.77</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -19510,27 +19572,27 @@
         <v>357</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -19542,7 +19604,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3676" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3676" uniqueCount="446">
   <si>
     <t>Metric</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-15T11:32:34.551Z</t>
+    <t>2026-07-15T11:41:18.692Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -645,9 +645,6 @@
     <t>2026-07-14 09:17 IST ENTRY_BUY BUY 5 @ 88.49; turnover 442.45; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
   </si>
   <si>
-    <t>official NSE delivery distribution ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid.</t>
-  </si>
-  <si>
     <t>Momentum continuation buy</t>
   </si>
   <si>
@@ -780,9 +777,6 @@
     <t>2026-07-13 09:17 IST ENTRY_BUY BUY 10 @ 9284; turnover 92840; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 5 @ 9251.5; turnover 46257.5; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -162.5</t>
   </si>
   <si>
-    <t>daily RS21 below zero official NSE delivery distribution setup grade WATCH ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. WAIT/WATCH: one primary weakness is not enough for a partial exit.</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -825,7 +819,7 @@
     <t>2026-07-10 09:17 IST ENTRY_BUY BUY 73 @ 1351.4; turnover 98652.2; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-14 09:17 IST PARTIAL_EXIT SELL 36 @ 1333.5; turnover 48006; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -644.4 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 18 @ 1305.2; turnover 23493.6; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -831.6</t>
   </si>
   <si>
-    <t>daily RS21 below zero daily RSI below 50 close below Supertrend close below 50-DMA official NSE delivery distribution setup grade WATCH ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. WAIT/WATCH: 1/3 completed deterioration closes confirmed.</t>
+    <t>daily RS21 below zero daily RSI below 50 close below Supertrend close below 50-DMA setup grade WATCH ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. WAIT/WATCH: 1/3 completed deterioration closes confirmed.</t>
   </si>
   <si>
     <t>16/21</t>
@@ -1200,6 +1194,9 @@
     <t>Capital Goods</t>
   </si>
   <si>
+    <t>SGFIN</t>
+  </si>
+  <si>
     <t>WAITING_CAPITAL</t>
   </si>
   <si>
@@ -1212,9 +1209,6 @@
     <t>Maximum open-position limit reached.</t>
   </si>
   <si>
-    <t>SGFIN</t>
-  </si>
-  <si>
     <t>CJGEL</t>
   </si>
   <si>
@@ -1338,7 +1332,7 @@
     <t>2026-07-15T10:40:23.503Z</t>
   </si>
   <si>
-    <t>2026-07-15T11:32:34.123Z</t>
+    <t>2026-07-15T11:41:18.161Z</t>
   </si>
   <si>
     <t>Type</t>
@@ -3610,7 +3604,7 @@
         <v>152</v>
       </c>
       <c r="BJ5" t="s">
-        <v>208</v>
+        <v>153</v>
       </c>
       <c r="BK5">
         <v>0</v>
@@ -3622,7 +3616,7 @@
         <v>154</v>
       </c>
       <c r="BN5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BO5" t="s">
         <v>156</v>
@@ -3640,10 +3634,10 @@
         <v>158</v>
       </c>
       <c r="BT5" t="s">
+        <v>209</v>
+      </c>
+      <c r="BU5" t="s">
         <v>210</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>211</v>
       </c>
       <c r="BV5" t="s">
         <v>27</v>
@@ -3670,13 +3664,13 @@
         <v>198</v>
       </c>
       <c r="CD5" t="s">
+        <v>211</v>
+      </c>
+      <c r="CE5" t="s">
         <v>212</v>
       </c>
-      <c r="CE5" t="s">
+      <c r="CF5" t="s">
         <v>213</v>
-      </c>
-      <c r="CF5" t="s">
-        <v>214</v>
       </c>
       <c r="CG5" t="s">
         <v>168</v>
@@ -3685,7 +3679,7 @@
         <v>169</v>
       </c>
       <c r="CI5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="CJ5" t="s">
         <v>171</v>
@@ -3721,7 +3715,7 @@
         <v>2.77</v>
       </c>
       <c r="CU5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CV5">
         <v>85.99</v>
@@ -3733,7 +3727,7 @@
         <v>84.44</v>
       </c>
       <c r="CY5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="CZ5" t="s">
         <v>150</v>
@@ -3750,16 +3744,16 @@
         <v>175</v>
       </c>
       <c r="D6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" t="s">
         <v>218</v>
-      </c>
-      <c r="E6" t="s">
-        <v>219</v>
       </c>
       <c r="F6" t="s">
         <v>146</v>
       </c>
       <c r="G6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H6" t="s">
         <v>178</v>
@@ -3903,7 +3897,7 @@
         <v>-1561.2</v>
       </c>
       <c r="BC6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BD6" t="s">
         <v>150</v>
@@ -3924,7 +3918,7 @@
         <v>152</v>
       </c>
       <c r="BJ6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="BK6">
         <v>1</v>
@@ -3948,13 +3942,13 @@
         <v>4</v>
       </c>
       <c r="BR6" t="s">
+        <v>222</v>
+      </c>
+      <c r="BS6" t="s">
         <v>223</v>
       </c>
-      <c r="BS6" t="s">
+      <c r="BT6" t="s">
         <v>224</v>
-      </c>
-      <c r="BT6" t="s">
-        <v>225</v>
       </c>
       <c r="BU6" t="s">
         <v>150</v>
@@ -3966,10 +3960,10 @@
         <v>150</v>
       </c>
       <c r="BX6" t="s">
+        <v>225</v>
+      </c>
+      <c r="BY6" t="s">
         <v>226</v>
-      </c>
-      <c r="BY6" t="s">
-        <v>227</v>
       </c>
       <c r="BZ6" t="s">
         <v>161</v>
@@ -3984,13 +3978,13 @@
         <v>184</v>
       </c>
       <c r="CD6" t="s">
+        <v>227</v>
+      </c>
+      <c r="CE6" t="s">
         <v>228</v>
       </c>
-      <c r="CE6" t="s">
+      <c r="CF6" t="s">
         <v>229</v>
-      </c>
-      <c r="CF6" t="s">
-        <v>230</v>
       </c>
       <c r="CG6" t="s">
         <v>188</v>
@@ -3999,7 +3993,7 @@
         <v>169</v>
       </c>
       <c r="CI6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CJ6" t="s">
         <v>171</v>
@@ -4047,7 +4041,7 @@
         <v>1981</v>
       </c>
       <c r="CY6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CZ6" t="s">
         <v>150</v>
@@ -4064,16 +4058,16 @@
         <v>175</v>
       </c>
       <c r="D7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" t="s">
         <v>233</v>
-      </c>
-      <c r="E7" t="s">
-        <v>234</v>
       </c>
       <c r="F7" t="s">
         <v>146</v>
       </c>
       <c r="G7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H7" t="s">
         <v>178</v>
@@ -4217,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="BC7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BD7" t="s">
         <v>150</v>
@@ -4238,19 +4232,19 @@
         <v>152</v>
       </c>
       <c r="BJ7" t="s">
+        <v>235</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>150</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>150</v>
+      </c>
+      <c r="BN7" t="s">
         <v>236</v>
-      </c>
-      <c r="BK7">
-        <v>0</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>150</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>150</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>237</v>
       </c>
       <c r="BO7" t="s">
         <v>156</v>
@@ -4262,10 +4256,10 @@
         <v>1</v>
       </c>
       <c r="BR7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="BT7" t="s">
         <v>150</v>
@@ -4298,13 +4292,13 @@
         <v>184</v>
       </c>
       <c r="CD7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="CE7" t="s">
+        <v>238</v>
+      </c>
+      <c r="CF7" t="s">
         <v>239</v>
-      </c>
-      <c r="CF7" t="s">
-        <v>240</v>
       </c>
       <c r="CG7" t="s">
         <v>188</v>
@@ -4313,7 +4307,7 @@
         <v>169</v>
       </c>
       <c r="CI7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CJ7" t="s">
         <v>171</v>
@@ -4361,7 +4355,7 @@
         <v>4319.5</v>
       </c>
       <c r="CY7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="CZ7" t="s">
         <v>150</v>
@@ -4378,16 +4372,16 @@
         <v>175</v>
       </c>
       <c r="D8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" t="s">
         <v>242</v>
-      </c>
-      <c r="E8" t="s">
-        <v>243</v>
       </c>
       <c r="F8" t="s">
         <v>146</v>
       </c>
       <c r="G8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H8" t="s">
         <v>178</v>
@@ -4531,7 +4525,7 @@
         <v>-867.1</v>
       </c>
       <c r="BC8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="BD8" t="s">
         <v>150</v>
@@ -4552,7 +4546,7 @@
         <v>152</v>
       </c>
       <c r="BJ8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="BK8">
         <v>0</v>
@@ -4576,10 +4570,10 @@
         <v>4</v>
       </c>
       <c r="BR8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="BT8" t="s">
         <v>150</v>
@@ -4612,13 +4606,13 @@
         <v>184</v>
       </c>
       <c r="CD8" t="s">
+        <v>245</v>
+      </c>
+      <c r="CE8" t="s">
         <v>246</v>
       </c>
-      <c r="CE8" t="s">
+      <c r="CF8" t="s">
         <v>247</v>
-      </c>
-      <c r="CF8" t="s">
-        <v>248</v>
       </c>
       <c r="CG8" t="s">
         <v>188</v>
@@ -4627,7 +4621,7 @@
         <v>169</v>
       </c>
       <c r="CI8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CJ8" t="s">
         <v>171</v>
@@ -4663,7 +4657,7 @@
         <v>0.55</v>
       </c>
       <c r="CU8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CV8">
         <v>199.5</v>
@@ -4675,7 +4669,7 @@
         <v>186.53</v>
       </c>
       <c r="CY8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="CZ8" t="s">
         <v>150</v>
@@ -4692,16 +4686,16 @@
         <v>175</v>
       </c>
       <c r="D9" t="s">
+        <v>249</v>
+      </c>
+      <c r="E9" t="s">
         <v>250</v>
-      </c>
-      <c r="E9" t="s">
-        <v>251</v>
       </c>
       <c r="F9" t="s">
         <v>146</v>
       </c>
       <c r="G9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H9" t="s">
         <v>178</v>
@@ -4845,7 +4839,7 @@
         <v>-162.5</v>
       </c>
       <c r="BC9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="BD9" t="s">
         <v>150</v>
@@ -4866,7 +4860,7 @@
         <v>152</v>
       </c>
       <c r="BJ9" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="BK9">
         <v>0</v>
@@ -4881,7 +4875,7 @@
         <v>181</v>
       </c>
       <c r="BO9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="BP9">
         <v>10</v>
@@ -4893,13 +4887,13 @@
         <v>157</v>
       </c>
       <c r="BS9" t="s">
+        <v>253</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BU9" t="s">
         <v>255</v>
-      </c>
-      <c r="BT9" t="s">
-        <v>256</v>
-      </c>
-      <c r="BU9" t="s">
-        <v>257</v>
       </c>
       <c r="BV9" t="s">
         <v>27</v>
@@ -4908,7 +4902,7 @@
         <v>150</v>
       </c>
       <c r="BX9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="BY9" t="s">
         <v>150</v>
@@ -4926,13 +4920,13 @@
         <v>184</v>
       </c>
       <c r="CD9" t="s">
+        <v>257</v>
+      </c>
+      <c r="CE9" t="s">
+        <v>258</v>
+      </c>
+      <c r="CF9" t="s">
         <v>259</v>
-      </c>
-      <c r="CE9" t="s">
-        <v>260</v>
-      </c>
-      <c r="CF9" t="s">
-        <v>261</v>
       </c>
       <c r="CG9" t="s">
         <v>168</v>
@@ -4941,7 +4935,7 @@
         <v>169</v>
       </c>
       <c r="CI9" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="CJ9" t="s">
         <v>171</v>
@@ -4977,7 +4971,7 @@
         <v>0.1</v>
       </c>
       <c r="CU9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CV9">
         <v>9100</v>
@@ -4989,7 +4983,7 @@
         <v>8955.5</v>
       </c>
       <c r="CY9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="CZ9" t="s">
         <v>150</v>
@@ -5000,25 +4994,25 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C10" t="s">
         <v>205</v>
       </c>
       <c r="D10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F10" t="s">
         <v>146</v>
       </c>
       <c r="G10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I10" t="s">
         <v>47</v>
@@ -5159,7 +5153,7 @@
         <v>-1476</v>
       </c>
       <c r="BC10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="BD10" t="s">
         <v>150</v>
@@ -5180,7 +5174,7 @@
         <v>152</v>
       </c>
       <c r="BJ10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="BK10">
         <v>1</v>
@@ -5204,7 +5198,7 @@
         <v>4</v>
       </c>
       <c r="BR10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS10" t="s">
         <v>150</v>
@@ -5240,22 +5234,22 @@
         <v>184</v>
       </c>
       <c r="CD10" t="s">
+        <v>267</v>
+      </c>
+      <c r="CE10" t="s">
+        <v>268</v>
+      </c>
+      <c r="CF10" t="s">
         <v>269</v>
       </c>
-      <c r="CE10" t="s">
+      <c r="CG10" t="s">
         <v>270</v>
       </c>
-      <c r="CF10" t="s">
+      <c r="CH10" t="s">
         <v>271</v>
       </c>
-      <c r="CG10" t="s">
+      <c r="CI10" t="s">
         <v>272</v>
-      </c>
-      <c r="CH10" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI10" t="s">
-        <v>274</v>
       </c>
       <c r="CJ10" t="s">
         <v>171</v>
@@ -5291,7 +5285,7 @@
         <v>150</v>
       </c>
       <c r="CU10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="CV10">
         <v>1321</v>
@@ -5303,7 +5297,7 @@
         <v>1321</v>
       </c>
       <c r="CY10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="CZ10" t="s">
         <v>150</v>
@@ -5314,25 +5308,25 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C11" t="s">
         <v>144</v>
       </c>
       <c r="D11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F11" t="s">
         <v>146</v>
       </c>
       <c r="G11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I11" t="s">
         <v>47</v>
@@ -5473,7 +5467,7 @@
         <v>-501.6</v>
       </c>
       <c r="BC11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="BD11" t="s">
         <v>150</v>
@@ -5494,13 +5488,13 @@
         <v>152</v>
       </c>
       <c r="BJ11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="BK11">
         <v>0</v>
       </c>
       <c r="BL11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="BM11" t="s">
         <v>150</v>
@@ -5518,7 +5512,7 @@
         <v>5</v>
       </c>
       <c r="BR11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS11" t="s">
         <v>150</v>
@@ -5554,22 +5548,22 @@
         <v>184</v>
       </c>
       <c r="CD11" t="s">
+        <v>278</v>
+      </c>
+      <c r="CE11" t="s">
+        <v>279</v>
+      </c>
+      <c r="CF11" t="s">
         <v>280</v>
       </c>
-      <c r="CE11" t="s">
-        <v>281</v>
-      </c>
-      <c r="CF11" t="s">
-        <v>282</v>
-      </c>
       <c r="CG11" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH11" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI11" t="s">
         <v>272</v>
-      </c>
-      <c r="CH11" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI11" t="s">
-        <v>274</v>
       </c>
       <c r="CJ11" t="s">
         <v>171</v>
@@ -5605,7 +5599,7 @@
         <v>150</v>
       </c>
       <c r="CU11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CV11">
         <v>425.45</v>
@@ -5617,7 +5611,7 @@
         <v>422.15</v>
       </c>
       <c r="CY11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="CZ11" t="s">
         <v>150</v>
@@ -5628,25 +5622,25 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C12" t="s">
         <v>144</v>
       </c>
       <c r="D12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F12" t="s">
         <v>146</v>
       </c>
       <c r="G12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I12" t="s">
         <v>47</v>
@@ -5787,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="BC12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="BD12" t="s">
         <v>150</v>
@@ -5832,7 +5826,7 @@
         <v>4</v>
       </c>
       <c r="BR12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS12" t="s">
         <v>150</v>
@@ -5868,22 +5862,22 @@
         <v>184</v>
       </c>
       <c r="CD12" t="s">
+        <v>284</v>
+      </c>
+      <c r="CE12" t="s">
+        <v>285</v>
+      </c>
+      <c r="CF12" t="s">
         <v>286</v>
       </c>
-      <c r="CE12" t="s">
-        <v>287</v>
-      </c>
-      <c r="CF12" t="s">
-        <v>288</v>
-      </c>
       <c r="CG12" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH12" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI12" t="s">
         <v>272</v>
-      </c>
-      <c r="CH12" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI12" t="s">
-        <v>274</v>
       </c>
       <c r="CJ12" t="s">
         <v>171</v>
@@ -5931,7 +5925,7 @@
         <v>6202.5</v>
       </c>
       <c r="CY12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="CZ12" t="s">
         <v>150</v>
@@ -5942,25 +5936,25 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C13" t="s">
         <v>205</v>
       </c>
       <c r="D13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F13" t="s">
         <v>146</v>
       </c>
       <c r="G13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I13" t="s">
         <v>47</v>
@@ -6101,7 +6095,7 @@
         <v>0</v>
       </c>
       <c r="BC13" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="BD13" t="s">
         <v>150</v>
@@ -6146,7 +6140,7 @@
         <v>3</v>
       </c>
       <c r="BR13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS13" t="s">
         <v>150</v>
@@ -6182,22 +6176,22 @@
         <v>184</v>
       </c>
       <c r="CD13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="CE13" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="CF13" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="CG13" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH13" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI13" t="s">
         <v>272</v>
-      </c>
-      <c r="CH13" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI13" t="s">
-        <v>274</v>
       </c>
       <c r="CJ13" t="s">
         <v>171</v>
@@ -6233,7 +6227,7 @@
         <v>150</v>
       </c>
       <c r="CU13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CV13">
         <v>1957</v>
@@ -6245,7 +6239,7 @@
         <v>1957</v>
       </c>
       <c r="CY13" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="CZ13" t="s">
         <v>150</v>
@@ -6256,25 +6250,25 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C14" t="s">
         <v>205</v>
       </c>
       <c r="D14" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E14" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F14" t="s">
         <v>146</v>
       </c>
       <c r="G14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I14" t="s">
         <v>47</v>
@@ -6415,7 +6409,7 @@
         <v>0</v>
       </c>
       <c r="BC14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="BD14" t="s">
         <v>150</v>
@@ -6460,7 +6454,7 @@
         <v>4</v>
       </c>
       <c r="BR14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS14" t="s">
         <v>150</v>
@@ -6496,22 +6490,22 @@
         <v>184</v>
       </c>
       <c r="CD14" t="s">
+        <v>295</v>
+      </c>
+      <c r="CE14" t="s">
+        <v>296</v>
+      </c>
+      <c r="CF14" t="s">
         <v>297</v>
       </c>
-      <c r="CE14" t="s">
-        <v>298</v>
-      </c>
-      <c r="CF14" t="s">
-        <v>299</v>
-      </c>
       <c r="CG14" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH14" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI14" t="s">
         <v>272</v>
-      </c>
-      <c r="CH14" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI14" t="s">
-        <v>274</v>
       </c>
       <c r="CJ14" t="s">
         <v>171</v>
@@ -6559,7 +6553,7 @@
         <v>1303.2</v>
       </c>
       <c r="CY14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="CZ14" t="s">
         <v>150</v>
@@ -6570,25 +6564,25 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C15" t="s">
         <v>144</v>
       </c>
       <c r="D15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F15" t="s">
         <v>146</v>
       </c>
       <c r="G15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I15" t="s">
         <v>47</v>
@@ -6729,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="BC15" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="BD15" t="s">
         <v>150</v>
@@ -6774,7 +6768,7 @@
         <v>3</v>
       </c>
       <c r="BR15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS15" t="s">
         <v>150</v>
@@ -6810,22 +6804,22 @@
         <v>184</v>
       </c>
       <c r="CD15" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="CE15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="CF15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="CG15" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH15" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI15" t="s">
         <v>272</v>
-      </c>
-      <c r="CH15" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI15" t="s">
-        <v>274</v>
       </c>
       <c r="CJ15" t="s">
         <v>171</v>
@@ -6873,7 +6867,7 @@
         <v>721.4</v>
       </c>
       <c r="CY15" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="CZ15" t="s">
         <v>150</v>
@@ -6884,25 +6878,25 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C16" t="s">
         <v>144</v>
       </c>
       <c r="D16" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E16" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F16" t="s">
         <v>146</v>
       </c>
       <c r="G16" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I16" t="s">
         <v>47</v>
@@ -7043,7 +7037,7 @@
         <v>54.4</v>
       </c>
       <c r="BC16" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="BD16" t="s">
         <v>150</v>
@@ -7088,7 +7082,7 @@
         <v>3</v>
       </c>
       <c r="BR16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS16" t="s">
         <v>150</v>
@@ -7124,22 +7118,22 @@
         <v>184</v>
       </c>
       <c r="CD16" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="CE16" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="CF16" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="CG16" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH16" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI16" t="s">
         <v>272</v>
-      </c>
-      <c r="CH16" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI16" t="s">
-        <v>274</v>
       </c>
       <c r="CJ16" t="s">
         <v>171</v>
@@ -7175,7 +7169,7 @@
         <v>150</v>
       </c>
       <c r="CU16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CV16">
         <v>2903.2</v>
@@ -7187,7 +7181,7 @@
         <v>2903.2</v>
       </c>
       <c r="CY16" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="CZ16" t="s">
         <v>150</v>
@@ -8017,19 +8011,19 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F2" t="s">
         <v>311</v>
       </c>
-      <c r="D2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F2" t="s">
-        <v>313</v>
-      </c>
       <c r="G2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H2" t="s">
         <v>178</v>
@@ -8038,7 +8032,7 @@
         <v>47</v>
       </c>
       <c r="J2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K2">
         <v>19.59</v>
@@ -8047,7 +8041,7 @@
         <v>19.59</v>
       </c>
       <c r="M2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N2">
         <v>16</v>
@@ -8122,7 +8116,7 @@
         <v>2</v>
       </c>
       <c r="AL2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AM2">
         <v>168.93</v>
@@ -8173,28 +8167,28 @@
         <v>-17.44</v>
       </c>
       <c r="BC2" t="s">
+        <v>315</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>316</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BI2" t="s">
         <v>317</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BJ2" t="s">
         <v>318</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>319</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>320</v>
       </c>
       <c r="BK2">
         <v>1</v>
@@ -8257,19 +8251,19 @@
         <v>185</v>
       </c>
       <c r="CE2" t="s">
+        <v>319</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>320</v>
+      </c>
+      <c r="CG2" t="s">
         <v>321</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>322</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>323</v>
       </c>
       <c r="CH2" t="s">
         <v>169</v>
       </c>
       <c r="CI2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="CJ2" t="s">
         <v>27</v>
@@ -8305,7 +8299,7 @@
         <v>0.76</v>
       </c>
       <c r="CU2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="CV2">
         <v>20</v>
@@ -8317,10 +8311,10 @@
         <v>19.01</v>
       </c>
       <c r="CY2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="CZ2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -9858,7 +9852,7 @@
         <v>152</v>
       </c>
       <c r="BJ5" t="s">
-        <v>208</v>
+        <v>153</v>
       </c>
       <c r="BK5">
         <v>0</v>
@@ -9870,7 +9864,7 @@
         <v>154</v>
       </c>
       <c r="BN5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BO5" t="s">
         <v>156</v>
@@ -9888,10 +9882,10 @@
         <v>158</v>
       </c>
       <c r="BT5" t="s">
+        <v>209</v>
+      </c>
+      <c r="BU5" t="s">
         <v>210</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>211</v>
       </c>
       <c r="BV5" t="s">
         <v>27</v>
@@ -9918,13 +9912,13 @@
         <v>198</v>
       </c>
       <c r="CD5" t="s">
+        <v>211</v>
+      </c>
+      <c r="CE5" t="s">
         <v>212</v>
       </c>
-      <c r="CE5" t="s">
+      <c r="CF5" t="s">
         <v>213</v>
-      </c>
-      <c r="CF5" t="s">
-        <v>214</v>
       </c>
       <c r="CG5" t="s">
         <v>168</v>
@@ -9933,7 +9927,7 @@
         <v>169</v>
       </c>
       <c r="CI5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="CJ5" t="s">
         <v>171</v>
@@ -9969,7 +9963,7 @@
         <v>2.77</v>
       </c>
       <c r="CU5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CV5">
         <v>85.99</v>
@@ -9981,7 +9975,7 @@
         <v>84.44</v>
       </c>
       <c r="CY5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="CZ5" t="s">
         <v>150</v>
@@ -9998,16 +9992,16 @@
         <v>175</v>
       </c>
       <c r="D6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" t="s">
         <v>218</v>
-      </c>
-      <c r="E6" t="s">
-        <v>219</v>
       </c>
       <c r="F6" t="s">
         <v>146</v>
       </c>
       <c r="G6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H6" t="s">
         <v>178</v>
@@ -10151,7 +10145,7 @@
         <v>-1561.2</v>
       </c>
       <c r="BC6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BD6" t="s">
         <v>150</v>
@@ -10172,7 +10166,7 @@
         <v>152</v>
       </c>
       <c r="BJ6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="BK6">
         <v>1</v>
@@ -10196,13 +10190,13 @@
         <v>4</v>
       </c>
       <c r="BR6" t="s">
+        <v>222</v>
+      </c>
+      <c r="BS6" t="s">
         <v>223</v>
       </c>
-      <c r="BS6" t="s">
+      <c r="BT6" t="s">
         <v>224</v>
-      </c>
-      <c r="BT6" t="s">
-        <v>225</v>
       </c>
       <c r="BU6" t="s">
         <v>150</v>
@@ -10214,10 +10208,10 @@
         <v>150</v>
       </c>
       <c r="BX6" t="s">
+        <v>225</v>
+      </c>
+      <c r="BY6" t="s">
         <v>226</v>
-      </c>
-      <c r="BY6" t="s">
-        <v>227</v>
       </c>
       <c r="BZ6" t="s">
         <v>161</v>
@@ -10232,13 +10226,13 @@
         <v>184</v>
       </c>
       <c r="CD6" t="s">
+        <v>227</v>
+      </c>
+      <c r="CE6" t="s">
         <v>228</v>
       </c>
-      <c r="CE6" t="s">
+      <c r="CF6" t="s">
         <v>229</v>
-      </c>
-      <c r="CF6" t="s">
-        <v>230</v>
       </c>
       <c r="CG6" t="s">
         <v>188</v>
@@ -10247,7 +10241,7 @@
         <v>169</v>
       </c>
       <c r="CI6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CJ6" t="s">
         <v>171</v>
@@ -10295,7 +10289,7 @@
         <v>1981</v>
       </c>
       <c r="CY6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CZ6" t="s">
         <v>150</v>
@@ -10312,16 +10306,16 @@
         <v>175</v>
       </c>
       <c r="D7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" t="s">
         <v>233</v>
-      </c>
-      <c r="E7" t="s">
-        <v>234</v>
       </c>
       <c r="F7" t="s">
         <v>146</v>
       </c>
       <c r="G7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H7" t="s">
         <v>178</v>
@@ -10465,7 +10459,7 @@
         <v>0</v>
       </c>
       <c r="BC7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BD7" t="s">
         <v>150</v>
@@ -10486,19 +10480,19 @@
         <v>152</v>
       </c>
       <c r="BJ7" t="s">
+        <v>235</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>150</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>150</v>
+      </c>
+      <c r="BN7" t="s">
         <v>236</v>
-      </c>
-      <c r="BK7">
-        <v>0</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>150</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>150</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>237</v>
       </c>
       <c r="BO7" t="s">
         <v>156</v>
@@ -10510,10 +10504,10 @@
         <v>1</v>
       </c>
       <c r="BR7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="BT7" t="s">
         <v>150</v>
@@ -10546,13 +10540,13 @@
         <v>184</v>
       </c>
       <c r="CD7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="CE7" t="s">
+        <v>238</v>
+      </c>
+      <c r="CF7" t="s">
         <v>239</v>
-      </c>
-      <c r="CF7" t="s">
-        <v>240</v>
       </c>
       <c r="CG7" t="s">
         <v>188</v>
@@ -10561,7 +10555,7 @@
         <v>169</v>
       </c>
       <c r="CI7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CJ7" t="s">
         <v>171</v>
@@ -10609,7 +10603,7 @@
         <v>4319.5</v>
       </c>
       <c r="CY7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="CZ7" t="s">
         <v>150</v>
@@ -10626,16 +10620,16 @@
         <v>175</v>
       </c>
       <c r="D8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" t="s">
         <v>242</v>
-      </c>
-      <c r="E8" t="s">
-        <v>243</v>
       </c>
       <c r="F8" t="s">
         <v>146</v>
       </c>
       <c r="G8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H8" t="s">
         <v>178</v>
@@ -10779,7 +10773,7 @@
         <v>-867.1</v>
       </c>
       <c r="BC8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="BD8" t="s">
         <v>150</v>
@@ -10800,7 +10794,7 @@
         <v>152</v>
       </c>
       <c r="BJ8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="BK8">
         <v>0</v>
@@ -10824,10 +10818,10 @@
         <v>4</v>
       </c>
       <c r="BR8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="BT8" t="s">
         <v>150</v>
@@ -10860,13 +10854,13 @@
         <v>184</v>
       </c>
       <c r="CD8" t="s">
+        <v>245</v>
+      </c>
+      <c r="CE8" t="s">
         <v>246</v>
       </c>
-      <c r="CE8" t="s">
+      <c r="CF8" t="s">
         <v>247</v>
-      </c>
-      <c r="CF8" t="s">
-        <v>248</v>
       </c>
       <c r="CG8" t="s">
         <v>188</v>
@@ -10875,7 +10869,7 @@
         <v>169</v>
       </c>
       <c r="CI8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CJ8" t="s">
         <v>171</v>
@@ -10911,7 +10905,7 @@
         <v>0.55</v>
       </c>
       <c r="CU8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CV8">
         <v>199.5</v>
@@ -10923,7 +10917,7 @@
         <v>186.53</v>
       </c>
       <c r="CY8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="CZ8" t="s">
         <v>150</v>
@@ -10940,16 +10934,16 @@
         <v>175</v>
       </c>
       <c r="D9" t="s">
+        <v>249</v>
+      </c>
+      <c r="E9" t="s">
         <v>250</v>
-      </c>
-      <c r="E9" t="s">
-        <v>251</v>
       </c>
       <c r="F9" t="s">
         <v>146</v>
       </c>
       <c r="G9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H9" t="s">
         <v>178</v>
@@ -11093,7 +11087,7 @@
         <v>-162.5</v>
       </c>
       <c r="BC9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="BD9" t="s">
         <v>150</v>
@@ -11114,7 +11108,7 @@
         <v>152</v>
       </c>
       <c r="BJ9" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="BK9">
         <v>0</v>
@@ -11129,7 +11123,7 @@
         <v>181</v>
       </c>
       <c r="BO9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="BP9">
         <v>10</v>
@@ -11141,13 +11135,13 @@
         <v>157</v>
       </c>
       <c r="BS9" t="s">
+        <v>253</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BU9" t="s">
         <v>255</v>
-      </c>
-      <c r="BT9" t="s">
-        <v>256</v>
-      </c>
-      <c r="BU9" t="s">
-        <v>257</v>
       </c>
       <c r="BV9" t="s">
         <v>27</v>
@@ -11156,7 +11150,7 @@
         <v>150</v>
       </c>
       <c r="BX9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="BY9" t="s">
         <v>150</v>
@@ -11174,13 +11168,13 @@
         <v>184</v>
       </c>
       <c r="CD9" t="s">
+        <v>257</v>
+      </c>
+      <c r="CE9" t="s">
+        <v>258</v>
+      </c>
+      <c r="CF9" t="s">
         <v>259</v>
-      </c>
-      <c r="CE9" t="s">
-        <v>260</v>
-      </c>
-      <c r="CF9" t="s">
-        <v>261</v>
       </c>
       <c r="CG9" t="s">
         <v>168</v>
@@ -11189,7 +11183,7 @@
         <v>169</v>
       </c>
       <c r="CI9" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="CJ9" t="s">
         <v>171</v>
@@ -11225,7 +11219,7 @@
         <v>0.1</v>
       </c>
       <c r="CU9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CV9">
         <v>9100</v>
@@ -11237,7 +11231,7 @@
         <v>8955.5</v>
       </c>
       <c r="CY9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="CZ9" t="s">
         <v>150</v>
@@ -11248,25 +11242,25 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C10" t="s">
         <v>205</v>
       </c>
       <c r="D10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F10" t="s">
         <v>146</v>
       </c>
       <c r="G10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I10" t="s">
         <v>47</v>
@@ -11407,7 +11401,7 @@
         <v>-1476</v>
       </c>
       <c r="BC10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="BD10" t="s">
         <v>150</v>
@@ -11428,7 +11422,7 @@
         <v>152</v>
       </c>
       <c r="BJ10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="BK10">
         <v>1</v>
@@ -11452,7 +11446,7 @@
         <v>4</v>
       </c>
       <c r="BR10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS10" t="s">
         <v>150</v>
@@ -11488,22 +11482,22 @@
         <v>184</v>
       </c>
       <c r="CD10" t="s">
+        <v>267</v>
+      </c>
+      <c r="CE10" t="s">
+        <v>268</v>
+      </c>
+      <c r="CF10" t="s">
         <v>269</v>
       </c>
-      <c r="CE10" t="s">
+      <c r="CG10" t="s">
         <v>270</v>
       </c>
-      <c r="CF10" t="s">
+      <c r="CH10" t="s">
         <v>271</v>
       </c>
-      <c r="CG10" t="s">
+      <c r="CI10" t="s">
         <v>272</v>
-      </c>
-      <c r="CH10" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI10" t="s">
-        <v>274</v>
       </c>
       <c r="CJ10" t="s">
         <v>171</v>
@@ -11539,7 +11533,7 @@
         <v>150</v>
       </c>
       <c r="CU10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="CV10">
         <v>1321</v>
@@ -11551,7 +11545,7 @@
         <v>1321</v>
       </c>
       <c r="CY10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="CZ10" t="s">
         <v>150</v>
@@ -11562,25 +11556,25 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C11" t="s">
         <v>144</v>
       </c>
       <c r="D11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F11" t="s">
         <v>146</v>
       </c>
       <c r="G11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I11" t="s">
         <v>47</v>
@@ -11721,7 +11715,7 @@
         <v>-501.6</v>
       </c>
       <c r="BC11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="BD11" t="s">
         <v>150</v>
@@ -11742,13 +11736,13 @@
         <v>152</v>
       </c>
       <c r="BJ11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="BK11">
         <v>0</v>
       </c>
       <c r="BL11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="BM11" t="s">
         <v>150</v>
@@ -11766,7 +11760,7 @@
         <v>5</v>
       </c>
       <c r="BR11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS11" t="s">
         <v>150</v>
@@ -11802,22 +11796,22 @@
         <v>184</v>
       </c>
       <c r="CD11" t="s">
+        <v>278</v>
+      </c>
+      <c r="CE11" t="s">
+        <v>279</v>
+      </c>
+      <c r="CF11" t="s">
         <v>280</v>
       </c>
-      <c r="CE11" t="s">
-        <v>281</v>
-      </c>
-      <c r="CF11" t="s">
-        <v>282</v>
-      </c>
       <c r="CG11" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH11" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI11" t="s">
         <v>272</v>
-      </c>
-      <c r="CH11" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI11" t="s">
-        <v>274</v>
       </c>
       <c r="CJ11" t="s">
         <v>171</v>
@@ -11853,7 +11847,7 @@
         <v>150</v>
       </c>
       <c r="CU11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CV11">
         <v>425.45</v>
@@ -11865,7 +11859,7 @@
         <v>422.15</v>
       </c>
       <c r="CY11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="CZ11" t="s">
         <v>150</v>
@@ -11876,25 +11870,25 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C12" t="s">
         <v>144</v>
       </c>
       <c r="D12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F12" t="s">
         <v>146</v>
       </c>
       <c r="G12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I12" t="s">
         <v>47</v>
@@ -12035,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="BC12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="BD12" t="s">
         <v>150</v>
@@ -12080,7 +12074,7 @@
         <v>4</v>
       </c>
       <c r="BR12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS12" t="s">
         <v>150</v>
@@ -12116,22 +12110,22 @@
         <v>184</v>
       </c>
       <c r="CD12" t="s">
+        <v>284</v>
+      </c>
+      <c r="CE12" t="s">
+        <v>285</v>
+      </c>
+      <c r="CF12" t="s">
         <v>286</v>
       </c>
-      <c r="CE12" t="s">
-        <v>287</v>
-      </c>
-      <c r="CF12" t="s">
-        <v>288</v>
-      </c>
       <c r="CG12" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH12" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI12" t="s">
         <v>272</v>
-      </c>
-      <c r="CH12" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI12" t="s">
-        <v>274</v>
       </c>
       <c r="CJ12" t="s">
         <v>171</v>
@@ -12179,7 +12173,7 @@
         <v>6202.5</v>
       </c>
       <c r="CY12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="CZ12" t="s">
         <v>150</v>
@@ -12190,25 +12184,25 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C13" t="s">
         <v>205</v>
       </c>
       <c r="D13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F13" t="s">
         <v>146</v>
       </c>
       <c r="G13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I13" t="s">
         <v>47</v>
@@ -12349,7 +12343,7 @@
         <v>0</v>
       </c>
       <c r="BC13" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="BD13" t="s">
         <v>150</v>
@@ -12394,7 +12388,7 @@
         <v>3</v>
       </c>
       <c r="BR13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS13" t="s">
         <v>150</v>
@@ -12430,22 +12424,22 @@
         <v>184</v>
       </c>
       <c r="CD13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="CE13" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="CF13" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="CG13" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH13" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI13" t="s">
         <v>272</v>
-      </c>
-      <c r="CH13" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI13" t="s">
-        <v>274</v>
       </c>
       <c r="CJ13" t="s">
         <v>171</v>
@@ -12481,7 +12475,7 @@
         <v>150</v>
       </c>
       <c r="CU13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CV13">
         <v>1957</v>
@@ -12493,7 +12487,7 @@
         <v>1957</v>
       </c>
       <c r="CY13" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="CZ13" t="s">
         <v>150</v>
@@ -12504,25 +12498,25 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C14" t="s">
         <v>205</v>
       </c>
       <c r="D14" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E14" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F14" t="s">
         <v>146</v>
       </c>
       <c r="G14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I14" t="s">
         <v>47</v>
@@ -12663,7 +12657,7 @@
         <v>0</v>
       </c>
       <c r="BC14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="BD14" t="s">
         <v>150</v>
@@ -12708,7 +12702,7 @@
         <v>4</v>
       </c>
       <c r="BR14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS14" t="s">
         <v>150</v>
@@ -12744,22 +12738,22 @@
         <v>184</v>
       </c>
       <c r="CD14" t="s">
+        <v>295</v>
+      </c>
+      <c r="CE14" t="s">
+        <v>296</v>
+      </c>
+      <c r="CF14" t="s">
         <v>297</v>
       </c>
-      <c r="CE14" t="s">
-        <v>298</v>
-      </c>
-      <c r="CF14" t="s">
-        <v>299</v>
-      </c>
       <c r="CG14" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH14" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI14" t="s">
         <v>272</v>
-      </c>
-      <c r="CH14" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI14" t="s">
-        <v>274</v>
       </c>
       <c r="CJ14" t="s">
         <v>171</v>
@@ -12807,7 +12801,7 @@
         <v>1303.2</v>
       </c>
       <c r="CY14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="CZ14" t="s">
         <v>150</v>
@@ -12818,25 +12812,25 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C15" t="s">
         <v>144</v>
       </c>
       <c r="D15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F15" t="s">
         <v>146</v>
       </c>
       <c r="G15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I15" t="s">
         <v>47</v>
@@ -12977,7 +12971,7 @@
         <v>0</v>
       </c>
       <c r="BC15" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="BD15" t="s">
         <v>150</v>
@@ -13022,7 +13016,7 @@
         <v>3</v>
       </c>
       <c r="BR15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS15" t="s">
         <v>150</v>
@@ -13058,22 +13052,22 @@
         <v>184</v>
       </c>
       <c r="CD15" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="CE15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="CF15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="CG15" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH15" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI15" t="s">
         <v>272</v>
-      </c>
-      <c r="CH15" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI15" t="s">
-        <v>274</v>
       </c>
       <c r="CJ15" t="s">
         <v>171</v>
@@ -13121,7 +13115,7 @@
         <v>721.4</v>
       </c>
       <c r="CY15" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="CZ15" t="s">
         <v>150</v>
@@ -13132,25 +13126,25 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C16" t="s">
         <v>144</v>
       </c>
       <c r="D16" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E16" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F16" t="s">
         <v>146</v>
       </c>
       <c r="G16" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I16" t="s">
         <v>47</v>
@@ -13291,7 +13285,7 @@
         <v>54.4</v>
       </c>
       <c r="BC16" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="BD16" t="s">
         <v>150</v>
@@ -13336,7 +13330,7 @@
         <v>3</v>
       </c>
       <c r="BR16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS16" t="s">
         <v>150</v>
@@ -13372,22 +13366,22 @@
         <v>184</v>
       </c>
       <c r="CD16" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="CE16" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="CF16" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="CG16" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH16" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI16" t="s">
         <v>272</v>
-      </c>
-      <c r="CH16" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI16" t="s">
-        <v>274</v>
       </c>
       <c r="CJ16" t="s">
         <v>171</v>
@@ -13423,7 +13417,7 @@
         <v>150</v>
       </c>
       <c r="CU16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CV16">
         <v>2903.2</v>
@@ -13435,7 +13429,7 @@
         <v>2903.2</v>
       </c>
       <c r="CY16" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="CZ16" t="s">
         <v>150</v>
@@ -13449,19 +13443,19 @@
         <v>41</v>
       </c>
       <c r="C17" t="s">
+        <v>309</v>
+      </c>
+      <c r="D17" t="s">
+        <v>310</v>
+      </c>
+      <c r="E17" t="s">
+        <v>310</v>
+      </c>
+      <c r="F17" t="s">
         <v>311</v>
       </c>
-      <c r="D17" t="s">
-        <v>312</v>
-      </c>
-      <c r="E17" t="s">
-        <v>312</v>
-      </c>
-      <c r="F17" t="s">
-        <v>313</v>
-      </c>
       <c r="G17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H17" t="s">
         <v>178</v>
@@ -13470,7 +13464,7 @@
         <v>47</v>
       </c>
       <c r="J17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K17">
         <v>19.59</v>
@@ -13479,7 +13473,7 @@
         <v>19.59</v>
       </c>
       <c r="M17" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N17">
         <v>16</v>
@@ -13554,7 +13548,7 @@
         <v>2</v>
       </c>
       <c r="AL17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AM17">
         <v>168.93</v>
@@ -13605,28 +13599,28 @@
         <v>-17.44</v>
       </c>
       <c r="BC17" t="s">
+        <v>315</v>
+      </c>
+      <c r="BD17" t="s">
+        <v>316</v>
+      </c>
+      <c r="BE17" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF17" t="s">
+        <v>150</v>
+      </c>
+      <c r="BG17" t="s">
+        <v>150</v>
+      </c>
+      <c r="BH17" t="s">
+        <v>150</v>
+      </c>
+      <c r="BI17" t="s">
         <v>317</v>
       </c>
-      <c r="BD17" t="s">
+      <c r="BJ17" t="s">
         <v>318</v>
-      </c>
-      <c r="BE17" t="s">
-        <v>150</v>
-      </c>
-      <c r="BF17" t="s">
-        <v>150</v>
-      </c>
-      <c r="BG17" t="s">
-        <v>150</v>
-      </c>
-      <c r="BH17" t="s">
-        <v>150</v>
-      </c>
-      <c r="BI17" t="s">
-        <v>319</v>
-      </c>
-      <c r="BJ17" t="s">
-        <v>320</v>
       </c>
       <c r="BK17">
         <v>1</v>
@@ -13689,19 +13683,19 @@
         <v>185</v>
       </c>
       <c r="CE17" t="s">
+        <v>319</v>
+      </c>
+      <c r="CF17" t="s">
+        <v>320</v>
+      </c>
+      <c r="CG17" t="s">
         <v>321</v>
-      </c>
-      <c r="CF17" t="s">
-        <v>322</v>
-      </c>
-      <c r="CG17" t="s">
-        <v>323</v>
       </c>
       <c r="CH17" t="s">
         <v>169</v>
       </c>
       <c r="CI17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="CJ17" t="s">
         <v>27</v>
@@ -13737,7 +13731,7 @@
         <v>0.76</v>
       </c>
       <c r="CU17" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="CV17">
         <v>20</v>
@@ -13749,10 +13743,10 @@
         <v>19.01</v>
       </c>
       <c r="CY17" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="CZ17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="1:104" x14ac:dyDescent="0.25">
@@ -13766,34 +13760,34 @@
         <v>205</v>
       </c>
       <c r="D18" t="s">
+        <v>325</v>
+      </c>
+      <c r="E18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F18" t="s">
+        <v>326</v>
+      </c>
+      <c r="G18" t="s">
+        <v>219</v>
+      </c>
+      <c r="H18" t="s">
+        <v>150</v>
+      </c>
+      <c r="I18" t="s">
+        <v>150</v>
+      </c>
+      <c r="J18" t="s">
+        <v>150</v>
+      </c>
+      <c r="K18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L18" t="s">
+        <v>150</v>
+      </c>
+      <c r="M18" t="s">
         <v>327</v>
-      </c>
-      <c r="E18" t="s">
-        <v>327</v>
-      </c>
-      <c r="F18" t="s">
-        <v>328</v>
-      </c>
-      <c r="G18" t="s">
-        <v>220</v>
-      </c>
-      <c r="H18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I18" t="s">
-        <v>150</v>
-      </c>
-      <c r="J18" t="s">
-        <v>150</v>
-      </c>
-      <c r="K18" t="s">
-        <v>150</v>
-      </c>
-      <c r="L18" t="s">
-        <v>150</v>
-      </c>
-      <c r="M18" t="s">
-        <v>329</v>
       </c>
       <c r="N18" t="s">
         <v>150</v>
@@ -13868,7 +13862,7 @@
         <v>150</v>
       </c>
       <c r="AL18" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AM18" t="s">
         <v>150</v>
@@ -13952,7 +13946,7 @@
         <v>150</v>
       </c>
       <c r="BN18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="BO18" t="s">
         <v>156</v>
@@ -13964,7 +13958,7 @@
         <v>4</v>
       </c>
       <c r="BR18" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="BS18" t="s">
         <v>150</v>
@@ -13991,31 +13985,31 @@
         <v>161</v>
       </c>
       <c r="CA18" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="CB18" t="s">
         <v>163</v>
       </c>
       <c r="CC18" t="s">
+        <v>331</v>
+      </c>
+      <c r="CD18" t="s">
+        <v>332</v>
+      </c>
+      <c r="CE18" t="s">
         <v>333</v>
       </c>
-      <c r="CD18" t="s">
+      <c r="CF18" t="s">
         <v>334</v>
       </c>
-      <c r="CE18" t="s">
+      <c r="CG18" t="s">
+        <v>270</v>
+      </c>
+      <c r="CH18" t="s">
+        <v>271</v>
+      </c>
+      <c r="CI18" t="s">
         <v>335</v>
-      </c>
-      <c r="CF18" t="s">
-        <v>336</v>
-      </c>
-      <c r="CG18" t="s">
-        <v>272</v>
-      </c>
-      <c r="CH18" t="s">
-        <v>273</v>
-      </c>
-      <c r="CI18" t="s">
-        <v>337</v>
       </c>
       <c r="CJ18" t="s">
         <v>171</v>
@@ -14063,7 +14057,7 @@
         <v>4305.8</v>
       </c>
       <c r="CY18" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="CZ18" t="s">
         <v>150</v>
@@ -14080,16 +14074,16 @@
         <v>205</v>
       </c>
       <c r="D19" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E19" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F19" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H19" t="s">
         <v>150</v>
@@ -14107,7 +14101,7 @@
         <v>150</v>
       </c>
       <c r="M19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N19" t="s">
         <v>150</v>
@@ -14182,7 +14176,7 @@
         <v>150</v>
       </c>
       <c r="AL19" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AM19" t="s">
         <v>150</v>
@@ -14278,7 +14272,7 @@
         <v>4</v>
       </c>
       <c r="BR19" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="BS19" t="s">
         <v>150</v>
@@ -14305,31 +14299,31 @@
         <v>161</v>
       </c>
       <c r="CA19" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="CB19" t="s">
         <v>163</v>
       </c>
       <c r="CC19" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="CD19" t="s">
+        <v>339</v>
+      </c>
+      <c r="CE19" t="s">
+        <v>340</v>
+      </c>
+      <c r="CF19" t="s">
         <v>341</v>
       </c>
-      <c r="CE19" t="s">
-        <v>342</v>
-      </c>
-      <c r="CF19" t="s">
-        <v>343</v>
-      </c>
       <c r="CG19" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="CH19" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="CI19" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="CJ19" t="s">
         <v>171</v>
@@ -14377,7 +14371,7 @@
         <v>1012.9</v>
       </c>
       <c r="CY19" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="CZ19" t="s">
         <v>150</v>
@@ -14394,16 +14388,16 @@
         <v>144</v>
       </c>
       <c r="D20" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E20" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F20" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H20" t="s">
         <v>150</v>
@@ -14421,7 +14415,7 @@
         <v>150</v>
       </c>
       <c r="M20" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N20" t="s">
         <v>150</v>
@@ -14496,7 +14490,7 @@
         <v>150</v>
       </c>
       <c r="AL20" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AM20" t="s">
         <v>150</v>
@@ -14583,7 +14577,7 @@
         <v>181</v>
       </c>
       <c r="BO20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="BP20">
         <v>12</v>
@@ -14592,7 +14586,7 @@
         <v>2</v>
       </c>
       <c r="BR20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BS20" t="s">
         <v>150</v>
@@ -14625,25 +14619,25 @@
         <v>163</v>
       </c>
       <c r="CC20" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="CD20" t="s">
+        <v>344</v>
+      </c>
+      <c r="CE20" t="s">
+        <v>345</v>
+      </c>
+      <c r="CF20" t="s">
         <v>346</v>
       </c>
-      <c r="CE20" t="s">
-        <v>347</v>
-      </c>
-      <c r="CF20" t="s">
-        <v>348</v>
-      </c>
       <c r="CG20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="CH20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="CI20" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="CJ20" t="s">
         <v>171</v>
@@ -14691,7 +14685,7 @@
         <v>688.05</v>
       </c>
       <c r="CY20" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="CZ20" t="s">
         <v>150</v>
@@ -14730,61 +14724,61 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -14792,10 +14786,10 @@
         <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D2" t="s">
         <v>148</v>
@@ -14854,10 +14848,10 @@
         <v>176</v>
       </c>
       <c r="B3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D3" t="s">
         <v>147</v>
@@ -14916,10 +14910,10 @@
         <v>193</v>
       </c>
       <c r="B4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D4" t="s">
         <v>147</v>
@@ -14978,10 +14972,10 @@
         <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D5" t="s">
         <v>147</v>
@@ -15037,13 +15031,13 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D6" t="s">
         <v>178</v>
@@ -15099,19 +15093,19 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D7" t="s">
         <v>178</v>
       </c>
       <c r="E7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F7">
         <v>2004.5</v>
@@ -15161,13 +15155,13 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D8" t="s">
         <v>147</v>
@@ -15223,13 +15217,13 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C9" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D9" t="s">
         <v>148</v>
@@ -15285,13 +15279,13 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B10" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D10" t="s">
         <v>178</v>
@@ -15347,13 +15341,13 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B11" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C11" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D11" t="s">
         <v>178</v>
@@ -15409,13 +15403,13 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B12" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C12" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D12" t="s">
         <v>148</v>
@@ -15471,13 +15465,13 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D13" t="s">
         <v>178</v>
@@ -15533,13 +15527,13 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B14" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C14" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D14" t="s">
         <v>148</v>
@@ -15595,16 +15589,16 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C15" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E15" t="s">
         <v>47</v>
@@ -15657,13 +15651,13 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B16" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C16" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D16" t="s">
         <v>147</v>
@@ -15719,13 +15713,13 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B17" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C17" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D17" t="s">
         <v>148</v>
@@ -15781,16 +15775,16 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B18" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C18" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E18" t="s">
         <v>47</v>
@@ -15843,19 +15837,19 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B19" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C19" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D19" t="s">
         <v>178</v>
       </c>
       <c r="E19" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F19">
         <v>432.65</v>
@@ -15905,16 +15899,16 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B20" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C20" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E20" t="s">
         <v>47</v>
@@ -15967,16 +15961,16 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B21" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C21" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E21" t="s">
         <v>47</v>
@@ -16029,16 +16023,16 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B22" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C22" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E22" t="s">
         <v>47</v>
@@ -16091,16 +16085,16 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B23" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C23" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D23" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E23" t="s">
         <v>47</v>
@@ -16153,16 +16147,16 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B24" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C24" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E24" t="s">
         <v>47</v>
@@ -16215,13 +16209,13 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C25" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D25" t="s">
         <v>148</v>
@@ -16277,13 +16271,13 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B26" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C26" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D26" t="s">
         <v>178</v>
@@ -16339,13 +16333,13 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B27" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C27" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D27" t="s">
         <v>178</v>
@@ -16401,13 +16395,13 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B28" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C28" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D28" t="s">
         <v>148</v>
@@ -16496,60 +16490,60 @@
         <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>105</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C2" t="s">
         <v>387</v>
-      </c>
-      <c r="B2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C2" t="s">
-        <v>389</v>
       </c>
       <c r="D2" t="s">
         <v>148</v>
@@ -16558,7 +16552,7 @@
         <v>156</v>
       </c>
       <c r="F2">
-        <v>210.96</v>
+        <v>216.12</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -16591,18 +16585,18 @@
         <v>1776.1</v>
       </c>
       <c r="Q2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D3" t="s">
         <v>148</v>
@@ -16611,7 +16605,7 @@
         <v>156</v>
       </c>
       <c r="F3">
-        <v>206.63</v>
+        <v>211.8</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -16644,121 +16638,121 @@
         <v>389.6</v>
       </c>
       <c r="Q3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="B4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C4" t="s">
-        <v>395</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
         <v>156</v>
       </c>
       <c r="F4">
-        <v>202.53</v>
+        <v>201.82</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="I4" t="s">
         <v>150</v>
       </c>
       <c r="J4">
-        <v>4.49</v>
+        <v>3.84</v>
       </c>
       <c r="K4">
-        <v>3.64</v>
+        <v>0.77</v>
       </c>
       <c r="L4">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="N4">
-        <v>62538</v>
+        <v>62565</v>
       </c>
       <c r="O4">
-        <v>1365</v>
+        <v>938</v>
       </c>
       <c r="P4">
-        <v>8739</v>
+        <v>616.27</v>
       </c>
       <c r="Q4" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B5" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>394</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="E5" t="s">
         <v>156</v>
       </c>
       <c r="F5">
-        <v>201.82</v>
+        <v>197.36</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="I5" t="s">
         <v>150</v>
       </c>
       <c r="J5">
-        <v>3.84</v>
+        <v>4.49</v>
       </c>
       <c r="K5">
-        <v>0.77</v>
+        <v>3.64</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="M5" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="N5">
-        <v>62565</v>
+        <v>62538</v>
       </c>
       <c r="O5">
-        <v>938</v>
+        <v>1365</v>
       </c>
       <c r="P5">
-        <v>616.27</v>
+        <v>8739</v>
       </c>
       <c r="Q5" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
@@ -16791,7 +16785,7 @@
         <v>2.69</v>
       </c>
       <c r="M6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N6">
         <v>62659.2</v>
@@ -16803,18 +16797,18 @@
         <v>22.45</v>
       </c>
       <c r="Q6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B7" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D7" t="s">
         <v>147</v>
@@ -16856,18 +16850,18 @@
         <v>805.05</v>
       </c>
       <c r="Q7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C8" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
@@ -16876,7 +16870,7 @@
         <v>156</v>
       </c>
       <c r="F8">
-        <v>190.52</v>
+        <v>195.69</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -16897,7 +16891,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N8">
         <v>60416.4</v>
@@ -16909,15 +16903,15 @@
         <v>2621</v>
       </c>
       <c r="Q8" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B9" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C9" t="s">
         <v>39</v>
@@ -16929,7 +16923,7 @@
         <v>156</v>
       </c>
       <c r="F9">
-        <v>190.07</v>
+        <v>195.23</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -16950,7 +16944,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N9">
         <v>59860</v>
@@ -16962,18 +16956,18 @@
         <v>5896.21</v>
       </c>
       <c r="Q9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D10" t="s">
         <v>147</v>
@@ -17003,7 +16997,7 @@
         <v>9.59</v>
       </c>
       <c r="M10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N10">
         <v>61938</v>
@@ -17015,15 +17009,15 @@
         <v>10168.16</v>
       </c>
       <c r="Q10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C11" t="s">
         <v>39</v>
@@ -17068,15 +17062,15 @@
         <v>175.16</v>
       </c>
       <c r="Q11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B12" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C12" t="s">
         <v>39</v>
@@ -17109,7 +17103,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N12">
         <v>61422</v>
@@ -17121,18 +17115,18 @@
         <v>5031.53</v>
       </c>
       <c r="Q12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B13" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C13" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D13" t="s">
         <v>147</v>
@@ -17174,15 +17168,15 @@
         <v>795.05</v>
       </c>
       <c r="Q13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B14" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C14" t="s">
         <v>39</v>
@@ -17215,7 +17209,7 @@
         <v>5.91</v>
       </c>
       <c r="M14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N14">
         <v>49092</v>
@@ -17227,15 +17221,15 @@
         <v>16002</v>
       </c>
       <c r="Q14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B15" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C15" t="s">
         <v>39</v>
@@ -17280,15 +17274,15 @@
         <v>150.3</v>
       </c>
       <c r="Q15" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B16" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -17333,7 +17327,7 @@
         <v>806.35</v>
       </c>
       <c r="Q16" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -17365,78 +17359,78 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B2" t="s">
         <v>178</v>
       </c>
       <c r="C2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D2" t="s">
         <v>394</v>
-      </c>
-      <c r="D2" t="s">
-        <v>395</v>
       </c>
       <c r="E2" t="s">
         <v>178</v>
       </c>
       <c r="G2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I2" t="s">
         <v>156</v>
@@ -17463,18 +17457,18 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B3" t="s">
         <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D3" t="s">
         <v>39</v>
@@ -17483,10 +17477,10 @@
         <v>178</v>
       </c>
       <c r="G3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I3" t="s">
         <v>156</v>
@@ -17513,12 +17507,12 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B4" t="s">
         <v>178</v>
@@ -17527,16 +17521,16 @@
         <v>206</v>
       </c>
       <c r="D4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E4" t="s">
         <v>178</v>
       </c>
       <c r="G4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I4" t="s">
         <v>156</v>
@@ -17563,12 +17557,12 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B5" t="s">
         <v>178</v>
@@ -17586,10 +17580,10 @@
         <v>622.5499877929688</v>
       </c>
       <c r="G5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I5" t="s">
         <v>156</v>
@@ -17616,33 +17610,33 @@
         <v>1</v>
       </c>
       <c r="Q5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C6" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D6" t="s">
         <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F6">
         <v>637.9000244140625</v>
       </c>
       <c r="G6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I6" t="s">
         <v>156</v>
@@ -17669,33 +17663,33 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C7" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F7">
         <v>814.9000244140625</v>
       </c>
       <c r="G7" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I7" t="s">
         <v>156</v>
@@ -17722,33 +17716,33 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C8" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D8" t="s">
         <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F8">
         <v>637.9000244140625</v>
       </c>
       <c r="G8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I8" t="s">
         <v>156</v>
@@ -17775,33 +17769,33 @@
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C9" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F9">
         <v>814.9000244140625</v>
       </c>
       <c r="G9" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I9" t="s">
         <v>156</v>
@@ -17828,12 +17822,12 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B10" t="s">
         <v>178</v>
@@ -17851,10 +17845,10 @@
         <v>863.5</v>
       </c>
       <c r="G10" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I10" t="s">
         <v>156</v>
@@ -17881,21 +17875,21 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B11" t="s">
         <v>178</v>
       </c>
       <c r="C11" t="s">
+        <v>393</v>
+      </c>
+      <c r="D11" t="s">
         <v>394</v>
-      </c>
-      <c r="D11" t="s">
-        <v>395</v>
       </c>
       <c r="E11" t="s">
         <v>178</v>
@@ -17904,10 +17898,10 @@
         <v>8782.5</v>
       </c>
       <c r="G11" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H11" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I11" t="s">
         <v>156</v>
@@ -17934,18 +17928,18 @@
         <v>1</v>
       </c>
       <c r="Q11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B12" t="s">
         <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D12" t="s">
         <v>39</v>
@@ -17957,10 +17951,10 @@
         <v>16326</v>
       </c>
       <c r="G12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I12" t="s">
         <v>156</v>
@@ -17987,18 +17981,18 @@
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B13" t="s">
         <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D13" t="s">
         <v>39</v>
@@ -18010,10 +18004,10 @@
         <v>23.700000762939453</v>
       </c>
       <c r="G13" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H13" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I13" t="s">
         <v>156</v>
@@ -18040,21 +18034,21 @@
         <v>1</v>
       </c>
       <c r="Q13" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B14" t="s">
         <v>147</v>
       </c>
       <c r="C14" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E14" t="s">
         <v>147</v>
@@ -18063,10 +18057,10 @@
         <v>813.2000122070312</v>
       </c>
       <c r="G14" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I14" t="s">
         <v>156</v>
@@ -18093,21 +18087,21 @@
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B15" t="s">
         <v>147</v>
       </c>
       <c r="C15" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E15" t="s">
         <v>147</v>
@@ -18116,10 +18110,10 @@
         <v>806.7000122070312</v>
       </c>
       <c r="G15" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H15" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I15" t="s">
         <v>156</v>
@@ -18146,21 +18140,21 @@
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B16" t="s">
         <v>178</v>
       </c>
       <c r="C16" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E16" t="s">
         <v>178</v>
@@ -18169,10 +18163,10 @@
         <v>1378.300048828125</v>
       </c>
       <c r="G16" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H16" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I16" t="s">
         <v>156</v>
@@ -18199,18 +18193,18 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B17" t="s">
         <v>178</v>
       </c>
       <c r="C17" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D17" t="s">
         <v>39</v>
@@ -18222,10 +18216,10 @@
         <v>56.9900016784668</v>
       </c>
       <c r="G17" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H17" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I17" t="s">
         <v>156</v>
@@ -18252,18 +18246,18 @@
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B18" t="s">
         <v>178</v>
       </c>
       <c r="C18" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D18" t="s">
         <v>39</v>
@@ -18275,10 +18269,10 @@
         <v>121</v>
       </c>
       <c r="G18" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H18" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I18" t="s">
         <v>156</v>
@@ -18305,18 +18299,18 @@
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B19" t="s">
         <v>178</v>
       </c>
       <c r="C19" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D19" t="s">
         <v>39</v>
@@ -18328,10 +18322,10 @@
         <v>5024</v>
       </c>
       <c r="G19" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H19" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I19" t="s">
         <v>156</v>
@@ -18358,18 +18352,18 @@
         <v>1</v>
       </c>
       <c r="Q19" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B20" t="s">
         <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D20" t="s">
         <v>39</v>
@@ -18381,10 +18375,10 @@
         <v>156.35000610351562</v>
       </c>
       <c r="G20" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I20" t="s">
         <v>156</v>
@@ -18411,18 +18405,18 @@
         <v>1</v>
       </c>
       <c r="Q20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B21" t="s">
         <v>178</v>
       </c>
       <c r="C21" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D21" t="s">
         <v>39</v>
@@ -18434,10 +18428,10 @@
         <v>422.45001220703125</v>
       </c>
       <c r="G21" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H21" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I21" t="s">
         <v>156</v>
@@ -18464,21 +18458,21 @@
         <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B22" t="s">
         <v>178</v>
       </c>
       <c r="C22" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D22" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E22" t="s">
         <v>178</v>
@@ -18487,10 +18481,10 @@
         <v>1378.300048828125</v>
       </c>
       <c r="G22" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H22" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I22" t="s">
         <v>156</v>
@@ -18517,18 +18511,18 @@
         <v>1</v>
       </c>
       <c r="Q22" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B23" t="s">
         <v>178</v>
       </c>
       <c r="C23" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D23" t="s">
         <v>39</v>
@@ -18540,10 +18534,10 @@
         <v>56.9900016784668</v>
       </c>
       <c r="G23" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H23" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I23" t="s">
         <v>156</v>
@@ -18570,18 +18564,18 @@
         <v>1</v>
       </c>
       <c r="Q23" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B24" t="s">
         <v>178</v>
       </c>
       <c r="C24" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D24" t="s">
         <v>39</v>
@@ -18593,10 +18587,10 @@
         <v>121</v>
       </c>
       <c r="G24" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H24" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I24" t="s">
         <v>156</v>
@@ -18623,18 +18617,18 @@
         <v>1</v>
       </c>
       <c r="Q24" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B25" t="s">
         <v>178</v>
       </c>
       <c r="C25" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D25" t="s">
         <v>39</v>
@@ -18646,10 +18640,10 @@
         <v>5024</v>
       </c>
       <c r="G25" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H25" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I25" t="s">
         <v>156</v>
@@ -18676,18 +18670,18 @@
         <v>1</v>
       </c>
       <c r="Q25" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B26" t="s">
         <v>178</v>
       </c>
       <c r="C26" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D26" t="s">
         <v>39</v>
@@ -18699,10 +18693,10 @@
         <v>156.35000610351562</v>
       </c>
       <c r="G26" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H26" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I26" t="s">
         <v>156</v>
@@ -18729,18 +18723,18 @@
         <v>1</v>
       </c>
       <c r="Q26" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B27" t="s">
         <v>178</v>
       </c>
       <c r="C27" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D27" t="s">
         <v>39</v>
@@ -18752,10 +18746,10 @@
         <v>422.45001220703125</v>
       </c>
       <c r="G27" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H27" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I27" t="s">
         <v>156</v>
@@ -18782,18 +18776,18 @@
         <v>1</v>
       </c>
       <c r="Q27" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B28" t="s">
         <v>178</v>
       </c>
       <c r="C28" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D28" t="s">
         <v>39</v>
@@ -18805,10 +18799,10 @@
         <v>179.52000427246094</v>
       </c>
       <c r="G28" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H28" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I28" t="s">
         <v>156</v>
@@ -18835,21 +18829,21 @@
         <v>1</v>
       </c>
       <c r="Q28" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B29" t="s">
         <v>147</v>
       </c>
       <c r="C29" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D29" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E29" t="s">
         <v>147</v>
@@ -18858,10 +18852,10 @@
         <v>10166</v>
       </c>
       <c r="G29" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H29" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I29" t="s">
         <v>156</v>
@@ -18888,18 +18882,18 @@
         <v>1</v>
       </c>
       <c r="Q29" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B30" t="s">
         <v>147</v>
       </c>
       <c r="C30" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D30" t="s">
         <v>39</v>
@@ -18911,10 +18905,10 @@
         <v>527.9000244140625</v>
       </c>
       <c r="G30" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H30" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I30" t="s">
         <v>156</v>
@@ -18941,21 +18935,21 @@
         <v>1</v>
       </c>
       <c r="Q30" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B31" t="s">
         <v>147</v>
       </c>
       <c r="C31" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D31" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E31" t="s">
         <v>147</v>
@@ -18964,10 +18958,10 @@
         <v>4442.39990234375</v>
       </c>
       <c r="G31" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H31" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I31" t="s">
         <v>156</v>
@@ -18994,18 +18988,18 @@
         <v>1</v>
       </c>
       <c r="Q31" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B32" t="s">
         <v>147</v>
       </c>
       <c r="C32" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D32" t="s">
         <v>39</v>
@@ -19017,10 +19011,10 @@
         <v>23.700000762939453</v>
       </c>
       <c r="G32" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H32" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I32" t="s">
         <v>156</v>
@@ -19047,21 +19041,21 @@
         <v>1</v>
       </c>
       <c r="Q32" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B33" t="s">
         <v>147</v>
       </c>
       <c r="C33" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D33" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E33" t="s">
         <v>147</v>
@@ -19070,10 +19064,10 @@
         <v>813.2000122070312</v>
       </c>
       <c r="G33" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H33" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I33" t="s">
         <v>156</v>
@@ -19100,18 +19094,18 @@
         <v>1</v>
       </c>
       <c r="Q33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B34" t="s">
         <v>147</v>
       </c>
       <c r="C34" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D34" t="s">
         <v>39</v>
@@ -19123,10 +19117,10 @@
         <v>739.3499755859375</v>
       </c>
       <c r="G34" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H34" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I34" t="s">
         <v>156</v>
@@ -19153,21 +19147,21 @@
         <v>1</v>
       </c>
       <c r="Q34" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B35" t="s">
         <v>147</v>
       </c>
       <c r="C35" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D35" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E35" t="s">
         <v>147</v>
@@ -19176,10 +19170,10 @@
         <v>806.7000122070312</v>
       </c>
       <c r="G35" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H35" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I35" t="s">
         <v>156</v>
@@ -19206,18 +19200,18 @@
         <v>1</v>
       </c>
       <c r="Q35" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B36" t="s">
         <v>147</v>
       </c>
       <c r="C36" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D36" t="s">
         <v>39</v>
@@ -19229,10 +19223,10 @@
         <v>527.9000244140625</v>
       </c>
       <c r="G36" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H36" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I36" t="s">
         <v>156</v>
@@ -19259,21 +19253,21 @@
         <v>1</v>
       </c>
       <c r="Q36" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B37" t="s">
         <v>147</v>
       </c>
       <c r="C37" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D37" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E37" t="s">
         <v>147</v>
@@ -19282,10 +19276,10 @@
         <v>4442.39990234375</v>
       </c>
       <c r="G37" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H37" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I37" t="s">
         <v>156</v>
@@ -19312,18 +19306,18 @@
         <v>1</v>
       </c>
       <c r="Q37" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B38" t="s">
         <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D38" t="s">
         <v>39</v>
@@ -19335,10 +19329,10 @@
         <v>739.3499755859375</v>
       </c>
       <c r="G38" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H38" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I38" t="s">
         <v>156</v>
@@ -19365,21 +19359,21 @@
         <v>1</v>
       </c>
       <c r="Q38" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B39" t="s">
         <v>148</v>
       </c>
       <c r="C39" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D39" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E39" t="s">
         <v>148</v>
@@ -19388,16 +19382,16 @@
         <v>1866.0999755859375</v>
       </c>
       <c r="G39" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H39" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I39" t="s">
         <v>156</v>
       </c>
       <c r="J39">
-        <v>210.96</v>
+        <v>216.12</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -19418,21 +19412,21 @@
         <v>1</v>
       </c>
       <c r="Q39" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B40" t="s">
         <v>148</v>
       </c>
       <c r="C40" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D40" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
@@ -19441,16 +19435,16 @@
         <v>417.95001220703125</v>
       </c>
       <c r="G40" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H40" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I40" t="s">
         <v>156</v>
       </c>
       <c r="J40">
-        <v>206.63</v>
+        <v>211.8</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -19471,18 +19465,18 @@
         <v>1</v>
       </c>
       <c r="Q40" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B41" t="s">
         <v>148</v>
       </c>
       <c r="C41" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D41" t="s">
         <v>39</v>
@@ -19494,10 +19488,10 @@
         <v>625.6500244140625</v>
       </c>
       <c r="G41" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H41" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I41" t="s">
         <v>156</v>
@@ -19524,21 +19518,21 @@
         <v>1</v>
       </c>
       <c r="Q41" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B42" t="s">
         <v>148</v>
       </c>
       <c r="C42" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D42" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E42" t="s">
         <v>148</v>
@@ -19547,16 +19541,16 @@
         <v>2746.199951171875</v>
       </c>
       <c r="G42" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H42" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I42" t="s">
         <v>156</v>
       </c>
       <c r="J42">
-        <v>190.52</v>
+        <v>195.69</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -19577,18 +19571,18 @@
         <v>1</v>
       </c>
       <c r="Q42" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B43" t="s">
         <v>148</v>
       </c>
       <c r="C43" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D43" t="s">
         <v>39</v>
@@ -19600,16 +19594,16 @@
         <v>5986</v>
       </c>
       <c r="G43" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H43" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I43" t="s">
         <v>156</v>
       </c>
       <c r="J43">
-        <v>190.07</v>
+        <v>195.23</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -19630,18 +19624,18 @@
         <v>1</v>
       </c>
       <c r="Q43" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B44" t="s">
         <v>148</v>
       </c>
       <c r="C44" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D44" t="s">
         <v>39</v>
@@ -19653,10 +19647,10 @@
         <v>5118.5</v>
       </c>
       <c r="G44" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H44" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I44" t="s">
         <v>156</v>
@@ -19683,18 +19677,18 @@
         <v>1</v>
       </c>
       <c r="Q44" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B45" t="s">
         <v>148</v>
       </c>
       <c r="C45" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D45" t="s">
         <v>39</v>
@@ -19706,10 +19700,10 @@
         <v>156.60000610351562</v>
       </c>
       <c r="G45" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H45" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I45" t="s">
         <v>156</v>
@@ -19736,18 +19730,18 @@
         <v>1</v>
       </c>
       <c r="Q45" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s">
         <v>148</v>
       </c>
       <c r="C46" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D46" t="s">
         <v>39</v>
@@ -19759,10 +19753,10 @@
         <v>841.2999877929688</v>
       </c>
       <c r="G46" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H46" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I46" t="s">
         <v>156</v>
@@ -19789,7 +19783,7 @@
         <v>1</v>
       </c>
       <c r="Q46" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -19813,30 +19807,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -19848,7 +19842,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3781" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3733" uniqueCount="452">
   <si>
     <t>Metric</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T03:39:00.698Z</t>
+    <t>2026-07-16T03:46:28.273Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -483,504 +483,504 @@
     <t/>
   </si>
   <si>
+    <t>Above</t>
+  </si>
+  <si>
+    <t>2026-07-15 09:17 IST ENTRY_BUY BUY 108 @ 921.25; turnover 99495; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. TREND RIDE: weekly/daily leadership and price structure remain healthy; trail the stop instead of cutting the winner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASS; </t>
+  </si>
+  <si>
+    <t>Breakout buy</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>2/5</t>
+  </si>
+  <si>
+    <t>3/10 (GTF C)</t>
+  </si>
+  <si>
+    <t>PROXY_UNVALIDATED</t>
+  </si>
+  <si>
+    <t>Clear</t>
+  </si>
+  <si>
+    <t>NIFTY 500 proxy is BULLISH; broad index support is positive.</t>
+  </si>
+  <si>
+    <t>Not present in NSE F&amp;O lot-size master; treat as cash-equity only.</t>
+  </si>
+  <si>
+    <t>NSE option-chain snapshot unavailable; mark this as data gap, not as bearish.</t>
+  </si>
+  <si>
+    <t>2/5 commodity/currency proxies are bullish; 2 bearish.</t>
+  </si>
+  <si>
+    <t>19/30</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Price-action base and higher-low structure; Bollinger trend/range context; Volume participation; MACD and OBV confirmation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Retracement/pullback buy setup; GTF demand/supply confluence; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Operator delivery confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Index option-chain positioning; News/event context</t>
+  </si>
+  <si>
+    <t>Intraday tick scalping; Broker-only live Greeks/order-book depth; Pair-trading spread execution; Short-selling execution; Options premium/straddle/strangle execution; Manual charting/terminal workflow</t>
+  </si>
+  <si>
+    <t>68.57% (120/175)</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>55D high retest</t>
+  </si>
+  <si>
+    <t>previous-high confirmation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 71.91 is above 50. Daily RSI 66.78 is above 50. Weekly RS 84.3% is above 0. Daily long RS55 36.1% is above 0. Daily short RS21 5.7% is above 0. Daily close 904.45 is above Supertrend(10, 3) 757.33. Entry style: Breakout buy. Price action strength: close crossed 55-day high 889.95. 52-week breakout: close crossed prior 52-week high 889.95. 20-day base breakout above 889.95 with a higher-low structure. Volume shocker: latest volume is 3.69x the 50-day average. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: close is above the middle band 824.65 with bandwidth 12.27%. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 5.20% of price. Liquidity strength: 20-day average turnover is Rs 136854458.94. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Delivery neutral: traded quantity 6.12x, delivery 3.57x, delivery percentage 27.61%. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Sector breadth strong: My List has 120/175 stocks (68.57%) passing daily strength. Institutional concept coverage: 19/30 applicable video-derived buckets are strong. Sector breadth strong: My List has 117/175 stocks (66.86%) passing daily strength. Institutional concept coverage: 19/30 applicable video-derived buckets are strong. Sector breadth strong: My List has 120/175 stocks (68.57%) passing daily strength. Institutional concept coverage: 19/30 applicable video-derived buckets are strong. Sector breadth strong: My List has 120/175 stocks (68.57%) passing daily strength. Institutional concept coverage: 19/30 applicable video-derived buckets are strong. Sector breadth strong: My List has 120/175 stocks (68.57%) passing daily strength. Institutional concept coverage: 19/30 applicable video-derived buckets are strong. AI evidence review (+1): Positive growth in income and margins. AI risk flag: positive growth. AI risk flag: improving margins. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 225.14; planned allocation Rs 99489.5, quantity 110, initial stop 832.09, planned risk Rs 7959.6. Closing signal dated 2026-07-14; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>All NSE Market</t>
+  </si>
+  <si>
+    <t>MAYURUNIQ</t>
+  </si>
+  <si>
+    <t>Mayur Uniquoters Ltd</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-14 09:17 IST ENTRY_BUY BUY 68 @ 853; turnover 58004; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
+  </si>
+  <si>
+    <t>daily RS21 below zero daily RSI below 50 setup grade WATCH ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. WAIT/WATCH: 1/3 completed deterioration closes confirmed.</t>
+  </si>
+  <si>
+    <t>Trend continuation buy</t>
+  </si>
+  <si>
+    <t>5/10 (GTF B)</t>
+  </si>
+  <si>
+    <t>weekly RBR 717-755; fresh; 7/7</t>
+  </si>
+  <si>
+    <t>1/5 commodity/currency proxies are bullish; 3 bearish.</t>
+  </si>
+  <si>
+    <t>16/30</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; GTF demand/supply confluence; Bollinger trend/range context; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Price-action base and higher-low structure; Retracement/pullback buy setup; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Volume participation; MACD and OBV confirmation; Operator delivery confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Sector breadth; Index option-chain positioning; News/event context</t>
+  </si>
+  <si>
+    <t>29.09% (510/1753)</t>
+  </si>
+  <si>
+    <t>Supertrend</t>
+  </si>
+  <si>
+    <t>previous-high confirmation + bullish engulfing</t>
+  </si>
+  <si>
+    <t>Weekly RSI 69.81 is above 50. Daily RSI 61.00 is above 50. Weekly RS 48.1% is above 0. Daily long RS55 47.4% is above 0. Daily short RS21 4.4% is above 0. Daily close 855.15 is above Supertrend(10, 3) 780.78. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 907.00. Momentum confirmation: MACD is not fully confirmed; OBV is rising. Retracement watch: pullback depth 5.72% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: close is above the middle band 834.63 with bandwidth 14.17%. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.11% of price. Liquidity strength: 20-day average turnover is Rs 110102528.58. Market regime supports longs: NIFTY 500 bullish/healthy. Weekly demand RBR 717-755: fresh, score 7/7, achievement 4R, two_exciting_candles. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Operator/delivery context: Delivery neutral: traded quantity 0.90x, delivery 0.99x, delivery percentage 55.11%. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 16/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 191.09; planned allocation Rs 58150.2, quantity 68, initial stop 805.6, planned risk Rs 3369.4. Closing signal dated 2026-07-13; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>SANGAMIND</t>
+  </si>
+  <si>
+    <t>Sangam (India) Limited</t>
+  </si>
+  <si>
+    <t>2026-07-14 09:17 IST ENTRY_BUY BUY 112 @ 649.15; turnover 72704.8; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
+  </si>
+  <si>
+    <t>ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid.</t>
+  </si>
+  <si>
+    <t>3/5</t>
+  </si>
+  <si>
+    <t>0/5 commodity/currency proxies are bullish; 2 bearish.</t>
+  </si>
+  <si>
+    <t>20/30</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Price-action base and higher-low structure; Bollinger trend/range context; Volume participation; MACD and OBV confirmation; Operator delivery confirmation; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>Retracement/pullback buy setup; GTF demand/supply confluence; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>28.82% (500/1735)</t>
+  </si>
+  <si>
+    <t>50-DMA</t>
+  </si>
+  <si>
+    <t>Weekly RSI 69.24 is above 50. Daily RSI 78.99 is above 50. Weekly RS 20.1% is above 0. Daily long RS55 17.3% is above 0. Daily short RS21 11.1% is above 0. Daily close 622.55 is above Supertrend(10, 3) 521.71. Entry style: Breakout buy. Price action strength: close crossed 55-day high 574.90. 52-week breakout: close crossed prior 52-week high 576.95. 20-day base breakout above 574.90 with a higher-low structure. Volume shocker: latest volume is 90.28x the 50-day average. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: close is above the middle band 547.68 with bandwidth 14.29%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 3.77% of price. Liquidity strength: 20-day average turnover is Rs 132125809.42. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 0/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Operator accumulation confirmed: price 11.42%, traded quantity 69.12x, delivery 12.84x, close above average price 620.33. Institutional confluence score 3/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 20/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 195.78; planned allocation Rs 72838.35, quantity 117, initial stop 572.75, planned risk Rs 5826.6. Closing signal dated 2026-07-13; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>All NSE Market, Default Nifty 500, My Custom List</t>
+  </si>
+  <si>
+    <t>NIVABUPA</t>
+  </si>
+  <si>
+    <t>2026-07-14 09:17 IST ENTRY_BUY BUY 5 @ 88.49; turnover 442.45; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
+  </si>
+  <si>
+    <t>Momentum continuation buy</t>
+  </si>
+  <si>
+    <t>daily DBR 84.13-85.12; tests 2; 4/7</t>
+  </si>
+  <si>
+    <t>weekly DBR 76.36-84.4; tests 2; 3/7</t>
+  </si>
+  <si>
+    <t>17/30</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; MACD and OBV confirmation; Operator delivery confirmation; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>Price-action base and higher-low structure; Retracement/pullback buy setup; GTF demand/supply confluence; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Bollinger trend/range context; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
+  </si>
+  <si>
+    <t>70.29% (123/175)</t>
+  </si>
+  <si>
+    <t>No bullish confirmation pattern</t>
+  </si>
+  <si>
+    <t>Weekly RSI 61.25 is above 50. Daily RSI 63.34 is above 50. Weekly RS 13.3% is above 0. Daily long RS55 10.5% is above 0. Daily short RS21 1.6% is above 0. Daily close 88.09 is above Supertrend(10, 3) 81.07. Entry style: Momentum continuation buy. Price action strength: close is within 15% of 52-week high 92.90. Volume shocker: latest volume is 2.77x the 50-day average. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: bandwidth 4.85% indicates a range-bound/compressed phase. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Volatility is controlled: ATR(14) is 2.54% of price. Liquidity strength: 20-day average turnover is Rs 190458904.28. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly sideways. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 0/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Operator accumulation confirmed: price 1.83%, traded quantity 6.96x, delivery 8.40x, close above average price 87.40. Institutional confluence score 3/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Sector breadth strong: My List has 123/175 stocks (70.29%) passing daily strength. Institutional concept coverage: 17/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 180.45; planned allocation Rs 440.45, quantity 5, initial stop 84.5, planned risk Rs 17.95. Closing signal dated 2026-07-13; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>GRINDWELL</t>
+  </si>
+  <si>
+    <t>Grindwell Norton Limited</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-13 09:17 IST ENTRY_BUY BUY 49 @ 2048.2; turnover 100361.8; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-13 09:15 IST PARTIAL_EXIT SELL 24 @ 2004.5; turnover 48108; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -1048.8 | 2026-07-14 09:17 IST PARTIAL_EXIT SELL 12 @ 2010.3; turnover 24123.6; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -454.8 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 6 @ 2038.6; turnover 12231.6; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -57.6</t>
+  </si>
+  <si>
+    <t>daily RS21 below zero close below Supertrend setup grade WATCH GTF confirms less than 2R room ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. WAIT/WATCH: 1/3 completed deterioration closes confirmed. GTF is secondary context only and cannot trigger an exit.</t>
+  </si>
+  <si>
+    <t>2/4</t>
+  </si>
+  <si>
+    <t>4/9 (GTF C)</t>
+  </si>
+  <si>
+    <t>daily DBR 1886.4-1932.3; fresh; 7/7</t>
+  </si>
+  <si>
+    <t>daily DBD 2244-2146.8; fresh; 7/7</t>
+  </si>
+  <si>
+    <t>0.49R</t>
+  </si>
+  <si>
+    <t>15/26</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>28.25% (495/1752)</t>
+  </si>
+  <si>
+    <t>Weekly RSI 63.02 is above 50. Daily RSI 52.01 is above 50. Weekly RS 25.7% is above 0. Daily long RS55 22.2% is above 0. Daily short RS21 2.9% is above 0. Daily close 2058.60 is above Supertrend(10, 3) 2015.38. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 2294.40. Retracement watch: pullback depth 10.28% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: close is below the middle band 2106.53 with bandwidth 12.00%. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 2.10% above daily Supertrend. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 3.57% of price. Liquidity strength: 20-day average turnover is Rs 210232154.56. Market regime supports longs: NIFTY 500 bullish/healthy. Daily demand DBR 1886.4-1932.3: fresh, score 7/7, achievement 7.89R, significant_gap. GTF 50-SMA slope: daily up, weekly up. Opposing daily supply 2146.8-2244; estimated room 0.49R. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next actual market session using the 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 15/26 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 170.76; planned allocation Rs 98812.8, quantity 48, initial stop 2015.38, planned risk Rs 2074.56. Closing signal dated 2026-07-10; buy fill must come from the next actual market session exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>INGERRAND</t>
+  </si>
+  <si>
+    <t>Ingersoll Rand (India) Limited</t>
+  </si>
+  <si>
+    <t>2026-07-13 09:17 IST ENTRY_BUY BUY 22 @ 4421.9; turnover 97281.8; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
+  </si>
+  <si>
+    <t>daily RS21 below zero setup grade WATCH ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. TREND RIDE: weekly/daily leadership and price structure remain healthy; trail the stop instead of cutting the winner. WAIT/WATCH: one primary weakness is not enough for a partial exit.</t>
+  </si>
+  <si>
+    <t>Retracement buy near 50-DMA</t>
+  </si>
+  <si>
+    <t>3/9 (GTF C)</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
+  </si>
+  <si>
+    <t>Weekly RSI 57.94 is above 50. Daily RSI 53.75 is above 50. Weekly RS 19.4% is above 0. Daily long RS55 2.1% is above 0. Daily short RS21 5.4% is above 0. Daily close 4452.00 is above Supertrend(10, 3) 4220.30. Entry style: Retracement buy near 50-DMA. Price action strength: close is within 15% of 52-week high 4756.20. Retracement buy: price pulled back 6.40% from the 55-day high and reclaimed near 50-DMA 4334.98; support distance is 2.63%. Retracement confirmation: pullback volume ratio 0.47 and reclaim volume ratio 0.65 with candle close location 61.83%. Bollinger context: close is below the middle band 4487.32 with bandwidth 10.02%. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 5.20% above daily Supertrend. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 2.90% of price. Liquidity strength: 20-day average turnover is Rs 79382544.10. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next actual market session using the 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 15/26 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 167.02; planned allocation Rs 97944, quantity 22, initial stop 4319.5, planned risk Rs 2915. Closing signal dated 2026-07-10; buy fill must come from the next actual market session exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>RAIN</t>
+  </si>
+  <si>
+    <t>Rain Industries Limited</t>
+  </si>
+  <si>
+    <t>2026-07-13 09:17 IST ENTRY_BUY BUY 291 @ 214.01; turnover 62276.91; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 145 @ 208.03; turnover 30164.35; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -867.1</t>
+  </si>
+  <si>
+    <t>GTF confirms less than 2R room ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. TREND RIDE: weekly/daily leadership and price structure remain healthy; trail the stop instead of cutting the winner. GTF is secondary context only and cannot trigger an exit.</t>
+  </si>
+  <si>
+    <t>14/26</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Bollinger trend/range context; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Volume participation; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 71.58 is above 50. Daily RSI 64.68 is above 50. Weekly RS 35.7% is above 0. Daily long RS55 56.1% is above 0. Daily short RS21 0.7% is above 0. Daily close 207.05 is above Supertrend(10, 3) 178.77. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 214.17. Retracement watch: pullback depth 3.32% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: close is above the middle band 192.70 with bandwidth 16.23%. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Volatility is controlled: ATR(14) is 4.35% of price. Liquidity strength: 20-day average turnover is Rs 991729867.12. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next actual market session using the 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 14/26 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 179.24; planned allocation Rs 99798.1, quantity 482, initial stop 196.45, planned risk Rs 5109.2. Closing signal dated 2026-07-10; buy fill must come from the next actual market session exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>CRAFTSMAN</t>
+  </si>
+  <si>
+    <t>Craftsman Automation Limited</t>
+  </si>
+  <si>
+    <t>2026-07-13 09:17 IST ENTRY_BUY BUY 10 @ 9284; turnover 92840; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 5 @ 9251.5; turnover 46257.5; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -162.5</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>0/9 (GTF neutral)</t>
+  </si>
+  <si>
+    <t>daily RBR 8613.5-8978; tests 4; 3/7</t>
+  </si>
+  <si>
+    <t>weekly DBR 8242.5-9074; tests 2; 4/7</t>
+  </si>
+  <si>
+    <t>daily RBD 9528-9402.5; fresh; 7/7</t>
+  </si>
+  <si>
+    <t>14/29</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Price-action base and higher-low structure; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; MACD and OBV confirmation; Operator delivery confirmation; Sector breadth; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>42.11% (16/38)</t>
+  </si>
+  <si>
+    <t>Weekly RSI 62.77 is above 50. Daily RSI 55.38 is above 50. Weekly RS 20.2% is above 0. Daily long RS55 17.2% is above 0. Daily short RS21 0.2% is above 0. Daily close 9301.00 is above Supertrend(10, 3) 8728.10. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 9938.00. Momentum confirmation: MACD is not fully confirmed; OBV is rising. Retracement watch: pullback depth 6.41% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: bandwidth 7.09% indicates a range-bound/compressed phase. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.16% above daily Supertrend. Volatility is controlled: ATR(14) is 2.80% of price. Liquidity strength: 20-day average turnover is Rs 787112608.80. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. Opposing daily supply 9402.5-9528; blocker/early-risk flag. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Operator/delivery context: Delivery neutral: traded quantity 0.33x, delivery 0.27x, delivery percentage 49.09%. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 14/29 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 131.92; planned allocation Rs 93010, quantity 10, initial stop 8955.5, planned risk Rs 3455. Closing signal dated 2026-07-10; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>Best only (A+/A)</t>
+  </si>
+  <si>
+    <t>KPIL</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 73 @ 1351.4; turnover 98652.2; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-14 09:17 IST PARTIAL_EXIT SELL 36 @ 1333.5; turnover 48006; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -644.4 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 18 @ 1305.2; turnover 23493.6; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -831.6</t>
+  </si>
+  <si>
+    <t>daily RS21 below zero daily RSI below 50 close below Supertrend close below 50-DMA setup grade WATCH ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. WAIT/WATCH: 1/3 completed deterioration closes confirmed.</t>
+  </si>
+  <si>
+    <t>16/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Index option-chain positioning</t>
+  </si>
+  <si>
+    <t>Intraday tick scalping; Broker-only live Greeks/order-book depth</t>
+  </si>
+  <si>
+    <t>64.29% (90/140)</t>
+  </si>
+  <si>
+    <t>bullish engulfing</t>
+  </si>
+  <si>
+    <t>Weekly RSI 66.89 is above 50. Daily RSI 50.91 is above 50. Weekly RS 27.5% is above 0. Daily long RS55 5.5% is above 0. Daily short RS21 2.1% is above 0. Daily close 1349.90 is above Supertrend(10, 3) 1313.78. Price action strength: close is within 15% of 52-week high 1479.60. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 2.68% above daily Supertrend. Price confirmation: bullish engulfing is present. Volatility is controlled: ATR(14) is 3.04% of price. Liquidity strength: 20-day average turnover is Rs 511253745.19. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 16/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>SIS</t>
+  </si>
+  <si>
+    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 228 @ 437.05; turnover 99647.4; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-13 09:15 IST PARTIAL_EXIT SELL 114 @ 432.65; turnover 49322.1; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -501.6</t>
+  </si>
+  <si>
+    <t>2026-07-14T03:32:23.269Z: SANGAMIND; Optional rotation cancelled before selling SIS: Rotation requires 2 distinct valid ENTRY closes; candidate has 0.</t>
+  </si>
+  <si>
+    <t>14/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 72.14 is above 50. Daily RSI 61.56 is above 50. Weekly RS 25.5% is above 0. Daily long RS55 29.2% is above 0. Daily short RS21 1.5% is above 0. Daily close 437.80 is above Supertrend(10, 3) 397.84. Price action strength: close is within 15% of 52-week high 480.95. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Volatility is controlled: ATR(14) is 3.42% of price. Liquidity strength: 20-day average turnover is Rs 261311772.23. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 14/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>PGHL</t>
+  </si>
+  <si>
+    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 15 @ 6621.5; turnover 99322.5; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
+  </si>
+  <si>
+    <t>17/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 73.92 is above 50. Daily RSI 70.18 is above 50. Weekly RS 23.0% is above 0. Daily long RS55 28.3% is above 0. Daily short RS21 2.2% is above 0. Daily close 6612.00 is above Supertrend(10, 3) 6036.47. Price action strength: close is within 15% of 52-week high 6739.00. Volume shocker: latest volume is 2.02x the 50-day average. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.56% of price. Liquidity strength: 20-day average turnover is Rs 92394456.38. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 17/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 49 @ 1995.8; turnover 97794.2; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 62.41 is above 50. Daily RSI 59.04 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 9.6% is above 0. Daily short RS21 0.7% is above 0. Daily close 1993.20 is above Supertrend(10, 3) 1864.19. Price action strength: close is within 15% of 52-week high 2093.30. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.47% above daily Supertrend. Volatility is controlled: ATR(14) is 2.56% of price. Liquidity strength: 20-day average turnover is Rs 580096417.25. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 16/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>VIJAYA</t>
+  </si>
+  <si>
+    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 71 @ 1373.5; turnover 97518.5; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
+  </si>
+  <si>
+    <t>15/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 66.67 is above 50. Daily RSI 57.60 is above 50. Weekly RS 42.2% is above 0. Daily long RS55 32.3% is above 0. Daily short RS21 4.5% is above 0. Daily close 1377.80 is above Supertrend(10, 3) 1215.62. Price action strength: close is within 15% of 52-week high 1427.80. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.06% of price. Liquidity strength: 20-day average turnover is Rs 464701789.72. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>PRECOT</t>
+  </si>
+  <si>
+    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 119 @ 811; turnover 96509; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Volatility and liquidity control; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 64.67 is above 50. Daily RSI 61.84 is above 50. Weekly RS 54.7% is above 0. Daily long RS55 46.8% is above 0. Daily short RS21 15.0% is above 0. Daily close 800.45 is above Supertrend(10, 3) 673.89. Price action strength: close is within 15% of 52-week high 861.25. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.91% of price. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 14/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>PRUDENT</t>
+  </si>
+  <si>
+    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 33 @ 2986; turnover 98538; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 16 @ 2989.4; turnover 47830.4; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 54.4</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Weekly RSI 63.57 is above 50. Daily RSI 53.42 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 4.7% is above 0. Daily close 2960.00 is above Supertrend(10, 3) 2759.71. Price action strength: close is within 15% of 52-week high 3160.10. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.77% above daily Supertrend. Volatility is controlled: ATR(14) is 3.14% of price. Liquidity strength: 20-day average turnover is Rs 67973469.69. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>My Custom List</t>
+  </si>
+  <si>
+    <t>NEXUSSURGL</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>09:21 IST</t>
+  </si>
+  <si>
+    <t>09:17 market order; first actual traded candle at 09:21 IST</t>
+  </si>
+  <si>
+    <t>09:17 order / 09:21 actual fill</t>
+  </si>
+  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>2026-07-15 09:17 IST ENTRY_BUY BUY 108 @ 921.25; turnover 99495; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. TREND RIDE: weekly/daily leadership and price structure remain healthy; trail the stop instead of cutting the winner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PASS; </t>
-  </si>
-  <si>
-    <t>Breakout buy</t>
-  </si>
-  <si>
-    <t>A+</t>
-  </si>
-  <si>
-    <t>2/5</t>
-  </si>
-  <si>
-    <t>3/10 (GTF C)</t>
-  </si>
-  <si>
-    <t>PROXY_UNVALIDATED</t>
-  </si>
-  <si>
-    <t>Clear</t>
-  </si>
-  <si>
-    <t>NIFTY 500 proxy is BULLISH; broad index support is positive.</t>
-  </si>
-  <si>
-    <t>Not present in NSE F&amp;O lot-size master; treat as cash-equity only.</t>
-  </si>
-  <si>
-    <t>NSE option-chain snapshot unavailable; mark this as data gap, not as bearish.</t>
-  </si>
-  <si>
-    <t>2/5 commodity/currency proxies are bullish; 2 bearish.</t>
-  </si>
-  <si>
-    <t>19/30</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Price-action base and higher-low structure; Bollinger trend/range context; Volume participation; MACD and OBV confirmation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Retracement/pullback buy setup; GTF demand/supply confluence; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Operator delivery confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Index option-chain positioning; News/event context</t>
-  </si>
-  <si>
-    <t>Intraday tick scalping; Broker-only live Greeks/order-book depth; Pair-trading spread execution; Short-selling execution; Options premium/straddle/strangle execution; Manual charting/terminal workflow</t>
-  </si>
-  <si>
-    <t>68.57% (120/175)</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>55D high retest</t>
-  </si>
-  <si>
-    <t>previous-high confirmation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 71.91 is above 50. Daily RSI 66.78 is above 50. Weekly RS 84.3% is above 0. Daily long RS55 36.1% is above 0. Daily short RS21 5.7% is above 0. Daily close 904.45 is above Supertrend(10, 3) 757.33. Entry style: Breakout buy. Price action strength: close crossed 55-day high 889.95. 52-week breakout: close crossed prior 52-week high 889.95. 20-day base breakout above 889.95 with a higher-low structure. Volume shocker: latest volume is 3.69x the 50-day average. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: close is above the middle band 824.65 with bandwidth 12.27%. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 5.20% of price. Liquidity strength: 20-day average turnover is Rs 136854458.94. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Delivery neutral: traded quantity 6.12x, delivery 3.57x, delivery percentage 27.61%. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Sector breadth strong: My List has 120/175 stocks (68.57%) passing daily strength. Institutional concept coverage: 19/30 applicable video-derived buckets are strong. Sector breadth strong: My List has 117/175 stocks (66.86%) passing daily strength. Institutional concept coverage: 19/30 applicable video-derived buckets are strong. Sector breadth strong: My List has 120/175 stocks (68.57%) passing daily strength. Institutional concept coverage: 19/30 applicable video-derived buckets are strong. Sector breadth strong: My List has 120/175 stocks (68.57%) passing daily strength. Institutional concept coverage: 19/30 applicable video-derived buckets are strong. Sector breadth strong: My List has 120/175 stocks (68.57%) passing daily strength. Institutional concept coverage: 19/30 applicable video-derived buckets are strong. AI evidence review (+1): Positive growth in income and margins. AI risk flag: positive growth. AI risk flag: improving margins. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 225.14; planned allocation Rs 99489.5, quantity 110, initial stop 832.09, planned risk Rs 7959.6. Closing signal dated 2026-07-14; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>All NSE Market</t>
-  </si>
-  <si>
-    <t>MAYURUNIQ</t>
-  </si>
-  <si>
-    <t>Mayur Uniquoters Ltd</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-07-14 09:17 IST ENTRY_BUY BUY 68 @ 853; turnover 58004; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
-  </si>
-  <si>
-    <t>daily RS21 below zero daily RSI below 50 setup grade WATCH ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. WAIT/WATCH: 1/3 completed deterioration closes confirmed.</t>
-  </si>
-  <si>
-    <t>Trend continuation buy</t>
-  </si>
-  <si>
-    <t>5/10 (GTF B)</t>
-  </si>
-  <si>
-    <t>weekly RBR 717-755; fresh; 7/7</t>
-  </si>
-  <si>
-    <t>1/5 commodity/currency proxies are bullish; 3 bearish.</t>
-  </si>
-  <si>
-    <t>16/30</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; GTF demand/supply confluence; Bollinger trend/range context; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Price-action base and higher-low structure; Retracement/pullback buy setup; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Volume participation; MACD and OBV confirmation; Operator delivery confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Sector breadth; Index option-chain positioning; News/event context</t>
-  </si>
-  <si>
-    <t>29.09% (510/1753)</t>
-  </si>
-  <si>
-    <t>Supertrend</t>
-  </si>
-  <si>
-    <t>previous-high confirmation + bullish engulfing</t>
-  </si>
-  <si>
-    <t>Weekly RSI 69.81 is above 50. Daily RSI 61.00 is above 50. Weekly RS 48.1% is above 0. Daily long RS55 47.4% is above 0. Daily short RS21 4.4% is above 0. Daily close 855.15 is above Supertrend(10, 3) 780.78. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 907.00. Momentum confirmation: MACD is not fully confirmed; OBV is rising. Retracement watch: pullback depth 5.72% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: close is above the middle band 834.63 with bandwidth 14.17%. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.11% of price. Liquidity strength: 20-day average turnover is Rs 110102528.58. Market regime supports longs: NIFTY 500 bullish/healthy. Weekly demand RBR 717-755: fresh, score 7/7, achievement 4R, two_exciting_candles. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Operator/delivery context: Delivery neutral: traded quantity 0.90x, delivery 0.99x, delivery percentage 55.11%. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 16/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 191.09; planned allocation Rs 58150.2, quantity 68, initial stop 805.6, planned risk Rs 3369.4. Closing signal dated 2026-07-13; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>SANGAMIND</t>
-  </si>
-  <si>
-    <t>Sangam (India) Limited</t>
-  </si>
-  <si>
-    <t>2026-07-14 09:17 IST ENTRY_BUY BUY 112 @ 649.15; turnover 72704.8; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
-  </si>
-  <si>
-    <t>ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid.</t>
-  </si>
-  <si>
-    <t>3/5</t>
-  </si>
-  <si>
-    <t>0/5 commodity/currency proxies are bullish; 2 bearish.</t>
-  </si>
-  <si>
-    <t>20/30</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Price-action base and higher-low structure; Bollinger trend/range context; Volume participation; MACD and OBV confirmation; Operator delivery confirmation; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>Retracement/pullback buy setup; GTF demand/supply confluence; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>28.82% (500/1735)</t>
-  </si>
-  <si>
-    <t>50-DMA</t>
-  </si>
-  <si>
-    <t>Weekly RSI 69.24 is above 50. Daily RSI 78.99 is above 50. Weekly RS 20.1% is above 0. Daily long RS55 17.3% is above 0. Daily short RS21 11.1% is above 0. Daily close 622.55 is above Supertrend(10, 3) 521.71. Entry style: Breakout buy. Price action strength: close crossed 55-day high 574.90. 52-week breakout: close crossed prior 52-week high 576.95. 20-day base breakout above 574.90 with a higher-low structure. Volume shocker: latest volume is 90.28x the 50-day average. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: close is above the middle band 547.68 with bandwidth 14.29%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 3.77% of price. Liquidity strength: 20-day average turnover is Rs 132125809.42. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 0/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Operator accumulation confirmed: price 11.42%, traded quantity 69.12x, delivery 12.84x, close above average price 620.33. Institutional confluence score 3/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 20/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 195.78; planned allocation Rs 72838.35, quantity 117, initial stop 572.75, planned risk Rs 5826.6. Closing signal dated 2026-07-13; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>All NSE Market, Default Nifty 500, My Custom List</t>
-  </si>
-  <si>
-    <t>NIVABUPA</t>
-  </si>
-  <si>
-    <t>Above</t>
-  </si>
-  <si>
-    <t>2026-07-14 09:17 IST ENTRY_BUY BUY 5 @ 88.49; turnover 442.45; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
-  </si>
-  <si>
-    <t>Momentum continuation buy</t>
-  </si>
-  <si>
-    <t>daily DBR 84.13-85.12; tests 2; 4/7</t>
-  </si>
-  <si>
-    <t>weekly DBR 76.36-84.4; tests 2; 3/7</t>
-  </si>
-  <si>
-    <t>17/30</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; MACD and OBV confirmation; Operator delivery confirmation; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>Price-action base and higher-low structure; Retracement/pullback buy setup; GTF demand/supply confluence; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Bollinger trend/range context; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
-  </si>
-  <si>
-    <t>70.29% (123/175)</t>
-  </si>
-  <si>
-    <t>No bullish confirmation pattern</t>
-  </si>
-  <si>
-    <t>Weekly RSI 61.25 is above 50. Daily RSI 63.34 is above 50. Weekly RS 13.3% is above 0. Daily long RS55 10.5% is above 0. Daily short RS21 1.6% is above 0. Daily close 88.09 is above Supertrend(10, 3) 81.07. Entry style: Momentum continuation buy. Price action strength: close is within 15% of 52-week high 92.90. Volume shocker: latest volume is 2.77x the 50-day average. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: bandwidth 4.85% indicates a range-bound/compressed phase. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Volatility is controlled: ATR(14) is 2.54% of price. Liquidity strength: 20-day average turnover is Rs 190458904.28. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly sideways. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 0/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Operator accumulation confirmed: price 1.83%, traded quantity 6.96x, delivery 8.40x, close above average price 87.40. Institutional confluence score 3/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Sector breadth strong: My List has 123/175 stocks (70.29%) passing daily strength. Institutional concept coverage: 17/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 180.45; planned allocation Rs 440.45, quantity 5, initial stop 84.5, planned risk Rs 17.95. Closing signal dated 2026-07-13; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>GRINDWELL</t>
-  </si>
-  <si>
-    <t>Grindwell Norton Limited</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>2026-07-13 09:17 IST ENTRY_BUY BUY 49 @ 2048.2; turnover 100361.8; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-13 09:15 IST PARTIAL_EXIT SELL 24 @ 2004.5; turnover 48108; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -1048.8 | 2026-07-14 09:17 IST PARTIAL_EXIT SELL 12 @ 2010.3; turnover 24123.6; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -454.8 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 6 @ 2038.6; turnover 12231.6; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -57.6</t>
-  </si>
-  <si>
-    <t>daily RS21 below zero close below Supertrend setup grade WATCH GTF confirms less than 2R room ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. WAIT/WATCH: 1/3 completed deterioration closes confirmed. GTF is secondary context only and cannot trigger an exit.</t>
-  </si>
-  <si>
-    <t>2/4</t>
-  </si>
-  <si>
-    <t>4/9 (GTF C)</t>
-  </si>
-  <si>
-    <t>daily DBR 1886.4-1932.3; fresh; 7/7</t>
-  </si>
-  <si>
-    <t>daily DBD 2244-2146.8; fresh; 7/7</t>
-  </si>
-  <si>
-    <t>0.49R</t>
-  </si>
-  <si>
-    <t>15/26</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>28.25% (495/1752)</t>
-  </si>
-  <si>
-    <t>Weekly RSI 63.02 is above 50. Daily RSI 52.01 is above 50. Weekly RS 25.7% is above 0. Daily long RS55 22.2% is above 0. Daily short RS21 2.9% is above 0. Daily close 2058.60 is above Supertrend(10, 3) 2015.38. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 2294.40. Retracement watch: pullback depth 10.28% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: close is below the middle band 2106.53 with bandwidth 12.00%. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 2.10% above daily Supertrend. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 3.57% of price. Liquidity strength: 20-day average turnover is Rs 210232154.56. Market regime supports longs: NIFTY 500 bullish/healthy. Daily demand DBR 1886.4-1932.3: fresh, score 7/7, achievement 7.89R, significant_gap. GTF 50-SMA slope: daily up, weekly up. Opposing daily supply 2146.8-2244; estimated room 0.49R. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next actual market session using the 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 15/26 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 170.76; planned allocation Rs 98812.8, quantity 48, initial stop 2015.38, planned risk Rs 2074.56. Closing signal dated 2026-07-10; buy fill must come from the next actual market session exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>INGERRAND</t>
-  </si>
-  <si>
-    <t>Ingersoll Rand (India) Limited</t>
-  </si>
-  <si>
-    <t>2026-07-13 09:17 IST ENTRY_BUY BUY 22 @ 4421.9; turnover 97281.8; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
-  </si>
-  <si>
-    <t>daily RS21 below zero setup grade WATCH ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. TREND RIDE: weekly/daily leadership and price structure remain healthy; trail the stop instead of cutting the winner. WAIT/WATCH: one primary weakness is not enough for a partial exit.</t>
-  </si>
-  <si>
-    <t>Retracement buy near 50-DMA</t>
-  </si>
-  <si>
-    <t>3/9 (GTF C)</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
-  </si>
-  <si>
-    <t>Weekly RSI 57.94 is above 50. Daily RSI 53.75 is above 50. Weekly RS 19.4% is above 0. Daily long RS55 2.1% is above 0. Daily short RS21 5.4% is above 0. Daily close 4452.00 is above Supertrend(10, 3) 4220.30. Entry style: Retracement buy near 50-DMA. Price action strength: close is within 15% of 52-week high 4756.20. Retracement buy: price pulled back 6.40% from the 55-day high and reclaimed near 50-DMA 4334.98; support distance is 2.63%. Retracement confirmation: pullback volume ratio 0.47 and reclaim volume ratio 0.65 with candle close location 61.83%. Bollinger context: close is below the middle band 4487.32 with bandwidth 10.02%. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 5.20% above daily Supertrend. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 2.90% of price. Liquidity strength: 20-day average turnover is Rs 79382544.10. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next actual market session using the 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 15/26 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 167.02; planned allocation Rs 97944, quantity 22, initial stop 4319.5, planned risk Rs 2915. Closing signal dated 2026-07-10; buy fill must come from the next actual market session exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>RAIN</t>
-  </si>
-  <si>
-    <t>Rain Industries Limited</t>
-  </si>
-  <si>
-    <t>2026-07-13 09:17 IST ENTRY_BUY BUY 291 @ 214.01; turnover 62276.91; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 145 @ 208.03; turnover 30164.35; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -867.1</t>
-  </si>
-  <si>
-    <t>GTF confirms less than 2R room ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. TREND RIDE: weekly/daily leadership and price structure remain healthy; trail the stop instead of cutting the winner. GTF is secondary context only and cannot trigger an exit.</t>
-  </si>
-  <si>
-    <t>14/26</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Bollinger trend/range context; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Volume participation; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 71.58 is above 50. Daily RSI 64.68 is above 50. Weekly RS 35.7% is above 0. Daily long RS55 56.1% is above 0. Daily short RS21 0.7% is above 0. Daily close 207.05 is above Supertrend(10, 3) 178.77. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 214.17. Retracement watch: pullback depth 3.32% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: close is above the middle band 192.70 with bandwidth 16.23%. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Volatility is controlled: ATR(14) is 4.35% of price. Liquidity strength: 20-day average turnover is Rs 991729867.12. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next actual market session using the 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 14/26 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 179.24; planned allocation Rs 99798.1, quantity 482, initial stop 196.45, planned risk Rs 5109.2. Closing signal dated 2026-07-10; buy fill must come from the next actual market session exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>CRAFTSMAN</t>
-  </si>
-  <si>
-    <t>Craftsman Automation Limited</t>
-  </si>
-  <si>
-    <t>2026-07-13 09:17 IST ENTRY_BUY BUY 10 @ 9284; turnover 92840; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 5 @ 9251.5; turnover 46257.5; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -162.5</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>0/9 (GTF neutral)</t>
-  </si>
-  <si>
-    <t>daily RBR 8613.5-8978; tests 4; 3/7</t>
-  </si>
-  <si>
-    <t>weekly DBR 8242.5-9074; tests 2; 4/7</t>
-  </si>
-  <si>
-    <t>daily RBD 9528-9402.5; fresh; 7/7</t>
-  </si>
-  <si>
-    <t>14/29</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Price-action base and higher-low structure; Retracement/pullback buy setup; GTF demand/supply confluence; Fibonacci retracement support; Bollinger trend/range context; Volume participation; MACD and OBV confirmation; Operator delivery confirmation; Sector breadth; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>42.11% (16/38)</t>
-  </si>
-  <si>
-    <t>Weekly RSI 62.77 is above 50. Daily RSI 55.38 is above 50. Weekly RS 20.2% is above 0. Daily long RS55 17.2% is above 0. Daily short RS21 0.2% is above 0. Daily close 9301.00 is above Supertrend(10, 3) 8728.10. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 9938.00. Momentum confirmation: MACD is not fully confirmed; OBV is rising. Retracement watch: pullback depth 6.41% is valid, but support/reclaim/volume/risk confirmation is incomplete. Bollinger context: bandwidth 7.09% indicates a range-bound/compressed phase. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.16% above daily Supertrend. Volatility is controlled: ATR(14) is 2.80% of price. Liquidity strength: 20-day average turnover is Rs 787112608.80. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. Opposing daily supply 9402.5-9528; blocker/early-risk flag. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Operator/delivery context: Delivery neutral: traded quantity 0.33x, delivery 0.27x, delivery percentage 49.09%. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Institutional concept coverage: 14/29 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 131.92; planned allocation Rs 93010, quantity 10, initial stop 8955.5, planned risk Rs 3455. Closing signal dated 2026-07-10; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>Best only (A+/A)</t>
-  </si>
-  <si>
-    <t>KPIL</t>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 73 @ 1351.4; turnover 98652.2; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-14 09:17 IST PARTIAL_EXIT SELL 36 @ 1333.5; turnover 48006; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -644.4 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 18 @ 1305.2; turnover 23493.6; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -831.6</t>
-  </si>
-  <si>
-    <t>daily RS21 below zero daily RSI below 50 close below Supertrend close below 50-DMA setup grade WATCH ENTRY RETEST GRACE: 1/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. WAIT/WATCH: 1/3 completed deterioration closes confirmed.</t>
-  </si>
-  <si>
-    <t>16/21</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Index option-chain positioning</t>
-  </si>
-  <si>
-    <t>Intraday tick scalping; Broker-only live Greeks/order-book depth</t>
-  </si>
-  <si>
-    <t>64.29% (90/140)</t>
-  </si>
-  <si>
-    <t>bullish engulfing</t>
-  </si>
-  <si>
-    <t>Weekly RSI 66.89 is above 50. Daily RSI 50.91 is above 50. Weekly RS 27.5% is above 0. Daily long RS55 5.5% is above 0. Daily short RS21 2.1% is above 0. Daily close 1349.90 is above Supertrend(10, 3) 1313.78. Price action strength: close is within 15% of 52-week high 1479.60. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 2.68% above daily Supertrend. Price confirmation: bullish engulfing is present. Volatility is controlled: ATR(14) is 3.04% of price. Liquidity strength: 20-day average turnover is Rs 511253745.19. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 16/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>SIS</t>
-  </si>
-  <si>
-    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 228 @ 437.05; turnover 99647.4; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-13 09:15 IST PARTIAL_EXIT SELL 114 @ 432.65; turnover 49322.1; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -501.6</t>
-  </si>
-  <si>
-    <t>2026-07-14T03:32:23.269Z: SANGAMIND; Optional rotation cancelled before selling SIS: Rotation requires 2 distinct valid ENTRY closes; candidate has 0.</t>
-  </si>
-  <si>
-    <t>14/21</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 72.14 is above 50. Daily RSI 61.56 is above 50. Weekly RS 25.5% is above 0. Daily long RS55 29.2% is above 0. Daily short RS21 1.5% is above 0. Daily close 437.80 is above Supertrend(10, 3) 397.84. Price action strength: close is within 15% of 52-week high 480.95. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Volatility is controlled: ATR(14) is 3.42% of price. Liquidity strength: 20-day average turnover is Rs 261311772.23. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 14/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>PGHL</t>
-  </si>
-  <si>
-    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 15 @ 6621.5; turnover 99322.5; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
-  </si>
-  <si>
-    <t>17/21</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 73.92 is above 50. Daily RSI 70.18 is above 50. Weekly RS 23.0% is above 0. Daily long RS55 28.3% is above 0. Daily short RS21 2.2% is above 0. Daily close 6612.00 is above Supertrend(10, 3) 6036.47. Price action strength: close is within 15% of 52-week high 6739.00. Volume shocker: latest volume is 2.02x the 50-day average. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.56% of price. Liquidity strength: 20-day average turnover is Rs 92394456.38. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 17/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>NH</t>
-  </si>
-  <si>
-    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 49 @ 1995.8; turnover 97794.2; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 62.41 is above 50. Daily RSI 59.04 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 9.6% is above 0. Daily short RS21 0.7% is above 0. Daily close 1993.20 is above Supertrend(10, 3) 1864.19. Price action strength: close is within 15% of 52-week high 2093.30. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.47% above daily Supertrend. Volatility is controlled: ATR(14) is 2.56% of price. Liquidity strength: 20-day average turnover is Rs 580096417.25. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 16/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>VIJAYA</t>
-  </si>
-  <si>
-    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 71 @ 1373.5; turnover 97518.5; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
-  </si>
-  <si>
-    <t>15/21</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Volume participation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 66.67 is above 50. Daily RSI 57.60 is above 50. Weekly RS 42.2% is above 0. Daily long RS55 32.3% is above 0. Daily short RS21 4.5% is above 0. Daily close 1377.80 is above Supertrend(10, 3) 1215.62. Price action strength: close is within 15% of 52-week high 1427.80. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.06% of price. Liquidity strength: 20-day average turnover is Rs 464701789.72. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>PRECOT</t>
-  </si>
-  <si>
-    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 119 @ 811; turnover 96509; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Volume participation; Volatility and liquidity control; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 64.67 is above 50. Daily RSI 61.84 is above 50. Weekly RS 54.7% is above 0. Daily long RS55 46.8% is above 0. Daily short RS21 15.0% is above 0. Daily close 800.45 is above Supertrend(10, 3) 673.89. Price action strength: close is within 15% of 52-week high 861.25. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.91% of price. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 14/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>PRUDENT</t>
-  </si>
-  <si>
-    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 33 @ 2986; turnover 98538; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 16 @ 2989.4; turnover 47830.4; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 54.4</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 63.57 is above 50. Daily RSI 53.42 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 4.7% is above 0. Daily close 2960.00 is above Supertrend(10, 3) 2759.71. Price action strength: close is within 15% of 52-week high 3160.10. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.77% above daily Supertrend. Volatility is controlled: ATR(14) is 3.14% of price. Liquidity strength: 20-day average turnover is Rs 67973469.69. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>My Custom List</t>
-  </si>
-  <si>
-    <t>NEXUSSURGL</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>09:21 IST</t>
-  </si>
-  <si>
-    <t>09:17 market order; first actual traded candle at 09:21 IST</t>
-  </si>
-  <si>
-    <t>09:17 order / 09:21 actual fill</t>
-  </si>
-  <si>
     <t>2026-07-13 09:17 IST ENTRY_BUY BUY 31 @ 19.59; turnover 607.29; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-13 09:17 IST PARTIAL_EXIT SELL 15 @ 19.59; turnover 293.85; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST FULL_EXIT SELL 16 @ 18.5; turnover 296; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -17.44</t>
   </si>
   <si>
@@ -1350,7 +1350,7 @@
     <t>2026-07-15T10:40:23.503Z</t>
   </si>
   <si>
-    <t>2026-07-16T03:39:00.315Z</t>
+    <t>2026-07-16T03:46:27.865Z</t>
   </si>
   <si>
     <t>Type</t>
@@ -2627,7 +2627,7 @@
         <v>213.48</v>
       </c>
       <c r="AN2">
-        <v>194.43</v>
+        <v>200.58</v>
       </c>
       <c r="AO2">
         <v>847.55</v>
@@ -2635,11 +2635,11 @@
       <c r="AP2">
         <v>847.55</v>
       </c>
-      <c r="AQ2" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>153</v>
+      <c r="AQ2">
+        <v>824.5</v>
+      </c>
+      <c r="AR2">
+        <v>739.8475000366074</v>
       </c>
       <c r="AS2" t="s">
         <v>154</v>
@@ -2950,7 +2950,7 @@
         <v>191.09</v>
       </c>
       <c r="AN3">
-        <v>111.85</v>
+        <v>118</v>
       </c>
       <c r="AO3">
         <v>805.6</v>
@@ -2958,11 +2958,11 @@
       <c r="AP3">
         <v>805.6</v>
       </c>
-      <c r="AQ3" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>153</v>
+      <c r="AQ3">
+        <v>833.5499877929688</v>
+      </c>
+      <c r="AR3">
+        <v>734.9542954011073</v>
       </c>
       <c r="AS3" t="s">
         <v>154</v>
@@ -3273,7 +3273,7 @@
         <v>195.78</v>
       </c>
       <c r="AN4">
-        <v>174.86</v>
+        <v>181.01</v>
       </c>
       <c r="AO4">
         <v>597.22</v>
@@ -3281,11 +3281,11 @@
       <c r="AP4">
         <v>597.22</v>
       </c>
-      <c r="AQ4" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>153</v>
+      <c r="AQ4">
+        <v>558.75</v>
+      </c>
+      <c r="AR4">
+        <v>521.6262350180588</v>
       </c>
       <c r="AS4" t="s">
         <v>154</v>
@@ -3611,7 +3611,7 @@
         <v>82.89704133721075</v>
       </c>
       <c r="AS5" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="AT5">
         <v>19.95</v>
@@ -3650,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BG5" t="s">
         <v>153</v>
@@ -3683,7 +3683,7 @@
         <v>158</v>
       </c>
       <c r="BQ5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BR5" t="s">
         <v>160</v>
@@ -3701,10 +3701,10 @@
         <v>162</v>
       </c>
       <c r="BW5" t="s">
+        <v>213</v>
+      </c>
+      <c r="BX5" t="s">
         <v>214</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>215</v>
       </c>
       <c r="BY5" t="s">
         <v>27</v>
@@ -3731,13 +3731,13 @@
         <v>202</v>
       </c>
       <c r="CG5" t="s">
+        <v>215</v>
+      </c>
+      <c r="CH5" t="s">
         <v>216</v>
       </c>
-      <c r="CH5" t="s">
+      <c r="CI5" t="s">
         <v>217</v>
-      </c>
-      <c r="CI5" t="s">
-        <v>218</v>
       </c>
       <c r="CJ5" t="s">
         <v>172</v>
@@ -3746,7 +3746,7 @@
         <v>173</v>
       </c>
       <c r="CL5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CM5" t="s">
         <v>175</v>
@@ -3782,7 +3782,7 @@
         <v>2.77</v>
       </c>
       <c r="CX5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CY5">
         <v>85.99</v>
@@ -3794,7 +3794,7 @@
         <v>84.44</v>
       </c>
       <c r="DB5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="DC5" t="s">
         <v>153</v>
@@ -3811,16 +3811,16 @@
         <v>179</v>
       </c>
       <c r="D6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E6" t="s">
         <v>222</v>
-      </c>
-      <c r="E6" t="s">
-        <v>223</v>
       </c>
       <c r="F6" t="s">
         <v>149</v>
       </c>
       <c r="G6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H6" t="s">
         <v>182</v>
@@ -3919,7 +3919,7 @@
         <v>170.76</v>
       </c>
       <c r="AN6">
-        <v>91.14</v>
+        <v>97.28</v>
       </c>
       <c r="AO6">
         <v>1974.43</v>
@@ -3927,11 +3927,11 @@
       <c r="AP6">
         <v>2014.24</v>
       </c>
-      <c r="AQ6" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>153</v>
+      <c r="AQ6">
+        <v>2058.60009765625</v>
+      </c>
+      <c r="AR6">
+        <v>1919.3071735958158</v>
       </c>
       <c r="AS6" t="s">
         <v>154</v>
@@ -3973,7 +3973,7 @@
         <v>-1561.2</v>
       </c>
       <c r="BF6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BG6" t="s">
         <v>153</v>
@@ -3994,7 +3994,7 @@
         <v>156</v>
       </c>
       <c r="BM6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="BN6">
         <v>1</v>
@@ -4018,13 +4018,13 @@
         <v>4</v>
       </c>
       <c r="BU6" t="s">
+        <v>226</v>
+      </c>
+      <c r="BV6" t="s">
         <v>227</v>
       </c>
-      <c r="BV6" t="s">
+      <c r="BW6" t="s">
         <v>228</v>
-      </c>
-      <c r="BW6" t="s">
-        <v>229</v>
       </c>
       <c r="BX6" t="s">
         <v>153</v>
@@ -4036,10 +4036,10 @@
         <v>153</v>
       </c>
       <c r="CA6" t="s">
+        <v>229</v>
+      </c>
+      <c r="CB6" t="s">
         <v>230</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>231</v>
       </c>
       <c r="CC6" t="s">
         <v>165</v>
@@ -4054,13 +4054,13 @@
         <v>188</v>
       </c>
       <c r="CG6" t="s">
+        <v>231</v>
+      </c>
+      <c r="CH6" t="s">
         <v>232</v>
       </c>
-      <c r="CH6" t="s">
+      <c r="CI6" t="s">
         <v>233</v>
-      </c>
-      <c r="CI6" t="s">
-        <v>234</v>
       </c>
       <c r="CJ6" t="s">
         <v>192</v>
@@ -4069,7 +4069,7 @@
         <v>173</v>
       </c>
       <c r="CL6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="CM6" t="s">
         <v>175</v>
@@ -4117,7 +4117,7 @@
         <v>1981</v>
       </c>
       <c r="DB6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="DC6" t="s">
         <v>153</v>
@@ -4134,16 +4134,16 @@
         <v>179</v>
       </c>
       <c r="D7" t="s">
+        <v>236</v>
+      </c>
+      <c r="E7" t="s">
         <v>237</v>
-      </c>
-      <c r="E7" t="s">
-        <v>238</v>
       </c>
       <c r="F7" t="s">
         <v>149</v>
       </c>
       <c r="G7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H7" t="s">
         <v>182</v>
@@ -4242,7 +4242,7 @@
         <v>167.02</v>
       </c>
       <c r="AN7">
-        <v>75.72</v>
+        <v>81.87</v>
       </c>
       <c r="AO7">
         <v>4319.5</v>
@@ -4250,11 +4250,11 @@
       <c r="AP7">
         <v>4352.73</v>
       </c>
-      <c r="AQ7" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>153</v>
+      <c r="AQ7">
+        <v>4452</v>
+      </c>
+      <c r="AR7">
+        <v>4279.016498604705</v>
       </c>
       <c r="AS7" t="s">
         <v>154</v>
@@ -4296,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="BF7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="BG7" t="s">
         <v>153</v>
@@ -4317,19 +4317,19 @@
         <v>156</v>
       </c>
       <c r="BM7" t="s">
+        <v>239</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>153</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>153</v>
+      </c>
+      <c r="BQ7" t="s">
         <v>240</v>
-      </c>
-      <c r="BN7">
-        <v>0</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>153</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>153</v>
-      </c>
-      <c r="BQ7" t="s">
-        <v>241</v>
       </c>
       <c r="BR7" t="s">
         <v>160</v>
@@ -4341,10 +4341,10 @@
         <v>1</v>
       </c>
       <c r="BU7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BW7" t="s">
         <v>153</v>
@@ -4377,13 +4377,13 @@
         <v>188</v>
       </c>
       <c r="CG7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CH7" t="s">
+        <v>242</v>
+      </c>
+      <c r="CI7" t="s">
         <v>243</v>
-      </c>
-      <c r="CI7" t="s">
-        <v>244</v>
       </c>
       <c r="CJ7" t="s">
         <v>192</v>
@@ -4392,7 +4392,7 @@
         <v>173</v>
       </c>
       <c r="CL7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="CM7" t="s">
         <v>175</v>
@@ -4440,7 +4440,7 @@
         <v>4319.5</v>
       </c>
       <c r="DB7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="DC7" t="s">
         <v>153</v>
@@ -4457,16 +4457,16 @@
         <v>179</v>
       </c>
       <c r="D8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E8" t="s">
         <v>246</v>
-      </c>
-      <c r="E8" t="s">
-        <v>247</v>
       </c>
       <c r="F8" t="s">
         <v>149</v>
       </c>
       <c r="G8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H8" t="s">
         <v>182</v>
@@ -4580,7 +4580,7 @@
         <v>174.58772588109068</v>
       </c>
       <c r="AS8" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="AT8">
         <v>5109.96</v>
@@ -4619,7 +4619,7 @@
         <v>-867.1</v>
       </c>
       <c r="BF8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="BG8" t="s">
         <v>153</v>
@@ -4640,7 +4640,7 @@
         <v>156</v>
       </c>
       <c r="BM8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="BN8">
         <v>0</v>
@@ -4664,10 +4664,10 @@
         <v>4</v>
       </c>
       <c r="BU8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BW8" t="s">
         <v>153</v>
@@ -4700,13 +4700,13 @@
         <v>188</v>
       </c>
       <c r="CG8" t="s">
+        <v>249</v>
+      </c>
+      <c r="CH8" t="s">
         <v>250</v>
       </c>
-      <c r="CH8" t="s">
+      <c r="CI8" t="s">
         <v>251</v>
-      </c>
-      <c r="CI8" t="s">
-        <v>252</v>
       </c>
       <c r="CJ8" t="s">
         <v>192</v>
@@ -4715,7 +4715,7 @@
         <v>173</v>
       </c>
       <c r="CL8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="CM8" t="s">
         <v>175</v>
@@ -4751,7 +4751,7 @@
         <v>0.55</v>
       </c>
       <c r="CX8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CY8">
         <v>199.5</v>
@@ -4763,7 +4763,7 @@
         <v>186.53</v>
       </c>
       <c r="DB8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="DC8" t="s">
         <v>153</v>
@@ -4780,16 +4780,16 @@
         <v>179</v>
       </c>
       <c r="D9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" t="s">
         <v>254</v>
-      </c>
-      <c r="E9" t="s">
-        <v>255</v>
       </c>
       <c r="F9" t="s">
         <v>149</v>
       </c>
       <c r="G9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H9" t="s">
         <v>182</v>
@@ -4888,7 +4888,7 @@
         <v>131.92</v>
       </c>
       <c r="AN9">
-        <v>103.8</v>
+        <v>109.94</v>
       </c>
       <c r="AO9">
         <v>8955.5</v>
@@ -4896,11 +4896,11 @@
       <c r="AP9">
         <v>9071</v>
       </c>
-      <c r="AQ9" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>153</v>
+      <c r="AQ9">
+        <v>9301</v>
+      </c>
+      <c r="AR9">
+        <v>8773.801138101968</v>
       </c>
       <c r="AS9" t="s">
         <v>154</v>
@@ -4942,7 +4942,7 @@
         <v>-162.5</v>
       </c>
       <c r="BF9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="BG9" t="s">
         <v>153</v>
@@ -4963,7 +4963,7 @@
         <v>156</v>
       </c>
       <c r="BM9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="BN9">
         <v>0</v>
@@ -4978,7 +4978,7 @@
         <v>185</v>
       </c>
       <c r="BR9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BS9">
         <v>10</v>
@@ -4990,13 +4990,13 @@
         <v>161</v>
       </c>
       <c r="BV9" t="s">
+        <v>257</v>
+      </c>
+      <c r="BW9" t="s">
         <v>258</v>
       </c>
-      <c r="BW9" t="s">
+      <c r="BX9" t="s">
         <v>259</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>260</v>
       </c>
       <c r="BY9" t="s">
         <v>27</v>
@@ -5005,7 +5005,7 @@
         <v>153</v>
       </c>
       <c r="CA9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="CB9" t="s">
         <v>153</v>
@@ -5023,13 +5023,13 @@
         <v>188</v>
       </c>
       <c r="CG9" t="s">
+        <v>261</v>
+      </c>
+      <c r="CH9" t="s">
         <v>262</v>
       </c>
-      <c r="CH9" t="s">
+      <c r="CI9" t="s">
         <v>263</v>
-      </c>
-      <c r="CI9" t="s">
-        <v>264</v>
       </c>
       <c r="CJ9" t="s">
         <v>172</v>
@@ -5038,7 +5038,7 @@
         <v>173</v>
       </c>
       <c r="CL9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="CM9" t="s">
         <v>175</v>
@@ -5074,7 +5074,7 @@
         <v>0.1</v>
       </c>
       <c r="CX9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CY9">
         <v>9100</v>
@@ -5086,7 +5086,7 @@
         <v>8955.5</v>
       </c>
       <c r="DB9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="DC9" t="s">
         <v>153</v>
@@ -5097,25 +5097,25 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C10" t="s">
         <v>209</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F10" t="s">
         <v>149</v>
       </c>
       <c r="G10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I10" t="s">
         <v>47</v>
@@ -5211,7 +5211,7 @@
         <v>153</v>
       </c>
       <c r="AN10">
-        <v>85.95</v>
+        <v>92.09</v>
       </c>
       <c r="AO10">
         <v>1251.2</v>
@@ -5219,11 +5219,11 @@
       <c r="AP10">
         <v>1278.43</v>
       </c>
-      <c r="AQ10" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>153</v>
+      <c r="AQ10">
+        <v>1352</v>
+      </c>
+      <c r="AR10">
+        <v>1304.032274715177</v>
       </c>
       <c r="AS10" t="s">
         <v>154</v>
@@ -5265,7 +5265,7 @@
         <v>-1476</v>
       </c>
       <c r="BF10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="BG10" t="s">
         <v>153</v>
@@ -5286,7 +5286,7 @@
         <v>156</v>
       </c>
       <c r="BM10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="BN10">
         <v>1</v>
@@ -5310,7 +5310,7 @@
         <v>4</v>
       </c>
       <c r="BU10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV10" t="s">
         <v>153</v>
@@ -5346,22 +5346,22 @@
         <v>188</v>
       </c>
       <c r="CG10" t="s">
+        <v>271</v>
+      </c>
+      <c r="CH10" t="s">
         <v>272</v>
       </c>
-      <c r="CH10" t="s">
+      <c r="CI10" t="s">
         <v>273</v>
       </c>
-      <c r="CI10" t="s">
+      <c r="CJ10" t="s">
         <v>274</v>
       </c>
-      <c r="CJ10" t="s">
+      <c r="CK10" t="s">
         <v>275</v>
       </c>
-      <c r="CK10" t="s">
+      <c r="CL10" t="s">
         <v>276</v>
-      </c>
-      <c r="CL10" t="s">
-        <v>277</v>
       </c>
       <c r="CM10" t="s">
         <v>175</v>
@@ -5397,7 +5397,7 @@
         <v>153</v>
       </c>
       <c r="CX10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="CY10">
         <v>1321</v>
@@ -5409,7 +5409,7 @@
         <v>1321</v>
       </c>
       <c r="DB10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="DC10" t="s">
         <v>153</v>
@@ -5420,25 +5420,25 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C11" t="s">
         <v>147</v>
       </c>
       <c r="D11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F11" t="s">
         <v>149</v>
       </c>
       <c r="G11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I11" t="s">
         <v>47</v>
@@ -5549,7 +5549,7 @@
         <v>398.6403308636572</v>
       </c>
       <c r="AS11" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="AT11">
         <v>7813.56</v>
@@ -5588,7 +5588,7 @@
         <v>-501.6</v>
       </c>
       <c r="BF11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="BG11" t="s">
         <v>153</v>
@@ -5609,13 +5609,13 @@
         <v>156</v>
       </c>
       <c r="BM11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="BN11">
         <v>0</v>
       </c>
       <c r="BO11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="BP11" t="s">
         <v>153</v>
@@ -5633,7 +5633,7 @@
         <v>5</v>
       </c>
       <c r="BU11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV11" t="s">
         <v>153</v>
@@ -5669,22 +5669,22 @@
         <v>188</v>
       </c>
       <c r="CG11" t="s">
+        <v>282</v>
+      </c>
+      <c r="CH11" t="s">
         <v>283</v>
       </c>
-      <c r="CH11" t="s">
+      <c r="CI11" t="s">
         <v>284</v>
       </c>
-      <c r="CI11" t="s">
-        <v>285</v>
-      </c>
       <c r="CJ11" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK11" t="s">
         <v>275</v>
       </c>
-      <c r="CK11" t="s">
+      <c r="CL11" t="s">
         <v>276</v>
-      </c>
-      <c r="CL11" t="s">
-        <v>277</v>
       </c>
       <c r="CM11" t="s">
         <v>175</v>
@@ -5720,7 +5720,7 @@
         <v>153</v>
       </c>
       <c r="CX11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CY11">
         <v>425.45</v>
@@ -5732,7 +5732,7 @@
         <v>422.15</v>
       </c>
       <c r="DB11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="DC11" t="s">
         <v>153</v>
@@ -5743,25 +5743,25 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C12" t="s">
         <v>147</v>
       </c>
       <c r="D12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F12" t="s">
         <v>149</v>
       </c>
       <c r="G12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I12" t="s">
         <v>47</v>
@@ -5857,7 +5857,7 @@
         <v>153</v>
       </c>
       <c r="AN12">
-        <v>198.61</v>
+        <v>204.75</v>
       </c>
       <c r="AO12">
         <v>6083.5</v>
@@ -5865,11 +5865,11 @@
       <c r="AP12">
         <v>6359.98</v>
       </c>
-      <c r="AQ12" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>153</v>
+      <c r="AQ12">
+        <v>6839</v>
+      </c>
+      <c r="AR12">
+        <v>5977.839360894776</v>
       </c>
       <c r="AS12" t="s">
         <v>154</v>
@@ -5911,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BG12" t="s">
         <v>153</v>
@@ -5956,7 +5956,7 @@
         <v>4</v>
       </c>
       <c r="BU12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV12" t="s">
         <v>153</v>
@@ -5992,22 +5992,22 @@
         <v>188</v>
       </c>
       <c r="CG12" t="s">
+        <v>288</v>
+      </c>
+      <c r="CH12" t="s">
         <v>289</v>
       </c>
-      <c r="CH12" t="s">
+      <c r="CI12" t="s">
         <v>290</v>
       </c>
-      <c r="CI12" t="s">
-        <v>291</v>
-      </c>
       <c r="CJ12" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK12" t="s">
         <v>275</v>
       </c>
-      <c r="CK12" t="s">
+      <c r="CL12" t="s">
         <v>276</v>
-      </c>
-      <c r="CL12" t="s">
-        <v>277</v>
       </c>
       <c r="CM12" t="s">
         <v>175</v>
@@ -6055,7 +6055,7 @@
         <v>6202.5</v>
       </c>
       <c r="DB12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="DC12" t="s">
         <v>153</v>
@@ -6066,25 +6066,25 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C13" t="s">
         <v>209</v>
       </c>
       <c r="D13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F13" t="s">
         <v>149</v>
       </c>
       <c r="G13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I13" t="s">
         <v>47</v>
@@ -6180,7 +6180,7 @@
         <v>153</v>
       </c>
       <c r="AN13">
-        <v>178.82</v>
+        <v>186.47</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -6188,11 +6188,11 @@
       <c r="AP13">
         <v>1968</v>
       </c>
-      <c r="AQ13" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>153</v>
+      <c r="AQ13">
+        <v>2027.300048828125</v>
+      </c>
+      <c r="AR13">
+        <v>1900.2560938383647</v>
       </c>
       <c r="AS13" t="s">
         <v>154</v>
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="BF13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BG13" t="s">
         <v>153</v>
@@ -6279,7 +6279,7 @@
         <v>3</v>
       </c>
       <c r="BU13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV13" t="s">
         <v>153</v>
@@ -6315,22 +6315,22 @@
         <v>188</v>
       </c>
       <c r="CG13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="CH13" t="s">
+        <v>294</v>
+      </c>
+      <c r="CI13" t="s">
         <v>295</v>
       </c>
-      <c r="CI13" t="s">
-        <v>296</v>
-      </c>
       <c r="CJ13" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK13" t="s">
         <v>275</v>
       </c>
-      <c r="CK13" t="s">
+      <c r="CL13" t="s">
         <v>276</v>
-      </c>
-      <c r="CL13" t="s">
-        <v>277</v>
       </c>
       <c r="CM13" t="s">
         <v>175</v>
@@ -6366,7 +6366,7 @@
         <v>153</v>
       </c>
       <c r="CX13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CY13">
         <v>1957</v>
@@ -6378,7 +6378,7 @@
         <v>1957</v>
       </c>
       <c r="DB13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="DC13" t="s">
         <v>153</v>
@@ -6389,25 +6389,25 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C14" t="s">
         <v>209</v>
       </c>
       <c r="D14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F14" t="s">
         <v>149</v>
       </c>
       <c r="G14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I14" t="s">
         <v>47</v>
@@ -6503,7 +6503,7 @@
         <v>153</v>
       </c>
       <c r="AN14">
-        <v>192.39</v>
+        <v>200.04</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -6511,11 +6511,11 @@
       <c r="AP14">
         <v>1324.8</v>
       </c>
-      <c r="AQ14" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>153</v>
+      <c r="AQ14">
+        <v>1389.0999755859375</v>
+      </c>
+      <c r="AR14">
+        <v>1270.5608205128772</v>
       </c>
       <c r="AS14" t="s">
         <v>154</v>
@@ -6557,7 +6557,7 @@
         <v>0</v>
       </c>
       <c r="BF14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BG14" t="s">
         <v>153</v>
@@ -6602,7 +6602,7 @@
         <v>4</v>
       </c>
       <c r="BU14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV14" t="s">
         <v>153</v>
@@ -6638,22 +6638,22 @@
         <v>188</v>
       </c>
       <c r="CG14" t="s">
+        <v>299</v>
+      </c>
+      <c r="CH14" t="s">
         <v>300</v>
       </c>
-      <c r="CH14" t="s">
+      <c r="CI14" t="s">
         <v>301</v>
       </c>
-      <c r="CI14" t="s">
-        <v>302</v>
-      </c>
       <c r="CJ14" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK14" t="s">
         <v>275</v>
       </c>
-      <c r="CK14" t="s">
+      <c r="CL14" t="s">
         <v>276</v>
-      </c>
-      <c r="CL14" t="s">
-        <v>277</v>
       </c>
       <c r="CM14" t="s">
         <v>175</v>
@@ -6701,7 +6701,7 @@
         <v>1303.2</v>
       </c>
       <c r="DB14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="DC14" t="s">
         <v>153</v>
@@ -6712,25 +6712,25 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C15" t="s">
         <v>147</v>
       </c>
       <c r="D15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F15" t="s">
         <v>149</v>
       </c>
       <c r="G15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I15" t="s">
         <v>47</v>
@@ -6826,7 +6826,7 @@
         <v>153</v>
       </c>
       <c r="AN15">
-        <v>187.86</v>
+        <v>194.01</v>
       </c>
       <c r="AO15">
         <v>771.79</v>
@@ -6834,11 +6834,11 @@
       <c r="AP15">
         <v>771.79</v>
       </c>
-      <c r="AQ15" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>153</v>
+      <c r="AQ15">
+        <v>809.9500122070312</v>
+      </c>
+      <c r="AR15">
+        <v>695.4346801872446</v>
       </c>
       <c r="AS15" t="s">
         <v>154</v>
@@ -6880,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="BF15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="BG15" t="s">
         <v>153</v>
@@ -6925,7 +6925,7 @@
         <v>3</v>
       </c>
       <c r="BU15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV15" t="s">
         <v>153</v>
@@ -6961,22 +6961,22 @@
         <v>188</v>
       </c>
       <c r="CG15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="CH15" t="s">
+        <v>305</v>
+      </c>
+      <c r="CI15" t="s">
         <v>306</v>
       </c>
-      <c r="CI15" t="s">
-        <v>307</v>
-      </c>
       <c r="CJ15" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK15" t="s">
         <v>275</v>
       </c>
-      <c r="CK15" t="s">
+      <c r="CL15" t="s">
         <v>276</v>
-      </c>
-      <c r="CL15" t="s">
-        <v>277</v>
       </c>
       <c r="CM15" t="s">
         <v>175</v>
@@ -7024,7 +7024,7 @@
         <v>721.4</v>
       </c>
       <c r="DB15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="DC15" t="s">
         <v>153</v>
@@ -7035,25 +7035,25 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C16" t="s">
         <v>147</v>
       </c>
       <c r="D16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F16" t="s">
         <v>149</v>
       </c>
       <c r="G16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I16" t="s">
         <v>47</v>
@@ -7149,7 +7149,7 @@
         <v>153</v>
       </c>
       <c r="AN16">
-        <v>86.56</v>
+        <v>92.7</v>
       </c>
       <c r="AO16">
         <v>2728.17</v>
@@ -7157,11 +7157,11 @@
       <c r="AP16">
         <v>2882.7</v>
       </c>
-      <c r="AQ16" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR16" t="s">
-        <v>153</v>
+      <c r="AQ16">
+        <v>2983.199951171875</v>
+      </c>
+      <c r="AR16">
+        <v>2827.406442040053</v>
       </c>
       <c r="AS16" t="s">
         <v>154</v>
@@ -7203,7 +7203,7 @@
         <v>54.4</v>
       </c>
       <c r="BF16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="BG16" t="s">
         <v>153</v>
@@ -7248,7 +7248,7 @@
         <v>3</v>
       </c>
       <c r="BU16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV16" t="s">
         <v>153</v>
@@ -7284,22 +7284,22 @@
         <v>188</v>
       </c>
       <c r="CG16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="CH16" t="s">
+        <v>310</v>
+      </c>
+      <c r="CI16" t="s">
         <v>311</v>
       </c>
-      <c r="CI16" t="s">
-        <v>312</v>
-      </c>
       <c r="CJ16" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK16" t="s">
         <v>275</v>
       </c>
-      <c r="CK16" t="s">
+      <c r="CL16" t="s">
         <v>276</v>
-      </c>
-      <c r="CL16" t="s">
-        <v>277</v>
       </c>
       <c r="CM16" t="s">
         <v>175</v>
@@ -7335,7 +7335,7 @@
         <v>153</v>
       </c>
       <c r="CX16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CY16">
         <v>2903.2</v>
@@ -7347,7 +7347,7 @@
         <v>2903.2</v>
       </c>
       <c r="DB16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="DC16" t="s">
         <v>153</v>
@@ -8203,19 +8203,19 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D2" t="s">
         <v>314</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F2" t="s">
         <v>315</v>
       </c>
-      <c r="E2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F2" t="s">
-        <v>316</v>
-      </c>
       <c r="G2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H2" t="s">
         <v>182</v>
@@ -8224,7 +8224,7 @@
         <v>47</v>
       </c>
       <c r="J2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K2">
         <v>19.59</v>
@@ -8233,7 +8233,7 @@
         <v>19.59</v>
       </c>
       <c r="M2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N2">
         <v>16</v>
@@ -8308,7 +8308,7 @@
         <v>2</v>
       </c>
       <c r="AL2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AM2">
         <v>168.93</v>
@@ -8329,7 +8329,7 @@
         <v>153</v>
       </c>
       <c r="AS2" t="s">
-        <v>154</v>
+        <v>319</v>
       </c>
       <c r="AT2">
         <v>17.98</v>
@@ -8464,7 +8464,7 @@
         <v>173</v>
       </c>
       <c r="CL2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CM2" t="s">
         <v>27</v>
@@ -9058,7 +9058,7 @@
         <v>213.48</v>
       </c>
       <c r="AN2">
-        <v>194.43</v>
+        <v>200.58</v>
       </c>
       <c r="AO2">
         <v>847.55</v>
@@ -9066,11 +9066,11 @@
       <c r="AP2">
         <v>847.55</v>
       </c>
-      <c r="AQ2" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>153</v>
+      <c r="AQ2">
+        <v>824.5</v>
+      </c>
+      <c r="AR2">
+        <v>739.8475000366074</v>
       </c>
       <c r="AS2" t="s">
         <v>154</v>
@@ -9381,7 +9381,7 @@
         <v>191.09</v>
       </c>
       <c r="AN3">
-        <v>111.85</v>
+        <v>118</v>
       </c>
       <c r="AO3">
         <v>805.6</v>
@@ -9389,11 +9389,11 @@
       <c r="AP3">
         <v>805.6</v>
       </c>
-      <c r="AQ3" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>153</v>
+      <c r="AQ3">
+        <v>833.5499877929688</v>
+      </c>
+      <c r="AR3">
+        <v>734.9542954011073</v>
       </c>
       <c r="AS3" t="s">
         <v>154</v>
@@ -9704,7 +9704,7 @@
         <v>195.78</v>
       </c>
       <c r="AN4">
-        <v>174.86</v>
+        <v>181.01</v>
       </c>
       <c r="AO4">
         <v>597.22</v>
@@ -9712,11 +9712,11 @@
       <c r="AP4">
         <v>597.22</v>
       </c>
-      <c r="AQ4" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>153</v>
+      <c r="AQ4">
+        <v>558.75</v>
+      </c>
+      <c r="AR4">
+        <v>521.6262350180588</v>
       </c>
       <c r="AS4" t="s">
         <v>154</v>
@@ -10042,7 +10042,7 @@
         <v>82.89704133721075</v>
       </c>
       <c r="AS5" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="AT5">
         <v>19.95</v>
@@ -10081,7 +10081,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BG5" t="s">
         <v>153</v>
@@ -10114,7 +10114,7 @@
         <v>158</v>
       </c>
       <c r="BQ5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BR5" t="s">
         <v>160</v>
@@ -10132,10 +10132,10 @@
         <v>162</v>
       </c>
       <c r="BW5" t="s">
+        <v>213</v>
+      </c>
+      <c r="BX5" t="s">
         <v>214</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>215</v>
       </c>
       <c r="BY5" t="s">
         <v>27</v>
@@ -10162,13 +10162,13 @@
         <v>202</v>
       </c>
       <c r="CG5" t="s">
+        <v>215</v>
+      </c>
+      <c r="CH5" t="s">
         <v>216</v>
       </c>
-      <c r="CH5" t="s">
+      <c r="CI5" t="s">
         <v>217</v>
-      </c>
-      <c r="CI5" t="s">
-        <v>218</v>
       </c>
       <c r="CJ5" t="s">
         <v>172</v>
@@ -10177,7 +10177,7 @@
         <v>173</v>
       </c>
       <c r="CL5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CM5" t="s">
         <v>175</v>
@@ -10213,7 +10213,7 @@
         <v>2.77</v>
       </c>
       <c r="CX5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CY5">
         <v>85.99</v>
@@ -10225,7 +10225,7 @@
         <v>84.44</v>
       </c>
       <c r="DB5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="DC5" t="s">
         <v>153</v>
@@ -10242,16 +10242,16 @@
         <v>179</v>
       </c>
       <c r="D6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E6" t="s">
         <v>222</v>
-      </c>
-      <c r="E6" t="s">
-        <v>223</v>
       </c>
       <c r="F6" t="s">
         <v>149</v>
       </c>
       <c r="G6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H6" t="s">
         <v>182</v>
@@ -10350,7 +10350,7 @@
         <v>170.76</v>
       </c>
       <c r="AN6">
-        <v>91.14</v>
+        <v>97.28</v>
       </c>
       <c r="AO6">
         <v>1974.43</v>
@@ -10358,11 +10358,11 @@
       <c r="AP6">
         <v>2014.24</v>
       </c>
-      <c r="AQ6" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>153</v>
+      <c r="AQ6">
+        <v>2058.60009765625</v>
+      </c>
+      <c r="AR6">
+        <v>1919.3071735958158</v>
       </c>
       <c r="AS6" t="s">
         <v>154</v>
@@ -10404,7 +10404,7 @@
         <v>-1561.2</v>
       </c>
       <c r="BF6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BG6" t="s">
         <v>153</v>
@@ -10425,7 +10425,7 @@
         <v>156</v>
       </c>
       <c r="BM6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="BN6">
         <v>1</v>
@@ -10449,13 +10449,13 @@
         <v>4</v>
       </c>
       <c r="BU6" t="s">
+        <v>226</v>
+      </c>
+      <c r="BV6" t="s">
         <v>227</v>
       </c>
-      <c r="BV6" t="s">
+      <c r="BW6" t="s">
         <v>228</v>
-      </c>
-      <c r="BW6" t="s">
-        <v>229</v>
       </c>
       <c r="BX6" t="s">
         <v>153</v>
@@ -10467,10 +10467,10 @@
         <v>153</v>
       </c>
       <c r="CA6" t="s">
+        <v>229</v>
+      </c>
+      <c r="CB6" t="s">
         <v>230</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>231</v>
       </c>
       <c r="CC6" t="s">
         <v>165</v>
@@ -10485,13 +10485,13 @@
         <v>188</v>
       </c>
       <c r="CG6" t="s">
+        <v>231</v>
+      </c>
+      <c r="CH6" t="s">
         <v>232</v>
       </c>
-      <c r="CH6" t="s">
+      <c r="CI6" t="s">
         <v>233</v>
-      </c>
-      <c r="CI6" t="s">
-        <v>234</v>
       </c>
       <c r="CJ6" t="s">
         <v>192</v>
@@ -10500,7 +10500,7 @@
         <v>173</v>
       </c>
       <c r="CL6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="CM6" t="s">
         <v>175</v>
@@ -10548,7 +10548,7 @@
         <v>1981</v>
       </c>
       <c r="DB6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="DC6" t="s">
         <v>153</v>
@@ -10565,16 +10565,16 @@
         <v>179</v>
       </c>
       <c r="D7" t="s">
+        <v>236</v>
+      </c>
+      <c r="E7" t="s">
         <v>237</v>
-      </c>
-      <c r="E7" t="s">
-        <v>238</v>
       </c>
       <c r="F7" t="s">
         <v>149</v>
       </c>
       <c r="G7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H7" t="s">
         <v>182</v>
@@ -10673,7 +10673,7 @@
         <v>167.02</v>
       </c>
       <c r="AN7">
-        <v>75.72</v>
+        <v>81.87</v>
       </c>
       <c r="AO7">
         <v>4319.5</v>
@@ -10681,11 +10681,11 @@
       <c r="AP7">
         <v>4352.73</v>
       </c>
-      <c r="AQ7" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>153</v>
+      <c r="AQ7">
+        <v>4452</v>
+      </c>
+      <c r="AR7">
+        <v>4279.016498604705</v>
       </c>
       <c r="AS7" t="s">
         <v>154</v>
@@ -10727,7 +10727,7 @@
         <v>0</v>
       </c>
       <c r="BF7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="BG7" t="s">
         <v>153</v>
@@ -10748,19 +10748,19 @@
         <v>156</v>
       </c>
       <c r="BM7" t="s">
+        <v>239</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>153</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>153</v>
+      </c>
+      <c r="BQ7" t="s">
         <v>240</v>
-      </c>
-      <c r="BN7">
-        <v>0</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>153</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>153</v>
-      </c>
-      <c r="BQ7" t="s">
-        <v>241</v>
       </c>
       <c r="BR7" t="s">
         <v>160</v>
@@ -10772,10 +10772,10 @@
         <v>1</v>
       </c>
       <c r="BU7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BW7" t="s">
         <v>153</v>
@@ -10808,13 +10808,13 @@
         <v>188</v>
       </c>
       <c r="CG7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CH7" t="s">
+        <v>242</v>
+      </c>
+      <c r="CI7" t="s">
         <v>243</v>
-      </c>
-      <c r="CI7" t="s">
-        <v>244</v>
       </c>
       <c r="CJ7" t="s">
         <v>192</v>
@@ -10823,7 +10823,7 @@
         <v>173</v>
       </c>
       <c r="CL7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="CM7" t="s">
         <v>175</v>
@@ -10871,7 +10871,7 @@
         <v>4319.5</v>
       </c>
       <c r="DB7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="DC7" t="s">
         <v>153</v>
@@ -10888,16 +10888,16 @@
         <v>179</v>
       </c>
       <c r="D8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E8" t="s">
         <v>246</v>
-      </c>
-      <c r="E8" t="s">
-        <v>247</v>
       </c>
       <c r="F8" t="s">
         <v>149</v>
       </c>
       <c r="G8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H8" t="s">
         <v>182</v>
@@ -11011,7 +11011,7 @@
         <v>174.58772588109068</v>
       </c>
       <c r="AS8" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="AT8">
         <v>5109.96</v>
@@ -11050,7 +11050,7 @@
         <v>-867.1</v>
       </c>
       <c r="BF8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="BG8" t="s">
         <v>153</v>
@@ -11071,7 +11071,7 @@
         <v>156</v>
       </c>
       <c r="BM8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="BN8">
         <v>0</v>
@@ -11095,10 +11095,10 @@
         <v>4</v>
       </c>
       <c r="BU8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BW8" t="s">
         <v>153</v>
@@ -11131,13 +11131,13 @@
         <v>188</v>
       </c>
       <c r="CG8" t="s">
+        <v>249</v>
+      </c>
+      <c r="CH8" t="s">
         <v>250</v>
       </c>
-      <c r="CH8" t="s">
+      <c r="CI8" t="s">
         <v>251</v>
-      </c>
-      <c r="CI8" t="s">
-        <v>252</v>
       </c>
       <c r="CJ8" t="s">
         <v>192</v>
@@ -11146,7 +11146,7 @@
         <v>173</v>
       </c>
       <c r="CL8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="CM8" t="s">
         <v>175</v>
@@ -11182,7 +11182,7 @@
         <v>0.55</v>
       </c>
       <c r="CX8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CY8">
         <v>199.5</v>
@@ -11194,7 +11194,7 @@
         <v>186.53</v>
       </c>
       <c r="DB8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="DC8" t="s">
         <v>153</v>
@@ -11211,16 +11211,16 @@
         <v>179</v>
       </c>
       <c r="D9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" t="s">
         <v>254</v>
-      </c>
-      <c r="E9" t="s">
-        <v>255</v>
       </c>
       <c r="F9" t="s">
         <v>149</v>
       </c>
       <c r="G9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H9" t="s">
         <v>182</v>
@@ -11319,7 +11319,7 @@
         <v>131.92</v>
       </c>
       <c r="AN9">
-        <v>103.8</v>
+        <v>109.94</v>
       </c>
       <c r="AO9">
         <v>8955.5</v>
@@ -11327,11 +11327,11 @@
       <c r="AP9">
         <v>9071</v>
       </c>
-      <c r="AQ9" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>153</v>
+      <c r="AQ9">
+        <v>9301</v>
+      </c>
+      <c r="AR9">
+        <v>8773.801138101968</v>
       </c>
       <c r="AS9" t="s">
         <v>154</v>
@@ -11373,7 +11373,7 @@
         <v>-162.5</v>
       </c>
       <c r="BF9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="BG9" t="s">
         <v>153</v>
@@ -11394,7 +11394,7 @@
         <v>156</v>
       </c>
       <c r="BM9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="BN9">
         <v>0</v>
@@ -11409,7 +11409,7 @@
         <v>185</v>
       </c>
       <c r="BR9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BS9">
         <v>10</v>
@@ -11421,13 +11421,13 @@
         <v>161</v>
       </c>
       <c r="BV9" t="s">
+        <v>257</v>
+      </c>
+      <c r="BW9" t="s">
         <v>258</v>
       </c>
-      <c r="BW9" t="s">
+      <c r="BX9" t="s">
         <v>259</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>260</v>
       </c>
       <c r="BY9" t="s">
         <v>27</v>
@@ -11436,7 +11436,7 @@
         <v>153</v>
       </c>
       <c r="CA9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="CB9" t="s">
         <v>153</v>
@@ -11454,13 +11454,13 @@
         <v>188</v>
       </c>
       <c r="CG9" t="s">
+        <v>261</v>
+      </c>
+      <c r="CH9" t="s">
         <v>262</v>
       </c>
-      <c r="CH9" t="s">
+      <c r="CI9" t="s">
         <v>263</v>
-      </c>
-      <c r="CI9" t="s">
-        <v>264</v>
       </c>
       <c r="CJ9" t="s">
         <v>172</v>
@@ -11469,7 +11469,7 @@
         <v>173</v>
       </c>
       <c r="CL9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="CM9" t="s">
         <v>175</v>
@@ -11505,7 +11505,7 @@
         <v>0.1</v>
       </c>
       <c r="CX9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CY9">
         <v>9100</v>
@@ -11517,7 +11517,7 @@
         <v>8955.5</v>
       </c>
       <c r="DB9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="DC9" t="s">
         <v>153</v>
@@ -11528,25 +11528,25 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C10" t="s">
         <v>209</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F10" t="s">
         <v>149</v>
       </c>
       <c r="G10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I10" t="s">
         <v>47</v>
@@ -11642,7 +11642,7 @@
         <v>153</v>
       </c>
       <c r="AN10">
-        <v>85.95</v>
+        <v>92.09</v>
       </c>
       <c r="AO10">
         <v>1251.2</v>
@@ -11650,11 +11650,11 @@
       <c r="AP10">
         <v>1278.43</v>
       </c>
-      <c r="AQ10" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>153</v>
+      <c r="AQ10">
+        <v>1352</v>
+      </c>
+      <c r="AR10">
+        <v>1304.032274715177</v>
       </c>
       <c r="AS10" t="s">
         <v>154</v>
@@ -11696,7 +11696,7 @@
         <v>-1476</v>
       </c>
       <c r="BF10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="BG10" t="s">
         <v>153</v>
@@ -11717,7 +11717,7 @@
         <v>156</v>
       </c>
       <c r="BM10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="BN10">
         <v>1</v>
@@ -11741,7 +11741,7 @@
         <v>4</v>
       </c>
       <c r="BU10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV10" t="s">
         <v>153</v>
@@ -11777,22 +11777,22 @@
         <v>188</v>
       </c>
       <c r="CG10" t="s">
+        <v>271</v>
+      </c>
+      <c r="CH10" t="s">
         <v>272</v>
       </c>
-      <c r="CH10" t="s">
+      <c r="CI10" t="s">
         <v>273</v>
       </c>
-      <c r="CI10" t="s">
+      <c r="CJ10" t="s">
         <v>274</v>
       </c>
-      <c r="CJ10" t="s">
+      <c r="CK10" t="s">
         <v>275</v>
       </c>
-      <c r="CK10" t="s">
+      <c r="CL10" t="s">
         <v>276</v>
-      </c>
-      <c r="CL10" t="s">
-        <v>277</v>
       </c>
       <c r="CM10" t="s">
         <v>175</v>
@@ -11828,7 +11828,7 @@
         <v>153</v>
       </c>
       <c r="CX10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="CY10">
         <v>1321</v>
@@ -11840,7 +11840,7 @@
         <v>1321</v>
       </c>
       <c r="DB10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="DC10" t="s">
         <v>153</v>
@@ -11851,25 +11851,25 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C11" t="s">
         <v>147</v>
       </c>
       <c r="D11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F11" t="s">
         <v>149</v>
       </c>
       <c r="G11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I11" t="s">
         <v>47</v>
@@ -11980,7 +11980,7 @@
         <v>398.6403308636572</v>
       </c>
       <c r="AS11" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="AT11">
         <v>7813.56</v>
@@ -12019,7 +12019,7 @@
         <v>-501.6</v>
       </c>
       <c r="BF11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="BG11" t="s">
         <v>153</v>
@@ -12040,13 +12040,13 @@
         <v>156</v>
       </c>
       <c r="BM11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="BN11">
         <v>0</v>
       </c>
       <c r="BO11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="BP11" t="s">
         <v>153</v>
@@ -12064,7 +12064,7 @@
         <v>5</v>
       </c>
       <c r="BU11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV11" t="s">
         <v>153</v>
@@ -12100,22 +12100,22 @@
         <v>188</v>
       </c>
       <c r="CG11" t="s">
+        <v>282</v>
+      </c>
+      <c r="CH11" t="s">
         <v>283</v>
       </c>
-      <c r="CH11" t="s">
+      <c r="CI11" t="s">
         <v>284</v>
       </c>
-      <c r="CI11" t="s">
-        <v>285</v>
-      </c>
       <c r="CJ11" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK11" t="s">
         <v>275</v>
       </c>
-      <c r="CK11" t="s">
+      <c r="CL11" t="s">
         <v>276</v>
-      </c>
-      <c r="CL11" t="s">
-        <v>277</v>
       </c>
       <c r="CM11" t="s">
         <v>175</v>
@@ -12151,7 +12151,7 @@
         <v>153</v>
       </c>
       <c r="CX11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CY11">
         <v>425.45</v>
@@ -12163,7 +12163,7 @@
         <v>422.15</v>
       </c>
       <c r="DB11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="DC11" t="s">
         <v>153</v>
@@ -12174,25 +12174,25 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C12" t="s">
         <v>147</v>
       </c>
       <c r="D12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F12" t="s">
         <v>149</v>
       </c>
       <c r="G12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I12" t="s">
         <v>47</v>
@@ -12288,7 +12288,7 @@
         <v>153</v>
       </c>
       <c r="AN12">
-        <v>198.61</v>
+        <v>204.75</v>
       </c>
       <c r="AO12">
         <v>6083.5</v>
@@ -12296,11 +12296,11 @@
       <c r="AP12">
         <v>6359.98</v>
       </c>
-      <c r="AQ12" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>153</v>
+      <c r="AQ12">
+        <v>6839</v>
+      </c>
+      <c r="AR12">
+        <v>5977.839360894776</v>
       </c>
       <c r="AS12" t="s">
         <v>154</v>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BG12" t="s">
         <v>153</v>
@@ -12387,7 +12387,7 @@
         <v>4</v>
       </c>
       <c r="BU12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV12" t="s">
         <v>153</v>
@@ -12423,22 +12423,22 @@
         <v>188</v>
       </c>
       <c r="CG12" t="s">
+        <v>288</v>
+      </c>
+      <c r="CH12" t="s">
         <v>289</v>
       </c>
-      <c r="CH12" t="s">
+      <c r="CI12" t="s">
         <v>290</v>
       </c>
-      <c r="CI12" t="s">
-        <v>291</v>
-      </c>
       <c r="CJ12" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK12" t="s">
         <v>275</v>
       </c>
-      <c r="CK12" t="s">
+      <c r="CL12" t="s">
         <v>276</v>
-      </c>
-      <c r="CL12" t="s">
-        <v>277</v>
       </c>
       <c r="CM12" t="s">
         <v>175</v>
@@ -12486,7 +12486,7 @@
         <v>6202.5</v>
       </c>
       <c r="DB12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="DC12" t="s">
         <v>153</v>
@@ -12497,25 +12497,25 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C13" t="s">
         <v>209</v>
       </c>
       <c r="D13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F13" t="s">
         <v>149</v>
       </c>
       <c r="G13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I13" t="s">
         <v>47</v>
@@ -12611,7 +12611,7 @@
         <v>153</v>
       </c>
       <c r="AN13">
-        <v>178.82</v>
+        <v>186.47</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -12619,11 +12619,11 @@
       <c r="AP13">
         <v>1968</v>
       </c>
-      <c r="AQ13" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>153</v>
+      <c r="AQ13">
+        <v>2027.300048828125</v>
+      </c>
+      <c r="AR13">
+        <v>1900.2560938383647</v>
       </c>
       <c r="AS13" t="s">
         <v>154</v>
@@ -12665,7 +12665,7 @@
         <v>0</v>
       </c>
       <c r="BF13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BG13" t="s">
         <v>153</v>
@@ -12710,7 +12710,7 @@
         <v>3</v>
       </c>
       <c r="BU13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV13" t="s">
         <v>153</v>
@@ -12746,22 +12746,22 @@
         <v>188</v>
       </c>
       <c r="CG13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="CH13" t="s">
+        <v>294</v>
+      </c>
+      <c r="CI13" t="s">
         <v>295</v>
       </c>
-      <c r="CI13" t="s">
-        <v>296</v>
-      </c>
       <c r="CJ13" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK13" t="s">
         <v>275</v>
       </c>
-      <c r="CK13" t="s">
+      <c r="CL13" t="s">
         <v>276</v>
-      </c>
-      <c r="CL13" t="s">
-        <v>277</v>
       </c>
       <c r="CM13" t="s">
         <v>175</v>
@@ -12797,7 +12797,7 @@
         <v>153</v>
       </c>
       <c r="CX13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CY13">
         <v>1957</v>
@@ -12809,7 +12809,7 @@
         <v>1957</v>
       </c>
       <c r="DB13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="DC13" t="s">
         <v>153</v>
@@ -12820,25 +12820,25 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C14" t="s">
         <v>209</v>
       </c>
       <c r="D14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F14" t="s">
         <v>149</v>
       </c>
       <c r="G14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I14" t="s">
         <v>47</v>
@@ -12934,7 +12934,7 @@
         <v>153</v>
       </c>
       <c r="AN14">
-        <v>192.39</v>
+        <v>200.04</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -12942,11 +12942,11 @@
       <c r="AP14">
         <v>1324.8</v>
       </c>
-      <c r="AQ14" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>153</v>
+      <c r="AQ14">
+        <v>1389.0999755859375</v>
+      </c>
+      <c r="AR14">
+        <v>1270.5608205128772</v>
       </c>
       <c r="AS14" t="s">
         <v>154</v>
@@ -12988,7 +12988,7 @@
         <v>0</v>
       </c>
       <c r="BF14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BG14" t="s">
         <v>153</v>
@@ -13033,7 +13033,7 @@
         <v>4</v>
       </c>
       <c r="BU14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV14" t="s">
         <v>153</v>
@@ -13069,22 +13069,22 @@
         <v>188</v>
       </c>
       <c r="CG14" t="s">
+        <v>299</v>
+      </c>
+      <c r="CH14" t="s">
         <v>300</v>
       </c>
-      <c r="CH14" t="s">
+      <c r="CI14" t="s">
         <v>301</v>
       </c>
-      <c r="CI14" t="s">
-        <v>302</v>
-      </c>
       <c r="CJ14" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK14" t="s">
         <v>275</v>
       </c>
-      <c r="CK14" t="s">
+      <c r="CL14" t="s">
         <v>276</v>
-      </c>
-      <c r="CL14" t="s">
-        <v>277</v>
       </c>
       <c r="CM14" t="s">
         <v>175</v>
@@ -13132,7 +13132,7 @@
         <v>1303.2</v>
       </c>
       <c r="DB14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="DC14" t="s">
         <v>153</v>
@@ -13143,25 +13143,25 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C15" t="s">
         <v>147</v>
       </c>
       <c r="D15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F15" t="s">
         <v>149</v>
       </c>
       <c r="G15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I15" t="s">
         <v>47</v>
@@ -13257,7 +13257,7 @@
         <v>153</v>
       </c>
       <c r="AN15">
-        <v>187.86</v>
+        <v>194.01</v>
       </c>
       <c r="AO15">
         <v>771.79</v>
@@ -13265,11 +13265,11 @@
       <c r="AP15">
         <v>771.79</v>
       </c>
-      <c r="AQ15" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>153</v>
+      <c r="AQ15">
+        <v>809.9500122070312</v>
+      </c>
+      <c r="AR15">
+        <v>695.4346801872446</v>
       </c>
       <c r="AS15" t="s">
         <v>154</v>
@@ -13311,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="BF15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="BG15" t="s">
         <v>153</v>
@@ -13356,7 +13356,7 @@
         <v>3</v>
       </c>
       <c r="BU15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV15" t="s">
         <v>153</v>
@@ -13392,22 +13392,22 @@
         <v>188</v>
       </c>
       <c r="CG15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="CH15" t="s">
+        <v>305</v>
+      </c>
+      <c r="CI15" t="s">
         <v>306</v>
       </c>
-      <c r="CI15" t="s">
-        <v>307</v>
-      </c>
       <c r="CJ15" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK15" t="s">
         <v>275</v>
       </c>
-      <c r="CK15" t="s">
+      <c r="CL15" t="s">
         <v>276</v>
-      </c>
-      <c r="CL15" t="s">
-        <v>277</v>
       </c>
       <c r="CM15" t="s">
         <v>175</v>
@@ -13455,7 +13455,7 @@
         <v>721.4</v>
       </c>
       <c r="DB15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="DC15" t="s">
         <v>153</v>
@@ -13466,25 +13466,25 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C16" t="s">
         <v>147</v>
       </c>
       <c r="D16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F16" t="s">
         <v>149</v>
       </c>
       <c r="G16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I16" t="s">
         <v>47</v>
@@ -13580,7 +13580,7 @@
         <v>153</v>
       </c>
       <c r="AN16">
-        <v>86.56</v>
+        <v>92.7</v>
       </c>
       <c r="AO16">
         <v>2728.17</v>
@@ -13588,11 +13588,11 @@
       <c r="AP16">
         <v>2882.7</v>
       </c>
-      <c r="AQ16" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR16" t="s">
-        <v>153</v>
+      <c r="AQ16">
+        <v>2983.199951171875</v>
+      </c>
+      <c r="AR16">
+        <v>2827.406442040053</v>
       </c>
       <c r="AS16" t="s">
         <v>154</v>
@@ -13634,7 +13634,7 @@
         <v>54.4</v>
       </c>
       <c r="BF16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="BG16" t="s">
         <v>153</v>
@@ -13679,7 +13679,7 @@
         <v>3</v>
       </c>
       <c r="BU16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV16" t="s">
         <v>153</v>
@@ -13715,22 +13715,22 @@
         <v>188</v>
       </c>
       <c r="CG16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="CH16" t="s">
+        <v>310</v>
+      </c>
+      <c r="CI16" t="s">
         <v>311</v>
       </c>
-      <c r="CI16" t="s">
-        <v>312</v>
-      </c>
       <c r="CJ16" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK16" t="s">
         <v>275</v>
       </c>
-      <c r="CK16" t="s">
+      <c r="CL16" t="s">
         <v>276</v>
-      </c>
-      <c r="CL16" t="s">
-        <v>277</v>
       </c>
       <c r="CM16" t="s">
         <v>175</v>
@@ -13766,7 +13766,7 @@
         <v>153</v>
       </c>
       <c r="CX16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="CY16">
         <v>2903.2</v>
@@ -13778,7 +13778,7 @@
         <v>2903.2</v>
       </c>
       <c r="DB16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="DC16" t="s">
         <v>153</v>
@@ -13792,19 +13792,19 @@
         <v>41</v>
       </c>
       <c r="C17" t="s">
+        <v>313</v>
+      </c>
+      <c r="D17" t="s">
         <v>314</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F17" t="s">
         <v>315</v>
       </c>
-      <c r="E17" t="s">
-        <v>315</v>
-      </c>
-      <c r="F17" t="s">
-        <v>316</v>
-      </c>
       <c r="G17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H17" t="s">
         <v>182</v>
@@ -13813,7 +13813,7 @@
         <v>47</v>
       </c>
       <c r="J17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K17">
         <v>19.59</v>
@@ -13822,7 +13822,7 @@
         <v>19.59</v>
       </c>
       <c r="M17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N17">
         <v>16</v>
@@ -13897,7 +13897,7 @@
         <v>2</v>
       </c>
       <c r="AL17" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AM17">
         <v>168.93</v>
@@ -13918,7 +13918,7 @@
         <v>153</v>
       </c>
       <c r="AS17" t="s">
-        <v>154</v>
+        <v>319</v>
       </c>
       <c r="AT17">
         <v>17.98</v>
@@ -14053,7 +14053,7 @@
         <v>173</v>
       </c>
       <c r="CL17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CM17" t="s">
         <v>27</v>
@@ -14127,7 +14127,7 @@
         <v>331</v>
       </c>
       <c r="G18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H18" t="s">
         <v>153</v>
@@ -14241,7 +14241,7 @@
         <v>153</v>
       </c>
       <c r="AS18" t="s">
-        <v>154</v>
+        <v>319</v>
       </c>
       <c r="AT18" t="s">
         <v>153</v>
@@ -14313,7 +14313,7 @@
         <v>153</v>
       </c>
       <c r="BQ18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="BR18" t="s">
         <v>160</v>
@@ -14370,10 +14370,10 @@
         <v>339</v>
       </c>
       <c r="CJ18" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK18" t="s">
         <v>275</v>
-      </c>
-      <c r="CK18" t="s">
-        <v>276</v>
       </c>
       <c r="CL18" t="s">
         <v>340</v>
@@ -14450,7 +14450,7 @@
         <v>331</v>
       </c>
       <c r="G19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H19" t="s">
         <v>153</v>
@@ -14564,7 +14564,7 @@
         <v>153</v>
       </c>
       <c r="AS19" t="s">
-        <v>154</v>
+        <v>319</v>
       </c>
       <c r="AT19" t="s">
         <v>153</v>
@@ -14693,10 +14693,10 @@
         <v>346</v>
       </c>
       <c r="CJ19" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK19" t="s">
         <v>275</v>
-      </c>
-      <c r="CK19" t="s">
-        <v>276</v>
       </c>
       <c r="CL19" t="s">
         <v>340</v>
@@ -14773,7 +14773,7 @@
         <v>331</v>
       </c>
       <c r="G20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H20" t="s">
         <v>153</v>
@@ -14887,7 +14887,7 @@
         <v>153</v>
       </c>
       <c r="AS20" t="s">
-        <v>154</v>
+        <v>319</v>
       </c>
       <c r="AT20" t="s">
         <v>153</v>
@@ -14962,7 +14962,7 @@
         <v>185</v>
       </c>
       <c r="BR20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BS20">
         <v>12</v>
@@ -14971,7 +14971,7 @@
         <v>2</v>
       </c>
       <c r="BU20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BV20" t="s">
         <v>153</v>
@@ -15016,10 +15016,10 @@
         <v>351</v>
       </c>
       <c r="CJ20" t="s">
+        <v>274</v>
+      </c>
+      <c r="CK20" t="s">
         <v>275</v>
-      </c>
-      <c r="CK20" t="s">
-        <v>276</v>
       </c>
       <c r="CL20" t="s">
         <v>340</v>
@@ -15416,7 +15416,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B6" t="s">
         <v>371</v>
@@ -15478,7 +15478,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B7" t="s">
         <v>373</v>
@@ -15540,7 +15540,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B8" t="s">
         <v>373</v>
@@ -15602,7 +15602,7 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B9" t="s">
         <v>373</v>
@@ -15664,7 +15664,7 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B10" t="s">
         <v>371</v>
@@ -15726,7 +15726,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B11" t="s">
         <v>371</v>
@@ -15788,7 +15788,7 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B12" t="s">
         <v>373</v>
@@ -15850,7 +15850,7 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B13" t="s">
         <v>371</v>
@@ -15912,7 +15912,7 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B14" t="s">
         <v>373</v>
@@ -15974,7 +15974,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B15" t="s">
         <v>371</v>
@@ -15983,7 +15983,7 @@
         <v>372</v>
       </c>
       <c r="D15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E15" t="s">
         <v>47</v>
@@ -16036,7 +16036,7 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B16" t="s">
         <v>373</v>
@@ -16098,7 +16098,7 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B17" t="s">
         <v>373</v>
@@ -16160,7 +16160,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B18" t="s">
         <v>371</v>
@@ -16169,7 +16169,7 @@
         <v>372</v>
       </c>
       <c r="D18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E18" t="s">
         <v>47</v>
@@ -16222,7 +16222,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B19" t="s">
         <v>373</v>
@@ -16284,7 +16284,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B20" t="s">
         <v>371</v>
@@ -16293,7 +16293,7 @@
         <v>372</v>
       </c>
       <c r="D20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E20" t="s">
         <v>47</v>
@@ -16346,7 +16346,7 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B21" t="s">
         <v>371</v>
@@ -16355,7 +16355,7 @@
         <v>372</v>
       </c>
       <c r="D21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E21" t="s">
         <v>47</v>
@@ -16408,7 +16408,7 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B22" t="s">
         <v>371</v>
@@ -16417,7 +16417,7 @@
         <v>372</v>
       </c>
       <c r="D22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E22" t="s">
         <v>47</v>
@@ -16470,7 +16470,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B23" t="s">
         <v>371</v>
@@ -16479,7 +16479,7 @@
         <v>372</v>
       </c>
       <c r="D23" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E23" t="s">
         <v>47</v>
@@ -16532,7 +16532,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B24" t="s">
         <v>371</v>
@@ -16541,7 +16541,7 @@
         <v>372</v>
       </c>
       <c r="D24" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E24" t="s">
         <v>47</v>
@@ -16594,7 +16594,7 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B25" t="s">
         <v>373</v>
@@ -16656,7 +16656,7 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B26" t="s">
         <v>371</v>
@@ -16718,7 +16718,7 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B27" t="s">
         <v>373</v>
@@ -16780,7 +16780,7 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s">
         <v>322</v>
@@ -16937,7 +16937,7 @@
         <v>160</v>
       </c>
       <c r="F2">
-        <v>215.69</v>
+        <v>223.34</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -16955,7 +16955,7 @@
         <v>1.86</v>
       </c>
       <c r="L2">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="M2" t="s">
         <v>159</v>
@@ -16990,7 +16990,7 @@
         <v>160</v>
       </c>
       <c r="F3">
-        <v>211.35</v>
+        <v>218.99</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -17008,7 +17008,7 @@
         <v>1.26</v>
       </c>
       <c r="L3">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="M3" t="s">
         <v>185</v>
@@ -17043,7 +17043,7 @@
         <v>160</v>
       </c>
       <c r="F4">
-        <v>201.41</v>
+        <v>209.06</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -17061,10 +17061,10 @@
         <v>0.77</v>
       </c>
       <c r="L4">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N4">
         <v>62565</v>
@@ -17096,7 +17096,7 @@
         <v>160</v>
       </c>
       <c r="F5">
-        <v>196.95</v>
+        <v>204.6</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -17114,7 +17114,7 @@
         <v>3.64</v>
       </c>
       <c r="L5">
-        <v>6.88</v>
+        <v>0</v>
       </c>
       <c r="M5" t="s">
         <v>185</v>
@@ -17149,7 +17149,7 @@
         <v>160</v>
       </c>
       <c r="F6">
-        <v>195.48</v>
+        <v>203.12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -17167,7 +17167,7 @@
         <v>3.2</v>
       </c>
       <c r="L6">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M6" t="s">
         <v>402</v>
@@ -17202,7 +17202,7 @@
         <v>160</v>
       </c>
       <c r="F7">
-        <v>195.4</v>
+        <v>203.05</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -17220,7 +17220,7 @@
         <v>2.41</v>
       </c>
       <c r="L7">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="M7" t="s">
         <v>159</v>
@@ -17255,7 +17255,7 @@
         <v>160</v>
       </c>
       <c r="F8">
-        <v>195.26</v>
+        <v>202.9</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -17273,7 +17273,7 @@
         <v>1.44</v>
       </c>
       <c r="L8">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="M8" t="s">
         <v>402</v>
@@ -17308,7 +17308,7 @@
         <v>160</v>
       </c>
       <c r="F9">
-        <v>194.87</v>
+        <v>202.51</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -17326,7 +17326,7 @@
         <v>1.88</v>
       </c>
       <c r="L9">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="M9" t="s">
         <v>407</v>
@@ -17361,7 +17361,7 @@
         <v>160</v>
       </c>
       <c r="F10">
-        <v>191.35</v>
+        <v>190.71</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -17379,7 +17379,7 @@
         <v>0.46</v>
       </c>
       <c r="L10">
-        <v>2.38</v>
+        <v>3.02</v>
       </c>
       <c r="M10" t="s">
         <v>409</v>
@@ -17467,7 +17467,7 @@
         <v>160</v>
       </c>
       <c r="F12">
-        <v>175.68</v>
+        <v>183.32</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -17485,7 +17485,7 @@
         <v>1.76</v>
       </c>
       <c r="L12">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
         <v>407</v>
@@ -17520,7 +17520,7 @@
         <v>160</v>
       </c>
       <c r="F13">
-        <v>171.95</v>
+        <v>179.6</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -17538,7 +17538,7 @@
         <v>1.12</v>
       </c>
       <c r="L13">
-        <v>15.53</v>
+        <v>7.88</v>
       </c>
       <c r="M13" t="s">
         <v>185</v>
@@ -17573,7 +17573,7 @@
         <v>160</v>
       </c>
       <c r="F14">
-        <v>171.41</v>
+        <v>179.06</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -17591,10 +17591,10 @@
         <v>1.91</v>
       </c>
       <c r="L14">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N14">
         <v>49092</v>
@@ -17626,7 +17626,7 @@
         <v>160</v>
       </c>
       <c r="F15">
-        <v>164.95</v>
+        <v>172.59</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -17644,7 +17644,7 @@
         <v>1.26</v>
       </c>
       <c r="L15">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="s">
         <v>185</v>
@@ -17679,7 +17679,7 @@
         <v>160</v>
       </c>
       <c r="F16">
-        <v>160.98</v>
+        <v>168.63</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -17697,7 +17697,7 @@
         <v>0.33</v>
       </c>
       <c r="L16">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="M16" t="s">
         <v>185</v>
@@ -18003,7 +18003,7 @@
         <v>429</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C6" t="s">
         <v>396</v>
@@ -18012,7 +18012,7 @@
         <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F6">
         <v>637.9000244140625</v>
@@ -18056,7 +18056,7 @@
         <v>429</v>
       </c>
       <c r="B7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" t="s">
         <v>412</v>
@@ -18065,7 +18065,7 @@
         <v>399</v>
       </c>
       <c r="E7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F7">
         <v>814.9000244140625</v>
@@ -18109,7 +18109,7 @@
         <v>430</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C8" t="s">
         <v>396</v>
@@ -18118,7 +18118,7 @@
         <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F8">
         <v>637.9000244140625</v>
@@ -18162,7 +18162,7 @@
         <v>430</v>
       </c>
       <c r="B9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C9" t="s">
         <v>412</v>
@@ -18171,7 +18171,7 @@
         <v>399</v>
       </c>
       <c r="E9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F9">
         <v>814.9000244140625</v>
@@ -19776,7 +19776,7 @@
         <v>160</v>
       </c>
       <c r="J39">
-        <v>215.69</v>
+        <v>223.34</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -19791,7 +19791,7 @@
         <v>1.86</v>
       </c>
       <c r="O39">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="P39">
         <v>1</v>
@@ -19829,7 +19829,7 @@
         <v>160</v>
       </c>
       <c r="J40">
-        <v>211.35</v>
+        <v>218.99</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -19844,7 +19844,7 @@
         <v>1.26</v>
       </c>
       <c r="O40">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="P40">
         <v>1</v>
@@ -19882,7 +19882,7 @@
         <v>160</v>
       </c>
       <c r="J41">
-        <v>201.41</v>
+        <v>209.06</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -19897,7 +19897,7 @@
         <v>0.77</v>
       </c>
       <c r="O41">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="P41">
         <v>1</v>
@@ -19935,7 +19935,7 @@
         <v>160</v>
       </c>
       <c r="J42">
-        <v>195.26</v>
+        <v>202.9</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -19950,7 +19950,7 @@
         <v>1.44</v>
       </c>
       <c r="O42">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="P42">
         <v>1</v>
@@ -19988,7 +19988,7 @@
         <v>160</v>
       </c>
       <c r="J43">
-        <v>194.87</v>
+        <v>202.51</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -20003,7 +20003,7 @@
         <v>1.88</v>
       </c>
       <c r="O43">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="P43">
         <v>1</v>
@@ -20041,7 +20041,7 @@
         <v>160</v>
       </c>
       <c r="J44">
-        <v>175.68</v>
+        <v>183.32</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -20056,7 +20056,7 @@
         <v>1.76</v>
       </c>
       <c r="O44">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="P44">
         <v>1</v>
@@ -20094,7 +20094,7 @@
         <v>160</v>
       </c>
       <c r="J45">
-        <v>164.95</v>
+        <v>172.59</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -20109,7 +20109,7 @@
         <v>1.26</v>
       </c>
       <c r="O45">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="P45">
         <v>1</v>
@@ -20147,7 +20147,7 @@
         <v>160</v>
       </c>
       <c r="J46">
-        <v>160.98</v>
+        <v>168.63</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -20162,7 +20162,7 @@
         <v>0.33</v>
       </c>
       <c r="O46">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="P46">
         <v>1</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3733" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3753" uniqueCount="457">
   <si>
     <t>Metric</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T03:46:28.273Z</t>
+    <t>2026-07-16T04:26:46.833Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1224,12 +1224,18 @@
     <t>Maximum open-position limit reached.</t>
   </si>
   <si>
+    <t>WAITING_RECONFIRMATION</t>
+  </si>
+  <si>
     <t>CJGEL</t>
   </si>
   <si>
     <t>Retracement buy near 55D high retest</t>
   </si>
   <si>
+    <t>Automated entry is blocked because 20-day average turnover Rs 30141.03 is below the compulsory liquidity standard; execution and exit costs are not reliable enough. Automated entry is blocked because requested CJGEL.NS resolved only through CJGEL.BO; exchange-consistent live and 09:17 execution coverage is required.</t>
+  </si>
+  <si>
     <t>ASTERDM</t>
   </si>
   <si>
@@ -1266,6 +1272,9 @@
     <t>KVFORGE</t>
   </si>
   <si>
+    <t>Automated entry is blocked because 20-day average turnover Rs 2202532.48 is below the compulsory liquidity standard; execution and exit costs are not reliable enough. Automated entry is blocked because requested KVFORGE.NS resolved only through KVFORGE.BO; exchange-consistent live and 09:17 execution coverage is required.</t>
+  </si>
+  <si>
     <t>YATHARTH</t>
   </si>
   <si>
@@ -1351,6 +1360,12 @@
   </si>
   <si>
     <t>2026-07-16T03:46:27.865Z</t>
+  </si>
+  <si>
+    <t>2026-07-16T04:26:46.468Z</t>
+  </si>
+  <si>
+    <t>DEFERRED</t>
   </si>
   <si>
     <t>Type</t>
@@ -6180,7 +6195,7 @@
         <v>153</v>
       </c>
       <c r="AN13">
-        <v>186.47</v>
+        <v>187.97</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -6503,7 +6518,7 @@
         <v>153</v>
       </c>
       <c r="AN14">
-        <v>200.04</v>
+        <v>201.54</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -12611,7 +12626,7 @@
         <v>153</v>
       </c>
       <c r="AN13">
-        <v>186.47</v>
+        <v>187.97</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -12934,7 +12949,7 @@
         <v>153</v>
       </c>
       <c r="AN14">
-        <v>200.04</v>
+        <v>201.54</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -16937,7 +16952,7 @@
         <v>160</v>
       </c>
       <c r="F2">
-        <v>223.34</v>
+        <v>224.84</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -16990,7 +17005,7 @@
         <v>160</v>
       </c>
       <c r="F3">
-        <v>218.99</v>
+        <v>220.49</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -17043,7 +17058,7 @@
         <v>160</v>
       </c>
       <c r="F4">
-        <v>209.06</v>
+        <v>210.56</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -17096,7 +17111,7 @@
         <v>160</v>
       </c>
       <c r="F5">
-        <v>204.6</v>
+        <v>206.1</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -17134,10 +17149,10 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
@@ -17149,7 +17164,7 @@
         <v>160</v>
       </c>
       <c r="F6">
-        <v>203.12</v>
+        <v>204.62</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -17170,7 +17185,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N6">
         <v>62659.2</v>
@@ -17182,7 +17197,7 @@
         <v>22.45</v>
       </c>
       <c r="Q6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -17190,7 +17205,7 @@
         <v>397</v>
       </c>
       <c r="B7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C7" t="s">
         <v>399</v>
@@ -17202,7 +17217,7 @@
         <v>160</v>
       </c>
       <c r="F7">
-        <v>203.05</v>
+        <v>204.55</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -17243,10 +17258,10 @@
         <v>390</v>
       </c>
       <c r="B8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C8" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D8" t="s">
         <v>151</v>
@@ -17255,7 +17270,7 @@
         <v>160</v>
       </c>
       <c r="F8">
-        <v>202.9</v>
+        <v>204.4</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -17276,7 +17291,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N8">
         <v>60416.4</v>
@@ -17296,7 +17311,7 @@
         <v>390</v>
       </c>
       <c r="B9" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C9" t="s">
         <v>39</v>
@@ -17308,7 +17323,7 @@
         <v>160</v>
       </c>
       <c r="F9">
-        <v>202.51</v>
+        <v>204.01</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -17329,7 +17344,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N9">
         <v>59860</v>
@@ -17349,10 +17364,10 @@
         <v>397</v>
       </c>
       <c r="B10" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D10" t="s">
         <v>150</v>
@@ -17382,7 +17397,7 @@
         <v>3.02</v>
       </c>
       <c r="M10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N10">
         <v>61938</v>
@@ -17402,7 +17417,7 @@
         <v>397</v>
       </c>
       <c r="B11" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C11" t="s">
         <v>39</v>
@@ -17455,7 +17470,7 @@
         <v>390</v>
       </c>
       <c r="B12" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C12" t="s">
         <v>39</v>
@@ -17467,7 +17482,7 @@
         <v>160</v>
       </c>
       <c r="F12">
-        <v>183.32</v>
+        <v>184.82</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -17488,7 +17503,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N12">
         <v>61422</v>
@@ -17508,7 +17523,7 @@
         <v>397</v>
       </c>
       <c r="B13" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C13" t="s">
         <v>399</v>
@@ -17520,7 +17535,7 @@
         <v>160</v>
       </c>
       <c r="F13">
-        <v>179.6</v>
+        <v>181.1</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -17538,7 +17553,7 @@
         <v>1.12</v>
       </c>
       <c r="L13">
-        <v>7.88</v>
+        <v>6.38</v>
       </c>
       <c r="M13" t="s">
         <v>185</v>
@@ -17561,7 +17576,7 @@
         <v>397</v>
       </c>
       <c r="B14" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C14" t="s">
         <v>39</v>
@@ -17573,7 +17588,7 @@
         <v>160</v>
       </c>
       <c r="F14">
-        <v>179.06</v>
+        <v>180.56</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -17611,10 +17626,10 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="B15" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C15" t="s">
         <v>39</v>
@@ -17626,7 +17641,7 @@
         <v>160</v>
       </c>
       <c r="F15">
-        <v>172.59</v>
+        <v>174.09</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -17659,7 +17674,7 @@
         <v>150.3</v>
       </c>
       <c r="Q15" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -17667,7 +17682,7 @@
         <v>390</v>
       </c>
       <c r="B16" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -17679,7 +17694,7 @@
         <v>160</v>
       </c>
       <c r="F16">
-        <v>168.63</v>
+        <v>170.13</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -17724,7 +17739,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -17744,10 +17759,10 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>51</v>
@@ -17756,16 +17771,16 @@
         <v>376</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>378</v>
@@ -17792,12 +17807,12 @@
         <v>380</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B2" t="s">
         <v>182</v>
@@ -17812,10 +17827,10 @@
         <v>182</v>
       </c>
       <c r="G2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I2" t="s">
         <v>160</v>
@@ -17842,18 +17857,18 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B3" t="s">
         <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D3" t="s">
         <v>39</v>
@@ -17862,10 +17877,10 @@
         <v>182</v>
       </c>
       <c r="G3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I3" t="s">
         <v>160</v>
@@ -17892,12 +17907,12 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B4" t="s">
         <v>182</v>
@@ -17906,16 +17921,16 @@
         <v>210</v>
       </c>
       <c r="D4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E4" t="s">
         <v>182</v>
       </c>
       <c r="G4" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H4" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I4" t="s">
         <v>160</v>
@@ -17942,12 +17957,12 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B5" t="s">
         <v>182</v>
@@ -17965,7 +17980,7 @@
         <v>622.5499877929688</v>
       </c>
       <c r="G5" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H5" t="s">
         <v>390</v>
@@ -18000,7 +18015,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B6" t="s">
         <v>223</v>
@@ -18018,7 +18033,7 @@
         <v>637.9000244140625</v>
       </c>
       <c r="G6" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H6" t="s">
         <v>390</v>
@@ -18053,13 +18068,13 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B7" t="s">
         <v>223</v>
       </c>
       <c r="C7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D7" t="s">
         <v>399</v>
@@ -18071,7 +18086,7 @@
         <v>814.9000244140625</v>
       </c>
       <c r="G7" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H7" t="s">
         <v>390</v>
@@ -18106,7 +18121,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B8" t="s">
         <v>223</v>
@@ -18124,10 +18139,10 @@
         <v>637.9000244140625</v>
       </c>
       <c r="G8" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H8" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I8" t="s">
         <v>160</v>
@@ -18154,18 +18169,18 @@
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B9" t="s">
         <v>223</v>
       </c>
       <c r="C9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D9" t="s">
         <v>399</v>
@@ -18177,10 +18192,10 @@
         <v>814.9000244140625</v>
       </c>
       <c r="G9" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H9" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I9" t="s">
         <v>160</v>
@@ -18207,12 +18222,12 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B10" t="s">
         <v>182</v>
@@ -18230,7 +18245,7 @@
         <v>863.5</v>
       </c>
       <c r="G10" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H10" t="s">
         <v>390</v>
@@ -18265,7 +18280,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B11" t="s">
         <v>182</v>
@@ -18283,7 +18298,7 @@
         <v>8782.5</v>
       </c>
       <c r="G11" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H11" t="s">
         <v>390</v>
@@ -18318,13 +18333,13 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B12" t="s">
         <v>182</v>
       </c>
       <c r="C12" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D12" t="s">
         <v>39</v>
@@ -18336,7 +18351,7 @@
         <v>16326</v>
       </c>
       <c r="G12" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H12" t="s">
         <v>390</v>
@@ -18371,13 +18386,13 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B13" t="s">
         <v>150</v>
       </c>
       <c r="C13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D13" t="s">
         <v>39</v>
@@ -18389,10 +18404,10 @@
         <v>23.700000762939453</v>
       </c>
       <c r="G13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H13" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I13" t="s">
         <v>160</v>
@@ -18419,18 +18434,18 @@
         <v>1</v>
       </c>
       <c r="Q13" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B14" t="s">
         <v>150</v>
       </c>
       <c r="C14" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D14" t="s">
         <v>399</v>
@@ -18442,10 +18457,10 @@
         <v>813.2000122070312</v>
       </c>
       <c r="G14" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H14" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I14" t="s">
         <v>160</v>
@@ -18472,18 +18487,18 @@
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B15" t="s">
         <v>150</v>
       </c>
       <c r="C15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D15" t="s">
         <v>399</v>
@@ -18495,10 +18510,10 @@
         <v>806.7000122070312</v>
       </c>
       <c r="G15" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H15" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I15" t="s">
         <v>160</v>
@@ -18525,18 +18540,18 @@
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B16" t="s">
         <v>182</v>
       </c>
       <c r="C16" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D16" t="s">
         <v>395</v>
@@ -18548,7 +18563,7 @@
         <v>1378.300048828125</v>
       </c>
       <c r="G16" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H16" t="s">
         <v>390</v>
@@ -18583,13 +18598,13 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B17" t="s">
         <v>182</v>
       </c>
       <c r="C17" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D17" t="s">
         <v>39</v>
@@ -18601,7 +18616,7 @@
         <v>56.9900016784668</v>
       </c>
       <c r="G17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H17" t="s">
         <v>390</v>
@@ -18636,13 +18651,13 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B18" t="s">
         <v>182</v>
       </c>
       <c r="C18" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D18" t="s">
         <v>39</v>
@@ -18654,7 +18669,7 @@
         <v>121</v>
       </c>
       <c r="G18" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H18" t="s">
         <v>390</v>
@@ -18689,13 +18704,13 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B19" t="s">
         <v>182</v>
       </c>
       <c r="C19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D19" t="s">
         <v>39</v>
@@ -18707,7 +18722,7 @@
         <v>5024</v>
       </c>
       <c r="G19" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H19" t="s">
         <v>390</v>
@@ -18742,13 +18757,13 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B20" t="s">
         <v>182</v>
       </c>
       <c r="C20" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D20" t="s">
         <v>39</v>
@@ -18760,7 +18775,7 @@
         <v>156.35000610351562</v>
       </c>
       <c r="G20" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H20" t="s">
         <v>390</v>
@@ -18795,13 +18810,13 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B21" t="s">
         <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D21" t="s">
         <v>39</v>
@@ -18813,7 +18828,7 @@
         <v>422.45001220703125</v>
       </c>
       <c r="G21" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H21" t="s">
         <v>390</v>
@@ -18848,13 +18863,13 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B22" t="s">
         <v>182</v>
       </c>
       <c r="C22" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D22" t="s">
         <v>395</v>
@@ -18866,10 +18881,10 @@
         <v>1378.300048828125</v>
       </c>
       <c r="G22" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H22" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I22" t="s">
         <v>160</v>
@@ -18896,18 +18911,18 @@
         <v>1</v>
       </c>
       <c r="Q22" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B23" t="s">
         <v>182</v>
       </c>
       <c r="C23" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D23" t="s">
         <v>39</v>
@@ -18919,10 +18934,10 @@
         <v>56.9900016784668</v>
       </c>
       <c r="G23" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H23" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I23" t="s">
         <v>160</v>
@@ -18949,18 +18964,18 @@
         <v>1</v>
       </c>
       <c r="Q23" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B24" t="s">
         <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D24" t="s">
         <v>39</v>
@@ -18972,10 +18987,10 @@
         <v>121</v>
       </c>
       <c r="G24" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H24" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I24" t="s">
         <v>160</v>
@@ -19002,18 +19017,18 @@
         <v>1</v>
       </c>
       <c r="Q24" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B25" t="s">
         <v>182</v>
       </c>
       <c r="C25" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D25" t="s">
         <v>39</v>
@@ -19025,10 +19040,10 @@
         <v>5024</v>
       </c>
       <c r="G25" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H25" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I25" t="s">
         <v>160</v>
@@ -19055,18 +19070,18 @@
         <v>1</v>
       </c>
       <c r="Q25" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B26" t="s">
         <v>182</v>
       </c>
       <c r="C26" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D26" t="s">
         <v>39</v>
@@ -19078,10 +19093,10 @@
         <v>156.35000610351562</v>
       </c>
       <c r="G26" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H26" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I26" t="s">
         <v>160</v>
@@ -19108,18 +19123,18 @@
         <v>1</v>
       </c>
       <c r="Q26" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B27" t="s">
         <v>182</v>
       </c>
       <c r="C27" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D27" t="s">
         <v>39</v>
@@ -19131,10 +19146,10 @@
         <v>422.45001220703125</v>
       </c>
       <c r="G27" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H27" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I27" t="s">
         <v>160</v>
@@ -19161,18 +19176,18 @@
         <v>1</v>
       </c>
       <c r="Q27" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B28" t="s">
         <v>182</v>
       </c>
       <c r="C28" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D28" t="s">
         <v>39</v>
@@ -19184,7 +19199,7 @@
         <v>179.52000427246094</v>
       </c>
       <c r="G28" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H28" t="s">
         <v>390</v>
@@ -19219,16 +19234,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B29" t="s">
         <v>150</v>
       </c>
       <c r="C29" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D29" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E29" t="s">
         <v>150</v>
@@ -19237,7 +19252,7 @@
         <v>10166</v>
       </c>
       <c r="G29" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H29" t="s">
         <v>390</v>
@@ -19272,13 +19287,13 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B30" t="s">
         <v>150</v>
       </c>
       <c r="C30" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D30" t="s">
         <v>39</v>
@@ -19290,7 +19305,7 @@
         <v>527.9000244140625</v>
       </c>
       <c r="G30" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H30" t="s">
         <v>390</v>
@@ -19325,7 +19340,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B31" t="s">
         <v>150</v>
@@ -19343,7 +19358,7 @@
         <v>4442.39990234375</v>
       </c>
       <c r="G31" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H31" t="s">
         <v>390</v>
@@ -19378,13 +19393,13 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B32" t="s">
         <v>150</v>
       </c>
       <c r="C32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D32" t="s">
         <v>39</v>
@@ -19396,7 +19411,7 @@
         <v>23.700000762939453</v>
       </c>
       <c r="G32" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H32" t="s">
         <v>390</v>
@@ -19431,13 +19446,13 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B33" t="s">
         <v>150</v>
       </c>
       <c r="C33" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D33" t="s">
         <v>399</v>
@@ -19449,7 +19464,7 @@
         <v>813.2000122070312</v>
       </c>
       <c r="G33" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H33" t="s">
         <v>390</v>
@@ -19484,7 +19499,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B34" t="s">
         <v>150</v>
@@ -19502,7 +19517,7 @@
         <v>739.3499755859375</v>
       </c>
       <c r="G34" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H34" t="s">
         <v>390</v>
@@ -19537,13 +19552,13 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B35" t="s">
         <v>150</v>
       </c>
       <c r="C35" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D35" t="s">
         <v>399</v>
@@ -19555,7 +19570,7 @@
         <v>806.7000122070312</v>
       </c>
       <c r="G35" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H35" t="s">
         <v>390</v>
@@ -19590,13 +19605,13 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B36" t="s">
         <v>150</v>
       </c>
       <c r="C36" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D36" t="s">
         <v>39</v>
@@ -19608,10 +19623,10 @@
         <v>527.9000244140625</v>
       </c>
       <c r="G36" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H36" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I36" t="s">
         <v>160</v>
@@ -19638,12 +19653,12 @@
         <v>1</v>
       </c>
       <c r="Q36" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B37" t="s">
         <v>150</v>
@@ -19661,10 +19676,10 @@
         <v>4442.39990234375</v>
       </c>
       <c r="G37" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H37" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I37" t="s">
         <v>160</v>
@@ -19691,12 +19706,12 @@
         <v>1</v>
       </c>
       <c r="Q37" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B38" t="s">
         <v>150</v>
@@ -19714,10 +19729,10 @@
         <v>739.3499755859375</v>
       </c>
       <c r="G38" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H38" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I38" t="s">
         <v>160</v>
@@ -19744,30 +19759,30 @@
         <v>1</v>
       </c>
       <c r="Q38" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B39" t="s">
         <v>151</v>
       </c>
       <c r="C39" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="D39" t="s">
-        <v>392</v>
+        <v>39</v>
       </c>
       <c r="E39" t="s">
         <v>151</v>
       </c>
       <c r="F39">
-        <v>1866.0999755859375</v>
+        <v>156.60000610351562</v>
       </c>
       <c r="G39" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H39" t="s">
         <v>390</v>
@@ -19776,7 +19791,7 @@
         <v>160</v>
       </c>
       <c r="J39">
-        <v>223.34</v>
+        <v>172.59</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -19785,10 +19800,10 @@
         <v>153</v>
       </c>
       <c r="M39">
-        <v>10.22</v>
+        <v>10.95</v>
       </c>
       <c r="N39">
-        <v>1.86</v>
+        <v>1.26</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -19802,25 +19817,25 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B40" t="s">
         <v>151</v>
       </c>
       <c r="C40" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D40" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E40" t="s">
         <v>151</v>
       </c>
       <c r="F40">
-        <v>417.95001220703125</v>
+        <v>1866.0999755859375</v>
       </c>
       <c r="G40" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H40" t="s">
         <v>390</v>
@@ -19829,7 +19844,7 @@
         <v>160</v>
       </c>
       <c r="J40">
-        <v>218.99</v>
+        <v>224.84</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -19838,10 +19853,10 @@
         <v>153</v>
       </c>
       <c r="M40">
-        <v>11.34</v>
+        <v>10.22</v>
       </c>
       <c r="N40">
-        <v>1.26</v>
+        <v>1.86</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -19855,25 +19870,25 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B41" t="s">
         <v>151</v>
       </c>
       <c r="C41" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>395</v>
       </c>
       <c r="E41" t="s">
         <v>151</v>
       </c>
       <c r="F41">
-        <v>625.6500244140625</v>
+        <v>417.95001220703125</v>
       </c>
       <c r="G41" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H41" t="s">
         <v>390</v>
@@ -19882,7 +19897,7 @@
         <v>160</v>
       </c>
       <c r="J41">
-        <v>209.06</v>
+        <v>220.49</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -19891,10 +19906,10 @@
         <v>153</v>
       </c>
       <c r="M41">
-        <v>3.84</v>
+        <v>11.34</v>
       </c>
       <c r="N41">
-        <v>0.77</v>
+        <v>1.26</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -19908,25 +19923,25 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B42" t="s">
         <v>151</v>
       </c>
       <c r="C42" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="D42" t="s">
-        <v>405</v>
+        <v>39</v>
       </c>
       <c r="E42" t="s">
         <v>151</v>
       </c>
       <c r="F42">
-        <v>2746.199951171875</v>
+        <v>625.6500244140625</v>
       </c>
       <c r="G42" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H42" t="s">
         <v>390</v>
@@ -19935,7 +19950,7 @@
         <v>160</v>
       </c>
       <c r="J42">
-        <v>202.9</v>
+        <v>210.56</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -19944,10 +19959,10 @@
         <v>153</v>
       </c>
       <c r="M42">
-        <v>8.51</v>
+        <v>3.84</v>
       </c>
       <c r="N42">
-        <v>1.44</v>
+        <v>0.77</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -19961,78 +19976,78 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B43" t="s">
         <v>151</v>
       </c>
       <c r="C43" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D43" t="s">
         <v>39</v>
       </c>
       <c r="E43" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F43">
-        <v>5986</v>
+        <v>23.700000762939453</v>
       </c>
       <c r="G43" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="H43" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="I43" t="s">
         <v>160</v>
       </c>
       <c r="J43">
-        <v>202.51</v>
+        <v>204.62</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="L43" t="s">
         <v>153</v>
       </c>
       <c r="M43">
-        <v>5.95</v>
+        <v>13.44</v>
       </c>
       <c r="N43">
-        <v>1.88</v>
+        <v>3.2</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B44" t="s">
         <v>151</v>
       </c>
       <c r="C44" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D44" t="s">
-        <v>39</v>
+        <v>407</v>
       </c>
       <c r="E44" t="s">
         <v>151</v>
       </c>
       <c r="F44">
-        <v>5118.5</v>
+        <v>2746.199951171875</v>
       </c>
       <c r="G44" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H44" t="s">
         <v>390</v>
@@ -20041,7 +20056,7 @@
         <v>160</v>
       </c>
       <c r="J44">
-        <v>183.32</v>
+        <v>204.4</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -20050,10 +20065,10 @@
         <v>153</v>
       </c>
       <c r="M44">
-        <v>5.93</v>
+        <v>8.51</v>
       </c>
       <c r="N44">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -20067,13 +20082,13 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B45" t="s">
         <v>151</v>
       </c>
       <c r="C45" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D45" t="s">
         <v>39</v>
@@ -20082,10 +20097,10 @@
         <v>151</v>
       </c>
       <c r="F45">
-        <v>156.60000610351562</v>
+        <v>5986</v>
       </c>
       <c r="G45" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H45" t="s">
         <v>390</v>
@@ -20094,7 +20109,7 @@
         <v>160</v>
       </c>
       <c r="J45">
-        <v>172.59</v>
+        <v>204.01</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -20103,10 +20118,10 @@
         <v>153</v>
       </c>
       <c r="M45">
-        <v>10.95</v>
+        <v>5.95</v>
       </c>
       <c r="N45">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -20120,13 +20135,13 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B46" t="s">
         <v>151</v>
       </c>
       <c r="C46" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D46" t="s">
         <v>39</v>
@@ -20135,10 +20150,10 @@
         <v>151</v>
       </c>
       <c r="F46">
-        <v>841.2999877929688</v>
+        <v>5118.5</v>
       </c>
       <c r="G46" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H46" t="s">
         <v>390</v>
@@ -20147,7 +20162,7 @@
         <v>160</v>
       </c>
       <c r="J46">
-        <v>168.63</v>
+        <v>184.82</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -20156,10 +20171,10 @@
         <v>153</v>
       </c>
       <c r="M46">
-        <v>5.21</v>
+        <v>5.93</v>
       </c>
       <c r="N46">
-        <v>0.33</v>
+        <v>1.76</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -20168,6 +20183,112 @@
         <v>1</v>
       </c>
       <c r="Q46" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>447</v>
+      </c>
+      <c r="B47" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" t="s">
+        <v>416</v>
+      </c>
+      <c r="D47" t="s">
+        <v>39</v>
+      </c>
+      <c r="E47" t="s">
+        <v>151</v>
+      </c>
+      <c r="F47">
+        <v>156.60000610351562</v>
+      </c>
+      <c r="G47" t="s">
+        <v>448</v>
+      </c>
+      <c r="H47" t="s">
+        <v>401</v>
+      </c>
+      <c r="I47" t="s">
+        <v>160</v>
+      </c>
+      <c r="J47">
+        <v>174.09</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47" t="s">
+        <v>153</v>
+      </c>
+      <c r="M47">
+        <v>10.95</v>
+      </c>
+      <c r="N47">
+        <v>1.26</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>447</v>
+      </c>
+      <c r="B48" t="s">
+        <v>151</v>
+      </c>
+      <c r="C48" t="s">
+        <v>418</v>
+      </c>
+      <c r="D48" t="s">
+        <v>39</v>
+      </c>
+      <c r="E48" t="s">
+        <v>151</v>
+      </c>
+      <c r="F48">
+        <v>841.2999877929688</v>
+      </c>
+      <c r="G48" t="s">
+        <v>431</v>
+      </c>
+      <c r="H48" t="s">
+        <v>390</v>
+      </c>
+      <c r="I48" t="s">
+        <v>160</v>
+      </c>
+      <c r="J48">
+        <v>170.13</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48" t="s">
+        <v>153</v>
+      </c>
+      <c r="M48">
+        <v>5.21</v>
+      </c>
+      <c r="N48">
+        <v>0.33</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="s">
         <v>393</v>
       </c>
     </row>
@@ -20195,27 +20316,27 @@
         <v>355</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B2" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -20227,7 +20348,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -30,7 +30,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T04:26:46.833Z</t>
+    <t>2026-07-16T04:35:23.337Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1362,7 +1362,7 @@
     <t>2026-07-16T03:46:27.865Z</t>
   </si>
   <si>
-    <t>2026-07-16T04:26:46.468Z</t>
+    <t>2026-07-16T04:35:22.922Z</t>
   </si>
   <si>
     <t>DEFERRED</t>
@@ -6195,7 +6195,7 @@
         <v>153</v>
       </c>
       <c r="AN13">
-        <v>187.97</v>
+        <v>189.47</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -6518,7 +6518,7 @@
         <v>153</v>
       </c>
       <c r="AN14">
-        <v>201.54</v>
+        <v>203.04</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -12626,7 +12626,7 @@
         <v>153</v>
       </c>
       <c r="AN13">
-        <v>187.97</v>
+        <v>189.47</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -12949,7 +12949,7 @@
         <v>153</v>
       </c>
       <c r="AN14">
-        <v>201.54</v>
+        <v>203.04</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -16952,7 +16952,7 @@
         <v>160</v>
       </c>
       <c r="F2">
-        <v>224.84</v>
+        <v>226.34</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -17005,7 +17005,7 @@
         <v>160</v>
       </c>
       <c r="F3">
-        <v>220.49</v>
+        <v>221.99</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -17058,7 +17058,7 @@
         <v>160</v>
       </c>
       <c r="F4">
-        <v>210.56</v>
+        <v>212.06</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -17111,7 +17111,7 @@
         <v>160</v>
       </c>
       <c r="F5">
-        <v>206.1</v>
+        <v>207.6</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -17164,7 +17164,7 @@
         <v>160</v>
       </c>
       <c r="F6">
-        <v>204.62</v>
+        <v>206.12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -17217,7 +17217,7 @@
         <v>160</v>
       </c>
       <c r="F7">
-        <v>204.55</v>
+        <v>206.05</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -17270,7 +17270,7 @@
         <v>160</v>
       </c>
       <c r="F8">
-        <v>204.4</v>
+        <v>205.9</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -17323,7 +17323,7 @@
         <v>160</v>
       </c>
       <c r="F9">
-        <v>204.01</v>
+        <v>205.51</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -17482,7 +17482,7 @@
         <v>160</v>
       </c>
       <c r="F12">
-        <v>184.82</v>
+        <v>186.32</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -17535,7 +17535,7 @@
         <v>160</v>
       </c>
       <c r="F13">
-        <v>181.1</v>
+        <v>182.6</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -17553,7 +17553,7 @@
         <v>1.12</v>
       </c>
       <c r="L13">
-        <v>6.38</v>
+        <v>4.88</v>
       </c>
       <c r="M13" t="s">
         <v>185</v>
@@ -17588,7 +17588,7 @@
         <v>160</v>
       </c>
       <c r="F14">
-        <v>180.56</v>
+        <v>182.06</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -17641,7 +17641,7 @@
         <v>160</v>
       </c>
       <c r="F15">
-        <v>174.09</v>
+        <v>175.59</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -17694,7 +17694,7 @@
         <v>160</v>
       </c>
       <c r="F16">
-        <v>170.13</v>
+        <v>171.63</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -19844,7 +19844,7 @@
         <v>160</v>
       </c>
       <c r="J40">
-        <v>224.84</v>
+        <v>226.34</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -19897,7 +19897,7 @@
         <v>160</v>
       </c>
       <c r="J41">
-        <v>220.49</v>
+        <v>221.99</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -19950,7 +19950,7 @@
         <v>160</v>
       </c>
       <c r="J42">
-        <v>210.56</v>
+        <v>212.06</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -20003,7 +20003,7 @@
         <v>160</v>
       </c>
       <c r="J43">
-        <v>204.62</v>
+        <v>206.12</v>
       </c>
       <c r="K43">
         <v>2.95</v>
@@ -20056,7 +20056,7 @@
         <v>160</v>
       </c>
       <c r="J44">
-        <v>204.4</v>
+        <v>205.9</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -20109,7 +20109,7 @@
         <v>160</v>
       </c>
       <c r="J45">
-        <v>204.01</v>
+        <v>205.51</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -20162,7 +20162,7 @@
         <v>160</v>
       </c>
       <c r="J46">
-        <v>184.82</v>
+        <v>186.32</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -20215,7 +20215,7 @@
         <v>160</v>
       </c>
       <c r="J47">
-        <v>174.09</v>
+        <v>175.59</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -20268,7 +20268,7 @@
         <v>160</v>
       </c>
       <c r="J48">
-        <v>170.13</v>
+        <v>171.63</v>
       </c>
       <c r="K48">
         <v>0</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -30,7 +30,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T04:35:23.337Z</t>
+    <t>2026-07-16T05:27:23.463Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1362,7 +1362,7 @@
     <t>2026-07-16T03:46:27.865Z</t>
   </si>
   <si>
-    <t>2026-07-16T04:35:22.922Z</t>
+    <t>2026-07-16T05:27:23.080Z</t>
   </si>
   <si>
     <t>DEFERRED</t>
@@ -4580,7 +4580,7 @@
         <v>179.24</v>
       </c>
       <c r="AN8">
-        <v>186.79</v>
+        <v>192.79</v>
       </c>
       <c r="AO8">
         <v>196.45</v>
@@ -5549,7 +5549,7 @@
         <v>153</v>
       </c>
       <c r="AN11">
-        <v>174.71</v>
+        <v>180.71</v>
       </c>
       <c r="AO11">
         <v>402.78</v>
@@ -6195,7 +6195,7 @@
         <v>153</v>
       </c>
       <c r="AN13">
-        <v>189.47</v>
+        <v>190.97</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -6518,7 +6518,7 @@
         <v>153</v>
       </c>
       <c r="AN14">
-        <v>203.04</v>
+        <v>204.54</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -11011,7 +11011,7 @@
         <v>179.24</v>
       </c>
       <c r="AN8">
-        <v>186.79</v>
+        <v>192.79</v>
       </c>
       <c r="AO8">
         <v>196.45</v>
@@ -11980,7 +11980,7 @@
         <v>153</v>
       </c>
       <c r="AN11">
-        <v>174.71</v>
+        <v>180.71</v>
       </c>
       <c r="AO11">
         <v>402.78</v>
@@ -12626,7 +12626,7 @@
         <v>153</v>
       </c>
       <c r="AN13">
-        <v>189.47</v>
+        <v>190.97</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -12949,7 +12949,7 @@
         <v>153</v>
       </c>
       <c r="AN14">
-        <v>203.04</v>
+        <v>204.54</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -16952,7 +16952,7 @@
         <v>160</v>
       </c>
       <c r="F2">
-        <v>226.34</v>
+        <v>227.84</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -17005,7 +17005,7 @@
         <v>160</v>
       </c>
       <c r="F3">
-        <v>221.99</v>
+        <v>223.49</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -17058,7 +17058,7 @@
         <v>160</v>
       </c>
       <c r="F4">
-        <v>212.06</v>
+        <v>213.56</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -17111,7 +17111,7 @@
         <v>160</v>
       </c>
       <c r="F5">
-        <v>207.6</v>
+        <v>209.1</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -17164,7 +17164,7 @@
         <v>160</v>
       </c>
       <c r="F6">
-        <v>206.12</v>
+        <v>207.62</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -17217,7 +17217,7 @@
         <v>160</v>
       </c>
       <c r="F7">
-        <v>206.05</v>
+        <v>207.55</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -17270,7 +17270,7 @@
         <v>160</v>
       </c>
       <c r="F8">
-        <v>205.9</v>
+        <v>207.4</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -17323,7 +17323,7 @@
         <v>160</v>
       </c>
       <c r="F9">
-        <v>205.51</v>
+        <v>207.01</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -17482,7 +17482,7 @@
         <v>160</v>
       </c>
       <c r="F12">
-        <v>186.32</v>
+        <v>187.82</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -17535,7 +17535,7 @@
         <v>160</v>
       </c>
       <c r="F13">
-        <v>182.6</v>
+        <v>184.1</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -17553,7 +17553,7 @@
         <v>1.12</v>
       </c>
       <c r="L13">
-        <v>4.88</v>
+        <v>3.38</v>
       </c>
       <c r="M13" t="s">
         <v>185</v>
@@ -17588,7 +17588,7 @@
         <v>160</v>
       </c>
       <c r="F14">
-        <v>182.06</v>
+        <v>183.56</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -17641,7 +17641,7 @@
         <v>160</v>
       </c>
       <c r="F15">
-        <v>175.59</v>
+        <v>177.09</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -17694,7 +17694,7 @@
         <v>160</v>
       </c>
       <c r="F16">
-        <v>171.63</v>
+        <v>173.13</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -19844,7 +19844,7 @@
         <v>160</v>
       </c>
       <c r="J40">
-        <v>226.34</v>
+        <v>227.84</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -19897,7 +19897,7 @@
         <v>160</v>
       </c>
       <c r="J41">
-        <v>221.99</v>
+        <v>223.49</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -19950,7 +19950,7 @@
         <v>160</v>
       </c>
       <c r="J42">
-        <v>212.06</v>
+        <v>213.56</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -20003,7 +20003,7 @@
         <v>160</v>
       </c>
       <c r="J43">
-        <v>206.12</v>
+        <v>207.62</v>
       </c>
       <c r="K43">
         <v>2.95</v>
@@ -20056,7 +20056,7 @@
         <v>160</v>
       </c>
       <c r="J44">
-        <v>205.9</v>
+        <v>207.4</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -20109,7 +20109,7 @@
         <v>160</v>
       </c>
       <c r="J45">
-        <v>205.51</v>
+        <v>207.01</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -20162,7 +20162,7 @@
         <v>160</v>
       </c>
       <c r="J46">
-        <v>186.32</v>
+        <v>187.82</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -20215,7 +20215,7 @@
         <v>160</v>
       </c>
       <c r="J47">
-        <v>175.59</v>
+        <v>177.09</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -20268,7 +20268,7 @@
         <v>160</v>
       </c>
       <c r="J48">
-        <v>171.63</v>
+        <v>173.13</v>
       </c>
       <c r="K48">
         <v>0</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -31,7 +31,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T05:59:12.113Z</t>
+    <t>2026-07-16T07:54:16.476Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1411,7 +1411,7 @@
     <t>2026-07-16T03:46:27.865Z</t>
   </si>
   <si>
-    <t>2026-07-16T05:59:10.258Z</t>
+    <t>2026-07-16T07:54:14.816Z</t>
   </si>
   <si>
     <t>DEFERRED</t>
@@ -6460,7 +6460,7 @@
         <v>157</v>
       </c>
       <c r="AN13">
-        <v>192.47</v>
+        <v>193.97</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -6795,7 +6795,7 @@
         <v>157</v>
       </c>
       <c r="AN14">
-        <v>206.04</v>
+        <v>207.54</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -13128,7 +13128,7 @@
         <v>157</v>
       </c>
       <c r="AN13">
-        <v>192.47</v>
+        <v>193.97</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -13463,7 +13463,7 @@
         <v>157</v>
       </c>
       <c r="AN14">
-        <v>206.04</v>
+        <v>207.54</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -17624,7 +17624,7 @@
         <v>164</v>
       </c>
       <c r="F2">
-        <v>229.34</v>
+        <v>230.84</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -17677,7 +17677,7 @@
         <v>164</v>
       </c>
       <c r="F3">
-        <v>224.99</v>
+        <v>226.49</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -17730,7 +17730,7 @@
         <v>164</v>
       </c>
       <c r="F4">
-        <v>215.06</v>
+        <v>216.56</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -17783,7 +17783,7 @@
         <v>164</v>
       </c>
       <c r="F5">
-        <v>210.6</v>
+        <v>212.1</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -17836,7 +17836,7 @@
         <v>164</v>
       </c>
       <c r="F6">
-        <v>209.12</v>
+        <v>210.62</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -17889,7 +17889,7 @@
         <v>164</v>
       </c>
       <c r="F7">
-        <v>209.05</v>
+        <v>210.55</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -17942,7 +17942,7 @@
         <v>164</v>
       </c>
       <c r="F8">
-        <v>208.9</v>
+        <v>210.4</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -17995,7 +17995,7 @@
         <v>164</v>
       </c>
       <c r="F9">
-        <v>208.51</v>
+        <v>210.01</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -18048,7 +18048,7 @@
         <v>164</v>
       </c>
       <c r="F10">
-        <v>190.71</v>
+        <v>191.35</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -18066,7 +18066,7 @@
         <v>0.46</v>
       </c>
       <c r="L10">
-        <v>3.02</v>
+        <v>2.38</v>
       </c>
       <c r="M10" t="s">
         <v>427</v>
@@ -18101,7 +18101,7 @@
         <v>164</v>
       </c>
       <c r="F11">
-        <v>189.32</v>
+        <v>190.82</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -18207,7 +18207,7 @@
         <v>164</v>
       </c>
       <c r="F13">
-        <v>185.6</v>
+        <v>187.1</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -18225,7 +18225,7 @@
         <v>1.12</v>
       </c>
       <c r="L13">
-        <v>1.88</v>
+        <v>0.38</v>
       </c>
       <c r="M13" t="s">
         <v>189</v>
@@ -18260,7 +18260,7 @@
         <v>164</v>
       </c>
       <c r="F14">
-        <v>185.06</v>
+        <v>186.56</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -18313,7 +18313,7 @@
         <v>164</v>
       </c>
       <c r="F15">
-        <v>178.59</v>
+        <v>180.09</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -18366,7 +18366,7 @@
         <v>164</v>
       </c>
       <c r="F16">
-        <v>174.63</v>
+        <v>176.13</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -20516,7 +20516,7 @@
         <v>164</v>
       </c>
       <c r="J40">
-        <v>229.34</v>
+        <v>230.84</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -20569,7 +20569,7 @@
         <v>164</v>
       </c>
       <c r="J41">
-        <v>224.99</v>
+        <v>226.49</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -20622,7 +20622,7 @@
         <v>164</v>
       </c>
       <c r="J42">
-        <v>215.06</v>
+        <v>216.56</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -20675,7 +20675,7 @@
         <v>164</v>
       </c>
       <c r="J43">
-        <v>209.12</v>
+        <v>210.62</v>
       </c>
       <c r="K43">
         <v>2.95</v>
@@ -20728,7 +20728,7 @@
         <v>164</v>
       </c>
       <c r="J44">
-        <v>208.9</v>
+        <v>210.4</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -20781,7 +20781,7 @@
         <v>164</v>
       </c>
       <c r="J45">
-        <v>208.51</v>
+        <v>210.01</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -20834,7 +20834,7 @@
         <v>164</v>
       </c>
       <c r="J46">
-        <v>189.32</v>
+        <v>190.82</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -20887,7 +20887,7 @@
         <v>164</v>
       </c>
       <c r="J47">
-        <v>178.59</v>
+        <v>180.09</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -20940,7 +20940,7 @@
         <v>164</v>
       </c>
       <c r="J48">
-        <v>174.63</v>
+        <v>176.13</v>
       </c>
       <c r="K48">
         <v>0</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -31,7 +31,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T07:54:16.476Z</t>
+    <t>2026-07-16T08:03:09.915Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1300,21 +1300,21 @@
     <t>Retracement buy near Fibonacci 38.2%</t>
   </si>
   <si>
+    <t>FINEORG</t>
+  </si>
+  <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
     <t>Weekly EMA13 reclaim buy</t>
   </si>
   <si>
-    <t>FINEORG</t>
+    <t>KIMS</t>
   </si>
   <si>
     <t>INDIGRID</t>
   </si>
   <si>
-    <t>KIMS</t>
-  </si>
-  <si>
     <t>LMW</t>
   </si>
   <si>
@@ -1411,7 +1411,7 @@
     <t>2026-07-16T03:46:27.865Z</t>
   </si>
   <si>
-    <t>2026-07-16T07:54:14.816Z</t>
+    <t>2026-07-16T08:03:07.854Z</t>
   </si>
   <si>
     <t>DEFERRED</t>
@@ -6460,7 +6460,7 @@
         <v>157</v>
       </c>
       <c r="AN13">
-        <v>193.97</v>
+        <v>195.47</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -6795,7 +6795,7 @@
         <v>157</v>
       </c>
       <c r="AN14">
-        <v>207.54</v>
+        <v>209.04</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -13128,7 +13128,7 @@
         <v>157</v>
       </c>
       <c r="AN13">
-        <v>193.97</v>
+        <v>195.47</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -13463,7 +13463,7 @@
         <v>157</v>
       </c>
       <c r="AN14">
-        <v>207.54</v>
+        <v>209.04</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -17624,7 +17624,7 @@
         <v>164</v>
       </c>
       <c r="F2">
-        <v>230.84</v>
+        <v>236.34</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -17677,7 +17677,7 @@
         <v>164</v>
       </c>
       <c r="F3">
-        <v>226.49</v>
+        <v>227.99</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -17730,7 +17730,7 @@
         <v>164</v>
       </c>
       <c r="F4">
-        <v>216.56</v>
+        <v>218.06</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -17783,7 +17783,7 @@
         <v>164</v>
       </c>
       <c r="F5">
-        <v>212.1</v>
+        <v>213.6</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -17836,7 +17836,7 @@
         <v>164</v>
       </c>
       <c r="F6">
-        <v>210.62</v>
+        <v>212.12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -17889,7 +17889,7 @@
         <v>164</v>
       </c>
       <c r="F7">
-        <v>210.55</v>
+        <v>212.05</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -17942,7 +17942,7 @@
         <v>164</v>
       </c>
       <c r="F8">
-        <v>210.4</v>
+        <v>211.9</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -17995,7 +17995,7 @@
         <v>164</v>
       </c>
       <c r="F9">
-        <v>210.01</v>
+        <v>211.51</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -18033,108 +18033,108 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B10" t="s">
         <v>426</v>
       </c>
       <c r="C10" t="s">
-        <v>423</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
         <v>164</v>
       </c>
       <c r="F10">
-        <v>191.35</v>
+        <v>192.32</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="I10" t="s">
         <v>157</v>
       </c>
       <c r="J10">
-        <v>6.9</v>
+        <v>5.93</v>
       </c>
       <c r="K10">
-        <v>0.46</v>
+        <v>1.76</v>
       </c>
       <c r="L10">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N10">
-        <v>61938</v>
+        <v>61422</v>
       </c>
       <c r="O10">
-        <v>4274.28</v>
+        <v>1043.64</v>
       </c>
       <c r="P10">
-        <v>9610.62</v>
+        <v>5031.53</v>
       </c>
       <c r="Q10" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B11" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>423</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
         <v>164</v>
       </c>
       <c r="F11">
-        <v>190.82</v>
+        <v>191.35</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="I11" t="s">
         <v>157</v>
       </c>
       <c r="J11">
-        <v>5.93</v>
+        <v>6.9</v>
       </c>
       <c r="K11">
-        <v>1.76</v>
+        <v>0.46</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M11" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="N11">
-        <v>61422</v>
+        <v>61938</v>
       </c>
       <c r="O11">
-        <v>1043.64</v>
+        <v>4274.28</v>
       </c>
       <c r="P11">
-        <v>5031.53</v>
+        <v>9610.62</v>
       </c>
       <c r="Q11" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -18145,31 +18145,31 @@
         <v>429</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>415</v>
       </c>
       <c r="D12" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s">
         <v>164</v>
       </c>
       <c r="F12">
-        <v>188.19</v>
+        <v>188.6</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="H12">
-        <v>-0.94</v>
+        <v>0.15</v>
       </c>
       <c r="I12" t="s">
         <v>157</v>
       </c>
       <c r="J12">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="K12">
-        <v>2.36</v>
+        <v>1.12</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -18178,13 +18178,13 @@
         <v>189</v>
       </c>
       <c r="N12">
-        <v>62596.16</v>
+        <v>62212.15</v>
       </c>
       <c r="O12">
-        <v>939.84</v>
+        <v>993.3</v>
       </c>
       <c r="P12">
-        <v>175.16</v>
+        <v>795.05</v>
       </c>
       <c r="Q12" t="s">
         <v>416</v>
@@ -18198,46 +18198,46 @@
         <v>430</v>
       </c>
       <c r="C13" t="s">
-        <v>415</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="E13" t="s">
         <v>164</v>
       </c>
       <c r="F13">
-        <v>187.1</v>
+        <v>188.19</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>0.15</v>
+        <v>-0.94</v>
       </c>
       <c r="I13" t="s">
         <v>157</v>
       </c>
       <c r="J13">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="K13">
-        <v>1.12</v>
+        <v>2.36</v>
       </c>
       <c r="L13">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="M13" t="s">
         <v>189</v>
       </c>
       <c r="N13">
-        <v>62212.15</v>
+        <v>62596.16</v>
       </c>
       <c r="O13">
-        <v>993.3</v>
+        <v>939.84</v>
       </c>
       <c r="P13">
-        <v>795.05</v>
+        <v>175.16</v>
       </c>
       <c r="Q13" t="s">
         <v>416</v>
@@ -18260,7 +18260,7 @@
         <v>164</v>
       </c>
       <c r="F14">
-        <v>186.56</v>
+        <v>188.06</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -18313,7 +18313,7 @@
         <v>164</v>
       </c>
       <c r="F15">
-        <v>180.09</v>
+        <v>181.59</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -18366,7 +18366,7 @@
         <v>164</v>
       </c>
       <c r="F16">
-        <v>176.13</v>
+        <v>177.63</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -18746,7 +18746,7 @@
         <v>227</v>
       </c>
       <c r="C7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D7" t="s">
         <v>415</v>
@@ -18852,7 +18852,7 @@
         <v>227</v>
       </c>
       <c r="C9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D9" t="s">
         <v>415</v>
@@ -19170,7 +19170,7 @@
         <v>154</v>
       </c>
       <c r="C15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D15" t="s">
         <v>415</v>
@@ -19382,7 +19382,7 @@
         <v>186</v>
       </c>
       <c r="C19" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D19" t="s">
         <v>41</v>
@@ -19700,7 +19700,7 @@
         <v>186</v>
       </c>
       <c r="C25" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D25" t="s">
         <v>41</v>
@@ -19859,7 +19859,7 @@
         <v>186</v>
       </c>
       <c r="C28" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D28" t="s">
         <v>41</v>
@@ -19912,7 +19912,7 @@
         <v>154</v>
       </c>
       <c r="C29" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D29" t="s">
         <v>423</v>
@@ -20230,7 +20230,7 @@
         <v>154</v>
       </c>
       <c r="C35" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D35" t="s">
         <v>415</v>
@@ -20516,7 +20516,7 @@
         <v>164</v>
       </c>
       <c r="J40">
-        <v>230.84</v>
+        <v>236.34</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -20569,7 +20569,7 @@
         <v>164</v>
       </c>
       <c r="J41">
-        <v>226.49</v>
+        <v>227.99</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -20622,7 +20622,7 @@
         <v>164</v>
       </c>
       <c r="J42">
-        <v>216.56</v>
+        <v>218.06</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -20675,7 +20675,7 @@
         <v>164</v>
       </c>
       <c r="J43">
-        <v>210.62</v>
+        <v>212.12</v>
       </c>
       <c r="K43">
         <v>2.95</v>
@@ -20728,7 +20728,7 @@
         <v>164</v>
       </c>
       <c r="J44">
-        <v>210.4</v>
+        <v>211.9</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -20781,7 +20781,7 @@
         <v>164</v>
       </c>
       <c r="J45">
-        <v>210.01</v>
+        <v>211.51</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -20813,7 +20813,7 @@
         <v>155</v>
       </c>
       <c r="C46" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D46" t="s">
         <v>41</v>
@@ -20834,7 +20834,7 @@
         <v>164</v>
       </c>
       <c r="J46">
-        <v>190.82</v>
+        <v>192.32</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -20887,7 +20887,7 @@
         <v>164</v>
       </c>
       <c r="J47">
-        <v>180.09</v>
+        <v>181.59</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -20940,7 +20940,7 @@
         <v>164</v>
       </c>
       <c r="J48">
-        <v>176.13</v>
+        <v>177.63</v>
       </c>
       <c r="K48">
         <v>0</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -31,7 +31,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T08:03:09.915Z</t>
+    <t>2026-07-16T08:11:15.282Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1312,12 +1312,12 @@
     <t>KIMS</t>
   </si>
   <si>
+    <t>LMW</t>
+  </si>
+  <si>
     <t>INDIGRID</t>
   </si>
   <si>
-    <t>LMW</t>
-  </si>
-  <si>
     <t>KVFORGE</t>
   </si>
   <si>
@@ -1411,7 +1411,7 @@
     <t>2026-07-16T03:46:27.865Z</t>
   </si>
   <si>
-    <t>2026-07-16T08:03:07.854Z</t>
+    <t>2026-07-16T08:11:13.432Z</t>
   </si>
   <si>
     <t>DEFERRED</t>
@@ -6460,7 +6460,7 @@
         <v>157</v>
       </c>
       <c r="AN13">
-        <v>195.47</v>
+        <v>196.97</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -6795,7 +6795,7 @@
         <v>157</v>
       </c>
       <c r="AN14">
-        <v>209.04</v>
+        <v>210.54</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -13128,7 +13128,7 @@
         <v>157</v>
       </c>
       <c r="AN13">
-        <v>195.47</v>
+        <v>196.97</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -13463,7 +13463,7 @@
         <v>157</v>
       </c>
       <c r="AN14">
-        <v>209.04</v>
+        <v>210.54</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -17624,7 +17624,7 @@
         <v>164</v>
       </c>
       <c r="F2">
-        <v>236.34</v>
+        <v>237.84</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -17677,7 +17677,7 @@
         <v>164</v>
       </c>
       <c r="F3">
-        <v>227.99</v>
+        <v>229.49</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -17730,7 +17730,7 @@
         <v>164</v>
       </c>
       <c r="F4">
-        <v>218.06</v>
+        <v>219.56</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -17783,7 +17783,7 @@
         <v>164</v>
       </c>
       <c r="F5">
-        <v>213.6</v>
+        <v>215.1</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -17836,7 +17836,7 @@
         <v>164</v>
       </c>
       <c r="F6">
-        <v>212.12</v>
+        <v>213.62</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -17889,7 +17889,7 @@
         <v>164</v>
       </c>
       <c r="F7">
-        <v>212.05</v>
+        <v>213.55</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -17942,7 +17942,7 @@
         <v>164</v>
       </c>
       <c r="F8">
-        <v>211.9</v>
+        <v>213.4</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -17995,7 +17995,7 @@
         <v>164</v>
       </c>
       <c r="F9">
-        <v>211.51</v>
+        <v>213.01</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -18048,7 +18048,7 @@
         <v>164</v>
       </c>
       <c r="F10">
-        <v>192.32</v>
+        <v>193.82</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -18154,7 +18154,7 @@
         <v>164</v>
       </c>
       <c r="F12">
-        <v>188.6</v>
+        <v>190.1</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -18207,37 +18207,37 @@
         <v>164</v>
       </c>
       <c r="F13">
-        <v>188.19</v>
+        <v>189.56</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>-0.94</v>
+        <v>0.23</v>
       </c>
       <c r="I13" t="s">
         <v>157</v>
       </c>
       <c r="J13">
-        <v>1.7</v>
+        <v>5.89</v>
       </c>
       <c r="K13">
-        <v>2.36</v>
+        <v>1.91</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>189</v>
+        <v>244</v>
       </c>
       <c r="N13">
-        <v>62596.16</v>
+        <v>49092</v>
       </c>
       <c r="O13">
-        <v>939.84</v>
+        <v>1086</v>
       </c>
       <c r="P13">
-        <v>175.16</v>
+        <v>16002</v>
       </c>
       <c r="Q13" t="s">
         <v>416</v>
@@ -18260,37 +18260,37 @@
         <v>164</v>
       </c>
       <c r="F14">
-        <v>188.06</v>
+        <v>188.19</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>0.23</v>
+        <v>-0.94</v>
       </c>
       <c r="I14" t="s">
         <v>157</v>
       </c>
       <c r="J14">
-        <v>5.89</v>
+        <v>1.7</v>
       </c>
       <c r="K14">
-        <v>1.91</v>
+        <v>2.36</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>244</v>
+        <v>189</v>
       </c>
       <c r="N14">
-        <v>49092</v>
+        <v>62596.16</v>
       </c>
       <c r="O14">
-        <v>1086</v>
+        <v>939.84</v>
       </c>
       <c r="P14">
-        <v>16002</v>
+        <v>175.16</v>
       </c>
       <c r="Q14" t="s">
         <v>416</v>
@@ -18313,7 +18313,7 @@
         <v>164</v>
       </c>
       <c r="F15">
-        <v>181.59</v>
+        <v>183.09</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -18366,7 +18366,7 @@
         <v>164</v>
       </c>
       <c r="F16">
-        <v>177.63</v>
+        <v>179.13</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -18540,7 +18540,7 @@
         <v>186</v>
       </c>
       <c r="C3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D3" t="s">
         <v>41</v>
@@ -19011,7 +19011,7 @@
         <v>186</v>
       </c>
       <c r="C12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D12" t="s">
         <v>41</v>
@@ -19859,7 +19859,7 @@
         <v>186</v>
       </c>
       <c r="C28" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D28" t="s">
         <v>41</v>
@@ -20516,7 +20516,7 @@
         <v>164</v>
       </c>
       <c r="J40">
-        <v>236.34</v>
+        <v>237.84</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -20569,7 +20569,7 @@
         <v>164</v>
       </c>
       <c r="J41">
-        <v>227.99</v>
+        <v>229.49</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -20622,7 +20622,7 @@
         <v>164</v>
       </c>
       <c r="J42">
-        <v>218.06</v>
+        <v>219.56</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -20675,7 +20675,7 @@
         <v>164</v>
       </c>
       <c r="J43">
-        <v>212.12</v>
+        <v>213.62</v>
       </c>
       <c r="K43">
         <v>2.95</v>
@@ -20728,7 +20728,7 @@
         <v>164</v>
       </c>
       <c r="J44">
-        <v>211.9</v>
+        <v>213.4</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -20781,7 +20781,7 @@
         <v>164</v>
       </c>
       <c r="J45">
-        <v>211.51</v>
+        <v>213.01</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -20834,7 +20834,7 @@
         <v>164</v>
       </c>
       <c r="J46">
-        <v>192.32</v>
+        <v>193.82</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -20887,7 +20887,7 @@
         <v>164</v>
       </c>
       <c r="J47">
-        <v>181.59</v>
+        <v>183.09</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -20940,7 +20940,7 @@
         <v>164</v>
       </c>
       <c r="J48">
-        <v>177.63</v>
+        <v>179.13</v>
       </c>
       <c r="K48">
         <v>0</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -31,7 +31,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T08:11:15.282Z</t>
+    <t>2026-07-16T08:15:31.809Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1303,15 +1303,15 @@
     <t>FINEORG</t>
   </si>
   <si>
+    <t>KIMS</t>
+  </si>
+  <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
     <t>Weekly EMA13 reclaim buy</t>
   </si>
   <si>
-    <t>KIMS</t>
-  </si>
-  <si>
     <t>LMW</t>
   </si>
   <si>
@@ -1411,7 +1411,7 @@
     <t>2026-07-16T03:46:27.865Z</t>
   </si>
   <si>
-    <t>2026-07-16T08:11:13.432Z</t>
+    <t>2026-07-16T08:15:30.047Z</t>
   </si>
   <si>
     <t>DEFERRED</t>
@@ -6460,7 +6460,7 @@
         <v>157</v>
       </c>
       <c r="AN13">
-        <v>196.97</v>
+        <v>198.47</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -6795,7 +6795,7 @@
         <v>157</v>
       </c>
       <c r="AN14">
-        <v>210.54</v>
+        <v>212.04</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -13128,7 +13128,7 @@
         <v>157</v>
       </c>
       <c r="AN13">
-        <v>196.97</v>
+        <v>198.47</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -13463,7 +13463,7 @@
         <v>157</v>
       </c>
       <c r="AN14">
-        <v>210.54</v>
+        <v>212.04</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -17624,7 +17624,7 @@
         <v>164</v>
       </c>
       <c r="F2">
-        <v>237.84</v>
+        <v>239.34</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -17677,7 +17677,7 @@
         <v>164</v>
       </c>
       <c r="F3">
-        <v>229.49</v>
+        <v>230.99</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -17730,7 +17730,7 @@
         <v>164</v>
       </c>
       <c r="F4">
-        <v>219.56</v>
+        <v>221.06</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -17783,7 +17783,7 @@
         <v>164</v>
       </c>
       <c r="F5">
-        <v>215.1</v>
+        <v>216.6</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -17836,7 +17836,7 @@
         <v>164</v>
       </c>
       <c r="F6">
-        <v>213.62</v>
+        <v>215.12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -17889,7 +17889,7 @@
         <v>164</v>
       </c>
       <c r="F7">
-        <v>213.55</v>
+        <v>215.05</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -17942,7 +17942,7 @@
         <v>164</v>
       </c>
       <c r="F8">
-        <v>213.4</v>
+        <v>214.9</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -17995,7 +17995,7 @@
         <v>164</v>
       </c>
       <c r="F9">
-        <v>213.01</v>
+        <v>214.51</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -18048,7 +18048,7 @@
         <v>164</v>
       </c>
       <c r="F10">
-        <v>193.82</v>
+        <v>195.32</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -18092,7 +18092,7 @@
         <v>427</v>
       </c>
       <c r="C11" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="D11" t="s">
         <v>154</v>
@@ -18101,37 +18101,37 @@
         <v>164</v>
       </c>
       <c r="F11">
-        <v>191.35</v>
+        <v>191.6</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
       <c r="H11">
-        <v>1.54</v>
+        <v>0.15</v>
       </c>
       <c r="I11" t="s">
         <v>157</v>
       </c>
       <c r="J11">
-        <v>6.9</v>
+        <v>3.2</v>
       </c>
       <c r="K11">
-        <v>0.46</v>
+        <v>1.12</v>
       </c>
       <c r="L11">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>428</v>
+        <v>189</v>
       </c>
       <c r="N11">
-        <v>61938</v>
+        <v>62212.15</v>
       </c>
       <c r="O11">
-        <v>4274.28</v>
+        <v>993.3</v>
       </c>
       <c r="P11">
-        <v>9610.62</v>
+        <v>795.05</v>
       </c>
       <c r="Q11" t="s">
         <v>416</v>
@@ -18142,10 +18142,10 @@
         <v>413</v>
       </c>
       <c r="B12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C12" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="D12" t="s">
         <v>154</v>
@@ -18154,37 +18154,37 @@
         <v>164</v>
       </c>
       <c r="F12">
-        <v>190.1</v>
+        <v>191.35</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="H12">
-        <v>0.15</v>
+        <v>1.54</v>
       </c>
       <c r="I12" t="s">
         <v>157</v>
       </c>
       <c r="J12">
-        <v>3.2</v>
+        <v>6.9</v>
       </c>
       <c r="K12">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="s">
-        <v>189</v>
+        <v>429</v>
       </c>
       <c r="N12">
-        <v>62212.15</v>
+        <v>61938</v>
       </c>
       <c r="O12">
-        <v>993.3</v>
+        <v>4274.28</v>
       </c>
       <c r="P12">
-        <v>795.05</v>
+        <v>9610.62</v>
       </c>
       <c r="Q12" t="s">
         <v>416</v>
@@ -18207,7 +18207,7 @@
         <v>164</v>
       </c>
       <c r="F13">
-        <v>189.56</v>
+        <v>191.06</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -18313,7 +18313,7 @@
         <v>164</v>
       </c>
       <c r="F15">
-        <v>183.09</v>
+        <v>184.59</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -18366,7 +18366,7 @@
         <v>164</v>
       </c>
       <c r="F16">
-        <v>179.13</v>
+        <v>180.63</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -18746,7 +18746,7 @@
         <v>227</v>
       </c>
       <c r="C7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D7" t="s">
         <v>415</v>
@@ -18852,7 +18852,7 @@
         <v>227</v>
       </c>
       <c r="C9" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D9" t="s">
         <v>415</v>
@@ -19170,7 +19170,7 @@
         <v>154</v>
       </c>
       <c r="C15" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D15" t="s">
         <v>415</v>
@@ -19912,7 +19912,7 @@
         <v>154</v>
       </c>
       <c r="C29" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D29" t="s">
         <v>423</v>
@@ -20230,7 +20230,7 @@
         <v>154</v>
       </c>
       <c r="C35" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D35" t="s">
         <v>415</v>
@@ -20516,7 +20516,7 @@
         <v>164</v>
       </c>
       <c r="J40">
-        <v>237.84</v>
+        <v>239.34</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -20569,7 +20569,7 @@
         <v>164</v>
       </c>
       <c r="J41">
-        <v>229.49</v>
+        <v>230.99</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -20622,7 +20622,7 @@
         <v>164</v>
       </c>
       <c r="J42">
-        <v>219.56</v>
+        <v>221.06</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -20675,7 +20675,7 @@
         <v>164</v>
       </c>
       <c r="J43">
-        <v>213.62</v>
+        <v>215.12</v>
       </c>
       <c r="K43">
         <v>2.95</v>
@@ -20728,7 +20728,7 @@
         <v>164</v>
       </c>
       <c r="J44">
-        <v>213.4</v>
+        <v>214.9</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -20781,7 +20781,7 @@
         <v>164</v>
       </c>
       <c r="J45">
-        <v>213.01</v>
+        <v>214.51</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -20834,7 +20834,7 @@
         <v>164</v>
       </c>
       <c r="J46">
-        <v>193.82</v>
+        <v>195.32</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -20887,7 +20887,7 @@
         <v>164</v>
       </c>
       <c r="J47">
-        <v>183.09</v>
+        <v>184.59</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -20940,7 +20940,7 @@
         <v>164</v>
       </c>
       <c r="J48">
-        <v>179.13</v>
+        <v>180.63</v>
       </c>
       <c r="K48">
         <v>0</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -31,7 +31,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T08:15:31.809Z</t>
+    <t>2026-07-16T08:35:27.887Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1261,6 +1261,12 @@
     <t>SGFIN</t>
   </si>
   <si>
+    <t>KOVAI</t>
+  </si>
+  <si>
+    <t>Retracement buy near Fibonacci 38.2%</t>
+  </si>
+  <si>
     <t>WAITING_CAPITAL</t>
   </si>
   <si>
@@ -1294,28 +1300,25 @@
     <t>Automobile and Auto Components</t>
   </si>
   <si>
-    <t>KOVAI</t>
-  </si>
-  <si>
-    <t>Retracement buy near Fibonacci 38.2%</t>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>Weekly EMA13 reclaim buy</t>
   </si>
   <si>
     <t>FINEORG</t>
   </si>
   <si>
+    <t>LMW</t>
+  </si>
+  <si>
+    <t>INDIGRID</t>
+  </si>
+  <si>
     <t>KIMS</t>
   </si>
   <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>Weekly EMA13 reclaim buy</t>
-  </si>
-  <si>
-    <t>LMW</t>
-  </si>
-  <si>
-    <t>INDIGRID</t>
+    <t>YATHARTH</t>
   </si>
   <si>
     <t>KVFORGE</t>
@@ -1324,9 +1327,6 @@
     <t>Automated entry is blocked because 20-day average turnover Rs 2202532.48 is below the compulsory liquidity standard; execution and exit costs are not reliable enough. Automated entry is blocked because requested KVFORGE.NS resolved only through KVFORGE.BO; exchange-consistent live and 09:17 execution coverage is required.</t>
   </si>
   <si>
-    <t>YATHARTH</t>
-  </si>
-  <si>
     <t>Evaluated At</t>
   </si>
   <si>
@@ -1411,7 +1411,7 @@
     <t>2026-07-16T03:46:27.865Z</t>
   </si>
   <si>
-    <t>2026-07-16T08:15:30.047Z</t>
+    <t>2026-07-16T08:35:26.245Z</t>
   </si>
   <si>
     <t>DEFERRED</t>
@@ -2775,7 +2775,7 @@
         <v>213.48</v>
       </c>
       <c r="AN2">
-        <v>200.58</v>
+        <v>209.58</v>
       </c>
       <c r="AO2">
         <v>847.55</v>
@@ -3110,7 +3110,7 @@
         <v>191.09</v>
       </c>
       <c r="AN3">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="AO3">
         <v>805.6</v>
@@ -3445,7 +3445,7 @@
         <v>195.78</v>
       </c>
       <c r="AN4">
-        <v>181.01</v>
+        <v>190.01</v>
       </c>
       <c r="AO4">
         <v>597.22</v>
@@ -4115,7 +4115,7 @@
         <v>170.76</v>
       </c>
       <c r="AN6">
-        <v>97.28</v>
+        <v>106.28</v>
       </c>
       <c r="AO6">
         <v>1974.43</v>
@@ -5120,7 +5120,7 @@
         <v>131.92</v>
       </c>
       <c r="AN9">
-        <v>109.94</v>
+        <v>112.94</v>
       </c>
       <c r="AO9">
         <v>8955.5</v>
@@ -5455,7 +5455,7 @@
         <v>157</v>
       </c>
       <c r="AN10">
-        <v>92.09</v>
+        <v>95.09</v>
       </c>
       <c r="AO10">
         <v>1251.2</v>
@@ -6125,7 +6125,7 @@
         <v>157</v>
       </c>
       <c r="AN12">
-        <v>204.75</v>
+        <v>216.75</v>
       </c>
       <c r="AO12">
         <v>6083.5</v>
@@ -6460,7 +6460,7 @@
         <v>157</v>
       </c>
       <c r="AN13">
-        <v>198.47</v>
+        <v>186.47</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -6795,7 +6795,7 @@
         <v>157</v>
       </c>
       <c r="AN14">
-        <v>212.04</v>
+        <v>200.04</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -7130,7 +7130,7 @@
         <v>157</v>
       </c>
       <c r="AN15">
-        <v>194.01</v>
+        <v>203.01</v>
       </c>
       <c r="AO15">
         <v>771.79</v>
@@ -7465,7 +7465,7 @@
         <v>157</v>
       </c>
       <c r="AN16">
-        <v>92.7</v>
+        <v>101.7</v>
       </c>
       <c r="AO16">
         <v>2728.17</v>
@@ -9443,7 +9443,7 @@
         <v>213.48</v>
       </c>
       <c r="AN2">
-        <v>200.58</v>
+        <v>209.58</v>
       </c>
       <c r="AO2">
         <v>847.55</v>
@@ -9778,7 +9778,7 @@
         <v>191.09</v>
       </c>
       <c r="AN3">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="AO3">
         <v>805.6</v>
@@ -10113,7 +10113,7 @@
         <v>195.78</v>
       </c>
       <c r="AN4">
-        <v>181.01</v>
+        <v>190.01</v>
       </c>
       <c r="AO4">
         <v>597.22</v>
@@ -10783,7 +10783,7 @@
         <v>170.76</v>
       </c>
       <c r="AN6">
-        <v>97.28</v>
+        <v>106.28</v>
       </c>
       <c r="AO6">
         <v>1974.43</v>
@@ -11788,7 +11788,7 @@
         <v>131.92</v>
       </c>
       <c r="AN9">
-        <v>109.94</v>
+        <v>112.94</v>
       </c>
       <c r="AO9">
         <v>8955.5</v>
@@ -12123,7 +12123,7 @@
         <v>157</v>
       </c>
       <c r="AN10">
-        <v>92.09</v>
+        <v>95.09</v>
       </c>
       <c r="AO10">
         <v>1251.2</v>
@@ -12793,7 +12793,7 @@
         <v>157</v>
       </c>
       <c r="AN12">
-        <v>204.75</v>
+        <v>216.75</v>
       </c>
       <c r="AO12">
         <v>6083.5</v>
@@ -13128,7 +13128,7 @@
         <v>157</v>
       </c>
       <c r="AN13">
-        <v>198.47</v>
+        <v>186.47</v>
       </c>
       <c r="AO13">
         <v>1842.85</v>
@@ -13463,7 +13463,7 @@
         <v>157</v>
       </c>
       <c r="AN14">
-        <v>212.04</v>
+        <v>200.04</v>
       </c>
       <c r="AO14">
         <v>1285.88</v>
@@ -13798,7 +13798,7 @@
         <v>157</v>
       </c>
       <c r="AN15">
-        <v>194.01</v>
+        <v>203.01</v>
       </c>
       <c r="AO15">
         <v>771.79</v>
@@ -14133,7 +14133,7 @@
         <v>157</v>
       </c>
       <c r="AN16">
-        <v>92.7</v>
+        <v>101.7</v>
       </c>
       <c r="AO16">
         <v>2728.17</v>
@@ -17624,7 +17624,7 @@
         <v>164</v>
       </c>
       <c r="F2">
-        <v>239.34</v>
+        <v>223.34</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -17642,7 +17642,7 @@
         <v>1.86</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M2" t="s">
         <v>163</v>
@@ -17677,7 +17677,7 @@
         <v>164</v>
       </c>
       <c r="F3">
-        <v>230.99</v>
+        <v>218.99</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -17695,7 +17695,7 @@
         <v>1.26</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M3" t="s">
         <v>189</v>
@@ -17730,7 +17730,7 @@
         <v>164</v>
       </c>
       <c r="F4">
-        <v>221.06</v>
+        <v>210.56</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -17748,7 +17748,7 @@
         <v>0.77</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="M4" t="s">
         <v>216</v>
@@ -17768,119 +17768,119 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>406</v>
+      </c>
+      <c r="B5" t="s">
         <v>413</v>
       </c>
-      <c r="B5" t="s">
-        <v>414</v>
-      </c>
       <c r="C5" t="s">
-        <v>415</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="E5" t="s">
         <v>164</v>
       </c>
       <c r="F5">
-        <v>216.6</v>
+        <v>209.16</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="I5" t="s">
         <v>157</v>
       </c>
       <c r="J5">
-        <v>4.49</v>
+        <v>5.95</v>
       </c>
       <c r="K5">
-        <v>3.64</v>
+        <v>1.88</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="M5" t="s">
-        <v>189</v>
+        <v>414</v>
       </c>
       <c r="N5">
-        <v>62538</v>
+        <v>59860</v>
       </c>
       <c r="O5">
-        <v>1365</v>
+        <v>897.9</v>
       </c>
       <c r="P5">
-        <v>8739</v>
+        <v>5896.21</v>
       </c>
       <c r="Q5" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C6" t="s">
         <v>417</v>
       </c>
-      <c r="B6" t="s">
-        <v>418</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
-      </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="E6" t="s">
         <v>164</v>
       </c>
       <c r="F6">
-        <v>215.12</v>
+        <v>203.95</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>2.95</v>
+        <v>1.73</v>
       </c>
       <c r="I6" t="s">
         <v>157</v>
       </c>
       <c r="J6">
-        <v>13.44</v>
+        <v>4.49</v>
       </c>
       <c r="K6">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>12.65</v>
       </c>
       <c r="M6" t="s">
-        <v>419</v>
+        <v>189</v>
       </c>
       <c r="N6">
-        <v>62659.2</v>
+        <v>62538</v>
       </c>
       <c r="O6">
-        <v>5007.6</v>
+        <v>1365</v>
       </c>
       <c r="P6">
-        <v>22.45</v>
+        <v>8739</v>
       </c>
       <c r="Q6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>415</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
         <v>154</v>
@@ -17889,93 +17889,93 @@
         <v>164</v>
       </c>
       <c r="F7">
-        <v>215.05</v>
+        <v>203.12</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7">
-        <v>1.4</v>
+        <v>2.95</v>
       </c>
       <c r="I7" t="s">
         <v>157</v>
       </c>
       <c r="J7">
-        <v>8.92</v>
+        <v>13.44</v>
       </c>
       <c r="K7">
-        <v>2.41</v>
+        <v>3.2</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M7" t="s">
-        <v>163</v>
+        <v>421</v>
       </c>
       <c r="N7">
-        <v>61845</v>
+        <v>62659.2</v>
       </c>
       <c r="O7">
-        <v>1466.25</v>
+        <v>5007.6</v>
       </c>
       <c r="P7">
-        <v>805.05</v>
+        <v>22.45</v>
       </c>
       <c r="Q7" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="B8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E8" t="s">
         <v>164</v>
       </c>
       <c r="F8">
-        <v>214.9</v>
+        <v>203.05</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="I8" t="s">
         <v>157</v>
       </c>
       <c r="J8">
-        <v>8.51</v>
+        <v>8.92</v>
       </c>
       <c r="K8">
-        <v>1.44</v>
+        <v>2.41</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M8" t="s">
-        <v>419</v>
+        <v>163</v>
       </c>
       <c r="N8">
-        <v>60416.4</v>
+        <v>61845</v>
       </c>
       <c r="O8">
-        <v>2754.4</v>
+        <v>1466.25</v>
       </c>
       <c r="P8">
-        <v>2621</v>
+        <v>805.05</v>
       </c>
       <c r="Q8" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -17986,7 +17986,7 @@
         <v>424</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>425</v>
       </c>
       <c r="D9" t="s">
         <v>155</v>
@@ -17995,7 +17995,7 @@
         <v>164</v>
       </c>
       <c r="F9">
-        <v>214.51</v>
+        <v>202.9</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -18007,25 +18007,25 @@
         <v>157</v>
       </c>
       <c r="J9">
-        <v>5.95</v>
+        <v>8.51</v>
       </c>
       <c r="K9">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M9" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="N9">
-        <v>59860</v>
+        <v>60416.4</v>
       </c>
       <c r="O9">
-        <v>897.9</v>
+        <v>2754.4</v>
       </c>
       <c r="P9">
-        <v>5896.21</v>
+        <v>2621</v>
       </c>
       <c r="Q9" t="s">
         <v>409</v>
@@ -18033,166 +18033,166 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="B10" t="s">
         <v>426</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>425</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E10" t="s">
         <v>164</v>
       </c>
       <c r="F10">
-        <v>195.32</v>
+        <v>191.35</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="I10" t="s">
         <v>157</v>
       </c>
       <c r="J10">
-        <v>5.93</v>
+        <v>6.9</v>
       </c>
       <c r="K10">
-        <v>1.76</v>
+        <v>0.46</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M10" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N10">
-        <v>61422</v>
+        <v>61938</v>
       </c>
       <c r="O10">
-        <v>1043.64</v>
+        <v>4274.28</v>
       </c>
       <c r="P10">
-        <v>5031.53</v>
+        <v>9610.62</v>
       </c>
       <c r="Q10" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C11" t="s">
-        <v>415</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
         <v>164</v>
       </c>
       <c r="F11">
-        <v>191.6</v>
+        <v>189.32</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="I11" t="s">
         <v>157</v>
       </c>
       <c r="J11">
-        <v>3.2</v>
+        <v>5.93</v>
       </c>
       <c r="K11">
-        <v>1.12</v>
+        <v>1.76</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M11" t="s">
-        <v>189</v>
+        <v>414</v>
       </c>
       <c r="N11">
-        <v>62212.15</v>
+        <v>61422</v>
       </c>
       <c r="O11">
-        <v>993.3</v>
+        <v>1043.64</v>
       </c>
       <c r="P11">
-        <v>795.05</v>
+        <v>5031.53</v>
       </c>
       <c r="Q11" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B12" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C12" t="s">
-        <v>423</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="E12" t="s">
         <v>164</v>
       </c>
       <c r="F12">
-        <v>191.35</v>
+        <v>185.06</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>1.54</v>
+        <v>0.23</v>
       </c>
       <c r="I12" t="s">
         <v>157</v>
       </c>
       <c r="J12">
-        <v>6.9</v>
+        <v>5.89</v>
       </c>
       <c r="K12">
-        <v>0.46</v>
+        <v>1.91</v>
       </c>
       <c r="L12">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="M12" t="s">
-        <v>429</v>
+        <v>244</v>
       </c>
       <c r="N12">
-        <v>61938</v>
+        <v>49092</v>
       </c>
       <c r="O12">
-        <v>4274.28</v>
+        <v>1086</v>
       </c>
       <c r="P12">
-        <v>9610.62</v>
+        <v>16002</v>
       </c>
       <c r="Q12" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B13" t="s">
         <v>430</v>
@@ -18207,98 +18207,98 @@
         <v>164</v>
       </c>
       <c r="F13">
-        <v>191.06</v>
+        <v>182.31</v>
       </c>
       <c r="G13">
         <v>3</v>
       </c>
       <c r="H13">
-        <v>0.23</v>
+        <v>-0.57</v>
       </c>
       <c r="I13" t="s">
         <v>157</v>
       </c>
       <c r="J13">
-        <v>5.89</v>
+        <v>2.06</v>
       </c>
       <c r="K13">
-        <v>1.91</v>
+        <v>2.76</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="M13" t="s">
-        <v>244</v>
+        <v>189</v>
       </c>
       <c r="N13">
-        <v>49092</v>
+        <v>62649.99</v>
       </c>
       <c r="O13">
-        <v>1086</v>
+        <v>940.68</v>
       </c>
       <c r="P13">
-        <v>16002</v>
+        <v>175.81</v>
       </c>
       <c r="Q13" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B14" t="s">
         <v>431</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>417</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="E14" t="s">
         <v>164</v>
       </c>
       <c r="F14">
-        <v>188.19</v>
+        <v>179.6</v>
       </c>
       <c r="G14">
         <v>2</v>
       </c>
       <c r="H14">
-        <v>-0.94</v>
+        <v>0.15</v>
       </c>
       <c r="I14" t="s">
         <v>157</v>
       </c>
       <c r="J14">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="K14">
-        <v>2.36</v>
+        <v>1.12</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M14" t="s">
         <v>189</v>
       </c>
       <c r="N14">
-        <v>62596.16</v>
+        <v>62212.15</v>
       </c>
       <c r="O14">
-        <v>939.84</v>
+        <v>993.3</v>
       </c>
       <c r="P14">
-        <v>175.16</v>
+        <v>795.05</v>
       </c>
       <c r="Q14" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B15" t="s">
         <v>432</v>
@@ -18313,7 +18313,7 @@
         <v>164</v>
       </c>
       <c r="F15">
-        <v>184.59</v>
+        <v>175.27</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -18325,36 +18325,36 @@
         <v>157</v>
       </c>
       <c r="J15">
-        <v>10.95</v>
+        <v>5.21</v>
       </c>
       <c r="K15">
-        <v>1.26</v>
+        <v>0.33</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="M15" t="s">
         <v>189</v>
       </c>
       <c r="N15">
-        <v>62640</v>
+        <v>62256.2</v>
       </c>
       <c r="O15">
-        <v>2520</v>
+        <v>2586.3</v>
       </c>
       <c r="P15">
-        <v>150.3</v>
+        <v>806.35</v>
       </c>
       <c r="Q15" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="B16" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
@@ -18366,7 +18366,7 @@
         <v>164</v>
       </c>
       <c r="F16">
-        <v>180.63</v>
+        <v>172.59</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -18378,28 +18378,28 @@
         <v>157</v>
       </c>
       <c r="J16">
-        <v>5.21</v>
+        <v>10.95</v>
       </c>
       <c r="K16">
-        <v>0.33</v>
+        <v>1.26</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M16" t="s">
         <v>189</v>
       </c>
       <c r="N16">
-        <v>62256.2</v>
+        <v>62640</v>
       </c>
       <c r="O16">
-        <v>2586.3</v>
+        <v>2520</v>
       </c>
       <c r="P16">
-        <v>806.35</v>
+        <v>150.3</v>
       </c>
       <c r="Q16" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -18490,10 +18490,10 @@
         <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E2" t="s">
         <v>186</v>
@@ -18540,7 +18540,7 @@
         <v>186</v>
       </c>
       <c r="C3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D3" t="s">
         <v>41</v>
@@ -18746,10 +18746,10 @@
         <v>227</v>
       </c>
       <c r="C7" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E7" t="s">
         <v>227</v>
@@ -18852,10 +18852,10 @@
         <v>227</v>
       </c>
       <c r="C9" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E9" t="s">
         <v>227</v>
@@ -18958,10 +18958,10 @@
         <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D11" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E11" t="s">
         <v>186</v>
@@ -19011,7 +19011,7 @@
         <v>186</v>
       </c>
       <c r="C12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D12" t="s">
         <v>41</v>
@@ -19064,7 +19064,7 @@
         <v>154</v>
       </c>
       <c r="C13" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D13" t="s">
         <v>41</v>
@@ -19117,10 +19117,10 @@
         <v>154</v>
       </c>
       <c r="C14" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D14" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E14" t="s">
         <v>154</v>
@@ -19170,10 +19170,10 @@
         <v>154</v>
       </c>
       <c r="C15" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D15" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E15" t="s">
         <v>154</v>
@@ -19382,7 +19382,7 @@
         <v>186</v>
       </c>
       <c r="C19" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D19" t="s">
         <v>41</v>
@@ -19435,7 +19435,7 @@
         <v>186</v>
       </c>
       <c r="C20" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D20" t="s">
         <v>41</v>
@@ -19700,7 +19700,7 @@
         <v>186</v>
       </c>
       <c r="C25" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D25" t="s">
         <v>41</v>
@@ -19753,7 +19753,7 @@
         <v>186</v>
       </c>
       <c r="C26" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D26" t="s">
         <v>41</v>
@@ -19859,7 +19859,7 @@
         <v>186</v>
       </c>
       <c r="C28" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D28" t="s">
         <v>41</v>
@@ -19912,10 +19912,10 @@
         <v>154</v>
       </c>
       <c r="C29" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D29" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E29" t="s">
         <v>154</v>
@@ -20071,7 +20071,7 @@
         <v>154</v>
       </c>
       <c r="C32" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D32" t="s">
         <v>41</v>
@@ -20124,10 +20124,10 @@
         <v>154</v>
       </c>
       <c r="C33" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D33" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E33" t="s">
         <v>154</v>
@@ -20230,10 +20230,10 @@
         <v>154</v>
       </c>
       <c r="C35" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D35" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E35" t="s">
         <v>154</v>
@@ -20442,7 +20442,7 @@
         <v>155</v>
       </c>
       <c r="C39" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D39" t="s">
         <v>41</v>
@@ -20516,7 +20516,7 @@
         <v>164</v>
       </c>
       <c r="J40">
-        <v>239.34</v>
+        <v>223.34</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -20531,7 +20531,7 @@
         <v>1.86</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P40">
         <v>1</v>
@@ -20569,7 +20569,7 @@
         <v>164</v>
       </c>
       <c r="J41">
-        <v>230.99</v>
+        <v>218.99</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -20584,7 +20584,7 @@
         <v>1.26</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P41">
         <v>1</v>
@@ -20622,7 +20622,7 @@
         <v>164</v>
       </c>
       <c r="J42">
-        <v>221.06</v>
+        <v>210.56</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -20637,7 +20637,7 @@
         <v>0.77</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="P42">
         <v>1</v>
@@ -20654,49 +20654,49 @@
         <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="D43" t="s">
         <v>41</v>
       </c>
       <c r="E43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F43">
-        <v>23.700000762939453</v>
+        <v>5986</v>
       </c>
       <c r="G43" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="H43" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="I43" t="s">
         <v>164</v>
       </c>
       <c r="J43">
-        <v>215.12</v>
+        <v>209.16</v>
       </c>
       <c r="K43">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="L43" t="s">
         <v>157</v>
       </c>
       <c r="M43">
-        <v>13.44</v>
+        <v>5.95</v>
       </c>
       <c r="N43">
-        <v>3.2</v>
+        <v>1.88</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="P43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -20707,49 +20707,49 @@
         <v>155</v>
       </c>
       <c r="C44" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D44" t="s">
-        <v>423</v>
+        <v>41</v>
       </c>
       <c r="E44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F44">
-        <v>2746.199951171875</v>
+        <v>23.700000762939453</v>
       </c>
       <c r="G44" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="H44" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="I44" t="s">
         <v>164</v>
       </c>
       <c r="J44">
-        <v>214.9</v>
+        <v>203.12</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="L44" t="s">
         <v>157</v>
       </c>
       <c r="M44">
-        <v>8.51</v>
+        <v>13.44</v>
       </c>
       <c r="N44">
-        <v>1.44</v>
+        <v>3.2</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -20763,13 +20763,13 @@
         <v>424</v>
       </c>
       <c r="D45" t="s">
-        <v>41</v>
+        <v>425</v>
       </c>
       <c r="E45" t="s">
         <v>155</v>
       </c>
       <c r="F45">
-        <v>5986</v>
+        <v>2746.199951171875</v>
       </c>
       <c r="G45" t="s">
         <v>447</v>
@@ -20781,7 +20781,7 @@
         <v>164</v>
       </c>
       <c r="J45">
-        <v>214.51</v>
+        <v>202.9</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -20790,13 +20790,13 @@
         <v>157</v>
       </c>
       <c r="M45">
-        <v>5.95</v>
+        <v>8.51</v>
       </c>
       <c r="N45">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P45">
         <v>1</v>
@@ -20813,7 +20813,7 @@
         <v>155</v>
       </c>
       <c r="C46" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D46" t="s">
         <v>41</v>
@@ -20834,7 +20834,7 @@
         <v>164</v>
       </c>
       <c r="J46">
-        <v>195.32</v>
+        <v>189.32</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -20849,7 +20849,7 @@
         <v>1.76</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P46">
         <v>1</v>
@@ -20875,19 +20875,19 @@
         <v>155</v>
       </c>
       <c r="F47">
-        <v>156.60000610351562</v>
+        <v>841.2999877929688</v>
       </c>
       <c r="G47" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="H47" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="I47" t="s">
         <v>164</v>
       </c>
       <c r="J47">
-        <v>184.59</v>
+        <v>175.27</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -20896,19 +20896,19 @@
         <v>157</v>
       </c>
       <c r="M47">
-        <v>10.95</v>
+        <v>5.21</v>
       </c>
       <c r="N47">
-        <v>1.26</v>
+        <v>0.33</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P47">
         <v>1</v>
       </c>
       <c r="Q47" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -20919,7 +20919,7 @@
         <v>155</v>
       </c>
       <c r="C48" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D48" t="s">
         <v>41</v>
@@ -20928,19 +20928,19 @@
         <v>155</v>
       </c>
       <c r="F48">
-        <v>841.2999877929688</v>
+        <v>156.60000610351562</v>
       </c>
       <c r="G48" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="H48" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="I48" t="s">
         <v>164</v>
       </c>
       <c r="J48">
-        <v>180.63</v>
+        <v>172.59</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -20949,19 +20949,19 @@
         <v>157</v>
       </c>
       <c r="M48">
-        <v>5.21</v>
+        <v>10.95</v>
       </c>
       <c r="N48">
-        <v>0.33</v>
+        <v>1.26</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P48">
         <v>1</v>
       </c>
       <c r="Q48" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -31,7 +31,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T08:35:27.887Z</t>
+    <t>2026-07-16T08:54:09.531Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1411,7 +1411,7 @@
     <t>2026-07-16T03:46:27.865Z</t>
   </si>
   <si>
-    <t>2026-07-16T08:35:26.245Z</t>
+    <t>2026-07-16T08:54:07.842Z</t>
   </si>
   <si>
     <t>DEFERRED</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -31,7 +31,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T08:54:09.531Z</t>
+    <t>2026-07-16T09:14:11.315Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1411,7 +1411,7 @@
     <t>2026-07-16T03:46:27.865Z</t>
   </si>
   <si>
-    <t>2026-07-16T08:54:07.842Z</t>
+    <t>2026-07-16T09:14:09.400Z</t>
   </si>
   <si>
     <t>DEFERRED</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -31,7 +31,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T09:14:11.315Z</t>
+    <t>2026-07-16T10:04:41.547Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1411,7 +1411,7 @@
     <t>2026-07-16T03:46:27.865Z</t>
   </si>
   <si>
-    <t>2026-07-16T09:14:09.400Z</t>
+    <t>2026-07-16T10:04:39.799Z</t>
   </si>
   <si>
     <t>DEFERRED</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -31,7 +31,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T10:04:41.547Z</t>
+    <t>2026-07-16T10:11:38.701Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1411,7 +1411,7 @@
     <t>2026-07-16T03:46:27.865Z</t>
   </si>
   <si>
-    <t>2026-07-16T10:04:39.799Z</t>
+    <t>2026-07-16T10:11:36.965Z</t>
   </si>
   <si>
     <t>DEFERRED</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3953" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3953" uniqueCount="490">
   <si>
     <t>Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T10:37:27.663Z</t>
+    <t>2026-07-16T10:49:23.614Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1469,6 +1469,9 @@
   </si>
   <si>
     <t>2026-07-16T10:37:25.710Z</t>
+  </si>
+  <si>
+    <t>2026-07-16T10:49:21.086Z</t>
   </si>
   <si>
     <t>Amount</t>
@@ -2242,13 +2245,13 @@
         <v>387</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>398</v>
@@ -2256,10 +2259,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -2271,7 +2274,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -21385,7 +21388,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B50" t="s">
         <v>314</v>
@@ -21438,7 +21441,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B51" t="s">
         <v>314</v>
@@ -21491,7 +21494,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B52" t="s">
         <v>314</v>
@@ -21544,7 +21547,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B53" t="s">
         <v>314</v>
@@ -21597,7 +21600,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B54" t="s">
         <v>314</v>
@@ -21650,7 +21653,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B55" t="s">
         <v>314</v>
@@ -21703,7 +21706,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B56" t="s">
         <v>314</v>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -31,7 +31,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T10:49:23.614Z</t>
+    <t>2026-07-16T10:55:41.292Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -1471,7 +1471,7 @@
     <t>2026-07-16T10:37:25.710Z</t>
   </si>
   <si>
-    <t>2026-07-16T10:49:21.086Z</t>
+    <t>2026-07-16T10:55:38.845Z</t>
   </si>
   <si>
     <t>Amount</t>

--- a/data/techno-funda-trade-sheet.xlsx
+++ b/data/techno-funda-trade-sheet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3953" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3951" uniqueCount="488">
   <si>
     <t>Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Updated At</t>
   </si>
   <si>
-    <t>2026-07-16T10:55:41.292Z</t>
+    <t>2026-07-16T11:03:32.768Z</t>
   </si>
   <si>
     <t>Total Capital</t>
@@ -835,12 +835,42 @@
     <t>Best only (A+/A)</t>
   </si>
   <si>
+    <t>PRUDENT</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 33 @ 2986; turnover 98538; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 16 @ 2989.4; turnover 47830.4; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 54.4</t>
+  </si>
+  <si>
+    <t>daily RS21 below zero daily RS55 below zero daily RSI below 50 setup grade WATCH ENTRY RETEST GRACE: 2/5 completed closes observed; normal pullback is tolerated while weekly RS, daily RS55 and original stop remain valid. RS55 EXIT CONFIRMATION: marginal reading -0.01 has 1/2 completed below-zero closes; immediate weekly, Supertrend/structural and hard-threshold protections remain active.</t>
+  </si>
+  <si>
+    <t>15/21</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Index option-chain positioning</t>
+  </si>
+  <si>
+    <t>Intraday tick scalping; Broker-only live Greeks/order-book depth</t>
+  </si>
+  <si>
+    <t>64.29% (90/140)</t>
+  </si>
+  <si>
+    <t>Weekly RSI 63.57 is above 50. Daily RSI 53.42 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 4.7% is above 0. Daily close 2960.00 is above Supertrend(10, 3) 2759.71. Price action strength: close is within 15% of 52-week high 3160.10. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.77% above daily Supertrend. Volatility is controlled: ATR(14) is 3.14% of price. Liquidity strength: 20-day average turnover is Rs 67973469.69. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
+  </si>
+  <si>
     <t>KPIL</t>
   </si>
   <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
     <t>2026-07-10 09:17 IST ENTRY_BUY BUY 73 @ 1351.4; turnover 98652.2; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-14 09:17 IST PARTIAL_EXIT SELL 36 @ 1333.5; turnover 48006; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -644.4 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 18 @ 1305.2; turnover 23493.6; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -831.6</t>
   </si>
   <si>
@@ -856,15 +886,6 @@
     <t>RS trend follow-through; Volume participation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
   </si>
   <si>
-    <t>Index option-chain positioning</t>
-  </si>
-  <si>
-    <t>Intraday tick scalping; Broker-only live Greeks/order-book depth</t>
-  </si>
-  <si>
-    <t>64.29% (90/140)</t>
-  </si>
-  <si>
     <t>bullish engulfing</t>
   </si>
   <si>
@@ -931,9 +952,6 @@
     <t>2026-07-10 09:17 IST ENTRY_BUY BUY 71 @ 1373.5; turnover 97518.5; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0</t>
   </si>
   <si>
-    <t>15/21</t>
-  </si>
-  <si>
     <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
   </si>
   <si>
@@ -958,228 +976,204 @@
     <t>Weekly RSI 64.67 is above 50. Daily RSI 61.84 is above 50. Weekly RS 54.7% is above 0. Daily long RS55 46.8% is above 0. Daily short RS21 15.0% is above 0. Daily close 800.45 is above Supertrend(10, 3) 673.89. Price action strength: close is within 15% of 52-week high 861.25. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation + bullish engulfing is present. Volatility is controlled: ATR(14) is 4.91% of price. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 14/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
   </si>
   <si>
-    <t>PRUDENT</t>
-  </si>
-  <si>
-    <t>PENDING_EXIT</t>
+    <t>My Custom List</t>
+  </si>
+  <si>
+    <t>NEXUSSURGL</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>09:21 IST</t>
+  </si>
+  <si>
+    <t>09:17 market order; first actual traded candle at 09:21 IST</t>
+  </si>
+  <si>
+    <t>09:17 order / 09:21 actual fill</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>2026-07-13 09:17 IST ENTRY_BUY BUY 31 @ 19.59; turnover 607.29; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-13 09:17 IST PARTIAL_EXIT SELL 15 @ 19.59; turnover 293.85; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST FULL_EXIT SELL 16 @ 18.5; turnover 296; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -17.44</t>
+  </si>
+  <si>
+    <t>MODEL_EXIT</t>
+  </si>
+  <si>
+    <t>FULL_EXIT</t>
+  </si>
+  <si>
+    <t>Daily RS55 is below zero and daily close is below Supertrend.</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Bollinger trend/range context; MACD and OBV confirmation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>Breakout or 52-week high zone; Price-action base and higher-low structure; Retracement/pullback buy setup; GTF demand/supply confluence; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Volume participation; Volatility and liquidity control; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
+  </si>
+  <si>
+    <t>Operator delivery confirmation; Index option-chain positioning; News/event context</t>
+  </si>
+  <si>
+    <t>hammer</t>
+  </si>
+  <si>
+    <t>Weekly RSI 58.57 is above 50. Daily RSI 52.69 is above 50. Weekly RS 21.8% is above 0. Daily long RS55 4.6% is above 0. Daily short RS21 1.3% is above 0. Daily close 20.87 is above Supertrend(10, 3) 18.63. Entry style: Trend continuation buy. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: close is above the middle band 20.41 with bandwidth 14.62%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: hammer is present. Volatility is controlled: ATR(14) is 5.69% of price. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 0/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Official NSE delivery history loaded for 2395 EQ symbols across 6 sessions. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Sector breadth strong: My List has 123/175 stocks (70.29%) passing daily strength. Institutional concept coverage: 16/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 168.93; planned allocation Rs 83.48, quantity 4, initial stop 20, planned risk Rs 3.48. Closing signal dated 2026-07-10; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>Daily RS55 is below zero and daily close is below Supertrend. Closing exit signal dated 2026-07-14; sell fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>SKIPPED_ENTRY</t>
+  </si>
+  <si>
+    <t>first_5m_candle_open</t>
+  </si>
+  <si>
+    <t>09:15-09:20 IST</t>
+  </si>
+  <si>
+    <t>3/4</t>
+  </si>
+  <si>
+    <t>F&amp;O listed with lot size 150; OI participation 2.01%, volume 72606.00.</t>
+  </si>
+  <si>
+    <t>2/5 commodity/currency proxies are bullish; 3 bearish.</t>
+  </si>
+  <si>
+    <t>20/22</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>Volume participation</t>
+  </si>
+  <si>
+    <t>66.43% (93/140)</t>
+  </si>
+  <si>
+    <t>Weekly RSI 55.15 is above 50. Daily RSI 60.53 is above 50. Weekly RS 6.8% is above 0. Daily long RS55 2.1% is above 0. Daily short RS21 2.3% is above 0. Daily close 4506.80 is above Supertrend(10, 3) 4193.48. Entry style: Retracement buy near 50-DMA. Price action strength: close is within 15% of 52-week high 5065.00. Retracement buy: price pulled back 6.81% from the 55-day high and reclaimed near 50-DMA 4407.24; support distance is 2.21%. Retracement confirmation: pullback volume ratio 0.58 and reclaim volume ratio 0.99 with candle close location 85.96%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.95% above daily Supertrend. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.15% of price. Liquidity strength: 20-day average turnover is Rs 3498340071.08. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 150; OI participation 2.01%, volume 72606.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 20/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>PREMIERENE</t>
+  </si>
+  <si>
+    <t>F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00.</t>
+  </si>
+  <si>
+    <t>18/22</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Retracement/pullback buy setup; Risk reference discipline</t>
+  </si>
+  <si>
+    <t>Weekly RSI 64.52 is above 50. Daily RSI 67.28 is above 50. Weekly RS 46.9% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 0.0% is above 0. Daily close 1117.20 is above Supertrend(10, 3) 1007.42. Entry style: Breakout buy. Price action strength: close crossed 55-day high 1103.90. Volume shocker: latest volume is 1.56x the 50-day average. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.97% of price. Liquidity strength: 20-day average turnover is Rs 1219054718.79. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 18/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>SBCL</t>
+  </si>
+  <si>
+    <t>14/22</t>
+  </si>
+  <si>
+    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
+  </si>
+  <si>
+    <t>RS trend follow-through; Retracement/pullback buy setup; Volume participation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
+  </si>
+  <si>
+    <t>Weekly RSI 66.35 is above 50. Daily RSI 53.52 is above 50. Weekly RS 45.4% is above 0. Daily long RS55 21.9% is above 0. Daily short RS21 5.9% is above 0. Daily close 747.05 is above Supertrend(10, 3) 679.08. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 814.00. Retracement watch: pullback depth 8.22% is valid, but support/reclaim/volume/risk confirmation is incomplete. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 4.83% of price. Liquidity strength: 20-day average turnover is Rs 407588740.32. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 14/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
+  </si>
+  <si>
+    <t>Transaction</t>
+  </si>
+  <si>
+    <t>Side</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Turnover</t>
+  </si>
+  <si>
+    <t>Brokerage</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Exchange Charges</t>
+  </si>
+  <si>
+    <t>SEBI Charges</t>
+  </si>
+  <si>
+    <t>Stamp Duty</t>
+  </si>
+  <si>
+    <t>IPFT</t>
+  </si>
+  <si>
+    <t>GST</t>
+  </si>
+  <si>
+    <t>DP Charge</t>
+  </si>
+  <si>
+    <t>Total Charges</t>
+  </si>
+  <si>
+    <t>Gross P&amp;L</t>
+  </si>
+  <si>
+    <t>Allocated Buy Charges</t>
+  </si>
+  <si>
+    <t>Net P&amp;L</t>
+  </si>
+  <si>
+    <t>ENTRY_BUY</t>
+  </si>
+  <si>
+    <t>BUY</t>
+  </si>
+  <si>
+    <t>PARTIAL_EXIT</t>
+  </si>
+  <si>
+    <t>SELL</t>
+  </si>
+  <si>
+    <t>09:15 IST</t>
+  </si>
+  <si>
+    <t>DIVIDEND</t>
+  </si>
+  <si>
+    <t>CASH</t>
   </si>
   <si>
     <t>2026-07-16</t>
   </si>
   <si>
-    <t>2026-07-10 09:17 IST ENTRY_BUY BUY 33 @ 2986; turnover 98538; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST PARTIAL_EXIT SELL 16 @ 2989.4; turnover 47830.4; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 54.4</t>
-  </si>
-  <si>
-    <t>MODEL_EXIT</t>
-  </si>
-  <si>
-    <t>FULL_EXIT</t>
-  </si>
-  <si>
-    <t>Completed-close daily long RS55 is below zero.</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Volume participation; Candle IPC confirmation; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Weekly RSI 63.57 is above 50. Daily RSI 53.42 is above 50. Weekly RS 17.4% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 4.7% is above 0. Daily close 2960.00 is above Supertrend(10, 3) 2759.71. Price action strength: close is within 15% of 52-week high 3160.10. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.77% above daily Supertrend. Volatility is controlled: ATR(14) is 3.14% of price. Liquidity strength: 20-day average turnover is Rs 67973469.69. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 1/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 90/140 stocks (64.29%) passing daily strength. Institutional concept coverage: 15/21 applicable video-derived buckets are strong. Trade sheet filter: My List, Best only (A+/A). Closing signal dated 2026-07-09; buy fill must come from the next session exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>Completed-close daily long RS55 is below zero. Closing exit signal dated 2026-07-16; sell fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>My Custom List</t>
-  </si>
-  <si>
-    <t>NEXUSSURGL</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>09:21 IST</t>
-  </si>
-  <si>
-    <t>09:17 market order; first actual traded candle at 09:21 IST</t>
-  </si>
-  <si>
-    <t>09:17 order / 09:21 actual fill</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>2026-07-13 09:17 IST ENTRY_BUY BUY 31 @ 19.59; turnover 607.29; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-13 09:17 IST PARTIAL_EXIT SELL 15 @ 19.59; turnover 293.85; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L 0 | 2026-07-15 09:17 IST FULL_EXIT SELL 16 @ 18.5; turnover 296; brokerage 0; STT 0; exchange 0; SEBI 0; stamp 0; GST 0; DP 0; total 0; net P&amp;L -17.44</t>
-  </si>
-  <si>
-    <t>Daily RS55 is below zero and daily close is below Supertrend.</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Bollinger trend/range context; MACD and OBV confirmation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Market regime; Index regime confirmation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>Breakout or 52-week high zone; Price-action base and higher-low structure; Retracement/pullback buy setup; GTF demand/supply confluence; GTF reacting from higher timeframe (secondary proxy); Fibonacci retracement support; Volume participation; Volatility and liquidity control; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation</t>
-  </si>
-  <si>
-    <t>Operator delivery confirmation; Index option-chain positioning; News/event context</t>
-  </si>
-  <si>
-    <t>hammer</t>
-  </si>
-  <si>
-    <t>Weekly RSI 58.57 is above 50. Daily RSI 52.69 is above 50. Weekly RS 21.8% is above 0. Daily long RS55 4.6% is above 0. Daily short RS21 1.3% is above 0. Daily close 20.87 is above Supertrend(10, 3) 18.63. Entry style: Trend continuation buy. Momentum confirmation: MACD is above signal and zero; OBV is rising. Bollinger context: close is above the middle band 20.41 with bandwidth 14.62%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: hammer is present. Volatility is controlled: ATR(14) is 5.69% of price. Market regime supports longs: NIFTY 500 bullish/healthy. GTF 50-SMA slope: daily up, weekly up. No active daily/weekly/higher-timeframe GTF supply blocker was detected above price. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 0/5 commodity/currency proxies are bullish; 2 bearish. Operator/delivery context: Official NSE delivery history loaded for 2395 EQ symbols across 6 sessions. Institutional confluence score 2/5 (Institutional C). Execution plan: buy on the next actual market session using the exact 09:17 one-minute candle open; weekends and exchange holidays are skipped. Sector breadth strong: My List has 123/175 stocks (70.29%) passing daily strength. Institutional concept coverage: 16/30 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Portfolio rank 168.93; planned allocation Rs 83.48, quantity 4, initial stop 20, planned risk Rs 3.48. Closing signal dated 2026-07-10; buy fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>Daily RS55 is below zero and daily close is below Supertrend. Closing exit signal dated 2026-07-14; sell fill must come from the next actual market session at exactly 09:17 IST, after skipping weekends and exchange holidays.</t>
-  </si>
-  <si>
-    <t>HAL</t>
-  </si>
-  <si>
-    <t>SKIPPED_ENTRY</t>
-  </si>
-  <si>
-    <t>first_5m_candle_open</t>
-  </si>
-  <si>
-    <t>09:15-09:20 IST</t>
-  </si>
-  <si>
-    <t>3/4</t>
-  </si>
-  <si>
-    <t>F&amp;O listed with lot size 150; OI participation 2.01%, volume 72606.00.</t>
-  </si>
-  <si>
-    <t>2/5 commodity/currency proxies are bullish; 3 bearish.</t>
-  </si>
-  <si>
-    <t>20/22</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RS trend follow-through; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Retracement/pullback buy setup; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Risk reference discipline; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>Volume participation</t>
-  </si>
-  <si>
-    <t>66.43% (93/140)</t>
-  </si>
-  <si>
-    <t>Weekly RSI 55.15 is above 50. Daily RSI 60.53 is above 50. Weekly RS 6.8% is above 0. Daily long RS55 2.1% is above 0. Daily short RS21 2.3% is above 0. Daily close 4506.80 is above Supertrend(10, 3) 4193.48. Entry style: Retracement buy near 50-DMA. Price action strength: close is within 15% of 52-week high 5065.00. Retracement buy: price pulled back 6.81% from the 55-day high and reclaimed near 50-DMA 4407.24; support distance is 2.21%. Retracement confirmation: pullback volume ratio 0.58 and reclaim volume ratio 0.99 with candle close location 85.96%. RS trend strength: weekly RS and daily RS55 are rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Risk reference: close is 6.95% above daily Supertrend. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.15% of price. Liquidity strength: 20-day average turnover is Rs 3498340071.08. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 150; OI participation 2.01%, volume 72606.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 20/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>PREMIERENE</t>
-  </si>
-  <si>
-    <t>F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00.</t>
-  </si>
-  <si>
-    <t>18/22</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Volume participation; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Derivative/F&amp;O eligibility; Derivative OI participation; Commodity/currency macro context; Fundamental improvement; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Retracement/pullback buy setup; Risk reference discipline</t>
-  </si>
-  <si>
-    <t>Weekly RSI 64.52 is above 50. Daily RSI 67.28 is above 50. Weekly RS 46.9% is above 0. Daily long RS55 7.2% is above 0. Daily short RS21 0.0% is above 0. Daily close 1117.20 is above Supertrend(10, 3) 1007.42. Entry style: Breakout buy. Price action strength: close crossed 55-day high 1103.90. Volume shocker: latest volume is 1.56x the 50-day average. RS trend strength: daily RS55 is rising. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 2.97% of price. Liquidity strength: 20-day average turnover is Rs 1219054718.79. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: F&amp;O listed with lot size 650; OI participation 9.81%, volume 19248.00. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 3/4 (Institutional B). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 18/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>SBCL</t>
-  </si>
-  <si>
-    <t>14/22</t>
-  </si>
-  <si>
-    <t>Compulsory multi-timeframe engine; Relative strength leadership; RSI momentum; Supertrend trend filter; Breakout or 52-week high zone; Sector breadth; 50/200 DMA trend structure; Candle IPC confirmation; Volatility and liquidity control; Market regime; Index regime confirmation; Commodity/currency macro context; Exit rule discipline; 09:17 execution discipline</t>
-  </si>
-  <si>
-    <t>RS trend follow-through; Retracement/pullback buy setup; Volume participation; Risk reference discipline; Derivative/F&amp;O eligibility; Derivative OI participation; Fundamental improvement</t>
-  </si>
-  <si>
-    <t>Weekly RSI 66.35 is above 50. Daily RSI 53.52 is above 50. Weekly RS 45.4% is above 0. Daily long RS55 21.9% is above 0. Daily short RS21 5.9% is above 0. Daily close 747.05 is above Supertrend(10, 3) 679.08. Entry style: Trend continuation buy. Price action strength: close is within 15% of 52-week high 814.00. Retracement watch: pullback depth 8.22% is valid, but support/reclaim/volume/risk confirmation is incomplete. Trend strength: close is above 50-DMA and 200-DMA, with fast DMA above slow DMA. Price confirmation: previous-high confirmation is present. Volatility is controlled: ATR(14) is 4.83% of price. Liquidity strength: 20-day average turnover is Rs 407588740.32. Market regime supports longs: NIFTY 500 bullish/healthy. Index context: NIFTY 500 proxy is BULLISH; broad index support is positive. Derivatives context: Not present in NSE F&amp;O lot-size master; treat as cash-equity only. Options context: NSE option-chain snapshot unavailable; mark this as data gap, not as bearish. Commodity/currency context: 2/5 commodity/currency proxies are bullish; 3 bearish. Institutional confluence score 2/4 (Institutional C). Execution plan: buy on the next trading session using the 09:17 one-minute candle open. Sector breadth strong: My List has 93/140 stocks (66.43%) passing daily strength. Institutional concept coverage: 14/22 applicable video-derived buckets are strong. Trade sheet filter: My List, Strong and best (A+/A/B). Closing signal dated 2026-07-10; buy fill must come from the next session at exactly 09:17 IST.</t>
-  </si>
-  <si>
-    <t>Transaction</t>
-  </si>
-  <si>
-    <t>Side</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Turnover</t>
-  </si>
-  <si>
-    <t>Brokerage</t>
-  </si>
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Exchange Charges</t>
-  </si>
-  <si>
-    <t>SEBI Charges</t>
-  </si>
-  <si>
-    <t>Stamp Duty</t>
-  </si>
-  <si>
-    <t>IPFT</t>
-  </si>
-  <si>
-    <t>GST</t>
-  </si>
-  <si>
-    <t>DP Charge</t>
-  </si>
-  <si>
-    <t>Total Charges</t>
-  </si>
-  <si>
-    <t>Gross P&amp;L</t>
-  </si>
-  <si>
-    <t>Allocated Buy Charges</t>
-  </si>
-  <si>
-    <t>Net P&amp;L</t>
-  </si>
-  <si>
-    <t>ENTRY_BUY</t>
-  </si>
-  <si>
-    <t>BUY</t>
-  </si>
-  <si>
-    <t>PARTIAL_EXIT</t>
-  </si>
-  <si>
-    <t>SELL</t>
-  </si>
-  <si>
-    <t>09:15 IST</t>
-  </si>
-  <si>
-    <t>DIVIDEND</t>
-  </si>
-  <si>
-    <t>CASH</t>
-  </si>
-  <si>
     <t>EX-DATE</t>
   </si>
   <si>
@@ -1471,7 +1465,7 @@
     <t>2026-07-16T10:37:25.710Z</t>
   </si>
   <si>
-    <t>2026-07-16T10:55:38.845Z</t>
+    <t>2026-07-16T11:03:30.470Z</t>
   </si>
   <si>
     <t>Amount</t>
@@ -2032,7 +2026,7 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2040,7 +2034,7 @@
         <v>21</v>
       </c>
       <c r="B19">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2080,7 +2074,7 @@
         <v>26</v>
       </c>
       <c r="B24">
-        <v>10240.73</v>
+        <v>8161.63</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2239,30 +2233,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>486</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C2">
         <v>1000000</v>
@@ -2274,7 +2268,7 @@
         <v>1000000</v>
       </c>
       <c r="F2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -2286,7 +2280,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DG15"/>
+  <dimension ref="A1:DG16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -5401,7 +5395,7 @@
         <v>270</v>
       </c>
       <c r="C10" t="s">
-        <v>213</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
         <v>271</v>
@@ -5425,40 +5419,40 @@
         <v>49</v>
       </c>
       <c r="K10">
-        <v>1351.4</v>
+        <v>2986</v>
       </c>
       <c r="L10">
-        <v>1351.4</v>
+        <v>2986</v>
       </c>
       <c r="M10" t="s">
         <v>156</v>
       </c>
       <c r="N10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O10">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="P10">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="Q10">
-        <v>25676.6</v>
+        <v>50762</v>
       </c>
       <c r="R10">
-        <v>25081.9</v>
+        <v>48682.9</v>
       </c>
       <c r="S10">
-        <v>1320.1</v>
+        <v>2863.7</v>
       </c>
       <c r="T10" s="2">
-        <v>-594.7</v>
+        <v>-2079.1</v>
       </c>
       <c r="U10">
-        <v>-2.32</v>
+        <v>-4.1</v>
       </c>
       <c r="V10">
-        <v>-594.7</v>
+        <v>-2079.1</v>
       </c>
       <c r="W10">
         <v>0</v>
@@ -5491,7 +5485,7 @@
         <v>157</v>
       </c>
       <c r="AG10">
-        <v>-1476</v>
+        <v>54.4</v>
       </c>
       <c r="AH10">
         <v>0</v>
@@ -5512,28 +5506,28 @@
         <v>157</v>
       </c>
       <c r="AN10">
-        <v>106.57</v>
+        <v>92.61</v>
       </c>
       <c r="AO10">
-        <v>1251.2</v>
+        <v>2728.17</v>
       </c>
       <c r="AP10">
-        <v>1278.43</v>
+        <v>2882.7</v>
       </c>
       <c r="AQ10">
-        <v>1352</v>
+        <v>2983.199951171875</v>
       </c>
       <c r="AR10">
-        <v>1304.032274715177</v>
+        <v>2827.406442040053</v>
       </c>
       <c r="AS10" t="s">
         <v>158</v>
       </c>
       <c r="AT10">
-        <v>7314.6</v>
+        <v>8508.39</v>
       </c>
       <c r="AU10">
-        <v>-0.31</v>
+        <v>-0.47</v>
       </c>
       <c r="AV10">
         <v>0</v>
@@ -5560,13 +5554,13 @@
         <v>157</v>
       </c>
       <c r="BD10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE10">
-        <v>-1476</v>
+        <v>54.4</v>
       </c>
       <c r="BF10">
-        <v>-1476</v>
+        <v>54.4</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -5617,10 +5611,10 @@
         <v>164</v>
       </c>
       <c r="BW10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BX10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BY10" t="s">
         <v>229</v>
@@ -5683,13 +5677,13 @@
         <v>29</v>
       </c>
       <c r="CS10">
-        <v>0.32</v>
+        <v>1.21</v>
       </c>
       <c r="CT10">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="CU10">
-        <v>2.68</v>
+        <v>6.77</v>
       </c>
       <c r="CV10" t="s">
         <v>29</v>
@@ -5710,19 +5704,19 @@
         <v>157</v>
       </c>
       <c r="DB10" t="s">
+        <v>223</v>
+      </c>
+      <c r="DC10">
+        <v>2903.2</v>
+      </c>
+      <c r="DD10">
+        <v>2903.2</v>
+      </c>
+      <c r="DE10">
+        <v>2903.2</v>
+      </c>
+      <c r="DF10" t="s">
         <v>281</v>
-      </c>
-      <c r="DC10">
-        <v>1321</v>
-      </c>
-      <c r="DD10">
-        <v>1321</v>
-      </c>
-      <c r="DE10">
-        <v>1321</v>
-      </c>
-      <c r="DF10" t="s">
-        <v>282</v>
       </c>
       <c r="DG10" t="s">
         <v>157</v>
@@ -5736,13 +5730,13 @@
         <v>270</v>
       </c>
       <c r="C11" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="D11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F11" t="s">
         <v>153</v>
@@ -5760,40 +5754,40 @@
         <v>49</v>
       </c>
       <c r="K11">
-        <v>437.05</v>
+        <v>1351.4</v>
       </c>
       <c r="L11">
-        <v>437.05</v>
+        <v>1351.4</v>
       </c>
       <c r="M11" t="s">
         <v>156</v>
       </c>
       <c r="N11">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="O11">
-        <v>228</v>
+        <v>73</v>
       </c>
       <c r="P11">
-        <v>228</v>
+        <v>73</v>
       </c>
       <c r="Q11">
-        <v>49823.7</v>
+        <v>25676.6</v>
       </c>
       <c r="R11">
-        <v>50188.5</v>
+        <v>25081.9</v>
       </c>
       <c r="S11">
-        <v>440.25</v>
-      </c>
-      <c r="T11" s="3">
-        <v>364.8</v>
+        <v>1320.1</v>
+      </c>
+      <c r="T11" s="2">
+        <v>-594.7</v>
       </c>
       <c r="U11">
-        <v>0.73</v>
+        <v>-2.32</v>
       </c>
       <c r="V11">
-        <v>364.8</v>
+        <v>-594.7</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -5826,7 +5820,7 @@
         <v>157</v>
       </c>
       <c r="AG11">
-        <v>-501.6</v>
+        <v>-1476</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -5847,28 +5841,28 @@
         <v>157</v>
       </c>
       <c r="AN11">
-        <v>180.01</v>
+        <v>106.57</v>
       </c>
       <c r="AO11">
-        <v>402.78</v>
+        <v>1251.2</v>
       </c>
       <c r="AP11">
-        <v>429.85</v>
+        <v>1278.43</v>
       </c>
       <c r="AQ11">
-        <v>435.5</v>
+        <v>1352</v>
       </c>
       <c r="AR11">
-        <v>398.6403308636572</v>
+        <v>1304.032274715177</v>
       </c>
       <c r="AS11" t="s">
         <v>158</v>
       </c>
       <c r="AT11">
-        <v>7813.56</v>
+        <v>7314.6</v>
       </c>
       <c r="AU11">
-        <v>0.09</v>
+        <v>-0.31</v>
       </c>
       <c r="AV11">
         <v>0</v>
@@ -5895,13 +5889,13 @@
         <v>157</v>
       </c>
       <c r="BD11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE11">
-        <v>-501.6</v>
+        <v>-1476</v>
       </c>
       <c r="BF11">
-        <v>-501.6</v>
+        <v>-1476</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -5913,7 +5907,7 @@
         <v>157</v>
       </c>
       <c r="BJ11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="BK11" t="s">
         <v>157</v>
@@ -5934,13 +5928,13 @@
         <v>160</v>
       </c>
       <c r="BQ11" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS11" t="s">
-        <v>285</v>
+        <v>157</v>
       </c>
       <c r="BT11" t="s">
         <v>157</v>
@@ -5952,10 +5946,10 @@
         <v>164</v>
       </c>
       <c r="BW11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BX11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BY11" t="s">
         <v>229</v>
@@ -5994,13 +5988,13 @@
         <v>192</v>
       </c>
       <c r="CK11" t="s">
+        <v>285</v>
+      </c>
+      <c r="CL11" t="s">
         <v>286</v>
       </c>
-      <c r="CL11" t="s">
+      <c r="CM11" t="s">
         <v>287</v>
-      </c>
-      <c r="CM11" t="s">
-        <v>288</v>
       </c>
       <c r="CN11" t="s">
         <v>278</v>
@@ -6018,13 +6012,13 @@
         <v>29</v>
       </c>
       <c r="CS11">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="CT11">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="CU11">
-        <v>9.13</v>
+        <v>2.68</v>
       </c>
       <c r="CV11" t="s">
         <v>29</v>
@@ -6045,16 +6039,16 @@
         <v>157</v>
       </c>
       <c r="DB11" t="s">
-        <v>223</v>
+        <v>288</v>
       </c>
       <c r="DC11">
-        <v>425.45</v>
+        <v>1321</v>
       </c>
       <c r="DD11">
-        <v>423.3</v>
+        <v>1321</v>
       </c>
       <c r="DE11">
-        <v>422.15</v>
+        <v>1321</v>
       </c>
       <c r="DF11" t="s">
         <v>289</v>
@@ -6095,40 +6089,40 @@
         <v>49</v>
       </c>
       <c r="K12">
-        <v>6621.5</v>
+        <v>437.05</v>
       </c>
       <c r="L12">
-        <v>6621.5</v>
+        <v>437.05</v>
       </c>
       <c r="M12" t="s">
         <v>156</v>
       </c>
       <c r="N12">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="O12">
-        <v>15</v>
+        <v>228</v>
       </c>
       <c r="P12">
-        <v>15</v>
+        <v>228</v>
       </c>
       <c r="Q12">
-        <v>99322.5</v>
+        <v>49823.7</v>
       </c>
       <c r="R12">
-        <v>102817.5</v>
+        <v>50188.5</v>
       </c>
       <c r="S12">
-        <v>6854.5</v>
+        <v>440.25</v>
       </c>
       <c r="T12" s="3">
-        <v>3495</v>
+        <v>364.8</v>
       </c>
       <c r="U12">
-        <v>3.52</v>
+        <v>0.73</v>
       </c>
       <c r="V12">
-        <v>3495</v>
+        <v>364.8</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -6161,7 +6155,7 @@
         <v>157</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>-501.6</v>
       </c>
       <c r="AH12">
         <v>0</v>
@@ -6182,28 +6176,28 @@
         <v>157</v>
       </c>
       <c r="AN12">
-        <v>216.76</v>
+        <v>180.01</v>
       </c>
       <c r="AO12">
-        <v>6083.5</v>
+        <v>402.78</v>
       </c>
       <c r="AP12">
-        <v>6359.98</v>
+        <v>429.85</v>
       </c>
       <c r="AQ12">
-        <v>6839</v>
+        <v>435.5</v>
       </c>
       <c r="AR12">
-        <v>5977.839360894776</v>
+        <v>398.6403308636572</v>
       </c>
       <c r="AS12" t="s">
         <v>158</v>
       </c>
       <c r="AT12">
-        <v>8070</v>
+        <v>7813.56</v>
       </c>
       <c r="AU12">
-        <v>0.43</v>
+        <v>0.09</v>
       </c>
       <c r="AV12">
         <v>0</v>
@@ -6230,13 +6224,13 @@
         <v>157</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>-501.6</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>-501.6</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -6269,13 +6263,13 @@
         <v>160</v>
       </c>
       <c r="BQ12" t="s">
-        <v>161</v>
+        <v>250</v>
       </c>
       <c r="BR12">
         <v>0</v>
       </c>
       <c r="BS12" t="s">
-        <v>157</v>
+        <v>292</v>
       </c>
       <c r="BT12" t="s">
         <v>157</v>
@@ -6287,10 +6281,10 @@
         <v>164</v>
       </c>
       <c r="BW12">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BX12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BY12" t="s">
         <v>229</v>
@@ -6329,13 +6323,13 @@
         <v>192</v>
       </c>
       <c r="CK12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="CL12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="CM12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CN12" t="s">
         <v>278</v>
@@ -6353,13 +6347,13 @@
         <v>29</v>
       </c>
       <c r="CS12">
-        <v>2.02</v>
+        <v>0.22</v>
       </c>
       <c r="CT12">
-        <v>2.56</v>
+        <v>3.42</v>
       </c>
       <c r="CU12">
-        <v>8.7</v>
+        <v>9.13</v>
       </c>
       <c r="CV12" t="s">
         <v>29</v>
@@ -6380,19 +6374,19 @@
         <v>157</v>
       </c>
       <c r="DB12" t="s">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="DC12">
-        <v>6202.5</v>
+        <v>425.45</v>
       </c>
       <c r="DD12">
-        <v>6202.5</v>
+        <v>423.3</v>
       </c>
       <c r="DE12">
-        <v>6202.5</v>
+        <v>422.15</v>
       </c>
       <c r="DF12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="DG12" t="s">
         <v>157</v>
@@ -6406,13 +6400,13 @@
         <v>270</v>
       </c>
       <c r="C13" t="s">
-        <v>213</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F13" t="s">
         <v>153</v>
@@ -6430,40 +6424,40 @@
         <v>49</v>
       </c>
       <c r="K13">
-        <v>1995.8</v>
+        <v>6621.5</v>
       </c>
       <c r="L13">
-        <v>1995.8</v>
+        <v>6621.5</v>
       </c>
       <c r="M13" t="s">
         <v>156</v>
       </c>
       <c r="N13">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="O13">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="P13">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="Q13">
-        <v>97794.2</v>
+        <v>99322.5</v>
       </c>
       <c r="R13">
-        <v>99705.2</v>
+        <v>102817.5</v>
       </c>
       <c r="S13">
-        <v>2034.8</v>
+        <v>6854.5</v>
       </c>
       <c r="T13" s="3">
-        <v>1911</v>
+        <v>3495</v>
       </c>
       <c r="U13">
-        <v>1.95</v>
+        <v>3.52</v>
       </c>
       <c r="V13">
-        <v>1911</v>
+        <v>3495</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -6517,28 +6511,28 @@
         <v>157</v>
       </c>
       <c r="AN13">
-        <v>188.75</v>
+        <v>216.76</v>
       </c>
       <c r="AO13">
-        <v>1842.85</v>
+        <v>6083.5</v>
       </c>
       <c r="AP13">
-        <v>1968</v>
+        <v>6359.98</v>
       </c>
       <c r="AQ13">
-        <v>2027.300048828125</v>
+        <v>6839</v>
       </c>
       <c r="AR13">
-        <v>1900.2560938383647</v>
+        <v>5977.839360894776</v>
       </c>
       <c r="AS13" t="s">
         <v>158</v>
       </c>
       <c r="AT13">
-        <v>7494.55</v>
+        <v>8070</v>
       </c>
       <c r="AU13">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="AV13">
         <v>0</v>
@@ -6583,7 +6577,7 @@
         <v>157</v>
       </c>
       <c r="BJ13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="BK13" t="s">
         <v>157</v>
@@ -6622,10 +6616,10 @@
         <v>164</v>
       </c>
       <c r="BW13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BX13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY13" t="s">
         <v>229</v>
@@ -6664,13 +6658,13 @@
         <v>192</v>
       </c>
       <c r="CK13" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="CL13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="CM13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="CN13" t="s">
         <v>278</v>
@@ -6688,13 +6682,13 @@
         <v>29</v>
       </c>
       <c r="CS13">
-        <v>0.55</v>
+        <v>2.02</v>
       </c>
       <c r="CT13">
         <v>2.56</v>
       </c>
       <c r="CU13">
-        <v>6.47</v>
+        <v>8.7</v>
       </c>
       <c r="CV13" t="s">
         <v>29</v>
@@ -6715,19 +6709,19 @@
         <v>157</v>
       </c>
       <c r="DB13" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="DC13">
-        <v>1957</v>
+        <v>6202.5</v>
       </c>
       <c r="DD13">
-        <v>1957</v>
+        <v>6202.5</v>
       </c>
       <c r="DE13">
-        <v>1957</v>
+        <v>6202.5</v>
       </c>
       <c r="DF13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="DG13" t="s">
         <v>157</v>
@@ -6744,10 +6738,10 @@
         <v>213</v>
       </c>
       <c r="D14" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E14" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F14" t="s">
         <v>153</v>
@@ -6765,40 +6759,40 @@
         <v>49</v>
       </c>
       <c r="K14">
-        <v>1373.5</v>
+        <v>1995.8</v>
       </c>
       <c r="L14">
-        <v>1373.5</v>
+        <v>1995.8</v>
       </c>
       <c r="M14" t="s">
         <v>156</v>
       </c>
       <c r="N14">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="O14">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="P14">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="Q14">
-        <v>97518.5</v>
+        <v>97794.2</v>
       </c>
       <c r="R14">
-        <v>100287.5</v>
+        <v>99705.2</v>
       </c>
       <c r="S14">
-        <v>1412.5</v>
+        <v>2034.8</v>
       </c>
       <c r="T14" s="3">
-        <v>2769</v>
+        <v>1911</v>
       </c>
       <c r="U14">
-        <v>2.84</v>
+        <v>1.95</v>
       </c>
       <c r="V14">
-        <v>2769</v>
+        <v>1911</v>
       </c>
       <c r="W14">
         <v>0</v>
@@ -6852,28 +6846,28 @@
         <v>157</v>
       </c>
       <c r="AN14">
-        <v>195.21</v>
+        <v>188.75</v>
       </c>
       <c r="AO14">
-        <v>1285.88</v>
+        <v>1842.85</v>
       </c>
       <c r="AP14">
-        <v>1324.8</v>
+        <v>1968</v>
       </c>
       <c r="AQ14">
-        <v>1389.0999755859375</v>
+        <v>2027.300048828125</v>
       </c>
       <c r="AR14">
-        <v>1270.5608205128772</v>
+        <v>1900.2560938383647</v>
       </c>
       <c r="AS14" t="s">
         <v>158</v>
       </c>
       <c r="AT14">
-        <v>6221.02</v>
+        <v>7494.55</v>
       </c>
       <c r="AU14">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="AV14">
         <v>0</v>
@@ -6918,7 +6912,7 @@
         <v>157</v>
       </c>
       <c r="BJ14" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="BK14" t="s">
         <v>157</v>
@@ -6957,10 +6951,10 @@
         <v>164</v>
       </c>
       <c r="BW14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BY14" t="s">
         <v>229</v>
@@ -6999,13 +6993,13 @@
         <v>192</v>
       </c>
       <c r="CK14" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="CL14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="CM14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="CN14" t="s">
         <v>278</v>
@@ -7023,13 +7017,13 @@
         <v>29</v>
       </c>
       <c r="CS14">
-        <v>0.72</v>
+        <v>0.55</v>
       </c>
       <c r="CT14">
-        <v>4.06</v>
+        <v>2.56</v>
       </c>
       <c r="CU14">
-        <v>11.77</v>
+        <v>6.47</v>
       </c>
       <c r="CV14" t="s">
         <v>29</v>
@@ -7050,19 +7044,19 @@
         <v>157</v>
       </c>
       <c r="DB14" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="DC14">
-        <v>1303.2</v>
+        <v>1957</v>
       </c>
       <c r="DD14">
-        <v>1303.2</v>
+        <v>1957</v>
       </c>
       <c r="DE14">
-        <v>1303.2</v>
+        <v>1957</v>
       </c>
       <c r="DF14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="DG14" t="s">
         <v>157</v>
@@ -7076,13 +7070,13 @@
         <v>270</v>
       </c>
       <c r="C15" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="D15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F15" t="s">
         <v>153</v>
@@ -7100,40 +7094,40 @@
         <v>49</v>
       </c>
       <c r="K15">
-        <v>811</v>
+        <v>1373.5</v>
       </c>
       <c r="L15">
-        <v>811</v>
+        <v>1373.5</v>
       </c>
       <c r="M15" t="s">
         <v>156</v>
       </c>
       <c r="N15">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="O15">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="P15">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="Q15">
-        <v>96509</v>
+        <v>97518.5</v>
       </c>
       <c r="R15">
-        <v>98889</v>
+        <v>100287.5</v>
       </c>
       <c r="S15">
-        <v>831</v>
+        <v>1412.5</v>
       </c>
       <c r="T15" s="3">
-        <v>2380</v>
+        <v>2769</v>
       </c>
       <c r="U15">
-        <v>2.47</v>
+        <v>2.84</v>
       </c>
       <c r="V15">
-        <v>2380</v>
+        <v>2769</v>
       </c>
       <c r="W15">
         <v>0</v>
@@ -7187,28 +7181,28 @@
         <v>157</v>
       </c>
       <c r="AN15">
-        <v>210.49</v>
+        <v>195.21</v>
       </c>
       <c r="AO15">
-        <v>771.79</v>
+        <v>1285.88</v>
       </c>
       <c r="AP15">
-        <v>771.79</v>
+        <v>1324.8</v>
       </c>
       <c r="AQ15">
-        <v>809.9500122070312</v>
+        <v>1389.0999755859375</v>
       </c>
       <c r="AR15">
-        <v>695.4346801872446</v>
+        <v>1270.5608205128772</v>
       </c>
       <c r="AS15" t="s">
         <v>158</v>
       </c>
       <c r="AT15">
-        <v>4665.99</v>
+        <v>6221.02</v>
       </c>
       <c r="AU15">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="AV15">
         <v>0</v>
@@ -7253,7 +7247,7 @@
         <v>157</v>
       </c>
       <c r="BJ15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="BK15" t="s">
         <v>157</v>
@@ -7295,7 +7289,7 @@
         <v>13</v>
       </c>
       <c r="BX15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY15" t="s">
         <v>229</v>
@@ -7334,13 +7328,13 @@
         <v>192</v>
       </c>
       <c r="CK15" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="CL15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="CM15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="CN15" t="s">
         <v>278</v>
@@ -7358,13 +7352,13 @@
         <v>29</v>
       </c>
       <c r="CS15">
-        <v>1.22</v>
+        <v>0.72</v>
       </c>
       <c r="CT15">
-        <v>4.91</v>
+        <v>4.06</v>
       </c>
       <c r="CU15">
-        <v>15.81</v>
+        <v>11.77</v>
       </c>
       <c r="CV15" t="s">
         <v>29</v>
@@ -7388,18 +7382,353 @@
         <v>199</v>
       </c>
       <c r="DC15">
+        <v>1303.2</v>
+      </c>
+      <c r="DD15">
+        <v>1303.2</v>
+      </c>
+      <c r="DE15">
+        <v>1303.2</v>
+      </c>
+      <c r="DF15" t="s">
+        <v>312</v>
+      </c>
+      <c r="DG15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>270</v>
+      </c>
+      <c r="C16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" t="s">
+        <v>313</v>
+      </c>
+      <c r="E16" t="s">
+        <v>313</v>
+      </c>
+      <c r="F16" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" t="s">
+        <v>272</v>
+      </c>
+      <c r="H16" t="s">
+        <v>227</v>
+      </c>
+      <c r="I16" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16">
+        <v>811</v>
+      </c>
+      <c r="L16">
+        <v>811</v>
+      </c>
+      <c r="M16" t="s">
+        <v>156</v>
+      </c>
+      <c r="N16">
+        <v>119</v>
+      </c>
+      <c r="O16">
+        <v>119</v>
+      </c>
+      <c r="P16">
+        <v>119</v>
+      </c>
+      <c r="Q16">
+        <v>96509</v>
+      </c>
+      <c r="R16">
+        <v>98889</v>
+      </c>
+      <c r="S16">
+        <v>831</v>
+      </c>
+      <c r="T16" s="3">
+        <v>2380</v>
+      </c>
+      <c r="U16">
+        <v>2.47</v>
+      </c>
+      <c r="V16">
+        <v>2380</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>157</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>157</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>157</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>157</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>157</v>
+      </c>
+      <c r="AN16">
+        <v>210.49</v>
+      </c>
+      <c r="AO16">
+        <v>771.79</v>
+      </c>
+      <c r="AP16">
+        <v>771.79</v>
+      </c>
+      <c r="AQ16">
+        <v>809.9500122070312</v>
+      </c>
+      <c r="AR16">
+        <v>695.4346801872446</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>158</v>
+      </c>
+      <c r="AT16">
+        <v>4665.99</v>
+      </c>
+      <c r="AU16">
+        <v>0.51</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>29</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>157</v>
+      </c>
+      <c r="AY16" t="s">
+        <v>157</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BB16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BJ16" t="s">
+        <v>314</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BL16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BN16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BO16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BP16" t="s">
+        <v>160</v>
+      </c>
+      <c r="BQ16" t="s">
+        <v>161</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BT16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BU16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BV16" t="s">
+        <v>164</v>
+      </c>
+      <c r="BW16">
+        <v>13</v>
+      </c>
+      <c r="BX16">
+        <v>3</v>
+      </c>
+      <c r="BY16" t="s">
+        <v>229</v>
+      </c>
+      <c r="BZ16" t="s">
+        <v>157</v>
+      </c>
+      <c r="CA16" t="s">
+        <v>157</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>157</v>
+      </c>
+      <c r="CC16" t="s">
+        <v>29</v>
+      </c>
+      <c r="CD16" t="s">
+        <v>157</v>
+      </c>
+      <c r="CE16" t="s">
+        <v>157</v>
+      </c>
+      <c r="CF16" t="s">
+        <v>157</v>
+      </c>
+      <c r="CG16" t="s">
+        <v>169</v>
+      </c>
+      <c r="CH16" t="s">
+        <v>170</v>
+      </c>
+      <c r="CI16" t="s">
+        <v>171</v>
+      </c>
+      <c r="CJ16" t="s">
+        <v>192</v>
+      </c>
+      <c r="CK16" t="s">
+        <v>293</v>
+      </c>
+      <c r="CL16" t="s">
+        <v>315</v>
+      </c>
+      <c r="CM16" t="s">
+        <v>316</v>
+      </c>
+      <c r="CN16" t="s">
+        <v>278</v>
+      </c>
+      <c r="CO16" t="s">
+        <v>279</v>
+      </c>
+      <c r="CP16" t="s">
+        <v>280</v>
+      </c>
+      <c r="CQ16" t="s">
+        <v>179</v>
+      </c>
+      <c r="CR16" t="s">
+        <v>29</v>
+      </c>
+      <c r="CS16">
+        <v>1.22</v>
+      </c>
+      <c r="CT16">
+        <v>4.91</v>
+      </c>
+      <c r="CU16">
+        <v>15.81</v>
+      </c>
+      <c r="CV16" t="s">
+        <v>29</v>
+      </c>
+      <c r="CW16" t="s">
+        <v>157</v>
+      </c>
+      <c r="CX16" t="s">
+        <v>157</v>
+      </c>
+      <c r="CY16" t="s">
+        <v>157</v>
+      </c>
+      <c r="CZ16" t="s">
+        <v>157</v>
+      </c>
+      <c r="DA16" t="s">
+        <v>157</v>
+      </c>
+      <c r="DB16" t="s">
+        <v>199</v>
+      </c>
+      <c r="DC16">
         <v>770</v>
       </c>
-      <c r="DD15">
+      <c r="DD16">
         <v>770</v>
       </c>
-      <c r="DE15">
+      <c r="DE16">
         <v>721.4</v>
       </c>
-      <c r="DF15" t="s">
-        <v>311</v>
-      </c>
-      <c r="DG15" t="s">
+      <c r="DF16" t="s">
+        <v>317</v>
+      </c>
+      <c r="DG16" t="s">
         <v>157</v>
       </c>
     </row>
@@ -7412,7 +7741,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DG2"/>
+  <dimension ref="A1:DG1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -7837,341 +8166,6 @@
       </c>
       <c r="DG1" s="1" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="2" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F2" t="s">
-        <v>313</v>
-      </c>
-      <c r="G2" t="s">
-        <v>272</v>
-      </c>
-      <c r="H2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K2">
-        <v>2986</v>
-      </c>
-      <c r="L2">
-        <v>2986</v>
-      </c>
-      <c r="M2" t="s">
-        <v>156</v>
-      </c>
-      <c r="N2">
-        <v>17</v>
-      </c>
-      <c r="O2">
-        <v>33</v>
-      </c>
-      <c r="P2">
-        <v>33</v>
-      </c>
-      <c r="Q2">
-        <v>50762</v>
-      </c>
-      <c r="R2">
-        <v>48682.9</v>
-      </c>
-      <c r="S2">
-        <v>2863.7</v>
-      </c>
-      <c r="T2" s="2">
-        <v>-2079.1</v>
-      </c>
-      <c r="U2">
-        <v>-4.1</v>
-      </c>
-      <c r="V2">
-        <v>-2079.1</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>314</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AG2">
-        <v>54.4</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AN2">
-        <v>92.61</v>
-      </c>
-      <c r="AO2">
-        <v>2728.17</v>
-      </c>
-      <c r="AP2">
-        <v>2882.7</v>
-      </c>
-      <c r="AQ2">
-        <v>2983.199951171875</v>
-      </c>
-      <c r="AR2">
-        <v>2827.406442040053</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>158</v>
-      </c>
-      <c r="AT2">
-        <v>8508.39</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BD2">
-        <v>1</v>
-      </c>
-      <c r="BE2">
-        <v>54.4</v>
-      </c>
-      <c r="BF2">
-        <v>54.4</v>
-      </c>
-      <c r="BG2">
-        <v>0</v>
-      </c>
-      <c r="BH2">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>315</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>316</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>317</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>318</v>
-      </c>
-      <c r="BR2">
-        <v>2</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>164</v>
-      </c>
-      <c r="BW2">
-        <v>12</v>
-      </c>
-      <c r="BX2">
-        <v>3</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>229</v>
-      </c>
-      <c r="BZ2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CA2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CB2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CC2" t="s">
-        <v>29</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>169</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>170</v>
-      </c>
-      <c r="CI2" t="s">
-        <v>171</v>
-      </c>
-      <c r="CJ2" t="s">
-        <v>192</v>
-      </c>
-      <c r="CK2" t="s">
-        <v>303</v>
-      </c>
-      <c r="CL2" t="s">
-        <v>319</v>
-      </c>
-      <c r="CM2" t="s">
-        <v>320</v>
-      </c>
-      <c r="CN2" t="s">
-        <v>278</v>
-      </c>
-      <c r="CO2" t="s">
-        <v>279</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>280</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>179</v>
-      </c>
-      <c r="CR2" t="s">
-        <v>29</v>
-      </c>
-      <c r="CS2">
-        <v>1.21</v>
-      </c>
-      <c r="CT2">
-        <v>3.14</v>
-      </c>
-      <c r="CU2">
-        <v>6.77</v>
-      </c>
-      <c r="CV2" t="s">
-        <v>29</v>
-      </c>
-      <c r="CW2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CX2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CY2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>157</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>157</v>
-      </c>
-      <c r="DB2" t="s">
-        <v>223</v>
-      </c>
-      <c r="DC2">
-        <v>2903.2</v>
-      </c>
-      <c r="DD2">
-        <v>2903.2</v>
-      </c>
-      <c r="DE2">
-        <v>2903.2</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>321</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -8618,16 +8612,16 @@
         <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="G2" t="s">
         <v>227</v>
@@ -8639,7 +8633,7 @@
         <v>49</v>
       </c>
       <c r="J2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="K2">
         <v>19.59</v>
@@ -8648,7 +8642,7 @@
         <v>19.59</v>
       </c>
       <c r="M2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N2">
         <v>16</v>
@@ -8723,7 +8717,7 @@
         <v>2</v>
       </c>
       <c r="AL2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AM2">
         <v>168.93</v>
@@ -8744,7 +8738,7 @@
         <v>157</v>
       </c>
       <c r="AS2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AT2">
         <v>17.98</v>
@@ -8795,10 +8789,10 @@
         <v>157</v>
       </c>
       <c r="BJ2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="BK2" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="BL2" t="s">
         <v>157</v>
@@ -8813,10 +8807,10 @@
         <v>157</v>
       </c>
       <c r="BP2" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="BQ2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="BR2">
         <v>1</v>
@@ -8879,13 +8873,13 @@
         <v>193</v>
       </c>
       <c r="CL2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="CM2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="CN2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="CO2" t="s">
         <v>177</v>
@@ -8927,7 +8921,7 @@
         <v>0.76</v>
       </c>
       <c r="DB2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="DC2">
         <v>20</v>
@@ -8939,10 +8933,10 @@
         <v>19.01</v>
       </c>
       <c r="DF2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="DG2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -9386,25 +9380,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
         <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>312</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>312</v>
+        <v>152</v>
       </c>
       <c r="F2" t="s">
-        <v>313</v>
+        <v>153</v>
       </c>
       <c r="G2" t="s">
-        <v>272</v>
+        <v>154</v>
       </c>
       <c r="H2" t="s">
-        <v>227</v>
+        <v>155</v>
       </c>
       <c r="I2" t="s">
         <v>49</v>
@@ -9413,40 +9407,40 @@
         <v>49</v>
       </c>
       <c r="K2">
-        <v>2986</v>
+        <v>921.25</v>
       </c>
       <c r="L2">
-        <v>2986</v>
+        <v>921.25</v>
       </c>
       <c r="M2" t="s">
         <v>156</v>
       </c>
       <c r="N2">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="O2">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="P2">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="Q2">
-        <v>50762</v>
+        <v>99495</v>
       </c>
       <c r="R2">
-        <v>48682.9</v>
+        <v>96870.6</v>
       </c>
       <c r="S2">
-        <v>2863.7</v>
+        <v>896.95</v>
       </c>
       <c r="T2" s="2">
-        <v>-2079.1</v>
+        <v>-2624.4</v>
       </c>
       <c r="U2">
-        <v>-4.1</v>
+        <v>-2.64</v>
       </c>
       <c r="V2">
-        <v>-2079.1</v>
+        <v>-2624.4</v>
       </c>
       <c r="W2">
         <v>0</v>
@@ -9455,7 +9449,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>314</v>
+        <v>157</v>
       </c>
       <c r="Z2" t="s">
         <v>157</v>
@@ -9479,7 +9473,7 @@
         <v>157</v>
       </c>
       <c r="AG2">
-        <v>54.4</v>
+        <v>0</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -9496,32 +9490,32 @@
       <c r="AL2" t="s">
         <v>49</v>
       </c>
-      <c r="AM2" t="s">
-        <v>157</v>
+      <c r="AM2">
+        <v>213.48</v>
       </c>
       <c r="AN2">
-        <v>92.61</v>
+        <v>208.42</v>
       </c>
       <c r="AO2">
-        <v>2728.17</v>
+        <v>847.55</v>
       </c>
       <c r="AP2">
-        <v>2882.7</v>
+        <v>847.55</v>
       </c>
       <c r="AQ2">
-        <v>2983.199951171875</v>
+        <v>824.5</v>
       </c>
       <c r="AR2">
-        <v>2827.406442040053</v>
+        <v>739.8475000366074</v>
       </c>
       <c r="AS2" t="s">
         <v>158</v>
       </c>
       <c r="AT2">
-        <v>8508.39</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>157</v>
+        <v>7959.6</v>
+      </c>
+      <c r="AU2">
+        <v>-0.33</v>
       </c>
       <c r="AV2">
         <v>0</v>
@@ -9548,13 +9542,13 @@
         <v>157</v>
       </c>
       <c r="BD2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE2">
-        <v>54.4</v>
+        <v>0</v>
       </c>
       <c r="BF2">
-        <v>54.4</v>
+        <v>0</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -9566,10 +9560,10 @@
         <v>157</v>
       </c>
       <c r="BJ2" t="s">
-        <v>315</v>
+        <v>159</v>
       </c>
       <c r="BK2" t="s">
-        <v>316</v>
+        <v>157</v>
       </c>
       <c r="BL2" t="s">
         <v>157</v>
@@ -9584,37 +9578,37 @@
         <v>157</v>
       </c>
       <c r="BP2" t="s">
-        <v>317</v>
+        <v>160</v>
       </c>
       <c r="BQ2" t="s">
-        <v>318</v>
+        <v>161</v>
       </c>
       <c r="BR2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="s">
         <v>157</v>
       </c>
       <c r="BT2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="BU2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="BV2" t="s">
         <v>164</v>
       </c>
       <c r="BW2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BX2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY2" t="s">
-        <v>229</v>
+        <v>165</v>
       </c>
       <c r="BZ2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="CA2" t="s">
         <v>157</v>
@@ -9626,13 +9620,13 @@
         <v>29</v>
       </c>
       <c r="CD2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="CE2" t="s">
         <v>157</v>
       </c>
       <c r="CF2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="CG2" t="s">
         <v>169</v>
@@ -9644,76 +9638,76 @@
         <v>171</v>
       </c>
       <c r="CJ2" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="CK2" t="s">
-        <v>303</v>
+        <v>173</v>
       </c>
       <c r="CL2" t="s">
-        <v>319</v>
+        <v>174</v>
       </c>
       <c r="CM2" t="s">
-        <v>320</v>
+        <v>175</v>
       </c>
       <c r="CN2" t="s">
-        <v>278</v>
+        <v>176</v>
       </c>
       <c r="CO2" t="s">
-        <v>279</v>
+        <v>177</v>
       </c>
       <c r="CP2" t="s">
-        <v>280</v>
+        <v>178</v>
       </c>
       <c r="CQ2" t="s">
         <v>179</v>
       </c>
       <c r="CR2" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="CS2">
-        <v>1.21</v>
+        <v>3.69</v>
       </c>
       <c r="CT2">
-        <v>3.14</v>
+        <v>5.2</v>
       </c>
       <c r="CU2">
-        <v>6.77</v>
+        <v>16.27</v>
       </c>
       <c r="CV2" t="s">
         <v>29</v>
       </c>
-      <c r="CW2" t="s">
-        <v>157</v>
+      <c r="CW2">
+        <v>0</v>
       </c>
       <c r="CX2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CY2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>157</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>157</v>
+        <v>180</v>
+      </c>
+      <c r="CY2">
+        <v>1.6</v>
+      </c>
+      <c r="CZ2">
+        <v>0.6</v>
+      </c>
+      <c r="DA2">
+        <v>3.69</v>
       </c>
       <c r="DB2" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="DC2">
-        <v>2903.2</v>
+        <v>822.4</v>
       </c>
       <c r="DD2">
-        <v>2903.2</v>
+        <v>800.6</v>
       </c>
       <c r="DE2">
-        <v>2903.2</v>
+        <v>794</v>
       </c>
       <c r="DF2" t="s">
-        <v>321</v>
+        <v>182</v>
       </c>
       <c r="DG2" t="s">
-        <v>322</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:111" x14ac:dyDescent="0.25">
@@ -9724,22 +9718,22 @@
         <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="E3" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="F3" t="s">
         <v>153</v>
       </c>
       <c r="G3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H3" t="s">
         <v>154</v>
-      </c>
-      <c r="H3" t="s">
-        <v>155</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
@@ -9748,40 +9742,40 @@
         <v>49</v>
       </c>
       <c r="K3">
-        <v>921.25</v>
+        <v>853</v>
       </c>
       <c r="L3">
-        <v>921.25</v>
+        <v>853</v>
       </c>
       <c r="M3" t="s">
         <v>156</v>
       </c>
       <c r="N3">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="O3">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="Q3">
-        <v>99495</v>
+        <v>58004</v>
       </c>
       <c r="R3">
-        <v>96870.6</v>
+        <v>55902.8</v>
       </c>
       <c r="S3">
-        <v>896.95</v>
+        <v>822.1</v>
       </c>
       <c r="T3" s="2">
-        <v>-2624.4</v>
+        <v>-2101.2</v>
       </c>
       <c r="U3">
-        <v>-2.64</v>
+        <v>-3.62</v>
       </c>
       <c r="V3">
-        <v>-2624.4</v>
+        <v>-2101.2</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -9832,31 +9826,31 @@
         <v>49</v>
       </c>
       <c r="AM3">
-        <v>213.48</v>
+        <v>191.09</v>
       </c>
       <c r="AN3">
-        <v>208.42</v>
+        <v>132.68</v>
       </c>
       <c r="AO3">
-        <v>847.55</v>
+        <v>805.6</v>
       </c>
       <c r="AP3">
-        <v>847.55</v>
+        <v>805.6</v>
       </c>
       <c r="AQ3">
-        <v>824.5</v>
+        <v>833.5499877929688</v>
       </c>
       <c r="AR3">
-        <v>739.8475000366074</v>
+        <v>734.9542954011073</v>
       </c>
       <c r="AS3" t="s">
         <v>158</v>
       </c>
       <c r="AT3">
-        <v>7959.6</v>
+        <v>3223.2</v>
       </c>
       <c r="AU3">
-        <v>-0.33</v>
+        <v>-0.65</v>
       </c>
       <c r="AV3">
         <v>0</v>
@@ -9901,7 +9895,7 @@
         <v>157</v>
       </c>
       <c r="BJ3" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="BK3" t="s">
         <v>157</v>
@@ -9922,7 +9916,7 @@
         <v>160</v>
       </c>
       <c r="BQ3" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="BR3">
         <v>0</v>
@@ -9934,13 +9928,13 @@
         <v>162</v>
       </c>
       <c r="BU3" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="BV3" t="s">
         <v>164</v>
       </c>
       <c r="BW3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="BX3">
         <v>4</v>
@@ -9949,13 +9943,13 @@
         <v>165</v>
       </c>
       <c r="BZ3" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="CA3" t="s">
         <v>157</v>
       </c>
       <c r="CB3" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="CC3" t="s">
         <v>29</v>
@@ -9979,73 +9973,73 @@
         <v>171</v>
       </c>
       <c r="CJ3" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="CK3" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="CL3" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="CM3" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="CN3" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="CO3" t="s">
         <v>177</v>
       </c>
       <c r="CP3" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="CQ3" t="s">
         <v>179</v>
       </c>
       <c r="CR3" t="s">
-        <v>179</v>
+        <v>29</v>
       </c>
       <c r="CS3">
-        <v>3.69</v>
+        <v>0.21</v>
       </c>
       <c r="CT3">
-        <v>5.2</v>
+        <v>4.11</v>
       </c>
       <c r="CU3">
-        <v>16.27</v>
+        <v>8.7</v>
       </c>
       <c r="CV3" t="s">
         <v>29</v>
       </c>
       <c r="CW3">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="CX3" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="CY3">
-        <v>1.6</v>
+        <v>8.7</v>
       </c>
       <c r="CZ3">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="DA3">
-        <v>3.69</v>
+        <v>0.21</v>
       </c>
       <c r="DB3" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="DC3">
-        <v>822.4</v>
+        <v>805.6</v>
       </c>
       <c r="DD3">
-        <v>800.6</v>
+        <v>805.6</v>
       </c>
       <c r="DE3">
-        <v>794</v>
+        <v>805.6</v>
       </c>
       <c r="DF3" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="DG3" t="s">
         <v>157</v>
@@ -10062,10 +10056,10 @@
         <v>183</v>
       </c>
       <c r="D4" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="F4" t="s">
         <v>153</v>
@@ -10083,40 +10077,40 @@
         <v>49</v>
       </c>
       <c r="K4">
-        <v>853</v>
+        <v>649.15</v>
       </c>
       <c r="L4">
-        <v>853</v>
+        <v>649.15</v>
       </c>
       <c r="M4" t="s">
         <v>156</v>
       </c>
       <c r="N4">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="P4">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="Q4">
-        <v>58004</v>
+        <v>72704.8</v>
       </c>
       <c r="R4">
-        <v>55902.8</v>
+        <v>70375.2</v>
       </c>
       <c r="S4">
-        <v>822.1</v>
+        <v>628.35</v>
       </c>
       <c r="T4" s="2">
-        <v>-2101.2</v>
+        <v>-2329.6</v>
       </c>
       <c r="U4">
-        <v>-3.62</v>
+        <v>-3.2</v>
       </c>
       <c r="V4">
-        <v>-2101.2</v>
+        <v>-2329.6</v>
       </c>
       <c r="W4">
         <v>0</v>
@@ -10167,31 +10161,31 @@
         <v>49</v>
       </c>
       <c r="AM4">
-        <v>191.09</v>
+        <v>195.78</v>
       </c>
       <c r="AN4">
-        <v>132.68</v>
+        <v>190</v>
       </c>
       <c r="AO4">
-        <v>805.6</v>
+        <v>597.22</v>
       </c>
       <c r="AP4">
-        <v>805.6</v>
+        <v>597.22</v>
       </c>
       <c r="AQ4">
-        <v>833.5499877929688</v>
+        <v>558.75</v>
       </c>
       <c r="AR4">
-        <v>734.9542954011073</v>
+        <v>521.6262350180588</v>
       </c>
       <c r="AS4" t="s">
         <v>158</v>
       </c>
       <c r="AT4">
-        <v>3223.2</v>
+        <v>5816.16</v>
       </c>
       <c r="AU4">
-        <v>-0.65</v>
+        <v>-0.4</v>
       </c>
       <c r="AV4">
         <v>0</v>
@@ -10236,7 +10230,7 @@
         <v>157</v>
       </c>
       <c r="BJ4" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="BK4" t="s">
         <v>157</v>
@@ -10257,7 +10251,7 @@
         <v>160</v>
       </c>
       <c r="BQ4" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="BR4">
         <v>0</v>
@@ -10269,28 +10263,28 @@
         <v>162</v>
       </c>
       <c r="BU4" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="BV4" t="s">
         <v>164</v>
       </c>
       <c r="BW4">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BX4">
         <v>4</v>
       </c>
       <c r="BY4" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="BZ4" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="CA4" t="s">
         <v>157</v>
       </c>
       <c r="CB4" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="CC4" t="s">
         <v>29</v>
@@ -10314,16 +10308,16 @@
         <v>171</v>
       </c>
       <c r="CJ4" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="CK4" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="CL4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="CM4" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="CN4" t="s">
         <v>196</v>
@@ -10332,55 +10326,55 @@
         <v>177</v>
       </c>
       <c r="CP4" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="CQ4" t="s">
         <v>179</v>
       </c>
       <c r="CR4" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="CS4">
-        <v>0.21</v>
+        <v>90.28</v>
       </c>
       <c r="CT4">
-        <v>4.11</v>
+        <v>3.77</v>
       </c>
       <c r="CU4">
-        <v>8.7</v>
+        <v>16.2</v>
       </c>
       <c r="CV4" t="s">
         <v>29</v>
       </c>
       <c r="CW4">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="CX4" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="CY4">
-        <v>8.7</v>
+        <v>15.12</v>
       </c>
       <c r="CZ4">
-        <v>0.33</v>
+        <v>1.31</v>
       </c>
       <c r="DA4">
-        <v>0.21</v>
+        <v>90.28</v>
       </c>
       <c r="DB4" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="DC4">
-        <v>805.6</v>
+        <v>556.8</v>
       </c>
       <c r="DD4">
-        <v>805.6</v>
+        <v>549</v>
       </c>
       <c r="DE4">
-        <v>805.6</v>
+        <v>536</v>
       </c>
       <c r="DF4" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="DG4" t="s">
         <v>157</v>
@@ -10394,13 +10388,13 @@
         <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="D5" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="E5" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="F5" t="s">
         <v>153</v>
@@ -10418,40 +10412,40 @@
         <v>49</v>
       </c>
       <c r="K5">
-        <v>649.15</v>
+        <v>88.49</v>
       </c>
       <c r="L5">
-        <v>649.15</v>
+        <v>88.49</v>
       </c>
       <c r="M5" t="s">
         <v>156</v>
       </c>
       <c r="N5">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>72704.8</v>
+        <v>442.45</v>
       </c>
       <c r="R5">
-        <v>70375.2</v>
+        <v>433.6</v>
       </c>
       <c r="S5">
-        <v>628.35</v>
+        <v>86.72</v>
       </c>
       <c r="T5" s="2">
-        <v>-2329.6</v>
+        <v>-8.85</v>
       </c>
       <c r="U5">
-        <v>-3.2</v>
+        <v>-2</v>
       </c>
       <c r="V5">
-        <v>-2329.6</v>
+        <v>-8.85</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -10502,31 +10496,31 @@
         <v>49</v>
       </c>
       <c r="AM5">
-        <v>195.78</v>
+        <v>176.28</v>
       </c>
       <c r="AN5">
-        <v>190</v>
+        <v>176.51</v>
       </c>
       <c r="AO5">
-        <v>597.22</v>
+        <v>84.5</v>
       </c>
       <c r="AP5">
-        <v>597.22</v>
+        <v>84.65</v>
       </c>
       <c r="AQ5">
-        <v>558.75</v>
+        <v>86.51000213623047</v>
       </c>
       <c r="AR5">
-        <v>521.6262350180588</v>
+        <v>82.89704133721075</v>
       </c>
       <c r="AS5" t="s">
         <v>158</v>
       </c>
       <c r="AT5">
-        <v>5816.16</v>
+        <v>19.95</v>
       </c>
       <c r="AU5">
-        <v>-0.4</v>
+        <v>-0.44</v>
       </c>
       <c r="AV5">
         <v>0</v>
@@ -10571,7 +10565,7 @@
         <v>157</v>
       </c>
       <c r="BJ5" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="BK5" t="s">
         <v>157</v>
@@ -10592,7 +10586,7 @@
         <v>160</v>
       </c>
       <c r="BQ5" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="BR5">
         <v>0</v>
@@ -10604,16 +10598,16 @@
         <v>162</v>
       </c>
       <c r="BU5" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="BV5" t="s">
         <v>164</v>
       </c>
       <c r="BW5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BX5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BY5" t="s">
         <v>205</v>
@@ -10622,10 +10616,10 @@
         <v>166</v>
       </c>
       <c r="CA5" t="s">
-        <v>157</v>
+        <v>217</v>
       </c>
       <c r="CB5" t="s">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="CC5" t="s">
         <v>29</v>
@@ -10652,70 +10646,70 @@
         <v>206</v>
       </c>
       <c r="CK5" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="CL5" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="CM5" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="CN5" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="CO5" t="s">
         <v>177</v>
       </c>
       <c r="CP5" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="CQ5" t="s">
         <v>179</v>
       </c>
       <c r="CR5" t="s">
-        <v>179</v>
+        <v>29</v>
       </c>
       <c r="CS5">
-        <v>90.28</v>
+        <v>2.77</v>
       </c>
       <c r="CT5">
-        <v>3.77</v>
+        <v>2.54</v>
       </c>
       <c r="CU5">
-        <v>16.2</v>
+        <v>7.97</v>
       </c>
       <c r="CV5" t="s">
         <v>29</v>
       </c>
       <c r="CW5">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="CX5" t="s">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="CY5">
-        <v>15.12</v>
+        <v>1.91</v>
       </c>
       <c r="CZ5">
-        <v>1.31</v>
+        <v>0.4</v>
       </c>
       <c r="DA5">
-        <v>90.28</v>
+        <v>2.77</v>
       </c>
       <c r="DB5" t="s">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="DC5">
-        <v>556.8</v>
+        <v>85.99</v>
       </c>
       <c r="DD5">
-        <v>549</v>
+        <v>84.5</v>
       </c>
       <c r="DE5">
-        <v>536</v>
+        <v>84.44</v>
       </c>
       <c r="DF5" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="DG5" t="s">
         <v>157</v>
@@ -10729,22 +10723,22 @@
         <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="D6" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="E6" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="F6" t="s">
         <v>153</v>
       </c>
       <c r="G6" t="s">
+        <v>227</v>
+      </c>
+      <c r="H6" t="s">
         <v>186</v>
-      </c>
-      <c r="H6" t="s">
-        <v>154</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
@@ -10753,40 +10747,40 @@
         <v>49</v>
       </c>
       <c r="K6">
-        <v>88.49</v>
+        <v>2048.2</v>
       </c>
       <c r="L6">
-        <v>88.49</v>
+        <v>2048.2</v>
       </c>
       <c r="M6" t="s">
         <v>156</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="P6">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="Q6">
-        <v>442.45</v>
+        <v>14337.4</v>
       </c>
       <c r="R6">
-        <v>433.6</v>
+        <v>16676.1</v>
       </c>
       <c r="S6">
-        <v>86.72</v>
-      </c>
-      <c r="T6" s="2">
-        <v>-8.85</v>
+        <v>2382.3</v>
+      </c>
+      <c r="T6" s="3">
+        <v>2338.7</v>
       </c>
       <c r="U6">
-        <v>-2</v>
+        <v>16.31</v>
       </c>
       <c r="V6">
-        <v>-8.85</v>
+        <v>2338.7</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -10819,7 +10813,7 @@
         <v>157</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>-1561.2</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -10837,31 +10831,31 @@
         <v>49</v>
       </c>
       <c r="AM6">
-        <v>176.28</v>
+        <v>170.76</v>
       </c>
       <c r="AN6">
-        <v>176.51</v>
+        <v>209.7</v>
       </c>
       <c r="AO6">
-        <v>84.5</v>
+        <v>1974.43</v>
       </c>
       <c r="AP6">
-        <v>84.65</v>
+        <v>2014.24</v>
       </c>
       <c r="AQ6">
-        <v>86.51000213623047</v>
+        <v>2058.60009765625</v>
       </c>
       <c r="AR6">
-        <v>82.89704133721075</v>
+        <v>1919.3071735958158</v>
       </c>
       <c r="AS6" t="s">
         <v>158</v>
       </c>
       <c r="AT6">
-        <v>19.95</v>
+        <v>3614.73</v>
       </c>
       <c r="AU6">
-        <v>-0.44</v>
+        <v>4.53</v>
       </c>
       <c r="AV6">
         <v>0</v>
@@ -10888,13 +10882,13 @@
         <v>157</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>-1561.2</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>-1561.2</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -10906,7 +10900,7 @@
         <v>157</v>
       </c>
       <c r="BJ6" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="BK6" t="s">
         <v>157</v>
@@ -10936,43 +10930,43 @@
         <v>157</v>
       </c>
       <c r="BT6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="BU6" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="BV6" t="s">
         <v>164</v>
       </c>
       <c r="BW6">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BX6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BY6" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="BZ6" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="CA6" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="CB6" t="s">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="CC6" t="s">
         <v>29</v>
       </c>
       <c r="CD6" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="CE6" t="s">
-        <v>157</v>
+        <v>232</v>
       </c>
       <c r="CF6" t="s">
-        <v>168</v>
+        <v>233</v>
       </c>
       <c r="CG6" t="s">
         <v>169</v>
@@ -10984,25 +10978,25 @@
         <v>171</v>
       </c>
       <c r="CJ6" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="CK6" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="CL6" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="CM6" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="CN6" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="CO6" t="s">
         <v>177</v>
       </c>
       <c r="CP6" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="CQ6" t="s">
         <v>179</v>
@@ -11011,46 +11005,46 @@
         <v>29</v>
       </c>
       <c r="CS6">
-        <v>2.77</v>
+        <v>0.3</v>
       </c>
       <c r="CT6">
-        <v>2.54</v>
+        <v>3.57</v>
       </c>
       <c r="CU6">
-        <v>7.97</v>
+        <v>2.1</v>
       </c>
       <c r="CV6" t="s">
         <v>29</v>
       </c>
       <c r="CW6">
-        <v>1.87</v>
+        <v>10.28</v>
       </c>
       <c r="CX6" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="CY6">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="CZ6">
-        <v>0.4</v>
+        <v>1.68</v>
       </c>
       <c r="DA6">
-        <v>2.77</v>
+        <v>0.3</v>
       </c>
       <c r="DB6" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="DC6">
-        <v>85.99</v>
+        <v>2002.3</v>
       </c>
       <c r="DD6">
-        <v>84.5</v>
+        <v>1981</v>
       </c>
       <c r="DE6">
-        <v>84.44</v>
+        <v>1981</v>
       </c>
       <c r="DF6" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="DG6" t="s">
         <v>157</v>
@@ -11067,10 +11061,10 @@
         <v>183</v>
       </c>
       <c r="D7" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="E7" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="F7" t="s">
         <v>153</v>
@@ -11088,40 +11082,40 @@
         <v>49</v>
       </c>
       <c r="K7">
-        <v>2048.2</v>
+        <v>4421.9</v>
       </c>
       <c r="L7">
-        <v>2048.2</v>
+        <v>4421.9</v>
       </c>
       <c r="M7" t="s">
         <v>156</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="O7">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="P7">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="Q7">
-        <v>14337.4</v>
+        <v>97281.8</v>
       </c>
       <c r="R7">
-        <v>16676.1</v>
+        <v>102891.8</v>
       </c>
       <c r="S7">
-        <v>2382.3</v>
+        <v>4676.9</v>
       </c>
       <c r="T7" s="3">
-        <v>2338.7</v>
+        <v>5610</v>
       </c>
       <c r="U7">
-        <v>16.31</v>
+        <v>5.77</v>
       </c>
       <c r="V7">
-        <v>2338.7</v>
+        <v>5610</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -11154,7 +11148,7 @@
         <v>157</v>
       </c>
       <c r="AG7">
-        <v>-1561.2</v>
+        <v>0</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -11172,31 +11166,31 @@
         <v>49</v>
       </c>
       <c r="AM7">
-        <v>170.76</v>
+        <v>167.02</v>
       </c>
       <c r="AN7">
-        <v>209.7</v>
+        <v>160.8</v>
       </c>
       <c r="AO7">
-        <v>1974.43</v>
+        <v>4319.5</v>
       </c>
       <c r="AP7">
-        <v>2014.24</v>
+        <v>4352.73</v>
       </c>
       <c r="AQ7">
-        <v>2058.60009765625</v>
+        <v>4452</v>
       </c>
       <c r="AR7">
-        <v>1919.3071735958158</v>
+        <v>4279.016498604705</v>
       </c>
       <c r="AS7" t="s">
         <v>158</v>
       </c>
       <c r="AT7">
-        <v>3614.73</v>
+        <v>2252.8</v>
       </c>
       <c r="AU7">
-        <v>4.53</v>
+        <v>2.49</v>
       </c>
       <c r="AV7">
         <v>0</v>
@@ -11223,13 +11217,13 @@
         <v>157</v>
       </c>
       <c r="BD7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE7">
-        <v>-1561.2</v>
+        <v>0</v>
       </c>
       <c r="BF7">
-        <v>-1561.2</v>
+        <v>0</v>
       </c>
       <c r="BG7">
         <v>0</v>
@@ -11241,7 +11235,7 @@
         <v>157</v>
       </c>
       <c r="BJ7" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="BK7" t="s">
         <v>157</v>
@@ -11274,25 +11268,25 @@
         <v>157</v>
       </c>
       <c r="BU7" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="BV7" t="s">
         <v>164</v>
       </c>
       <c r="BW7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BX7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BY7" t="s">
         <v>229</v>
       </c>
       <c r="BZ7" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="CA7" t="s">
-        <v>231</v>
+        <v>157</v>
       </c>
       <c r="CB7" t="s">
         <v>157</v>
@@ -11304,10 +11298,10 @@
         <v>157</v>
       </c>
       <c r="CE7" t="s">
-        <v>232</v>
+        <v>157</v>
       </c>
       <c r="CF7" t="s">
-        <v>233</v>
+        <v>168</v>
       </c>
       <c r="CG7" t="s">
         <v>169</v>
@@ -11325,10 +11319,10 @@
         <v>234</v>
       </c>
       <c r="CL7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="CM7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="CN7" t="s">
         <v>196</v>
@@ -11346,46 +11340,46 @@
         <v>29</v>
       </c>
       <c r="CS7">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
       <c r="CT7">
-        <v>3.57</v>
+        <v>2.9</v>
       </c>
       <c r="CU7">
-        <v>2.1</v>
+        <v>5.2</v>
       </c>
       <c r="CV7" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="CW7">
-        <v>10.28</v>
+        <v>6.4</v>
       </c>
       <c r="CX7" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="CY7">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="CZ7">
-        <v>1.68</v>
+        <v>0.47</v>
       </c>
       <c r="DA7">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
       <c r="DB7" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="DC7">
-        <v>2002.3</v>
+        <v>4335</v>
       </c>
       <c r="DD7">
-        <v>1981</v>
+        <v>4319.5</v>
       </c>
       <c r="DE7">
-        <v>1981</v>
+        <v>4319.5</v>
       </c>
       <c r="DF7" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="DG7" t="s">
         <v>157</v>
@@ -11402,10 +11396,10 @@
         <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F8" t="s">
         <v>153</v>
@@ -11423,40 +11417,40 @@
         <v>49</v>
       </c>
       <c r="K8">
-        <v>4421.9</v>
+        <v>214.01</v>
       </c>
       <c r="L8">
-        <v>4421.9</v>
+        <v>214.01</v>
       </c>
       <c r="M8" t="s">
         <v>156</v>
       </c>
       <c r="N8">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="O8">
-        <v>22</v>
+        <v>291</v>
       </c>
       <c r="P8">
-        <v>22</v>
+        <v>291</v>
       </c>
       <c r="Q8">
-        <v>97281.8</v>
+        <v>31245.46</v>
       </c>
       <c r="R8">
-        <v>102891.8</v>
+        <v>31191.44</v>
       </c>
       <c r="S8">
-        <v>4676.9</v>
-      </c>
-      <c r="T8" s="3">
-        <v>5610</v>
+        <v>213.64</v>
+      </c>
+      <c r="T8" s="2">
+        <v>-54.02</v>
       </c>
       <c r="U8">
-        <v>5.77</v>
+        <v>-0.17</v>
       </c>
       <c r="V8">
-        <v>5610</v>
+        <v>-54.02</v>
       </c>
       <c r="W8">
         <v>0</v>
@@ -11489,7 +11483,7 @@
         <v>157</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>-867.1</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -11507,31 +11501,31 @@
         <v>49</v>
       </c>
       <c r="AM8">
-        <v>167.02</v>
+        <v>179.24</v>
       </c>
       <c r="AN8">
-        <v>160.8</v>
+        <v>205.65</v>
       </c>
       <c r="AO8">
-        <v>4319.5</v>
+        <v>196.45</v>
       </c>
       <c r="AP8">
-        <v>4352.73</v>
+        <v>199.5</v>
       </c>
       <c r="AQ8">
-        <v>4452</v>
+        <v>207.0500030517578</v>
       </c>
       <c r="AR8">
-        <v>4279.016498604705</v>
+        <v>174.58772588109068</v>
       </c>
       <c r="AS8" t="s">
         <v>158</v>
       </c>
       <c r="AT8">
-        <v>2252.8</v>
+        <v>5109.96</v>
       </c>
       <c r="AU8">
-        <v>2.49</v>
+        <v>-0.02</v>
       </c>
       <c r="AV8">
         <v>0</v>
@@ -11558,13 +11552,13 @@
         <v>157</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>-867.1</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>-867.1</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -11576,7 +11570,7 @@
         <v>157</v>
       </c>
       <c r="BJ8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="BK8" t="s">
         <v>157</v>
@@ -11597,7 +11591,7 @@
         <v>160</v>
       </c>
       <c r="BQ8" t="s">
-        <v>161</v>
+        <v>250</v>
       </c>
       <c r="BR8">
         <v>0</v>
@@ -11609,16 +11603,16 @@
         <v>157</v>
       </c>
       <c r="BU8" t="s">
-        <v>242</v>
+        <v>189</v>
       </c>
       <c r="BV8" t="s">
         <v>164</v>
       </c>
       <c r="BW8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BX8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BY8" t="s">
         <v>229</v>
@@ -11657,13 +11651,13 @@
         <v>192</v>
       </c>
       <c r="CK8" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="CL8" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="CM8" t="s">
-        <v>